--- a/data/dados_atuais.xlsx
+++ b/data/dados_atuais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delgadiadema.sharepoint.com/sites/GestoEstratgica/Documentos Compartilhados/Controle Master/BSW/Novo controle (Em processo)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="675" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01440C8C-64C3-470E-963D-5741F6CE805C}"/>
+  <xr:revisionPtr revIDLastSave="689" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F3BA450-5B28-412E-82C4-E944558592F1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E398004-7492-4AA0-94C2-EA9B761AAA49}"/>
   </bookViews>
@@ -321,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6233" uniqueCount="1406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6243" uniqueCount="1408">
   <si>
     <t>Código
 Bobina Mâe</t>
@@ -4658,6 +4658,24 @@
   <si>
     <t>Produtos com processo de corte laser com reduções significativas no peso bruto unitário. Aumento da quantidade de peças / chapa.
 Em análise a redução do comprimento da chapa, mantendo a quantidade de peças / chapa.</t>
+  </si>
+  <si>
+    <t>DJ000059Z / 060Z</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Redução no passo do blank. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>AGUARDANDO RETORNO DO FORNECEDOR EM RELAÇÃO À MP.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -5407,7 +5425,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.37680005792085014</c:v>
+                  <c:v>0.38521698042732067</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6325,7 +6343,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.24010429823778848</c:v>
+                  <c:v>0.26354378919303767</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6984,7 +7002,7 @@
                   <c:v>885025.4800000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>20671.96</c:v>
+                  <c:v>38173.78</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -7279,7 +7297,7 @@
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>905697.44000000006</c:v>
+                  <c:v>923199.26000000013</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7651,7 +7669,7 @@
                   <c:v>1322.6778035000002</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>392.45735950000005</c:v>
+                  <c:v>430.76987950000006</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -13459,7 +13477,7 @@
       <c r="AL5" s="1"/>
       <c r="AM5" s="1"/>
     </row>
-    <row r="6" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
         <v>39</v>
       </c>
@@ -13753,7 +13771,7 @@
       <c r="AL8" s="1"/>
       <c r="AM8" s="1"/>
     </row>
-    <row r="9" spans="1:39" s="26" customFormat="1" ht="132.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:39" s="26" customFormat="1" ht="132.6" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
         <v>48</v>
       </c>
@@ -14089,7 +14107,7 @@
       <c r="AL11" s="1"/>
       <c r="AM11" s="1"/>
     </row>
-    <row r="12" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
         <v>56</v>
       </c>
@@ -14919,7 +14937,7 @@
       <c r="AL19" s="1"/>
       <c r="AM19" s="1"/>
     </row>
-    <row r="20" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
         <v>61</v>
       </c>
@@ -15027,7 +15045,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="21" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="22" t="s">
         <v>67</v>
       </c>
@@ -15751,7 +15769,7 @@
       <c r="AL27" s="1"/>
       <c r="AM27" s="1"/>
     </row>
-    <row r="28" spans="1:39" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:39" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A28" s="22" t="s">
         <v>72</v>
       </c>
@@ -15861,7 +15879,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="29" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="22" t="s">
         <v>77</v>
       </c>
@@ -16041,7 +16059,7 @@
       <c r="AL30" s="1"/>
       <c r="AM30" s="1"/>
     </row>
-    <row r="31" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>81</v>
       </c>
@@ -16112,28 +16130,48 @@
         <f>AVERAGE(U31:X31)</f>
         <v>38.312520000000006</v>
       </c>
-      <c r="Z31" s="10"/>
-      <c r="AA31" s="10"/>
-      <c r="AB31" s="10"/>
-      <c r="AC31" s="10"/>
-      <c r="AD31" s="10"/>
-      <c r="AE31" s="10"/>
-      <c r="AF31" s="10"/>
+      <c r="Z31" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AA31" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AB31" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AC31" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AD31" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AE31" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AF31" s="10" t="s">
+        <v>693</v>
+      </c>
       <c r="AG31" s="38">
         <f>COUNTIF(Z31:AF31,"X")/7</f>
-        <v>0</v>
-      </c>
-      <c r="AH31" s="51" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH31" s="51">
         <f>IF(AG31=100%,Y31," ")</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="AI31" s="64"/>
-      <c r="AJ31" s="1"/>
+        <v>38.312520000000006</v>
+      </c>
+      <c r="AI31" s="64">
+        <v>2</v>
+      </c>
+      <c r="AJ31" s="1" t="s">
+        <v>1406</v>
+      </c>
       <c r="AK31" s="65">
-        <v>0</v>
+        <v>17501.82</v>
       </c>
       <c r="AL31" s="1"/>
-      <c r="AM31" s="1"/>
+      <c r="AM31" s="1" t="s">
+        <v>1398</v>
+      </c>
     </row>
     <row r="32" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
@@ -16307,7 +16345,7 @@
       <c r="AL33" s="1"/>
       <c r="AM33" s="1"/>
     </row>
-    <row r="34" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
         <v>86</v>
       </c>
@@ -16399,7 +16437,9 @@
         <v>0</v>
       </c>
       <c r="AL34" s="1"/>
-      <c r="AM34" s="1"/>
+      <c r="AM34" s="1" t="s">
+        <v>1407</v>
+      </c>
     </row>
     <row r="35" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="19" t="s">
@@ -16669,7 +16709,7 @@
       <c r="AL37" s="1"/>
       <c r="AM37" s="1"/>
     </row>
-    <row r="38" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="22" t="s">
         <v>89</v>
       </c>
@@ -16939,7 +16979,7 @@
       <c r="AL40" s="1"/>
       <c r="AM40" s="1"/>
     </row>
-    <row r="41" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="22" t="s">
         <v>95</v>
       </c>
@@ -17031,7 +17071,7 @@
       <c r="AL41" s="1"/>
       <c r="AM41" s="1"/>
     </row>
-    <row r="42" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>97</v>
       </c>
@@ -17125,7 +17165,7 @@
       <c r="AL42" s="1"/>
       <c r="AM42" s="1"/>
     </row>
-    <row r="43" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="22" t="s">
         <v>100</v>
       </c>
@@ -17307,7 +17347,7 @@
       <c r="AL44" s="1"/>
       <c r="AM44" s="1"/>
     </row>
-    <row r="45" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="22" t="s">
         <v>103</v>
       </c>
@@ -17401,7 +17441,7 @@
       <c r="AL45" s="1"/>
       <c r="AM45" s="1"/>
     </row>
-    <row r="46" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="22" t="s">
         <v>109</v>
       </c>
@@ -17493,7 +17533,7 @@
       <c r="AL46" s="1"/>
       <c r="AM46" s="1"/>
     </row>
-    <row r="47" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="22" t="s">
         <v>113</v>
       </c>
@@ -17585,7 +17625,7 @@
       <c r="AL47" s="1"/>
       <c r="AM47" s="1"/>
     </row>
-    <row r="48" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="22" t="s">
         <v>117</v>
       </c>
@@ -17855,7 +17895,7 @@
       <c r="AL50" s="1"/>
       <c r="AM50" s="1"/>
     </row>
-    <row r="51" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="22" t="s">
         <v>121</v>
       </c>
@@ -18035,7 +18075,7 @@
       <c r="AL52" s="1"/>
       <c r="AM52" s="1"/>
     </row>
-    <row r="53" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="22" t="s">
         <v>124</v>
       </c>
@@ -18213,7 +18253,7 @@
       <c r="AL54" s="1"/>
       <c r="AM54" s="1"/>
     </row>
-    <row r="55" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="22" t="s">
         <v>126</v>
       </c>
@@ -18395,7 +18435,7 @@
       <c r="AL56" s="1"/>
       <c r="AM56" s="1"/>
     </row>
-    <row r="57" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="22" t="s">
         <v>127</v>
       </c>
@@ -18487,7 +18527,7 @@
       <c r="AL57" s="1"/>
       <c r="AM57" s="1"/>
     </row>
-    <row r="58" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="22" t="s">
         <v>129</v>
       </c>
@@ -18669,7 +18709,7 @@
       <c r="AL59" s="1"/>
       <c r="AM59" s="1"/>
     </row>
-    <row r="60" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A60" s="22" t="s">
         <v>131</v>
       </c>
@@ -18941,7 +18981,7 @@
       <c r="AL62" s="1"/>
       <c r="AM62" s="1"/>
     </row>
-    <row r="63" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="22" t="s">
         <v>134</v>
       </c>
@@ -19211,7 +19251,7 @@
       <c r="AL65" s="1"/>
       <c r="AM65" s="1"/>
     </row>
-    <row r="66" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="22" t="s">
         <v>137</v>
       </c>
@@ -19569,7 +19609,7 @@
       <c r="AL69" s="1"/>
       <c r="AM69" s="1"/>
     </row>
-    <row r="70" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="22" t="s">
         <v>139</v>
       </c>
@@ -19663,7 +19703,7 @@
       <c r="AL70" s="1"/>
       <c r="AM70" s="1"/>
     </row>
-    <row r="71" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="22" t="s">
         <v>140</v>
       </c>
@@ -19755,7 +19795,7 @@
       <c r="AL71" s="1"/>
       <c r="AM71" s="1"/>
     </row>
-    <row r="72" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="22" t="s">
         <v>143</v>
       </c>
@@ -19847,7 +19887,7 @@
       <c r="AL72" s="1"/>
       <c r="AM72" s="1"/>
     </row>
-    <row r="73" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="22" t="s">
         <v>147</v>
       </c>
@@ -20111,7 +20151,7 @@
       <c r="AL75" s="1"/>
       <c r="AM75" s="1"/>
     </row>
-    <row r="76" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="22" t="s">
         <v>151</v>
       </c>
@@ -20295,7 +20335,7 @@
       <c r="AL77" s="1"/>
       <c r="AM77" s="1"/>
     </row>
-    <row r="78" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="22" t="s">
         <v>157</v>
       </c>
@@ -20477,7 +20517,7 @@
       <c r="AL79" s="1"/>
       <c r="AM79" s="1"/>
     </row>
-    <row r="80" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A80" s="22" t="s">
         <v>161</v>
       </c>
@@ -20743,7 +20783,7 @@
       <c r="AL82" s="1"/>
       <c r="AM82" s="1"/>
     </row>
-    <row r="83" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A83" s="22" t="s">
         <v>162</v>
       </c>
@@ -20835,7 +20875,7 @@
       <c r="AL83" s="1"/>
       <c r="AM83" s="1"/>
     </row>
-    <row r="84" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A84" s="22" t="s">
         <v>165</v>
       </c>
@@ -21287,7 +21327,7 @@
       <c r="AL88" s="1"/>
       <c r="AM88" s="1"/>
     </row>
-    <row r="89" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="22" t="s">
         <v>171</v>
       </c>
@@ -21559,7 +21599,7 @@
       <c r="AL91" s="1"/>
       <c r="AM91" s="1"/>
     </row>
-    <row r="92" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A92" s="22" t="s">
         <v>174</v>
       </c>
@@ -21655,7 +21695,7 @@
       <c r="AL92" s="1"/>
       <c r="AM92" s="1"/>
     </row>
-    <row r="93" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A93" s="22" t="s">
         <v>176</v>
       </c>
@@ -21745,7 +21785,7 @@
       <c r="AL93" s="1"/>
       <c r="AM93" s="1"/>
     </row>
-    <row r="94" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A94" s="22" t="s">
         <v>178</v>
       </c>
@@ -22107,7 +22147,7 @@
       <c r="AL97" s="1"/>
       <c r="AM97" s="1"/>
     </row>
-    <row r="98" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="22" t="s">
         <v>180</v>
       </c>
@@ -22199,7 +22239,7 @@
       <c r="AL98" s="1"/>
       <c r="AM98" s="1"/>
     </row>
-    <row r="99" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A99" s="22" t="s">
         <v>184</v>
       </c>
@@ -22381,7 +22421,7 @@
       <c r="AL100" s="1"/>
       <c r="AM100" s="1"/>
     </row>
-    <row r="101" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A101" s="22" t="s">
         <v>188</v>
       </c>
@@ -22895,7 +22935,7 @@
       <c r="AL106" s="1"/>
       <c r="AM106" s="1"/>
     </row>
-    <row r="107" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A107" s="22" t="s">
         <v>191</v>
       </c>
@@ -22987,7 +23027,7 @@
       <c r="AL107" s="1"/>
       <c r="AM107" s="1"/>
     </row>
-    <row r="108" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A108" s="22" t="s">
         <v>197</v>
       </c>
@@ -23789,7 +23829,7 @@
       <c r="AL116" s="1"/>
       <c r="AM116" s="1"/>
     </row>
-    <row r="117" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A117" s="22" t="s">
         <v>199</v>
       </c>
@@ -23881,7 +23921,7 @@
       <c r="AL117" s="1"/>
       <c r="AM117" s="1"/>
     </row>
-    <row r="118" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A118" s="22" t="s">
         <v>201</v>
       </c>
@@ -23973,7 +24013,7 @@
       <c r="AL118" s="1"/>
       <c r="AM118" s="1"/>
     </row>
-    <row r="119" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A119" s="22" t="s">
         <v>204</v>
       </c>
@@ -24155,7 +24195,7 @@
       <c r="AL120" s="1"/>
       <c r="AM120" s="1"/>
     </row>
-    <row r="121" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A121" s="22" t="s">
         <v>207</v>
       </c>
@@ -24247,7 +24287,7 @@
       <c r="AL121" s="1"/>
       <c r="AM121" s="1"/>
     </row>
-    <row r="122" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A122" s="22" t="s">
         <v>210</v>
       </c>
@@ -24771,7 +24811,7 @@
       <c r="AL127" s="1"/>
       <c r="AM127" s="1"/>
     </row>
-    <row r="128" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A128" s="22" t="s">
         <v>212</v>
       </c>
@@ -24953,7 +24993,7 @@
       <c r="AL129" s="1"/>
       <c r="AM129" s="1"/>
     </row>
-    <row r="130" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A130" s="22" t="s">
         <v>216</v>
       </c>
@@ -25225,7 +25265,7 @@
       <c r="AL132" s="1"/>
       <c r="AM132" s="1"/>
     </row>
-    <row r="133" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A133" s="22" t="s">
         <v>221</v>
       </c>
@@ -25493,7 +25533,7 @@
       <c r="AL135" s="1"/>
       <c r="AM135" s="1"/>
     </row>
-    <row r="136" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A136" s="22" t="s">
         <v>223</v>
       </c>
@@ -25585,7 +25625,7 @@
       <c r="AL136" s="1"/>
       <c r="AM136" s="1"/>
     </row>
-    <row r="137" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A137" s="22" t="s">
         <v>225</v>
       </c>
@@ -25929,7 +25969,7 @@
       <c r="AL140" s="1"/>
       <c r="AM140" s="1"/>
     </row>
-    <row r="141" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A141" s="22" t="s">
         <v>227</v>
       </c>
@@ -26197,7 +26237,7 @@
       <c r="AL143" s="1"/>
       <c r="AM143" s="1"/>
     </row>
-    <row r="144" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A144" s="22" t="s">
         <v>228</v>
       </c>
@@ -26375,7 +26415,7 @@
       <c r="AL145" s="1"/>
       <c r="AM145" s="1"/>
     </row>
-    <row r="146" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A146" s="22" t="s">
         <v>232</v>
       </c>
@@ -26467,7 +26507,7 @@
       <c r="AL146" s="1"/>
       <c r="AM146" s="1"/>
     </row>
-    <row r="147" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A147" s="22" t="s">
         <v>234</v>
       </c>
@@ -26559,7 +26599,7 @@
       <c r="AL147" s="1"/>
       <c r="AM147" s="1"/>
     </row>
-    <row r="148" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A148" s="22" t="s">
         <v>236</v>
       </c>
@@ -26909,7 +26949,7 @@
       <c r="AL151" s="1"/>
       <c r="AM151" s="1"/>
     </row>
-    <row r="152" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A152" s="22" t="s">
         <v>240</v>
       </c>
@@ -27089,7 +27129,7 @@
       <c r="AL153" s="1"/>
       <c r="AM153" s="1"/>
     </row>
-    <row r="154" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A154" s="22" t="s">
         <v>243</v>
       </c>
@@ -27181,7 +27221,7 @@
       <c r="AL154" s="1"/>
       <c r="AM154" s="1"/>
     </row>
-    <row r="155" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A155" s="22" t="s">
         <v>245</v>
       </c>
@@ -27359,7 +27399,7 @@
       <c r="AL156" s="1"/>
       <c r="AM156" s="1"/>
     </row>
-    <row r="157" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A157" s="22" t="s">
         <v>246</v>
       </c>
@@ -27623,7 +27663,7 @@
       <c r="AL159" s="1"/>
       <c r="AM159" s="1"/>
     </row>
-    <row r="160" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A160" s="22" t="s">
         <v>249</v>
       </c>
@@ -27715,7 +27755,7 @@
       <c r="AL160" s="1"/>
       <c r="AM160" s="1"/>
     </row>
-    <row r="161" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A161" s="22" t="s">
         <v>251</v>
       </c>
@@ -27981,7 +28021,7 @@
       <c r="AL163" s="1"/>
       <c r="AM163" s="1"/>
     </row>
-    <row r="164" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A164" s="22" t="s">
         <v>253</v>
       </c>
@@ -28689,7 +28729,7 @@
       <c r="AL171" s="1"/>
       <c r="AM171" s="1"/>
     </row>
-    <row r="172" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A172" s="22" t="s">
         <v>256</v>
       </c>
@@ -28961,7 +29001,7 @@
       <c r="AL174" s="1"/>
       <c r="AM174" s="1"/>
     </row>
-    <row r="175" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A175" s="22" t="s">
         <v>258</v>
       </c>
@@ -29051,7 +29091,7 @@
       <c r="AL175" s="1"/>
       <c r="AM175" s="1"/>
     </row>
-    <row r="176" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A176" s="22" t="s">
         <v>261</v>
       </c>
@@ -29143,7 +29183,7 @@
       <c r="AL176" s="1"/>
       <c r="AM176" s="1"/>
     </row>
-    <row r="177" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A177" s="22" t="s">
         <v>265</v>
       </c>
@@ -29321,7 +29361,7 @@
       <c r="AL178" s="1"/>
       <c r="AM178" s="1"/>
     </row>
-    <row r="179" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A179" s="22" t="s">
         <v>268</v>
       </c>
@@ -29411,7 +29451,7 @@
       <c r="AL179" s="1"/>
       <c r="AM179" s="1"/>
     </row>
-    <row r="180" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A180" s="22" t="s">
         <v>270</v>
       </c>
@@ -29593,7 +29633,7 @@
       <c r="AL181" s="1"/>
       <c r="AM181" s="1"/>
     </row>
-    <row r="182" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A182" s="22" t="s">
         <v>272</v>
       </c>
@@ -29863,7 +29903,7 @@
       <c r="AL184" s="1"/>
       <c r="AM184" s="1"/>
     </row>
-    <row r="185" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A185" s="22" t="s">
         <v>275</v>
       </c>
@@ -29955,7 +29995,7 @@
       <c r="AL185" s="1"/>
       <c r="AM185" s="1"/>
     </row>
-    <row r="186" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A186" s="22" t="s">
         <v>278</v>
       </c>
@@ -30463,7 +30503,7 @@
       <c r="AL191" s="1"/>
       <c r="AM191" s="1"/>
     </row>
-    <row r="192" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A192" s="22" t="s">
         <v>281</v>
       </c>
@@ -30643,7 +30683,7 @@
       <c r="AL193" s="1"/>
       <c r="AM193" s="1"/>
     </row>
-    <row r="194" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A194" s="22" t="s">
         <v>283</v>
       </c>
@@ -31085,7 +31125,7 @@
       <c r="AL198" s="1"/>
       <c r="AM198" s="1"/>
     </row>
-    <row r="199" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A199" s="22" t="s">
         <v>285</v>
       </c>
@@ -31265,7 +31305,7 @@
       <c r="AL200" s="1"/>
       <c r="AM200" s="1"/>
     </row>
-    <row r="201" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A201" s="22" t="s">
         <v>287</v>
       </c>
@@ -31515,7 +31555,7 @@
       <c r="AL203" s="1"/>
       <c r="AM203" s="1"/>
     </row>
-    <row r="204" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A204" s="22" t="s">
         <v>289</v>
       </c>
@@ -31945,7 +31985,7 @@
       <c r="AL208" s="1"/>
       <c r="AM208" s="1"/>
     </row>
-    <row r="209" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A209" s="22" t="s">
         <v>292</v>
       </c>
@@ -32037,7 +32077,7 @@
       <c r="AL209" s="1"/>
       <c r="AM209" s="1"/>
     </row>
-    <row r="210" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A210" s="22" t="s">
         <v>294</v>
       </c>
@@ -32129,7 +32169,7 @@
       <c r="AL210" s="1"/>
       <c r="AM210" s="1"/>
     </row>
-    <row r="211" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A211" s="22" t="s">
         <v>299</v>
       </c>
@@ -32463,7 +32503,7 @@
       <c r="AL214" s="1"/>
       <c r="AM214" s="1"/>
     </row>
-    <row r="215" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A215" s="22" t="s">
         <v>303</v>
       </c>
@@ -32551,7 +32591,7 @@
       <c r="AL215" s="1"/>
       <c r="AM215" s="1"/>
     </row>
-    <row r="216" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A216" s="22" t="s">
         <v>307</v>
       </c>
@@ -32715,7 +32755,7 @@
       <c r="AL217" s="1"/>
       <c r="AM217" s="1"/>
     </row>
-    <row r="218" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A218" s="22" t="s">
         <v>310</v>
       </c>
@@ -32893,7 +32933,7 @@
       <c r="AL219" s="1"/>
       <c r="AM219" s="1"/>
     </row>
-    <row r="220" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A220" s="22" t="s">
         <v>312</v>
       </c>
@@ -34899,7 +34939,7 @@
       <c r="AL244" s="1"/>
       <c r="AM244" s="1"/>
     </row>
-    <row r="245" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A245" s="22" t="s">
         <v>315</v>
       </c>
@@ -36117,7 +36157,7 @@
       <c r="AL259" s="1"/>
       <c r="AM259" s="1"/>
     </row>
-    <row r="260" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A260" s="22" t="s">
         <v>318</v>
       </c>
@@ -36297,7 +36337,7 @@
       <c r="AL261" s="1"/>
       <c r="AM261" s="1"/>
     </row>
-    <row r="262" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A262" s="3" t="s">
         <v>320</v>
       </c>
@@ -36389,7 +36429,7 @@
       <c r="AL262" s="1"/>
       <c r="AM262" s="1"/>
     </row>
-    <row r="263" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A263" s="22" t="s">
         <v>324</v>
       </c>
@@ -36475,7 +36515,7 @@
       <c r="AL263" s="1"/>
       <c r="AM263" s="1"/>
     </row>
-    <row r="264" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A264" s="22" t="s">
         <v>325</v>
       </c>
@@ -36891,7 +36931,7 @@
       <c r="AL268" s="1"/>
       <c r="AM268" s="1"/>
     </row>
-    <row r="269" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A269" s="22" t="s">
         <v>327</v>
       </c>
@@ -37781,7 +37821,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="280" spans="1:39" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:39" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A280" s="22" t="s">
         <v>330</v>
       </c>
@@ -37871,7 +37911,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="281" spans="1:39" s="26" customFormat="1" ht="122.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:39" s="26" customFormat="1" ht="122.4" x14ac:dyDescent="0.3">
       <c r="A281" s="22" t="s">
         <v>333</v>
       </c>
@@ -38561,7 +38601,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="289" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A289" s="22" t="s">
         <v>336</v>
       </c>
@@ -39029,7 +39069,7 @@
       <c r="AL294" s="1"/>
       <c r="AM294" s="1"/>
     </row>
-    <row r="295" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A295" s="22" t="s">
         <v>337</v>
       </c>
@@ -39269,7 +39309,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="298" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A298" s="22" t="s">
         <v>339</v>
       </c>
@@ -39679,7 +39719,7 @@
       <c r="AL302" s="1"/>
       <c r="AM302" s="1"/>
     </row>
-    <row r="303" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A303" s="22" t="s">
         <v>341</v>
       </c>
@@ -39929,7 +39969,7 @@
       <c r="AL305" s="1"/>
       <c r="AM305" s="1"/>
     </row>
-    <row r="306" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A306" s="22" t="s">
         <v>343</v>
       </c>
@@ -40015,7 +40055,7 @@
       <c r="AL306" s="1"/>
       <c r="AM306" s="1"/>
     </row>
-    <row r="307" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A307" s="22" t="s">
         <v>344</v>
       </c>
@@ -40107,7 +40147,7 @@
       <c r="AL307" s="1"/>
       <c r="AM307" s="1"/>
     </row>
-    <row r="308" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A308" s="22" t="s">
         <v>346</v>
       </c>
@@ -40197,7 +40237,7 @@
       <c r="AL308" s="1"/>
       <c r="AM308" s="1"/>
     </row>
-    <row r="309" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A309" s="22" t="s">
         <v>348</v>
       </c>
@@ -40515,7 +40555,7 @@
       <c r="AL312" s="1"/>
       <c r="AM312" s="1"/>
     </row>
-    <row r="313" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A313" s="22" t="s">
         <v>350</v>
       </c>
@@ -40761,7 +40801,7 @@
       <c r="AL315" s="1"/>
       <c r="AM315" s="1"/>
     </row>
-    <row r="316" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A316" s="22" t="s">
         <v>352</v>
       </c>
@@ -41177,7 +41217,7 @@
       <c r="AL320" s="1"/>
       <c r="AM320" s="1"/>
     </row>
-    <row r="321" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
         <v>354</v>
       </c>
@@ -41441,7 +41481,7 @@
       <c r="AL323" s="1"/>
       <c r="AM323" s="1"/>
     </row>
-    <row r="324" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A324" s="22" t="s">
         <v>356</v>
       </c>
@@ -41689,7 +41729,7 @@
       <c r="AL326" s="1"/>
       <c r="AM326" s="1"/>
     </row>
-    <row r="327" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A327" s="22" t="s">
         <v>358</v>
       </c>
@@ -41849,7 +41889,7 @@
       <c r="AL328" s="1"/>
       <c r="AM328" s="1"/>
     </row>
-    <row r="329" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A329" s="22" t="s">
         <v>362</v>
       </c>
@@ -41941,7 +41981,7 @@
       <c r="AL329" s="1"/>
       <c r="AM329" s="1"/>
     </row>
-    <row r="330" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A330" s="22" t="s">
         <v>364</v>
       </c>
@@ -42485,7 +42525,7 @@
       <c r="AL336" s="1"/>
       <c r="AM336" s="1"/>
     </row>
-    <row r="337" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A337" s="22" t="s">
         <v>366</v>
       </c>
@@ -42967,7 +43007,7 @@
       <c r="AL342" s="1"/>
       <c r="AM342" s="1"/>
     </row>
-    <row r="343" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A343" s="22" t="s">
         <v>368</v>
       </c>
@@ -43213,7 +43253,7 @@
       <c r="AL345" s="1"/>
       <c r="AM345" s="1"/>
     </row>
-    <row r="346" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A346" s="22" t="s">
         <v>370</v>
       </c>
@@ -43779,7 +43819,7 @@
       <c r="AL352" s="1"/>
       <c r="AM352" s="1"/>
     </row>
-    <row r="353" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A353" s="22" t="s">
         <v>372</v>
       </c>
@@ -44039,7 +44079,7 @@
       <c r="AL355" s="1"/>
       <c r="AM355" s="1"/>
     </row>
-    <row r="356" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A356" s="22" t="s">
         <v>373</v>
       </c>
@@ -44375,7 +44415,7 @@
       <c r="AL359" s="1"/>
       <c r="AM359" s="1"/>
     </row>
-    <row r="360" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A360" s="22" t="s">
         <v>375</v>
       </c>
@@ -44463,7 +44503,7 @@
       <c r="AL360" s="1"/>
       <c r="AM360" s="1"/>
     </row>
-    <row r="361" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A361" s="22" t="s">
         <v>378</v>
       </c>
@@ -45423,7 +45463,7 @@
       <c r="AL372" s="1"/>
       <c r="AM372" s="1"/>
     </row>
-    <row r="373" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A373" s="22" t="s">
         <v>380</v>
       </c>
@@ -45745,7 +45785,7 @@
       <c r="AL376" s="1"/>
       <c r="AM376" s="1"/>
     </row>
-    <row r="377" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A377" s="22" t="s">
         <v>383</v>
       </c>
@@ -45827,7 +45867,7 @@
       <c r="AL377" s="1"/>
       <c r="AM377" s="1"/>
     </row>
-    <row r="378" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A378" s="22" t="s">
         <v>384</v>
       </c>
@@ -46477,7 +46517,7 @@
       <c r="AL385" s="1"/>
       <c r="AM385" s="1"/>
     </row>
-    <row r="386" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A386" s="22" t="s">
         <v>385</v>
       </c>
@@ -46785,7 +46825,7 @@
       <c r="AL389" s="1"/>
       <c r="AM389" s="1"/>
     </row>
-    <row r="390" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A390" s="22" t="s">
         <v>387</v>
       </c>
@@ -46877,7 +46917,7 @@
       <c r="AL390" s="1"/>
       <c r="AM390" s="1"/>
     </row>
-    <row r="391" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A391" s="22" t="s">
         <v>389</v>
       </c>
@@ -46959,7 +46999,7 @@
       <c r="AL391" s="1"/>
       <c r="AM391" s="1"/>
     </row>
-    <row r="392" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A392" s="22" t="s">
         <v>390</v>
       </c>
@@ -47263,7 +47303,7 @@
       <c r="AL395" s="1"/>
       <c r="AM395" s="1"/>
     </row>
-    <row r="396" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A396" s="22" t="s">
         <v>392</v>
       </c>
@@ -47657,7 +47697,7 @@
       <c r="AL400" s="1"/>
       <c r="AM400" s="1"/>
     </row>
-    <row r="401" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A401" s="22" t="s">
         <v>394</v>
       </c>
@@ -47829,7 +47869,7 @@
       <c r="AL402" s="1"/>
       <c r="AM402" s="1"/>
     </row>
-    <row r="403" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A403" s="22" t="s">
         <v>396</v>
       </c>
@@ -47911,7 +47951,7 @@
       <c r="AL403" s="1"/>
       <c r="AM403" s="1"/>
     </row>
-    <row r="404" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A404" s="22" t="s">
         <v>397</v>
       </c>
@@ -48299,7 +48339,7 @@
       <c r="AL408" s="1"/>
       <c r="AM408" s="1"/>
     </row>
-    <row r="409" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A409" s="15" t="s">
         <v>400</v>
       </c>
@@ -48623,7 +48663,7 @@
       <c r="AL412" s="1"/>
       <c r="AM412" s="1"/>
     </row>
-    <row r="413" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A413" s="15" t="s">
         <v>402</v>
       </c>
@@ -48795,7 +48835,7 @@
       <c r="AL414" s="1"/>
       <c r="AM414" s="1"/>
     </row>
-    <row r="415" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A415" s="15" t="s">
         <v>403</v>
       </c>
@@ -48879,7 +48919,7 @@
       <c r="AL415" s="1"/>
       <c r="AM415" s="1"/>
     </row>
-    <row r="416" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A416" s="15" t="s">
         <v>404</v>
       </c>
@@ -49031,7 +49071,7 @@
       <c r="AL417" s="1"/>
       <c r="AM417" s="1"/>
     </row>
-    <row r="418" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A418" s="15" t="s">
         <v>405</v>
       </c>
@@ -49435,7 +49475,7 @@
       <c r="AL422" s="1"/>
       <c r="AM422" s="1"/>
     </row>
-    <row r="423" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A423" s="15" t="s">
         <v>406</v>
       </c>
@@ -49525,7 +49565,7 @@
       <c r="AL423" s="1"/>
       <c r="AM423" s="1"/>
     </row>
-    <row r="424" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A424" s="15" t="s">
         <v>409</v>
       </c>
@@ -49609,7 +49649,7 @@
       <c r="AL424" s="1"/>
       <c r="AM424" s="1"/>
     </row>
-    <row r="425" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A425" s="15" t="s">
         <v>410</v>
       </c>
@@ -49693,7 +49733,7 @@
       <c r="AL425" s="1"/>
       <c r="AM425" s="1"/>
     </row>
-    <row r="426" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A426" s="15" t="s">
         <v>411</v>
       </c>
@@ -49777,7 +49817,7 @@
       <c r="AL426" s="1"/>
       <c r="AM426" s="1"/>
     </row>
-    <row r="427" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A427" s="15" t="s">
         <v>412</v>
       </c>
@@ -49955,7 +49995,7 @@
       <c r="AL428" s="1"/>
       <c r="AM428" s="1"/>
     </row>
-    <row r="429" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A429" s="15" t="s">
         <v>416</v>
       </c>
@@ -50039,7 +50079,7 @@
       <c r="AL429" s="1"/>
       <c r="AM429" s="1"/>
     </row>
-    <row r="430" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A430" s="15" t="s">
         <v>418</v>
       </c>
@@ -50125,7 +50165,7 @@
       <c r="AL430" s="1"/>
       <c r="AM430" s="1"/>
     </row>
-    <row r="431" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A431" s="15" t="s">
         <v>421</v>
       </c>
@@ -50215,7 +50255,7 @@
       <c r="AL431" s="1"/>
       <c r="AM431" s="1"/>
     </row>
-    <row r="432" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A432" s="15" t="s">
         <v>423</v>
       </c>
@@ -50301,7 +50341,7 @@
       <c r="AL432" s="1"/>
       <c r="AM432" s="1"/>
     </row>
-    <row r="433" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A433" s="15" t="s">
         <v>426</v>
       </c>
@@ -50391,7 +50431,7 @@
       <c r="AL433" s="1"/>
       <c r="AM433" s="1"/>
     </row>
-    <row r="434" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A434" s="15" t="s">
         <v>428</v>
       </c>
@@ -50481,7 +50521,7 @@
       <c r="AL434" s="1"/>
       <c r="AM434" s="1"/>
     </row>
-    <row r="435" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A435" s="15" t="s">
         <v>430</v>
       </c>
@@ -50565,7 +50605,7 @@
       <c r="AL435" s="1"/>
       <c r="AM435" s="1"/>
     </row>
-    <row r="436" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A436" s="15" t="s">
         <v>432</v>
       </c>
@@ -50655,7 +50695,7 @@
       <c r="AL436" s="1"/>
       <c r="AM436" s="1"/>
     </row>
-    <row r="437" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A437" s="15" t="s">
         <v>435</v>
       </c>
@@ -50741,7 +50781,7 @@
       <c r="AL437" s="1"/>
       <c r="AM437" s="1"/>
     </row>
-    <row r="438" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A438" s="15" t="s">
         <v>437</v>
       </c>
@@ -50827,7 +50867,7 @@
       <c r="AL438" s="1"/>
       <c r="AM438" s="1"/>
     </row>
-    <row r="439" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A439" s="15" t="s">
         <v>439</v>
       </c>
@@ -50913,7 +50953,7 @@
       <c r="AL439" s="1"/>
       <c r="AM439" s="1"/>
     </row>
-    <row r="440" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A440" s="15" t="s">
         <v>441</v>
       </c>
@@ -50999,7 +51039,7 @@
       <c r="AL440" s="1"/>
       <c r="AM440" s="1"/>
     </row>
-    <row r="441" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A441" s="15" t="s">
         <v>444</v>
       </c>
@@ -51085,7 +51125,7 @@
       <c r="AL441" s="1"/>
       <c r="AM441" s="1"/>
     </row>
-    <row r="442" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A442" s="15" t="s">
         <v>446</v>
       </c>
@@ -51171,7 +51211,7 @@
       <c r="AL442" s="1"/>
       <c r="AM442" s="1"/>
     </row>
-    <row r="443" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A443" s="15" t="s">
         <v>448</v>
       </c>
@@ -51257,7 +51297,7 @@
       <c r="AL443" s="1"/>
       <c r="AM443" s="1"/>
     </row>
-    <row r="444" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A444" s="15" t="s">
         <v>450</v>
       </c>
@@ -51343,7 +51383,7 @@
       <c r="AL444" s="1"/>
       <c r="AM444" s="1"/>
     </row>
-    <row r="445" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A445" s="15" t="s">
         <v>452</v>
       </c>
@@ -51429,7 +51469,7 @@
       <c r="AL445" s="1"/>
       <c r="AM445" s="1"/>
     </row>
-    <row r="446" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A446" s="15" t="s">
         <v>454</v>
       </c>
@@ -51519,7 +51559,7 @@
       <c r="AL446" s="1"/>
       <c r="AM446" s="1"/>
     </row>
-    <row r="447" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A447" s="15" t="s">
         <v>457</v>
       </c>
@@ -51605,7 +51645,7 @@
       <c r="AL447" s="1"/>
       <c r="AM447" s="1"/>
     </row>
-    <row r="448" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A448" s="15" t="s">
         <v>459</v>
       </c>
@@ -51691,7 +51731,7 @@
       <c r="AL448" s="1"/>
       <c r="AM448" s="1"/>
     </row>
-    <row r="449" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A449" s="15" t="s">
         <v>461</v>
       </c>
@@ -51777,7 +51817,7 @@
       <c r="AL449" s="1"/>
       <c r="AM449" s="1"/>
     </row>
-    <row r="450" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A450" s="15" t="s">
         <v>463</v>
       </c>
@@ -51863,7 +51903,7 @@
       <c r="AL450" s="1"/>
       <c r="AM450" s="1"/>
     </row>
-    <row r="451" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A451" s="15" t="s">
         <v>465</v>
       </c>
@@ -51949,7 +51989,7 @@
       <c r="AL451" s="1"/>
       <c r="AM451" s="1"/>
     </row>
-    <row r="452" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A452" s="15" t="s">
         <v>467</v>
       </c>
@@ -52035,7 +52075,7 @@
       <c r="AL452" s="1"/>
       <c r="AM452" s="1"/>
     </row>
-    <row r="453" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A453" s="15" t="s">
         <v>469</v>
       </c>
@@ -52121,7 +52161,7 @@
       <c r="AL453" s="1"/>
       <c r="AM453" s="1"/>
     </row>
-    <row r="454" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A454" s="15" t="s">
         <v>471</v>
       </c>
@@ -52207,7 +52247,7 @@
       <c r="AL454" s="1"/>
       <c r="AM454" s="1"/>
     </row>
-    <row r="455" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A455" s="15" t="s">
         <v>473</v>
       </c>
@@ -52293,7 +52333,7 @@
       <c r="AL455" s="1"/>
       <c r="AM455" s="1"/>
     </row>
-    <row r="456" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A456" s="15" t="s">
         <v>475</v>
       </c>
@@ -52379,7 +52419,7 @@
       <c r="AL456" s="1"/>
       <c r="AM456" s="1"/>
     </row>
-    <row r="457" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A457" s="15" t="s">
         <v>477</v>
       </c>
@@ -52465,7 +52505,7 @@
       <c r="AL457" s="1"/>
       <c r="AM457" s="1"/>
     </row>
-    <row r="458" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A458" s="15" t="s">
         <v>479</v>
       </c>
@@ -52551,7 +52591,7 @@
       <c r="AL458" s="1"/>
       <c r="AM458" s="1"/>
     </row>
-    <row r="459" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A459" s="15" t="s">
         <v>481</v>
       </c>
@@ -52623,7 +52663,7 @@
       <c r="AL459" s="1"/>
       <c r="AM459" s="1"/>
     </row>
-    <row r="460" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A460" s="15" t="s">
         <v>482</v>
       </c>
@@ -52709,7 +52749,7 @@
       <c r="AL460" s="1"/>
       <c r="AM460" s="1"/>
     </row>
-    <row r="461" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A461" s="15" t="s">
         <v>485</v>
       </c>
@@ -52793,7 +52833,7 @@
       <c r="AL461" s="1"/>
       <c r="AM461" s="1"/>
     </row>
-    <row r="462" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A462" s="15" t="s">
         <v>487</v>
       </c>
@@ -52883,7 +52923,7 @@
       <c r="AL462" s="1"/>
       <c r="AM462" s="1"/>
     </row>
-    <row r="463" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A463" s="15" t="s">
         <v>488</v>
       </c>
@@ -52969,7 +53009,7 @@
       <c r="AL463" s="1"/>
       <c r="AM463" s="1"/>
     </row>
-    <row r="464" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A464" s="15" t="s">
         <v>492</v>
       </c>
@@ -53061,7 +53101,7 @@
       <c r="AL464" s="1"/>
       <c r="AM464" s="1"/>
     </row>
-    <row r="465" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A465" s="15" t="s">
         <v>495</v>
       </c>
@@ -53153,7 +53193,7 @@
       <c r="AL465" s="1"/>
       <c r="AM465" s="1"/>
     </row>
-    <row r="466" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A466" s="15" t="s">
         <v>498</v>
       </c>
@@ -53243,7 +53283,7 @@
       <c r="AL466" s="1"/>
       <c r="AM466" s="1"/>
     </row>
-    <row r="467" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A467" s="15" t="s">
         <v>500</v>
       </c>
@@ -53329,7 +53369,7 @@
       <c r="AL467" s="1"/>
       <c r="AM467" s="1"/>
     </row>
-    <row r="468" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A468" s="15" t="s">
         <v>501</v>
       </c>
@@ -53415,7 +53455,7 @@
       <c r="AL468" s="1"/>
       <c r="AM468" s="1"/>
     </row>
-    <row r="469" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A469" s="15" t="s">
         <v>503</v>
       </c>
@@ -53501,7 +53541,7 @@
       <c r="AL469" s="1"/>
       <c r="AM469" s="1"/>
     </row>
-    <row r="470" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A470" s="15" t="s">
         <v>506</v>
       </c>
@@ -53587,7 +53627,7 @@
       <c r="AL470" s="1"/>
       <c r="AM470" s="1"/>
     </row>
-    <row r="471" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A471" s="15" t="s">
         <v>508</v>
       </c>
@@ -53673,7 +53713,7 @@
       <c r="AL471" s="1"/>
       <c r="AM471" s="1"/>
     </row>
-    <row r="472" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A472" s="15" t="s">
         <v>511</v>
       </c>
@@ -53759,7 +53799,7 @@
       <c r="AL472" s="1"/>
       <c r="AM472" s="1"/>
     </row>
-    <row r="473" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A473" s="15" t="s">
         <v>514</v>
       </c>
@@ -53843,7 +53883,7 @@
       <c r="AL473" s="1"/>
       <c r="AM473" s="1"/>
     </row>
-    <row r="474" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A474" s="15" t="s">
         <v>516</v>
       </c>
@@ -53929,7 +53969,7 @@
       <c r="AL474" s="1"/>
       <c r="AM474" s="1"/>
     </row>
-    <row r="475" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A475" s="15" t="s">
         <v>518</v>
       </c>
@@ -54013,7 +54053,7 @@
       <c r="AL475" s="1"/>
       <c r="AM475" s="1"/>
     </row>
-    <row r="476" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A476" s="15" t="s">
         <v>520</v>
       </c>
@@ -54099,7 +54139,7 @@
       <c r="AL476" s="1"/>
       <c r="AM476" s="1"/>
     </row>
-    <row r="477" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A477" s="15" t="s">
         <v>522</v>
       </c>
@@ -54185,7 +54225,7 @@
       <c r="AL477" s="1"/>
       <c r="AM477" s="1"/>
     </row>
-    <row r="478" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A478" s="15" t="s">
         <v>525</v>
       </c>
@@ -54271,7 +54311,7 @@
       <c r="AL478" s="1"/>
       <c r="AM478" s="1"/>
     </row>
-    <row r="479" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A479" s="15" t="s">
         <v>528</v>
       </c>
@@ -54357,7 +54397,7 @@
       <c r="AL479" s="1"/>
       <c r="AM479" s="1"/>
     </row>
-    <row r="480" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A480" s="15" t="s">
         <v>531</v>
       </c>
@@ -54443,7 +54483,7 @@
       <c r="AL480" s="1"/>
       <c r="AM480" s="1"/>
     </row>
-    <row r="481" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A481" s="15" t="s">
         <v>535</v>
       </c>
@@ -54529,7 +54569,7 @@
       <c r="AL481" s="1"/>
       <c r="AM481" s="1"/>
     </row>
-    <row r="482" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A482" s="15" t="s">
         <v>537</v>
       </c>
@@ -54615,7 +54655,7 @@
       <c r="AL482" s="1"/>
       <c r="AM482" s="1"/>
     </row>
-    <row r="483" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A483" s="15" t="s">
         <v>539</v>
       </c>
@@ -54701,7 +54741,7 @@
       <c r="AL483" s="1"/>
       <c r="AM483" s="1"/>
     </row>
-    <row r="484" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A484" s="15" t="s">
         <v>541</v>
       </c>
@@ -54785,7 +54825,7 @@
       <c r="AL484" s="1"/>
       <c r="AM484" s="1"/>
     </row>
-    <row r="485" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A485" s="15" t="s">
         <v>543</v>
       </c>
@@ -54871,7 +54911,7 @@
       <c r="AL485" s="1"/>
       <c r="AM485" s="1"/>
     </row>
-    <row r="486" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A486" s="15" t="s">
         <v>546</v>
       </c>
@@ -54961,7 +55001,7 @@
       <c r="AL486" s="1"/>
       <c r="AM486" s="1"/>
     </row>
-    <row r="487" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A487" s="15" t="s">
         <v>547</v>
       </c>
@@ -55047,7 +55087,7 @@
       <c r="AL487" s="1"/>
       <c r="AM487" s="1"/>
     </row>
-    <row r="488" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A488" s="15" t="s">
         <v>548</v>
       </c>
@@ -55133,7 +55173,7 @@
       <c r="AL488" s="1"/>
       <c r="AM488" s="1"/>
     </row>
-    <row r="489" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A489" s="15" t="s">
         <v>550</v>
       </c>
@@ -55219,7 +55259,7 @@
       <c r="AL489" s="1"/>
       <c r="AM489" s="1"/>
     </row>
-    <row r="490" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A490" s="15" t="s">
         <v>551</v>
       </c>
@@ -55309,7 +55349,7 @@
       <c r="AL490" s="1"/>
       <c r="AM490" s="1"/>
     </row>
-    <row r="491" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A491" s="15" t="s">
         <v>552</v>
       </c>
@@ -55395,7 +55435,7 @@
       <c r="AL491" s="1"/>
       <c r="AM491" s="1"/>
     </row>
-    <row r="492" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A492" s="15" t="s">
         <v>555</v>
       </c>
@@ -55481,7 +55521,7 @@
       <c r="AL492" s="1"/>
       <c r="AM492" s="1"/>
     </row>
-    <row r="493" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A493" s="15" t="s">
         <v>557</v>
       </c>
@@ -55567,7 +55607,7 @@
       <c r="AL493" s="1"/>
       <c r="AM493" s="1"/>
     </row>
-    <row r="494" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A494" s="15" t="s">
         <v>559</v>
       </c>
@@ -55653,7 +55693,7 @@
       <c r="AL494" s="1"/>
       <c r="AM494" s="1"/>
     </row>
-    <row r="495" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A495" s="15" t="s">
         <v>561</v>
       </c>
@@ -55739,7 +55779,7 @@
       <c r="AL495" s="1"/>
       <c r="AM495" s="1"/>
     </row>
-    <row r="496" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A496" s="15" t="s">
         <v>563</v>
       </c>
@@ -55825,7 +55865,7 @@
       <c r="AL496" s="1"/>
       <c r="AM496" s="1"/>
     </row>
-    <row r="497" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A497" s="15" t="s">
         <v>565</v>
       </c>
@@ -55911,7 +55951,7 @@
       <c r="AL497" s="1"/>
       <c r="AM497" s="1"/>
     </row>
-    <row r="498" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A498" s="15" t="s">
         <v>567</v>
       </c>
@@ -55997,7 +56037,7 @@
       <c r="AL498" s="1"/>
       <c r="AM498" s="1"/>
     </row>
-    <row r="499" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A499" s="15" t="s">
         <v>570</v>
       </c>
@@ -56085,7 +56125,7 @@
       <c r="AL499" s="1"/>
       <c r="AM499" s="1"/>
     </row>
-    <row r="500" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A500" s="15" t="s">
         <v>573</v>
       </c>
@@ -56169,7 +56209,7 @@
       <c r="AL500" s="1"/>
       <c r="AM500" s="1"/>
     </row>
-    <row r="501" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A501" s="15" t="s">
         <v>575</v>
       </c>
@@ -56255,7 +56295,7 @@
       <c r="AL501" s="1"/>
       <c r="AM501" s="1"/>
     </row>
-    <row r="502" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A502" s="15" t="s">
         <v>578</v>
       </c>
@@ -56339,7 +56379,7 @@
       <c r="AL502" s="1"/>
       <c r="AM502" s="1"/>
     </row>
-    <row r="503" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A503" s="15" t="s">
         <v>580</v>
       </c>
@@ -56423,7 +56463,7 @@
       <c r="AL503" s="1"/>
       <c r="AM503" s="1"/>
     </row>
-    <row r="504" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A504" s="15" t="s">
         <v>582</v>
       </c>
@@ -56503,7 +56543,7 @@
       <c r="AL504" s="1"/>
       <c r="AM504" s="1"/>
     </row>
-    <row r="505" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A505" s="15" t="s">
         <v>583</v>
       </c>
@@ -56587,7 +56627,7 @@
       <c r="AL505" s="1"/>
       <c r="AM505" s="1"/>
     </row>
-    <row r="506" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A506" s="15" t="s">
         <v>586</v>
       </c>
@@ -56671,7 +56711,7 @@
       <c r="AL506" s="1"/>
       <c r="AM506" s="1"/>
     </row>
-    <row r="507" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A507" s="15" t="s">
         <v>589</v>
       </c>
@@ -56755,7 +56795,7 @@
       <c r="AL507" s="1"/>
       <c r="AM507" s="1"/>
     </row>
-    <row r="508" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A508" s="15" t="s">
         <v>591</v>
       </c>
@@ -56843,7 +56883,7 @@
       <c r="AL508" s="1"/>
       <c r="AM508" s="1"/>
     </row>
-    <row r="509" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A509" s="15" t="s">
         <v>593</v>
       </c>
@@ -56925,7 +56965,7 @@
       <c r="AL509" s="1"/>
       <c r="AM509" s="1"/>
     </row>
-    <row r="510" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A510" s="15" t="s">
         <v>595</v>
       </c>
@@ -57011,7 +57051,7 @@
       <c r="AL510" s="1"/>
       <c r="AM510" s="1"/>
     </row>
-    <row r="511" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A511" s="15" t="s">
         <v>597</v>
       </c>
@@ -57097,7 +57137,7 @@
       <c r="AL511" s="1"/>
       <c r="AM511" s="1"/>
     </row>
-    <row r="512" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A512" s="15" t="s">
         <v>600</v>
       </c>
@@ -57181,7 +57221,7 @@
       <c r="AL512" s="1"/>
       <c r="AM512" s="1"/>
     </row>
-    <row r="513" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A513" s="15" t="s">
         <v>602</v>
       </c>
@@ -57263,7 +57303,7 @@
       <c r="AL513" s="1"/>
       <c r="AM513" s="1"/>
     </row>
-    <row r="514" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A514" s="15" t="s">
         <v>603</v>
       </c>
@@ -57347,7 +57387,7 @@
       <c r="AL514" s="1"/>
       <c r="AM514" s="1"/>
     </row>
-    <row r="515" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A515" s="15" t="s">
         <v>605</v>
       </c>
@@ -57431,7 +57471,7 @@
       <c r="AL515" s="1"/>
       <c r="AM515" s="1"/>
     </row>
-    <row r="516" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A516" s="15" t="s">
         <v>607</v>
       </c>
@@ -57511,7 +57551,7 @@
       <c r="AL516" s="1"/>
       <c r="AM516" s="1"/>
     </row>
-    <row r="517" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A517" s="15" t="s">
         <v>608</v>
       </c>
@@ -57681,7 +57721,7 @@
       <c r="AL518" s="1"/>
       <c r="AM518" s="1"/>
     </row>
-    <row r="519" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A519" s="15" t="s">
         <v>611</v>
       </c>
@@ -57767,7 +57807,7 @@
       <c r="AL519" s="1"/>
       <c r="AM519" s="1"/>
     </row>
-    <row r="520" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A520" s="15" t="s">
         <v>614</v>
       </c>
@@ -57853,7 +57893,7 @@
       <c r="AL520" s="1"/>
       <c r="AM520" s="1"/>
     </row>
-    <row r="521" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A521" s="15" t="s">
         <v>616</v>
       </c>
@@ -57939,7 +57979,7 @@
       <c r="AL521" s="1"/>
       <c r="AM521" s="1"/>
     </row>
-    <row r="522" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A522" s="15" t="s">
         <v>619</v>
       </c>
@@ -58029,7 +58069,7 @@
       <c r="AL522" s="1"/>
       <c r="AM522" s="1"/>
     </row>
-    <row r="523" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A523" s="15" t="s">
         <v>622</v>
       </c>
@@ -58119,7 +58159,7 @@
       <c r="AL523" s="1"/>
       <c r="AM523" s="1"/>
     </row>
-    <row r="524" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A524" s="15" t="s">
         <v>624</v>
       </c>
@@ -58209,7 +58249,7 @@
       <c r="AL524" s="1"/>
       <c r="AM524" s="1"/>
     </row>
-    <row r="525" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A525" s="15" t="s">
         <v>626</v>
       </c>
@@ -58295,7 +58335,7 @@
       <c r="AL525" s="1"/>
       <c r="AM525" s="1"/>
     </row>
-    <row r="526" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A526" s="15" t="s">
         <v>628</v>
       </c>
@@ -58381,7 +58421,7 @@
       <c r="AL526" s="1"/>
       <c r="AM526" s="1"/>
     </row>
-    <row r="527" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A527" s="15" t="s">
         <v>630</v>
       </c>
@@ -58471,7 +58511,7 @@
       <c r="AL527" s="1"/>
       <c r="AM527" s="1"/>
     </row>
-    <row r="528" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A528" s="15" t="s">
         <v>632</v>
       </c>
@@ -58557,7 +58597,7 @@
       <c r="AL528" s="1"/>
       <c r="AM528" s="1"/>
     </row>
-    <row r="529" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A529" s="15" t="s">
         <v>634</v>
       </c>
@@ -58641,7 +58681,7 @@
       <c r="AL529" s="1"/>
       <c r="AM529" s="1"/>
     </row>
-    <row r="530" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A530" s="15" t="s">
         <v>636</v>
       </c>
@@ -58727,7 +58767,7 @@
       <c r="AL530" s="1"/>
       <c r="AM530" s="1"/>
     </row>
-    <row r="531" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A531" s="15" t="s">
         <v>638</v>
       </c>
@@ -58813,7 +58853,7 @@
       <c r="AL531" s="1"/>
       <c r="AM531" s="1"/>
     </row>
-    <row r="532" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A532" s="15" t="s">
         <v>640</v>
       </c>
@@ -58899,7 +58939,7 @@
       <c r="AL532" s="1"/>
       <c r="AM532" s="1"/>
     </row>
-    <row r="533" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A533" s="15" t="s">
         <v>642</v>
       </c>
@@ -58985,7 +59025,7 @@
       <c r="AL533" s="1"/>
       <c r="AM533" s="1"/>
     </row>
-    <row r="534" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A534" s="15" t="s">
         <v>644</v>
       </c>
@@ -59071,7 +59111,7 @@
       <c r="AL534" s="1"/>
       <c r="AM534" s="1"/>
     </row>
-    <row r="535" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A535" s="15" t="s">
         <v>645</v>
       </c>
@@ -59155,7 +59195,7 @@
       <c r="AL535" s="1"/>
       <c r="AM535" s="1"/>
     </row>
-    <row r="536" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A536" s="15" t="s">
         <v>647</v>
       </c>
@@ -59239,7 +59279,7 @@
       <c r="AL536" s="1"/>
       <c r="AM536" s="1"/>
     </row>
-    <row r="537" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A537" s="15" t="s">
         <v>649</v>
       </c>
@@ -59323,7 +59363,7 @@
       <c r="AL537" s="1"/>
       <c r="AM537" s="1"/>
     </row>
-    <row r="538" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A538" s="15" t="s">
         <v>651</v>
       </c>
@@ -59407,7 +59447,7 @@
       <c r="AL538" s="1"/>
       <c r="AM538" s="1"/>
     </row>
-    <row r="539" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A539" s="15" t="s">
         <v>653</v>
       </c>
@@ -59493,7 +59533,7 @@
       <c r="AL539" s="1"/>
       <c r="AM539" s="1"/>
     </row>
-    <row r="540" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A540" s="15" t="s">
         <v>655</v>
       </c>
@@ -59579,7 +59619,7 @@
       <c r="AL540" s="1"/>
       <c r="AM540" s="1"/>
     </row>
-    <row r="541" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A541" s="15" t="s">
         <v>657</v>
       </c>
@@ -59665,7 +59705,7 @@
       <c r="AL541" s="1"/>
       <c r="AM541" s="1"/>
     </row>
-    <row r="542" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A542" s="15" t="s">
         <v>659</v>
       </c>
@@ -59751,7 +59791,7 @@
       <c r="AL542" s="1"/>
       <c r="AM542" s="1"/>
     </row>
-    <row r="543" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A543" s="15" t="s">
         <v>661</v>
       </c>
@@ -59837,7 +59877,7 @@
       <c r="AL543" s="1"/>
       <c r="AM543" s="1"/>
     </row>
-    <row r="544" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A544" s="15" t="s">
         <v>663</v>
       </c>
@@ -59921,7 +59961,7 @@
       <c r="AL544" s="1"/>
       <c r="AM544" s="1"/>
     </row>
-    <row r="545" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A545" s="15" t="s">
         <v>664</v>
       </c>
@@ -60001,7 +60041,7 @@
       <c r="AL545" s="1"/>
       <c r="AM545" s="1"/>
     </row>
-    <row r="546" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A546" s="15" t="s">
         <v>665</v>
       </c>
@@ -60081,7 +60121,7 @@
       <c r="AL546" s="1"/>
       <c r="AM546" s="1"/>
     </row>
-    <row r="547" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A547" s="15" t="s">
         <v>666</v>
       </c>
@@ -60157,7 +60197,7 @@
       <c r="AL547" s="1"/>
       <c r="AM547" s="1"/>
     </row>
-    <row r="548" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A548" s="15" t="s">
         <v>668</v>
       </c>
@@ -60237,7 +60277,7 @@
       <c r="AL548" s="1"/>
       <c r="AM548" s="1"/>
     </row>
-    <row r="549" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A549" s="15" t="s">
         <v>669</v>
       </c>
@@ -60317,7 +60357,7 @@
       <c r="AL549" s="1"/>
       <c r="AM549" s="1"/>
     </row>
-    <row r="550" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A550" s="15" t="s">
         <v>670</v>
       </c>
@@ -60397,7 +60437,7 @@
       <c r="AL550" s="1"/>
       <c r="AM550" s="1"/>
     </row>
-    <row r="551" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A551" s="15" t="s">
         <v>671</v>
       </c>
@@ -60477,7 +60517,7 @@
       <c r="AL551" s="1"/>
       <c r="AM551" s="1"/>
     </row>
-    <row r="552" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A552" s="15" t="s">
         <v>672</v>
       </c>
@@ -60557,7 +60597,7 @@
       <c r="AL552" s="1"/>
       <c r="AM552" s="1"/>
     </row>
-    <row r="553" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A553" s="15" t="s">
         <v>674</v>
       </c>
@@ -60637,7 +60677,7 @@
       <c r="AL553" s="1"/>
       <c r="AM553" s="1"/>
     </row>
-    <row r="554" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A554" s="15" t="s">
         <v>675</v>
       </c>
@@ -60717,7 +60757,7 @@
       <c r="AL554" s="1"/>
       <c r="AM554" s="1"/>
     </row>
-    <row r="555" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A555" s="15" t="s">
         <v>676</v>
       </c>
@@ -60797,7 +60837,7 @@
       <c r="AL555" s="1"/>
       <c r="AM555" s="1"/>
     </row>
-    <row r="556" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A556" s="31" t="s">
         <v>677</v>
       </c>
@@ -60877,7 +60917,7 @@
       <c r="AL556" s="1"/>
       <c r="AM556" s="1"/>
     </row>
-    <row r="557" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A557" s="15" t="s">
         <v>678</v>
       </c>
@@ -60957,7 +60997,7 @@
       <c r="AL557" s="1"/>
       <c r="AM557" s="1"/>
     </row>
-    <row r="558" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A558" s="15" t="s">
         <v>679</v>
       </c>
@@ -61037,7 +61077,7 @@
       <c r="AL558" s="1"/>
       <c r="AM558" s="1"/>
     </row>
-    <row r="559" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A559" s="15" t="s">
         <v>680</v>
       </c>
@@ -61117,7 +61157,7 @@
       <c r="AL559" s="1"/>
       <c r="AM559" s="1"/>
     </row>
-    <row r="560" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A560" s="15" t="s">
         <v>681</v>
       </c>
@@ -61197,7 +61237,7 @@
       <c r="AL560" s="1"/>
       <c r="AM560" s="1"/>
     </row>
-    <row r="561" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A561" s="15" t="s">
         <v>682</v>
       </c>
@@ -61277,7 +61317,7 @@
       <c r="AL561" s="1"/>
       <c r="AM561" s="1"/>
     </row>
-    <row r="562" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A562" s="15" t="s">
         <v>683</v>
       </c>
@@ -72904,12 +72944,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:AL707" xr:uid="{2AA437EE-405D-4A43-9EB9-23F1BEB36011}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="6,00"/>
-        <filter val="6,30"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="17">
       <filters>
         <filter val="Diadema"/>
@@ -73058,15 +73092,15 @@
       </c>
       <c r="D3" s="52">
         <f>SUMIF(Controle!R:R,Formulas!A3,Controle!AH:AH)</f>
-        <v>392.45735950000005</v>
+        <v>430.76987950000006</v>
       </c>
       <c r="E3" s="49">
         <f t="shared" ref="E3:E5" si="0">D3/C3</f>
-        <v>0.24010429823778848</v>
+        <v>0.26354378919303767</v>
       </c>
       <c r="F3" s="66">
         <f>SUMIF(Controle!$R:$R,Formulas!A3,Controle!$AK:$AK)</f>
-        <v>20671.96</v>
+        <v>38173.78</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -73133,15 +73167,15 @@
       </c>
       <c r="D6" s="55">
         <f t="shared" si="1"/>
-        <v>1715.1351630000004</v>
+        <v>1753.4476830000003</v>
       </c>
       <c r="E6" s="56">
         <f>D6/C6</f>
-        <v>0.37680005792085014</v>
+        <v>0.38521698042732067</v>
       </c>
       <c r="F6" s="67">
         <f t="shared" si="1"/>
-        <v>905697.44000000006</v>
+        <v>923199.26000000013</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -73179,7 +73213,7 @@
       </c>
       <c r="E10" s="66">
         <f>SUMIF(Controle!$L:$L,A10,Controle!$AK:$AK)</f>
-        <v>345413.89</v>
+        <v>362915.71</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -73849,7 +73883,7 @@
       </c>
       <c r="E42" s="68">
         <f>SUM(E10:E41)</f>
-        <v>905697.44</v>
+        <v>923199.26</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">

--- a/data/dados_atuais.xlsx
+++ b/data/dados_atuais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delgadiadema.sharepoint.com/sites/GestoEstratgica/Documentos Compartilhados/Controle Master/BSW/Novo controle (Em processo)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="689" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F3BA450-5B28-412E-82C4-E944558592F1}"/>
+  <xr:revisionPtr revIDLastSave="760" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC19E163-D936-4F25-812E-A708E260AC2E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E398004-7492-4AA0-94C2-EA9B761AAA49}"/>
   </bookViews>
@@ -321,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6243" uniqueCount="1408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6278" uniqueCount="1421">
   <si>
     <t>Código
 Bobina Mâe</t>
@@ -4677,6 +4677,71 @@
       <t>AGUARDANDO RETORNO DO FORNECEDOR EM RELAÇÃO À MP.</t>
     </r>
   </si>
+  <si>
+    <t>VW00581Z / 582Z</t>
+  </si>
+  <si>
+    <t>GM000390Z / GM000391Z / GM000392Z / GM000393Z / DJ000131Z / DJ000132Z</t>
+  </si>
+  <si>
+    <t>VW000745Z / 746Z</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>GM000378Z / 379Z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/ GM000396Z / 397Z / GM000380Z / 381Z</t>
+    </r>
+  </si>
+  <si>
+    <t>Redução no passo do blank. Aguardando validação da Controladoria.</t>
+  </si>
+  <si>
+    <t>VW000585Z / 586Z</t>
+  </si>
+  <si>
+    <t>VW000506Z / VW000522AA / VW000597Z / VW000815Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DA000489AA / DA000490AA</t>
+  </si>
+  <si>
+    <t>VW000887AA / VW000888AA</t>
+  </si>
+  <si>
+    <t>DA000475AA / DA000476AA / DA000477AA / DA000478AA / DA000479AA</t>
+  </si>
+  <si>
+    <t>VB000347LA / DA000496Z / DA000498Z / DA000499Z / DA000501Z / DA000500Z / DA000502Z / DA000506Z / DA000530Z / DA000531</t>
+  </si>
+  <si>
+    <t>DJ000049Z / DJ000050Z / DJ000232Z / DJ000233Z</t>
+  </si>
+  <si>
+    <t>DA000213Z</t>
+  </si>
 </sst>
 </file>
 
@@ -4687,7 +4752,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4792,6 +4857,18 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -4889,7 +4966,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5095,6 +5172,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5425,7 +5514,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.38521698042732067</c:v>
+                  <c:v>0.39198599504207626</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6343,7 +6432,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.26354378919303767</c:v>
+                  <c:v>0.28239417740993544</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7002,7 +7091,7 @@
                   <c:v>885025.4800000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>38173.78</c:v>
+                  <c:v>50984.49</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -7297,7 +7386,7 @@
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>923199.26000000013</c:v>
+                  <c:v>936009.97000000009</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7669,7 +7758,7 @@
                   <c:v>1322.6778035000002</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>430.76987950000006</c:v>
+                  <c:v>461.58137950000003</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -15963,8 +16052,12 @@
         <f>IF(AG29=100%,Y29," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AI29" s="64"/>
-      <c r="AJ29" s="1"/>
+      <c r="AI29" s="64">
+        <v>2</v>
+      </c>
+      <c r="AJ29" s="1" t="s">
+        <v>1410</v>
+      </c>
       <c r="AK29" s="65">
         <v>0</v>
       </c>
@@ -16416,25 +16509,39 @@
         <f>AVERAGE(U34:X34)</f>
         <v>36.241950000000003</v>
       </c>
-      <c r="Z34" s="10"/>
-      <c r="AA34" s="10"/>
-      <c r="AB34" s="10"/>
-      <c r="AC34" s="10"/>
+      <c r="Z34" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AA34" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AB34" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AC34" s="10" t="s">
+        <v>693</v>
+      </c>
       <c r="AD34" s="10"/>
       <c r="AE34" s="10"/>
-      <c r="AF34" s="10"/>
+      <c r="AF34" s="10" t="s">
+        <v>693</v>
+      </c>
       <c r="AG34" s="38">
         <f>COUNTIF(Z34:AF34,"X")/7</f>
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AH34" s="51" t="str">
         <f>IF(AG34=100%,Y34," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AI34" s="64"/>
-      <c r="AJ34" s="1"/>
+      <c r="AI34" s="64">
+        <v>2</v>
+      </c>
+      <c r="AJ34" s="1" t="s">
+        <v>1408</v>
+      </c>
       <c r="AK34" s="65">
-        <v>0</v>
+        <v>12810.71</v>
       </c>
       <c r="AL34" s="1"/>
       <c r="AM34" s="1" t="s">
@@ -16709,7 +16816,7 @@
       <c r="AL37" s="1"/>
       <c r="AM37" s="1"/>
     </row>
-    <row r="38" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:39" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A38" s="22" t="s">
         <v>89</v>
       </c>
@@ -16776,28 +16883,44 @@
         <f>AVERAGE(U38:X38)</f>
         <v>33.56026</v>
       </c>
-      <c r="Z38" s="10"/>
-      <c r="AA38" s="10"/>
-      <c r="AB38" s="10"/>
-      <c r="AC38" s="10"/>
+      <c r="Z38" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AA38" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AB38" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AC38" s="10" t="s">
+        <v>693</v>
+      </c>
       <c r="AD38" s="10"/>
       <c r="AE38" s="10"/>
-      <c r="AF38" s="10"/>
+      <c r="AF38" s="10" t="s">
+        <v>693</v>
+      </c>
       <c r="AG38" s="38">
         <f>COUNTIF(Z38:AF38,"X")/7</f>
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AH38" s="51" t="str">
         <f>IF(AG38=100%,Y38," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AI38" s="64"/>
-      <c r="AJ38" s="1"/>
+      <c r="AI38" s="64">
+        <v>6</v>
+      </c>
+      <c r="AJ38" s="2" t="s">
+        <v>1411</v>
+      </c>
       <c r="AK38" s="65">
         <v>0</v>
       </c>
       <c r="AL38" s="1"/>
-      <c r="AM38" s="1"/>
+      <c r="AM38" s="1" t="s">
+        <v>1412</v>
+      </c>
     </row>
     <row r="39" spans="1:39" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="19" t="s">
@@ -17063,15 +17186,19 @@
         <f>IF(AG41=100%,Y41," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AI41" s="64"/>
-      <c r="AJ41" s="1"/>
+      <c r="AI41" s="64">
+        <v>2</v>
+      </c>
+      <c r="AJ41" s="19" t="s">
+        <v>1413</v>
+      </c>
       <c r="AK41" s="65">
         <v>0</v>
       </c>
       <c r="AL41" s="1"/>
       <c r="AM41" s="1"/>
     </row>
-    <row r="42" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:39" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>97</v>
       </c>
@@ -17142,30 +17269,44 @@
         <f>AVERAGE(U42:X42)</f>
         <v>31.700772499999999</v>
       </c>
-      <c r="Z42" s="10"/>
-      <c r="AA42" s="10"/>
-      <c r="AB42" s="10"/>
-      <c r="AC42" s="10"/>
+      <c r="Z42" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AA42" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AB42" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AC42" s="10" t="s">
+        <v>693</v>
+      </c>
       <c r="AD42" s="10"/>
       <c r="AE42" s="10"/>
-      <c r="AF42" s="10"/>
+      <c r="AF42" s="10" t="s">
+        <v>693</v>
+      </c>
       <c r="AG42" s="38">
         <f>COUNTIF(Z42:AF42,"X")/7</f>
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AH42" s="51" t="str">
         <f>IF(AG42=100%,Y42," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AI42" s="64"/>
-      <c r="AJ42" s="1"/>
+      <c r="AI42" s="64">
+        <v>6</v>
+      </c>
+      <c r="AJ42" s="77" t="s">
+        <v>1409</v>
+      </c>
       <c r="AK42" s="65">
         <v>0</v>
       </c>
       <c r="AL42" s="1"/>
       <c r="AM42" s="1"/>
     </row>
-    <row r="43" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:39" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A43" s="22" t="s">
         <v>100</v>
       </c>
@@ -17249,8 +17390,12 @@
         <f>IF(AG43=100%,Y43," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AI43" s="64"/>
-      <c r="AJ43" s="1"/>
+      <c r="AI43" s="64">
+        <v>4</v>
+      </c>
+      <c r="AJ43" s="19" t="s">
+        <v>1414</v>
+      </c>
       <c r="AK43" s="65">
         <v>0</v>
       </c>
@@ -17418,30 +17563,48 @@
         <f>AVERAGE(U45:X45)</f>
         <v>30.811499999999995</v>
       </c>
-      <c r="Z45" s="10"/>
-      <c r="AA45" s="10"/>
-      <c r="AB45" s="10"/>
-      <c r="AC45" s="10"/>
-      <c r="AD45" s="10"/>
-      <c r="AE45" s="10"/>
-      <c r="AF45" s="10"/>
+      <c r="Z45" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AA45" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AB45" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AC45" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AD45" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AE45" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AF45" s="10" t="s">
+        <v>693</v>
+      </c>
       <c r="AG45" s="38">
         <f>COUNTIF(Z45:AF45,"X")/7</f>
-        <v>0</v>
-      </c>
-      <c r="AH45" s="51" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH45" s="51">
         <f>IF(AG45=100%,Y45," ")</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="AI45" s="64"/>
-      <c r="AJ45" s="1"/>
+        <v>30.811499999999995</v>
+      </c>
+      <c r="AI45" s="64">
+        <v>2</v>
+      </c>
+      <c r="AJ45" s="78" t="s">
+        <v>1415</v>
+      </c>
       <c r="AK45" s="65">
         <v>0</v>
       </c>
       <c r="AL45" s="1"/>
       <c r="AM45" s="1"/>
     </row>
-    <row r="46" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:39" s="26" customFormat="1" ht="51" x14ac:dyDescent="0.3">
       <c r="A46" s="22" t="s">
         <v>109</v>
       </c>
@@ -17525,15 +17688,19 @@
         <f>IF(AG46=100%,Y46," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AI46" s="64"/>
-      <c r="AJ46" s="1"/>
+      <c r="AI46" s="64">
+        <v>10</v>
+      </c>
+      <c r="AJ46" s="79" t="s">
+        <v>1418</v>
+      </c>
       <c r="AK46" s="65">
         <v>0</v>
       </c>
       <c r="AL46" s="1"/>
       <c r="AM46" s="1"/>
     </row>
-    <row r="47" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:39" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A47" s="22" t="s">
         <v>113</v>
       </c>
@@ -17617,8 +17784,12 @@
         <f>IF(AG47=100%,Y47," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AI47" s="64"/>
-      <c r="AJ47" s="1"/>
+      <c r="AI47" s="64">
+        <v>4</v>
+      </c>
+      <c r="AJ47" s="80" t="s">
+        <v>1419</v>
+      </c>
       <c r="AK47" s="65">
         <v>0</v>
       </c>
@@ -17709,8 +17880,12 @@
         <f>IF(AG48=100%,Y48," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AI48" s="64"/>
-      <c r="AJ48" s="1"/>
+      <c r="AI48" s="64">
+        <v>1</v>
+      </c>
+      <c r="AJ48" s="80" t="s">
+        <v>1420</v>
+      </c>
       <c r="AK48" s="65">
         <v>0</v>
       </c>
@@ -17979,8 +18154,12 @@
         <f>IF(AG51=100%,Y51," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AI51" s="64"/>
-      <c r="AJ51" s="1"/>
+      <c r="AI51" s="64">
+        <v>2</v>
+      </c>
+      <c r="AJ51" s="2" t="s">
+        <v>1416</v>
+      </c>
       <c r="AK51" s="65">
         <v>0</v>
       </c>
@@ -18075,7 +18254,7 @@
       <c r="AL52" s="1"/>
       <c r="AM52" s="1"/>
     </row>
-    <row r="53" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:39" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A53" s="22" t="s">
         <v>124</v>
       </c>
@@ -18157,8 +18336,12 @@
         <f>IF(AG53=100%,Y53," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AI53" s="64"/>
-      <c r="AJ53" s="1"/>
+      <c r="AI53" s="64">
+        <v>5</v>
+      </c>
+      <c r="AJ53" s="2" t="s">
+        <v>1417</v>
+      </c>
       <c r="AK53" s="65">
         <v>0</v>
       </c>
@@ -73092,15 +73275,15 @@
       </c>
       <c r="D3" s="52">
         <f>SUMIF(Controle!R:R,Formulas!A3,Controle!AH:AH)</f>
-        <v>430.76987950000006</v>
+        <v>461.58137950000003</v>
       </c>
       <c r="E3" s="49">
         <f t="shared" ref="E3:E5" si="0">D3/C3</f>
-        <v>0.26354378919303767</v>
+        <v>0.28239417740993544</v>
       </c>
       <c r="F3" s="66">
         <f>SUMIF(Controle!$R:$R,Formulas!A3,Controle!$AK:$AK)</f>
-        <v>38173.78</v>
+        <v>50984.49</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -73167,15 +73350,15 @@
       </c>
       <c r="D6" s="55">
         <f t="shared" si="1"/>
-        <v>1753.4476830000003</v>
+        <v>1784.2591830000001</v>
       </c>
       <c r="E6" s="56">
         <f>D6/C6</f>
-        <v>0.38521698042732067</v>
+        <v>0.39198599504207626</v>
       </c>
       <c r="F6" s="67">
         <f t="shared" si="1"/>
-        <v>923199.26000000013</v>
+        <v>936009.97000000009</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -73318,7 +73501,7 @@
       </c>
       <c r="E15" s="66">
         <f>SUMIF(Controle!$L:$L,A15,Controle!$AK:$AK)</f>
-        <v>0</v>
+        <v>12810.71</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -73883,7 +74066,7 @@
       </c>
       <c r="E42" s="68">
         <f>SUM(E10:E41)</f>
-        <v>923199.26</v>
+        <v>936009.97</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">

--- a/data/dados_atuais.xlsx
+++ b/data/dados_atuais.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delgadiadema.sharepoint.com/sites/GestoEstratgica/Documentos Compartilhados/Controle Master/BSW/Novo controle (Em processo)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="760" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC19E163-D936-4F25-812E-A708E260AC2E}"/>
+  <xr:revisionPtr revIDLastSave="835" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEAF20B0-9399-4F8A-8409-22F9172E6583}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E398004-7492-4AA0-94C2-EA9B761AAA49}"/>
   </bookViews>
   <sheets>
     <sheet name="Controle" sheetId="1" r:id="rId1"/>
-    <sheet name="Formulas" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Planilha1" sheetId="3" r:id="rId2"/>
+    <sheet name="Formulas" sheetId="2" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Controle!$A$2:$AL$707</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Formulas!$A$9:$D$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Formulas!$A$9:$D$41</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -321,7 +322,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6278" uniqueCount="1421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6327" uniqueCount="1427">
   <si>
     <t>Código
 Bobina Mâe</t>
@@ -4741,6 +4742,59 @@
   </si>
   <si>
     <t>DA000213Z</t>
+  </si>
+  <si>
+    <t>MB003601Z</t>
+  </si>
+  <si>
+    <t>GM000408Z / GM000409Z</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>VB000346LA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / DA000480Z / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MB003597LA / MB003598LA / MB003594LA / MB003595LA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / MB003607LA / MB003608LA / MB002301LA / MB003563Z / MB003564Z / MB003540Z / MB003541Z</t>
+    </r>
+  </si>
+  <si>
+    <t>DA000491AA / DA000492AA</t>
+  </si>
+  <si>
+    <t>MB002289Z / MB002290Z</t>
+  </si>
+  <si>
+    <t>MB002446LA / MB003670LA / MB003671LA</t>
   </si>
 </sst>
 </file>
@@ -4966,7 +5020,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5183,6 +5237,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5514,7 +5583,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.39198599504207626</c:v>
+                  <c:v>0.41414588085673165</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6432,7 +6501,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.28239417740993544</c:v>
+                  <c:v>0.34410514632080136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7758,7 +7827,7 @@
                   <c:v>1322.6778035000002</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>461.58137950000003</c:v>
+                  <c:v>562.44972749999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -18687,23 +18756,41 @@
         <f>AVERAGE(U57:X57)</f>
         <v>25.433042499999999</v>
       </c>
-      <c r="Z57" s="10"/>
-      <c r="AA57" s="10"/>
-      <c r="AB57" s="10"/>
-      <c r="AC57" s="10"/>
-      <c r="AD57" s="10"/>
-      <c r="AE57" s="10"/>
-      <c r="AF57" s="10"/>
+      <c r="Z57" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AA57" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AB57" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AC57" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AD57" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AE57" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AF57" s="10" t="s">
+        <v>693</v>
+      </c>
       <c r="AG57" s="38">
         <f>COUNTIF(Z57:AF57,"X")/7</f>
-        <v>0</v>
-      </c>
-      <c r="AH57" s="51" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH57" s="51">
         <f>IF(AG57=100%,Y57," ")</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="AI57" s="64"/>
-      <c r="AJ57" s="1"/>
+        <v>25.433042499999999</v>
+      </c>
+      <c r="AI57" s="64">
+        <v>1</v>
+      </c>
+      <c r="AJ57" s="81" t="s">
+        <v>1421</v>
+      </c>
       <c r="AK57" s="65">
         <v>0</v>
       </c>
@@ -19863,23 +19950,41 @@
         <f>AVERAGE(U70:X70)</f>
         <v>21.069427500000003</v>
       </c>
-      <c r="Z70" s="10"/>
-      <c r="AA70" s="10"/>
-      <c r="AB70" s="10"/>
-      <c r="AC70" s="10"/>
-      <c r="AD70" s="10"/>
-      <c r="AE70" s="10"/>
-      <c r="AF70" s="10"/>
+      <c r="Z70" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AA70" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AB70" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AC70" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AD70" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AE70" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AF70" s="10" t="s">
+        <v>693</v>
+      </c>
       <c r="AG70" s="38">
         <f>COUNTIF(Z70:AF70,"X")/7</f>
-        <v>0</v>
-      </c>
-      <c r="AH70" s="51" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH70" s="51">
         <f>IF(AG70=100%,Y70," ")</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="AI70" s="64"/>
-      <c r="AJ70" s="1"/>
+        <v>21.069427500000003</v>
+      </c>
+      <c r="AI70" s="64">
+        <v>2</v>
+      </c>
+      <c r="AJ70" s="82" t="s">
+        <v>1422</v>
+      </c>
       <c r="AK70" s="65">
         <v>0</v>
       </c>
@@ -19955,7 +20060,9 @@
         <f>AVERAGE(U71:X71)</f>
         <v>21.0627</v>
       </c>
-      <c r="Z71" s="10"/>
+      <c r="Z71" s="10" t="s">
+        <v>693</v>
+      </c>
       <c r="AA71" s="10"/>
       <c r="AB71" s="10"/>
       <c r="AC71" s="10"/>
@@ -19964,7 +20071,7 @@
       <c r="AF71" s="10"/>
       <c r="AG71" s="38">
         <f>COUNTIF(Z71:AF71,"X")/7</f>
-        <v>0</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="AH71" s="51" t="str">
         <f>IF(AG71=100%,Y71," ")</f>
@@ -20403,20 +20510,34 @@
         <f>AVERAGE(U76:X76)</f>
         <v>18.897327999999998</v>
       </c>
-      <c r="Z76" s="10"/>
-      <c r="AA76" s="10"/>
-      <c r="AB76" s="10"/>
-      <c r="AC76" s="10"/>
-      <c r="AD76" s="10"/>
-      <c r="AE76" s="10"/>
-      <c r="AF76" s="10"/>
+      <c r="Z76" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AA76" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AB76" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AC76" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AD76" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AE76" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AF76" s="10" t="s">
+        <v>693</v>
+      </c>
       <c r="AG76" s="38">
         <f>COUNTIF(Z76:AF76,"X")/7</f>
-        <v>0</v>
-      </c>
-      <c r="AH76" s="51" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH76" s="51">
         <f>IF(AG76=100%,Y76," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>18.897327999999998</v>
       </c>
       <c r="AI76" s="64"/>
       <c r="AJ76" s="1"/>
@@ -21782,7 +21903,7 @@
       <c r="AL91" s="1"/>
       <c r="AM91" s="1"/>
     </row>
-    <row r="92" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:39" s="26" customFormat="1" ht="71.400000000000006" x14ac:dyDescent="0.3">
       <c r="A92" s="22" t="s">
         <v>174</v>
       </c>
@@ -21855,23 +21976,41 @@
         <f>AVERAGE(U92:X92)</f>
         <v>14.416340000000002</v>
       </c>
-      <c r="Z92" s="10"/>
-      <c r="AA92" s="10"/>
-      <c r="AB92" s="10"/>
-      <c r="AC92" s="10"/>
-      <c r="AD92" s="10"/>
-      <c r="AE92" s="10"/>
-      <c r="AF92" s="10"/>
+      <c r="Z92" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AA92" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AB92" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AC92" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AD92" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AE92" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AF92" s="10" t="s">
+        <v>693</v>
+      </c>
       <c r="AG92" s="38">
         <f>COUNTIF(Z92:AF92,"X")/7</f>
-        <v>0</v>
-      </c>
-      <c r="AH92" s="51" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH92" s="51">
         <f>IF(AG92=100%,Y92," ")</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="AI92" s="64"/>
-      <c r="AJ92" s="1"/>
+        <v>14.416340000000002</v>
+      </c>
+      <c r="AI92" s="64">
+        <v>13</v>
+      </c>
+      <c r="AJ92" s="83" t="s">
+        <v>1423</v>
+      </c>
       <c r="AK92" s="65">
         <v>0</v>
       </c>
@@ -22039,23 +22178,41 @@
         <f>AVERAGE(U94:X94)</f>
         <v>14.171620000000001</v>
       </c>
-      <c r="Z94" s="10"/>
-      <c r="AA94" s="10"/>
-      <c r="AB94" s="10"/>
-      <c r="AC94" s="10"/>
-      <c r="AD94" s="10"/>
-      <c r="AE94" s="10"/>
-      <c r="AF94" s="10"/>
+      <c r="Z94" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AA94" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AB94" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AC94" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AD94" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AE94" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AF94" s="10" t="s">
+        <v>693</v>
+      </c>
       <c r="AG94" s="38">
         <f>COUNTIF(Z94:AF94,"X")/7</f>
-        <v>0</v>
-      </c>
-      <c r="AH94" s="51" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH94" s="51">
         <f>IF(AG94=100%,Y94," ")</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="AI94" s="64"/>
-      <c r="AJ94" s="1"/>
+        <v>14.171620000000001</v>
+      </c>
+      <c r="AI94" s="64">
+        <v>2</v>
+      </c>
+      <c r="AJ94" s="82" t="s">
+        <v>1424</v>
+      </c>
       <c r="AK94" s="65">
         <v>0</v>
       </c>
@@ -25337,23 +25494,39 @@
         <f>AVERAGE(U131:X131)</f>
         <v>6.8805899999999998</v>
       </c>
-      <c r="Z131" s="10"/>
-      <c r="AA131" s="10"/>
-      <c r="AB131" s="10"/>
-      <c r="AC131" s="10"/>
-      <c r="AD131" s="10"/>
-      <c r="AE131" s="10"/>
-      <c r="AF131" s="10"/>
+      <c r="Z131" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AA131" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AB131" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AC131" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AD131" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AE131" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="AF131" s="10" t="s">
+        <v>693</v>
+      </c>
       <c r="AG131" s="38">
         <f>COUNTIF(Z131:AF131,"X")/7</f>
-        <v>0</v>
-      </c>
-      <c r="AH131" s="51" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH131" s="51">
         <f>IF(AG131=100%,Y131," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>6.8805899999999998</v>
       </c>
       <c r="AI131" s="64"/>
-      <c r="AJ131" s="1"/>
+      <c r="AJ131" s="81" t="s">
+        <v>1425</v>
+      </c>
       <c r="AK131" s="65">
         <v>0</v>
       </c>
@@ -26420,7 +26593,7 @@
       <c r="AL143" s="1"/>
       <c r="AM143" s="1"/>
     </row>
-    <row r="144" spans="1:39" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:39" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A144" s="22" t="s">
         <v>228</v>
       </c>
@@ -26505,7 +26678,9 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI144" s="64"/>
-      <c r="AJ144" s="1"/>
+      <c r="AJ144" s="82" t="s">
+        <v>1426</v>
+      </c>
       <c r="AK144" s="65">
         <v>0</v>
       </c>
@@ -26591,7 +26766,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI145" s="64"/>
-      <c r="AJ145" s="1"/>
+      <c r="AJ145" s="84"/>
       <c r="AK145" s="65">
         <v>0</v>
       </c>
@@ -26683,7 +26858,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI146" s="64"/>
-      <c r="AJ146" s="1"/>
+      <c r="AJ146" s="85"/>
       <c r="AK146" s="65">
         <v>0</v>
       </c>
@@ -26775,7 +26950,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AI147" s="64"/>
-      <c r="AJ147" s="1"/>
+      <c r="AJ147" s="81"/>
       <c r="AK147" s="65">
         <v>0</v>
       </c>
@@ -73203,6 +73378,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{179A2EE8-1335-4D6B-B158-248E4A1AFF5C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D813743-8135-4F32-BACA-A0CD44F9427F}">
   <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -73275,11 +73465,11 @@
       </c>
       <c r="D3" s="52">
         <f>SUMIF(Controle!R:R,Formulas!A3,Controle!AH:AH)</f>
-        <v>461.58137950000003</v>
+        <v>562.44972749999999</v>
       </c>
       <c r="E3" s="49">
         <f t="shared" ref="E3:E5" si="0">D3/C3</f>
-        <v>0.28239417740993544</v>
+        <v>0.34410514632080136</v>
       </c>
       <c r="F3" s="66">
         <f>SUMIF(Controle!$R:$R,Formulas!A3,Controle!$AK:$AK)</f>
@@ -73350,11 +73540,11 @@
       </c>
       <c r="D6" s="55">
         <f t="shared" si="1"/>
-        <v>1784.2591830000001</v>
+        <v>1885.1275310000001</v>
       </c>
       <c r="E6" s="56">
         <f>D6/C6</f>
-        <v>0.39198599504207626</v>
+        <v>0.41414588085673165</v>
       </c>
       <c r="F6" s="67">
         <f t="shared" si="1"/>

--- a/data/dados_atuais.xlsx
+++ b/data/dados_atuais.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1211" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D10C9E9F-BA43-4A12-9434-74D38E1AF5AD}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3E398004-7492-4AA0-94C2-EA9B761AAA49}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E398004-7492-4AA0-94C2-EA9B761AAA49}"/>
   </bookViews>
   <sheets>
     <sheet name="Controle" sheetId="1" r:id="rId1"/>

--- a/data/dados_atuais.xlsx
+++ b/data/dados_atuais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delgadiadema.sharepoint.com/sites/GestoEstratgica/Documentos Compartilhados/Controle Master/BSW/Novo controle (Em processo)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1636" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C46CBE5-0A97-4F7C-A26F-C4660965C891}"/>
+  <xr:revisionPtr revIDLastSave="1810" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{548A54A1-6758-49FA-BE07-AD68F7D5BAB3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E398004-7492-4AA0-94C2-EA9B761AAA49}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="23016" windowHeight="12216" xr2:uid="{3E398004-7492-4AA0-94C2-EA9B761AAA49}"/>
   </bookViews>
   <sheets>
     <sheet name="Controle" sheetId="1" r:id="rId1"/>
@@ -322,7 +322,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7019" uniqueCount="1454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7052" uniqueCount="1470">
   <si>
     <t>Código
 Bobina Mâe</t>
@@ -4808,9 +4808,6 @@
     <t>Ganho por usina</t>
   </si>
   <si>
-    <t>Primeiro Ganho previsto (MÊS/Ano)</t>
-  </si>
-  <si>
     <t>"Pulmão" da Saveiro, sem proposta de KAIZEN.</t>
   </si>
   <si>
@@ -4882,6 +4879,57 @@
   </si>
   <si>
     <t>Ganho MENSAL</t>
+  </si>
+  <si>
+    <t>VW000942AB / VW000943AB</t>
+  </si>
+  <si>
+    <t>VW000812Z</t>
+  </si>
+  <si>
+    <t>VW000947AA</t>
+  </si>
+  <si>
+    <t>VW000983AA / VW000984AA</t>
+  </si>
+  <si>
+    <t>VW000944AA / VW000945Z</t>
+  </si>
+  <si>
+    <t>VW001225AA</t>
+  </si>
+  <si>
+    <t>VW000956Z / VW000957Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primeiro Ganho previsto </t>
+  </si>
+  <si>
+    <t>VW000952Z / VW000953Z</t>
+  </si>
+  <si>
+    <t>VW000870Z</t>
+  </si>
+  <si>
+    <t>VW001217AC</t>
+  </si>
+  <si>
+    <t>VW000927AB / VW000927AC</t>
+  </si>
+  <si>
+    <t>VW000927AD / VW000927AE</t>
+  </si>
+  <si>
+    <t>VW000940AA / VW000941AA</t>
+  </si>
+  <si>
+    <t>VW001217AB</t>
+  </si>
+  <si>
+    <t>VW001220Z / VW001221Z</t>
+  </si>
+  <si>
+    <t>VW000946AD</t>
   </si>
 </sst>
 </file>
@@ -4895,7 +4943,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
     <numFmt numFmtId="166" formatCode="mmmm\,\ yyyy;@"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5013,11 +5061,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
@@ -5025,7 +5068,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5059,6 +5102,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5121,7 +5170,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5352,22 +5401,25 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Moeda" xfId="5" builtinId="4"/>
@@ -7277,7 +7329,7 @@
                   <c:v>200466.71999999994</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>100757.38500000001</c:v>
+                  <c:v>125302.11083333334</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -7569,7 +7621,7 @@
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>392916.05583333329</c:v>
+                  <c:v>417460.78166666662</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12728,7 +12780,7 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Gráfico 11">
+        <xdr:cNvPr id="12" name="Gráfico 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B54A52A7-FB35-49E2-8FF2-5CDCD47387D0}"/>
@@ -13251,7 +13303,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA437EE-405D-4A43-9EB9-23F1BEB36011}">
   <sheetPr codeName="Folha1"/>
-  <dimension ref="A1:AO717"/>
+  <dimension ref="A2:AO717"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
@@ -13290,11 +13342,9 @@
     <col min="37" max="37" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="14.88671875" hidden="1" customWidth="1"/>
     <col min="39" max="39" width="91.109375" customWidth="1"/>
-    <col min="40" max="40" width="27.88671875" style="50" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="18.21875" style="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="151.35" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:40" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A2" s="39" t="s">
         <v>0</v>
@@ -13404,8 +13454,8 @@
       <c r="AJ2" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="AK2" s="88" t="s">
-        <v>1453</v>
+      <c r="AK2" s="90" t="s">
+        <v>1452</v>
       </c>
       <c r="AL2" s="44" t="s">
         <v>36</v>
@@ -13413,8 +13463,8 @@
       <c r="AM2" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="AN2" s="44" t="s">
-        <v>1431</v>
+      <c r="AN2" s="91" t="s">
+        <v>1460</v>
       </c>
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.3">
@@ -13527,12 +13577,12 @@
         <v>0</v>
       </c>
       <c r="AL3" s="1"/>
-      <c r="AM3" s="86" t="s">
+      <c r="AM3" s="87" t="s">
         <v>72</v>
       </c>
-      <c r="AN3" s="85"/>
+      <c r="AN3" s="89"/>
     </row>
-    <row r="4" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:40" s="26" customFormat="1" ht="132.6" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
         <v>50</v>
       </c>
@@ -13642,10 +13692,10 @@
         <v>22693.47</v>
       </c>
       <c r="AL4" s="1"/>
-      <c r="AM4" s="87" t="s">
+      <c r="AM4" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="AN4" s="85"/>
+      <c r="AN4" s="89"/>
     </row>
     <row r="5" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
@@ -13758,9 +13808,9 @@
       </c>
       <c r="AL5" s="1"/>
       <c r="AM5" s="1" t="s">
-        <v>1433</v>
-      </c>
-      <c r="AN5" s="85"/>
+        <v>1432</v>
+      </c>
+      <c r="AN5" s="89"/>
     </row>
     <row r="6" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
@@ -13867,9 +13917,9 @@
       </c>
       <c r="AL6" s="1"/>
       <c r="AM6" s="1" t="s">
-        <v>1434</v>
-      </c>
-      <c r="AN6" s="85"/>
+        <v>1433</v>
+      </c>
+      <c r="AN6" s="89"/>
     </row>
     <row r="7" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="22" t="s">
@@ -13982,9 +14032,9 @@
       </c>
       <c r="AL7" s="1"/>
       <c r="AM7" s="1" t="s">
-        <v>1432</v>
-      </c>
-      <c r="AN7" s="85"/>
+        <v>1431</v>
+      </c>
+      <c r="AN7" s="89"/>
     </row>
     <row r="8" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
@@ -14081,7 +14131,7 @@
       </c>
       <c r="AL8" s="1"/>
       <c r="AM8" s="1"/>
-      <c r="AN8" s="85"/>
+      <c r="AN8" s="89"/>
     </row>
     <row r="9" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
@@ -14196,7 +14246,7 @@
       <c r="AM9" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="AN9" s="85"/>
+      <c r="AN9" s="89"/>
     </row>
     <row r="10" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -14309,9 +14359,9 @@
       </c>
       <c r="AL10" s="1"/>
       <c r="AM10" s="1" t="s">
-        <v>1433</v>
-      </c>
-      <c r="AN10" s="85"/>
+        <v>1432</v>
+      </c>
+      <c r="AN10" s="89"/>
     </row>
     <row r="11" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="22" t="s">
@@ -14420,9 +14470,9 @@
       </c>
       <c r="AL11" s="1"/>
       <c r="AM11" s="1" t="s">
-        <v>1435</v>
-      </c>
-      <c r="AN11" s="85"/>
+        <v>1434</v>
+      </c>
+      <c r="AN11" s="89"/>
     </row>
     <row r="12" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
@@ -14519,7 +14569,7 @@
       </c>
       <c r="AL12" s="1"/>
       <c r="AM12" s="1"/>
-      <c r="AN12" s="85"/>
+      <c r="AN12" s="89"/>
     </row>
     <row r="13" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="22" t="s">
@@ -14614,9 +14664,9 @@
       </c>
       <c r="AL13" s="1"/>
       <c r="AM13" s="1"/>
-      <c r="AN13" s="85"/>
+      <c r="AN13" s="89"/>
     </row>
-    <row r="14" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
         <v>109</v>
       </c>
@@ -14719,7 +14769,7 @@
       </c>
       <c r="AL14" s="1"/>
       <c r="AM14" s="1"/>
-      <c r="AN14" s="85"/>
+      <c r="AN14" s="89"/>
     </row>
     <row r="15" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="22" t="s">
@@ -14812,9 +14862,9 @@
       </c>
       <c r="AL15" s="1"/>
       <c r="AM15" s="1"/>
-      <c r="AN15" s="85"/>
+      <c r="AN15" s="89"/>
     </row>
-    <row r="16" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:40" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
         <v>116</v>
       </c>
@@ -14921,9 +14971,9 @@
       </c>
       <c r="AL16" s="1"/>
       <c r="AM16" s="1"/>
-      <c r="AN16" s="85"/>
+      <c r="AN16" s="89"/>
     </row>
-    <row r="17" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A17" s="22" t="s">
         <v>120</v>
       </c>
@@ -15018,7 +15068,7 @@
       </c>
       <c r="AL17" s="1"/>
       <c r="AM17" s="1"/>
-      <c r="AN17" s="85"/>
+      <c r="AN17" s="89"/>
     </row>
     <row r="18" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
@@ -15113,7 +15163,7 @@
       </c>
       <c r="AL18" s="1"/>
       <c r="AM18" s="1"/>
-      <c r="AN18" s="85"/>
+      <c r="AN18" s="89"/>
     </row>
     <row r="19" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="22" t="s">
@@ -15210,7 +15260,7 @@
       </c>
       <c r="AL19" s="1"/>
       <c r="AM19" s="1"/>
-      <c r="AN19" s="85"/>
+      <c r="AN19" s="89"/>
     </row>
     <row r="20" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
@@ -15309,7 +15359,7 @@
       <c r="AM20" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="AN20" s="85"/>
+      <c r="AN20" s="89"/>
     </row>
     <row r="21" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="22" t="s">
@@ -15420,7 +15470,7 @@
       </c>
       <c r="AL21" s="1"/>
       <c r="AM21" s="1"/>
-      <c r="AN21" s="85"/>
+      <c r="AN21" s="89"/>
     </row>
     <row r="22" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
@@ -15513,7 +15563,7 @@
       </c>
       <c r="AL22" s="1"/>
       <c r="AM22" s="1"/>
-      <c r="AN22" s="85"/>
+      <c r="AN22" s="89"/>
     </row>
     <row r="23" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="22" t="s">
@@ -15624,7 +15674,7 @@
       </c>
       <c r="AL23" s="1"/>
       <c r="AM23" s="1"/>
-      <c r="AN23" s="85"/>
+      <c r="AN23" s="89"/>
     </row>
     <row r="24" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
@@ -15717,7 +15767,7 @@
       </c>
       <c r="AL24" s="1"/>
       <c r="AM24" s="1"/>
-      <c r="AN24" s="85"/>
+      <c r="AN24" s="89"/>
     </row>
     <row r="25" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="22" t="s">
@@ -15810,7 +15860,7 @@
       </c>
       <c r="AL25" s="1"/>
       <c r="AM25" s="1"/>
-      <c r="AN25" s="85"/>
+      <c r="AN25" s="89"/>
     </row>
     <row r="26" spans="1:40" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
@@ -15905,7 +15955,7 @@
       </c>
       <c r="AL26" s="1"/>
       <c r="AM26" s="1"/>
-      <c r="AN26" s="85"/>
+      <c r="AN26" s="89"/>
     </row>
     <row r="27" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="22" t="s">
@@ -15998,7 +16048,7 @@
       </c>
       <c r="AL27" s="1"/>
       <c r="AM27" s="1"/>
-      <c r="AN27" s="85"/>
+      <c r="AN27" s="89"/>
     </row>
     <row r="28" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="22" t="s">
@@ -16093,7 +16143,7 @@
       </c>
       <c r="AL28" s="1"/>
       <c r="AM28" s="62"/>
-      <c r="AN28" s="85"/>
+      <c r="AN28" s="89"/>
     </row>
     <row r="29" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="22" t="s">
@@ -16188,7 +16238,7 @@
       </c>
       <c r="AL29" s="1"/>
       <c r="AM29" s="1"/>
-      <c r="AN29" s="85"/>
+      <c r="AN29" s="89"/>
     </row>
     <row r="30" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
@@ -16281,7 +16331,7 @@
       </c>
       <c r="AL30" s="1"/>
       <c r="AM30" s="1"/>
-      <c r="AN30" s="85"/>
+      <c r="AN30" s="89"/>
     </row>
     <row r="31" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="22" t="s">
@@ -16370,7 +16420,7 @@
       <c r="AM31" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="AN31" s="85"/>
+      <c r="AN31" s="89"/>
     </row>
     <row r="32" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
@@ -16483,7 +16533,7 @@
       </c>
       <c r="AL32" s="1"/>
       <c r="AM32" s="1"/>
-      <c r="AN32" s="85"/>
+      <c r="AN32" s="89"/>
     </row>
     <row r="33" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="22" t="s">
@@ -16576,7 +16626,7 @@
       </c>
       <c r="AL33" s="1"/>
       <c r="AM33" s="1"/>
-      <c r="AN33" s="85"/>
+      <c r="AN33" s="89"/>
     </row>
     <row r="34" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
@@ -16671,7 +16721,7 @@
       <c r="AM34" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="AN34" s="85"/>
+      <c r="AN34" s="89"/>
     </row>
     <row r="35" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="22" t="s">
@@ -16766,7 +16816,7 @@
       </c>
       <c r="AL35" s="1"/>
       <c r="AM35" s="1"/>
-      <c r="AN35" s="85"/>
+      <c r="AN35" s="89"/>
     </row>
     <row r="36" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="22" t="s">
@@ -16861,7 +16911,7 @@
       </c>
       <c r="AL36" s="1"/>
       <c r="AM36" s="1"/>
-      <c r="AN36" s="85"/>
+      <c r="AN36" s="89"/>
     </row>
     <row r="37" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="22" t="s">
@@ -16948,7 +16998,7 @@
       </c>
       <c r="AL37" s="1"/>
       <c r="AM37" s="1"/>
-      <c r="AN37" s="85"/>
+      <c r="AN37" s="89"/>
     </row>
     <row r="38" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="22" t="s">
@@ -17051,9 +17101,9 @@
       <c r="AM38" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="AN38" s="85"/>
+      <c r="AN38" s="89"/>
     </row>
-    <row r="39" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:40" s="26" customFormat="1" ht="71.400000000000006" x14ac:dyDescent="0.3">
       <c r="A39" s="22" t="s">
         <v>195</v>
       </c>
@@ -17166,7 +17216,7 @@
       </c>
       <c r="AL39" s="1"/>
       <c r="AM39" s="1"/>
-      <c r="AN39" s="85"/>
+      <c r="AN39" s="89"/>
     </row>
     <row r="40" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
@@ -17259,7 +17309,7 @@
       </c>
       <c r="AL40" s="1"/>
       <c r="AM40" s="1"/>
-      <c r="AN40" s="85"/>
+      <c r="AN40" s="89"/>
     </row>
     <row r="41" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="22" t="s">
@@ -17354,7 +17404,7 @@
       <c r="AM41" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="AN41" s="85"/>
+      <c r="AN41" s="89"/>
     </row>
     <row r="42" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
@@ -17449,7 +17499,7 @@
       <c r="AM42" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="AN42" s="85"/>
+      <c r="AN42" s="89"/>
     </row>
     <row r="43" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="22" t="s">
@@ -17542,7 +17592,7 @@
       </c>
       <c r="AL43" s="1"/>
       <c r="AM43" s="1"/>
-      <c r="AN43" s="85"/>
+      <c r="AN43" s="89"/>
     </row>
     <row r="44" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="22" t="s">
@@ -17655,7 +17705,7 @@
       </c>
       <c r="AL44" s="1"/>
       <c r="AM44" s="1"/>
-      <c r="AN44" s="85"/>
+      <c r="AN44" s="89"/>
     </row>
     <row r="45" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="22" t="s">
@@ -17748,7 +17798,7 @@
       <c r="AM45" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="AN45" s="85"/>
+      <c r="AN45" s="89"/>
     </row>
     <row r="46" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="22" t="s">
@@ -17841,7 +17891,7 @@
       </c>
       <c r="AL46" s="1"/>
       <c r="AM46" s="1"/>
-      <c r="AN46" s="85"/>
+      <c r="AN46" s="89"/>
     </row>
     <row r="47" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="22" t="s">
@@ -17934,7 +17984,7 @@
       </c>
       <c r="AL47" s="1"/>
       <c r="AM47" s="1"/>
-      <c r="AN47" s="85"/>
+      <c r="AN47" s="89"/>
     </row>
     <row r="48" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="22" t="s">
@@ -18027,7 +18077,7 @@
       </c>
       <c r="AL48" s="1"/>
       <c r="AM48" s="1"/>
-      <c r="AN48" s="85"/>
+      <c r="AN48" s="89"/>
     </row>
     <row r="49" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="22" t="s">
@@ -18120,7 +18170,7 @@
       </c>
       <c r="AL49" s="1"/>
       <c r="AM49" s="1"/>
-      <c r="AN49" s="85"/>
+      <c r="AN49" s="89"/>
     </row>
     <row r="50" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="22" t="s">
@@ -18213,7 +18263,7 @@
       </c>
       <c r="AL50" s="1"/>
       <c r="AM50" s="1"/>
-      <c r="AN50" s="85"/>
+      <c r="AN50" s="89"/>
     </row>
     <row r="51" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="22" t="s">
@@ -18306,7 +18356,7 @@
       </c>
       <c r="AL51" s="1"/>
       <c r="AM51" s="1"/>
-      <c r="AN51" s="85"/>
+      <c r="AN51" s="89"/>
     </row>
     <row r="52" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="22" t="s">
@@ -18399,7 +18449,7 @@
       </c>
       <c r="AL52" s="1"/>
       <c r="AM52" s="1"/>
-      <c r="AN52" s="85"/>
+      <c r="AN52" s="89"/>
     </row>
     <row r="53" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="22" t="s">
@@ -18492,7 +18542,7 @@
       </c>
       <c r="AL53" s="1"/>
       <c r="AM53" s="1"/>
-      <c r="AN53" s="85"/>
+      <c r="AN53" s="89"/>
     </row>
     <row r="54" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="22" t="s">
@@ -18585,7 +18635,7 @@
       </c>
       <c r="AL54" s="1"/>
       <c r="AM54" s="1"/>
-      <c r="AN54" s="85"/>
+      <c r="AN54" s="89"/>
     </row>
     <row r="55" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="22" t="s">
@@ -18678,7 +18728,7 @@
       </c>
       <c r="AL55" s="1"/>
       <c r="AM55" s="1"/>
-      <c r="AN55" s="85"/>
+      <c r="AN55" s="89"/>
     </row>
     <row r="56" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="22" t="s">
@@ -18791,7 +18841,7 @@
       </c>
       <c r="AL56" s="1"/>
       <c r="AM56" s="1"/>
-      <c r="AN56" s="85"/>
+      <c r="AN56" s="89"/>
     </row>
     <row r="57" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="22" t="s">
@@ -18884,7 +18934,7 @@
       </c>
       <c r="AL57" s="1"/>
       <c r="AM57" s="1"/>
-      <c r="AN57" s="85"/>
+      <c r="AN57" s="89"/>
     </row>
     <row r="58" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="22" t="s">
@@ -18977,7 +19027,7 @@
       </c>
       <c r="AL58" s="1"/>
       <c r="AM58" s="1"/>
-      <c r="AN58" s="85"/>
+      <c r="AN58" s="89"/>
     </row>
     <row r="59" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="22" t="s">
@@ -19070,9 +19120,9 @@
       </c>
       <c r="AL59" s="1"/>
       <c r="AM59" s="1"/>
-      <c r="AN59" s="85"/>
+      <c r="AN59" s="89"/>
     </row>
-    <row r="60" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A60" s="22" t="s">
         <v>260</v>
       </c>
@@ -19179,7 +19229,7 @@
       </c>
       <c r="AL60" s="1"/>
       <c r="AM60" s="1"/>
-      <c r="AN60" s="85"/>
+      <c r="AN60" s="89"/>
     </row>
     <row r="61" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="22" t="s">
@@ -19288,7 +19338,7 @@
       </c>
       <c r="AL61" s="1"/>
       <c r="AM61" s="1"/>
-      <c r="AN61" s="85"/>
+      <c r="AN61" s="89"/>
     </row>
     <row r="62" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="22" t="s">
@@ -19381,7 +19431,7 @@
       </c>
       <c r="AL62" s="1"/>
       <c r="AM62" s="1"/>
-      <c r="AN62" s="85"/>
+      <c r="AN62" s="89"/>
     </row>
     <row r="63" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="22" t="s">
@@ -19474,7 +19524,7 @@
       </c>
       <c r="AL63" s="1"/>
       <c r="AM63" s="1"/>
-      <c r="AN63" s="85"/>
+      <c r="AN63" s="89"/>
     </row>
     <row r="64" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="22" t="s">
@@ -19567,7 +19617,7 @@
       </c>
       <c r="AL64" s="1"/>
       <c r="AM64" s="1"/>
-      <c r="AN64" s="85"/>
+      <c r="AN64" s="89"/>
     </row>
     <row r="65" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="22" t="s">
@@ -19662,7 +19712,7 @@
       </c>
       <c r="AL65" s="1"/>
       <c r="AM65" s="1"/>
-      <c r="AN65" s="85"/>
+      <c r="AN65" s="89"/>
     </row>
     <row r="66" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="22" t="s">
@@ -19757,7 +19807,7 @@
       </c>
       <c r="AL66" s="1"/>
       <c r="AM66" s="1"/>
-      <c r="AN66" s="85"/>
+      <c r="AN66" s="89"/>
     </row>
     <row r="67" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="22" t="s">
@@ -19846,7 +19896,7 @@
       </c>
       <c r="AL67" s="1"/>
       <c r="AM67" s="1"/>
-      <c r="AN67" s="85"/>
+      <c r="AN67" s="89"/>
     </row>
     <row r="68" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="22" t="s">
@@ -19939,7 +19989,7 @@
       </c>
       <c r="AL68" s="1"/>
       <c r="AM68" s="1"/>
-      <c r="AN68" s="85"/>
+      <c r="AN68" s="89"/>
     </row>
     <row r="69" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="22" t="s">
@@ -20034,7 +20084,7 @@
       </c>
       <c r="AL69" s="1"/>
       <c r="AM69" s="1"/>
-      <c r="AN69" s="85"/>
+      <c r="AN69" s="89"/>
     </row>
     <row r="70" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="22" t="s">
@@ -20127,7 +20177,7 @@
       </c>
       <c r="AL70" s="1"/>
       <c r="AM70" s="1"/>
-      <c r="AN70" s="85"/>
+      <c r="AN70" s="89"/>
     </row>
     <row r="71" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="22" t="s">
@@ -20220,7 +20270,7 @@
       </c>
       <c r="AL71" s="1"/>
       <c r="AM71" s="1"/>
-      <c r="AN71" s="85"/>
+      <c r="AN71" s="89"/>
     </row>
     <row r="72" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="22" t="s">
@@ -20315,7 +20365,7 @@
       </c>
       <c r="AL72" s="1"/>
       <c r="AM72" s="1"/>
-      <c r="AN72" s="85"/>
+      <c r="AN72" s="89"/>
     </row>
     <row r="73" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="22" t="s">
@@ -20408,7 +20458,7 @@
       </c>
       <c r="AL73" s="1"/>
       <c r="AM73" s="1"/>
-      <c r="AN73" s="85"/>
+      <c r="AN73" s="89"/>
     </row>
     <row r="74" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="22" t="s">
@@ -20501,7 +20551,7 @@
       </c>
       <c r="AL74" s="1"/>
       <c r="AM74" s="1"/>
-      <c r="AN74" s="85"/>
+      <c r="AN74" s="89"/>
     </row>
     <row r="75" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="22" t="s">
@@ -20592,7 +20642,7 @@
       </c>
       <c r="AL75" s="1"/>
       <c r="AM75" s="1"/>
-      <c r="AN75" s="85"/>
+      <c r="AN75" s="89"/>
     </row>
     <row r="76" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="22" t="s">
@@ -20685,7 +20735,7 @@
       </c>
       <c r="AL76" s="1"/>
       <c r="AM76" s="1"/>
-      <c r="AN76" s="85"/>
+      <c r="AN76" s="89"/>
     </row>
     <row r="77" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="22" t="s">
@@ -20776,7 +20826,7 @@
       </c>
       <c r="AL77" s="1"/>
       <c r="AM77" s="1"/>
-      <c r="AN77" s="85"/>
+      <c r="AN77" s="89"/>
     </row>
     <row r="78" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="22" t="s">
@@ -20883,7 +20933,7 @@
       </c>
       <c r="AL78" s="1"/>
       <c r="AM78" s="1"/>
-      <c r="AN78" s="85"/>
+      <c r="AN78" s="89"/>
     </row>
     <row r="79" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" s="22" t="s">
@@ -20976,7 +21026,7 @@
       </c>
       <c r="AL79" s="1"/>
       <c r="AM79" s="1"/>
-      <c r="AN79" s="85"/>
+      <c r="AN79" s="89"/>
     </row>
     <row r="80" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A80" s="22" t="s">
@@ -21083,7 +21133,7 @@
       </c>
       <c r="AL80" s="1"/>
       <c r="AM80" s="1"/>
-      <c r="AN80" s="85"/>
+      <c r="AN80" s="89"/>
     </row>
     <row r="81" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A81" s="22" t="s">
@@ -21192,7 +21242,7 @@
       </c>
       <c r="AL81" s="1"/>
       <c r="AM81" s="1"/>
-      <c r="AN81" s="85"/>
+      <c r="AN81" s="89"/>
     </row>
     <row r="82" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="22" t="s">
@@ -21285,7 +21335,7 @@
       </c>
       <c r="AL82" s="1"/>
       <c r="AM82" s="1"/>
-      <c r="AN82" s="85"/>
+      <c r="AN82" s="89"/>
     </row>
     <row r="83" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A83" s="22" t="s">
@@ -21378,7 +21428,7 @@
       </c>
       <c r="AL83" s="1"/>
       <c r="AM83" s="1"/>
-      <c r="AN83" s="85"/>
+      <c r="AN83" s="89"/>
     </row>
     <row r="84" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A84" s="22" t="s">
@@ -21487,7 +21537,7 @@
       </c>
       <c r="AL84" s="1"/>
       <c r="AM84" s="1"/>
-      <c r="AN84" s="85"/>
+      <c r="AN84" s="89"/>
     </row>
     <row r="85" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="22" t="s">
@@ -21580,7 +21630,7 @@
       </c>
       <c r="AL85" s="1"/>
       <c r="AM85" s="1"/>
-      <c r="AN85" s="85"/>
+      <c r="AN85" s="89"/>
     </row>
     <row r="86" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="22" t="s">
@@ -21669,7 +21719,7 @@
       </c>
       <c r="AL86" s="1"/>
       <c r="AM86" s="1"/>
-      <c r="AN86" s="85"/>
+      <c r="AN86" s="89"/>
     </row>
     <row r="87" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="22" t="s">
@@ -21762,7 +21812,7 @@
       </c>
       <c r="AL87" s="1"/>
       <c r="AM87" s="1"/>
-      <c r="AN87" s="85"/>
+      <c r="AN87" s="89"/>
     </row>
     <row r="88" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A88" s="22" t="s">
@@ -21871,7 +21921,7 @@
       </c>
       <c r="AL88" s="1"/>
       <c r="AM88" s="1"/>
-      <c r="AN88" s="85"/>
+      <c r="AN88" s="89"/>
     </row>
     <row r="89" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="22" t="s">
@@ -21964,7 +22014,7 @@
       </c>
       <c r="AL89" s="1"/>
       <c r="AM89" s="1"/>
-      <c r="AN89" s="85"/>
+      <c r="AN89" s="89"/>
     </row>
     <row r="90" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A90" s="22" t="s">
@@ -22057,7 +22107,7 @@
       </c>
       <c r="AL90" s="1"/>
       <c r="AM90" s="1"/>
-      <c r="AN90" s="85"/>
+      <c r="AN90" s="89"/>
     </row>
     <row r="91" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A91" s="22" t="s">
@@ -22150,7 +22200,7 @@
       </c>
       <c r="AL91" s="1"/>
       <c r="AM91" s="1"/>
-      <c r="AN91" s="85"/>
+      <c r="AN91" s="89"/>
     </row>
     <row r="92" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A92" s="22" t="s">
@@ -22243,7 +22293,7 @@
       </c>
       <c r="AL92" s="1"/>
       <c r="AM92" s="1"/>
-      <c r="AN92" s="85"/>
+      <c r="AN92" s="89"/>
     </row>
     <row r="93" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A93" s="22" t="s">
@@ -22348,7 +22398,7 @@
       </c>
       <c r="AL93" s="1"/>
       <c r="AM93" s="1"/>
-      <c r="AN93" s="85"/>
+      <c r="AN93" s="89"/>
     </row>
     <row r="94" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A94" s="22" t="s">
@@ -22441,7 +22491,7 @@
       </c>
       <c r="AL94" s="1"/>
       <c r="AM94" s="1"/>
-      <c r="AN94" s="85"/>
+      <c r="AN94" s="89"/>
     </row>
     <row r="95" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A95" s="15" t="s">
@@ -22534,7 +22584,7 @@
       </c>
       <c r="AL95" s="1"/>
       <c r="AM95" s="1"/>
-      <c r="AN95" s="85"/>
+      <c r="AN95" s="89"/>
     </row>
     <row r="96" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A96" s="22" t="s">
@@ -22641,7 +22691,7 @@
       </c>
       <c r="AL96" s="1"/>
       <c r="AM96" s="1"/>
-      <c r="AN96" s="85"/>
+      <c r="AN96" s="89"/>
     </row>
     <row r="97" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A97" s="22" t="s">
@@ -22728,7 +22778,7 @@
       </c>
       <c r="AL97" s="1"/>
       <c r="AM97" s="1"/>
-      <c r="AN97" s="85"/>
+      <c r="AN97" s="89"/>
     </row>
     <row r="98" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
@@ -22837,7 +22887,7 @@
       </c>
       <c r="AL98" s="1"/>
       <c r="AM98" s="1"/>
-      <c r="AN98" s="85"/>
+      <c r="AN98" s="89"/>
     </row>
     <row r="99" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A99" s="22" t="s">
@@ -22946,7 +22996,7 @@
       </c>
       <c r="AL99" s="1"/>
       <c r="AM99" s="1"/>
-      <c r="AN99" s="85"/>
+      <c r="AN99" s="89"/>
     </row>
     <row r="100" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="22" t="s">
@@ -23039,7 +23089,7 @@
       </c>
       <c r="AL100" s="1"/>
       <c r="AM100" s="1"/>
-      <c r="AN100" s="85"/>
+      <c r="AN100" s="89"/>
     </row>
     <row r="101" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A101" s="22" t="s">
@@ -23132,7 +23182,7 @@
       </c>
       <c r="AL101" s="1"/>
       <c r="AM101" s="1"/>
-      <c r="AN101" s="85"/>
+      <c r="AN101" s="89"/>
     </row>
     <row r="102" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A102" s="22" t="s">
@@ -23221,7 +23271,7 @@
       </c>
       <c r="AL102" s="1"/>
       <c r="AM102" s="1"/>
-      <c r="AN102" s="85"/>
+      <c r="AN102" s="89"/>
     </row>
     <row r="103" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A103" s="22" t="s">
@@ -23314,7 +23364,7 @@
       </c>
       <c r="AL103" s="1"/>
       <c r="AM103" s="1"/>
-      <c r="AN103" s="85"/>
+      <c r="AN103" s="89"/>
     </row>
     <row r="104" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A104" s="22" t="s">
@@ -23409,7 +23459,7 @@
       </c>
       <c r="AL104" s="1"/>
       <c r="AM104" s="1"/>
-      <c r="AN104" s="85"/>
+      <c r="AN104" s="89"/>
     </row>
     <row r="105" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A105" s="22" t="s">
@@ -23496,7 +23546,7 @@
       </c>
       <c r="AL105" s="1"/>
       <c r="AM105" s="1"/>
-      <c r="AN105" s="85"/>
+      <c r="AN105" s="89"/>
     </row>
     <row r="106" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A106" s="22" t="s">
@@ -23589,7 +23639,7 @@
       </c>
       <c r="AL106" s="1"/>
       <c r="AM106" s="1"/>
-      <c r="AN106" s="85"/>
+      <c r="AN106" s="89"/>
     </row>
     <row r="107" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A107" s="15" t="s">
@@ -23676,7 +23726,7 @@
       </c>
       <c r="AL107" s="1"/>
       <c r="AM107" s="1"/>
-      <c r="AN107" s="85"/>
+      <c r="AN107" s="89"/>
     </row>
     <row r="108" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A108" s="22" t="s">
@@ -23767,7 +23817,7 @@
       </c>
       <c r="AL108" s="1"/>
       <c r="AM108" s="1"/>
-      <c r="AN108" s="85"/>
+      <c r="AN108" s="89"/>
     </row>
     <row r="109" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A109" s="22" t="s">
@@ -23860,7 +23910,7 @@
       </c>
       <c r="AL109" s="1"/>
       <c r="AM109" s="1"/>
-      <c r="AN109" s="85"/>
+      <c r="AN109" s="89"/>
     </row>
     <row r="110" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A110" s="22" t="s">
@@ -23973,7 +24023,7 @@
       </c>
       <c r="AL110" s="1"/>
       <c r="AM110" s="1"/>
-      <c r="AN110" s="85"/>
+      <c r="AN110" s="89"/>
     </row>
     <row r="111" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A111" s="22" t="s">
@@ -24068,7 +24118,7 @@
       </c>
       <c r="AL111" s="1"/>
       <c r="AM111" s="1"/>
-      <c r="AN111" s="85"/>
+      <c r="AN111" s="89"/>
     </row>
     <row r="112" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A112" s="22" t="s">
@@ -24179,7 +24229,7 @@
       </c>
       <c r="AL112" s="1"/>
       <c r="AM112" s="1"/>
-      <c r="AN112" s="85"/>
+      <c r="AN112" s="89"/>
     </row>
     <row r="113" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A113" s="22" t="s">
@@ -24268,7 +24318,7 @@
       </c>
       <c r="AL113" s="1"/>
       <c r="AM113" s="1"/>
-      <c r="AN113" s="85"/>
+      <c r="AN113" s="89"/>
     </row>
     <row r="114" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A114" s="22" t="s">
@@ -24355,7 +24405,7 @@
       </c>
       <c r="AL114" s="1"/>
       <c r="AM114" s="1"/>
-      <c r="AN114" s="85"/>
+      <c r="AN114" s="89"/>
     </row>
     <row r="115" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
@@ -24448,7 +24498,7 @@
       </c>
       <c r="AL115" s="1"/>
       <c r="AM115" s="1"/>
-      <c r="AN115" s="85"/>
+      <c r="AN115" s="89"/>
     </row>
     <row r="116" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A116" s="22" t="s">
@@ -24533,7 +24583,7 @@
       </c>
       <c r="AL116" s="1"/>
       <c r="AM116" s="1"/>
-      <c r="AN116" s="85"/>
+      <c r="AN116" s="89"/>
     </row>
     <row r="117" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A117" s="22" t="s">
@@ -24628,7 +24678,7 @@
       </c>
       <c r="AL117" s="1"/>
       <c r="AM117" s="1"/>
-      <c r="AN117" s="85"/>
+      <c r="AN117" s="89"/>
     </row>
     <row r="118" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A118" s="22" t="s">
@@ -24721,7 +24771,7 @@
       </c>
       <c r="AL118" s="1"/>
       <c r="AM118" s="1"/>
-      <c r="AN118" s="85"/>
+      <c r="AN118" s="89"/>
     </row>
     <row r="119" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A119" s="22" t="s">
@@ -24812,7 +24862,7 @@
       </c>
       <c r="AL119" s="1"/>
       <c r="AM119" s="1"/>
-      <c r="AN119" s="85"/>
+      <c r="AN119" s="89"/>
     </row>
     <row r="120" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A120" s="15" t="s">
@@ -24897,7 +24947,7 @@
       </c>
       <c r="AL120" s="1"/>
       <c r="AM120" s="1"/>
-      <c r="AN120" s="85"/>
+      <c r="AN120" s="89"/>
     </row>
     <row r="121" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A121" s="22" t="s">
@@ -24988,7 +25038,7 @@
       </c>
       <c r="AL121" s="1"/>
       <c r="AM121" s="1"/>
-      <c r="AN121" s="85"/>
+      <c r="AN121" s="89"/>
     </row>
     <row r="122" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A122" s="15" t="s">
@@ -25075,9 +25125,9 @@
       </c>
       <c r="AL122" s="1"/>
       <c r="AM122" s="1"/>
-      <c r="AN122" s="85"/>
+      <c r="AN122" s="89"/>
     </row>
-    <row r="123" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A123" s="22" t="s">
         <v>418</v>
       </c>
@@ -25182,7 +25232,7 @@
       </c>
       <c r="AL123" s="1"/>
       <c r="AM123" s="1"/>
-      <c r="AN123" s="85"/>
+      <c r="AN123" s="89"/>
     </row>
     <row r="124" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A124" s="22" t="s">
@@ -25267,7 +25317,7 @@
       </c>
       <c r="AL124" s="1"/>
       <c r="AM124" s="1"/>
-      <c r="AN124" s="85"/>
+      <c r="AN124" s="89"/>
     </row>
     <row r="125" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A125" s="22" t="s">
@@ -25362,7 +25412,7 @@
       </c>
       <c r="AL125" s="1"/>
       <c r="AM125" s="1"/>
-      <c r="AN125" s="85"/>
+      <c r="AN125" s="89"/>
     </row>
     <row r="126" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A126" s="22" t="s">
@@ -25451,9 +25501,9 @@
       </c>
       <c r="AL126" s="1"/>
       <c r="AM126" s="1"/>
-      <c r="AN126" s="85"/>
+      <c r="AN126" s="89"/>
     </row>
-    <row r="127" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A127" s="22" t="s">
         <v>426</v>
       </c>
@@ -25544,7 +25594,7 @@
       </c>
       <c r="AL127" s="1"/>
       <c r="AM127" s="1"/>
-      <c r="AN127" s="85"/>
+      <c r="AN127" s="89"/>
     </row>
     <row r="128" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A128" s="22" t="s">
@@ -25633,7 +25683,7 @@
       </c>
       <c r="AL128" s="1"/>
       <c r="AM128" s="1"/>
-      <c r="AN128" s="85"/>
+      <c r="AN128" s="89"/>
     </row>
     <row r="129" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A129" s="15" t="s">
@@ -25726,7 +25776,7 @@
       </c>
       <c r="AL129" s="1"/>
       <c r="AM129" s="1"/>
-      <c r="AN129" s="85"/>
+      <c r="AN129" s="89"/>
     </row>
     <row r="130" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A130" s="22" t="s">
@@ -25809,7 +25859,7 @@
       </c>
       <c r="AL130" s="1"/>
       <c r="AM130" s="1"/>
-      <c r="AN130" s="85"/>
+      <c r="AN130" s="89"/>
     </row>
     <row r="131" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A131" s="22" t="s">
@@ -25892,9 +25942,9 @@
       </c>
       <c r="AL131" s="1"/>
       <c r="AM131" s="1"/>
-      <c r="AN131" s="85"/>
+      <c r="AN131" s="89"/>
     </row>
-    <row r="132" spans="1:40" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A132" s="22" t="s">
         <v>435</v>
       </c>
@@ -25985,7 +26035,7 @@
       </c>
       <c r="AL132" s="1"/>
       <c r="AM132" s="1"/>
-      <c r="AN132" s="85"/>
+      <c r="AN132" s="89"/>
     </row>
     <row r="133" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A133" s="22" t="s">
@@ -26080,7 +26130,7 @@
       </c>
       <c r="AL133" s="1"/>
       <c r="AM133" s="1"/>
-      <c r="AN133" s="85"/>
+      <c r="AN133" s="89"/>
     </row>
     <row r="134" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A134" s="22" t="s">
@@ -26171,7 +26221,7 @@
       </c>
       <c r="AL134" s="1"/>
       <c r="AM134" s="1"/>
-      <c r="AN134" s="85"/>
+      <c r="AN134" s="89"/>
     </row>
     <row r="135" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A135" s="15" t="s">
@@ -26260,7 +26310,7 @@
       </c>
       <c r="AL135" s="1"/>
       <c r="AM135" s="1"/>
-      <c r="AN135" s="85"/>
+      <c r="AN135" s="89"/>
     </row>
     <row r="136" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A136" s="22" t="s">
@@ -26351,7 +26401,7 @@
       </c>
       <c r="AL136" s="1"/>
       <c r="AM136" s="1"/>
-      <c r="AN136" s="85"/>
+      <c r="AN136" s="89"/>
     </row>
     <row r="137" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A137" s="15" t="s">
@@ -26436,9 +26486,9 @@
       </c>
       <c r="AL137" s="1"/>
       <c r="AM137" s="1"/>
-      <c r="AN137" s="85"/>
+      <c r="AN137" s="89"/>
     </row>
-    <row r="138" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A138" s="22" t="s">
         <v>447</v>
       </c>
@@ -26527,7 +26577,7 @@
       </c>
       <c r="AL138" s="1"/>
       <c r="AM138" s="1"/>
-      <c r="AN138" s="85"/>
+      <c r="AN138" s="89"/>
     </row>
     <row r="139" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A139" s="15" t="s">
@@ -26614,7 +26664,7 @@
       </c>
       <c r="AL139" s="1"/>
       <c r="AM139" s="1"/>
-      <c r="AN139" s="85"/>
+      <c r="AN139" s="89"/>
     </row>
     <row r="140" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A140" s="22" t="s">
@@ -26705,7 +26755,7 @@
       </c>
       <c r="AL140" s="1"/>
       <c r="AM140" s="1"/>
-      <c r="AN140" s="85"/>
+      <c r="AN140" s="89"/>
     </row>
     <row r="141" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A141" s="22" t="s">
@@ -26790,9 +26840,9 @@
       </c>
       <c r="AL141" s="1"/>
       <c r="AM141" s="1"/>
-      <c r="AN141" s="85"/>
+      <c r="AN141" s="89"/>
     </row>
-    <row r="142" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A142" s="15" t="s">
         <v>455</v>
       </c>
@@ -26881,7 +26931,7 @@
       </c>
       <c r="AL142" s="1"/>
       <c r="AM142" s="1"/>
-      <c r="AN142" s="85"/>
+      <c r="AN142" s="89"/>
     </row>
     <row r="143" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A143" s="15" t="s">
@@ -26968,7 +27018,7 @@
       </c>
       <c r="AL143" s="1"/>
       <c r="AM143" s="1"/>
-      <c r="AN143" s="85"/>
+      <c r="AN143" s="89"/>
     </row>
     <row r="144" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A144" s="15" t="s">
@@ -27063,9 +27113,9 @@
       </c>
       <c r="AL144" s="1"/>
       <c r="AM144" s="1"/>
-      <c r="AN144" s="85"/>
+      <c r="AN144" s="89"/>
     </row>
-    <row r="145" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A145" s="15" t="s">
         <v>462</v>
       </c>
@@ -27150,7 +27200,7 @@
       </c>
       <c r="AL145" s="1"/>
       <c r="AM145" s="1"/>
-      <c r="AN145" s="85"/>
+      <c r="AN145" s="89"/>
     </row>
     <row r="146" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A146" s="15" t="s">
@@ -27235,7 +27285,7 @@
       </c>
       <c r="AL146" s="1"/>
       <c r="AM146" s="1"/>
-      <c r="AN146" s="85"/>
+      <c r="AN146" s="89"/>
     </row>
     <row r="147" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A147" s="15" t="s">
@@ -27316,7 +27366,7 @@
       </c>
       <c r="AL147" s="1"/>
       <c r="AM147" s="1"/>
-      <c r="AN147" s="85"/>
+      <c r="AN147" s="89"/>
     </row>
     <row r="148" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A148" s="15" t="s">
@@ -27409,7 +27459,7 @@
       </c>
       <c r="AL148" s="1"/>
       <c r="AM148" s="1"/>
-      <c r="AN148" s="85"/>
+      <c r="AN148" s="89"/>
     </row>
     <row r="149" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A149" s="15" t="s">
@@ -27500,7 +27550,7 @@
       </c>
       <c r="AL149" s="1"/>
       <c r="AM149" s="1"/>
-      <c r="AN149" s="85"/>
+      <c r="AN149" s="89"/>
     </row>
     <row r="150" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A150" s="15" t="s">
@@ -27581,7 +27631,7 @@
       </c>
       <c r="AL150" s="1"/>
       <c r="AM150" s="1"/>
-      <c r="AN150" s="85"/>
+      <c r="AN150" s="89"/>
     </row>
     <row r="151" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A151" s="15" t="s">
@@ -27668,7 +27718,7 @@
       </c>
       <c r="AL151" s="1"/>
       <c r="AM151" s="1"/>
-      <c r="AN151" s="85"/>
+      <c r="AN151" s="89"/>
     </row>
     <row r="152" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A152" s="15" t="s">
@@ -27759,7 +27809,7 @@
       </c>
       <c r="AL152" s="1"/>
       <c r="AM152" s="1"/>
-      <c r="AN152" s="85"/>
+      <c r="AN152" s="89"/>
     </row>
     <row r="153" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A153" s="15" t="s">
@@ -27846,7 +27896,7 @@
       </c>
       <c r="AL153" s="1"/>
       <c r="AM153" s="1"/>
-      <c r="AN153" s="85"/>
+      <c r="AN153" s="89"/>
     </row>
     <row r="154" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A154" s="15" t="s">
@@ -27933,7 +27983,7 @@
       </c>
       <c r="AL154" s="1"/>
       <c r="AM154" s="1"/>
-      <c r="AN154" s="85"/>
+      <c r="AN154" s="89"/>
     </row>
     <row r="155" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A155" s="15" t="s">
@@ -28020,7 +28070,7 @@
       </c>
       <c r="AL155" s="1"/>
       <c r="AM155" s="1"/>
-      <c r="AN155" s="85"/>
+      <c r="AN155" s="89"/>
     </row>
     <row r="156" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A156" s="15" t="s">
@@ -28109,7 +28159,7 @@
       </c>
       <c r="AL156" s="1"/>
       <c r="AM156" s="1"/>
-      <c r="AN156" s="85"/>
+      <c r="AN156" s="89"/>
     </row>
     <row r="157" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A157" s="15" t="s">
@@ -28196,7 +28246,7 @@
       </c>
       <c r="AL157" s="1"/>
       <c r="AM157" s="1"/>
-      <c r="AN157" s="85"/>
+      <c r="AN157" s="89"/>
     </row>
     <row r="158" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A158" s="15" t="s">
@@ -28283,7 +28333,7 @@
       </c>
       <c r="AL158" s="1"/>
       <c r="AM158" s="1"/>
-      <c r="AN158" s="85"/>
+      <c r="AN158" s="89"/>
     </row>
     <row r="159" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A159" s="15" t="s">
@@ -28372,7 +28422,7 @@
       </c>
       <c r="AL159" s="1"/>
       <c r="AM159" s="1"/>
-      <c r="AN159" s="85"/>
+      <c r="AN159" s="89"/>
     </row>
     <row r="160" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A160" s="15" t="s">
@@ -28459,7 +28509,7 @@
       </c>
       <c r="AL160" s="1"/>
       <c r="AM160" s="1"/>
-      <c r="AN160" s="85"/>
+      <c r="AN160" s="89"/>
     </row>
     <row r="161" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A161" s="15" t="s">
@@ -28546,7 +28596,7 @@
       </c>
       <c r="AL161" s="1"/>
       <c r="AM161" s="1"/>
-      <c r="AN161" s="85"/>
+      <c r="AN161" s="89"/>
     </row>
     <row r="162" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A162" s="15" t="s">
@@ -28637,7 +28687,7 @@
       </c>
       <c r="AL162" s="1"/>
       <c r="AM162" s="1"/>
-      <c r="AN162" s="85"/>
+      <c r="AN162" s="89"/>
     </row>
     <row r="163" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A163" s="15" t="s">
@@ -28724,7 +28774,7 @@
       </c>
       <c r="AL163" s="1"/>
       <c r="AM163" s="1"/>
-      <c r="AN163" s="85"/>
+      <c r="AN163" s="89"/>
     </row>
     <row r="164" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A164" s="15" t="s">
@@ -28811,7 +28861,7 @@
       </c>
       <c r="AL164" s="1"/>
       <c r="AM164" s="1"/>
-      <c r="AN164" s="85"/>
+      <c r="AN164" s="89"/>
     </row>
     <row r="165" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A165" s="15" t="s">
@@ -28900,7 +28950,7 @@
       </c>
       <c r="AL165" s="1"/>
       <c r="AM165" s="1"/>
-      <c r="AN165" s="85"/>
+      <c r="AN165" s="89"/>
     </row>
     <row r="166" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A166" s="15" t="s">
@@ -28989,7 +29039,7 @@
       </c>
       <c r="AL166" s="1"/>
       <c r="AM166" s="1"/>
-      <c r="AN166" s="85"/>
+      <c r="AN166" s="89"/>
     </row>
     <row r="167" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A167" s="15" t="s">
@@ -29078,7 +29128,7 @@
       </c>
       <c r="AL167" s="1"/>
       <c r="AM167" s="1"/>
-      <c r="AN167" s="85"/>
+      <c r="AN167" s="89"/>
     </row>
     <row r="168" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A168" s="15" t="s">
@@ -29167,7 +29217,7 @@
       </c>
       <c r="AL168" s="1"/>
       <c r="AM168" s="1"/>
-      <c r="AN168" s="85"/>
+      <c r="AN168" s="89"/>
     </row>
     <row r="169" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A169" s="15" t="s">
@@ -29254,7 +29304,7 @@
       </c>
       <c r="AL169" s="1"/>
       <c r="AM169" s="1"/>
-      <c r="AN169" s="85"/>
+      <c r="AN169" s="89"/>
     </row>
     <row r="170" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A170" s="15" t="s">
@@ -29343,7 +29393,7 @@
       </c>
       <c r="AL170" s="1"/>
       <c r="AM170" s="1"/>
-      <c r="AN170" s="85"/>
+      <c r="AN170" s="89"/>
     </row>
     <row r="171" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A171" s="15" t="s">
@@ -29432,7 +29482,7 @@
       </c>
       <c r="AL171" s="1"/>
       <c r="AM171" s="1"/>
-      <c r="AN171" s="85"/>
+      <c r="AN171" s="89"/>
     </row>
     <row r="172" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A172" s="15" t="s">
@@ -29519,7 +29569,7 @@
       </c>
       <c r="AL172" s="1"/>
       <c r="AM172" s="1"/>
-      <c r="AN172" s="85"/>
+      <c r="AN172" s="89"/>
     </row>
     <row r="173" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A173" s="15" t="s">
@@ -29608,7 +29658,7 @@
       </c>
       <c r="AL173" s="1"/>
       <c r="AM173" s="1"/>
-      <c r="AN173" s="85"/>
+      <c r="AN173" s="89"/>
     </row>
     <row r="174" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A174" s="15" t="s">
@@ -29697,7 +29747,7 @@
       </c>
       <c r="AL174" s="1"/>
       <c r="AM174" s="1"/>
-      <c r="AN174" s="85"/>
+      <c r="AN174" s="89"/>
     </row>
     <row r="175" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A175" s="15" t="s">
@@ -29770,7 +29820,7 @@
       </c>
       <c r="AL175" s="1"/>
       <c r="AM175" s="1"/>
-      <c r="AN175" s="85"/>
+      <c r="AN175" s="89"/>
     </row>
     <row r="176" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A176" s="15" t="s">
@@ -29857,7 +29907,7 @@
       </c>
       <c r="AL176" s="1"/>
       <c r="AM176" s="1"/>
-      <c r="AN176" s="85"/>
+      <c r="AN176" s="89"/>
     </row>
     <row r="177" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A177" s="15" t="s">
@@ -29942,7 +29992,7 @@
       </c>
       <c r="AL177" s="1"/>
       <c r="AM177" s="1"/>
-      <c r="AN177" s="85"/>
+      <c r="AN177" s="89"/>
     </row>
     <row r="178" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A178" s="15" t="s">
@@ -30033,7 +30083,7 @@
       </c>
       <c r="AL178" s="1"/>
       <c r="AM178" s="1"/>
-      <c r="AN178" s="85"/>
+      <c r="AN178" s="89"/>
     </row>
     <row r="179" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A179" s="15" t="s">
@@ -30120,7 +30170,7 @@
       </c>
       <c r="AL179" s="1"/>
       <c r="AM179" s="1"/>
-      <c r="AN179" s="85"/>
+      <c r="AN179" s="89"/>
     </row>
     <row r="180" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A180" s="15" t="s">
@@ -30231,7 +30281,7 @@
       </c>
       <c r="AL180" s="1"/>
       <c r="AM180" s="1"/>
-      <c r="AN180" s="85"/>
+      <c r="AN180" s="89"/>
     </row>
     <row r="181" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A181" s="15" t="s">
@@ -30342,7 +30392,7 @@
       </c>
       <c r="AL181" s="1"/>
       <c r="AM181" s="1"/>
-      <c r="AN181" s="85"/>
+      <c r="AN181" s="89"/>
     </row>
     <row r="182" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A182" s="15" t="s">
@@ -30433,7 +30483,7 @@
       </c>
       <c r="AL182" s="1"/>
       <c r="AM182" s="1"/>
-      <c r="AN182" s="85"/>
+      <c r="AN182" s="89"/>
     </row>
     <row r="183" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A183" s="15" t="s">
@@ -30522,7 +30572,7 @@
       </c>
       <c r="AL183" s="1"/>
       <c r="AM183" s="1"/>
-      <c r="AN183" s="85"/>
+      <c r="AN183" s="89"/>
     </row>
     <row r="184" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A184" s="15" t="s">
@@ -30611,7 +30661,7 @@
       </c>
       <c r="AL184" s="1"/>
       <c r="AM184" s="1"/>
-      <c r="AN184" s="85"/>
+      <c r="AN184" s="89"/>
     </row>
     <row r="185" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A185" s="15" t="s">
@@ -30698,7 +30748,7 @@
       </c>
       <c r="AL185" s="1"/>
       <c r="AM185" s="1"/>
-      <c r="AN185" s="85"/>
+      <c r="AN185" s="89"/>
     </row>
     <row r="186" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A186" s="15" t="s">
@@ -30785,7 +30835,7 @@
       </c>
       <c r="AL186" s="1"/>
       <c r="AM186" s="1"/>
-      <c r="AN186" s="85"/>
+      <c r="AN186" s="89"/>
     </row>
     <row r="187" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A187" s="15" t="s">
@@ -30872,7 +30922,7 @@
       </c>
       <c r="AL187" s="1"/>
       <c r="AM187" s="1"/>
-      <c r="AN187" s="85"/>
+      <c r="AN187" s="89"/>
     </row>
     <row r="188" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A188" s="15" t="s">
@@ -30959,7 +31009,7 @@
       </c>
       <c r="AL188" s="1"/>
       <c r="AM188" s="1"/>
-      <c r="AN188" s="85"/>
+      <c r="AN188" s="89"/>
     </row>
     <row r="189" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A189" s="15" t="s">
@@ -31046,7 +31096,7 @@
       </c>
       <c r="AL189" s="1"/>
       <c r="AM189" s="1"/>
-      <c r="AN189" s="85"/>
+      <c r="AN189" s="89"/>
     </row>
     <row r="190" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A190" s="15" t="s">
@@ -31133,7 +31183,7 @@
       </c>
       <c r="AL190" s="1"/>
       <c r="AM190" s="1"/>
-      <c r="AN190" s="85"/>
+      <c r="AN190" s="89"/>
     </row>
     <row r="191" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A191" s="15" t="s">
@@ -31214,7 +31264,7 @@
       </c>
       <c r="AL191" s="1"/>
       <c r="AM191" s="1"/>
-      <c r="AN191" s="85"/>
+      <c r="AN191" s="89"/>
     </row>
     <row r="192" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A192" s="15" t="s">
@@ -31301,7 +31351,7 @@
       </c>
       <c r="AL192" s="1"/>
       <c r="AM192" s="1"/>
-      <c r="AN192" s="85"/>
+      <c r="AN192" s="89"/>
     </row>
     <row r="193" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A193" s="15" t="s">
@@ -31390,7 +31440,7 @@
       </c>
       <c r="AL193" s="1"/>
       <c r="AM193" s="1"/>
-      <c r="AN193" s="85"/>
+      <c r="AN193" s="89"/>
     </row>
     <row r="194" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A194" s="15" t="s">
@@ -31477,7 +31527,7 @@
       </c>
       <c r="AL194" s="1"/>
       <c r="AM194" s="1"/>
-      <c r="AN194" s="85"/>
+      <c r="AN194" s="89"/>
     </row>
     <row r="195" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A195" s="15" t="s">
@@ -31564,7 +31614,7 @@
       </c>
       <c r="AL195" s="1"/>
       <c r="AM195" s="1"/>
-      <c r="AN195" s="85"/>
+      <c r="AN195" s="89"/>
     </row>
     <row r="196" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A196" s="15" t="s">
@@ -31653,7 +31703,7 @@
       </c>
       <c r="AL196" s="1"/>
       <c r="AM196" s="1"/>
-      <c r="AN196" s="85"/>
+      <c r="AN196" s="89"/>
     </row>
     <row r="197" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A197" s="15" t="s">
@@ -31742,7 +31792,7 @@
       </c>
       <c r="AL197" s="1"/>
       <c r="AM197" s="1"/>
-      <c r="AN197" s="85"/>
+      <c r="AN197" s="89"/>
     </row>
     <row r="198" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A198" s="15" t="s">
@@ -31831,7 +31881,7 @@
       </c>
       <c r="AL198" s="1"/>
       <c r="AM198" s="1"/>
-      <c r="AN198" s="85"/>
+      <c r="AN198" s="89"/>
     </row>
     <row r="199" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A199" s="15" t="s">
@@ -31918,7 +31968,7 @@
       </c>
       <c r="AL199" s="1"/>
       <c r="AM199" s="1"/>
-      <c r="AN199" s="85"/>
+      <c r="AN199" s="89"/>
     </row>
     <row r="200" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A200" s="15" t="s">
@@ -32005,7 +32055,7 @@
       </c>
       <c r="AL200" s="1"/>
       <c r="AM200" s="1"/>
-      <c r="AN200" s="85"/>
+      <c r="AN200" s="89"/>
     </row>
     <row r="201" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A201" s="15" t="s">
@@ -32092,7 +32142,7 @@
       </c>
       <c r="AL201" s="1"/>
       <c r="AM201" s="1"/>
-      <c r="AN201" s="85"/>
+      <c r="AN201" s="89"/>
     </row>
     <row r="202" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A202" s="15" t="s">
@@ -32183,7 +32233,7 @@
       </c>
       <c r="AL202" s="1"/>
       <c r="AM202" s="1"/>
-      <c r="AN202" s="85"/>
+      <c r="AN202" s="89"/>
     </row>
     <row r="203" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A203" s="15" t="s">
@@ -32270,7 +32320,7 @@
       </c>
       <c r="AL203" s="1"/>
       <c r="AM203" s="1"/>
-      <c r="AN203" s="85"/>
+      <c r="AN203" s="89"/>
     </row>
     <row r="204" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A204" s="15" t="s">
@@ -32357,7 +32407,7 @@
       </c>
       <c r="AL204" s="1"/>
       <c r="AM204" s="1"/>
-      <c r="AN204" s="85"/>
+      <c r="AN204" s="89"/>
     </row>
     <row r="205" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A205" s="15" t="s">
@@ -32446,7 +32496,7 @@
       </c>
       <c r="AL205" s="1"/>
       <c r="AM205" s="1"/>
-      <c r="AN205" s="85"/>
+      <c r="AN205" s="89"/>
     </row>
     <row r="206" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A206" s="15" t="s">
@@ -32539,7 +32589,7 @@
       </c>
       <c r="AL206" s="1"/>
       <c r="AM206" s="1"/>
-      <c r="AN206" s="85"/>
+      <c r="AN206" s="89"/>
     </row>
     <row r="207" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A207" s="15" t="s">
@@ -32626,7 +32676,7 @@
       </c>
       <c r="AL207" s="1"/>
       <c r="AM207" s="1"/>
-      <c r="AN207" s="85"/>
+      <c r="AN207" s="89"/>
     </row>
     <row r="208" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A208" s="15" t="s">
@@ -32715,7 +32765,7 @@
       </c>
       <c r="AL208" s="1"/>
       <c r="AM208" s="1"/>
-      <c r="AN208" s="85"/>
+      <c r="AN208" s="89"/>
     </row>
     <row r="209" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A209" s="15" t="s">
@@ -32802,7 +32852,7 @@
       </c>
       <c r="AL209" s="1"/>
       <c r="AM209" s="1"/>
-      <c r="AN209" s="85"/>
+      <c r="AN209" s="89"/>
     </row>
     <row r="210" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A210" s="15" t="s">
@@ -32889,7 +32939,7 @@
       </c>
       <c r="AL210" s="1"/>
       <c r="AM210" s="1"/>
-      <c r="AN210" s="85"/>
+      <c r="AN210" s="89"/>
     </row>
     <row r="211" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A211" s="15" t="s">
@@ -32976,7 +33026,7 @@
       </c>
       <c r="AL211" s="1"/>
       <c r="AM211" s="1"/>
-      <c r="AN211" s="85"/>
+      <c r="AN211" s="89"/>
     </row>
     <row r="212" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A212" s="15" t="s">
@@ -33065,9 +33115,9 @@
       </c>
       <c r="AL212" s="1"/>
       <c r="AM212" s="1"/>
-      <c r="AN212" s="85"/>
+      <c r="AN212" s="89"/>
     </row>
-    <row r="213" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A213" s="15" t="s">
         <v>607</v>
       </c>
@@ -33152,9 +33202,9 @@
       </c>
       <c r="AL213" s="1"/>
       <c r="AM213" s="1"/>
-      <c r="AN213" s="85"/>
+      <c r="AN213" s="89"/>
     </row>
-    <row r="214" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A214" s="15" t="s">
         <v>609</v>
       </c>
@@ -33239,9 +33289,9 @@
       </c>
       <c r="AL214" s="1"/>
       <c r="AM214" s="1"/>
-      <c r="AN214" s="85"/>
+      <c r="AN214" s="89"/>
     </row>
-    <row r="215" spans="1:40" s="26" customFormat="1" ht="122.4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A215" s="15" t="s">
         <v>612</v>
       </c>
@@ -33328,7 +33378,7 @@
       </c>
       <c r="AL215" s="1"/>
       <c r="AM215" s="1"/>
-      <c r="AN215" s="85"/>
+      <c r="AN215" s="89"/>
     </row>
     <row r="216" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A216" s="15" t="s">
@@ -33413,7 +33463,7 @@
       </c>
       <c r="AL216" s="1"/>
       <c r="AM216" s="1"/>
-      <c r="AN216" s="85"/>
+      <c r="AN216" s="89"/>
     </row>
     <row r="217" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A217" s="15" t="s">
@@ -33500,9 +33550,9 @@
       </c>
       <c r="AL217" s="1"/>
       <c r="AM217" s="1"/>
-      <c r="AN217" s="85"/>
+      <c r="AN217" s="89"/>
     </row>
-    <row r="218" spans="1:40" s="26" customFormat="1" ht="81.599999999999994" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A218" s="15" t="s">
         <v>620</v>
       </c>
@@ -33585,7 +33635,7 @@
       </c>
       <c r="AL218" s="1"/>
       <c r="AM218" s="1"/>
-      <c r="AN218" s="85"/>
+      <c r="AN218" s="89"/>
     </row>
     <row r="219" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A219" s="15" t="s">
@@ -33670,7 +33720,7 @@
       </c>
       <c r="AL219" s="1"/>
       <c r="AM219" s="1"/>
-      <c r="AN219" s="85"/>
+      <c r="AN219" s="89"/>
     </row>
     <row r="220" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A220" s="15" t="s">
@@ -33751,9 +33801,9 @@
       </c>
       <c r="AL220" s="1"/>
       <c r="AM220" s="1"/>
-      <c r="AN220" s="85"/>
+      <c r="AN220" s="89"/>
     </row>
-    <row r="221" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A221" s="15" t="s">
         <v>625</v>
       </c>
@@ -33836,7 +33886,7 @@
       </c>
       <c r="AL221" s="1"/>
       <c r="AM221" s="1"/>
-      <c r="AN221" s="85"/>
+      <c r="AN221" s="89"/>
     </row>
     <row r="222" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A222" s="15" t="s">
@@ -33921,7 +33971,7 @@
       </c>
       <c r="AL222" s="1"/>
       <c r="AM222" s="1"/>
-      <c r="AN222" s="85"/>
+      <c r="AN222" s="89"/>
     </row>
     <row r="223" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A223" s="15" t="s">
@@ -34006,7 +34056,7 @@
       </c>
       <c r="AL223" s="1"/>
       <c r="AM223" s="1"/>
-      <c r="AN223" s="85"/>
+      <c r="AN223" s="89"/>
     </row>
     <row r="224" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A224" s="15" t="s">
@@ -34095,9 +34145,9 @@
       </c>
       <c r="AL224" s="1"/>
       <c r="AM224" s="1"/>
-      <c r="AN224" s="85"/>
+      <c r="AN224" s="89"/>
     </row>
-    <row r="225" spans="1:40" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A225" s="15" t="s">
         <v>635</v>
       </c>
@@ -34178,7 +34228,7 @@
       </c>
       <c r="AL225" s="1"/>
       <c r="AM225" s="1"/>
-      <c r="AN225" s="85"/>
+      <c r="AN225" s="89"/>
     </row>
     <row r="226" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A226" s="15" t="s">
@@ -34265,7 +34315,7 @@
       </c>
       <c r="AL226" s="1"/>
       <c r="AM226" s="1"/>
-      <c r="AN226" s="85"/>
+      <c r="AN226" s="89"/>
     </row>
     <row r="227" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A227" s="15" t="s">
@@ -34352,7 +34402,7 @@
       </c>
       <c r="AL227" s="1"/>
       <c r="AM227" s="1"/>
-      <c r="AN227" s="85"/>
+      <c r="AN227" s="89"/>
     </row>
     <row r="228" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A228" s="15" t="s">
@@ -34437,7 +34487,7 @@
       </c>
       <c r="AL228" s="1"/>
       <c r="AM228" s="1"/>
-      <c r="AN228" s="85"/>
+      <c r="AN228" s="89"/>
     </row>
     <row r="229" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A229" s="15" t="s">
@@ -34520,7 +34570,7 @@
       </c>
       <c r="AL229" s="1"/>
       <c r="AM229" s="1"/>
-      <c r="AN229" s="85"/>
+      <c r="AN229" s="89"/>
     </row>
     <row r="230" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A230" s="15" t="s">
@@ -34605,7 +34655,7 @@
       </c>
       <c r="AL230" s="1"/>
       <c r="AM230" s="1"/>
-      <c r="AN230" s="85"/>
+      <c r="AN230" s="89"/>
     </row>
     <row r="231" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A231" s="15" t="s">
@@ -34690,7 +34740,7 @@
       </c>
       <c r="AL231" s="1"/>
       <c r="AM231" s="1"/>
-      <c r="AN231" s="85"/>
+      <c r="AN231" s="89"/>
     </row>
     <row r="232" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A232" s="15" t="s">
@@ -34771,7 +34821,7 @@
       </c>
       <c r="AL232" s="1"/>
       <c r="AM232" s="1"/>
-      <c r="AN232" s="85"/>
+      <c r="AN232" s="89"/>
     </row>
     <row r="233" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A233" s="15" t="s">
@@ -34856,7 +34906,7 @@
       </c>
       <c r="AL233" s="1"/>
       <c r="AM233" s="1"/>
-      <c r="AN233" s="85"/>
+      <c r="AN233" s="89"/>
     </row>
     <row r="234" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A234" s="15" t="s">
@@ -34945,7 +34995,7 @@
       </c>
       <c r="AL234" s="1"/>
       <c r="AM234" s="1"/>
-      <c r="AN234" s="85"/>
+      <c r="AN234" s="89"/>
     </row>
     <row r="235" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A235" s="15" t="s">
@@ -35032,7 +35082,7 @@
       </c>
       <c r="AL235" s="1"/>
       <c r="AM235" s="1"/>
-      <c r="AN235" s="85"/>
+      <c r="AN235" s="89"/>
     </row>
     <row r="236" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A236" s="15" t="s">
@@ -35119,7 +35169,7 @@
       </c>
       <c r="AL236" s="1"/>
       <c r="AM236" s="1"/>
-      <c r="AN236" s="85"/>
+      <c r="AN236" s="89"/>
     </row>
     <row r="237" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A237" s="15" t="s">
@@ -35206,7 +35256,7 @@
       </c>
       <c r="AL237" s="1"/>
       <c r="AM237" s="1"/>
-      <c r="AN237" s="85"/>
+      <c r="AN237" s="89"/>
     </row>
     <row r="238" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A238" s="15" t="s">
@@ -35297,7 +35347,7 @@
       </c>
       <c r="AL238" s="1"/>
       <c r="AM238" s="1"/>
-      <c r="AN238" s="85"/>
+      <c r="AN238" s="89"/>
     </row>
     <row r="239" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A239" s="15" t="s">
@@ -35388,7 +35438,7 @@
       </c>
       <c r="AL239" s="1"/>
       <c r="AM239" s="1"/>
-      <c r="AN239" s="85"/>
+      <c r="AN239" s="89"/>
     </row>
     <row r="240" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A240" s="15" t="s">
@@ -35479,7 +35529,7 @@
       </c>
       <c r="AL240" s="1"/>
       <c r="AM240" s="1"/>
-      <c r="AN240" s="85"/>
+      <c r="AN240" s="89"/>
     </row>
     <row r="241" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A241" s="15" t="s">
@@ -35568,7 +35618,7 @@
       </c>
       <c r="AL241" s="1"/>
       <c r="AM241" s="1"/>
-      <c r="AN241" s="85"/>
+      <c r="AN241" s="89"/>
     </row>
     <row r="242" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A242" s="15" t="s">
@@ -35655,7 +35705,7 @@
       </c>
       <c r="AL242" s="1"/>
       <c r="AM242" s="1"/>
-      <c r="AN242" s="85"/>
+      <c r="AN242" s="89"/>
     </row>
     <row r="243" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A243" s="15" t="s">
@@ -35748,7 +35798,7 @@
       </c>
       <c r="AL243" s="1"/>
       <c r="AM243" s="1"/>
-      <c r="AN243" s="85"/>
+      <c r="AN243" s="89"/>
     </row>
     <row r="244" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A244" s="15" t="s">
@@ -35835,7 +35885,7 @@
       </c>
       <c r="AL244" s="1"/>
       <c r="AM244" s="1"/>
-      <c r="AN244" s="85"/>
+      <c r="AN244" s="89"/>
     </row>
     <row r="245" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A245" s="15" t="s">
@@ -35920,7 +35970,7 @@
       </c>
       <c r="AL245" s="1"/>
       <c r="AM245" s="1"/>
-      <c r="AN245" s="85"/>
+      <c r="AN245" s="89"/>
     </row>
     <row r="246" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A246" s="15" t="s">
@@ -36007,7 +36057,7 @@
       </c>
       <c r="AL246" s="1"/>
       <c r="AM246" s="1"/>
-      <c r="AN246" s="85"/>
+      <c r="AN246" s="89"/>
     </row>
     <row r="247" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A247" s="15" t="s">
@@ -36094,7 +36144,7 @@
       </c>
       <c r="AL247" s="1"/>
       <c r="AM247" s="1"/>
-      <c r="AN247" s="85"/>
+      <c r="AN247" s="89"/>
     </row>
     <row r="248" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A248" s="15" t="s">
@@ -36181,7 +36231,7 @@
       </c>
       <c r="AL248" s="1"/>
       <c r="AM248" s="1"/>
-      <c r="AN248" s="85"/>
+      <c r="AN248" s="89"/>
     </row>
     <row r="249" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A249" s="15" t="s">
@@ -36268,7 +36318,7 @@
       </c>
       <c r="AL249" s="1"/>
       <c r="AM249" s="1"/>
-      <c r="AN249" s="85"/>
+      <c r="AN249" s="89"/>
     </row>
     <row r="250" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A250" s="15" t="s">
@@ -36357,7 +36407,7 @@
       </c>
       <c r="AL250" s="1"/>
       <c r="AM250" s="1"/>
-      <c r="AN250" s="85"/>
+      <c r="AN250" s="89"/>
     </row>
     <row r="251" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A251" s="15" t="s">
@@ -36442,7 +36492,7 @@
       </c>
       <c r="AL251" s="1"/>
       <c r="AM251" s="1"/>
-      <c r="AN251" s="85"/>
+      <c r="AN251" s="89"/>
     </row>
     <row r="252" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A252" s="15" t="s">
@@ -36527,7 +36577,7 @@
       </c>
       <c r="AL252" s="1"/>
       <c r="AM252" s="1"/>
-      <c r="AN252" s="85"/>
+      <c r="AN252" s="89"/>
     </row>
     <row r="253" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A253" s="15" t="s">
@@ -36612,7 +36662,7 @@
       </c>
       <c r="AL253" s="1"/>
       <c r="AM253" s="1"/>
-      <c r="AN253" s="85"/>
+      <c r="AN253" s="89"/>
     </row>
     <row r="254" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A254" s="15" t="s">
@@ -36697,7 +36747,7 @@
       </c>
       <c r="AL254" s="1"/>
       <c r="AM254" s="1"/>
-      <c r="AN254" s="85"/>
+      <c r="AN254" s="89"/>
     </row>
     <row r="255" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A255" s="15" t="s">
@@ -36784,7 +36834,7 @@
       </c>
       <c r="AL255" s="1"/>
       <c r="AM255" s="1"/>
-      <c r="AN255" s="85"/>
+      <c r="AN255" s="89"/>
     </row>
     <row r="256" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A256" s="15" t="s">
@@ -36873,7 +36923,7 @@
       </c>
       <c r="AL256" s="1"/>
       <c r="AM256" s="1"/>
-      <c r="AN256" s="85"/>
+      <c r="AN256" s="89"/>
     </row>
     <row r="257" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A257" s="15" t="s">
@@ -36960,7 +37010,7 @@
       </c>
       <c r="AL257" s="1"/>
       <c r="AM257" s="1"/>
-      <c r="AN257" s="85"/>
+      <c r="AN257" s="89"/>
     </row>
     <row r="258" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A258" s="15" t="s">
@@ -37047,7 +37097,7 @@
       </c>
       <c r="AL258" s="1"/>
       <c r="AM258" s="1"/>
-      <c r="AN258" s="85"/>
+      <c r="AN258" s="89"/>
     </row>
     <row r="259" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A259" s="15" t="s">
@@ -37134,7 +37184,7 @@
       </c>
       <c r="AL259" s="1"/>
       <c r="AM259" s="1"/>
-      <c r="AN259" s="85"/>
+      <c r="AN259" s="89"/>
     </row>
     <row r="260" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A260" s="15" t="s">
@@ -37219,7 +37269,7 @@
       </c>
       <c r="AL260" s="1"/>
       <c r="AM260" s="1"/>
-      <c r="AN260" s="85"/>
+      <c r="AN260" s="89"/>
     </row>
     <row r="261" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A261" s="15" t="s">
@@ -37300,7 +37350,7 @@
       </c>
       <c r="AL261" s="1"/>
       <c r="AM261" s="1"/>
-      <c r="AN261" s="85"/>
+      <c r="AN261" s="89"/>
     </row>
     <row r="262" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A262" s="15" t="s">
@@ -37381,7 +37431,7 @@
       </c>
       <c r="AL262" s="1"/>
       <c r="AM262" s="1"/>
-      <c r="AN262" s="85"/>
+      <c r="AN262" s="89"/>
     </row>
     <row r="263" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A263" s="15" t="s">
@@ -37458,7 +37508,7 @@
       </c>
       <c r="AL263" s="1"/>
       <c r="AM263" s="1"/>
-      <c r="AN263" s="85"/>
+      <c r="AN263" s="89"/>
     </row>
     <row r="264" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A264" s="15" t="s">
@@ -37539,7 +37589,7 @@
       </c>
       <c r="AL264" s="1"/>
       <c r="AM264" s="1"/>
-      <c r="AN264" s="85"/>
+      <c r="AN264" s="89"/>
     </row>
     <row r="265" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A265" s="15" t="s">
@@ -37616,7 +37666,7 @@
       </c>
       <c r="AL265" s="1"/>
       <c r="AM265" s="1"/>
-      <c r="AN265" s="85"/>
+      <c r="AN265" s="89"/>
     </row>
     <row r="266" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A266" s="15" t="s">
@@ -37697,7 +37747,7 @@
       </c>
       <c r="AL266" s="1"/>
       <c r="AM266" s="1"/>
-      <c r="AN266" s="85"/>
+      <c r="AN266" s="89"/>
     </row>
     <row r="267" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A267" s="15" t="s">
@@ -37780,7 +37830,7 @@
       </c>
       <c r="AL267" s="1"/>
       <c r="AM267" s="1"/>
-      <c r="AN267" s="85"/>
+      <c r="AN267" s="89"/>
     </row>
     <row r="268" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A268" s="15" t="s">
@@ -37861,7 +37911,7 @@
       </c>
       <c r="AL268" s="1"/>
       <c r="AM268" s="1"/>
-      <c r="AN268" s="85"/>
+      <c r="AN268" s="89"/>
     </row>
     <row r="269" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A269" s="15" t="s">
@@ -37942,7 +37992,7 @@
       </c>
       <c r="AL269" s="1"/>
       <c r="AM269" s="1"/>
-      <c r="AN269" s="85"/>
+      <c r="AN269" s="89"/>
     </row>
     <row r="270" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A270" s="15" t="s">
@@ -38023,7 +38073,7 @@
       </c>
       <c r="AL270" s="1"/>
       <c r="AM270" s="1"/>
-      <c r="AN270" s="85"/>
+      <c r="AN270" s="89"/>
     </row>
     <row r="271" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A271" s="15" t="s">
@@ -38104,7 +38154,7 @@
       </c>
       <c r="AL271" s="1"/>
       <c r="AM271" s="1"/>
-      <c r="AN271" s="85"/>
+      <c r="AN271" s="89"/>
     </row>
     <row r="272" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A272" s="31" t="s">
@@ -38185,7 +38235,7 @@
       </c>
       <c r="AL272" s="1"/>
       <c r="AM272" s="1"/>
-      <c r="AN272" s="85"/>
+      <c r="AN272" s="89"/>
     </row>
     <row r="273" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A273" s="15" t="s">
@@ -38268,7 +38318,7 @@
       </c>
       <c r="AL273" s="1"/>
       <c r="AM273" s="1"/>
-      <c r="AN273" s="85"/>
+      <c r="AN273" s="89"/>
     </row>
     <row r="274" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A274" s="15" t="s">
@@ -38349,7 +38399,7 @@
       </c>
       <c r="AL274" s="1"/>
       <c r="AM274" s="1"/>
-      <c r="AN274" s="85"/>
+      <c r="AN274" s="89"/>
     </row>
     <row r="275" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A275" s="15" t="s">
@@ -38430,7 +38480,7 @@
       </c>
       <c r="AL275" s="1"/>
       <c r="AM275" s="1"/>
-      <c r="AN275" s="85"/>
+      <c r="AN275" s="89"/>
     </row>
     <row r="276" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A276" s="15" t="s">
@@ -38511,7 +38561,7 @@
       </c>
       <c r="AL276" s="1"/>
       <c r="AM276" s="1"/>
-      <c r="AN276" s="85"/>
+      <c r="AN276" s="89"/>
     </row>
     <row r="277" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A277" s="15" t="s">
@@ -38592,7 +38642,7 @@
       </c>
       <c r="AL277" s="1"/>
       <c r="AM277" s="1"/>
-      <c r="AN277" s="85"/>
+      <c r="AN277" s="89"/>
     </row>
     <row r="278" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A278" s="15" t="s">
@@ -38673,9 +38723,9 @@
       </c>
       <c r="AL278" s="1"/>
       <c r="AM278" s="1"/>
-      <c r="AN278" s="85"/>
+      <c r="AN278" s="89"/>
     </row>
-    <row r="279" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A279" s="22" t="s">
         <v>726</v>
       </c>
@@ -38788,9 +38838,9 @@
       <c r="AM279" s="62" t="s">
         <v>735</v>
       </c>
-      <c r="AN279" s="85"/>
+      <c r="AN279" s="89"/>
     </row>
-    <row r="280" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A280" s="22" t="s">
         <v>736</v>
       </c>
@@ -38901,9 +38951,9 @@
       </c>
       <c r="AL280" s="1"/>
       <c r="AM280" s="62"/>
-      <c r="AN280" s="85"/>
+      <c r="AN280" s="89"/>
     </row>
-    <row r="281" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:40" s="26" customFormat="1" ht="122.4" x14ac:dyDescent="0.3">
       <c r="A281" s="22" t="s">
         <v>738</v>
       </c>
@@ -39016,7 +39066,7 @@
       <c r="AM281" s="62" t="s">
         <v>745</v>
       </c>
-      <c r="AN281" s="85"/>
+      <c r="AN281" s="89"/>
     </row>
     <row r="282" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A282" s="22" t="s">
@@ -39129,7 +39179,7 @@
       </c>
       <c r="AL282" s="1"/>
       <c r="AM282" s="1"/>
-      <c r="AN282" s="85"/>
+      <c r="AN282" s="89"/>
     </row>
     <row r="283" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A283" s="22" t="s">
@@ -39242,9 +39292,9 @@
       <c r="AM283" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="AN283" s="85"/>
+      <c r="AN283" s="89"/>
     </row>
-    <row r="284" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:40" s="26" customFormat="1" ht="81.599999999999994" x14ac:dyDescent="0.3">
       <c r="A284" s="22" t="s">
         <v>756</v>
       </c>
@@ -39357,7 +39407,7 @@
       <c r="AM284" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="AN284" s="85"/>
+      <c r="AN284" s="89"/>
     </row>
     <row r="285" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A285" s="22" t="s">
@@ -39472,7 +39522,7 @@
       <c r="AM285" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="AN285" s="85"/>
+      <c r="AN285" s="89"/>
     </row>
     <row r="286" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A286" s="22" t="s">
@@ -39587,9 +39637,9 @@
       <c r="AM286" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="AN286" s="85"/>
+      <c r="AN286" s="89"/>
     </row>
-    <row r="287" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A287" s="22" t="s">
         <v>768</v>
       </c>
@@ -39702,7 +39752,7 @@
       <c r="AM287" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="AN287" s="85"/>
+      <c r="AN287" s="89"/>
     </row>
     <row r="288" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A288" s="22" t="s">
@@ -39817,7 +39867,7 @@
       <c r="AM288" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="AN288" s="85"/>
+      <c r="AN288" s="89"/>
     </row>
     <row r="289" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A289" s="22" t="s">
@@ -39835,7 +39885,7 @@
       <c r="E289" s="23" t="s">
         <v>587</v>
       </c>
-      <c r="F289" s="89" t="s">
+      <c r="F289" s="85" t="s">
         <v>774</v>
       </c>
       <c r="G289" s="3" t="s">
@@ -39932,7 +39982,7 @@
       <c r="AM289" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="AN289" s="85"/>
+      <c r="AN289" s="89"/>
     </row>
     <row r="290" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A290" s="22" t="s">
@@ -40029,9 +40079,9 @@
       <c r="AM290" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="AN290" s="85"/>
+      <c r="AN290" s="89"/>
     </row>
-    <row r="291" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:40" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A291" s="22" t="s">
         <v>782</v>
       </c>
@@ -40142,7 +40192,7 @@
       <c r="AM291" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="AN291" s="85"/>
+      <c r="AN291" s="89"/>
     </row>
     <row r="292" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A292" s="22" t="s">
@@ -40237,7 +40287,7 @@
       </c>
       <c r="AL292" s="1"/>
       <c r="AM292" s="1"/>
-      <c r="AN292" s="85"/>
+      <c r="AN292" s="89"/>
     </row>
     <row r="293" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A293" s="22" t="s">
@@ -40326,7 +40376,7 @@
       </c>
       <c r="AL293" s="1"/>
       <c r="AM293" s="1"/>
-      <c r="AN293" s="85"/>
+      <c r="AN293" s="89"/>
     </row>
     <row r="294" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A294" s="22" t="s">
@@ -40417,7 +40467,7 @@
       </c>
       <c r="AL294" s="1"/>
       <c r="AM294" s="1"/>
-      <c r="AN294" s="85"/>
+      <c r="AN294" s="89"/>
     </row>
     <row r="295" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A295" s="22" t="s">
@@ -40502,7 +40552,7 @@
       </c>
       <c r="AL295" s="1"/>
       <c r="AM295" s="1"/>
-      <c r="AN295" s="85"/>
+      <c r="AN295" s="89"/>
     </row>
     <row r="296" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A296" s="22" t="s">
@@ -40593,7 +40643,7 @@
       </c>
       <c r="AL296" s="1"/>
       <c r="AM296" s="1"/>
-      <c r="AN296" s="85"/>
+      <c r="AN296" s="89"/>
     </row>
     <row r="297" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A297" s="22" t="s">
@@ -40684,7 +40734,7 @@
       <c r="AM297" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="AN297" s="85"/>
+      <c r="AN297" s="89"/>
     </row>
     <row r="298" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A298" s="22" t="s">
@@ -40773,7 +40823,7 @@
       </c>
       <c r="AL298" s="1"/>
       <c r="AM298" s="1"/>
-      <c r="AN298" s="85"/>
+      <c r="AN298" s="89"/>
     </row>
     <row r="299" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A299" s="22" t="s">
@@ -40864,7 +40914,7 @@
       </c>
       <c r="AL299" s="1"/>
       <c r="AM299" s="1"/>
-      <c r="AN299" s="85"/>
+      <c r="AN299" s="89"/>
     </row>
     <row r="300" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A300" s="22" t="s">
@@ -40953,7 +41003,7 @@
       </c>
       <c r="AL300" s="1"/>
       <c r="AM300" s="1"/>
-      <c r="AN300" s="85"/>
+      <c r="AN300" s="89"/>
     </row>
     <row r="301" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A301" s="22" t="s">
@@ -41044,7 +41094,7 @@
       </c>
       <c r="AL301" s="1"/>
       <c r="AM301" s="1"/>
-      <c r="AN301" s="85"/>
+      <c r="AN301" s="89"/>
     </row>
     <row r="302" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A302" s="22" t="s">
@@ -41133,7 +41183,7 @@
       </c>
       <c r="AL302" s="1"/>
       <c r="AM302" s="1"/>
-      <c r="AN302" s="85"/>
+      <c r="AN302" s="89"/>
     </row>
     <row r="303" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A303" s="22" t="s">
@@ -41224,7 +41274,7 @@
       </c>
       <c r="AL303" s="1"/>
       <c r="AM303" s="1"/>
-      <c r="AN303" s="85"/>
+      <c r="AN303" s="89"/>
     </row>
     <row r="304" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A304" s="22" t="s">
@@ -41315,7 +41365,7 @@
       </c>
       <c r="AL304" s="1"/>
       <c r="AM304" s="1"/>
-      <c r="AN304" s="85"/>
+      <c r="AN304" s="89"/>
     </row>
     <row r="305" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A305" s="22" t="s">
@@ -41406,7 +41456,7 @@
       </c>
       <c r="AL305" s="1"/>
       <c r="AM305" s="1"/>
-      <c r="AN305" s="85"/>
+      <c r="AN305" s="89"/>
     </row>
     <row r="306" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A306" s="22" t="s">
@@ -41489,7 +41539,7 @@
       </c>
       <c r="AL306" s="1"/>
       <c r="AM306" s="1"/>
-      <c r="AN306" s="85"/>
+      <c r="AN306" s="89"/>
     </row>
     <row r="307" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A307" s="22" t="s">
@@ -41580,7 +41630,7 @@
       </c>
       <c r="AL307" s="1"/>
       <c r="AM307" s="1"/>
-      <c r="AN307" s="85"/>
+      <c r="AN307" s="89"/>
     </row>
     <row r="308" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A308" s="22" t="s">
@@ -41669,7 +41719,7 @@
       </c>
       <c r="AL308" s="1"/>
       <c r="AM308" s="1"/>
-      <c r="AN308" s="85"/>
+      <c r="AN308" s="89"/>
     </row>
     <row r="309" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A309" s="22" t="s">
@@ -41760,7 +41810,7 @@
       </c>
       <c r="AL309" s="1"/>
       <c r="AM309" s="1"/>
-      <c r="AN309" s="85"/>
+      <c r="AN309" s="89"/>
     </row>
     <row r="310" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A310" s="22" t="s">
@@ -41845,7 +41895,7 @@
       </c>
       <c r="AL310" s="1"/>
       <c r="AM310" s="1"/>
-      <c r="AN310" s="85"/>
+      <c r="AN310" s="89"/>
     </row>
     <row r="311" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A311" s="22" t="s">
@@ -41936,7 +41986,7 @@
       </c>
       <c r="AL311" s="1"/>
       <c r="AM311" s="1"/>
-      <c r="AN311" s="85"/>
+      <c r="AN311" s="89"/>
     </row>
     <row r="312" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A312" s="22" t="s">
@@ -42025,7 +42075,7 @@
       </c>
       <c r="AL312" s="1"/>
       <c r="AM312" s="1"/>
-      <c r="AN312" s="85"/>
+      <c r="AN312" s="89"/>
     </row>
     <row r="313" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A313" s="22">
@@ -42098,7 +42148,7 @@
       </c>
       <c r="AL313" s="1"/>
       <c r="AM313" s="1"/>
-      <c r="AN313" s="85"/>
+      <c r="AN313" s="89"/>
     </row>
     <row r="314" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A314" s="22" t="s">
@@ -42193,7 +42243,7 @@
       </c>
       <c r="AL314" s="1"/>
       <c r="AM314" s="1"/>
-      <c r="AN314" s="85"/>
+      <c r="AN314" s="89"/>
     </row>
     <row r="315" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A315" s="22" t="s">
@@ -42284,7 +42334,7 @@
       </c>
       <c r="AL315" s="1"/>
       <c r="AM315" s="1"/>
-      <c r="AN315" s="85"/>
+      <c r="AN315" s="89"/>
     </row>
     <row r="316" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A316" s="3" t="s">
@@ -42371,7 +42421,7 @@
       </c>
       <c r="AL316" s="1"/>
       <c r="AM316" s="1"/>
-      <c r="AN316" s="85"/>
+      <c r="AN316" s="89"/>
     </row>
     <row r="317" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A317" s="22" t="s">
@@ -42456,7 +42506,7 @@
       </c>
       <c r="AL317" s="1"/>
       <c r="AM317" s="1"/>
-      <c r="AN317" s="85"/>
+      <c r="AN317" s="89"/>
     </row>
     <row r="318" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A318" s="22" t="s">
@@ -42547,7 +42597,7 @@
       </c>
       <c r="AL318" s="1"/>
       <c r="AM318" s="1"/>
-      <c r="AN318" s="85"/>
+      <c r="AN318" s="89"/>
     </row>
     <row r="319" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A319" s="22" t="s">
@@ -42642,7 +42692,7 @@
       </c>
       <c r="AL319" s="1"/>
       <c r="AM319" s="1"/>
-      <c r="AN319" s="85"/>
+      <c r="AN319" s="89"/>
     </row>
     <row r="320" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A320" s="22" t="s">
@@ -42731,7 +42781,7 @@
       </c>
       <c r="AL320" s="1"/>
       <c r="AM320" s="1"/>
-      <c r="AN320" s="85"/>
+      <c r="AN320" s="89"/>
     </row>
     <row r="321" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A321" s="22" t="s">
@@ -42812,7 +42862,7 @@
       </c>
       <c r="AL321" s="1"/>
       <c r="AM321" s="1"/>
-      <c r="AN321" s="85"/>
+      <c r="AN321" s="89"/>
     </row>
     <row r="322" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A322" s="3" t="s">
@@ -42899,7 +42949,7 @@
       </c>
       <c r="AL322" s="1"/>
       <c r="AM322" s="1"/>
-      <c r="AN322" s="85"/>
+      <c r="AN322" s="89"/>
     </row>
     <row r="323" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A323" s="22" t="s">
@@ -42986,7 +43036,7 @@
       </c>
       <c r="AL323" s="1"/>
       <c r="AM323" s="1"/>
-      <c r="AN323" s="85"/>
+      <c r="AN323" s="89"/>
     </row>
     <row r="324" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A324" s="22" t="s">
@@ -43069,7 +43119,7 @@
       </c>
       <c r="AL324" s="1"/>
       <c r="AM324" s="1"/>
-      <c r="AN324" s="85"/>
+      <c r="AN324" s="89"/>
     </row>
     <row r="325" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A325" s="22" t="s">
@@ -43158,7 +43208,7 @@
       </c>
       <c r="AL325" s="1"/>
       <c r="AM325" s="1"/>
-      <c r="AN325" s="85"/>
+      <c r="AN325" s="89"/>
     </row>
     <row r="326" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A326" s="3" t="s">
@@ -43247,7 +43297,7 @@
       </c>
       <c r="AL326" s="1"/>
       <c r="AM326" s="1"/>
-      <c r="AN326" s="85"/>
+      <c r="AN326" s="89"/>
     </row>
     <row r="327" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A327" s="22" t="s">
@@ -43332,7 +43382,7 @@
       </c>
       <c r="AL327" s="1"/>
       <c r="AM327" s="1"/>
-      <c r="AN327" s="85"/>
+      <c r="AN327" s="89"/>
     </row>
     <row r="328" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A328" s="3" t="s">
@@ -43419,7 +43469,7 @@
       </c>
       <c r="AL328" s="1"/>
       <c r="AM328" s="1"/>
-      <c r="AN328" s="85"/>
+      <c r="AN328" s="89"/>
     </row>
     <row r="329" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
@@ -43506,7 +43556,7 @@
       </c>
       <c r="AL329" s="1"/>
       <c r="AM329" s="1"/>
-      <c r="AN329" s="85"/>
+      <c r="AN329" s="89"/>
     </row>
     <row r="330" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A330" s="3" t="s">
@@ -43593,7 +43643,7 @@
       </c>
       <c r="AL330" s="1"/>
       <c r="AM330" s="1"/>
-      <c r="AN330" s="85"/>
+      <c r="AN330" s="89"/>
     </row>
     <row r="331" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
@@ -43676,7 +43726,7 @@
       </c>
       <c r="AL331" s="1"/>
       <c r="AM331" s="1"/>
-      <c r="AN331" s="85"/>
+      <c r="AN331" s="89"/>
     </row>
     <row r="332" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A332" s="3" t="s">
@@ -43759,7 +43809,7 @@
       </c>
       <c r="AL332" s="1"/>
       <c r="AM332" s="1"/>
-      <c r="AN332" s="85"/>
+      <c r="AN332" s="89"/>
     </row>
     <row r="333" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
@@ -43846,7 +43896,7 @@
       </c>
       <c r="AL333" s="1"/>
       <c r="AM333" s="1"/>
-      <c r="AN333" s="85"/>
+      <c r="AN333" s="89"/>
     </row>
     <row r="334" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A334" s="22" t="s">
@@ -43937,7 +43987,7 @@
       </c>
       <c r="AL334" s="1"/>
       <c r="AM334" s="1"/>
-      <c r="AN334" s="85"/>
+      <c r="AN334" s="89"/>
     </row>
     <row r="335" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A335" s="22" t="s">
@@ -44020,7 +44070,7 @@
       </c>
       <c r="AL335" s="1"/>
       <c r="AM335" s="1"/>
-      <c r="AN335" s="85"/>
+      <c r="AN335" s="89"/>
     </row>
     <row r="336" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A336" s="3" t="s">
@@ -44097,7 +44147,7 @@
       </c>
       <c r="AL336" s="1"/>
       <c r="AM336" s="1"/>
-      <c r="AN336" s="85"/>
+      <c r="AN336" s="89"/>
     </row>
     <row r="337" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A337" s="22" t="s">
@@ -44188,7 +44238,7 @@
       </c>
       <c r="AL337" s="1"/>
       <c r="AM337" s="1"/>
-      <c r="AN337" s="85"/>
+      <c r="AN337" s="89"/>
     </row>
     <row r="338" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A338" s="3" t="s">
@@ -44271,7 +44321,7 @@
       </c>
       <c r="AL338" s="1"/>
       <c r="AM338" s="1"/>
-      <c r="AN338" s="85"/>
+      <c r="AN338" s="89"/>
     </row>
     <row r="339" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A339" s="22" t="s">
@@ -44354,7 +44404,7 @@
       </c>
       <c r="AL339" s="1"/>
       <c r="AM339" s="1"/>
-      <c r="AN339" s="85"/>
+      <c r="AN339" s="89"/>
     </row>
     <row r="340" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A340" s="3" t="s">
@@ -44437,7 +44487,7 @@
       </c>
       <c r="AL340" s="1"/>
       <c r="AM340" s="1"/>
-      <c r="AN340" s="85"/>
+      <c r="AN340" s="89"/>
     </row>
     <row r="341" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A341" s="22" t="s">
@@ -44520,7 +44570,7 @@
       </c>
       <c r="AL341" s="1"/>
       <c r="AM341" s="1"/>
-      <c r="AN341" s="85"/>
+      <c r="AN341" s="89"/>
     </row>
     <row r="342" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A342" s="22" t="s">
@@ -44603,7 +44653,7 @@
       </c>
       <c r="AL342" s="1"/>
       <c r="AM342" s="1"/>
-      <c r="AN342" s="85"/>
+      <c r="AN342" s="89"/>
     </row>
     <row r="343" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
@@ -44692,7 +44742,7 @@
       </c>
       <c r="AL343" s="1"/>
       <c r="AM343" s="1"/>
-      <c r="AN343" s="85"/>
+      <c r="AN343" s="89"/>
     </row>
     <row r="344" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A344" s="22" t="s">
@@ -44779,7 +44829,7 @@
       </c>
       <c r="AL344" s="1"/>
       <c r="AM344" s="1"/>
-      <c r="AN344" s="85"/>
+      <c r="AN344" s="89"/>
     </row>
     <row r="345" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
@@ -44866,7 +44916,7 @@
       </c>
       <c r="AL345" s="1"/>
       <c r="AM345" s="1"/>
-      <c r="AN345" s="85"/>
+      <c r="AN345" s="89"/>
     </row>
     <row r="346" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A346" s="3" t="s">
@@ -44953,7 +45003,7 @@
       </c>
       <c r="AL346" s="1"/>
       <c r="AM346" s="1"/>
-      <c r="AN346" s="85"/>
+      <c r="AN346" s="89"/>
     </row>
     <row r="347" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A347" s="22" t="s">
@@ -45032,7 +45082,7 @@
       </c>
       <c r="AL347" s="1"/>
       <c r="AM347" s="1"/>
-      <c r="AN347" s="85"/>
+      <c r="AN347" s="89"/>
     </row>
     <row r="348" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A348" s="3" t="s">
@@ -45119,7 +45169,7 @@
       </c>
       <c r="AL348" s="1"/>
       <c r="AM348" s="1"/>
-      <c r="AN348" s="85"/>
+      <c r="AN348" s="89"/>
     </row>
     <row r="349" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A349" s="22" t="s">
@@ -45206,7 +45256,7 @@
       </c>
       <c r="AL349" s="1"/>
       <c r="AM349" s="1"/>
-      <c r="AN349" s="85"/>
+      <c r="AN349" s="89"/>
     </row>
     <row r="350" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A350" s="3" t="s">
@@ -45289,7 +45339,7 @@
       </c>
       <c r="AL350" s="1"/>
       <c r="AM350" s="1"/>
-      <c r="AN350" s="85"/>
+      <c r="AN350" s="89"/>
     </row>
     <row r="351" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A351" s="22" t="s">
@@ -45380,7 +45430,7 @@
       </c>
       <c r="AL351" s="1"/>
       <c r="AM351" s="1"/>
-      <c r="AN351" s="85"/>
+      <c r="AN351" s="89"/>
     </row>
     <row r="352" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A352" s="22" t="s">
@@ -45463,7 +45513,7 @@
       </c>
       <c r="AL352" s="1"/>
       <c r="AM352" s="1"/>
-      <c r="AN352" s="85"/>
+      <c r="AN352" s="89"/>
     </row>
     <row r="353" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
@@ -45550,7 +45600,7 @@
       </c>
       <c r="AL353" s="1"/>
       <c r="AM353" s="1"/>
-      <c r="AN353" s="85"/>
+      <c r="AN353" s="89"/>
     </row>
     <row r="354" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A354" s="3" t="s">
@@ -45633,7 +45683,7 @@
       </c>
       <c r="AL354" s="1"/>
       <c r="AM354" s="1"/>
-      <c r="AN354" s="85"/>
+      <c r="AN354" s="89"/>
     </row>
     <row r="355" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A355" s="22" t="s">
@@ -45724,7 +45774,7 @@
       </c>
       <c r="AL355" s="1"/>
       <c r="AM355" s="1"/>
-      <c r="AN355" s="85"/>
+      <c r="AN355" s="89"/>
     </row>
     <row r="356" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A356" s="3" t="s">
@@ -45807,7 +45857,7 @@
       </c>
       <c r="AL356" s="1"/>
       <c r="AM356" s="1"/>
-      <c r="AN356" s="85"/>
+      <c r="AN356" s="89"/>
     </row>
     <row r="357" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A357" s="22" t="s">
@@ -45890,7 +45940,7 @@
       </c>
       <c r="AL357" s="1"/>
       <c r="AM357" s="1"/>
-      <c r="AN357" s="85"/>
+      <c r="AN357" s="89"/>
     </row>
     <row r="358" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A358" s="22" t="s">
@@ -45973,7 +46023,7 @@
       </c>
       <c r="AL358" s="1"/>
       <c r="AM358" s="1"/>
-      <c r="AN358" s="85"/>
+      <c r="AN358" s="89"/>
     </row>
     <row r="359" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
@@ -46060,7 +46110,7 @@
       </c>
       <c r="AL359" s="1"/>
       <c r="AM359" s="1"/>
-      <c r="AN359" s="85"/>
+      <c r="AN359" s="89"/>
     </row>
     <row r="360" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A360" s="22" t="s">
@@ -46151,7 +46201,7 @@
       </c>
       <c r="AL360" s="1"/>
       <c r="AM360" s="1"/>
-      <c r="AN360" s="85"/>
+      <c r="AN360" s="89"/>
     </row>
     <row r="361" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
@@ -46234,7 +46284,7 @@
       </c>
       <c r="AL361" s="1"/>
       <c r="AM361" s="1"/>
-      <c r="AN361" s="85"/>
+      <c r="AN361" s="89"/>
     </row>
     <row r="362" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A362" s="3" t="s">
@@ -46321,7 +46371,7 @@
       </c>
       <c r="AL362" s="1"/>
       <c r="AM362" s="1"/>
-      <c r="AN362" s="85"/>
+      <c r="AN362" s="89"/>
     </row>
     <row r="363" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A363" s="22" t="s">
@@ -46404,7 +46454,7 @@
       </c>
       <c r="AL363" s="1"/>
       <c r="AM363" s="1"/>
-      <c r="AN363" s="85"/>
+      <c r="AN363" s="89"/>
     </row>
     <row r="364" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A364" s="3" t="s">
@@ -46487,7 +46537,7 @@
       </c>
       <c r="AL364" s="1"/>
       <c r="AM364" s="1"/>
-      <c r="AN364" s="85"/>
+      <c r="AN364" s="89"/>
     </row>
     <row r="365" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A365" s="22" t="s">
@@ -46570,7 +46620,7 @@
       </c>
       <c r="AL365" s="1"/>
       <c r="AM365" s="1"/>
-      <c r="AN365" s="85"/>
+      <c r="AN365" s="89"/>
     </row>
     <row r="366" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A366" s="3" t="s">
@@ -46653,7 +46703,7 @@
       </c>
       <c r="AL366" s="1"/>
       <c r="AM366" s="1"/>
-      <c r="AN366" s="85"/>
+      <c r="AN366" s="89"/>
     </row>
     <row r="367" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
@@ -46736,7 +46786,7 @@
       </c>
       <c r="AL367" s="1"/>
       <c r="AM367" s="1"/>
-      <c r="AN367" s="85"/>
+      <c r="AN367" s="89"/>
     </row>
     <row r="368" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A368" s="3" t="s">
@@ -46819,7 +46869,7 @@
       </c>
       <c r="AL368" s="1"/>
       <c r="AM368" s="1"/>
-      <c r="AN368" s="85"/>
+      <c r="AN368" s="89"/>
     </row>
     <row r="369" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
@@ -46902,7 +46952,7 @@
       </c>
       <c r="AL369" s="1"/>
       <c r="AM369" s="1"/>
-      <c r="AN369" s="85"/>
+      <c r="AN369" s="89"/>
     </row>
     <row r="370" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A370" s="22" t="s">
@@ -46985,7 +47035,7 @@
       </c>
       <c r="AL370" s="1"/>
       <c r="AM370" s="1"/>
-      <c r="AN370" s="85"/>
+      <c r="AN370" s="89"/>
     </row>
     <row r="371" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A371" s="22" t="s">
@@ -47068,7 +47118,7 @@
       </c>
       <c r="AL371" s="1"/>
       <c r="AM371" s="1"/>
-      <c r="AN371" s="85"/>
+      <c r="AN371" s="89"/>
     </row>
     <row r="372" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A372" s="22" t="s">
@@ -47151,7 +47201,7 @@
       </c>
       <c r="AL372" s="1"/>
       <c r="AM372" s="1"/>
-      <c r="AN372" s="85"/>
+      <c r="AN372" s="89"/>
     </row>
     <row r="373" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
@@ -47234,7 +47284,7 @@
       </c>
       <c r="AL373" s="1"/>
       <c r="AM373" s="1"/>
-      <c r="AN373" s="85"/>
+      <c r="AN373" s="89"/>
     </row>
     <row r="374" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A374" s="3" t="s">
@@ -47317,7 +47367,7 @@
       </c>
       <c r="AL374" s="1"/>
       <c r="AM374" s="1"/>
-      <c r="AN374" s="85"/>
+      <c r="AN374" s="89"/>
     </row>
     <row r="375" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A375" s="22" t="s">
@@ -47400,7 +47450,7 @@
       </c>
       <c r="AL375" s="1"/>
       <c r="AM375" s="1"/>
-      <c r="AN375" s="85"/>
+      <c r="AN375" s="89"/>
     </row>
     <row r="376" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A376" s="3" t="s">
@@ -47483,7 +47533,7 @@
       </c>
       <c r="AL376" s="1"/>
       <c r="AM376" s="1"/>
-      <c r="AN376" s="85"/>
+      <c r="AN376" s="89"/>
     </row>
     <row r="377" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A377" s="22" t="s">
@@ -47566,7 +47616,7 @@
       </c>
       <c r="AL377" s="1"/>
       <c r="AM377" s="1"/>
-      <c r="AN377" s="85"/>
+      <c r="AN377" s="89"/>
     </row>
     <row r="378" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A378" s="22" t="s">
@@ -47649,7 +47699,7 @@
       </c>
       <c r="AL378" s="1"/>
       <c r="AM378" s="1"/>
-      <c r="AN378" s="85"/>
+      <c r="AN378" s="89"/>
     </row>
     <row r="379" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A379" s="22" t="s">
@@ -47732,7 +47782,7 @@
       </c>
       <c r="AL379" s="1"/>
       <c r="AM379" s="1"/>
-      <c r="AN379" s="85"/>
+      <c r="AN379" s="89"/>
     </row>
     <row r="380" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A380" s="22" t="s">
@@ -47815,7 +47865,7 @@
       </c>
       <c r="AL380" s="1"/>
       <c r="AM380" s="1"/>
-      <c r="AN380" s="85"/>
+      <c r="AN380" s="89"/>
     </row>
     <row r="381" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A381" s="22" t="s">
@@ -47902,7 +47952,7 @@
       </c>
       <c r="AL381" s="1"/>
       <c r="AM381" s="1"/>
-      <c r="AN381" s="85"/>
+      <c r="AN381" s="89"/>
     </row>
     <row r="382" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A382" s="3" t="s">
@@ -47981,7 +48031,7 @@
       </c>
       <c r="AL382" s="1"/>
       <c r="AM382" s="1"/>
-      <c r="AN382" s="85"/>
+      <c r="AN382" s="89"/>
     </row>
     <row r="383" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A383" s="22" t="s">
@@ -48064,7 +48114,7 @@
       </c>
       <c r="AL383" s="1"/>
       <c r="AM383" s="1"/>
-      <c r="AN383" s="85"/>
+      <c r="AN383" s="89"/>
     </row>
     <row r="384" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A384" s="22" t="s">
@@ -48147,7 +48197,7 @@
       </c>
       <c r="AL384" s="1"/>
       <c r="AM384" s="1"/>
-      <c r="AN384" s="85"/>
+      <c r="AN384" s="89"/>
     </row>
     <row r="385" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
@@ -48234,7 +48284,7 @@
       </c>
       <c r="AL385" s="1"/>
       <c r="AM385" s="1"/>
-      <c r="AN385" s="85"/>
+      <c r="AN385" s="89"/>
     </row>
     <row r="386" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A386" s="22" t="s">
@@ -48317,7 +48367,7 @@
       </c>
       <c r="AL386" s="1"/>
       <c r="AM386" s="1"/>
-      <c r="AN386" s="85"/>
+      <c r="AN386" s="89"/>
     </row>
     <row r="387" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A387" s="22" t="s">
@@ -48400,7 +48450,7 @@
       </c>
       <c r="AL387" s="1"/>
       <c r="AM387" s="1"/>
-      <c r="AN387" s="85"/>
+      <c r="AN387" s="89"/>
     </row>
     <row r="388" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A388" s="3" t="s">
@@ -48483,7 +48533,7 @@
       </c>
       <c r="AL388" s="1"/>
       <c r="AM388" s="1"/>
-      <c r="AN388" s="85"/>
+      <c r="AN388" s="89"/>
     </row>
     <row r="389" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A389" s="22" t="s">
@@ -48574,7 +48624,7 @@
       </c>
       <c r="AL389" s="1"/>
       <c r="AM389" s="1"/>
-      <c r="AN389" s="85"/>
+      <c r="AN389" s="89"/>
     </row>
     <row r="390" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A390" s="22" t="s">
@@ -48665,7 +48715,7 @@
       </c>
       <c r="AL390" s="1"/>
       <c r="AM390" s="1"/>
-      <c r="AN390" s="85"/>
+      <c r="AN390" s="89"/>
     </row>
     <row r="391" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A391" s="22" t="s">
@@ -48748,7 +48798,7 @@
       </c>
       <c r="AL391" s="1"/>
       <c r="AM391" s="1"/>
-      <c r="AN391" s="85"/>
+      <c r="AN391" s="89"/>
     </row>
     <row r="392" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A392" s="22" t="s">
@@ -48831,7 +48881,7 @@
       </c>
       <c r="AL392" s="1"/>
       <c r="AM392" s="1"/>
-      <c r="AN392" s="85"/>
+      <c r="AN392" s="89"/>
     </row>
     <row r="393" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A393" s="22" t="s">
@@ -48922,7 +48972,7 @@
       </c>
       <c r="AL393" s="1"/>
       <c r="AM393" s="1"/>
-      <c r="AN393" s="85"/>
+      <c r="AN393" s="89"/>
     </row>
     <row r="394" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A394" s="22" t="s">
@@ -49005,7 +49055,7 @@
       </c>
       <c r="AL394" s="1"/>
       <c r="AM394" s="1"/>
-      <c r="AN394" s="85"/>
+      <c r="AN394" s="89"/>
     </row>
     <row r="395" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A395" s="22" t="s">
@@ -49096,7 +49146,7 @@
       </c>
       <c r="AL395" s="1"/>
       <c r="AM395" s="1"/>
-      <c r="AN395" s="85"/>
+      <c r="AN395" s="89"/>
     </row>
     <row r="396" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A396" s="22" t="s">
@@ -49179,7 +49229,7 @@
       </c>
       <c r="AL396" s="1"/>
       <c r="AM396" s="1"/>
-      <c r="AN396" s="85"/>
+      <c r="AN396" s="89"/>
     </row>
     <row r="397" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A397" s="22" t="s">
@@ -49262,7 +49312,7 @@
       </c>
       <c r="AL397" s="1"/>
       <c r="AM397" s="1"/>
-      <c r="AN397" s="85"/>
+      <c r="AN397" s="89"/>
     </row>
     <row r="398" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A398" s="22" t="s">
@@ -49345,7 +49395,7 @@
       </c>
       <c r="AL398" s="1"/>
       <c r="AM398" s="1"/>
-      <c r="AN398" s="85"/>
+      <c r="AN398" s="89"/>
     </row>
     <row r="399" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A399" s="22" t="s">
@@ -49428,7 +49478,7 @@
       </c>
       <c r="AL399" s="1"/>
       <c r="AM399" s="1"/>
-      <c r="AN399" s="85"/>
+      <c r="AN399" s="89"/>
     </row>
     <row r="400" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A400" s="3" t="s">
@@ -49511,7 +49561,7 @@
       </c>
       <c r="AL400" s="1"/>
       <c r="AM400" s="1"/>
-      <c r="AN400" s="85"/>
+      <c r="AN400" s="89"/>
     </row>
     <row r="401" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
@@ -49598,7 +49648,7 @@
       </c>
       <c r="AL401" s="1"/>
       <c r="AM401" s="1"/>
-      <c r="AN401" s="85"/>
+      <c r="AN401" s="89"/>
     </row>
     <row r="402" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A402" s="22" t="s">
@@ -49681,7 +49731,7 @@
       </c>
       <c r="AL402" s="1"/>
       <c r="AM402" s="1"/>
-      <c r="AN402" s="85"/>
+      <c r="AN402" s="89"/>
     </row>
     <row r="403" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A403" s="22" t="s">
@@ -49764,7 +49814,7 @@
       </c>
       <c r="AL403" s="1"/>
       <c r="AM403" s="1"/>
-      <c r="AN403" s="85"/>
+      <c r="AN403" s="89"/>
     </row>
     <row r="404" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A404" s="22" t="s">
@@ -49853,7 +49903,7 @@
       </c>
       <c r="AL404" s="1"/>
       <c r="AM404" s="1"/>
-      <c r="AN404" s="85"/>
+      <c r="AN404" s="89"/>
     </row>
     <row r="405" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A405" s="22" t="s">
@@ -49944,7 +49994,7 @@
       </c>
       <c r="AL405" s="1"/>
       <c r="AM405" s="1"/>
-      <c r="AN405" s="85"/>
+      <c r="AN405" s="89"/>
     </row>
     <row r="406" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A406" s="3" t="s">
@@ -50031,7 +50081,7 @@
       </c>
       <c r="AL406" s="1"/>
       <c r="AM406" s="1"/>
-      <c r="AN406" s="85"/>
+      <c r="AN406" s="89"/>
     </row>
     <row r="407" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A407" s="22" t="s">
@@ -50122,7 +50172,7 @@
       </c>
       <c r="AL407" s="1"/>
       <c r="AM407" s="1"/>
-      <c r="AN407" s="85"/>
+      <c r="AN407" s="89"/>
     </row>
     <row r="408" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A408" s="22" t="s">
@@ -50205,7 +50255,7 @@
       </c>
       <c r="AL408" s="1"/>
       <c r="AM408" s="1"/>
-      <c r="AN408" s="85"/>
+      <c r="AN408" s="89"/>
     </row>
     <row r="409" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A409" s="22" t="s">
@@ -50288,7 +50338,7 @@
       </c>
       <c r="AL409" s="1"/>
       <c r="AM409" s="1"/>
-      <c r="AN409" s="85"/>
+      <c r="AN409" s="89"/>
     </row>
     <row r="410" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A410" s="22" t="s">
@@ -50371,7 +50421,7 @@
       </c>
       <c r="AL410" s="1"/>
       <c r="AM410" s="1"/>
-      <c r="AN410" s="85"/>
+      <c r="AN410" s="89"/>
     </row>
     <row r="411" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A411" s="22" t="s">
@@ -50454,7 +50504,7 @@
       </c>
       <c r="AL411" s="1"/>
       <c r="AM411" s="1"/>
-      <c r="AN411" s="85"/>
+      <c r="AN411" s="89"/>
     </row>
     <row r="412" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A412" s="22" t="s">
@@ -50537,7 +50587,7 @@
       </c>
       <c r="AL412" s="1"/>
       <c r="AM412" s="1"/>
-      <c r="AN412" s="85"/>
+      <c r="AN412" s="89"/>
     </row>
     <row r="413" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A413" s="22" t="s">
@@ -50620,7 +50670,7 @@
       </c>
       <c r="AL413" s="1"/>
       <c r="AM413" s="1"/>
-      <c r="AN413" s="85"/>
+      <c r="AN413" s="89"/>
     </row>
     <row r="414" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A414" s="22" t="s">
@@ -50703,7 +50753,7 @@
       </c>
       <c r="AL414" s="1"/>
       <c r="AM414" s="1"/>
-      <c r="AN414" s="85"/>
+      <c r="AN414" s="89"/>
     </row>
     <row r="415" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A415" s="22" t="s">
@@ -50792,7 +50842,7 @@
       </c>
       <c r="AL415" s="1"/>
       <c r="AM415" s="1"/>
-      <c r="AN415" s="85"/>
+      <c r="AN415" s="89"/>
     </row>
     <row r="416" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A416" s="22" t="s">
@@ -50883,7 +50933,7 @@
       </c>
       <c r="AL416" s="1"/>
       <c r="AM416" s="1"/>
-      <c r="AN416" s="85"/>
+      <c r="AN416" s="89"/>
     </row>
     <row r="417" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A417" s="22" t="s">
@@ -50974,7 +51024,7 @@
       </c>
       <c r="AL417" s="1"/>
       <c r="AM417" s="1"/>
-      <c r="AN417" s="85"/>
+      <c r="AN417" s="89"/>
     </row>
     <row r="418" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A418" s="22" t="s">
@@ -51063,7 +51113,7 @@
       </c>
       <c r="AL418" s="1"/>
       <c r="AM418" s="1"/>
-      <c r="AN418" s="85"/>
+      <c r="AN418" s="89"/>
     </row>
     <row r="419" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A419" s="22" t="s">
@@ -51154,7 +51204,7 @@
       </c>
       <c r="AL419" s="1"/>
       <c r="AM419" s="1"/>
-      <c r="AN419" s="85"/>
+      <c r="AN419" s="89"/>
     </row>
     <row r="420" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A420" s="22" t="s">
@@ -51237,7 +51287,7 @@
       </c>
       <c r="AL420" s="1"/>
       <c r="AM420" s="1"/>
-      <c r="AN420" s="85"/>
+      <c r="AN420" s="89"/>
     </row>
     <row r="421" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A421" s="22" t="s">
@@ -51320,7 +51370,7 @@
       </c>
       <c r="AL421" s="1"/>
       <c r="AM421" s="1"/>
-      <c r="AN421" s="85"/>
+      <c r="AN421" s="89"/>
     </row>
     <row r="422" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A422" s="22" t="s">
@@ -51403,7 +51453,7 @@
       </c>
       <c r="AL422" s="1"/>
       <c r="AM422" s="1"/>
-      <c r="AN422" s="85"/>
+      <c r="AN422" s="89"/>
     </row>
     <row r="423" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A423" s="22" t="s">
@@ -51486,7 +51536,7 @@
       </c>
       <c r="AL423" s="1"/>
       <c r="AM423" s="1"/>
-      <c r="AN423" s="85"/>
+      <c r="AN423" s="89"/>
     </row>
     <row r="424" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A424" s="22" t="s">
@@ -51569,7 +51619,7 @@
       </c>
       <c r="AL424" s="1"/>
       <c r="AM424" s="1"/>
-      <c r="AN424" s="85"/>
+      <c r="AN424" s="89"/>
     </row>
     <row r="425" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A425" s="22" t="s">
@@ -51652,7 +51702,7 @@
       </c>
       <c r="AL425" s="1"/>
       <c r="AM425" s="1"/>
-      <c r="AN425" s="85"/>
+      <c r="AN425" s="89"/>
     </row>
     <row r="426" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A426" s="22" t="s">
@@ -51735,7 +51785,7 @@
       </c>
       <c r="AL426" s="1"/>
       <c r="AM426" s="1"/>
-      <c r="AN426" s="85"/>
+      <c r="AN426" s="89"/>
     </row>
     <row r="427" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A427" s="22" t="s">
@@ -51818,7 +51868,7 @@
       </c>
       <c r="AL427" s="1"/>
       <c r="AM427" s="1"/>
-      <c r="AN427" s="85"/>
+      <c r="AN427" s="89"/>
     </row>
     <row r="428" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A428" s="22" t="s">
@@ -51901,7 +51951,7 @@
       </c>
       <c r="AL428" s="1"/>
       <c r="AM428" s="1"/>
-      <c r="AN428" s="85"/>
+      <c r="AN428" s="89"/>
     </row>
     <row r="429" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A429" s="22" t="s">
@@ -51984,7 +52034,7 @@
       </c>
       <c r="AL429" s="1"/>
       <c r="AM429" s="1"/>
-      <c r="AN429" s="85"/>
+      <c r="AN429" s="89"/>
     </row>
     <row r="430" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A430" s="22" t="s">
@@ -52067,7 +52117,7 @@
       </c>
       <c r="AL430" s="1"/>
       <c r="AM430" s="1"/>
-      <c r="AN430" s="85"/>
+      <c r="AN430" s="89"/>
     </row>
     <row r="431" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A431" s="22" t="s">
@@ -52150,7 +52200,7 @@
       </c>
       <c r="AL431" s="1"/>
       <c r="AM431" s="1"/>
-      <c r="AN431" s="85"/>
+      <c r="AN431" s="89"/>
     </row>
     <row r="432" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A432" s="22" t="s">
@@ -52233,9 +52283,9 @@
       </c>
       <c r="AL432" s="1"/>
       <c r="AM432" s="1"/>
-      <c r="AN432" s="85"/>
+      <c r="AN432" s="89"/>
     </row>
-    <row r="433" spans="1:40" s="26" customFormat="1" ht="132.6" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A433" s="22" t="s">
         <v>1017</v>
       </c>
@@ -52316,7 +52366,7 @@
       </c>
       <c r="AL433" s="1"/>
       <c r="AM433" s="1"/>
-      <c r="AN433" s="85"/>
+      <c r="AN433" s="89"/>
     </row>
     <row r="434" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A434" s="22" t="s">
@@ -52399,7 +52449,7 @@
       </c>
       <c r="AL434" s="1"/>
       <c r="AM434" s="1"/>
-      <c r="AN434" s="85"/>
+      <c r="AN434" s="89"/>
     </row>
     <row r="435" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A435" s="22" t="s">
@@ -52482,7 +52532,7 @@
       </c>
       <c r="AL435" s="1"/>
       <c r="AM435" s="1"/>
-      <c r="AN435" s="85"/>
+      <c r="AN435" s="89"/>
     </row>
     <row r="436" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A436" s="22" t="s">
@@ -52565,7 +52615,7 @@
       </c>
       <c r="AL436" s="1"/>
       <c r="AM436" s="1"/>
-      <c r="AN436" s="85"/>
+      <c r="AN436" s="89"/>
     </row>
     <row r="437" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A437" s="22" t="s">
@@ -52648,7 +52698,7 @@
       </c>
       <c r="AL437" s="1"/>
       <c r="AM437" s="1"/>
-      <c r="AN437" s="85"/>
+      <c r="AN437" s="89"/>
     </row>
     <row r="438" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A438" s="22" t="s">
@@ -52731,7 +52781,7 @@
       </c>
       <c r="AL438" s="1"/>
       <c r="AM438" s="1"/>
-      <c r="AN438" s="85"/>
+      <c r="AN438" s="89"/>
     </row>
     <row r="439" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A439" s="22" t="s">
@@ -52814,7 +52864,7 @@
       </c>
       <c r="AL439" s="1"/>
       <c r="AM439" s="1"/>
-      <c r="AN439" s="85"/>
+      <c r="AN439" s="89"/>
     </row>
     <row r="440" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A440" s="22" t="s">
@@ -52897,7 +52947,7 @@
       </c>
       <c r="AL440" s="1"/>
       <c r="AM440" s="1"/>
-      <c r="AN440" s="85"/>
+      <c r="AN440" s="89"/>
     </row>
     <row r="441" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A441" s="22" t="s">
@@ -52980,7 +53030,7 @@
       </c>
       <c r="AL441" s="1"/>
       <c r="AM441" s="1"/>
-      <c r="AN441" s="85"/>
+      <c r="AN441" s="89"/>
     </row>
     <row r="442" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A442" s="22" t="s">
@@ -53063,9 +53113,9 @@
       </c>
       <c r="AL442" s="1"/>
       <c r="AM442" s="1"/>
-      <c r="AN442" s="85"/>
+      <c r="AN442" s="89"/>
     </row>
-    <row r="443" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A443" s="22" t="s">
         <v>1033</v>
       </c>
@@ -53146,7 +53196,7 @@
       </c>
       <c r="AL443" s="1"/>
       <c r="AM443" s="1"/>
-      <c r="AN443" s="85"/>
+      <c r="AN443" s="89"/>
     </row>
     <row r="444" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A444" s="22" t="s">
@@ -53229,9 +53279,9 @@
       </c>
       <c r="AL444" s="1"/>
       <c r="AM444" s="1"/>
-      <c r="AN444" s="85"/>
+      <c r="AN444" s="89"/>
     </row>
-    <row r="445" spans="1:40" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A445" s="22" t="s">
         <v>1038</v>
       </c>
@@ -53312,9 +53362,9 @@
       </c>
       <c r="AL445" s="1"/>
       <c r="AM445" s="1"/>
-      <c r="AN445" s="85"/>
+      <c r="AN445" s="89"/>
     </row>
-    <row r="446" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A446" s="22" t="s">
         <v>1039</v>
       </c>
@@ -53395,7 +53445,7 @@
       </c>
       <c r="AL446" s="1"/>
       <c r="AM446" s="1"/>
-      <c r="AN446" s="85"/>
+      <c r="AN446" s="89"/>
     </row>
     <row r="447" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A447" s="3" t="s">
@@ -53470,7 +53520,7 @@
       </c>
       <c r="AL447" s="1"/>
       <c r="AM447" s="1"/>
-      <c r="AN447" s="85"/>
+      <c r="AN447" s="89"/>
     </row>
     <row r="448" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A448" s="3" t="s">
@@ -53553,7 +53603,7 @@
       </c>
       <c r="AL448" s="1"/>
       <c r="AM448" s="1"/>
-      <c r="AN448" s="85"/>
+      <c r="AN448" s="89"/>
     </row>
     <row r="449" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A449" s="3" t="s">
@@ -53636,7 +53686,7 @@
       </c>
       <c r="AL449" s="1"/>
       <c r="AM449" s="1"/>
-      <c r="AN449" s="85"/>
+      <c r="AN449" s="89"/>
     </row>
     <row r="450" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A450" s="3" t="s">
@@ -53719,7 +53769,7 @@
       </c>
       <c r="AL450" s="1"/>
       <c r="AM450" s="1"/>
-      <c r="AN450" s="85"/>
+      <c r="AN450" s="89"/>
     </row>
     <row r="451" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A451" s="3" t="s">
@@ -53802,7 +53852,7 @@
       </c>
       <c r="AL451" s="1"/>
       <c r="AM451" s="1"/>
-      <c r="AN451" s="85"/>
+      <c r="AN451" s="89"/>
     </row>
     <row r="452" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A452" s="3" t="s">
@@ -53885,7 +53935,7 @@
       </c>
       <c r="AL452" s="1"/>
       <c r="AM452" s="1"/>
-      <c r="AN452" s="85"/>
+      <c r="AN452" s="89"/>
     </row>
     <row r="453" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A453" s="3" t="s">
@@ -53968,7 +54018,7 @@
       </c>
       <c r="AL453" s="1"/>
       <c r="AM453" s="1"/>
-      <c r="AN453" s="85"/>
+      <c r="AN453" s="89"/>
     </row>
     <row r="454" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A454" s="3" t="s">
@@ -54051,9 +54101,9 @@
       </c>
       <c r="AL454" s="1"/>
       <c r="AM454" s="1"/>
-      <c r="AN454" s="85"/>
+      <c r="AN454" s="89"/>
     </row>
-    <row r="455" spans="1:40" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A455" s="3" t="s">
         <v>1047</v>
       </c>
@@ -54134,7 +54184,7 @@
       </c>
       <c r="AL455" s="1"/>
       <c r="AM455" s="1"/>
-      <c r="AN455" s="85"/>
+      <c r="AN455" s="89"/>
     </row>
     <row r="456" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A456" s="3" t="s">
@@ -54217,7 +54267,7 @@
       </c>
       <c r="AL456" s="1"/>
       <c r="AM456" s="1"/>
-      <c r="AN456" s="85"/>
+      <c r="AN456" s="89"/>
     </row>
     <row r="457" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A457" s="3" t="s">
@@ -54300,7 +54350,7 @@
       </c>
       <c r="AL457" s="1"/>
       <c r="AM457" s="1"/>
-      <c r="AN457" s="85"/>
+      <c r="AN457" s="89"/>
     </row>
     <row r="458" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A458" s="3" t="s">
@@ -54383,7 +54433,7 @@
       </c>
       <c r="AL458" s="1"/>
       <c r="AM458" s="1"/>
-      <c r="AN458" s="85"/>
+      <c r="AN458" s="89"/>
     </row>
     <row r="459" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A459" s="3" t="s">
@@ -54466,7 +54516,7 @@
       </c>
       <c r="AL459" s="1"/>
       <c r="AM459" s="1"/>
-      <c r="AN459" s="85"/>
+      <c r="AN459" s="89"/>
     </row>
     <row r="460" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A460" s="3" t="s">
@@ -54549,7 +54599,7 @@
       </c>
       <c r="AL460" s="1"/>
       <c r="AM460" s="1"/>
-      <c r="AN460" s="85"/>
+      <c r="AN460" s="89"/>
     </row>
     <row r="461" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A461" s="3" t="s">
@@ -54632,7 +54682,7 @@
       </c>
       <c r="AL461" s="1"/>
       <c r="AM461" s="1"/>
-      <c r="AN461" s="85"/>
+      <c r="AN461" s="89"/>
     </row>
     <row r="462" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A462" s="3" t="s">
@@ -54715,7 +54765,7 @@
       </c>
       <c r="AL462" s="1"/>
       <c r="AM462" s="1"/>
-      <c r="AN462" s="85"/>
+      <c r="AN462" s="89"/>
     </row>
     <row r="463" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A463" s="3" t="s">
@@ -54802,7 +54852,7 @@
       </c>
       <c r="AL463" s="1"/>
       <c r="AM463" s="1"/>
-      <c r="AN463" s="85"/>
+      <c r="AN463" s="89"/>
     </row>
     <row r="464" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A464" s="3" t="s">
@@ -54885,7 +54935,7 @@
       </c>
       <c r="AL464" s="1"/>
       <c r="AM464" s="1"/>
-      <c r="AN464" s="85"/>
+      <c r="AN464" s="89"/>
     </row>
     <row r="465" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A465" s="3" t="s">
@@ -54968,7 +55018,7 @@
       </c>
       <c r="AL465" s="1"/>
       <c r="AM465" s="1"/>
-      <c r="AN465" s="85"/>
+      <c r="AN465" s="89"/>
     </row>
     <row r="466" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A466" s="3" t="s">
@@ -55051,7 +55101,7 @@
       </c>
       <c r="AL466" s="1"/>
       <c r="AM466" s="1"/>
-      <c r="AN466" s="85"/>
+      <c r="AN466" s="89"/>
     </row>
     <row r="467" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A467" s="3" t="s">
@@ -55134,9 +55184,9 @@
       </c>
       <c r="AL467" s="1"/>
       <c r="AM467" s="1"/>
-      <c r="AN467" s="85"/>
+      <c r="AN467" s="89"/>
     </row>
-    <row r="468" spans="1:40" s="26" customFormat="1" ht="71.400000000000006" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A468" s="3" t="s">
         <v>1064</v>
       </c>
@@ -55217,7 +55267,7 @@
       </c>
       <c r="AL468" s="1"/>
       <c r="AM468" s="1"/>
-      <c r="AN468" s="85"/>
+      <c r="AN468" s="89"/>
     </row>
     <row r="469" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A469" s="3" t="s">
@@ -55300,7 +55350,7 @@
       </c>
       <c r="AL469" s="1"/>
       <c r="AM469" s="1"/>
-      <c r="AN469" s="85"/>
+      <c r="AN469" s="89"/>
     </row>
     <row r="470" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A470" s="3" t="s">
@@ -55383,7 +55433,7 @@
       </c>
       <c r="AL470" s="1"/>
       <c r="AM470" s="1"/>
-      <c r="AN470" s="85"/>
+      <c r="AN470" s="89"/>
     </row>
     <row r="471" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A471" s="3" t="s">
@@ -55466,7 +55516,7 @@
       </c>
       <c r="AL471" s="1"/>
       <c r="AM471" s="1"/>
-      <c r="AN471" s="85"/>
+      <c r="AN471" s="89"/>
     </row>
     <row r="472" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A472" s="3" t="s">
@@ -55549,7 +55599,7 @@
       </c>
       <c r="AL472" s="1"/>
       <c r="AM472" s="1"/>
-      <c r="AN472" s="85"/>
+      <c r="AN472" s="89"/>
     </row>
     <row r="473" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A473" s="3" t="s">
@@ -55632,7 +55682,7 @@
       </c>
       <c r="AL473" s="1"/>
       <c r="AM473" s="1"/>
-      <c r="AN473" s="85"/>
+      <c r="AN473" s="89"/>
     </row>
     <row r="474" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A474" s="3" t="s">
@@ -55715,7 +55765,7 @@
       </c>
       <c r="AL474" s="1"/>
       <c r="AM474" s="1"/>
-      <c r="AN474" s="85"/>
+      <c r="AN474" s="89"/>
     </row>
     <row r="475" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A475" s="3" t="s">
@@ -55798,7 +55848,7 @@
       </c>
       <c r="AL475" s="1"/>
       <c r="AM475" s="1"/>
-      <c r="AN475" s="85"/>
+      <c r="AN475" s="89"/>
     </row>
     <row r="476" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A476" s="3" t="s">
@@ -55881,7 +55931,7 @@
       </c>
       <c r="AL476" s="1"/>
       <c r="AM476" s="1"/>
-      <c r="AN476" s="85"/>
+      <c r="AN476" s="89"/>
     </row>
     <row r="477" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A477" s="3" t="s">
@@ -55968,7 +56018,7 @@
       </c>
       <c r="AL477" s="1"/>
       <c r="AM477" s="1"/>
-      <c r="AN477" s="85"/>
+      <c r="AN477" s="89"/>
     </row>
     <row r="478" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A478" s="3" t="s">
@@ -56055,7 +56105,7 @@
       </c>
       <c r="AL478" s="1"/>
       <c r="AM478" s="1"/>
-      <c r="AN478" s="85"/>
+      <c r="AN478" s="89"/>
     </row>
     <row r="479" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A479" s="3" t="s">
@@ -56142,7 +56192,7 @@
       </c>
       <c r="AL479" s="1"/>
       <c r="AM479" s="1"/>
-      <c r="AN479" s="85"/>
+      <c r="AN479" s="89"/>
     </row>
     <row r="480" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A480" s="3" t="s">
@@ -56225,7 +56275,7 @@
       </c>
       <c r="AL480" s="1"/>
       <c r="AM480" s="1"/>
-      <c r="AN480" s="85"/>
+      <c r="AN480" s="89"/>
     </row>
     <row r="481" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A481" s="3" t="s">
@@ -56308,7 +56358,7 @@
       </c>
       <c r="AL481" s="1"/>
       <c r="AM481" s="1"/>
-      <c r="AN481" s="85"/>
+      <c r="AN481" s="89"/>
     </row>
     <row r="482" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A482" s="3" t="s">
@@ -56391,7 +56441,7 @@
       </c>
       <c r="AL482" s="1"/>
       <c r="AM482" s="1"/>
-      <c r="AN482" s="85"/>
+      <c r="AN482" s="89"/>
     </row>
     <row r="483" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A483" s="3" t="s">
@@ -56478,7 +56528,7 @@
       </c>
       <c r="AL483" s="1"/>
       <c r="AM483" s="1"/>
-      <c r="AN483" s="85"/>
+      <c r="AN483" s="89"/>
     </row>
     <row r="484" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A484" s="3" t="s">
@@ -56565,7 +56615,7 @@
       </c>
       <c r="AL484" s="1"/>
       <c r="AM484" s="1"/>
-      <c r="AN484" s="85"/>
+      <c r="AN484" s="89"/>
     </row>
     <row r="485" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A485" s="3" t="s">
@@ -56648,7 +56698,7 @@
       </c>
       <c r="AL485" s="1"/>
       <c r="AM485" s="1"/>
-      <c r="AN485" s="85"/>
+      <c r="AN485" s="89"/>
     </row>
     <row r="486" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A486" s="22" t="s">
@@ -56731,7 +56781,7 @@
       </c>
       <c r="AL486" s="1"/>
       <c r="AM486" s="1"/>
-      <c r="AN486" s="85"/>
+      <c r="AN486" s="89"/>
     </row>
     <row r="487" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A487" s="22" t="s">
@@ -56814,7 +56864,7 @@
       </c>
       <c r="AL487" s="1"/>
       <c r="AM487" s="1"/>
-      <c r="AN487" s="85"/>
+      <c r="AN487" s="89"/>
     </row>
     <row r="488" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A488" s="22" t="s">
@@ -56897,9 +56947,9 @@
       </c>
       <c r="AL488" s="1"/>
       <c r="AM488" s="1"/>
-      <c r="AN488" s="85"/>
+      <c r="AN488" s="89"/>
     </row>
-    <row r="489" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A489" s="22" t="s">
         <v>1094</v>
       </c>
@@ -56980,7 +57030,7 @@
       </c>
       <c r="AL489" s="1"/>
       <c r="AM489" s="1"/>
-      <c r="AN489" s="85"/>
+      <c r="AN489" s="89"/>
     </row>
     <row r="490" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A490" s="22" t="s">
@@ -57063,7 +57113,7 @@
       </c>
       <c r="AL490" s="1"/>
       <c r="AM490" s="1"/>
-      <c r="AN490" s="85"/>
+      <c r="AN490" s="89"/>
     </row>
     <row r="491" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A491" s="22" t="s">
@@ -57154,7 +57204,7 @@
       </c>
       <c r="AL491" s="1"/>
       <c r="AM491" s="1"/>
-      <c r="AN491" s="85"/>
+      <c r="AN491" s="89"/>
     </row>
     <row r="492" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A492" s="22" t="s">
@@ -57233,7 +57283,7 @@
       </c>
       <c r="AL492" s="1"/>
       <c r="AM492" s="1"/>
-      <c r="AN492" s="85"/>
+      <c r="AN492" s="89"/>
     </row>
     <row r="493" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A493" s="22" t="s">
@@ -57302,7 +57352,7 @@
       </c>
       <c r="AL493" s="1"/>
       <c r="AM493" s="1"/>
-      <c r="AN493" s="85"/>
+      <c r="AN493" s="89"/>
     </row>
     <row r="494" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A494" s="22" t="s">
@@ -57371,7 +57421,7 @@
       </c>
       <c r="AL494" s="1"/>
       <c r="AM494" s="1"/>
-      <c r="AN494" s="85"/>
+      <c r="AN494" s="89"/>
     </row>
     <row r="495" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A495" s="22" t="s">
@@ -57440,7 +57490,7 @@
       </c>
       <c r="AL495" s="1"/>
       <c r="AM495" s="1"/>
-      <c r="AN495" s="85"/>
+      <c r="AN495" s="89"/>
     </row>
     <row r="496" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A496" s="22" t="s">
@@ -57509,7 +57559,7 @@
       </c>
       <c r="AL496" s="1"/>
       <c r="AM496" s="1"/>
-      <c r="AN496" s="85"/>
+      <c r="AN496" s="89"/>
     </row>
     <row r="497" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A497" s="22" t="s">
@@ -57578,9 +57628,9 @@
       </c>
       <c r="AL497" s="1"/>
       <c r="AM497" s="1"/>
-      <c r="AN497" s="85"/>
+      <c r="AN497" s="89"/>
     </row>
-    <row r="498" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A498" s="19" t="s">
         <v>1105</v>
       </c>
@@ -57597,7 +57647,7 @@
         <v>315</v>
       </c>
       <c r="F498" s="23" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="G498" s="20" t="s">
         <v>1106</v>
@@ -57682,15 +57732,16 @@
         <v>2</v>
       </c>
       <c r="AJ498" s="62" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="AK498" s="65">
-        <v>8082.1508333333331</v>
+        <f>8082.15083333333</f>
+        <v>8082.1508333333304</v>
       </c>
       <c r="AL498" s="1"/>
       <c r="AM498" s="1"/>
-      <c r="AN498" s="85"/>
-      <c r="AO498" s="90"/>
+      <c r="AN498" s="89"/>
+      <c r="AO498" s="86"/>
     </row>
     <row r="499" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A499" s="19" t="s">
@@ -57793,16 +57844,17 @@
       <c r="AI499" s="64">
         <v>1</v>
       </c>
-      <c r="AJ499" s="87" t="s">
-        <v>1438</v>
+      <c r="AJ499" s="62" t="s">
+        <v>1437</v>
       </c>
       <c r="AK499" s="65">
-        <v>14011.740833333335</v>
+        <f>14011.7408333333</f>
+        <v>14011.740833333301</v>
       </c>
       <c r="AL499" s="1"/>
       <c r="AM499" s="1"/>
-      <c r="AN499" s="85"/>
-      <c r="AO499" s="90"/>
+      <c r="AN499" s="89"/>
+      <c r="AO499" s="86"/>
     </row>
     <row r="500" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A500" s="19" t="s">
@@ -57903,16 +57955,17 @@
       <c r="AI500" s="64">
         <v>1</v>
       </c>
-      <c r="AJ500" s="87" t="s">
-        <v>1439</v>
+      <c r="AJ500" s="62" t="s">
+        <v>1438</v>
       </c>
       <c r="AK500" s="65">
-        <v>17038.236666666668</v>
+        <f>17038.2366666667</f>
+        <v>17038.2366666667</v>
       </c>
       <c r="AL500" s="1"/>
       <c r="AM500" s="1"/>
-      <c r="AN500" s="85"/>
-      <c r="AO500" s="90"/>
+      <c r="AN500" s="89"/>
+      <c r="AO500" s="86"/>
     </row>
     <row r="501" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A501" s="19" t="s">
@@ -58015,18 +58068,19 @@
       <c r="AI501" s="64">
         <v>1</v>
       </c>
-      <c r="AJ501" s="87" t="s">
-        <v>1440</v>
+      <c r="AJ501" s="62" t="s">
+        <v>1439</v>
       </c>
       <c r="AK501" s="65">
+        <f>9475.1525</f>
         <v>9475.1525000000001</v>
       </c>
       <c r="AL501" s="1"/>
       <c r="AM501" s="1"/>
-      <c r="AN501" s="85"/>
-      <c r="AO501" s="90"/>
+      <c r="AN501" s="89"/>
+      <c r="AO501" s="86"/>
     </row>
-    <row r="502" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A502" s="19" t="s">
         <v>1121</v>
       </c>
@@ -58127,16 +58181,17 @@
       <c r="AI502" s="64">
         <v>2</v>
       </c>
-      <c r="AJ502" s="87" t="s">
-        <v>1441</v>
+      <c r="AJ502" s="62" t="s">
+        <v>1440</v>
       </c>
       <c r="AK502" s="65">
+        <f>9521.9975</f>
         <v>9521.9974999999995</v>
       </c>
       <c r="AL502" s="1"/>
       <c r="AM502" s="1"/>
-      <c r="AN502" s="85"/>
-      <c r="AO502" s="90"/>
+      <c r="AN502" s="89"/>
+      <c r="AO502" s="86"/>
     </row>
     <row r="503" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A503" s="19" t="s">
@@ -58239,16 +58294,17 @@
       <c r="AI503" s="64">
         <v>1</v>
       </c>
-      <c r="AJ503" s="87" t="s">
-        <v>1442</v>
+      <c r="AJ503" s="62" t="s">
+        <v>1441</v>
       </c>
       <c r="AK503" s="65">
-        <v>4547.8324999999995</v>
+        <f>4547.8325</f>
+        <v>4547.8325000000004</v>
       </c>
       <c r="AL503" s="1"/>
       <c r="AM503" s="1"/>
-      <c r="AN503" s="85"/>
-      <c r="AO503" s="90"/>
+      <c r="AN503" s="89"/>
+      <c r="AO503" s="86"/>
     </row>
     <row r="504" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A504" s="19" t="s">
@@ -58346,13 +58402,11 @@
       </c>
       <c r="AI504" s="64"/>
       <c r="AJ504" s="1"/>
-      <c r="AK504" s="65">
-        <v>0</v>
-      </c>
+      <c r="AK504" s="65"/>
       <c r="AL504" s="1"/>
       <c r="AM504" s="1"/>
-      <c r="AN504" s="85"/>
-      <c r="AO504" s="90"/>
+      <c r="AN504" s="89"/>
+      <c r="AO504" s="86"/>
     </row>
     <row r="505" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A505" s="19" t="s">
@@ -58455,16 +58509,17 @@
       <c r="AI505" s="64">
         <v>1</v>
       </c>
-      <c r="AJ505" s="87" t="s">
-        <v>1443</v>
+      <c r="AJ505" s="62" t="s">
+        <v>1442</v>
       </c>
       <c r="AK505" s="65">
+        <f>2352.08</f>
         <v>2352.08</v>
       </c>
       <c r="AL505" s="1"/>
       <c r="AM505" s="1"/>
-      <c r="AN505" s="85"/>
-      <c r="AO505" s="90"/>
+      <c r="AN505" s="89"/>
+      <c r="AO505" s="86"/>
     </row>
     <row r="506" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A506" s="19" t="s">
@@ -58568,17 +58623,18 @@
         <v>1</v>
       </c>
       <c r="AJ506" s="1" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="AK506" s="65">
+        <f>6579.9675</f>
         <v>6579.9674999999997</v>
       </c>
       <c r="AL506" s="1"/>
       <c r="AM506" s="1"/>
-      <c r="AN506" s="85"/>
-      <c r="AO506" s="90"/>
+      <c r="AN506" s="89"/>
+      <c r="AO506" s="86"/>
     </row>
-    <row r="507" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:41" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A507" s="19" t="s">
         <v>1136</v>
       </c>
@@ -58679,16 +58735,17 @@
       <c r="AI507" s="64">
         <v>3</v>
       </c>
-      <c r="AJ507" s="87" t="s">
-        <v>1444</v>
+      <c r="AJ507" s="62" t="s">
+        <v>1443</v>
       </c>
       <c r="AK507" s="65">
-        <v>2993.1208333333329</v>
+        <f>2993.12083333333</f>
+        <v>2993.1208333333302</v>
       </c>
       <c r="AL507" s="1"/>
       <c r="AM507" s="1"/>
-      <c r="AN507" s="85"/>
-      <c r="AO507" s="90"/>
+      <c r="AN507" s="89"/>
+      <c r="AO507" s="86"/>
     </row>
     <row r="508" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A508" s="19" t="s">
@@ -58787,12 +58844,13 @@
       <c r="AI508" s="64"/>
       <c r="AJ508" s="1"/>
       <c r="AK508" s="65">
+        <f>0</f>
         <v>0</v>
       </c>
       <c r="AL508" s="1"/>
       <c r="AM508" s="1"/>
-      <c r="AN508" s="85"/>
-      <c r="AO508" s="90"/>
+      <c r="AN508" s="89"/>
+      <c r="AO508" s="86"/>
     </row>
     <row r="509" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A509" s="19" t="s">
@@ -58895,16 +58953,17 @@
       <c r="AI509" s="64">
         <v>1</v>
       </c>
-      <c r="AJ509" s="87" t="s">
-        <v>1445</v>
+      <c r="AJ509" s="62" t="s">
+        <v>1444</v>
       </c>
       <c r="AK509" s="65">
+        <f>6736.4775</f>
         <v>6736.4775</v>
       </c>
       <c r="AL509" s="1"/>
       <c r="AM509" s="1"/>
-      <c r="AN509" s="85"/>
-      <c r="AO509" s="90"/>
+      <c r="AN509" s="89"/>
+      <c r="AO509" s="86"/>
     </row>
     <row r="510" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A510" s="19" t="s">
@@ -59003,12 +59062,13 @@
       <c r="AI510" s="64"/>
       <c r="AJ510" s="1"/>
       <c r="AK510" s="65">
+        <f>0</f>
         <v>0</v>
       </c>
       <c r="AL510" s="1"/>
       <c r="AM510" s="1"/>
-      <c r="AN510" s="85"/>
-      <c r="AO510" s="90"/>
+      <c r="AN510" s="89"/>
+      <c r="AO510" s="86"/>
     </row>
     <row r="511" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A511" s="19" t="s">
@@ -59105,12 +59165,13 @@
       <c r="AI511" s="64"/>
       <c r="AJ511" s="1"/>
       <c r="AK511" s="65">
+        <f>0</f>
         <v>0</v>
       </c>
       <c r="AL511" s="1"/>
       <c r="AM511" s="1"/>
-      <c r="AN511" s="85"/>
-      <c r="AO511" s="90"/>
+      <c r="AN511" s="89"/>
+      <c r="AO511" s="86"/>
     </row>
     <row r="512" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A512" s="19" t="s">
@@ -59213,18 +59274,19 @@
       <c r="AI512" s="64">
         <v>1</v>
       </c>
-      <c r="AJ512" s="87" t="s">
-        <v>1446</v>
+      <c r="AJ512" s="62" t="s">
+        <v>1445</v>
       </c>
       <c r="AK512" s="65">
-        <v>3584.8349999999996</v>
+        <f>3584.835</f>
+        <v>3584.835</v>
       </c>
       <c r="AL512" s="1"/>
       <c r="AM512" s="1"/>
-      <c r="AN512" s="85"/>
-      <c r="AO512" s="90"/>
+      <c r="AN512" s="89"/>
+      <c r="AO512" s="86"/>
     </row>
-    <row r="513" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A513" s="19" t="s">
         <v>1148</v>
       </c>
@@ -59325,16 +59387,17 @@
       <c r="AI513" s="64">
         <v>2</v>
       </c>
-      <c r="AJ513" s="87" t="s">
-        <v>1447</v>
+      <c r="AJ513" s="62" t="s">
+        <v>1446</v>
       </c>
       <c r="AK513" s="65">
-        <v>7843.8866666666654</v>
+        <f>7843.88666666667</f>
+        <v>7843.88666666667</v>
       </c>
       <c r="AL513" s="1"/>
       <c r="AM513" s="1"/>
-      <c r="AN513" s="85"/>
-      <c r="AO513" s="90"/>
+      <c r="AN513" s="89"/>
+      <c r="AO513" s="86"/>
     </row>
     <row r="514" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A514" s="19" t="s">
@@ -59437,16 +59500,17 @@
       <c r="AI514" s="64">
         <v>1</v>
       </c>
-      <c r="AJ514" s="87" t="s">
-        <v>1448</v>
+      <c r="AJ514" s="62" t="s">
+        <v>1447</v>
       </c>
       <c r="AK514" s="65">
-        <v>5209.4533333333338</v>
+        <f>5209.45333333333</f>
+        <v>5209.4533333333302</v>
       </c>
       <c r="AL514" s="1"/>
       <c r="AM514" s="1"/>
-      <c r="AN514" s="85"/>
-      <c r="AO514" s="90"/>
+      <c r="AN514" s="89"/>
+      <c r="AO514" s="86"/>
     </row>
     <row r="515" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A515" s="19" t="s">
@@ -59461,7 +59525,9 @@
       <c r="D515" s="23">
         <v>625</v>
       </c>
-      <c r="E515" s="23"/>
+      <c r="E515" s="23">
+        <v>645</v>
+      </c>
       <c r="F515" s="23" t="s">
         <v>92</v>
       </c>
@@ -59487,7 +59553,9 @@
       <c r="N515" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="O515" s="6"/>
+      <c r="O515" s="6" t="s">
+        <v>137</v>
+      </c>
       <c r="P515" s="6"/>
       <c r="Q515" s="27"/>
       <c r="R515" s="28" t="s">
@@ -59542,15 +59610,20 @@
         <f>IF(AG515=100%,Y515," ")</f>
         <v>16.496479999999998</v>
       </c>
-      <c r="AI515" s="64"/>
-      <c r="AJ515" s="1"/>
+      <c r="AI515" s="64">
+        <v>1</v>
+      </c>
+      <c r="AJ515" s="1" t="s">
+        <v>1455</v>
+      </c>
       <c r="AK515" s="65">
-        <v>0</v>
+        <f>27611.06/12</f>
+        <v>2300.9216666666666</v>
       </c>
       <c r="AL515" s="1"/>
       <c r="AM515" s="1"/>
-      <c r="AN515" s="85"/>
-      <c r="AO515" s="90"/>
+      <c r="AN515" s="89"/>
+      <c r="AO515" s="86"/>
     </row>
     <row r="516" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A516" s="19" t="s">
@@ -59648,17 +59721,22 @@
         <f>IF(AG516=100%,Y516," ")</f>
         <v>15.870118400000001</v>
       </c>
-      <c r="AI516" s="64"/>
-      <c r="AJ516" s="1"/>
+      <c r="AI516" s="64">
+        <v>1</v>
+      </c>
+      <c r="AJ516" s="1" t="s">
+        <v>1453</v>
+      </c>
       <c r="AK516" s="65">
-        <v>0</v>
+        <f>42227.41/12</f>
+        <v>3518.9508333333338</v>
       </c>
       <c r="AL516" s="1"/>
       <c r="AM516" s="1"/>
-      <c r="AN516" s="85"/>
-      <c r="AO516" s="90"/>
+      <c r="AN516" s="89"/>
+      <c r="AO516" s="86"/>
     </row>
-    <row r="517" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A517" s="19" t="s">
         <v>369</v>
       </c>
@@ -59700,7 +59778,7 @@
         <v>186</v>
       </c>
       <c r="O517" s="6" t="s">
-        <v>46</v>
+        <v>137</v>
       </c>
       <c r="P517" s="6"/>
       <c r="Q517" s="27"/>
@@ -59759,16 +59837,17 @@
       <c r="AI517" s="64">
         <v>2</v>
       </c>
-      <c r="AJ517" s="87" t="s">
-        <v>1449</v>
+      <c r="AJ517" s="62" t="s">
+        <v>1448</v>
       </c>
       <c r="AK517" s="65">
-        <v>451.54833333333335</v>
+        <f>451.548333333333+933.24</f>
+        <v>1384.788333333333</v>
       </c>
       <c r="AL517" s="1"/>
       <c r="AM517" s="1"/>
-      <c r="AN517" s="85"/>
-      <c r="AO517" s="90"/>
+      <c r="AN517" s="89"/>
+      <c r="AO517" s="86"/>
     </row>
     <row r="518" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A518" s="19" t="s">
@@ -59783,7 +59862,9 @@
       <c r="D518" s="23">
         <v>1150</v>
       </c>
-      <c r="E518" s="23"/>
+      <c r="E518" s="23">
+        <v>250</v>
+      </c>
       <c r="F518" s="23" t="s">
         <v>1158</v>
       </c>
@@ -59809,7 +59890,9 @@
       <c r="N518" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="O518" s="6"/>
+      <c r="O518" s="6" t="s">
+        <v>137</v>
+      </c>
       <c r="P518" s="6"/>
       <c r="Q518" s="27"/>
       <c r="R518" s="28" t="s">
@@ -59864,15 +59947,20 @@
         <f>IF(AG518=100%,Y518," ")</f>
         <v>13.909891000000002</v>
       </c>
-      <c r="AI518" s="64"/>
-      <c r="AJ518" s="1"/>
+      <c r="AI518" s="64">
+        <v>1</v>
+      </c>
+      <c r="AJ518" s="1" t="s">
+        <v>1454</v>
+      </c>
       <c r="AK518" s="65">
-        <v>0</v>
+        <f>34245.48/12</f>
+        <v>2853.7900000000004</v>
       </c>
       <c r="AL518" s="1"/>
       <c r="AM518" s="1"/>
-      <c r="AN518" s="85"/>
-      <c r="AO518" s="90"/>
+      <c r="AN518" s="89"/>
+      <c r="AO518" s="86"/>
     </row>
     <row r="519" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A519" s="19" t="s">
@@ -59887,7 +59975,9 @@
       <c r="D519" s="23">
         <v>550</v>
       </c>
-      <c r="E519" s="23"/>
+      <c r="E519" s="23">
+        <v>740</v>
+      </c>
       <c r="F519" s="23" t="s">
         <v>92</v>
       </c>
@@ -59913,7 +60003,9 @@
       <c r="N519" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="O519" s="6"/>
+      <c r="O519" s="6" t="s">
+        <v>137</v>
+      </c>
       <c r="P519" s="6"/>
       <c r="Q519" s="27"/>
       <c r="R519" s="28" t="s">
@@ -59971,14 +60063,15 @@
       <c r="AI519" s="64"/>
       <c r="AJ519" s="1"/>
       <c r="AK519" s="65">
-        <v>0</v>
+        <f>26601.63/12</f>
+        <v>2216.8025000000002</v>
       </c>
       <c r="AL519" s="1"/>
       <c r="AM519" s="1"/>
-      <c r="AN519" s="85"/>
-      <c r="AO519" s="90"/>
+      <c r="AN519" s="89"/>
+      <c r="AO519" s="86"/>
     </row>
-    <row r="520" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A520" s="19" t="s">
         <v>1163</v>
       </c>
@@ -60079,16 +60172,17 @@
       <c r="AI520" s="64">
         <v>2</v>
       </c>
-      <c r="AJ520" s="87" t="s">
-        <v>1450</v>
+      <c r="AJ520" s="62" t="s">
+        <v>1449</v>
       </c>
       <c r="AK520" s="65">
-        <v>1268.7483333333332</v>
+        <f>1268.74833333333</f>
+        <v>1268.74833333333</v>
       </c>
       <c r="AL520" s="1"/>
       <c r="AM520" s="1"/>
-      <c r="AN520" s="85"/>
-      <c r="AO520" s="90"/>
+      <c r="AN520" s="89"/>
+      <c r="AO520" s="86"/>
     </row>
     <row r="521" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A521" s="19" t="s">
@@ -60187,12 +60281,13 @@
       <c r="AI521" s="64"/>
       <c r="AJ521" s="1"/>
       <c r="AK521" s="65">
+        <f>0</f>
         <v>0</v>
       </c>
       <c r="AL521" s="1"/>
       <c r="AM521" s="1"/>
-      <c r="AN521" s="85"/>
-      <c r="AO521" s="90"/>
+      <c r="AN521" s="89"/>
+      <c r="AO521" s="86"/>
     </row>
     <row r="522" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A522" s="19" t="s">
@@ -60205,9 +60300,11 @@
         <v>1.8</v>
       </c>
       <c r="D522" s="23">
-        <v>1200</v>
-      </c>
-      <c r="E522" s="23"/>
+        <v>300</v>
+      </c>
+      <c r="E522" s="23">
+        <v>180</v>
+      </c>
       <c r="F522" s="23" t="s">
         <v>1170</v>
       </c>
@@ -60288,15 +60385,20 @@
         <f>IF(AG522=100%,Y522," ")</f>
         <v>12.292592639999999</v>
       </c>
-      <c r="AI522" s="64"/>
-      <c r="AJ522" s="1"/>
+      <c r="AI522" s="64">
+        <v>1</v>
+      </c>
+      <c r="AJ522" s="1" t="s">
+        <v>1456</v>
+      </c>
       <c r="AK522" s="65">
-        <v>0</v>
+        <f>8426.39/12</f>
+        <v>702.19916666666666</v>
       </c>
       <c r="AL522" s="1"/>
       <c r="AM522" s="1"/>
-      <c r="AN522" s="85"/>
-      <c r="AO522" s="90"/>
+      <c r="AN522" s="89"/>
+      <c r="AO522" s="86"/>
     </row>
     <row r="523" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A523" s="19" t="s">
@@ -60391,12 +60493,13 @@
       <c r="AI523" s="64"/>
       <c r="AJ523" s="1"/>
       <c r="AK523" s="65">
+        <f>0</f>
         <v>0</v>
       </c>
       <c r="AL523" s="1"/>
       <c r="AM523" s="1"/>
-      <c r="AN523" s="85"/>
-      <c r="AO523" s="90"/>
+      <c r="AN523" s="89"/>
+      <c r="AO523" s="86"/>
     </row>
     <row r="524" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A524" s="19" t="s">
@@ -60411,7 +60514,9 @@
       <c r="D524" s="23">
         <v>520</v>
       </c>
-      <c r="E524" s="23"/>
+      <c r="E524" s="23">
+        <v>248</v>
+      </c>
       <c r="F524" s="23" t="s">
         <v>1170</v>
       </c>
@@ -60437,7 +60542,9 @@
       <c r="N524" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="O524" s="6"/>
+      <c r="O524" s="6" t="s">
+        <v>137</v>
+      </c>
       <c r="P524" s="6"/>
       <c r="Q524" s="27"/>
       <c r="R524" s="28" t="s">
@@ -60492,15 +60599,20 @@
         <f>IF(AG524=100%,Y524," ")</f>
         <v>10.64362</v>
       </c>
-      <c r="AI524" s="64"/>
-      <c r="AJ524" s="1"/>
+      <c r="AI524" s="64">
+        <v>1</v>
+      </c>
+      <c r="AJ524" s="1" t="s">
+        <v>1457</v>
+      </c>
       <c r="AK524" s="65">
-        <v>0</v>
+        <f>20698.99/12</f>
+        <v>1724.9158333333335</v>
       </c>
       <c r="AL524" s="1"/>
       <c r="AM524" s="1"/>
-      <c r="AN524" s="85"/>
-      <c r="AO524" s="90"/>
+      <c r="AN524" s="89"/>
+      <c r="AO524" s="86"/>
     </row>
     <row r="525" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A525" s="19" t="s">
@@ -60544,7 +60656,7 @@
         <v>1123</v>
       </c>
       <c r="O525" s="6" t="s">
-        <v>46</v>
+        <v>137</v>
       </c>
       <c r="P525" s="6"/>
       <c r="Q525" s="27"/>
@@ -60603,16 +60715,17 @@
       <c r="AI525" s="64">
         <v>1</v>
       </c>
-      <c r="AJ525" s="87" t="s">
-        <v>1451</v>
+      <c r="AJ525" s="62" t="s">
+        <v>1450</v>
       </c>
       <c r="AK525" s="65">
-        <v>1060.1566666666665</v>
+        <f>1060.15666666667+1161.48</f>
+        <v>2221.63666666667</v>
       </c>
       <c r="AL525" s="1"/>
       <c r="AM525" s="1"/>
-      <c r="AN525" s="85"/>
-      <c r="AO525" s="90"/>
+      <c r="AN525" s="89"/>
+      <c r="AO525" s="86"/>
     </row>
     <row r="526" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A526" s="19" t="s">
@@ -60715,8 +60828,8 @@
       </c>
       <c r="AL526" s="1"/>
       <c r="AM526" s="1"/>
-      <c r="AN526" s="85"/>
-      <c r="AO526" s="90"/>
+      <c r="AN526" s="89"/>
+      <c r="AO526" s="86"/>
     </row>
     <row r="527" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A527" s="19" t="s">
@@ -60731,7 +60844,9 @@
       <c r="D527" s="23">
         <v>1100</v>
       </c>
-      <c r="E527" s="23"/>
+      <c r="E527" s="23">
+        <v>165</v>
+      </c>
       <c r="F527" s="23" t="s">
         <v>92</v>
       </c>
@@ -60821,8 +60936,8 @@
       </c>
       <c r="AL527" s="1"/>
       <c r="AM527" s="1"/>
-      <c r="AN527" s="85"/>
-      <c r="AO527" s="90"/>
+      <c r="AN527" s="89"/>
+      <c r="AO527" s="86"/>
     </row>
     <row r="528" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A528" s="19" t="s">
@@ -60921,8 +61036,8 @@
       </c>
       <c r="AL528" s="1"/>
       <c r="AM528" s="1"/>
-      <c r="AN528" s="85"/>
-      <c r="AO528" s="90"/>
+      <c r="AN528" s="89"/>
+      <c r="AO528" s="86"/>
     </row>
     <row r="529" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A529" s="19" t="s">
@@ -60937,7 +61052,9 @@
       <c r="D529" s="23">
         <v>375</v>
       </c>
-      <c r="E529" s="23"/>
+      <c r="E529" s="23">
+        <v>183</v>
+      </c>
       <c r="F529" s="23" t="s">
         <v>1178</v>
       </c>
@@ -60961,7 +61078,9 @@
       <c r="N529" s="6">
         <v>246</v>
       </c>
-      <c r="O529" s="6"/>
+      <c r="O529" s="6" t="s">
+        <v>137</v>
+      </c>
       <c r="P529" s="6"/>
       <c r="Q529" s="27"/>
       <c r="R529" s="28" t="s">
@@ -61016,15 +61135,20 @@
         <f>IF(AG529=100%,Y529," ")</f>
         <v>6.8000640000000008</v>
       </c>
-      <c r="AI529" s="64"/>
-      <c r="AJ529" s="1"/>
+      <c r="AI529" s="64">
+        <v>1</v>
+      </c>
+      <c r="AJ529" s="1" t="s">
+        <v>1458</v>
+      </c>
       <c r="AK529" s="65">
-        <v>0</v>
+        <f>6829.6/12</f>
+        <v>569.13333333333333</v>
       </c>
       <c r="AL529" s="1"/>
       <c r="AM529" s="1"/>
-      <c r="AN529" s="85"/>
-      <c r="AO529" s="90"/>
+      <c r="AN529" s="89"/>
+      <c r="AO529" s="86"/>
     </row>
     <row r="530" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A530" s="19" t="s">
@@ -61127,8 +61251,8 @@
       </c>
       <c r="AL530" s="1"/>
       <c r="AM530" s="1"/>
-      <c r="AN530" s="85"/>
-      <c r="AO530" s="90"/>
+      <c r="AN530" s="89"/>
+      <c r="AO530" s="86"/>
     </row>
     <row r="531" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A531" s="19" t="s">
@@ -61231,8 +61355,8 @@
       </c>
       <c r="AL531" s="1"/>
       <c r="AM531" s="1"/>
-      <c r="AN531" s="85"/>
-      <c r="AO531" s="90"/>
+      <c r="AN531" s="89"/>
+      <c r="AO531" s="86"/>
     </row>
     <row r="532" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A532" s="19" t="s">
@@ -61245,9 +61369,11 @@
         <v>2.5</v>
       </c>
       <c r="D532" s="23">
-        <v>1050</v>
-      </c>
-      <c r="E532" s="23"/>
+        <v>525</v>
+      </c>
+      <c r="E532" s="23">
+        <v>97</v>
+      </c>
       <c r="F532" s="23" t="s">
         <v>1191</v>
       </c>
@@ -61273,7 +61399,9 @@
       <c r="N532" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="O532" s="6"/>
+      <c r="O532" s="6" t="s">
+        <v>137</v>
+      </c>
       <c r="P532" s="6"/>
       <c r="Q532" s="27"/>
       <c r="R532" s="28" t="s">
@@ -61328,15 +61456,20 @@
         <f>IF(AG532=100%,Y532," ")</f>
         <v>6.3897599999999999</v>
       </c>
-      <c r="AI532" s="64"/>
-      <c r="AJ532" s="1"/>
+      <c r="AI532" s="64">
+        <v>1</v>
+      </c>
+      <c r="AJ532" s="1" t="s">
+        <v>1459</v>
+      </c>
       <c r="AK532" s="65">
-        <v>0</v>
+        <f>9529.58/12</f>
+        <v>794.13166666666666</v>
       </c>
       <c r="AL532" s="1"/>
       <c r="AM532" s="1"/>
-      <c r="AN532" s="85"/>
-      <c r="AO532" s="90"/>
+      <c r="AN532" s="89"/>
+      <c r="AO532" s="86"/>
     </row>
     <row r="533" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A533" s="19" t="s">
@@ -61351,7 +61484,9 @@
       <c r="D533" s="23">
         <v>467</v>
       </c>
-      <c r="E533" s="23"/>
+      <c r="E533" s="23">
+        <v>130</v>
+      </c>
       <c r="F533" s="23" t="s">
         <v>1178</v>
       </c>
@@ -61375,7 +61510,9 @@
       <c r="N533" s="6">
         <v>246</v>
       </c>
-      <c r="O533" s="6"/>
+      <c r="O533" s="6" t="s">
+        <v>137</v>
+      </c>
       <c r="P533" s="6"/>
       <c r="Q533" s="27"/>
       <c r="R533" s="28" t="s">
@@ -61430,15 +61567,20 @@
         <f>IF(AG533=100%,Y533," ")</f>
         <v>5.9438399999999998</v>
       </c>
-      <c r="AI533" s="64"/>
-      <c r="AJ533" s="1"/>
+      <c r="AI533" s="64">
+        <v>1</v>
+      </c>
+      <c r="AJ533" s="1">
+        <f>6072.26/12</f>
+        <v>506.0216666666667</v>
+      </c>
       <c r="AK533" s="65">
         <v>0</v>
       </c>
       <c r="AL533" s="1"/>
       <c r="AM533" s="1"/>
-      <c r="AN533" s="85"/>
-      <c r="AO533" s="90"/>
+      <c r="AN533" s="89"/>
+      <c r="AO533" s="86"/>
     </row>
     <row r="534" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A534" s="19" t="s">
@@ -61541,8 +61683,8 @@
       </c>
       <c r="AL534" s="1"/>
       <c r="AM534" s="1"/>
-      <c r="AN534" s="85"/>
-      <c r="AO534" s="90"/>
+      <c r="AN534" s="89"/>
+      <c r="AO534" s="86"/>
     </row>
     <row r="535" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A535" s="19" t="s">
@@ -61555,9 +61697,11 @@
         <v>0.75</v>
       </c>
       <c r="D535" s="23">
-        <v>1000</v>
-      </c>
-      <c r="E535" s="23"/>
+        <v>500</v>
+      </c>
+      <c r="E535" s="23">
+        <v>325</v>
+      </c>
       <c r="F535" s="23" t="s">
         <v>92</v>
       </c>
@@ -61638,15 +61782,20 @@
         <f>IF(AG535=100%,Y535," ")</f>
         <v>5.6067839999999993</v>
       </c>
-      <c r="AI535" s="64"/>
-      <c r="AJ535" s="1"/>
+      <c r="AI535" s="64">
+        <v>1</v>
+      </c>
+      <c r="AJ535" s="1" t="s">
+        <v>1461</v>
+      </c>
       <c r="AK535" s="65">
-        <v>0</v>
+        <f>10239.63/12</f>
+        <v>853.3024999999999</v>
       </c>
       <c r="AL535" s="1"/>
       <c r="AM535" s="1"/>
-      <c r="AN535" s="85"/>
-      <c r="AO535" s="90"/>
+      <c r="AN535" s="89"/>
+      <c r="AO535" s="86"/>
     </row>
     <row r="536" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A536" s="19" t="s">
@@ -61661,7 +61810,9 @@
       <c r="D536" s="23">
         <v>750</v>
       </c>
-      <c r="E536" s="23"/>
+      <c r="E536" s="23">
+        <v>241</v>
+      </c>
       <c r="F536" s="23" t="s">
         <v>92</v>
       </c>
@@ -61685,7 +61836,9 @@
       <c r="N536" s="6">
         <v>246</v>
       </c>
-      <c r="O536" s="6"/>
+      <c r="O536" s="6" t="s">
+        <v>137</v>
+      </c>
       <c r="P536" s="6"/>
       <c r="Q536" s="27"/>
       <c r="R536" s="28" t="s">
@@ -61740,14 +61893,19 @@
         <f>IF(AG536=100%,Y536," ")</f>
         <v>5.1632960000000008</v>
       </c>
-      <c r="AI536" s="64"/>
-      <c r="AJ536" s="1"/>
+      <c r="AI536" s="64">
+        <v>1</v>
+      </c>
+      <c r="AJ536" s="1" t="s">
+        <v>1463</v>
+      </c>
       <c r="AK536" s="65">
-        <v>0</v>
+        <f>25247/12</f>
+        <v>2103.9166666666665</v>
       </c>
       <c r="AL536" s="1"/>
       <c r="AM536" s="1"/>
-      <c r="AN536" s="85"/>
+      <c r="AN536" s="89"/>
     </row>
     <row r="537" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A537" s="19" t="s">
@@ -61760,9 +61918,11 @@
         <v>0.8</v>
       </c>
       <c r="D537" s="23">
-        <v>1050</v>
-      </c>
-      <c r="E537" s="23"/>
+        <v>350</v>
+      </c>
+      <c r="E537" s="23">
+        <v>180</v>
+      </c>
       <c r="F537" s="23" t="s">
         <v>92</v>
       </c>
@@ -61788,7 +61948,9 @@
       <c r="N537" s="6" t="s">
         <v>1123</v>
       </c>
-      <c r="O537" s="6"/>
+      <c r="O537" s="6" t="s">
+        <v>137</v>
+      </c>
       <c r="P537" s="6"/>
       <c r="Q537" s="27"/>
       <c r="R537" s="28" t="s">
@@ -61843,14 +62005,19 @@
         <f>IF(AG537=100%,Y537," ")</f>
         <v>5.0388000000000002</v>
       </c>
-      <c r="AI537" s="64"/>
-      <c r="AJ537" s="1"/>
+      <c r="AI537" s="64">
+        <v>1</v>
+      </c>
+      <c r="AJ537" s="1" t="s">
+        <v>1462</v>
+      </c>
       <c r="AK537" s="65">
-        <v>0</v>
+        <f>8902.03/12</f>
+        <v>741.83583333333343</v>
       </c>
       <c r="AL537" s="1"/>
       <c r="AM537" s="1"/>
-      <c r="AN537" s="85"/>
+      <c r="AN537" s="89"/>
     </row>
     <row r="538" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A538" s="19" t="s">
@@ -61953,7 +62120,7 @@
       </c>
       <c r="AL538" s="1"/>
       <c r="AM538" s="1"/>
-      <c r="AN538" s="85"/>
+      <c r="AN538" s="89"/>
     </row>
     <row r="539" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A539" s="19" t="s">
@@ -62052,7 +62219,7 @@
       </c>
       <c r="AL539" s="1"/>
       <c r="AM539" s="1"/>
-      <c r="AN539" s="85"/>
+      <c r="AN539" s="89"/>
     </row>
     <row r="540" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A540" s="19" t="s">
@@ -62153,7 +62320,7 @@
       </c>
       <c r="AL540" s="1"/>
       <c r="AM540" s="1"/>
-      <c r="AN540" s="85"/>
+      <c r="AN540" s="89"/>
     </row>
     <row r="541" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A541" s="19" t="s">
@@ -62256,7 +62423,7 @@
       </c>
       <c r="AL541" s="1"/>
       <c r="AM541" s="1"/>
-      <c r="AN541" s="85"/>
+      <c r="AN541" s="89"/>
     </row>
     <row r="542" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A542" s="19" t="s">
@@ -62269,9 +62436,11 @@
         <v>1.5</v>
       </c>
       <c r="D542" s="23">
-        <v>1050</v>
-      </c>
-      <c r="E542" s="23"/>
+        <v>350</v>
+      </c>
+      <c r="E542" s="23">
+        <v>161</v>
+      </c>
       <c r="F542" s="23" t="s">
         <v>1170</v>
       </c>
@@ -62297,7 +62466,9 @@
       <c r="N542" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="O542" s="6"/>
+      <c r="O542" s="6" t="s">
+        <v>137</v>
+      </c>
       <c r="P542" s="6"/>
       <c r="Q542" s="27"/>
       <c r="R542" s="28" t="s">
@@ -62352,14 +62523,19 @@
         <f>IF(AG542=100%,Y542," ")</f>
         <v>4.1429680000000007</v>
       </c>
-      <c r="AI542" s="64"/>
-      <c r="AJ542" s="1"/>
+      <c r="AI542" s="64">
+        <v>1</v>
+      </c>
+      <c r="AJ542" s="1" t="s">
+        <v>1464</v>
+      </c>
       <c r="AK542" s="65">
-        <v>0</v>
+        <f>6584.07/12</f>
+        <v>548.67250000000001</v>
       </c>
       <c r="AL542" s="1"/>
       <c r="AM542" s="1"/>
-      <c r="AN542" s="85"/>
+      <c r="AN542" s="89"/>
     </row>
     <row r="543" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A543" s="19" t="s">
@@ -62462,7 +62638,7 @@
       </c>
       <c r="AL543" s="1"/>
       <c r="AM543" s="1"/>
-      <c r="AN543" s="85"/>
+      <c r="AN543" s="89"/>
     </row>
     <row r="544" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A544" s="19" t="s">
@@ -62475,9 +62651,11 @@
         <v>1.5</v>
       </c>
       <c r="D544" s="23">
-        <v>1100</v>
-      </c>
-      <c r="E544" s="23"/>
+        <v>367</v>
+      </c>
+      <c r="E544" s="23">
+        <v>145</v>
+      </c>
       <c r="F544" s="23" t="s">
         <v>1170</v>
       </c>
@@ -62503,7 +62681,9 @@
       <c r="N544" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="O544" s="6"/>
+      <c r="O544" s="6" t="s">
+        <v>137</v>
+      </c>
       <c r="P544" s="6"/>
       <c r="Q544" s="27"/>
       <c r="R544" s="28" t="s">
@@ -62558,14 +62738,19 @@
         <f>IF(AG544=100%,Y544," ")</f>
         <v>3.9114491999999998</v>
       </c>
-      <c r="AI544" s="64"/>
-      <c r="AJ544" s="1"/>
+      <c r="AI544" s="64">
+        <v>1</v>
+      </c>
+      <c r="AJ544" s="1" t="s">
+        <v>1465</v>
+      </c>
       <c r="AK544" s="65">
-        <v>0</v>
+        <f>6302.45/12</f>
+        <v>525.20416666666665</v>
       </c>
       <c r="AL544" s="1"/>
       <c r="AM544" s="1"/>
-      <c r="AN544" s="85"/>
+      <c r="AN544" s="89"/>
     </row>
     <row r="545" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A545" s="19" t="s">
@@ -62668,7 +62853,7 @@
       </c>
       <c r="AL545" s="1"/>
       <c r="AM545" s="1"/>
-      <c r="AN545" s="85"/>
+      <c r="AN545" s="89"/>
     </row>
     <row r="546" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A546" s="19" t="s">
@@ -62681,9 +62866,11 @@
         <v>1.6</v>
       </c>
       <c r="D546" s="23">
-        <v>1250</v>
-      </c>
-      <c r="E546" s="23"/>
+        <v>417</v>
+      </c>
+      <c r="E546" s="23">
+        <v>125</v>
+      </c>
       <c r="F546" s="23" t="s">
         <v>1170</v>
       </c>
@@ -62709,7 +62896,9 @@
       <c r="N546" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="O546" s="6"/>
+      <c r="O546" s="6" t="s">
+        <v>137</v>
+      </c>
       <c r="P546" s="6"/>
       <c r="Q546" s="27"/>
       <c r="R546" s="28" t="s">
@@ -62764,14 +62953,19 @@
         <f>IF(AG546=100%,Y546," ")</f>
         <v>3.834384</v>
       </c>
-      <c r="AI546" s="64"/>
-      <c r="AJ546" s="1"/>
+      <c r="AI546" s="64">
+        <v>1</v>
+      </c>
+      <c r="AJ546" s="1" t="s">
+        <v>1466</v>
+      </c>
       <c r="AK546" s="65">
-        <v>0</v>
+        <f>6848.75/12</f>
+        <v>570.72916666666663</v>
       </c>
       <c r="AL546" s="1"/>
       <c r="AM546" s="1"/>
-      <c r="AN546" s="85"/>
+      <c r="AN546" s="89"/>
     </row>
     <row r="547" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A547" s="19" t="s">
@@ -62874,7 +63068,7 @@
       </c>
       <c r="AL547" s="1"/>
       <c r="AM547" s="1"/>
-      <c r="AN547" s="85"/>
+      <c r="AN547" s="89"/>
     </row>
     <row r="548" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A548" s="19" t="s">
@@ -62977,7 +63171,7 @@
       </c>
       <c r="AL548" s="1"/>
       <c r="AM548" s="1"/>
-      <c r="AN548" s="85"/>
+      <c r="AN548" s="89"/>
     </row>
     <row r="549" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A549" s="19" t="s">
@@ -63080,7 +63274,7 @@
       </c>
       <c r="AL549" s="1"/>
       <c r="AM549" s="1"/>
-      <c r="AN549" s="85"/>
+      <c r="AN549" s="89"/>
     </row>
     <row r="550" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A550" s="19" t="s">
@@ -63181,7 +63375,7 @@
       </c>
       <c r="AL550" s="1"/>
       <c r="AM550" s="1"/>
-      <c r="AN550" s="85"/>
+      <c r="AN550" s="89"/>
     </row>
     <row r="551" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A551" s="19" t="s">
@@ -63284,7 +63478,7 @@
       </c>
       <c r="AL551" s="1"/>
       <c r="AM551" s="1"/>
-      <c r="AN551" s="85"/>
+      <c r="AN551" s="89"/>
     </row>
     <row r="552" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A552" s="19" t="s">
@@ -63387,7 +63581,7 @@
       </c>
       <c r="AL552" s="1"/>
       <c r="AM552" s="1"/>
-      <c r="AN552" s="85"/>
+      <c r="AN552" s="89"/>
     </row>
     <row r="553" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A553" s="19" t="s">
@@ -63488,7 +63682,7 @@
       </c>
       <c r="AL553" s="1"/>
       <c r="AM553" s="1"/>
-      <c r="AN553" s="85"/>
+      <c r="AN553" s="89"/>
     </row>
     <row r="554" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A554" s="19" t="s">
@@ -63591,7 +63785,7 @@
       </c>
       <c r="AL554" s="1"/>
       <c r="AM554" s="1"/>
-      <c r="AN554" s="85"/>
+      <c r="AN554" s="89"/>
     </row>
     <row r="555" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A555" s="19" t="s">
@@ -63694,7 +63888,7 @@
       </c>
       <c r="AL555" s="1"/>
       <c r="AM555" s="1"/>
-      <c r="AN555" s="85"/>
+      <c r="AN555" s="89"/>
     </row>
     <row r="556" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A556" s="19" t="s">
@@ -63795,7 +63989,7 @@
       </c>
       <c r="AL556" s="1"/>
       <c r="AM556" s="1"/>
-      <c r="AN556" s="85"/>
+      <c r="AN556" s="89"/>
     </row>
     <row r="557" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A557" s="19" t="s">
@@ -63898,7 +64092,7 @@
       </c>
       <c r="AL557" s="1"/>
       <c r="AM557" s="1"/>
-      <c r="AN557" s="85"/>
+      <c r="AN557" s="89"/>
     </row>
     <row r="558" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A558" s="19" t="s">
@@ -63913,7 +64107,9 @@
       <c r="D558" s="23">
         <v>350</v>
       </c>
-      <c r="E558" s="23"/>
+      <c r="E558" s="23">
+        <v>107</v>
+      </c>
       <c r="F558" s="23" t="s">
         <v>1219</v>
       </c>
@@ -63937,7 +64133,9 @@
       <c r="N558" s="6">
         <v>246</v>
       </c>
-      <c r="O558" s="6"/>
+      <c r="O558" s="6" t="s">
+        <v>137</v>
+      </c>
       <c r="P558" s="6"/>
       <c r="Q558" s="27"/>
       <c r="R558" s="28" t="s">
@@ -63992,14 +64190,19 @@
         <f>IF(AG558=100%,Y558," ")</f>
         <v>2.2925439999999999</v>
       </c>
-      <c r="AI558" s="64"/>
-      <c r="AJ558" s="1"/>
+      <c r="AI558" s="64">
+        <v>1</v>
+      </c>
+      <c r="AJ558" s="1" t="s">
+        <v>1467</v>
+      </c>
       <c r="AK558" s="65">
-        <v>0</v>
+        <f>8029.74/12</f>
+        <v>669.14499999999998</v>
       </c>
       <c r="AL558" s="1"/>
       <c r="AM558" s="1"/>
-      <c r="AN558" s="85"/>
+      <c r="AN558" s="89"/>
     </row>
     <row r="559" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A559" s="19" t="s">
@@ -64102,7 +64305,7 @@
       </c>
       <c r="AL559" s="1"/>
       <c r="AM559" s="1"/>
-      <c r="AN559" s="85"/>
+      <c r="AN559" s="89"/>
     </row>
     <row r="560" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A560" s="19" t="s">
@@ -64205,7 +64408,7 @@
       </c>
       <c r="AL560" s="1"/>
       <c r="AM560" s="1"/>
-      <c r="AN560" s="85"/>
+      <c r="AN560" s="89"/>
     </row>
     <row r="561" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A561" s="19" t="s">
@@ -64220,7 +64423,9 @@
       <c r="D561" s="23">
         <v>350</v>
       </c>
-      <c r="E561" s="23"/>
+      <c r="E561" s="23">
+        <v>250</v>
+      </c>
       <c r="F561" s="23" t="s">
         <v>92</v>
       </c>
@@ -64246,7 +64451,9 @@
       <c r="N561" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="O561" s="6"/>
+      <c r="O561" s="6" t="s">
+        <v>137</v>
+      </c>
       <c r="P561" s="6"/>
       <c r="Q561" s="27"/>
       <c r="R561" s="28" t="s">
@@ -64301,14 +64508,19 @@
         <f>IF(AG561=100%,Y561," ")</f>
         <v>2.1762000000000001</v>
       </c>
-      <c r="AI561" s="64"/>
-      <c r="AJ561" s="1"/>
+      <c r="AI561" s="64">
+        <v>1</v>
+      </c>
+      <c r="AJ561" s="1" t="s">
+        <v>1235</v>
+      </c>
       <c r="AK561" s="65">
-        <v>0</v>
+        <f>7375.39/12</f>
+        <v>614.6158333333334</v>
       </c>
       <c r="AL561" s="1"/>
       <c r="AM561" s="1"/>
-      <c r="AN561" s="85"/>
+      <c r="AN561" s="89"/>
     </row>
     <row r="562" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A562" s="19" t="s">
@@ -64323,7 +64535,9 @@
       <c r="D562" s="23">
         <v>270</v>
       </c>
-      <c r="E562" s="23"/>
+      <c r="E562" s="23">
+        <v>131</v>
+      </c>
       <c r="F562" s="23" t="s">
         <v>92</v>
       </c>
@@ -64347,7 +64561,9 @@
       <c r="N562" s="6">
         <v>246</v>
       </c>
-      <c r="O562" s="6"/>
+      <c r="O562" s="6" t="s">
+        <v>137</v>
+      </c>
       <c r="P562" s="6"/>
       <c r="Q562" s="27"/>
       <c r="R562" s="28" t="s">
@@ -64402,14 +64618,19 @@
         <f>IF(AG562=100%,Y562," ")</f>
         <v>2.04</v>
       </c>
-      <c r="AI562" s="64"/>
-      <c r="AJ562" s="1"/>
+      <c r="AI562" s="64">
+        <v>1</v>
+      </c>
+      <c r="AJ562" s="1" t="s">
+        <v>1468</v>
+      </c>
       <c r="AK562" s="65">
-        <v>0</v>
+        <f>6109.21/12</f>
+        <v>509.10083333333336</v>
       </c>
       <c r="AL562" s="1"/>
       <c r="AM562" s="1"/>
-      <c r="AN562" s="85"/>
+      <c r="AN562" s="89"/>
     </row>
     <row r="563" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A563" s="19" t="s">
@@ -64510,7 +64731,7 @@
       </c>
       <c r="AL563" s="1"/>
       <c r="AM563" s="1"/>
-      <c r="AN563" s="85"/>
+      <c r="AN563" s="89"/>
     </row>
     <row r="564" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A564" s="19" t="s">
@@ -64613,7 +64834,7 @@
       </c>
       <c r="AL564" s="1"/>
       <c r="AM564" s="1"/>
-      <c r="AN564" s="85"/>
+      <c r="AN564" s="89"/>
     </row>
     <row r="565" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A565" s="32" t="s">
@@ -64714,7 +64935,7 @@
       </c>
       <c r="AL565" s="1"/>
       <c r="AM565" s="1"/>
-      <c r="AN565" s="85"/>
+      <c r="AN565" s="89"/>
     </row>
     <row r="566" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A566" s="19" t="s">
@@ -64817,7 +65038,7 @@
       </c>
       <c r="AL566" s="1"/>
       <c r="AM566" s="1"/>
-      <c r="AN566" s="85"/>
+      <c r="AN566" s="89"/>
     </row>
     <row r="567" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A567" s="19" t="s">
@@ -64830,9 +65051,11 @@
         <v>1.5</v>
       </c>
       <c r="D567" s="23">
-        <v>1050</v>
-      </c>
-      <c r="E567" s="23"/>
+        <v>263</v>
+      </c>
+      <c r="E567" s="23">
+        <v>107</v>
+      </c>
       <c r="F567" s="23" t="s">
         <v>1170</v>
       </c>
@@ -64858,7 +65081,9 @@
       <c r="N567" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="O567" s="6"/>
+      <c r="O567" s="6" t="s">
+        <v>137</v>
+      </c>
       <c r="P567" s="6"/>
       <c r="Q567" s="27"/>
       <c r="R567" s="28" t="s">
@@ -64913,14 +65138,19 @@
         <f>IF(AG567=100%,Y567," ")</f>
         <v>1.004256</v>
       </c>
-      <c r="AI567" s="64"/>
-      <c r="AJ567" s="1"/>
+      <c r="AI567" s="64">
+        <v>1</v>
+      </c>
+      <c r="AJ567" s="1" t="s">
+        <v>1469</v>
+      </c>
       <c r="AK567" s="65">
-        <v>0</v>
+        <f>7591.66/12</f>
+        <v>632.63833333333332</v>
       </c>
       <c r="AL567" s="1"/>
       <c r="AM567" s="1"/>
-      <c r="AN567" s="85"/>
+      <c r="AN567" s="89"/>
     </row>
     <row r="568" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A568" s="19" t="s">
@@ -65021,7 +65251,7 @@
       </c>
       <c r="AL568" s="1"/>
       <c r="AM568" s="1"/>
-      <c r="AN568" s="85"/>
+      <c r="AN568" s="89"/>
     </row>
     <row r="569" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A569" s="19" t="s">
@@ -65122,7 +65352,7 @@
       </c>
       <c r="AL569" s="1"/>
       <c r="AM569" s="1"/>
-      <c r="AN569" s="85"/>
+      <c r="AN569" s="89"/>
     </row>
     <row r="570" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A570" s="19" t="s">
@@ -65223,7 +65453,7 @@
       </c>
       <c r="AL570" s="1"/>
       <c r="AM570" s="1"/>
-      <c r="AN570" s="85"/>
+      <c r="AN570" s="89"/>
     </row>
     <row r="571" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A571" s="19" t="s">
@@ -65326,7 +65556,7 @@
       </c>
       <c r="AL571" s="1"/>
       <c r="AM571" s="1"/>
-      <c r="AN571" s="85"/>
+      <c r="AN571" s="89"/>
     </row>
     <row r="572" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A572" s="19" t="s">
@@ -65429,7 +65659,7 @@
       </c>
       <c r="AL572" s="1"/>
       <c r="AM572" s="1"/>
-      <c r="AN572" s="85"/>
+      <c r="AN572" s="89"/>
     </row>
     <row r="573" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A573" s="19" t="s">
@@ -65532,7 +65762,7 @@
       </c>
       <c r="AL573" s="1"/>
       <c r="AM573" s="1"/>
-      <c r="AN573" s="85"/>
+      <c r="AN573" s="89"/>
     </row>
     <row r="574" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A574" s="19" t="s">
@@ -65635,7 +65865,7 @@
       </c>
       <c r="AL574" s="1"/>
       <c r="AM574" s="1"/>
-      <c r="AN574" s="85"/>
+      <c r="AN574" s="89"/>
     </row>
     <row r="575" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A575" s="19" t="s">
@@ -65738,7 +65968,7 @@
       </c>
       <c r="AL575" s="1"/>
       <c r="AM575" s="1"/>
-      <c r="AN575" s="85"/>
+      <c r="AN575" s="89"/>
     </row>
     <row r="576" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A576" s="19" t="s">
@@ -65839,7 +66069,7 @@
       </c>
       <c r="AL576" s="1"/>
       <c r="AM576" s="1"/>
-      <c r="AN576" s="85"/>
+      <c r="AN576" s="89"/>
     </row>
     <row r="577" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A577" s="19" t="s">
@@ -65942,7 +66172,7 @@
       </c>
       <c r="AL577" s="1"/>
       <c r="AM577" s="1"/>
-      <c r="AN577" s="85"/>
+      <c r="AN577" s="89"/>
     </row>
     <row r="578" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A578" s="19" t="s">
@@ -66045,7 +66275,7 @@
       </c>
       <c r="AL578" s="1"/>
       <c r="AM578" s="1"/>
-      <c r="AN578" s="85"/>
+      <c r="AN578" s="89"/>
     </row>
     <row r="579" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A579" s="19" t="s">
@@ -66148,7 +66378,7 @@
       </c>
       <c r="AL579" s="1"/>
       <c r="AM579" s="1"/>
-      <c r="AN579" s="85"/>
+      <c r="AN579" s="89"/>
     </row>
     <row r="580" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A580" s="19" t="s">
@@ -66251,7 +66481,7 @@
       </c>
       <c r="AL580" s="1"/>
       <c r="AM580" s="1"/>
-      <c r="AN580" s="85"/>
+      <c r="AN580" s="89"/>
     </row>
     <row r="581" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A581" s="19" t="s">
@@ -66354,7 +66584,7 @@
       </c>
       <c r="AL581" s="1"/>
       <c r="AM581" s="1"/>
-      <c r="AN581" s="85"/>
+      <c r="AN581" s="89"/>
     </row>
     <row r="582" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A582" s="19" t="s">
@@ -66457,7 +66687,7 @@
       </c>
       <c r="AL582" s="1"/>
       <c r="AM582" s="1"/>
-      <c r="AN582" s="85"/>
+      <c r="AN582" s="89"/>
     </row>
     <row r="583" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A583" s="19" t="s">
@@ -66560,7 +66790,7 @@
       </c>
       <c r="AL583" s="1"/>
       <c r="AM583" s="1"/>
-      <c r="AN583" s="85"/>
+      <c r="AN583" s="89"/>
     </row>
     <row r="584" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A584" s="19" t="s">
@@ -66659,7 +66889,7 @@
       </c>
       <c r="AL584" s="1"/>
       <c r="AM584" s="1"/>
-      <c r="AN584" s="85"/>
+      <c r="AN584" s="89"/>
     </row>
     <row r="585" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A585" s="19" t="s">
@@ -66744,7 +66974,7 @@
       </c>
       <c r="AL585" s="1"/>
       <c r="AM585" s="1"/>
-      <c r="AN585" s="85"/>
+      <c r="AN585" s="89"/>
     </row>
     <row r="586" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A586" s="19" t="s">
@@ -66833,7 +67063,7 @@
       </c>
       <c r="AL586" s="1"/>
       <c r="AM586" s="1"/>
-      <c r="AN586" s="85"/>
+      <c r="AN586" s="89"/>
     </row>
     <row r="587" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A587" s="19" t="s">
@@ -66922,7 +67152,7 @@
       </c>
       <c r="AL587" s="1"/>
       <c r="AM587" s="1"/>
-      <c r="AN587" s="85"/>
+      <c r="AN587" s="89"/>
     </row>
     <row r="588" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A588" s="22" t="s">
@@ -66997,7 +67227,7 @@
       </c>
       <c r="AL588" s="1"/>
       <c r="AM588" s="1"/>
-      <c r="AN588" s="85"/>
+      <c r="AN588" s="89"/>
     </row>
     <row r="589" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A589" s="22" t="s">
@@ -67070,7 +67300,7 @@
       </c>
       <c r="AL589" s="1"/>
       <c r="AM589" s="1"/>
-      <c r="AN589" s="85"/>
+      <c r="AN589" s="89"/>
     </row>
     <row r="590" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A590" s="22" t="s">
@@ -67143,7 +67373,7 @@
       </c>
       <c r="AL590" s="1"/>
       <c r="AM590" s="1"/>
-      <c r="AN590" s="85"/>
+      <c r="AN590" s="89"/>
     </row>
     <row r="591" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A591" s="22" t="s">
@@ -67216,7 +67446,7 @@
       </c>
       <c r="AL591" s="1"/>
       <c r="AM591" s="1"/>
-      <c r="AN591" s="85"/>
+      <c r="AN591" s="89"/>
     </row>
     <row r="592" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A592" s="22" t="s">
@@ -67289,7 +67519,7 @@
       </c>
       <c r="AL592" s="1"/>
       <c r="AM592" s="1"/>
-      <c r="AN592" s="85"/>
+      <c r="AN592" s="89"/>
     </row>
     <row r="593" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A593" s="22" t="s">
@@ -67362,7 +67592,7 @@
       </c>
       <c r="AL593" s="1"/>
       <c r="AM593" s="1"/>
-      <c r="AN593" s="85"/>
+      <c r="AN593" s="89"/>
     </row>
     <row r="594" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A594" s="22" t="s">
@@ -67435,7 +67665,7 @@
       </c>
       <c r="AL594" s="1"/>
       <c r="AM594" s="1"/>
-      <c r="AN594" s="85"/>
+      <c r="AN594" s="89"/>
     </row>
     <row r="595" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A595" s="22" t="s">
@@ -67508,7 +67738,7 @@
       </c>
       <c r="AL595" s="1"/>
       <c r="AM595" s="1"/>
-      <c r="AN595" s="85"/>
+      <c r="AN595" s="89"/>
     </row>
     <row r="596" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A596" s="22" t="s">
@@ -67581,7 +67811,7 @@
       </c>
       <c r="AL596" s="1"/>
       <c r="AM596" s="1"/>
-      <c r="AN596" s="85"/>
+      <c r="AN596" s="89"/>
     </row>
     <row r="597" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A597" s="22" t="s">
@@ -67654,7 +67884,7 @@
       </c>
       <c r="AL597" s="1"/>
       <c r="AM597" s="1"/>
-      <c r="AN597" s="85"/>
+      <c r="AN597" s="89"/>
     </row>
     <row r="598" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A598" s="22" t="s">
@@ -67727,7 +67957,7 @@
       </c>
       <c r="AL598" s="1"/>
       <c r="AM598" s="1"/>
-      <c r="AN598" s="85"/>
+      <c r="AN598" s="89"/>
     </row>
     <row r="599" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A599" s="22" t="s">
@@ -67800,7 +68030,7 @@
       </c>
       <c r="AL599" s="1"/>
       <c r="AM599" s="1"/>
-      <c r="AN599" s="85"/>
+      <c r="AN599" s="89"/>
     </row>
     <row r="600" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A600" s="22" t="s">
@@ -67873,7 +68103,7 @@
       </c>
       <c r="AL600" s="1"/>
       <c r="AM600" s="1"/>
-      <c r="AN600" s="85"/>
+      <c r="AN600" s="89"/>
     </row>
     <row r="601" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A601" s="22" t="s">
@@ -67946,7 +68176,7 @@
       </c>
       <c r="AL601" s="1"/>
       <c r="AM601" s="1"/>
-      <c r="AN601" s="85"/>
+      <c r="AN601" s="89"/>
     </row>
     <row r="602" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A602" s="22" t="s">
@@ -68019,7 +68249,7 @@
       </c>
       <c r="AL602" s="1"/>
       <c r="AM602" s="1"/>
-      <c r="AN602" s="85"/>
+      <c r="AN602" s="89"/>
     </row>
     <row r="603" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A603" s="22" t="s">
@@ -68094,7 +68324,7 @@
       </c>
       <c r="AL603" s="1"/>
       <c r="AM603" s="1"/>
-      <c r="AN603" s="85"/>
+      <c r="AN603" s="89"/>
     </row>
     <row r="604" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A604" s="22" t="s">
@@ -68167,7 +68397,7 @@
       </c>
       <c r="AL604" s="1"/>
       <c r="AM604" s="1"/>
-      <c r="AN604" s="85"/>
+      <c r="AN604" s="89"/>
     </row>
     <row r="605" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A605" s="22" t="s">
@@ -68240,7 +68470,7 @@
       </c>
       <c r="AL605" s="1"/>
       <c r="AM605" s="1"/>
-      <c r="AN605" s="85"/>
+      <c r="AN605" s="89"/>
     </row>
     <row r="606" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A606" s="22" t="s">
@@ -68313,7 +68543,7 @@
       </c>
       <c r="AL606" s="1"/>
       <c r="AM606" s="1"/>
-      <c r="AN606" s="85"/>
+      <c r="AN606" s="89"/>
     </row>
     <row r="607" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A607" s="22" t="s">
@@ -68386,7 +68616,7 @@
       </c>
       <c r="AL607" s="1"/>
       <c r="AM607" s="1"/>
-      <c r="AN607" s="85"/>
+      <c r="AN607" s="89"/>
     </row>
     <row r="608" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A608" s="22" t="s">
@@ -68459,7 +68689,7 @@
       </c>
       <c r="AL608" s="1"/>
       <c r="AM608" s="1"/>
-      <c r="AN608" s="85"/>
+      <c r="AN608" s="89"/>
     </row>
     <row r="609" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A609" s="22" t="s">
@@ -68532,7 +68762,7 @@
       </c>
       <c r="AL609" s="1"/>
       <c r="AM609" s="1"/>
-      <c r="AN609" s="85"/>
+      <c r="AN609" s="89"/>
     </row>
     <row r="610" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A610" s="22" t="s">
@@ -68605,7 +68835,7 @@
       </c>
       <c r="AL610" s="1"/>
       <c r="AM610" s="1"/>
-      <c r="AN610" s="85"/>
+      <c r="AN610" s="89"/>
     </row>
     <row r="611" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A611" s="22" t="s">
@@ -68678,7 +68908,7 @@
       </c>
       <c r="AL611" s="1"/>
       <c r="AM611" s="1"/>
-      <c r="AN611" s="85"/>
+      <c r="AN611" s="89"/>
     </row>
     <row r="612" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A612" s="22" t="s">
@@ -68751,7 +68981,7 @@
       </c>
       <c r="AL612" s="1"/>
       <c r="AM612" s="1"/>
-      <c r="AN612" s="85"/>
+      <c r="AN612" s="89"/>
     </row>
     <row r="613" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A613" s="22" t="s">
@@ -68824,7 +69054,7 @@
       </c>
       <c r="AL613" s="1"/>
       <c r="AM613" s="1"/>
-      <c r="AN613" s="85"/>
+      <c r="AN613" s="89"/>
     </row>
     <row r="614" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A614" s="22" t="s">
@@ -68897,7 +69127,7 @@
       </c>
       <c r="AL614" s="1"/>
       <c r="AM614" s="1"/>
-      <c r="AN614" s="85"/>
+      <c r="AN614" s="89"/>
     </row>
     <row r="615" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A615" s="22" t="s">
@@ -68970,7 +69200,7 @@
       </c>
       <c r="AL615" s="1"/>
       <c r="AM615" s="1"/>
-      <c r="AN615" s="85"/>
+      <c r="AN615" s="89"/>
     </row>
     <row r="616" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A616" s="22" t="s">
@@ -69043,7 +69273,7 @@
       </c>
       <c r="AL616" s="1"/>
       <c r="AM616" s="1"/>
-      <c r="AN616" s="85"/>
+      <c r="AN616" s="89"/>
     </row>
     <row r="617" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A617" s="22" t="s">
@@ -69116,7 +69346,7 @@
       </c>
       <c r="AL617" s="1"/>
       <c r="AM617" s="1"/>
-      <c r="AN617" s="85"/>
+      <c r="AN617" s="89"/>
     </row>
     <row r="618" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A618" s="22" t="s">
@@ -69189,7 +69419,7 @@
       </c>
       <c r="AL618" s="1"/>
       <c r="AM618" s="1"/>
-      <c r="AN618" s="85"/>
+      <c r="AN618" s="89"/>
     </row>
     <row r="619" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A619" s="22" t="s">
@@ -69262,7 +69492,7 @@
       </c>
       <c r="AL619" s="1"/>
       <c r="AM619" s="1"/>
-      <c r="AN619" s="85"/>
+      <c r="AN619" s="89"/>
     </row>
     <row r="620" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A620" s="22" t="s">
@@ -69335,7 +69565,7 @@
       </c>
       <c r="AL620" s="1"/>
       <c r="AM620" s="1"/>
-      <c r="AN620" s="85"/>
+      <c r="AN620" s="89"/>
     </row>
     <row r="621" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A621" s="22" t="s">
@@ -69408,7 +69638,7 @@
       </c>
       <c r="AL621" s="1"/>
       <c r="AM621" s="1"/>
-      <c r="AN621" s="85"/>
+      <c r="AN621" s="89"/>
     </row>
     <row r="622" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A622" s="22" t="s">
@@ -69481,7 +69711,7 @@
       </c>
       <c r="AL622" s="1"/>
       <c r="AM622" s="1"/>
-      <c r="AN622" s="85"/>
+      <c r="AN622" s="89"/>
     </row>
     <row r="623" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A623" s="22" t="s">
@@ -69554,7 +69784,7 @@
       </c>
       <c r="AL623" s="1"/>
       <c r="AM623" s="1"/>
-      <c r="AN623" s="85"/>
+      <c r="AN623" s="89"/>
     </row>
     <row r="624" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A624" s="22" t="s">
@@ -69627,7 +69857,7 @@
       </c>
       <c r="AL624" s="1"/>
       <c r="AM624" s="1"/>
-      <c r="AN624" s="85"/>
+      <c r="AN624" s="89"/>
     </row>
     <row r="625" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A625" s="22" t="s">
@@ -69700,7 +69930,7 @@
       </c>
       <c r="AL625" s="1"/>
       <c r="AM625" s="1"/>
-      <c r="AN625" s="85"/>
+      <c r="AN625" s="89"/>
     </row>
     <row r="626" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A626" s="22" t="s">
@@ -69773,7 +70003,7 @@
       </c>
       <c r="AL626" s="1"/>
       <c r="AM626" s="1"/>
-      <c r="AN626" s="85"/>
+      <c r="AN626" s="89"/>
     </row>
     <row r="627" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A627" s="22" t="s">
@@ -69846,7 +70076,7 @@
       </c>
       <c r="AL627" s="1"/>
       <c r="AM627" s="1"/>
-      <c r="AN627" s="85"/>
+      <c r="AN627" s="89"/>
     </row>
     <row r="628" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A628" s="22" t="s">
@@ -69919,7 +70149,7 @@
       </c>
       <c r="AL628" s="1"/>
       <c r="AM628" s="1"/>
-      <c r="AN628" s="85"/>
+      <c r="AN628" s="89"/>
     </row>
     <row r="629" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A629" s="22" t="s">
@@ -69992,7 +70222,7 @@
       </c>
       <c r="AL629" s="1"/>
       <c r="AM629" s="1"/>
-      <c r="AN629" s="85"/>
+      <c r="AN629" s="89"/>
     </row>
     <row r="630" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A630" s="22" t="s">
@@ -70065,7 +70295,7 @@
       </c>
       <c r="AL630" s="1"/>
       <c r="AM630" s="1"/>
-      <c r="AN630" s="85"/>
+      <c r="AN630" s="89"/>
     </row>
     <row r="631" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A631" s="22" t="s">
@@ -70138,7 +70368,7 @@
       </c>
       <c r="AL631" s="1"/>
       <c r="AM631" s="1"/>
-      <c r="AN631" s="85"/>
+      <c r="AN631" s="89"/>
     </row>
     <row r="632" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A632" s="22" t="s">
@@ -70211,7 +70441,7 @@
       </c>
       <c r="AL632" s="1"/>
       <c r="AM632" s="1"/>
-      <c r="AN632" s="85"/>
+      <c r="AN632" s="89"/>
     </row>
     <row r="633" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A633" s="22" t="s">
@@ -70284,7 +70514,7 @@
       </c>
       <c r="AL633" s="1"/>
       <c r="AM633" s="1"/>
-      <c r="AN633" s="85"/>
+      <c r="AN633" s="89"/>
     </row>
     <row r="634" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A634" s="22" t="s">
@@ -70357,7 +70587,7 @@
       </c>
       <c r="AL634" s="1"/>
       <c r="AM634" s="1"/>
-      <c r="AN634" s="85"/>
+      <c r="AN634" s="89"/>
     </row>
     <row r="635" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A635" s="22" t="s">
@@ -70430,7 +70660,7 @@
       </c>
       <c r="AL635" s="1"/>
       <c r="AM635" s="1"/>
-      <c r="AN635" s="85"/>
+      <c r="AN635" s="89"/>
     </row>
     <row r="636" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A636" s="22" t="s">
@@ -70503,7 +70733,7 @@
       </c>
       <c r="AL636" s="1"/>
       <c r="AM636" s="1"/>
-      <c r="AN636" s="85"/>
+      <c r="AN636" s="89"/>
     </row>
     <row r="637" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A637" s="22" t="s">
@@ -70576,7 +70806,7 @@
       </c>
       <c r="AL637" s="1"/>
       <c r="AM637" s="1"/>
-      <c r="AN637" s="85"/>
+      <c r="AN637" s="89"/>
     </row>
     <row r="638" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A638" s="22" t="s">
@@ -70649,7 +70879,7 @@
       </c>
       <c r="AL638" s="1"/>
       <c r="AM638" s="1"/>
-      <c r="AN638" s="85"/>
+      <c r="AN638" s="89"/>
     </row>
     <row r="639" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A639" s="22" t="s">
@@ -70722,7 +70952,7 @@
       </c>
       <c r="AL639" s="1"/>
       <c r="AM639" s="1"/>
-      <c r="AN639" s="85"/>
+      <c r="AN639" s="89"/>
     </row>
     <row r="640" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A640" s="22" t="s">
@@ -70795,7 +71025,7 @@
       </c>
       <c r="AL640" s="1"/>
       <c r="AM640" s="1"/>
-      <c r="AN640" s="85"/>
+      <c r="AN640" s="89"/>
     </row>
     <row r="641" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A641" s="22" t="s">
@@ -70868,7 +71098,7 @@
       </c>
       <c r="AL641" s="1"/>
       <c r="AM641" s="1"/>
-      <c r="AN641" s="85"/>
+      <c r="AN641" s="89"/>
     </row>
     <row r="642" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A642" s="22" t="s">
@@ -70941,7 +71171,7 @@
       </c>
       <c r="AL642" s="1"/>
       <c r="AM642" s="1"/>
-      <c r="AN642" s="85"/>
+      <c r="AN642" s="89"/>
     </row>
     <row r="643" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A643" s="22" t="s">
@@ -71014,7 +71244,7 @@
       </c>
       <c r="AL643" s="1"/>
       <c r="AM643" s="1"/>
-      <c r="AN643" s="85"/>
+      <c r="AN643" s="89"/>
     </row>
     <row r="644" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A644" s="22" t="s">
@@ -71087,7 +71317,7 @@
       </c>
       <c r="AL644" s="1"/>
       <c r="AM644" s="1"/>
-      <c r="AN644" s="85"/>
+      <c r="AN644" s="89"/>
     </row>
     <row r="645" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A645" s="22" t="s">
@@ -71160,7 +71390,7 @@
       </c>
       <c r="AL645" s="1"/>
       <c r="AM645" s="1"/>
-      <c r="AN645" s="85"/>
+      <c r="AN645" s="89"/>
     </row>
     <row r="646" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A646" s="22" t="s">
@@ -71235,7 +71465,7 @@
       </c>
       <c r="AL646" s="1"/>
       <c r="AM646" s="1"/>
-      <c r="AN646" s="85"/>
+      <c r="AN646" s="89"/>
     </row>
     <row r="647" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A647" s="22" t="s">
@@ -71308,7 +71538,7 @@
       </c>
       <c r="AL647" s="1"/>
       <c r="AM647" s="1"/>
-      <c r="AN647" s="85"/>
+      <c r="AN647" s="89"/>
     </row>
     <row r="648" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A648" s="22" t="s">
@@ -71379,7 +71609,7 @@
       </c>
       <c r="AL648" s="1"/>
       <c r="AM648" s="1"/>
-      <c r="AN648" s="85"/>
+      <c r="AN648" s="89"/>
     </row>
     <row r="649" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A649" s="22" t="s">
@@ -71452,7 +71682,7 @@
       </c>
       <c r="AL649" s="1"/>
       <c r="AM649" s="1"/>
-      <c r="AN649" s="85"/>
+      <c r="AN649" s="89"/>
     </row>
     <row r="650" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A650" s="22" t="s">
@@ -71525,7 +71755,7 @@
       </c>
       <c r="AL650" s="1"/>
       <c r="AM650" s="1"/>
-      <c r="AN650" s="85"/>
+      <c r="AN650" s="89"/>
     </row>
     <row r="651" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A651" s="22" t="s">
@@ -71598,7 +71828,7 @@
       </c>
       <c r="AL651" s="1"/>
       <c r="AM651" s="1"/>
-      <c r="AN651" s="85"/>
+      <c r="AN651" s="89"/>
     </row>
     <row r="652" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A652" s="22" t="s">
@@ -71671,7 +71901,7 @@
       </c>
       <c r="AL652" s="1"/>
       <c r="AM652" s="1"/>
-      <c r="AN652" s="85"/>
+      <c r="AN652" s="89"/>
     </row>
     <row r="653" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A653" s="22" t="s">
@@ -71744,7 +71974,7 @@
       </c>
       <c r="AL653" s="1"/>
       <c r="AM653" s="1"/>
-      <c r="AN653" s="85"/>
+      <c r="AN653" s="89"/>
     </row>
     <row r="654" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A654" s="22" t="s">
@@ -71817,7 +72047,7 @@
       </c>
       <c r="AL654" s="1"/>
       <c r="AM654" s="1"/>
-      <c r="AN654" s="85"/>
+      <c r="AN654" s="89"/>
     </row>
     <row r="655" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A655" s="22" t="s">
@@ -71890,7 +72120,7 @@
       </c>
       <c r="AL655" s="1"/>
       <c r="AM655" s="1"/>
-      <c r="AN655" s="85"/>
+      <c r="AN655" s="89"/>
     </row>
     <row r="656" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A656" s="22" t="s">
@@ -71963,7 +72193,7 @@
       </c>
       <c r="AL656" s="1"/>
       <c r="AM656" s="1"/>
-      <c r="AN656" s="85"/>
+      <c r="AN656" s="89"/>
     </row>
     <row r="657" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A657" s="22" t="s">
@@ -72036,7 +72266,7 @@
       </c>
       <c r="AL657" s="1"/>
       <c r="AM657" s="1"/>
-      <c r="AN657" s="85"/>
+      <c r="AN657" s="89"/>
     </row>
     <row r="658" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A658" s="22" t="s">
@@ -72109,7 +72339,7 @@
       </c>
       <c r="AL658" s="1"/>
       <c r="AM658" s="1"/>
-      <c r="AN658" s="85"/>
+      <c r="AN658" s="89"/>
     </row>
     <row r="659" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A659" s="22" t="s">
@@ -72182,7 +72412,7 @@
       </c>
       <c r="AL659" s="1"/>
       <c r="AM659" s="1"/>
-      <c r="AN659" s="85"/>
+      <c r="AN659" s="89"/>
     </row>
     <row r="660" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A660" s="22" t="s">
@@ -72255,7 +72485,7 @@
       </c>
       <c r="AL660" s="1"/>
       <c r="AM660" s="1"/>
-      <c r="AN660" s="85"/>
+      <c r="AN660" s="89"/>
     </row>
     <row r="661" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A661" s="22" t="s">
@@ -72338,7 +72568,7 @@
       </c>
       <c r="AL661" s="1"/>
       <c r="AM661" s="1"/>
-      <c r="AN661" s="85"/>
+      <c r="AN661" s="89"/>
     </row>
     <row r="662" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A662" s="22" t="s">
@@ -72411,7 +72641,7 @@
       </c>
       <c r="AL662" s="1"/>
       <c r="AM662" s="1"/>
-      <c r="AN662" s="85"/>
+      <c r="AN662" s="89"/>
     </row>
     <row r="663" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A663" s="22" t="s">
@@ -72484,7 +72714,7 @@
       </c>
       <c r="AL663" s="1"/>
       <c r="AM663" s="1"/>
-      <c r="AN663" s="85"/>
+      <c r="AN663" s="89"/>
     </row>
     <row r="664" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A664" s="22" t="s">
@@ -72557,7 +72787,7 @@
       </c>
       <c r="AL664" s="1"/>
       <c r="AM664" s="1"/>
-      <c r="AN664" s="85"/>
+      <c r="AN664" s="89"/>
     </row>
     <row r="665" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A665" s="22" t="s">
@@ -72630,7 +72860,7 @@
       </c>
       <c r="AL665" s="1"/>
       <c r="AM665" s="1"/>
-      <c r="AN665" s="85"/>
+      <c r="AN665" s="89"/>
     </row>
     <row r="666" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A666" s="22" t="s">
@@ -72703,7 +72933,7 @@
       </c>
       <c r="AL666" s="1"/>
       <c r="AM666" s="1"/>
-      <c r="AN666" s="85"/>
+      <c r="AN666" s="89"/>
     </row>
     <row r="667" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A667" s="22" t="s">
@@ -72776,7 +73006,7 @@
       </c>
       <c r="AL667" s="1"/>
       <c r="AM667" s="1"/>
-      <c r="AN667" s="85"/>
+      <c r="AN667" s="89"/>
     </row>
     <row r="668" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A668" s="22" t="s">
@@ -72849,7 +73079,7 @@
       </c>
       <c r="AL668" s="1"/>
       <c r="AM668" s="1"/>
-      <c r="AN668" s="85"/>
+      <c r="AN668" s="89"/>
     </row>
     <row r="669" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A669" s="22" t="s">
@@ -72922,7 +73152,7 @@
       </c>
       <c r="AL669" s="1"/>
       <c r="AM669" s="1"/>
-      <c r="AN669" s="85"/>
+      <c r="AN669" s="89"/>
     </row>
     <row r="670" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A670" s="22" t="s">
@@ -72995,7 +73225,7 @@
       </c>
       <c r="AL670" s="1"/>
       <c r="AM670" s="1"/>
-      <c r="AN670" s="85"/>
+      <c r="AN670" s="89"/>
     </row>
     <row r="671" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A671" s="22" t="s">
@@ -73066,7 +73296,7 @@
       </c>
       <c r="AL671" s="1"/>
       <c r="AM671" s="1"/>
-      <c r="AN671" s="85"/>
+      <c r="AN671" s="89"/>
     </row>
     <row r="672" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A672" s="22" t="s">
@@ -73139,7 +73369,7 @@
       </c>
       <c r="AL672" s="1"/>
       <c r="AM672" s="1"/>
-      <c r="AN672" s="85"/>
+      <c r="AN672" s="89"/>
     </row>
     <row r="673" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A673" s="22" t="s">
@@ -73212,7 +73442,7 @@
       </c>
       <c r="AL673" s="1"/>
       <c r="AM673" s="1"/>
-      <c r="AN673" s="85"/>
+      <c r="AN673" s="89"/>
     </row>
     <row r="674" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A674" s="22" t="s">
@@ -73285,7 +73515,7 @@
       </c>
       <c r="AL674" s="1"/>
       <c r="AM674" s="1"/>
-      <c r="AN674" s="85"/>
+      <c r="AN674" s="89"/>
     </row>
     <row r="675" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A675" s="22" t="s">
@@ -73358,7 +73588,7 @@
       </c>
       <c r="AL675" s="1"/>
       <c r="AM675" s="1"/>
-      <c r="AN675" s="85"/>
+      <c r="AN675" s="89"/>
     </row>
     <row r="676" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A676" s="22" t="s">
@@ -73431,7 +73661,7 @@
       </c>
       <c r="AL676" s="1"/>
       <c r="AM676" s="1"/>
-      <c r="AN676" s="85"/>
+      <c r="AN676" s="89"/>
     </row>
     <row r="677" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A677" s="22" t="s">
@@ -73504,7 +73734,7 @@
       </c>
       <c r="AL677" s="1"/>
       <c r="AM677" s="1"/>
-      <c r="AN677" s="85"/>
+      <c r="AN677" s="89"/>
     </row>
     <row r="678" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A678" s="22" t="s">
@@ -73577,7 +73807,7 @@
       </c>
       <c r="AL678" s="1"/>
       <c r="AM678" s="1"/>
-      <c r="AN678" s="85"/>
+      <c r="AN678" s="89"/>
     </row>
     <row r="679" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A679" s="22" t="s">
@@ -73650,7 +73880,7 @@
       </c>
       <c r="AL679" s="1"/>
       <c r="AM679" s="1"/>
-      <c r="AN679" s="85"/>
+      <c r="AN679" s="89"/>
     </row>
     <row r="680" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A680" s="22" t="s">
@@ -73723,7 +73953,7 @@
       </c>
       <c r="AL680" s="1"/>
       <c r="AM680" s="1"/>
-      <c r="AN680" s="85"/>
+      <c r="AN680" s="89"/>
     </row>
     <row r="681" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A681" s="22" t="s">
@@ -73796,7 +74026,7 @@
       </c>
       <c r="AL681" s="1"/>
       <c r="AM681" s="1"/>
-      <c r="AN681" s="85"/>
+      <c r="AN681" s="89"/>
     </row>
     <row r="682" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A682" s="22" t="s">
@@ -73869,7 +74099,7 @@
       </c>
       <c r="AL682" s="1"/>
       <c r="AM682" s="1"/>
-      <c r="AN682" s="85"/>
+      <c r="AN682" s="89"/>
     </row>
     <row r="683" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A683" s="22" t="s">
@@ -73942,7 +74172,7 @@
       </c>
       <c r="AL683" s="1"/>
       <c r="AM683" s="1"/>
-      <c r="AN683" s="85"/>
+      <c r="AN683" s="89"/>
     </row>
     <row r="684" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A684" s="22" t="s">
@@ -74015,7 +74245,7 @@
       </c>
       <c r="AL684" s="1"/>
       <c r="AM684" s="1"/>
-      <c r="AN684" s="85"/>
+      <c r="AN684" s="89"/>
     </row>
     <row r="685" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A685" s="22" t="s">
@@ -74088,7 +74318,7 @@
       </c>
       <c r="AL685" s="1"/>
       <c r="AM685" s="1"/>
-      <c r="AN685" s="85"/>
+      <c r="AN685" s="89"/>
     </row>
     <row r="686" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A686" s="22" t="s">
@@ -74161,7 +74391,7 @@
       </c>
       <c r="AL686" s="1"/>
       <c r="AM686" s="1"/>
-      <c r="AN686" s="85"/>
+      <c r="AN686" s="89"/>
     </row>
     <row r="687" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A687" s="22" t="s">
@@ -74234,7 +74464,7 @@
       </c>
       <c r="AL687" s="1"/>
       <c r="AM687" s="1"/>
-      <c r="AN687" s="85"/>
+      <c r="AN687" s="89"/>
     </row>
     <row r="688" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A688" s="22" t="s">
@@ -74307,7 +74537,7 @@
       </c>
       <c r="AL688" s="1"/>
       <c r="AM688" s="1"/>
-      <c r="AN688" s="85"/>
+      <c r="AN688" s="89"/>
     </row>
     <row r="689" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A689" s="22" t="s">
@@ -74380,7 +74610,7 @@
       </c>
       <c r="AL689" s="1"/>
       <c r="AM689" s="1"/>
-      <c r="AN689" s="85"/>
+      <c r="AN689" s="89"/>
     </row>
     <row r="690" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A690" s="22" t="s">
@@ -74453,7 +74683,7 @@
       </c>
       <c r="AL690" s="1"/>
       <c r="AM690" s="1"/>
-      <c r="AN690" s="85"/>
+      <c r="AN690" s="89"/>
     </row>
     <row r="691" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A691" s="22" t="s">
@@ -74526,7 +74756,7 @@
       </c>
       <c r="AL691" s="1"/>
       <c r="AM691" s="1"/>
-      <c r="AN691" s="85"/>
+      <c r="AN691" s="89"/>
     </row>
     <row r="692" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A692" s="22" t="s">
@@ -74599,7 +74829,7 @@
       </c>
       <c r="AL692" s="1"/>
       <c r="AM692" s="1"/>
-      <c r="AN692" s="85"/>
+      <c r="AN692" s="89"/>
     </row>
     <row r="693" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A693" s="22" t="s">
@@ -74672,7 +74902,7 @@
       </c>
       <c r="AL693" s="1"/>
       <c r="AM693" s="1"/>
-      <c r="AN693" s="85"/>
+      <c r="AN693" s="89"/>
     </row>
     <row r="694" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A694" s="22" t="s">
@@ -74745,7 +74975,7 @@
       </c>
       <c r="AL694" s="1"/>
       <c r="AM694" s="1"/>
-      <c r="AN694" s="85"/>
+      <c r="AN694" s="89"/>
     </row>
     <row r="695" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A695" s="22" t="s">
@@ -74818,7 +75048,7 @@
       </c>
       <c r="AL695" s="1"/>
       <c r="AM695" s="1"/>
-      <c r="AN695" s="85"/>
+      <c r="AN695" s="89"/>
     </row>
     <row r="696" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A696" s="22" t="s">
@@ -74891,7 +75121,7 @@
       </c>
       <c r="AL696" s="1"/>
       <c r="AM696" s="1"/>
-      <c r="AN696" s="85"/>
+      <c r="AN696" s="89"/>
     </row>
     <row r="697" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A697" s="22" t="s">
@@ -74964,7 +75194,7 @@
       </c>
       <c r="AL697" s="1"/>
       <c r="AM697" s="1"/>
-      <c r="AN697" s="85"/>
+      <c r="AN697" s="89"/>
     </row>
     <row r="698" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A698" s="22" t="s">
@@ -75037,7 +75267,7 @@
       </c>
       <c r="AL698" s="1"/>
       <c r="AM698" s="1"/>
-      <c r="AN698" s="85"/>
+      <c r="AN698" s="89"/>
     </row>
     <row r="699" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A699" s="22" t="s">
@@ -75110,7 +75340,7 @@
       </c>
       <c r="AL699" s="1"/>
       <c r="AM699" s="1"/>
-      <c r="AN699" s="85"/>
+      <c r="AN699" s="89"/>
     </row>
     <row r="700" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A700" s="22" t="s">
@@ -75183,7 +75413,7 @@
       </c>
       <c r="AL700" s="1"/>
       <c r="AM700" s="1"/>
-      <c r="AN700" s="85"/>
+      <c r="AN700" s="89"/>
     </row>
     <row r="701" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A701" s="22" t="s">
@@ -75256,7 +75486,7 @@
       </c>
       <c r="AL701" s="1"/>
       <c r="AM701" s="1"/>
-      <c r="AN701" s="85"/>
+      <c r="AN701" s="89"/>
     </row>
     <row r="702" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A702" s="22" t="s">
@@ -75329,7 +75559,7 @@
       </c>
       <c r="AL702" s="1"/>
       <c r="AM702" s="1"/>
-      <c r="AN702" s="85"/>
+      <c r="AN702" s="89"/>
     </row>
     <row r="703" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A703" s="22" t="s">
@@ -75402,7 +75632,7 @@
       </c>
       <c r="AL703" s="1"/>
       <c r="AM703" s="1"/>
-      <c r="AN703" s="85"/>
+      <c r="AN703" s="89"/>
     </row>
     <row r="704" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A704" s="22" t="s">
@@ -75475,7 +75705,7 @@
       </c>
       <c r="AL704" s="1"/>
       <c r="AM704" s="1"/>
-      <c r="AN704" s="85"/>
+      <c r="AN704" s="89"/>
     </row>
     <row r="705" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A705" s="22" t="s">
@@ -75548,7 +75778,7 @@
       </c>
       <c r="AL705" s="1"/>
       <c r="AM705" s="1"/>
-      <c r="AN705" s="85"/>
+      <c r="AN705" s="89"/>
     </row>
     <row r="706" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A706" s="22" t="s">
@@ -75621,7 +75851,7 @@
       </c>
       <c r="AL706" s="1"/>
       <c r="AM706" s="1"/>
-      <c r="AN706" s="85"/>
+      <c r="AN706" s="89"/>
     </row>
     <row r="707" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A707" s="22" t="s">
@@ -75694,7 +75924,7 @@
       </c>
       <c r="AL707" s="1"/>
       <c r="AM707" s="1"/>
-      <c r="AN707" s="85"/>
+      <c r="AN707" s="89"/>
     </row>
     <row r="708" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A708" s="39"/>
@@ -75756,7 +75986,7 @@
       <c r="AK708" s="63"/>
       <c r="AL708" s="46"/>
       <c r="AM708" s="46"/>
-      <c r="AN708" s="85"/>
+      <c r="AN708" s="89"/>
     </row>
     <row r="713" spans="1:40" x14ac:dyDescent="0.3">
       <c r="AA713" s="73"/>
@@ -75783,11 +76013,7 @@
       <c r="AB717" s="73"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AL707" xr:uid="{2AA437EE-405D-4A43-9EB9-23F1BEB36011}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AL707">
-      <sortCondition ref="R2:R707"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A2:AL707" xr:uid="{2AA437EE-405D-4A43-9EB9-23F1BEB36011}"/>
   <conditionalFormatting sqref="A193:A213 A4:A95 A97:A118">
     <cfRule type="duplicateValues" dxfId="4" priority="12"/>
   </conditionalFormatting>
@@ -75821,9 +76047,12 @@
       <formula>NOT(ISERROR(SEARCH("X",AH4)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z4:AF708" xr:uid="{9319459A-71C7-4E4C-B697-82B431D05145}">
       <formula1>"X"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN3:AN708" xr:uid="{BF910421-2488-43D8-8890-88191156FCAE}">
+      <formula1>"jan/2026,fev/2026,mar/2026,abr/2026,mai/2026,jun/2026,jul/2026,ago/2026,set/2026,out/2026,nov/2026,dez/2026,jan/2027,fev/2027,mar/2027,abr/2026,mai/2027,jun/2027,jul/2027,ago/2027,set/2027,out/2027,nov/2027,dez/2027"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -75960,7 +76189,7 @@
       </c>
       <c r="F4" s="66">
         <f>SUMIF(Controle!$R:$R,Formulas!A4,Controle!$AK:$AK)</f>
-        <v>100757.38500000001</v>
+        <v>125302.11083333334</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -76010,7 +76239,7 @@
       </c>
       <c r="F6" s="67">
         <f t="shared" si="1"/>
-        <v>392916.05583333329</v>
+        <v>417460.78166666662</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -76069,7 +76298,7 @@
       </c>
       <c r="E11" s="66">
         <f>SUMIF(Controle!$L:$L,A11,Controle!$AK:$AK)</f>
-        <v>78719.767500000016</v>
+        <v>96135.268333333297</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -76174,7 +76403,7 @@
       </c>
       <c r="E16" s="66">
         <f>SUMIF(Controle!$L:$L,A16,Controle!$AK:$AK)</f>
-        <v>4999.3808333333327</v>
+        <v>8786.4108333333334</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -76195,7 +76424,7 @@
       </c>
       <c r="E17" s="66">
         <f>SUMIF(Controle!$L:$L,A17,Controle!$AK:$AK)</f>
-        <v>17038.236666666668</v>
+        <v>17038.2366666667</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -76216,7 +76445,7 @@
       </c>
       <c r="E18" s="66">
         <f>SUMIF(Controle!$L:$L,A18,Controle!$AK:$AK)</f>
-        <v>0</v>
+        <v>3342.1949999999997</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -76718,7 +76947,7 @@
       </c>
       <c r="E42" s="68">
         <f>SUM(E10:E41)</f>
-        <v>392916.05583333346</v>
+        <v>417460.78166666673</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -76969,16 +77198,16 @@
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE495743-F761-4961-A762-7A3D120C6961}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="c06ce65c-ed18-47f4-a957-afd315448c9c"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="f5ab1930-d403-4c69-b2cd-8cc48f527d10"/>
-    <ds:schemaRef ds:uri="c06ce65c-ed18-47f4-a957-afd315448c9c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/dados_atuais.xlsx
+++ b/data/dados_atuais.xlsx
@@ -5,20 +5,21 @@
   <workbookPr codeName="EsteLivro"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabriel.souza.DELGADIADEMA\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delgadiadema.sharepoint.com/sites/GestoEstratgica/Documentos Compartilhados/Controle Master/BSW/Novo controle (Em processo)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5759F119-FAB5-4931-8352-76DE5B42E428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2078" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C9D8836-533B-48DD-A7BC-4E47E2A31386}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3E398004-7492-4AA0-94C2-EA9B761AAA49}"/>
+    <workbookView minimized="1" xWindow="3696" yWindow="3696" windowWidth="17280" windowHeight="8880" xr2:uid="{3E398004-7492-4AA0-94C2-EA9B761AAA49}"/>
   </bookViews>
   <sheets>
     <sheet name="Controle" sheetId="1" r:id="rId1"/>
     <sheet name="Formulas" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Controle!$A$2:$AN$710</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Controle!$A$2:$AN$711</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Formulas!$A$9:$D$41</definedName>
+    <definedName name="_FiltrarBaseDados" localSheetId="0" hidden="1">Controle!$A$2:$AL$710</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -212,16 +213,16 @@
     </comment>
     <comment ref="A555" authorId="3" shapeId="0" xr:uid="{33C328EB-7B56-47E9-A787-F392CA006902}">
       <text>
-        <t>[Comentário por tópicos]
-A sua versão do Excel permite-lhe ler este comentário por tópicos. No entanto, as edições feitas ao comentário serão removidas se o ficheiro for aberto numa versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
+        <t>[Comentário encadeado]
+Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
 Comentário:
     Utilizando material 1,60x417</t>
       </text>
     </comment>
     <comment ref="A564" authorId="4" shapeId="0" xr:uid="{C01DA7E7-015C-4D77-8E50-06C386F35AF3}">
       <text>
-        <t>[Comentário por tópicos]
-A sua versão do Excel permite-lhe ler este comentário por tópicos. No entanto, as edições feitas ao comentário serão removidas se o ficheiro for aberto numa versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
+        <t>[Comentário encadeado]
+Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
 Comentário:
     Temos na Fitametal 
 BOZ0070TJ1350 - 10249kg</t>
@@ -253,16 +254,16 @@
     </comment>
     <comment ref="A574" authorId="6" shapeId="0" xr:uid="{67F1D739-35C9-474A-BA1D-BDA6C83EF4A4}">
       <text>
-        <t>[Comentário por tópicos]
-A sua versão do Excel permite-lhe ler este comentário por tópicos. No entanto, as edições feitas ao comentário serão removidas se o ficheiro for aberto numa versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
+        <t>[Comentário encadeado]
+Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
 Comentário:
     CORTAR SLEETER DE MATERIAL SEMELHANTE DEVIDO AO BAIXO VOLUME TEMOS O MESMO MATERIAL COM OUTRAS LARGURAS</t>
       </text>
     </comment>
     <comment ref="A575" authorId="7" shapeId="0" xr:uid="{9641E501-4748-445C-B1A5-D0E296582A82}">
       <text>
-        <t>[Comentário por tópicos]
-A sua versão do Excel permite-lhe ler este comentário por tópicos. No entanto, as edições feitas ao comentário serão removidas se o ficheiro for aberto numa versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
+        <t>[Comentário encadeado]
+Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
 Comentário:
     Usar material BOZ0060HU1000 como material alternativo</t>
       </text>
@@ -5532,7 +5533,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 10 2" xfId="3" xr:uid="{1B383F52-B05A-44D9-B6C7-8BD991E51E85}"/>
     <cellStyle name="Normal 4" xfId="2" xr:uid="{F191687B-6134-4FCE-8079-A034ADDB0F30}"/>
-    <cellStyle name="Percentagem" xfId="4" builtinId="5"/>
+    <cellStyle name="Porcentagem" xfId="4" builtinId="5"/>
     <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="5">
@@ -5603,7 +5604,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-PT"/>
+  <c:lang val="pt-BR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5968,7 +5969,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-PT"/>
+  <c:lang val="pt-BR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6274,7 +6275,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-PT"/>
+  <c:lang val="pt-BR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6580,7 +6581,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-PT"/>
+  <c:lang val="pt-BR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6886,7 +6887,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-PT"/>
+  <c:lang val="pt-BR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7192,7 +7193,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-PT"/>
+  <c:lang val="pt-BR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7547,7 +7548,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-PT"/>
+  <c:lang val="pt-BR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7840,7 +7841,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="pt-PT"/>
+  <c:lang val="pt-BR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -13574,7 +13575,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>40</v>
       </c>
@@ -13689,7 +13690,7 @@
       </c>
       <c r="AN3" s="83"/>
     </row>
-    <row r="4" spans="1:40" s="26" customFormat="1" ht="132.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:40" s="26" customFormat="1" ht="132.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
         <v>53</v>
       </c>
@@ -13806,7 +13807,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="5" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
         <v>63</v>
       </c>
@@ -13923,7 +13924,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="6" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
         <v>70</v>
       </c>
@@ -14032,7 +14033,7 @@
       </c>
       <c r="AN6" s="83"/>
     </row>
-    <row r="7" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="22" t="s">
         <v>78</v>
       </c>
@@ -14147,7 +14148,7 @@
       </c>
       <c r="AN7" s="83"/>
     </row>
-    <row r="8" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
         <v>85</v>
       </c>
@@ -14244,7 +14245,7 @@
       <c r="AM8" s="1"/>
       <c r="AN8" s="83"/>
     </row>
-    <row r="9" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
         <v>90</v>
       </c>
@@ -14361,7 +14362,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="10" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>97</v>
       </c>
@@ -14478,7 +14479,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="11" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="22" t="s">
         <v>103</v>
       </c>
@@ -14591,7 +14592,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="12" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
         <v>108</v>
       </c>
@@ -14688,7 +14689,7 @@
       <c r="AM12" s="1"/>
       <c r="AN12" s="83"/>
     </row>
-    <row r="13" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="22" t="s">
         <v>111</v>
       </c>
@@ -14787,7 +14788,7 @@
       <c r="AM13" s="1"/>
       <c r="AN13" s="83"/>
     </row>
-    <row r="14" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
         <v>115</v>
       </c>
@@ -14892,7 +14893,7 @@
       <c r="AM14" s="1"/>
       <c r="AN14" s="83"/>
     </row>
-    <row r="15" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="22" t="s">
         <v>118</v>
       </c>
@@ -14985,7 +14986,7 @@
       <c r="AM15" s="1"/>
       <c r="AN15" s="83"/>
     </row>
-    <row r="16" spans="1:40" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:40" s="26" customFormat="1" ht="30.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
         <v>122</v>
       </c>
@@ -15102,7 +15103,7 @@
         <v>46235</v>
       </c>
     </row>
-    <row r="17" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="22" t="s">
         <v>127</v>
       </c>
@@ -15199,7 +15200,7 @@
       <c r="AM17" s="1"/>
       <c r="AN17" s="83"/>
     </row>
-    <row r="18" spans="1:40" s="26" customFormat="1" ht="51" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:40" s="26" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
         <v>132</v>
       </c>
@@ -15296,7 +15297,7 @@
       <c r="AM18" s="1"/>
       <c r="AN18" s="83"/>
     </row>
-    <row r="19" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="22" t="s">
         <v>137</v>
       </c>
@@ -15395,7 +15396,7 @@
       </c>
       <c r="AN19" s="83"/>
     </row>
-    <row r="20" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
         <v>142</v>
       </c>
@@ -15492,7 +15493,7 @@
       <c r="AM20" s="1"/>
       <c r="AN20" s="83"/>
     </row>
-    <row r="21" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="22" t="s">
         <v>147</v>
       </c>
@@ -15607,7 +15608,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="22" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
         <v>154</v>
       </c>
@@ -15700,7 +15701,7 @@
       <c r="AM22" s="1"/>
       <c r="AN22" s="83"/>
     </row>
-    <row r="23" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="22" t="s">
         <v>156</v>
       </c>
@@ -15815,7 +15816,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="24" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
         <v>160</v>
       </c>
@@ -15908,7 +15909,7 @@
       <c r="AM24" s="1"/>
       <c r="AN24" s="83"/>
     </row>
-    <row r="25" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="22" t="s">
         <v>161</v>
       </c>
@@ -16001,7 +16002,7 @@
       <c r="AM25" s="1"/>
       <c r="AN25" s="83"/>
     </row>
-    <row r="26" spans="1:40" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:40" s="26" customFormat="1" ht="30.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
         <v>163</v>
       </c>
@@ -16096,7 +16097,7 @@
       <c r="AM26" s="1"/>
       <c r="AN26" s="83"/>
     </row>
-    <row r="27" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="22" t="s">
         <v>166</v>
       </c>
@@ -16189,7 +16190,7 @@
       <c r="AM27" s="1"/>
       <c r="AN27" s="83"/>
     </row>
-    <row r="28" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="22" t="s">
         <v>169</v>
       </c>
@@ -16284,7 +16285,7 @@
       <c r="AM28" s="62"/>
       <c r="AN28" s="83"/>
     </row>
-    <row r="29" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="22" t="s">
         <v>172</v>
       </c>
@@ -16379,7 +16380,7 @@
       <c r="AM29" s="1"/>
       <c r="AN29" s="83"/>
     </row>
-    <row r="30" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
         <v>175</v>
       </c>
@@ -16472,7 +16473,7 @@
       <c r="AM30" s="1"/>
       <c r="AN30" s="83"/>
     </row>
-    <row r="31" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="22" t="s">
         <v>179</v>
       </c>
@@ -16559,7 +16560,7 @@
       <c r="AM31" s="1"/>
       <c r="AN31" s="83"/>
     </row>
-    <row r="32" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
         <v>181</v>
       </c>
@@ -16676,7 +16677,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="33" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="22" t="s">
         <v>184</v>
       </c>
@@ -16791,7 +16792,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="34" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
         <v>190</v>
       </c>
@@ -16884,7 +16885,7 @@
       <c r="AM34" s="1"/>
       <c r="AN34" s="83"/>
     </row>
-    <row r="35" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="22" t="s">
         <v>194</v>
       </c>
@@ -17001,7 +17002,7 @@
         <v>46235</v>
       </c>
     </row>
-    <row r="36" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="22" t="s">
         <v>200</v>
       </c>
@@ -17096,7 +17097,7 @@
       <c r="AM36" s="1"/>
       <c r="AN36" s="83"/>
     </row>
-    <row r="37" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="22" t="s">
         <v>201</v>
       </c>
@@ -17183,7 +17184,7 @@
       <c r="AM37" s="1"/>
       <c r="AN37" s="83"/>
     </row>
-    <row r="38" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="22" t="s">
         <v>204</v>
       </c>
@@ -17284,7 +17285,7 @@
       <c r="AM38" s="1"/>
       <c r="AN38" s="83"/>
     </row>
-    <row r="39" spans="1:40" s="26" customFormat="1" ht="71.400000000000006" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:40" s="26" customFormat="1" ht="71.400000000000006" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="22" t="s">
         <v>207</v>
       </c>
@@ -17403,7 +17404,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="40" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
         <v>211</v>
       </c>
@@ -17496,7 +17497,7 @@
       <c r="AM40" s="1"/>
       <c r="AN40" s="83"/>
     </row>
-    <row r="41" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="22" t="s">
         <v>214</v>
       </c>
@@ -17589,7 +17590,7 @@
       <c r="AM41" s="1"/>
       <c r="AN41" s="83"/>
     </row>
-    <row r="42" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>217</v>
       </c>
@@ -17682,7 +17683,7 @@
       <c r="AM42" s="1"/>
       <c r="AN42" s="83"/>
     </row>
-    <row r="43" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="22" t="s">
         <v>221</v>
       </c>
@@ -17775,7 +17776,7 @@
       <c r="AM43" s="1"/>
       <c r="AN43" s="83"/>
     </row>
-    <row r="44" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="22" t="s">
         <v>225</v>
       </c>
@@ -17892,7 +17893,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="45" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="22" t="s">
         <v>230</v>
       </c>
@@ -18005,7 +18006,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="46" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="22" t="s">
         <v>234</v>
       </c>
@@ -18098,7 +18099,7 @@
       <c r="AM46" s="1"/>
       <c r="AN46" s="83"/>
     </row>
-    <row r="47" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="22" t="s">
         <v>241</v>
       </c>
@@ -18191,7 +18192,7 @@
       <c r="AM47" s="1"/>
       <c r="AN47" s="83"/>
     </row>
-    <row r="48" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="22" t="s">
         <v>244</v>
       </c>
@@ -18284,7 +18285,7 @@
       <c r="AM48" s="1"/>
       <c r="AN48" s="83"/>
     </row>
-    <row r="49" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="22" t="s">
         <v>246</v>
       </c>
@@ -18377,7 +18378,7 @@
       <c r="AM49" s="1"/>
       <c r="AN49" s="83"/>
     </row>
-    <row r="50" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="22" t="s">
         <v>248</v>
       </c>
@@ -18470,7 +18471,7 @@
       <c r="AM50" s="1"/>
       <c r="AN50" s="83"/>
     </row>
-    <row r="51" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="22" t="s">
         <v>251</v>
       </c>
@@ -18563,7 +18564,7 @@
       <c r="AM51" s="1"/>
       <c r="AN51" s="83"/>
     </row>
-    <row r="52" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="22" t="s">
         <v>254</v>
       </c>
@@ -18656,7 +18657,7 @@
       <c r="AM52" s="1"/>
       <c r="AN52" s="83"/>
     </row>
-    <row r="53" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="22" t="s">
         <v>257</v>
       </c>
@@ -18749,7 +18750,7 @@
       <c r="AM53" s="1"/>
       <c r="AN53" s="83"/>
     </row>
-    <row r="54" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="22" t="s">
         <v>259</v>
       </c>
@@ -18842,7 +18843,7 @@
       <c r="AM54" s="1"/>
       <c r="AN54" s="83"/>
     </row>
-    <row r="55" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="22" t="s">
         <v>263</v>
       </c>
@@ -18935,7 +18936,7 @@
       <c r="AM55" s="1"/>
       <c r="AN55" s="83"/>
     </row>
-    <row r="56" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="22" t="s">
         <v>266</v>
       </c>
@@ -19052,7 +19053,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="57" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="22" t="s">
         <v>270</v>
       </c>
@@ -19145,7 +19146,7 @@
       <c r="AM57" s="1"/>
       <c r="AN57" s="83"/>
     </row>
-    <row r="58" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="22" t="s">
         <v>271</v>
       </c>
@@ -19238,7 +19239,7 @@
       <c r="AM58" s="1"/>
       <c r="AN58" s="83"/>
     </row>
-    <row r="59" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="22" t="s">
         <v>273</v>
       </c>
@@ -19331,7 +19332,7 @@
       <c r="AM59" s="1"/>
       <c r="AN59" s="83"/>
     </row>
-    <row r="60" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="22" t="s">
         <v>275</v>
       </c>
@@ -19442,7 +19443,7 @@
       </c>
       <c r="AN60" s="83"/>
     </row>
-    <row r="61" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="22" t="s">
         <v>281</v>
       </c>
@@ -19555,7 +19556,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="62" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="22" t="s">
         <v>287</v>
       </c>
@@ -19648,7 +19649,7 @@
       <c r="AM62" s="1"/>
       <c r="AN62" s="83"/>
     </row>
-    <row r="63" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="22" t="s">
         <v>289</v>
       </c>
@@ -19741,7 +19742,7 @@
       <c r="AM63" s="1"/>
       <c r="AN63" s="83"/>
     </row>
-    <row r="64" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="22" t="s">
         <v>292</v>
       </c>
@@ -19834,7 +19835,7 @@
       <c r="AM64" s="1"/>
       <c r="AN64" s="83"/>
     </row>
-    <row r="65" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="22" t="s">
         <v>294</v>
       </c>
@@ -19929,7 +19930,7 @@
       <c r="AM65" s="1"/>
       <c r="AN65" s="83"/>
     </row>
-    <row r="66" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="22" t="s">
         <v>296</v>
       </c>
@@ -20024,7 +20025,7 @@
       <c r="AM66" s="1"/>
       <c r="AN66" s="83"/>
     </row>
-    <row r="67" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="22" t="s">
         <v>298</v>
       </c>
@@ -20113,7 +20114,7 @@
       <c r="AM67" s="1"/>
       <c r="AN67" s="83"/>
     </row>
-    <row r="68" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="22" t="s">
         <v>299</v>
       </c>
@@ -20206,7 +20207,7 @@
       <c r="AM68" s="1"/>
       <c r="AN68" s="83"/>
     </row>
-    <row r="69" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="22" t="s">
         <v>301</v>
       </c>
@@ -20301,7 +20302,7 @@
       <c r="AM69" s="1"/>
       <c r="AN69" s="83"/>
     </row>
-    <row r="70" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="22" t="s">
         <v>304</v>
       </c>
@@ -20394,7 +20395,7 @@
       <c r="AM70" s="1"/>
       <c r="AN70" s="83"/>
     </row>
-    <row r="71" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="22" t="s">
         <v>306</v>
       </c>
@@ -20487,7 +20488,7 @@
       <c r="AM71" s="1"/>
       <c r="AN71" s="83"/>
     </row>
-    <row r="72" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="22" t="s">
         <v>309</v>
       </c>
@@ -20582,7 +20583,7 @@
       <c r="AM72" s="1"/>
       <c r="AN72" s="83"/>
     </row>
-    <row r="73" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="22" t="s">
         <v>312</v>
       </c>
@@ -20675,7 +20676,7 @@
       <c r="AM73" s="1"/>
       <c r="AN73" s="83"/>
     </row>
-    <row r="74" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="22" t="s">
         <v>314</v>
       </c>
@@ -20768,7 +20769,7 @@
       <c r="AM74" s="1"/>
       <c r="AN74" s="83"/>
     </row>
-    <row r="75" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="22" t="s">
         <v>316</v>
       </c>
@@ -20859,7 +20860,7 @@
       <c r="AM75" s="1"/>
       <c r="AN75" s="83"/>
     </row>
-    <row r="76" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="22" t="s">
         <v>319</v>
       </c>
@@ -20952,7 +20953,7 @@
       <c r="AM76" s="1"/>
       <c r="AN76" s="83"/>
     </row>
-    <row r="77" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="22" t="s">
         <v>323</v>
       </c>
@@ -21043,7 +21044,7 @@
       <c r="AM77" s="1"/>
       <c r="AN77" s="83"/>
     </row>
-    <row r="78" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="22" t="s">
         <v>325</v>
       </c>
@@ -21156,7 +21157,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="79" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="22" t="s">
         <v>329</v>
       </c>
@@ -21249,7 +21250,7 @@
       <c r="AM79" s="1"/>
       <c r="AN79" s="83"/>
     </row>
-    <row r="80" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="22" t="s">
         <v>332</v>
       </c>
@@ -21362,7 +21363,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="81" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="22" t="s">
         <v>336</v>
       </c>
@@ -21457,7 +21458,7 @@
       <c r="AM81" s="1"/>
       <c r="AN81" s="83"/>
     </row>
-    <row r="82" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="22" t="s">
         <v>338</v>
       </c>
@@ -21550,7 +21551,7 @@
       <c r="AM82" s="1"/>
       <c r="AN82" s="83"/>
     </row>
-    <row r="83" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="22" t="s">
         <v>340</v>
       </c>
@@ -21643,7 +21644,7 @@
       <c r="AM83" s="1"/>
       <c r="AN83" s="83"/>
     </row>
-    <row r="84" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="22" t="s">
         <v>342</v>
       </c>
@@ -21738,7 +21739,7 @@
       <c r="AM84" s="1"/>
       <c r="AN84" s="83"/>
     </row>
-    <row r="85" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="22" t="s">
         <v>345</v>
       </c>
@@ -21831,7 +21832,7 @@
       <c r="AM85" s="1"/>
       <c r="AN85" s="83"/>
     </row>
-    <row r="86" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="22" t="s">
         <v>347</v>
       </c>
@@ -21920,7 +21921,7 @@
       <c r="AM86" s="1"/>
       <c r="AN86" s="83"/>
     </row>
-    <row r="87" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="22" t="s">
         <v>352</v>
       </c>
@@ -22013,7 +22014,7 @@
       <c r="AM87" s="1"/>
       <c r="AN87" s="83"/>
     </row>
-    <row r="88" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="22" t="s">
         <v>354</v>
       </c>
@@ -22108,7 +22109,7 @@
       <c r="AM88" s="1"/>
       <c r="AN88" s="83"/>
     </row>
-    <row r="89" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="22" t="s">
         <v>359</v>
       </c>
@@ -22201,7 +22202,7 @@
       <c r="AM89" s="1"/>
       <c r="AN89" s="83"/>
     </row>
-    <row r="90" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="22" t="s">
         <v>362</v>
       </c>
@@ -22294,7 +22295,7 @@
       <c r="AM90" s="1"/>
       <c r="AN90" s="83"/>
     </row>
-    <row r="91" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="22" t="s">
         <v>364</v>
       </c>
@@ -22387,7 +22388,7 @@
       <c r="AM91" s="1"/>
       <c r="AN91" s="83"/>
     </row>
-    <row r="92" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="22" t="s">
         <v>367</v>
       </c>
@@ -22480,7 +22481,7 @@
       <c r="AM92" s="1"/>
       <c r="AN92" s="83"/>
     </row>
-    <row r="93" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="22" t="s">
         <v>370</v>
       </c>
@@ -22571,7 +22572,7 @@
       <c r="AM93" s="1"/>
       <c r="AN93" s="83"/>
     </row>
-    <row r="94" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="22" t="s">
         <v>372</v>
       </c>
@@ -22664,7 +22665,7 @@
       <c r="AM94" s="1"/>
       <c r="AN94" s="83"/>
     </row>
-    <row r="95" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="15" t="s">
         <v>375</v>
       </c>
@@ -22757,7 +22758,7 @@
       <c r="AM95" s="1"/>
       <c r="AN95" s="83"/>
     </row>
-    <row r="96" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="22" t="s">
         <v>378</v>
       </c>
@@ -22870,7 +22871,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="97" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="22" t="s">
         <v>381</v>
       </c>
@@ -22957,7 +22958,7 @@
       <c r="AM97" s="1"/>
       <c r="AN97" s="83"/>
     </row>
-    <row r="98" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>382</v>
       </c>
@@ -23052,7 +23053,7 @@
       <c r="AM98" s="1"/>
       <c r="AN98" s="83"/>
     </row>
-    <row r="99" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="22" t="s">
         <v>386</v>
       </c>
@@ -23147,7 +23148,7 @@
       <c r="AM99" s="1"/>
       <c r="AN99" s="83"/>
     </row>
-    <row r="100" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="22" t="s">
         <v>388</v>
       </c>
@@ -23240,7 +23241,7 @@
       <c r="AM100" s="1"/>
       <c r="AN100" s="83"/>
     </row>
-    <row r="101" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="22" t="s">
         <v>391</v>
       </c>
@@ -23333,7 +23334,7 @@
       <c r="AM101" s="1"/>
       <c r="AN101" s="83"/>
     </row>
-    <row r="102" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="22" t="s">
         <v>394</v>
       </c>
@@ -23422,7 +23423,7 @@
       <c r="AM102" s="1"/>
       <c r="AN102" s="83"/>
     </row>
-    <row r="103" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="22" t="s">
         <v>397</v>
       </c>
@@ -23515,7 +23516,7 @@
       <c r="AM103" s="1"/>
       <c r="AN103" s="83"/>
     </row>
-    <row r="104" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="22" t="s">
         <v>398</v>
       </c>
@@ -23610,7 +23611,7 @@
       <c r="AM104" s="1"/>
       <c r="AN104" s="83"/>
     </row>
-    <row r="105" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="22" t="s">
         <v>400</v>
       </c>
@@ -23697,7 +23698,7 @@
       <c r="AM105" s="1"/>
       <c r="AN105" s="83"/>
     </row>
-    <row r="106" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="22" t="s">
         <v>402</v>
       </c>
@@ -23790,7 +23791,7 @@
       <c r="AM106" s="1"/>
       <c r="AN106" s="83"/>
     </row>
-    <row r="107" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="15" t="s">
         <v>404</v>
       </c>
@@ -23877,7 +23878,7 @@
       <c r="AM107" s="1"/>
       <c r="AN107" s="83"/>
     </row>
-    <row r="108" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="22" t="s">
         <v>406</v>
       </c>
@@ -23968,7 +23969,7 @@
       <c r="AM108" s="1"/>
       <c r="AN108" s="83"/>
     </row>
-    <row r="109" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="22" t="s">
         <v>408</v>
       </c>
@@ -24061,7 +24062,7 @@
       <c r="AM109" s="1"/>
       <c r="AN109" s="83"/>
     </row>
-    <row r="110" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="22" t="s">
         <v>410</v>
       </c>
@@ -24176,7 +24177,7 @@
       </c>
       <c r="AN110" s="83"/>
     </row>
-    <row r="111" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="22" t="s">
         <v>414</v>
       </c>
@@ -24271,7 +24272,7 @@
       <c r="AM111" s="1"/>
       <c r="AN111" s="83"/>
     </row>
-    <row r="112" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="22" t="s">
         <v>416</v>
       </c>
@@ -24386,7 +24387,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="113" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="22" t="s">
         <v>419</v>
       </c>
@@ -24475,7 +24476,7 @@
       <c r="AM113" s="1"/>
       <c r="AN113" s="83"/>
     </row>
-    <row r="114" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="22" t="s">
         <v>423</v>
       </c>
@@ -24562,7 +24563,7 @@
       <c r="AM114" s="1"/>
       <c r="AN114" s="83"/>
     </row>
-    <row r="115" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>424</v>
       </c>
@@ -24655,7 +24656,7 @@
       <c r="AM115" s="1"/>
       <c r="AN115" s="83"/>
     </row>
-    <row r="116" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="22" t="s">
         <v>426</v>
       </c>
@@ -24740,7 +24741,7 @@
       <c r="AM116" s="1"/>
       <c r="AN116" s="83"/>
     </row>
-    <row r="117" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="22" t="s">
         <v>428</v>
       </c>
@@ -24835,7 +24836,7 @@
       <c r="AM117" s="1"/>
       <c r="AN117" s="83"/>
     </row>
-    <row r="118" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="22" t="s">
         <v>430</v>
       </c>
@@ -24928,7 +24929,7 @@
       <c r="AM118" s="1"/>
       <c r="AN118" s="83"/>
     </row>
-    <row r="119" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="22" t="s">
         <v>432</v>
       </c>
@@ -25019,7 +25020,7 @@
       <c r="AM119" s="1"/>
       <c r="AN119" s="83"/>
     </row>
-    <row r="120" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="15" t="s">
         <v>434</v>
       </c>
@@ -25104,7 +25105,7 @@
       <c r="AM120" s="1"/>
       <c r="AN120" s="83"/>
     </row>
-    <row r="121" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="22" t="s">
         <v>435</v>
       </c>
@@ -25195,7 +25196,7 @@
       <c r="AM121" s="1"/>
       <c r="AN121" s="83"/>
     </row>
-    <row r="122" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="15" t="s">
         <v>437</v>
       </c>
@@ -25282,7 +25283,7 @@
       <c r="AM122" s="1"/>
       <c r="AN122" s="83"/>
     </row>
-    <row r="123" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="22" t="s">
         <v>438</v>
       </c>
@@ -25393,7 +25394,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="124" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="22" t="s">
         <v>440</v>
       </c>
@@ -25478,7 +25479,7 @@
       <c r="AM124" s="1"/>
       <c r="AN124" s="83"/>
     </row>
-    <row r="125" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="22" t="s">
         <v>441</v>
       </c>
@@ -25573,7 +25574,7 @@
       <c r="AM125" s="1"/>
       <c r="AN125" s="83"/>
     </row>
-    <row r="126" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="22" t="s">
         <v>443</v>
       </c>
@@ -25662,7 +25663,7 @@
       <c r="AM126" s="1"/>
       <c r="AN126" s="83"/>
     </row>
-    <row r="127" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="22" t="s">
         <v>446</v>
       </c>
@@ -25755,7 +25756,7 @@
       <c r="AM127" s="1"/>
       <c r="AN127" s="83"/>
     </row>
-    <row r="128" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="22" t="s">
         <v>448</v>
       </c>
@@ -25844,7 +25845,7 @@
       <c r="AM128" s="1"/>
       <c r="AN128" s="83"/>
     </row>
-    <row r="129" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="15" t="s">
         <v>451</v>
       </c>
@@ -25937,7 +25938,7 @@
       <c r="AM129" s="1"/>
       <c r="AN129" s="83"/>
     </row>
-    <row r="130" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="22" t="s">
         <v>453</v>
       </c>
@@ -26020,7 +26021,7 @@
       <c r="AM130" s="1"/>
       <c r="AN130" s="83"/>
     </row>
-    <row r="131" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="22" t="s">
         <v>454</v>
       </c>
@@ -26103,7 +26104,7 @@
       <c r="AM131" s="1"/>
       <c r="AN131" s="83"/>
     </row>
-    <row r="132" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="22" t="s">
         <v>455</v>
       </c>
@@ -26196,7 +26197,7 @@
       <c r="AM132" s="1"/>
       <c r="AN132" s="83"/>
     </row>
-    <row r="133" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="22" t="s">
         <v>457</v>
       </c>
@@ -26291,7 +26292,7 @@
       <c r="AM133" s="1"/>
       <c r="AN133" s="83"/>
     </row>
-    <row r="134" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="22" t="s">
         <v>459</v>
       </c>
@@ -26382,7 +26383,7 @@
       <c r="AM134" s="1"/>
       <c r="AN134" s="83"/>
     </row>
-    <row r="135" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="15" t="s">
         <v>461</v>
       </c>
@@ -26471,7 +26472,7 @@
       <c r="AM135" s="1"/>
       <c r="AN135" s="83"/>
     </row>
-    <row r="136" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="22" t="s">
         <v>463</v>
       </c>
@@ -26562,7 +26563,7 @@
       <c r="AM136" s="1"/>
       <c r="AN136" s="83"/>
     </row>
-    <row r="137" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="15" t="s">
         <v>465</v>
       </c>
@@ -26647,7 +26648,7 @@
       <c r="AM137" s="1"/>
       <c r="AN137" s="83"/>
     </row>
-    <row r="138" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="22" t="s">
         <v>467</v>
       </c>
@@ -26738,7 +26739,7 @@
       <c r="AM138" s="1"/>
       <c r="AN138" s="83"/>
     </row>
-    <row r="139" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="15" t="s">
         <v>468</v>
       </c>
@@ -26825,7 +26826,7 @@
       <c r="AM139" s="1"/>
       <c r="AN139" s="83"/>
     </row>
-    <row r="140" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="22" t="s">
         <v>471</v>
       </c>
@@ -26916,7 +26917,7 @@
       <c r="AM140" s="1"/>
       <c r="AN140" s="83"/>
     </row>
-    <row r="141" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="22" t="s">
         <v>474</v>
       </c>
@@ -27001,7 +27002,7 @@
       <c r="AM141" s="1"/>
       <c r="AN141" s="83"/>
     </row>
-    <row r="142" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="15" t="s">
         <v>475</v>
       </c>
@@ -27092,7 +27093,7 @@
       <c r="AM142" s="1"/>
       <c r="AN142" s="83"/>
     </row>
-    <row r="143" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="15" t="s">
         <v>477</v>
       </c>
@@ -27179,7 +27180,7 @@
       <c r="AM143" s="1"/>
       <c r="AN143" s="83"/>
     </row>
-    <row r="144" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="15" t="s">
         <v>480</v>
       </c>
@@ -27274,7 +27275,7 @@
       <c r="AM144" s="1"/>
       <c r="AN144" s="83"/>
     </row>
-    <row r="145" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="15" t="s">
         <v>482</v>
       </c>
@@ -27361,7 +27362,7 @@
       <c r="AM145" s="1"/>
       <c r="AN145" s="83"/>
     </row>
-    <row r="146" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="15" t="s">
         <v>483</v>
       </c>
@@ -27446,7 +27447,7 @@
       <c r="AM146" s="1"/>
       <c r="AN146" s="83"/>
     </row>
-    <row r="147" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="15" t="s">
         <v>484</v>
       </c>
@@ -27527,7 +27528,7 @@
       <c r="AM147" s="1"/>
       <c r="AN147" s="83"/>
     </row>
-    <row r="148" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="15" t="s">
         <v>485</v>
       </c>
@@ -27620,7 +27621,7 @@
       <c r="AM148" s="1"/>
       <c r="AN148" s="83"/>
     </row>
-    <row r="149" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="15" t="s">
         <v>487</v>
       </c>
@@ -27711,7 +27712,7 @@
       <c r="AM149" s="1"/>
       <c r="AN149" s="83"/>
     </row>
-    <row r="150" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="15" t="s">
         <v>489</v>
       </c>
@@ -27792,7 +27793,7 @@
       <c r="AM150" s="1"/>
       <c r="AN150" s="83"/>
     </row>
-    <row r="151" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="15" t="s">
         <v>490</v>
       </c>
@@ -27879,7 +27880,7 @@
       <c r="AM151" s="1"/>
       <c r="AN151" s="83"/>
     </row>
-    <row r="152" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="15" t="s">
         <v>492</v>
       </c>
@@ -27970,7 +27971,7 @@
       <c r="AM152" s="1"/>
       <c r="AN152" s="83"/>
     </row>
-    <row r="153" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="15" t="s">
         <v>495</v>
       </c>
@@ -28057,7 +28058,7 @@
       <c r="AM153" s="1"/>
       <c r="AN153" s="83"/>
     </row>
-    <row r="154" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="15" t="s">
         <v>497</v>
       </c>
@@ -28144,7 +28145,7 @@
       <c r="AM154" s="1"/>
       <c r="AN154" s="83"/>
     </row>
-    <row r="155" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="15" t="s">
         <v>499</v>
       </c>
@@ -28231,7 +28232,7 @@
       <c r="AM155" s="1"/>
       <c r="AN155" s="83"/>
     </row>
-    <row r="156" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="15" t="s">
         <v>501</v>
       </c>
@@ -28320,7 +28321,7 @@
       <c r="AM156" s="1"/>
       <c r="AN156" s="83"/>
     </row>
-    <row r="157" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="15" t="s">
         <v>504</v>
       </c>
@@ -28407,7 +28408,7 @@
       <c r="AM157" s="1"/>
       <c r="AN157" s="83"/>
     </row>
-    <row r="158" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="15" t="s">
         <v>506</v>
       </c>
@@ -28494,7 +28495,7 @@
       <c r="AM158" s="1"/>
       <c r="AN158" s="83"/>
     </row>
-    <row r="159" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="15" t="s">
         <v>508</v>
       </c>
@@ -28583,7 +28584,7 @@
       <c r="AM159" s="1"/>
       <c r="AN159" s="83"/>
     </row>
-    <row r="160" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="15" t="s">
         <v>510</v>
       </c>
@@ -28670,7 +28671,7 @@
       <c r="AM160" s="1"/>
       <c r="AN160" s="83"/>
     </row>
-    <row r="161" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="15" t="s">
         <v>512</v>
       </c>
@@ -28757,7 +28758,7 @@
       <c r="AM161" s="1"/>
       <c r="AN161" s="83"/>
     </row>
-    <row r="162" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="15" t="s">
         <v>514</v>
       </c>
@@ -28848,7 +28849,7 @@
       <c r="AM162" s="1"/>
       <c r="AN162" s="83"/>
     </row>
-    <row r="163" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="15" t="s">
         <v>517</v>
       </c>
@@ -28935,7 +28936,7 @@
       <c r="AM163" s="1"/>
       <c r="AN163" s="83"/>
     </row>
-    <row r="164" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="15" t="s">
         <v>519</v>
       </c>
@@ -29022,7 +29023,7 @@
       <c r="AM164" s="1"/>
       <c r="AN164" s="83"/>
     </row>
-    <row r="165" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="15" t="s">
         <v>521</v>
       </c>
@@ -29111,7 +29112,7 @@
       <c r="AM165" s="1"/>
       <c r="AN165" s="83"/>
     </row>
-    <row r="166" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="15" t="s">
         <v>523</v>
       </c>
@@ -29200,7 +29201,7 @@
       <c r="AM166" s="1"/>
       <c r="AN166" s="83"/>
     </row>
-    <row r="167" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="15" t="s">
         <v>525</v>
       </c>
@@ -29289,7 +29290,7 @@
       <c r="AM167" s="1"/>
       <c r="AN167" s="83"/>
     </row>
-    <row r="168" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="15" t="s">
         <v>527</v>
       </c>
@@ -29378,7 +29379,7 @@
       <c r="AM168" s="1"/>
       <c r="AN168" s="83"/>
     </row>
-    <row r="169" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="15" t="s">
         <v>529</v>
       </c>
@@ -29465,7 +29466,7 @@
       <c r="AM169" s="1"/>
       <c r="AN169" s="83"/>
     </row>
-    <row r="170" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="15" t="s">
         <v>531</v>
       </c>
@@ -29554,7 +29555,7 @@
       <c r="AM170" s="1"/>
       <c r="AN170" s="83"/>
     </row>
-    <row r="171" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="15" t="s">
         <v>533</v>
       </c>
@@ -29643,7 +29644,7 @@
       <c r="AM171" s="1"/>
       <c r="AN171" s="83"/>
     </row>
-    <row r="172" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="15" t="s">
         <v>535</v>
       </c>
@@ -29730,7 +29731,7 @@
       <c r="AM172" s="1"/>
       <c r="AN172" s="83"/>
     </row>
-    <row r="173" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="15" t="s">
         <v>537</v>
       </c>
@@ -29819,7 +29820,7 @@
       <c r="AM173" s="1"/>
       <c r="AN173" s="83"/>
     </row>
-    <row r="174" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="15" t="s">
         <v>539</v>
       </c>
@@ -29908,7 +29909,7 @@
       <c r="AM174" s="1"/>
       <c r="AN174" s="83"/>
     </row>
-    <row r="175" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="15" t="s">
         <v>541</v>
       </c>
@@ -29981,7 +29982,7 @@
       <c r="AM175" s="1"/>
       <c r="AN175" s="83"/>
     </row>
-    <row r="176" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="15" t="s">
         <v>542</v>
       </c>
@@ -30068,7 +30069,7 @@
       <c r="AM176" s="1"/>
       <c r="AN176" s="83"/>
     </row>
-    <row r="177" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="15" t="s">
         <v>545</v>
       </c>
@@ -30153,7 +30154,7 @@
       <c r="AM177" s="1"/>
       <c r="AN177" s="83"/>
     </row>
-    <row r="178" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="15" t="s">
         <v>547</v>
       </c>
@@ -30244,7 +30245,7 @@
       <c r="AM178" s="1"/>
       <c r="AN178" s="83"/>
     </row>
-    <row r="179" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="15" t="s">
         <v>548</v>
       </c>
@@ -30331,7 +30332,7 @@
       <c r="AM179" s="1"/>
       <c r="AN179" s="83"/>
     </row>
-    <row r="180" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="15" t="s">
         <v>552</v>
       </c>
@@ -30446,7 +30447,7 @@
         <v>46204</v>
       </c>
     </row>
-    <row r="181" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="15" t="s">
         <v>557</v>
       </c>
@@ -30561,7 +30562,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="182" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="15" t="s">
         <v>562</v>
       </c>
@@ -30652,7 +30653,7 @@
       <c r="AM182" s="1"/>
       <c r="AN182" s="83"/>
     </row>
-    <row r="183" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="15" t="s">
         <v>564</v>
       </c>
@@ -30741,7 +30742,7 @@
       <c r="AM183" s="1"/>
       <c r="AN183" s="83"/>
     </row>
-    <row r="184" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="15" t="s">
         <v>565</v>
       </c>
@@ -30830,7 +30831,7 @@
       <c r="AM184" s="1"/>
       <c r="AN184" s="83"/>
     </row>
-    <row r="185" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="15" t="s">
         <v>567</v>
       </c>
@@ -30917,7 +30918,7 @@
       <c r="AM185" s="1"/>
       <c r="AN185" s="83"/>
     </row>
-    <row r="186" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="15" t="s">
         <v>570</v>
       </c>
@@ -31004,7 +31005,7 @@
       <c r="AM186" s="1"/>
       <c r="AN186" s="83"/>
     </row>
-    <row r="187" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="15" t="s">
         <v>572</v>
       </c>
@@ -31091,7 +31092,7 @@
       <c r="AM187" s="1"/>
       <c r="AN187" s="83"/>
     </row>
-    <row r="188" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="15" t="s">
         <v>575</v>
       </c>
@@ -31178,7 +31179,7 @@
       <c r="AM188" s="1"/>
       <c r="AN188" s="83"/>
     </row>
-    <row r="189" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="15" t="s">
         <v>578</v>
       </c>
@@ -31265,7 +31266,7 @@
       <c r="AM189" s="1"/>
       <c r="AN189" s="83"/>
     </row>
-    <row r="190" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="15" t="s">
         <v>580</v>
       </c>
@@ -31352,7 +31353,7 @@
       <c r="AM190" s="1"/>
       <c r="AN190" s="83"/>
     </row>
-    <row r="191" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="15" t="s">
         <v>582</v>
       </c>
@@ -31433,7 +31434,7 @@
       <c r="AM191" s="1"/>
       <c r="AN191" s="83"/>
     </row>
-    <row r="192" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="15" t="s">
         <v>584</v>
       </c>
@@ -31520,7 +31521,7 @@
       <c r="AM192" s="1"/>
       <c r="AN192" s="83"/>
     </row>
-    <row r="193" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="15" t="s">
         <v>586</v>
       </c>
@@ -31609,7 +31610,7 @@
       <c r="AM193" s="1"/>
       <c r="AN193" s="83"/>
     </row>
-    <row r="194" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="15" t="s">
         <v>589</v>
       </c>
@@ -31696,7 +31697,7 @@
       <c r="AM194" s="1"/>
       <c r="AN194" s="83"/>
     </row>
-    <row r="195" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="15" t="s">
         <v>592</v>
       </c>
@@ -31783,7 +31784,7 @@
       <c r="AM195" s="1"/>
       <c r="AN195" s="83"/>
     </row>
-    <row r="196" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="15" t="s">
         <v>595</v>
       </c>
@@ -31872,7 +31873,7 @@
       <c r="AM196" s="1"/>
       <c r="AN196" s="83"/>
     </row>
-    <row r="197" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="15" t="s">
         <v>599</v>
       </c>
@@ -31961,7 +31962,7 @@
       <c r="AM197" s="1"/>
       <c r="AN197" s="83"/>
     </row>
-    <row r="198" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="15" t="s">
         <v>601</v>
       </c>
@@ -32050,7 +32051,7 @@
       <c r="AM198" s="1"/>
       <c r="AN198" s="83"/>
     </row>
-    <row r="199" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="15" t="s">
         <v>603</v>
       </c>
@@ -32137,7 +32138,7 @@
       <c r="AM199" s="1"/>
       <c r="AN199" s="83"/>
     </row>
-    <row r="200" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="15" t="s">
         <v>605</v>
       </c>
@@ -32224,7 +32225,7 @@
       <c r="AM200" s="1"/>
       <c r="AN200" s="83"/>
     </row>
-    <row r="201" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="15" t="s">
         <v>607</v>
       </c>
@@ -32311,7 +32312,7 @@
       <c r="AM201" s="1"/>
       <c r="AN201" s="83"/>
     </row>
-    <row r="202" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="15" t="s">
         <v>610</v>
       </c>
@@ -32402,7 +32403,7 @@
       <c r="AM202" s="1"/>
       <c r="AN202" s="83"/>
     </row>
-    <row r="203" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="15" t="s">
         <v>611</v>
       </c>
@@ -32489,7 +32490,7 @@
       <c r="AM203" s="1"/>
       <c r="AN203" s="83"/>
     </row>
-    <row r="204" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="15" t="s">
         <v>612</v>
       </c>
@@ -32576,7 +32577,7 @@
       <c r="AM204" s="1"/>
       <c r="AN204" s="83"/>
     </row>
-    <row r="205" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="15" t="s">
         <v>614</v>
       </c>
@@ -32665,7 +32666,7 @@
       <c r="AM205" s="1"/>
       <c r="AN205" s="83"/>
     </row>
-    <row r="206" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="15" t="s">
         <v>615</v>
       </c>
@@ -32758,7 +32759,7 @@
       <c r="AM206" s="1"/>
       <c r="AN206" s="83"/>
     </row>
-    <row r="207" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="15" t="s">
         <v>616</v>
       </c>
@@ -32845,7 +32846,7 @@
       <c r="AM207" s="1"/>
       <c r="AN207" s="83"/>
     </row>
-    <row r="208" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="15" t="s">
         <v>619</v>
       </c>
@@ -32934,7 +32935,7 @@
       <c r="AM208" s="1"/>
       <c r="AN208" s="83"/>
     </row>
-    <row r="209" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="15" t="s">
         <v>621</v>
       </c>
@@ -33021,7 +33022,7 @@
       <c r="AM209" s="1"/>
       <c r="AN209" s="83"/>
     </row>
-    <row r="210" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="15" t="s">
         <v>623</v>
       </c>
@@ -33108,7 +33109,7 @@
       <c r="AM210" s="1"/>
       <c r="AN210" s="83"/>
     </row>
-    <row r="211" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="15" t="s">
         <v>625</v>
       </c>
@@ -33195,7 +33196,7 @@
       <c r="AM211" s="1"/>
       <c r="AN211" s="83"/>
     </row>
-    <row r="212" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="15" t="s">
         <v>627</v>
       </c>
@@ -33284,7 +33285,7 @@
       <c r="AM212" s="1"/>
       <c r="AN212" s="83"/>
     </row>
-    <row r="213" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="15" t="s">
         <v>629</v>
       </c>
@@ -33371,7 +33372,7 @@
       <c r="AM213" s="1"/>
       <c r="AN213" s="83"/>
     </row>
-    <row r="214" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="15" t="s">
         <v>631</v>
       </c>
@@ -33458,7 +33459,7 @@
       <c r="AM214" s="1"/>
       <c r="AN214" s="83"/>
     </row>
-    <row r="215" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="15" t="s">
         <v>634</v>
       </c>
@@ -33547,7 +33548,7 @@
       <c r="AM215" s="1"/>
       <c r="AN215" s="83"/>
     </row>
-    <row r="216" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="15" t="s">
         <v>637</v>
       </c>
@@ -33632,7 +33633,7 @@
       <c r="AM216" s="1"/>
       <c r="AN216" s="83"/>
     </row>
-    <row r="217" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="15" t="s">
         <v>639</v>
       </c>
@@ -33719,7 +33720,7 @@
       <c r="AM217" s="1"/>
       <c r="AN217" s="83"/>
     </row>
-    <row r="218" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="15" t="s">
         <v>642</v>
       </c>
@@ -33804,7 +33805,7 @@
       <c r="AM218" s="1"/>
       <c r="AN218" s="83"/>
     </row>
-    <row r="219" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="15" t="s">
         <v>644</v>
       </c>
@@ -33889,7 +33890,7 @@
       <c r="AM219" s="1"/>
       <c r="AN219" s="83"/>
     </row>
-    <row r="220" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="15" t="s">
         <v>646</v>
       </c>
@@ -33970,7 +33971,7 @@
       <c r="AM220" s="1"/>
       <c r="AN220" s="83"/>
     </row>
-    <row r="221" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="15" t="s">
         <v>647</v>
       </c>
@@ -34055,7 +34056,7 @@
       <c r="AM221" s="1"/>
       <c r="AN221" s="83"/>
     </row>
-    <row r="222" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="15" t="s">
         <v>650</v>
       </c>
@@ -34140,7 +34141,7 @@
       <c r="AM222" s="1"/>
       <c r="AN222" s="83"/>
     </row>
-    <row r="223" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="15" t="s">
         <v>653</v>
       </c>
@@ -34225,7 +34226,7 @@
       <c r="AM223" s="1"/>
       <c r="AN223" s="83"/>
     </row>
-    <row r="224" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="15" t="s">
         <v>655</v>
       </c>
@@ -34314,7 +34315,7 @@
       <c r="AM224" s="1"/>
       <c r="AN224" s="83"/>
     </row>
-    <row r="225" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="15" t="s">
         <v>657</v>
       </c>
@@ -34397,7 +34398,7 @@
       <c r="AM225" s="1"/>
       <c r="AN225" s="83"/>
     </row>
-    <row r="226" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="15" t="s">
         <v>659</v>
       </c>
@@ -34484,7 +34485,7 @@
       <c r="AM226" s="1"/>
       <c r="AN226" s="83"/>
     </row>
-    <row r="227" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="15" t="s">
         <v>661</v>
       </c>
@@ -34571,7 +34572,7 @@
       <c r="AM227" s="1"/>
       <c r="AN227" s="83"/>
     </row>
-    <row r="228" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="15" t="s">
         <v>664</v>
       </c>
@@ -34656,7 +34657,7 @@
       <c r="AM228" s="1"/>
       <c r="AN228" s="83"/>
     </row>
-    <row r="229" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="15" t="s">
         <v>666</v>
       </c>
@@ -34739,7 +34740,7 @@
       <c r="AM229" s="1"/>
       <c r="AN229" s="83"/>
     </row>
-    <row r="230" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="15" t="s">
         <v>667</v>
       </c>
@@ -34824,7 +34825,7 @@
       <c r="AM230" s="1"/>
       <c r="AN230" s="83"/>
     </row>
-    <row r="231" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="15" t="s">
         <v>669</v>
       </c>
@@ -34909,7 +34910,7 @@
       <c r="AM231" s="1"/>
       <c r="AN231" s="83"/>
     </row>
-    <row r="232" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="15" t="s">
         <v>671</v>
       </c>
@@ -34990,7 +34991,7 @@
       <c r="AM232" s="1"/>
       <c r="AN232" s="83"/>
     </row>
-    <row r="233" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="15" t="s">
         <v>672</v>
       </c>
@@ -35075,7 +35076,7 @@
       <c r="AM233" s="1"/>
       <c r="AN233" s="83"/>
     </row>
-    <row r="234" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="15" t="s">
         <v>674</v>
       </c>
@@ -35164,7 +35165,7 @@
       <c r="AM234" s="1"/>
       <c r="AN234" s="83"/>
     </row>
-    <row r="235" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="15" t="s">
         <v>675</v>
       </c>
@@ -35251,7 +35252,7 @@
       <c r="AM235" s="1"/>
       <c r="AN235" s="83"/>
     </row>
-    <row r="236" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="15" t="s">
         <v>678</v>
       </c>
@@ -35338,7 +35339,7 @@
       <c r="AM236" s="1"/>
       <c r="AN236" s="83"/>
     </row>
-    <row r="237" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="15" t="s">
         <v>680</v>
       </c>
@@ -35425,7 +35426,7 @@
       <c r="AM237" s="1"/>
       <c r="AN237" s="83"/>
     </row>
-    <row r="238" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="15" t="s">
         <v>683</v>
       </c>
@@ -35516,7 +35517,7 @@
       <c r="AM238" s="1"/>
       <c r="AN238" s="83"/>
     </row>
-    <row r="239" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="15" t="s">
         <v>686</v>
       </c>
@@ -35607,7 +35608,7 @@
       <c r="AM239" s="1"/>
       <c r="AN239" s="83"/>
     </row>
-    <row r="240" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="15" t="s">
         <v>688</v>
       </c>
@@ -35698,7 +35699,7 @@
       <c r="AM240" s="1"/>
       <c r="AN240" s="83"/>
     </row>
-    <row r="241" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="15" t="s">
         <v>690</v>
       </c>
@@ -35787,7 +35788,7 @@
       <c r="AM241" s="1"/>
       <c r="AN241" s="83"/>
     </row>
-    <row r="242" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="15" t="s">
         <v>692</v>
       </c>
@@ -35874,7 +35875,7 @@
       <c r="AM242" s="1"/>
       <c r="AN242" s="83"/>
     </row>
-    <row r="243" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="15" t="s">
         <v>694</v>
       </c>
@@ -35967,7 +35968,7 @@
       <c r="AM243" s="1"/>
       <c r="AN243" s="83"/>
     </row>
-    <row r="244" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="15" t="s">
         <v>696</v>
       </c>
@@ -36054,7 +36055,7 @@
       <c r="AM244" s="1"/>
       <c r="AN244" s="83"/>
     </row>
-    <row r="245" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="15" t="s">
         <v>698</v>
       </c>
@@ -36139,7 +36140,7 @@
       <c r="AM245" s="1"/>
       <c r="AN245" s="83"/>
     </row>
-    <row r="246" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="15" t="s">
         <v>700</v>
       </c>
@@ -36226,7 +36227,7 @@
       <c r="AM246" s="1"/>
       <c r="AN246" s="83"/>
     </row>
-    <row r="247" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="15" t="s">
         <v>702</v>
       </c>
@@ -36313,7 +36314,7 @@
       <c r="AM247" s="1"/>
       <c r="AN247" s="83"/>
     </row>
-    <row r="248" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="15" t="s">
         <v>704</v>
       </c>
@@ -36400,7 +36401,7 @@
       <c r="AM248" s="1"/>
       <c r="AN248" s="83"/>
     </row>
-    <row r="249" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="15" t="s">
         <v>706</v>
       </c>
@@ -36487,7 +36488,7 @@
       <c r="AM249" s="1"/>
       <c r="AN249" s="83"/>
     </row>
-    <row r="250" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="15" t="s">
         <v>708</v>
       </c>
@@ -36576,7 +36577,7 @@
       <c r="AM250" s="1"/>
       <c r="AN250" s="83"/>
     </row>
-    <row r="251" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="15" t="s">
         <v>709</v>
       </c>
@@ -36661,7 +36662,7 @@
       <c r="AM251" s="1"/>
       <c r="AN251" s="83"/>
     </row>
-    <row r="252" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="15" t="s">
         <v>711</v>
       </c>
@@ -36746,7 +36747,7 @@
       <c r="AM252" s="1"/>
       <c r="AN252" s="83"/>
     </row>
-    <row r="253" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="15" t="s">
         <v>713</v>
       </c>
@@ -36831,7 +36832,7 @@
       <c r="AM253" s="1"/>
       <c r="AN253" s="83"/>
     </row>
-    <row r="254" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="15" t="s">
         <v>715</v>
       </c>
@@ -36916,7 +36917,7 @@
       <c r="AM254" s="1"/>
       <c r="AN254" s="83"/>
     </row>
-    <row r="255" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="15" t="s">
         <v>717</v>
       </c>
@@ -37003,7 +37004,7 @@
       <c r="AM255" s="1"/>
       <c r="AN255" s="83"/>
     </row>
-    <row r="256" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="15" t="s">
         <v>719</v>
       </c>
@@ -37092,7 +37093,7 @@
       <c r="AM256" s="1"/>
       <c r="AN256" s="83"/>
     </row>
-    <row r="257" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="15" t="s">
         <v>721</v>
       </c>
@@ -37179,7 +37180,7 @@
       <c r="AM257" s="1"/>
       <c r="AN257" s="83"/>
     </row>
-    <row r="258" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="15" t="s">
         <v>723</v>
       </c>
@@ -37266,7 +37267,7 @@
       <c r="AM258" s="1"/>
       <c r="AN258" s="83"/>
     </row>
-    <row r="259" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="15" t="s">
         <v>725</v>
       </c>
@@ -37353,7 +37354,7 @@
       <c r="AM259" s="1"/>
       <c r="AN259" s="83"/>
     </row>
-    <row r="260" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="15" t="s">
         <v>727</v>
       </c>
@@ -37438,7 +37439,7 @@
       <c r="AM260" s="1"/>
       <c r="AN260" s="83"/>
     </row>
-    <row r="261" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="15" t="s">
         <v>728</v>
       </c>
@@ -37519,7 +37520,7 @@
       <c r="AM261" s="1"/>
       <c r="AN261" s="83"/>
     </row>
-    <row r="262" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="15" t="s">
         <v>729</v>
       </c>
@@ -37600,7 +37601,7 @@
       <c r="AM262" s="1"/>
       <c r="AN262" s="83"/>
     </row>
-    <row r="263" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="15" t="s">
         <v>730</v>
       </c>
@@ -37677,7 +37678,7 @@
       <c r="AM263" s="1"/>
       <c r="AN263" s="83"/>
     </row>
-    <row r="264" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="15" t="s">
         <v>732</v>
       </c>
@@ -37758,7 +37759,7 @@
       <c r="AM264" s="1"/>
       <c r="AN264" s="83"/>
     </row>
-    <row r="265" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="15" t="s">
         <v>733</v>
       </c>
@@ -37835,7 +37836,7 @@
       <c r="AM265" s="1"/>
       <c r="AN265" s="83"/>
     </row>
-    <row r="266" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="15" t="s">
         <v>734</v>
       </c>
@@ -37916,7 +37917,7 @@
       <c r="AM266" s="1"/>
       <c r="AN266" s="83"/>
     </row>
-    <row r="267" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="15" t="s">
         <v>735</v>
       </c>
@@ -37999,7 +38000,7 @@
       <c r="AM267" s="1"/>
       <c r="AN267" s="83"/>
     </row>
-    <row r="268" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="15" t="s">
         <v>736</v>
       </c>
@@ -38080,7 +38081,7 @@
       <c r="AM268" s="1"/>
       <c r="AN268" s="83"/>
     </row>
-    <row r="269" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="15" t="s">
         <v>738</v>
       </c>
@@ -38161,7 +38162,7 @@
       <c r="AM269" s="1"/>
       <c r="AN269" s="83"/>
     </row>
-    <row r="270" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="15" t="s">
         <v>739</v>
       </c>
@@ -38242,7 +38243,7 @@
       <c r="AM270" s="1"/>
       <c r="AN270" s="83"/>
     </row>
-    <row r="271" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="15" t="s">
         <v>740</v>
       </c>
@@ -38323,7 +38324,7 @@
       <c r="AM271" s="1"/>
       <c r="AN271" s="83"/>
     </row>
-    <row r="272" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="31" t="s">
         <v>741</v>
       </c>
@@ -38404,7 +38405,7 @@
       <c r="AM272" s="1"/>
       <c r="AN272" s="83"/>
     </row>
-    <row r="273" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="15" t="s">
         <v>742</v>
       </c>
@@ -38487,7 +38488,7 @@
       <c r="AM273" s="1"/>
       <c r="AN273" s="83"/>
     </row>
-    <row r="274" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="15" t="s">
         <v>743</v>
       </c>
@@ -38568,7 +38569,7 @@
       <c r="AM274" s="1"/>
       <c r="AN274" s="83"/>
     </row>
-    <row r="275" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="15" t="s">
         <v>744</v>
       </c>
@@ -38649,7 +38650,7 @@
       <c r="AM275" s="1"/>
       <c r="AN275" s="83"/>
     </row>
-    <row r="276" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="15" t="s">
         <v>745</v>
       </c>
@@ -38730,7 +38731,7 @@
       <c r="AM276" s="1"/>
       <c r="AN276" s="83"/>
     </row>
-    <row r="277" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="15" t="s">
         <v>746</v>
       </c>
@@ -38811,7 +38812,7 @@
       <c r="AM277" s="1"/>
       <c r="AN277" s="83"/>
     </row>
-    <row r="278" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="15" t="s">
         <v>747</v>
       </c>
@@ -57805,7 +57806,7 @@
       <c r="AM497" s="1"/>
       <c r="AN497" s="83"/>
     </row>
-    <row r="498" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" s="19" t="s">
         <v>1129</v>
       </c>
@@ -57920,7 +57921,7 @@
       </c>
       <c r="AO498" s="81"/>
     </row>
-    <row r="499" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" s="19" t="s">
         <v>1136</v>
       </c>
@@ -58035,7 +58036,7 @@
       </c>
       <c r="AO499" s="81"/>
     </row>
-    <row r="500" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" s="19" t="s">
         <v>1141</v>
       </c>
@@ -58148,7 +58149,7 @@
       </c>
       <c r="AO500" s="81"/>
     </row>
-    <row r="501" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" s="19" t="s">
         <v>1147</v>
       </c>
@@ -58263,7 +58264,7 @@
       </c>
       <c r="AO501" s="81"/>
     </row>
-    <row r="502" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" s="19" t="s">
         <v>1150</v>
       </c>
@@ -58378,7 +58379,7 @@
       </c>
       <c r="AO502" s="81"/>
     </row>
-    <row r="503" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" s="19" t="s">
         <v>1154</v>
       </c>
@@ -58493,7 +58494,7 @@
       </c>
       <c r="AO503" s="81"/>
     </row>
-    <row r="504" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" s="19" t="s">
         <v>1158</v>
       </c>
@@ -58595,7 +58596,7 @@
       <c r="AN504" s="83"/>
       <c r="AO504" s="81"/>
     </row>
-    <row r="505" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" s="19" t="s">
         <v>1162</v>
       </c>
@@ -58710,7 +58711,7 @@
       </c>
       <c r="AO505" s="81"/>
     </row>
-    <row r="506" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" s="19" t="s">
         <v>1166</v>
       </c>
@@ -58825,7 +58826,7 @@
       </c>
       <c r="AO506" s="81"/>
     </row>
-    <row r="507" spans="1:41" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:41" s="26" customFormat="1" ht="30.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" s="19" t="s">
         <v>1169</v>
       </c>
@@ -58940,7 +58941,7 @@
       </c>
       <c r="AO507" s="81"/>
     </row>
-    <row r="508" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" s="19" t="s">
         <v>1172</v>
       </c>
@@ -59045,7 +59046,7 @@
       <c r="AN508" s="83"/>
       <c r="AO508" s="81"/>
     </row>
-    <row r="509" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" s="19" t="s">
         <v>1174</v>
       </c>
@@ -59160,7 +59161,7 @@
       </c>
       <c r="AO509" s="81"/>
     </row>
-    <row r="510" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" s="19" t="s">
         <v>1177</v>
       </c>
@@ -59266,7 +59267,7 @@
       </c>
       <c r="AO510" s="81"/>
     </row>
-    <row r="511" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" s="19" t="s">
         <v>1179</v>
       </c>
@@ -59369,7 +59370,7 @@
       <c r="AN511" s="83"/>
       <c r="AO511" s="81"/>
     </row>
-    <row r="512" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" s="19" t="s">
         <v>1181</v>
       </c>
@@ -59484,7 +59485,7 @@
       </c>
       <c r="AO512" s="81"/>
     </row>
-    <row r="513" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" s="19" t="s">
         <v>1184</v>
       </c>
@@ -59599,7 +59600,7 @@
       </c>
       <c r="AO513" s="81"/>
     </row>
-    <row r="514" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" s="19" t="s">
         <v>1187</v>
       </c>
@@ -59714,7 +59715,7 @@
       </c>
       <c r="AO514" s="81"/>
     </row>
-    <row r="515" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" s="19" t="s">
         <v>1190</v>
       </c>
@@ -59829,7 +59830,7 @@
       </c>
       <c r="AO515" s="81"/>
     </row>
-    <row r="516" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="19" t="s">
         <v>1193</v>
       </c>
@@ -59942,7 +59943,7 @@
       </c>
       <c r="AO516" s="81"/>
     </row>
-    <row r="517" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" s="19" t="s">
         <v>388</v>
       </c>
@@ -60209,7 +60210,7 @@
       </c>
       <c r="AO519" s="81"/>
     </row>
-    <row r="520" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" s="19" t="s">
         <v>1200</v>
       </c>
@@ -60324,7 +60325,7 @@
       </c>
       <c r="AO520" s="81"/>
     </row>
-    <row r="521" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" s="19" t="s">
         <v>1205</v>
       </c>
@@ -60435,7 +60436,7 @@
       </c>
       <c r="AO521" s="81"/>
     </row>
-    <row r="522" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" s="19" t="s">
         <v>1207</v>
       </c>
@@ -60550,7 +60551,7 @@
       </c>
       <c r="AO522" s="81"/>
     </row>
-    <row r="523" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" s="19" t="s">
         <v>1210</v>
       </c>
@@ -60655,7 +60656,7 @@
       <c r="AN523" s="83"/>
       <c r="AO523" s="81"/>
     </row>
-    <row r="524" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" s="19" t="s">
         <v>1214</v>
       </c>
@@ -60768,7 +60769,7 @@
       </c>
       <c r="AO524" s="81"/>
     </row>
-    <row r="525" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" s="19" t="s">
         <v>1218</v>
       </c>
@@ -60869,7 +60870,7 @@
       <c r="AN525" s="83"/>
       <c r="AO525" s="81"/>
     </row>
-    <row r="526" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" s="19" t="s">
         <v>1221</v>
       </c>
@@ -60984,7 +60985,7 @@
       </c>
       <c r="AO526" s="81"/>
     </row>
-    <row r="527" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" s="19" t="s">
         <v>1224</v>
       </c>
@@ -61099,7 +61100,7 @@
       </c>
       <c r="AO527" s="81"/>
     </row>
-    <row r="528" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" s="19" t="s">
         <v>1228</v>
       </c>
@@ -61214,7 +61215,7 @@
       </c>
       <c r="AO528" s="81"/>
     </row>
-    <row r="529" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="19" t="s">
         <v>1231</v>
       </c>
@@ -61330,7 +61331,7 @@
       </c>
       <c r="AO529" s="81"/>
     </row>
-    <row r="530" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" s="19" t="s">
         <v>723</v>
       </c>
@@ -61430,7 +61431,7 @@
       <c r="AN530" s="83"/>
       <c r="AO530" s="81"/>
     </row>
-    <row r="531" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" s="19" t="s">
         <v>1234</v>
       </c>
@@ -61543,7 +61544,7 @@
       </c>
       <c r="AO531" s="81"/>
     </row>
-    <row r="532" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" s="19" t="s">
         <v>1237</v>
       </c>
@@ -61647,7 +61648,7 @@
       <c r="AN532" s="83"/>
       <c r="AO532" s="81"/>
     </row>
-    <row r="533" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" s="19" t="s">
         <v>1239</v>
       </c>
@@ -61751,7 +61752,7 @@
       <c r="AN533" s="83"/>
       <c r="AO533" s="81"/>
     </row>
-    <row r="534" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" s="19" t="s">
         <v>1241</v>
       </c>
@@ -61866,7 +61867,7 @@
       </c>
       <c r="AO534" s="81"/>
     </row>
-    <row r="535" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" s="19" t="s">
         <v>1245</v>
       </c>
@@ -61977,7 +61978,7 @@
       <c r="AN535" s="83"/>
       <c r="AO535" s="81"/>
     </row>
-    <row r="536" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" s="19" t="s">
         <v>1247</v>
       </c>
@@ -62081,7 +62082,7 @@
       <c r="AN536" s="83"/>
       <c r="AO536" s="81"/>
     </row>
-    <row r="537" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" s="19" t="s">
         <v>734</v>
       </c>
@@ -62194,7 +62195,7 @@
       </c>
       <c r="AO537" s="81"/>
     </row>
-    <row r="538" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" s="19" t="s">
         <v>1251</v>
       </c>
@@ -62306,7 +62307,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="539" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" s="19" t="s">
         <v>1253</v>
       </c>
@@ -62420,7 +62421,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="540" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" s="19" t="s">
         <v>1256</v>
       </c>
@@ -62523,7 +62524,7 @@
       <c r="AM540" s="1"/>
       <c r="AN540" s="83"/>
     </row>
-    <row r="541" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" s="19" t="s">
         <v>719</v>
       </c>
@@ -62622,7 +62623,7 @@
       <c r="AM541" s="1"/>
       <c r="AN541" s="83"/>
     </row>
-    <row r="542" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" s="19" t="s">
         <v>1259</v>
       </c>
@@ -62736,7 +62737,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="543" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" s="19" t="s">
         <v>1261</v>
       </c>
@@ -62839,7 +62840,7 @@
       <c r="AM543" s="1"/>
       <c r="AN543" s="83"/>
     </row>
-    <row r="544" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" s="19" t="s">
         <v>1263</v>
       </c>
@@ -62953,7 +62954,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="545" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="19" t="s">
         <v>1266</v>
       </c>
@@ -63067,7 +63068,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="546" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="19" t="s">
         <v>1268</v>
       </c>
@@ -63181,7 +63182,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="547" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" s="19" t="s">
         <v>1270</v>
       </c>
@@ -63284,7 +63285,7 @@
       <c r="AM547" s="1"/>
       <c r="AN547" s="83"/>
     </row>
-    <row r="548" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="19" t="s">
         <v>1271</v>
       </c>
@@ -63398,7 +63399,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="549" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="19" t="s">
         <v>1274</v>
       </c>
@@ -63501,7 +63502,7 @@
       <c r="AM549" s="1"/>
       <c r="AN549" s="83"/>
     </row>
-    <row r="550" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="19" t="s">
         <v>1275</v>
       </c>
@@ -63604,7 +63605,7 @@
       <c r="AM550" s="1"/>
       <c r="AN550" s="83"/>
     </row>
-    <row r="551" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" s="19" t="s">
         <v>1277</v>
       </c>
@@ -63707,7 +63708,7 @@
       <c r="AM551" s="1"/>
       <c r="AN551" s="83"/>
     </row>
-    <row r="552" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" s="19" t="s">
         <v>738</v>
       </c>
@@ -63808,7 +63809,7 @@
       <c r="AM552" s="1"/>
       <c r="AN552" s="83"/>
     </row>
-    <row r="553" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="19" t="s">
         <v>1278</v>
       </c>
@@ -63922,7 +63923,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="554" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" s="19" t="s">
         <v>1282</v>
       </c>
@@ -64025,7 +64026,7 @@
       <c r="AM554" s="1"/>
       <c r="AN554" s="83"/>
     </row>
-    <row r="555" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" s="19" t="s">
         <v>1283</v>
       </c>
@@ -64126,7 +64127,7 @@
       <c r="AM555" s="1"/>
       <c r="AN555" s="83"/>
     </row>
-    <row r="556" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" s="19" t="s">
         <v>1284</v>
       </c>
@@ -64240,7 +64241,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="557" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="19" t="s">
         <v>1287</v>
       </c>
@@ -64343,7 +64344,7 @@
       <c r="AM557" s="1"/>
       <c r="AN557" s="83"/>
     </row>
-    <row r="558" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="19" t="s">
         <v>1289</v>
       </c>
@@ -64444,7 +64445,7 @@
       <c r="AM558" s="1"/>
       <c r="AN558" s="83"/>
     </row>
-    <row r="559" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" s="19" t="s">
         <v>1291</v>
       </c>
@@ -64545,7 +64546,7 @@
       <c r="AM559" s="1"/>
       <c r="AN559" s="83"/>
     </row>
-    <row r="560" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" s="19" t="s">
         <v>1293</v>
       </c>
@@ -64657,7 +64658,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="561" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" s="19" t="s">
         <v>586</v>
       </c>
@@ -64760,7 +64761,7 @@
       <c r="AM561" s="1"/>
       <c r="AN561" s="83"/>
     </row>
-    <row r="562" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" s="19" t="s">
         <v>1296</v>
       </c>
@@ -64874,7 +64875,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="563" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" s="19" t="s">
         <v>1298</v>
       </c>
@@ -64988,7 +64989,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="564" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="19" t="s">
         <v>1301</v>
       </c>
@@ -65100,7 +65101,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="565" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="19" t="s">
         <v>1304</v>
       </c>
@@ -65201,7 +65202,7 @@
       <c r="AM565" s="1"/>
       <c r="AN565" s="83"/>
     </row>
-    <row r="566" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="19" t="s">
         <v>1306</v>
       </c>
@@ -65304,7 +65305,7 @@
       <c r="AM566" s="1"/>
       <c r="AN566" s="83"/>
     </row>
-    <row r="567" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" s="32" t="s">
         <v>1308</v>
       </c>
@@ -65405,7 +65406,7 @@
       <c r="AM567" s="1"/>
       <c r="AN567" s="83"/>
     </row>
-    <row r="568" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" s="19" t="s">
         <v>1310</v>
       </c>
@@ -65508,7 +65509,7 @@
       <c r="AM568" s="1"/>
       <c r="AN568" s="83"/>
     </row>
-    <row r="569" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" s="19" t="s">
         <v>1312</v>
       </c>
@@ -65622,7 +65623,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="570" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" s="19" t="s">
         <v>1315</v>
       </c>
@@ -65723,7 +65724,7 @@
       <c r="AM570" s="1"/>
       <c r="AN570" s="83"/>
     </row>
-    <row r="571" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="19" t="s">
         <v>1317</v>
       </c>
@@ -65824,7 +65825,7 @@
       <c r="AM571" s="1"/>
       <c r="AN571" s="83"/>
     </row>
-    <row r="572" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" s="19" t="s">
         <v>1318</v>
       </c>
@@ -65925,7 +65926,7 @@
       <c r="AM572" s="1"/>
       <c r="AN572" s="83"/>
     </row>
-    <row r="573" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" s="19" t="s">
         <v>1320</v>
       </c>
@@ -66028,7 +66029,7 @@
       <c r="AM573" s="1"/>
       <c r="AN573" s="83"/>
     </row>
-    <row r="574" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="19" t="s">
         <v>1322</v>
       </c>
@@ -66131,7 +66132,7 @@
       <c r="AM574" s="1"/>
       <c r="AN574" s="83"/>
     </row>
-    <row r="575" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" s="19" t="s">
         <v>1325</v>
       </c>
@@ -66234,7 +66235,7 @@
       <c r="AM575" s="1"/>
       <c r="AN575" s="83"/>
     </row>
-    <row r="576" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" s="19" t="s">
         <v>1327</v>
       </c>
@@ -66337,7 +66338,7 @@
       <c r="AM576" s="1"/>
       <c r="AN576" s="83"/>
     </row>
-    <row r="577" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" s="19" t="s">
         <v>1329</v>
       </c>
@@ -66440,7 +66441,7 @@
       <c r="AM577" s="1"/>
       <c r="AN577" s="83"/>
     </row>
-    <row r="578" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" s="19" t="s">
         <v>1331</v>
       </c>
@@ -66541,7 +66542,7 @@
       <c r="AM578" s="1"/>
       <c r="AN578" s="83"/>
     </row>
-    <row r="579" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579" s="19" t="s">
         <v>1332</v>
       </c>
@@ -66644,7 +66645,7 @@
       <c r="AM579" s="1"/>
       <c r="AN579" s="83"/>
     </row>
-    <row r="580" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" s="19" t="s">
         <v>1334</v>
       </c>
@@ -66747,7 +66748,7 @@
       <c r="AM580" s="1"/>
       <c r="AN580" s="83"/>
     </row>
-    <row r="581" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" s="19" t="s">
         <v>1335</v>
       </c>
@@ -66850,7 +66851,7 @@
       <c r="AM581" s="1"/>
       <c r="AN581" s="83"/>
     </row>
-    <row r="582" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582" s="19" t="s">
         <v>1337</v>
       </c>
@@ -66953,7 +66954,7 @@
       <c r="AM582" s="1"/>
       <c r="AN582" s="83"/>
     </row>
-    <row r="583" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="19" t="s">
         <v>1339</v>
       </c>
@@ -67016,7 +67017,7 @@
       <c r="AM583" s="1"/>
       <c r="AN583" s="83"/>
     </row>
-    <row r="584" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="19" t="s">
         <v>1340</v>
       </c>
@@ -67119,7 +67120,7 @@
       <c r="AM584" s="1"/>
       <c r="AN584" s="83"/>
     </row>
-    <row r="585" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" s="19" t="s">
         <v>1342</v>
       </c>
@@ -67222,7 +67223,7 @@
       <c r="AM585" s="1"/>
       <c r="AN585" s="83"/>
     </row>
-    <row r="586" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" s="19" t="s">
         <v>1344</v>
       </c>
@@ -67325,7 +67326,7 @@
       <c r="AM586" s="1"/>
       <c r="AN586" s="83"/>
     </row>
-    <row r="587" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" s="19" t="s">
         <v>1346</v>
       </c>
@@ -67424,7 +67425,7 @@
       <c r="AM587" s="1"/>
       <c r="AN587" s="83"/>
     </row>
-    <row r="588" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" s="19" t="s">
         <v>299</v>
       </c>
@@ -67523,7 +67524,7 @@
       <c r="AM588" s="1"/>
       <c r="AN588" s="83"/>
     </row>
-    <row r="589" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" s="19" t="s">
         <v>1349</v>
       </c>
@@ -67626,7 +67627,7 @@
       <c r="AM589" s="1"/>
       <c r="AN589" s="83"/>
     </row>
-    <row r="590" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" s="19" t="s">
         <v>1351</v>
       </c>
@@ -67729,7 +67730,7 @@
       <c r="AM590" s="1"/>
       <c r="AN590" s="83"/>
     </row>
-    <row r="591" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591" s="22" t="s">
         <v>1353</v>
       </c>
@@ -67804,7 +67805,7 @@
       <c r="AM591" s="1"/>
       <c r="AN591" s="83"/>
     </row>
-    <row r="592" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592" s="22" t="s">
         <v>1356</v>
       </c>
@@ -67877,7 +67878,7 @@
       <c r="AM592" s="1"/>
       <c r="AN592" s="83"/>
     </row>
-    <row r="593" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" s="22" t="s">
         <v>1359</v>
       </c>
@@ -67950,7 +67951,7 @@
       <c r="AM593" s="1"/>
       <c r="AN593" s="83"/>
     </row>
-    <row r="594" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" s="22" t="s">
         <v>1360</v>
       </c>
@@ -68023,7 +68024,7 @@
       <c r="AM594" s="1"/>
       <c r="AN594" s="83"/>
     </row>
-    <row r="595" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="22" t="s">
         <v>647</v>
       </c>
@@ -68096,7 +68097,7 @@
       <c r="AM595" s="1"/>
       <c r="AN595" s="83"/>
     </row>
-    <row r="596" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="22" t="s">
         <v>1363</v>
       </c>
@@ -68169,7 +68170,7 @@
       <c r="AM596" s="1"/>
       <c r="AN596" s="83"/>
     </row>
-    <row r="597" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" s="22" t="s">
         <v>1364</v>
       </c>
@@ -68242,7 +68243,7 @@
       <c r="AM597" s="1"/>
       <c r="AN597" s="83"/>
     </row>
-    <row r="598" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" s="22" t="s">
         <v>1365</v>
       </c>
@@ -68315,7 +68316,7 @@
       <c r="AM598" s="1"/>
       <c r="AN598" s="83"/>
     </row>
-    <row r="599" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="22" t="s">
         <v>1368</v>
       </c>
@@ -68388,7 +68389,7 @@
       <c r="AM599" s="1"/>
       <c r="AN599" s="83"/>
     </row>
-    <row r="600" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" s="22" t="s">
         <v>1369</v>
       </c>
@@ -68461,7 +68462,7 @@
       <c r="AM600" s="1"/>
       <c r="AN600" s="83"/>
     </row>
-    <row r="601" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" s="22" t="s">
         <v>1371</v>
       </c>
@@ -68534,7 +68535,7 @@
       <c r="AM601" s="1"/>
       <c r="AN601" s="83"/>
     </row>
-    <row r="602" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" s="22" t="s">
         <v>868</v>
       </c>
@@ -68607,7 +68608,7 @@
       <c r="AM602" s="1"/>
       <c r="AN602" s="83"/>
     </row>
-    <row r="603" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603" s="22" t="s">
         <v>1373</v>
       </c>
@@ -68680,7 +68681,7 @@
       <c r="AM603" s="1"/>
       <c r="AN603" s="83"/>
     </row>
-    <row r="604" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604" s="22" t="s">
         <v>1374</v>
       </c>
@@ -68753,7 +68754,7 @@
       <c r="AM604" s="1"/>
       <c r="AN604" s="83"/>
     </row>
-    <row r="605" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605" s="22" t="s">
         <v>655</v>
       </c>
@@ -68826,7 +68827,7 @@
       <c r="AM605" s="1"/>
       <c r="AN605" s="83"/>
     </row>
-    <row r="606" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606" s="22" t="s">
         <v>275</v>
       </c>
@@ -68901,7 +68902,7 @@
       <c r="AM606" s="1"/>
       <c r="AN606" s="83"/>
     </row>
-    <row r="607" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607" s="22" t="s">
         <v>1377</v>
       </c>
@@ -68974,7 +68975,7 @@
       <c r="AM607" s="1"/>
       <c r="AN607" s="83"/>
     </row>
-    <row r="608" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608" s="22" t="s">
         <v>1378</v>
       </c>
@@ -69047,7 +69048,7 @@
       <c r="AM608" s="1"/>
       <c r="AN608" s="83"/>
     </row>
-    <row r="609" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609" s="22" t="s">
         <v>378</v>
       </c>
@@ -69120,7 +69121,7 @@
       <c r="AM609" s="1"/>
       <c r="AN609" s="83"/>
     </row>
-    <row r="610" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610" s="22" t="s">
         <v>370</v>
       </c>
@@ -69193,7 +69194,7 @@
       <c r="AM610" s="1"/>
       <c r="AN610" s="83"/>
     </row>
-    <row r="611" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611" s="22" t="s">
         <v>1379</v>
       </c>
@@ -69266,7 +69267,7 @@
       <c r="AM611" s="1"/>
       <c r="AN611" s="83"/>
     </row>
-    <row r="612" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612" s="22" t="s">
         <v>1380</v>
       </c>
@@ -69339,7 +69340,7 @@
       <c r="AM612" s="1"/>
       <c r="AN612" s="83"/>
     </row>
-    <row r="613" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613" s="22" t="s">
         <v>1381</v>
       </c>
@@ -69412,7 +69413,7 @@
       <c r="AM613" s="1"/>
       <c r="AN613" s="83"/>
     </row>
-    <row r="614" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614" s="22" t="s">
         <v>1383</v>
       </c>
@@ -69485,7 +69486,7 @@
       <c r="AM614" s="1"/>
       <c r="AN614" s="83"/>
     </row>
-    <row r="615" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615" s="22" t="s">
         <v>672</v>
       </c>
@@ -69558,7 +69559,7 @@
       <c r="AM615" s="1"/>
       <c r="AN615" s="83"/>
     </row>
-    <row r="616" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616" s="22" t="s">
         <v>1384</v>
       </c>
@@ -69631,7 +69632,7 @@
       <c r="AM616" s="1"/>
       <c r="AN616" s="83"/>
     </row>
-    <row r="617" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617" s="22" t="s">
         <v>1386</v>
       </c>
@@ -69704,7 +69705,7 @@
       <c r="AM617" s="1"/>
       <c r="AN617" s="83"/>
     </row>
-    <row r="618" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618" s="22" t="s">
         <v>880</v>
       </c>
@@ -69777,7 +69778,7 @@
       <c r="AM618" s="1"/>
       <c r="AN618" s="83"/>
     </row>
-    <row r="619" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619" s="22" t="s">
         <v>907</v>
       </c>
@@ -69850,7 +69851,7 @@
       <c r="AM619" s="1"/>
       <c r="AN619" s="83"/>
     </row>
-    <row r="620" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620" s="22" t="s">
         <v>877</v>
       </c>
@@ -69923,7 +69924,7 @@
       <c r="AM620" s="1"/>
       <c r="AN620" s="83"/>
     </row>
-    <row r="621" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621" s="22" t="s">
         <v>1389</v>
       </c>
@@ -69996,7 +69997,7 @@
       <c r="AM621" s="1"/>
       <c r="AN621" s="83"/>
     </row>
-    <row r="622" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622" s="22" t="s">
         <v>1390</v>
       </c>
@@ -70069,7 +70070,7 @@
       <c r="AM622" s="1"/>
       <c r="AN622" s="83"/>
     </row>
-    <row r="623" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" s="22" t="s">
         <v>859</v>
       </c>
@@ -70142,7 +70143,7 @@
       <c r="AM623" s="1"/>
       <c r="AN623" s="83"/>
     </row>
-    <row r="624" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" s="22" t="s">
         <v>1392</v>
       </c>
@@ -70215,7 +70216,7 @@
       <c r="AM624" s="1"/>
       <c r="AN624" s="83"/>
     </row>
-    <row r="625" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" s="22" t="s">
         <v>1393</v>
       </c>
@@ -70288,7 +70289,7 @@
       <c r="AM625" s="1"/>
       <c r="AN625" s="83"/>
     </row>
-    <row r="626" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626" s="22" t="s">
         <v>406</v>
       </c>
@@ -70361,7 +70362,7 @@
       <c r="AM626" s="1"/>
       <c r="AN626" s="83"/>
     </row>
-    <row r="627" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A627" s="22" t="s">
         <v>1396</v>
       </c>
@@ -70434,7 +70435,7 @@
       <c r="AM627" s="1"/>
       <c r="AN627" s="83"/>
     </row>
-    <row r="628" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628" s="22" t="s">
         <v>921</v>
       </c>
@@ -70507,7 +70508,7 @@
       <c r="AM628" s="1"/>
       <c r="AN628" s="83"/>
     </row>
-    <row r="629" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629" s="22" t="s">
         <v>1398</v>
       </c>
@@ -70580,7 +70581,7 @@
       <c r="AM629" s="1"/>
       <c r="AN629" s="83"/>
     </row>
-    <row r="630" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" s="22" t="s">
         <v>892</v>
       </c>
@@ -70653,7 +70654,7 @@
       <c r="AM630" s="1"/>
       <c r="AN630" s="83"/>
     </row>
-    <row r="631" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631" s="22" t="s">
         <v>1400</v>
       </c>
@@ -70726,7 +70727,7 @@
       <c r="AM631" s="1"/>
       <c r="AN631" s="83"/>
     </row>
-    <row r="632" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632" s="22" t="s">
         <v>1401</v>
       </c>
@@ -70799,7 +70800,7 @@
       <c r="AM632" s="1"/>
       <c r="AN632" s="83"/>
     </row>
-    <row r="633" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633" s="22" t="s">
         <v>1403</v>
       </c>
@@ -70872,7 +70873,7 @@
       <c r="AM633" s="1"/>
       <c r="AN633" s="83"/>
     </row>
-    <row r="634" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634" s="22" t="s">
         <v>1404</v>
       </c>
@@ -70945,7 +70946,7 @@
       <c r="AM634" s="1"/>
       <c r="AN634" s="83"/>
     </row>
-    <row r="635" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635" s="22" t="s">
         <v>1405</v>
       </c>
@@ -71018,7 +71019,7 @@
       <c r="AM635" s="1"/>
       <c r="AN635" s="83"/>
     </row>
-    <row r="636" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636" s="22" t="s">
         <v>1406</v>
       </c>
@@ -71091,7 +71092,7 @@
       <c r="AM636" s="1"/>
       <c r="AN636" s="83"/>
     </row>
-    <row r="637" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637" s="22" t="s">
         <v>1407</v>
       </c>
@@ -71164,7 +71165,7 @@
       <c r="AM637" s="1"/>
       <c r="AN637" s="83"/>
     </row>
-    <row r="638" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638" s="22" t="s">
         <v>1409</v>
       </c>
@@ -71237,7 +71238,7 @@
       <c r="AM638" s="1"/>
       <c r="AN638" s="83"/>
     </row>
-    <row r="639" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639" s="22" t="s">
         <v>1410</v>
       </c>
@@ -71310,7 +71311,7 @@
       <c r="AM639" s="1"/>
       <c r="AN639" s="83"/>
     </row>
-    <row r="640" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" s="22" t="s">
         <v>1411</v>
       </c>
@@ -71383,7 +71384,7 @@
       <c r="AM640" s="1"/>
       <c r="AN640" s="83"/>
     </row>
-    <row r="641" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" s="22" t="s">
         <v>898</v>
       </c>
@@ -71456,7 +71457,7 @@
       <c r="AM641" s="1"/>
       <c r="AN641" s="83"/>
     </row>
-    <row r="642" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" s="22" t="s">
         <v>967</v>
       </c>
@@ -71529,7 +71530,7 @@
       <c r="AM642" s="1"/>
       <c r="AN642" s="83"/>
     </row>
-    <row r="643" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" s="22" t="s">
         <v>1412</v>
       </c>
@@ -71602,7 +71603,7 @@
       <c r="AM643" s="1"/>
       <c r="AN643" s="83"/>
     </row>
-    <row r="644" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644" s="22" t="s">
         <v>1414</v>
       </c>
@@ -71675,7 +71676,7 @@
       <c r="AM644" s="1"/>
       <c r="AN644" s="83"/>
     </row>
-    <row r="645" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645" s="22" t="s">
         <v>874</v>
       </c>
@@ -71748,7 +71749,7 @@
       <c r="AM645" s="1"/>
       <c r="AN645" s="83"/>
     </row>
-    <row r="646" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646" s="22" t="s">
         <v>1415</v>
       </c>
@@ -71821,7 +71822,7 @@
       <c r="AM646" s="1"/>
       <c r="AN646" s="83"/>
     </row>
-    <row r="647" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647" s="22" t="s">
         <v>946</v>
       </c>
@@ -71894,7 +71895,7 @@
       <c r="AM647" s="1"/>
       <c r="AN647" s="83"/>
     </row>
-    <row r="648" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648" s="22" t="s">
         <v>1416</v>
       </c>
@@ -71967,7 +71968,7 @@
       <c r="AM648" s="1"/>
       <c r="AN648" s="83"/>
     </row>
-    <row r="649" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649" s="22" t="s">
         <v>97</v>
       </c>
@@ -72042,7 +72043,7 @@
       <c r="AM649" s="1"/>
       <c r="AN649" s="83"/>
     </row>
-    <row r="650" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650" s="22" t="s">
         <v>1419</v>
       </c>
@@ -72115,7 +72116,7 @@
       <c r="AM650" s="1"/>
       <c r="AN650" s="83"/>
     </row>
-    <row r="651" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651" s="22" t="s">
         <v>1420</v>
       </c>
@@ -72186,7 +72187,7 @@
       <c r="AM651" s="1"/>
       <c r="AN651" s="83"/>
     </row>
-    <row r="652" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A652" s="22" t="s">
         <v>650</v>
       </c>
@@ -72259,7 +72260,7 @@
       <c r="AM652" s="1"/>
       <c r="AN652" s="83"/>
     </row>
-    <row r="653" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653" s="22" t="s">
         <v>1421</v>
       </c>
@@ -72332,7 +72333,7 @@
       <c r="AM653" s="1"/>
       <c r="AN653" s="83"/>
     </row>
-    <row r="654" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654" s="22" t="s">
         <v>1423</v>
       </c>
@@ -72405,7 +72406,7 @@
       <c r="AM654" s="1"/>
       <c r="AN654" s="83"/>
     </row>
-    <row r="655" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655" s="22" t="s">
         <v>1424</v>
       </c>
@@ -72478,7 +72479,7 @@
       <c r="AM655" s="1"/>
       <c r="AN655" s="83"/>
     </row>
-    <row r="656" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A656" s="22" t="s">
         <v>1426</v>
       </c>
@@ -72551,7 +72552,7 @@
       <c r="AM656" s="1"/>
       <c r="AN656" s="83"/>
     </row>
-    <row r="657" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A657" s="22" t="s">
         <v>1427</v>
       </c>
@@ -72624,7 +72625,7 @@
       <c r="AM657" s="1"/>
       <c r="AN657" s="83"/>
     </row>
-    <row r="658" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A658" s="22" t="s">
         <v>1428</v>
       </c>
@@ -72697,7 +72698,7 @@
       <c r="AM658" s="1"/>
       <c r="AN658" s="83"/>
     </row>
-    <row r="659" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A659" s="22" t="s">
         <v>1429</v>
       </c>
@@ -72770,7 +72771,7 @@
       <c r="AM659" s="1"/>
       <c r="AN659" s="83"/>
     </row>
-    <row r="660" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660" s="22" t="s">
         <v>1430</v>
       </c>
@@ -72843,7 +72844,7 @@
       <c r="AM660" s="1"/>
       <c r="AN660" s="83"/>
     </row>
-    <row r="661" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A661" s="22" t="s">
         <v>1431</v>
       </c>
@@ -72916,7 +72917,7 @@
       <c r="AM661" s="1"/>
       <c r="AN661" s="83"/>
     </row>
-    <row r="662" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662" s="22" t="s">
         <v>1432</v>
       </c>
@@ -72989,7 +72990,7 @@
       <c r="AM662" s="1"/>
       <c r="AN662" s="83"/>
     </row>
-    <row r="663" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663" s="22" t="s">
         <v>966</v>
       </c>
@@ -73062,7 +73063,7 @@
       <c r="AM663" s="1"/>
       <c r="AN663" s="83"/>
     </row>
-    <row r="664" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664" s="22" t="s">
         <v>578</v>
       </c>
@@ -73145,7 +73146,7 @@
       <c r="AM664" s="1"/>
       <c r="AN664" s="83"/>
     </row>
-    <row r="665" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665" s="22" t="s">
         <v>1435</v>
       </c>
@@ -73218,7 +73219,7 @@
       <c r="AM665" s="1"/>
       <c r="AN665" s="83"/>
     </row>
-    <row r="666" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A666" s="22" t="s">
         <v>1437</v>
       </c>
@@ -73291,7 +73292,7 @@
       <c r="AM666" s="1"/>
       <c r="AN666" s="83"/>
     </row>
-    <row r="667" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A667" s="22" t="s">
         <v>1439</v>
       </c>
@@ -73364,7 +73365,7 @@
       <c r="AM667" s="1"/>
       <c r="AN667" s="83"/>
     </row>
-    <row r="668" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A668" s="22" t="s">
         <v>1441</v>
       </c>
@@ -73437,7 +73438,7 @@
       <c r="AM668" s="1"/>
       <c r="AN668" s="83"/>
     </row>
-    <row r="669" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A669" s="22" t="s">
         <v>1442</v>
       </c>
@@ -73510,7 +73511,7 @@
       <c r="AM669" s="1"/>
       <c r="AN669" s="83"/>
     </row>
-    <row r="670" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A670" s="22" t="s">
         <v>1443</v>
       </c>
@@ -73583,7 +73584,7 @@
       <c r="AM670" s="1"/>
       <c r="AN670" s="83"/>
     </row>
-    <row r="671" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A671" s="22" t="s">
         <v>1445</v>
       </c>
@@ -73656,7 +73657,7 @@
       <c r="AM671" s="1"/>
       <c r="AN671" s="83"/>
     </row>
-    <row r="672" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A672" s="22" t="s">
         <v>1447</v>
       </c>
@@ -73729,7 +73730,7 @@
       <c r="AM672" s="1"/>
       <c r="AN672" s="83"/>
     </row>
-    <row r="673" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A673" s="22" t="s">
         <v>1448</v>
       </c>
@@ -73802,7 +73803,7 @@
       <c r="AM673" s="1"/>
       <c r="AN673" s="83"/>
     </row>
-    <row r="674" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A674" s="22" t="s">
         <v>1449</v>
       </c>
@@ -73873,7 +73874,7 @@
       <c r="AM674" s="1"/>
       <c r="AN674" s="83"/>
     </row>
-    <row r="675" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A675" s="22" t="s">
         <v>1450</v>
       </c>
@@ -73946,7 +73947,7 @@
       <c r="AM675" s="1"/>
       <c r="AN675" s="83"/>
     </row>
-    <row r="676" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A676" s="22" t="s">
         <v>1451</v>
       </c>
@@ -74019,7 +74020,7 @@
       <c r="AM676" s="1"/>
       <c r="AN676" s="83"/>
     </row>
-    <row r="677" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A677" s="22" t="s">
         <v>1452</v>
       </c>
@@ -74092,7 +74093,7 @@
       <c r="AM677" s="1"/>
       <c r="AN677" s="83"/>
     </row>
-    <row r="678" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A678" s="22" t="s">
         <v>1453</v>
       </c>
@@ -74165,7 +74166,7 @@
       <c r="AM678" s="1"/>
       <c r="AN678" s="83"/>
     </row>
-    <row r="679" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A679" s="22" t="s">
         <v>1454</v>
       </c>
@@ -74238,7 +74239,7 @@
       <c r="AM679" s="1"/>
       <c r="AN679" s="83"/>
     </row>
-    <row r="680" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A680" s="22" t="s">
         <v>1455</v>
       </c>
@@ -74311,7 +74312,7 @@
       <c r="AM680" s="1"/>
       <c r="AN680" s="83"/>
     </row>
-    <row r="681" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A681" s="22" t="s">
         <v>870</v>
       </c>
@@ -74384,7 +74385,7 @@
       <c r="AM681" s="1"/>
       <c r="AN681" s="83"/>
     </row>
-    <row r="682" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A682" s="22" t="s">
         <v>1456</v>
       </c>
@@ -74457,7 +74458,7 @@
       <c r="AM682" s="1"/>
       <c r="AN682" s="83"/>
     </row>
-    <row r="683" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A683" s="22" t="s">
         <v>1457</v>
       </c>
@@ -74530,7 +74531,7 @@
       <c r="AM683" s="1"/>
       <c r="AN683" s="83"/>
     </row>
-    <row r="684" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A684" s="22" t="s">
         <v>1458</v>
       </c>
@@ -74603,7 +74604,7 @@
       <c r="AM684" s="1"/>
       <c r="AN684" s="83"/>
     </row>
-    <row r="685" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A685" s="22" t="s">
         <v>1459</v>
       </c>
@@ -74676,7 +74677,7 @@
       <c r="AM685" s="1"/>
       <c r="AN685" s="83"/>
     </row>
-    <row r="686" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A686" s="22" t="s">
         <v>1460</v>
       </c>
@@ -74749,7 +74750,7 @@
       <c r="AM686" s="1"/>
       <c r="AN686" s="83"/>
     </row>
-    <row r="687" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A687" s="22" t="s">
         <v>1461</v>
       </c>
@@ -74822,7 +74823,7 @@
       <c r="AM687" s="1"/>
       <c r="AN687" s="83"/>
     </row>
-    <row r="688" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A688" s="22" t="s">
         <v>1462</v>
       </c>
@@ -74895,7 +74896,7 @@
       <c r="AM688" s="1"/>
       <c r="AN688" s="83"/>
     </row>
-    <row r="689" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A689" s="22" t="s">
         <v>1463</v>
       </c>
@@ -74968,7 +74969,7 @@
       <c r="AM689" s="1"/>
       <c r="AN689" s="83"/>
     </row>
-    <row r="690" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A690" s="22" t="s">
         <v>1464</v>
       </c>
@@ -75041,7 +75042,7 @@
       <c r="AM690" s="1"/>
       <c r="AN690" s="83"/>
     </row>
-    <row r="691" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A691" s="22" t="s">
         <v>1465</v>
       </c>
@@ -75114,7 +75115,7 @@
       <c r="AM691" s="1"/>
       <c r="AN691" s="83"/>
     </row>
-    <row r="692" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A692" s="22" t="s">
         <v>1466</v>
       </c>
@@ -75187,7 +75188,7 @@
       <c r="AM692" s="1"/>
       <c r="AN692" s="83"/>
     </row>
-    <row r="693" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A693" s="22" t="s">
         <v>1467</v>
       </c>
@@ -75260,7 +75261,7 @@
       <c r="AM693" s="1"/>
       <c r="AN693" s="83"/>
     </row>
-    <row r="694" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A694" s="22" t="s">
         <v>1468</v>
       </c>
@@ -75333,7 +75334,7 @@
       <c r="AM694" s="1"/>
       <c r="AN694" s="83"/>
     </row>
-    <row r="695" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A695" s="22" t="s">
         <v>1469</v>
       </c>
@@ -75406,7 +75407,7 @@
       <c r="AM695" s="1"/>
       <c r="AN695" s="83"/>
     </row>
-    <row r="696" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A696" s="22" t="s">
         <v>1470</v>
       </c>
@@ -75479,7 +75480,7 @@
       <c r="AM696" s="1"/>
       <c r="AN696" s="83"/>
     </row>
-    <row r="697" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A697" s="22" t="s">
         <v>1081</v>
       </c>
@@ -75552,7 +75553,7 @@
       <c r="AM697" s="1"/>
       <c r="AN697" s="83"/>
     </row>
-    <row r="698" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A698" s="22" t="s">
         <v>1472</v>
       </c>
@@ -75625,7 +75626,7 @@
       <c r="AM698" s="1"/>
       <c r="AN698" s="83"/>
     </row>
-    <row r="699" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A699" s="22" t="s">
         <v>1473</v>
       </c>
@@ -75698,7 +75699,7 @@
       <c r="AM699" s="1"/>
       <c r="AN699" s="83"/>
     </row>
-    <row r="700" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A700" s="22" t="s">
         <v>1474</v>
       </c>
@@ -75771,7 +75772,7 @@
       <c r="AM700" s="1"/>
       <c r="AN700" s="83"/>
     </row>
-    <row r="701" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A701" s="22" t="s">
         <v>1475</v>
       </c>
@@ -75844,7 +75845,7 @@
       <c r="AM701" s="1"/>
       <c r="AN701" s="83"/>
     </row>
-    <row r="702" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A702" s="22" t="s">
         <v>1476</v>
       </c>
@@ -75917,7 +75918,7 @@
       <c r="AM702" s="1"/>
       <c r="AN702" s="83"/>
     </row>
-    <row r="703" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A703" s="22" t="s">
         <v>1477</v>
       </c>
@@ -75990,7 +75991,7 @@
       <c r="AM703" s="1"/>
       <c r="AN703" s="83"/>
     </row>
-    <row r="704" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A704" s="22" t="s">
         <v>1109</v>
       </c>
@@ -76063,7 +76064,7 @@
       <c r="AM704" s="1"/>
       <c r="AN704" s="83"/>
     </row>
-    <row r="705" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A705" s="22" t="s">
         <v>1478</v>
       </c>
@@ -76136,7 +76137,7 @@
       <c r="AM705" s="1"/>
       <c r="AN705" s="83"/>
     </row>
-    <row r="706" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A706" s="22" t="s">
         <v>1479</v>
       </c>
@@ -76209,7 +76210,7 @@
       <c r="AM706" s="1"/>
       <c r="AN706" s="83"/>
     </row>
-    <row r="707" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A707" s="22" t="s">
         <v>1480</v>
       </c>
@@ -76282,7 +76283,7 @@
       <c r="AM707" s="1"/>
       <c r="AN707" s="83"/>
     </row>
-    <row r="708" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A708" s="22" t="s">
         <v>1481</v>
       </c>
@@ -76355,7 +76356,7 @@
       <c r="AM708" s="1"/>
       <c r="AN708" s="83"/>
     </row>
-    <row r="709" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A709" s="22" t="s">
         <v>1482</v>
       </c>
@@ -76428,7 +76429,7 @@
       <c r="AM709" s="1"/>
       <c r="AN709" s="83"/>
     </row>
-    <row r="710" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A710" s="22" t="s">
         <v>1483</v>
       </c>
@@ -76590,7 +76591,7 @@
       <c r="AB720" s="73"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AN710" xr:uid="{2AA437EE-405D-4A43-9EB9-23F1BEB36011}"/>
+  <autoFilter ref="A2:AN711" xr:uid="{2AA437EE-405D-4A43-9EB9-23F1BEB36011}"/>
   <conditionalFormatting sqref="A193:A213 A4:A95 A97:A118">
     <cfRule type="duplicateValues" dxfId="4" priority="12"/>
   </conditionalFormatting>
@@ -77768,9 +77769,15 @@
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE495743-F761-4961-A762-7A3D120C6961}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="c06ce65c-ed18-47f4-a957-afd315448c9c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="f5ab1930-d403-4c69-b2cd-8cc48f527d10"/>
-    <ds:schemaRef ds:uri="c06ce65c-ed18-47f4-a957-afd315448c9c"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/dados_atuais.xlsx
+++ b/data/dados_atuais.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
   <workbookPr codeName="EsteLivro"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delgadiadema.sharepoint.com/sites/GestoEstratgica/Documentos Compartilhados/Controle Master/BSW/Novo controle (Em processo)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2078" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C9D8836-533B-48DD-A7BC-4E47E2A31386}"/>
+  <xr:revisionPtr revIDLastSave="2079" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{757586D1-4CE9-47A5-905B-B68F9CB661D8}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="3696" yWindow="3696" windowWidth="17280" windowHeight="8880" xr2:uid="{3E398004-7492-4AA0-94C2-EA9B761AAA49}"/>
   </bookViews>
@@ -17,8 +17,8 @@
     <sheet name="Formulas" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Formulas!$A$9:$D$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Controle!$A$2:$AN$711</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Formulas!$A$9:$D$41</definedName>
     <definedName name="_FiltrarBaseDados" localSheetId="0" hidden="1">Controle!$A$2:$AL$710</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -213,17 +213,17 @@
     </comment>
     <comment ref="A555" authorId="3" shapeId="0" xr:uid="{33C328EB-7B56-47E9-A787-F392CA006902}">
       <text>
-        <t>[Comentário encadeado]
-Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
-Comentário:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Utilizando material 1,60x417</t>
       </text>
     </comment>
     <comment ref="A564" authorId="4" shapeId="0" xr:uid="{C01DA7E7-015C-4D77-8E50-06C386F35AF3}">
       <text>
-        <t>[Comentário encadeado]
-Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
-Comentário:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Temos na Fitametal 
 BOZ0070TJ1350 - 10249kg</t>
       </text>
@@ -254,17 +254,17 @@
     </comment>
     <comment ref="A574" authorId="6" shapeId="0" xr:uid="{67F1D739-35C9-474A-BA1D-BDA6C83EF4A4}">
       <text>
-        <t>[Comentário encadeado]
-Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
-Comentário:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     CORTAR SLEETER DE MATERIAL SEMELHANTE DEVIDO AO BAIXO VOLUME TEMOS O MESMO MATERIAL COM OUTRAS LARGURAS</t>
       </text>
     </comment>
     <comment ref="A575" authorId="7" shapeId="0" xr:uid="{9641E501-4748-445C-B1A5-D0E296582A82}">
       <text>
-        <t>[Comentário encadeado]
-Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
-Comentário:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Usar material BOZ0060HU1000 como material alternativo</t>
       </text>
     </comment>
@@ -322,7 +322,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7118" uniqueCount="1497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7119" uniqueCount="1497">
   <si>
     <t>Código
 Bobina Mâe</t>
@@ -5033,7 +5033,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
     <numFmt numFmtId="166" formatCode="mmmm\,\ yyyy;@"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7436,7 +7436,7 @@
                   <c:v>256393.97999999995</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>133836.72333333336</c:v>
+                  <c:v>136436.7233333333</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -7728,7 +7728,7 @@
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>479111.14083333325</c:v>
+                  <c:v>481711.14083333325</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13063,10 +13063,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
-</file>
-
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Eric da Silva Maia" id="{D9E3AE94-B136-43DC-991E-9F5A8D1687A6}" userId="S::eric.maia@delga.com.br::43e774bf-1d7b-4030-aa96-fdc0a837fc3b" providerId="AD"/>
@@ -13411,49 +13407,49 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA437EE-405D-4A43-9EB9-23F1BEB36011}">
   <sheetPr codeName="Folha1"/>
   <dimension ref="A1:AO720"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" customWidth="1"/>
-    <col min="7" max="7" width="28.5546875" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" customWidth="1"/>
-    <col min="9" max="9" width="10.109375" customWidth="1"/>
-    <col min="10" max="10" width="9.5546875" customWidth="1"/>
-    <col min="11" max="11" width="21.44140625" customWidth="1"/>
-    <col min="12" max="12" width="20.44140625" customWidth="1"/>
-    <col min="13" max="13" width="23.5546875" customWidth="1"/>
-    <col min="14" max="14" width="32.44140625" customWidth="1"/>
-    <col min="15" max="15" width="8.5546875" customWidth="1"/>
-    <col min="16" max="16" width="10.44140625" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="12.44140625" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5546875" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="7" max="7" width="28.5703125" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" customWidth="1"/>
+    <col min="9" max="9" width="10.140625" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" customWidth="1"/>
+    <col min="11" max="11" width="21.42578125" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" customWidth="1"/>
+    <col min="13" max="13" width="23.5703125" customWidth="1"/>
+    <col min="14" max="14" width="32.42578125" customWidth="1"/>
+    <col min="15" max="15" width="8.5703125" customWidth="1"/>
+    <col min="16" max="16" width="10.42578125" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="12.42578125" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="11.5703125" customWidth="1"/>
     <col min="19" max="19" width="15" customWidth="1"/>
-    <col min="20" max="20" width="15.5546875" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="16.44140625" hidden="1" customWidth="1"/>
-    <col min="22" max="24" width="15.44140625" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="15.44140625" customWidth="1"/>
-    <col min="26" max="26" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.5703125" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="16.42578125" hidden="1" customWidth="1"/>
+    <col min="22" max="24" width="15.42578125" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="15.42578125" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="13" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.88671875" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="24.109375" customWidth="1"/>
-    <col min="37" max="37" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.88671875" hidden="1" customWidth="1"/>
-    <col min="39" max="39" width="91.109375" customWidth="1"/>
-    <col min="40" max="40" width="28.33203125" style="50" customWidth="1"/>
+    <col min="34" max="34" width="12.85546875" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="24.140625" customWidth="1"/>
+    <col min="37" max="37" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.85546875" hidden="1" customWidth="1"/>
+    <col min="39" max="39" width="91.140625" customWidth="1"/>
+    <col min="40" max="40" width="28.28515625" style="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="151.35" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:40" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:40" ht="151.35" customHeight="1"/>
+    <row r="2" spans="1:40" ht="30.6">
       <c r="A2" s="39" t="s">
         <v>0</v>
       </c>
@@ -13575,7 +13571,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:40" hidden="1">
       <c r="A3" s="22" t="s">
         <v>40</v>
       </c>
@@ -13690,7 +13686,7 @@
       </c>
       <c r="AN3" s="83"/>
     </row>
-    <row r="4" spans="1:40" s="26" customFormat="1" ht="132.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:40" s="26" customFormat="1" ht="132.6" hidden="1">
       <c r="A4" s="22" t="s">
         <v>53</v>
       </c>
@@ -13807,7 +13803,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="5" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A5" s="22" t="s">
         <v>63</v>
       </c>
@@ -13924,7 +13920,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="6" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A6" s="22" t="s">
         <v>70</v>
       </c>
@@ -14033,7 +14029,7 @@
       </c>
       <c r="AN6" s="83"/>
     </row>
-    <row r="7" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A7" s="22" t="s">
         <v>78</v>
       </c>
@@ -14148,7 +14144,7 @@
       </c>
       <c r="AN7" s="83"/>
     </row>
-    <row r="8" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A8" s="22" t="s">
         <v>85</v>
       </c>
@@ -14245,7 +14241,7 @@
       <c r="AM8" s="1"/>
       <c r="AN8" s="83"/>
     </row>
-    <row r="9" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
       <c r="A9" s="22" t="s">
         <v>90</v>
       </c>
@@ -14362,7 +14358,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="10" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A10" s="3" t="s">
         <v>97</v>
       </c>
@@ -14479,7 +14475,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="11" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A11" s="22" t="s">
         <v>103</v>
       </c>
@@ -14592,7 +14588,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="12" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A12" s="22" t="s">
         <v>108</v>
       </c>
@@ -14689,7 +14685,7 @@
       <c r="AM12" s="1"/>
       <c r="AN12" s="83"/>
     </row>
-    <row r="13" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
       <c r="A13" s="22" t="s">
         <v>111</v>
       </c>
@@ -14788,7 +14784,7 @@
       <c r="AM13" s="1"/>
       <c r="AN13" s="83"/>
     </row>
-    <row r="14" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
       <c r="A14" s="22" t="s">
         <v>115</v>
       </c>
@@ -14893,7 +14889,7 @@
       <c r="AM14" s="1"/>
       <c r="AN14" s="83"/>
     </row>
-    <row r="15" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A15" s="22" t="s">
         <v>118</v>
       </c>
@@ -14986,7 +14982,7 @@
       <c r="AM15" s="1"/>
       <c r="AN15" s="83"/>
     </row>
-    <row r="16" spans="1:40" s="26" customFormat="1" ht="30.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:40" s="26" customFormat="1" ht="30.6" hidden="1">
       <c r="A16" s="22" t="s">
         <v>122</v>
       </c>
@@ -15103,7 +15099,7 @@
         <v>46235</v>
       </c>
     </row>
-    <row r="17" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
       <c r="A17" s="22" t="s">
         <v>127</v>
       </c>
@@ -15200,7 +15196,7 @@
       <c r="AM17" s="1"/>
       <c r="AN17" s="83"/>
     </row>
-    <row r="18" spans="1:40" s="26" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:40" s="26" customFormat="1" ht="51" hidden="1">
       <c r="A18" s="22" t="s">
         <v>132</v>
       </c>
@@ -15297,7 +15293,7 @@
       <c r="AM18" s="1"/>
       <c r="AN18" s="83"/>
     </row>
-    <row r="19" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A19" s="22" t="s">
         <v>137</v>
       </c>
@@ -15396,7 +15392,7 @@
       </c>
       <c r="AN19" s="83"/>
     </row>
-    <row r="20" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A20" s="22" t="s">
         <v>142</v>
       </c>
@@ -15493,7 +15489,7 @@
       <c r="AM20" s="1"/>
       <c r="AN20" s="83"/>
     </row>
-    <row r="21" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A21" s="22" t="s">
         <v>147</v>
       </c>
@@ -15608,7 +15604,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="22" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A22" s="22" t="s">
         <v>154</v>
       </c>
@@ -15701,7 +15697,7 @@
       <c r="AM22" s="1"/>
       <c r="AN22" s="83"/>
     </row>
-    <row r="23" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A23" s="22" t="s">
         <v>156</v>
       </c>
@@ -15816,7 +15812,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="24" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A24" s="22" t="s">
         <v>160</v>
       </c>
@@ -15909,7 +15905,7 @@
       <c r="AM24" s="1"/>
       <c r="AN24" s="83"/>
     </row>
-    <row r="25" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A25" s="22" t="s">
         <v>161</v>
       </c>
@@ -16002,7 +15998,7 @@
       <c r="AM25" s="1"/>
       <c r="AN25" s="83"/>
     </row>
-    <row r="26" spans="1:40" s="26" customFormat="1" ht="30.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:40" s="26" customFormat="1" ht="30.6" hidden="1">
       <c r="A26" s="22" t="s">
         <v>163</v>
       </c>
@@ -16097,7 +16093,7 @@
       <c r="AM26" s="1"/>
       <c r="AN26" s="83"/>
     </row>
-    <row r="27" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A27" s="22" t="s">
         <v>166</v>
       </c>
@@ -16190,7 +16186,7 @@
       <c r="AM27" s="1"/>
       <c r="AN27" s="83"/>
     </row>
-    <row r="28" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A28" s="22" t="s">
         <v>169</v>
       </c>
@@ -16285,7 +16281,7 @@
       <c r="AM28" s="62"/>
       <c r="AN28" s="83"/>
     </row>
-    <row r="29" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A29" s="22" t="s">
         <v>172</v>
       </c>
@@ -16380,7 +16376,7 @@
       <c r="AM29" s="1"/>
       <c r="AN29" s="83"/>
     </row>
-    <row r="30" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A30" s="22" t="s">
         <v>175</v>
       </c>
@@ -16473,7 +16469,7 @@
       <c r="AM30" s="1"/>
       <c r="AN30" s="83"/>
     </row>
-    <row r="31" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A31" s="22" t="s">
         <v>179</v>
       </c>
@@ -16560,7 +16556,7 @@
       <c r="AM31" s="1"/>
       <c r="AN31" s="83"/>
     </row>
-    <row r="32" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A32" s="22" t="s">
         <v>181</v>
       </c>
@@ -16677,7 +16673,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="33" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A33" s="22" t="s">
         <v>184</v>
       </c>
@@ -16792,7 +16788,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="34" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A34" s="22" t="s">
         <v>190</v>
       </c>
@@ -16885,7 +16881,7 @@
       <c r="AM34" s="1"/>
       <c r="AN34" s="83"/>
     </row>
-    <row r="35" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A35" s="22" t="s">
         <v>194</v>
       </c>
@@ -17002,7 +16998,7 @@
         <v>46235</v>
       </c>
     </row>
-    <row r="36" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A36" s="22" t="s">
         <v>200</v>
       </c>
@@ -17097,7 +17093,7 @@
       <c r="AM36" s="1"/>
       <c r="AN36" s="83"/>
     </row>
-    <row r="37" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A37" s="22" t="s">
         <v>201</v>
       </c>
@@ -17184,7 +17180,7 @@
       <c r="AM37" s="1"/>
       <c r="AN37" s="83"/>
     </row>
-    <row r="38" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A38" s="22" t="s">
         <v>204</v>
       </c>
@@ -17285,7 +17281,7 @@
       <c r="AM38" s="1"/>
       <c r="AN38" s="83"/>
     </row>
-    <row r="39" spans="1:40" s="26" customFormat="1" ht="71.400000000000006" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:40" s="26" customFormat="1" ht="71.45" hidden="1">
       <c r="A39" s="22" t="s">
         <v>207</v>
       </c>
@@ -17404,7 +17400,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="40" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A40" s="22" t="s">
         <v>211</v>
       </c>
@@ -17497,7 +17493,7 @@
       <c r="AM40" s="1"/>
       <c r="AN40" s="83"/>
     </row>
-    <row r="41" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A41" s="22" t="s">
         <v>214</v>
       </c>
@@ -17590,7 +17586,7 @@
       <c r="AM41" s="1"/>
       <c r="AN41" s="83"/>
     </row>
-    <row r="42" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A42" s="22" t="s">
         <v>217</v>
       </c>
@@ -17683,7 +17679,7 @@
       <c r="AM42" s="1"/>
       <c r="AN42" s="83"/>
     </row>
-    <row r="43" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A43" s="22" t="s">
         <v>221</v>
       </c>
@@ -17776,7 +17772,7 @@
       <c r="AM43" s="1"/>
       <c r="AN43" s="83"/>
     </row>
-    <row r="44" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A44" s="22" t="s">
         <v>225</v>
       </c>
@@ -17893,7 +17889,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="45" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A45" s="22" t="s">
         <v>230</v>
       </c>
@@ -18006,7 +18002,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="46" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A46" s="22" t="s">
         <v>234</v>
       </c>
@@ -18099,7 +18095,7 @@
       <c r="AM46" s="1"/>
       <c r="AN46" s="83"/>
     </row>
-    <row r="47" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A47" s="22" t="s">
         <v>241</v>
       </c>
@@ -18192,7 +18188,7 @@
       <c r="AM47" s="1"/>
       <c r="AN47" s="83"/>
     </row>
-    <row r="48" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A48" s="22" t="s">
         <v>244</v>
       </c>
@@ -18285,7 +18281,7 @@
       <c r="AM48" s="1"/>
       <c r="AN48" s="83"/>
     </row>
-    <row r="49" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A49" s="22" t="s">
         <v>246</v>
       </c>
@@ -18378,7 +18374,7 @@
       <c r="AM49" s="1"/>
       <c r="AN49" s="83"/>
     </row>
-    <row r="50" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A50" s="22" t="s">
         <v>248</v>
       </c>
@@ -18471,7 +18467,7 @@
       <c r="AM50" s="1"/>
       <c r="AN50" s="83"/>
     </row>
-    <row r="51" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A51" s="22" t="s">
         <v>251</v>
       </c>
@@ -18564,7 +18560,7 @@
       <c r="AM51" s="1"/>
       <c r="AN51" s="83"/>
     </row>
-    <row r="52" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A52" s="22" t="s">
         <v>254</v>
       </c>
@@ -18657,7 +18653,7 @@
       <c r="AM52" s="1"/>
       <c r="AN52" s="83"/>
     </row>
-    <row r="53" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A53" s="22" t="s">
         <v>257</v>
       </c>
@@ -18750,7 +18746,7 @@
       <c r="AM53" s="1"/>
       <c r="AN53" s="83"/>
     </row>
-    <row r="54" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A54" s="22" t="s">
         <v>259</v>
       </c>
@@ -18843,7 +18839,7 @@
       <c r="AM54" s="1"/>
       <c r="AN54" s="83"/>
     </row>
-    <row r="55" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A55" s="22" t="s">
         <v>263</v>
       </c>
@@ -18936,7 +18932,7 @@
       <c r="AM55" s="1"/>
       <c r="AN55" s="83"/>
     </row>
-    <row r="56" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A56" s="22" t="s">
         <v>266</v>
       </c>
@@ -19053,7 +19049,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="57" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A57" s="22" t="s">
         <v>270</v>
       </c>
@@ -19146,7 +19142,7 @@
       <c r="AM57" s="1"/>
       <c r="AN57" s="83"/>
     </row>
-    <row r="58" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A58" s="22" t="s">
         <v>271</v>
       </c>
@@ -19239,7 +19235,7 @@
       <c r="AM58" s="1"/>
       <c r="AN58" s="83"/>
     </row>
-    <row r="59" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A59" s="22" t="s">
         <v>273</v>
       </c>
@@ -19332,7 +19328,7 @@
       <c r="AM59" s="1"/>
       <c r="AN59" s="83"/>
     </row>
-    <row r="60" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
       <c r="A60" s="22" t="s">
         <v>275</v>
       </c>
@@ -19443,7 +19439,7 @@
       </c>
       <c r="AN60" s="83"/>
     </row>
-    <row r="61" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A61" s="22" t="s">
         <v>281</v>
       </c>
@@ -19556,7 +19552,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="62" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A62" s="22" t="s">
         <v>287</v>
       </c>
@@ -19649,7 +19645,7 @@
       <c r="AM62" s="1"/>
       <c r="AN62" s="83"/>
     </row>
-    <row r="63" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A63" s="22" t="s">
         <v>289</v>
       </c>
@@ -19742,7 +19738,7 @@
       <c r="AM63" s="1"/>
       <c r="AN63" s="83"/>
     </row>
-    <row r="64" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A64" s="22" t="s">
         <v>292</v>
       </c>
@@ -19835,7 +19831,7 @@
       <c r="AM64" s="1"/>
       <c r="AN64" s="83"/>
     </row>
-    <row r="65" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A65" s="22" t="s">
         <v>294</v>
       </c>
@@ -19930,7 +19926,7 @@
       <c r="AM65" s="1"/>
       <c r="AN65" s="83"/>
     </row>
-    <row r="66" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A66" s="22" t="s">
         <v>296</v>
       </c>
@@ -20025,7 +20021,7 @@
       <c r="AM66" s="1"/>
       <c r="AN66" s="83"/>
     </row>
-    <row r="67" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A67" s="22" t="s">
         <v>298</v>
       </c>
@@ -20114,7 +20110,7 @@
       <c r="AM67" s="1"/>
       <c r="AN67" s="83"/>
     </row>
-    <row r="68" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A68" s="22" t="s">
         <v>299</v>
       </c>
@@ -20207,7 +20203,7 @@
       <c r="AM68" s="1"/>
       <c r="AN68" s="83"/>
     </row>
-    <row r="69" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A69" s="22" t="s">
         <v>301</v>
       </c>
@@ -20302,7 +20298,7 @@
       <c r="AM69" s="1"/>
       <c r="AN69" s="83"/>
     </row>
-    <row r="70" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A70" s="22" t="s">
         <v>304</v>
       </c>
@@ -20395,7 +20391,7 @@
       <c r="AM70" s="1"/>
       <c r="AN70" s="83"/>
     </row>
-    <row r="71" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A71" s="22" t="s">
         <v>306</v>
       </c>
@@ -20488,7 +20484,7 @@
       <c r="AM71" s="1"/>
       <c r="AN71" s="83"/>
     </row>
-    <row r="72" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A72" s="22" t="s">
         <v>309</v>
       </c>
@@ -20583,7 +20579,7 @@
       <c r="AM72" s="1"/>
       <c r="AN72" s="83"/>
     </row>
-    <row r="73" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A73" s="22" t="s">
         <v>312</v>
       </c>
@@ -20676,7 +20672,7 @@
       <c r="AM73" s="1"/>
       <c r="AN73" s="83"/>
     </row>
-    <row r="74" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A74" s="22" t="s">
         <v>314</v>
       </c>
@@ -20769,7 +20765,7 @@
       <c r="AM74" s="1"/>
       <c r="AN74" s="83"/>
     </row>
-    <row r="75" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A75" s="22" t="s">
         <v>316</v>
       </c>
@@ -20860,7 +20856,7 @@
       <c r="AM75" s="1"/>
       <c r="AN75" s="83"/>
     </row>
-    <row r="76" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A76" s="22" t="s">
         <v>319</v>
       </c>
@@ -20953,7 +20949,7 @@
       <c r="AM76" s="1"/>
       <c r="AN76" s="83"/>
     </row>
-    <row r="77" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A77" s="22" t="s">
         <v>323</v>
       </c>
@@ -21044,7 +21040,7 @@
       <c r="AM77" s="1"/>
       <c r="AN77" s="83"/>
     </row>
-    <row r="78" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A78" s="22" t="s">
         <v>325</v>
       </c>
@@ -21157,7 +21153,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="79" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A79" s="22" t="s">
         <v>329</v>
       </c>
@@ -21250,7 +21246,7 @@
       <c r="AM79" s="1"/>
       <c r="AN79" s="83"/>
     </row>
-    <row r="80" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A80" s="22" t="s">
         <v>332</v>
       </c>
@@ -21363,7 +21359,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="81" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A81" s="22" t="s">
         <v>336</v>
       </c>
@@ -21458,7 +21454,7 @@
       <c r="AM81" s="1"/>
       <c r="AN81" s="83"/>
     </row>
-    <row r="82" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A82" s="22" t="s">
         <v>338</v>
       </c>
@@ -21551,7 +21547,7 @@
       <c r="AM82" s="1"/>
       <c r="AN82" s="83"/>
     </row>
-    <row r="83" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A83" s="22" t="s">
         <v>340</v>
       </c>
@@ -21644,7 +21640,7 @@
       <c r="AM83" s="1"/>
       <c r="AN83" s="83"/>
     </row>
-    <row r="84" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A84" s="22" t="s">
         <v>342</v>
       </c>
@@ -21739,7 +21735,7 @@
       <c r="AM84" s="1"/>
       <c r="AN84" s="83"/>
     </row>
-    <row r="85" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A85" s="22" t="s">
         <v>345</v>
       </c>
@@ -21832,7 +21828,7 @@
       <c r="AM85" s="1"/>
       <c r="AN85" s="83"/>
     </row>
-    <row r="86" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A86" s="22" t="s">
         <v>347</v>
       </c>
@@ -21921,7 +21917,7 @@
       <c r="AM86" s="1"/>
       <c r="AN86" s="83"/>
     </row>
-    <row r="87" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A87" s="22" t="s">
         <v>352</v>
       </c>
@@ -22014,7 +22010,7 @@
       <c r="AM87" s="1"/>
       <c r="AN87" s="83"/>
     </row>
-    <row r="88" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A88" s="22" t="s">
         <v>354</v>
       </c>
@@ -22109,7 +22105,7 @@
       <c r="AM88" s="1"/>
       <c r="AN88" s="83"/>
     </row>
-    <row r="89" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A89" s="22" t="s">
         <v>359</v>
       </c>
@@ -22202,7 +22198,7 @@
       <c r="AM89" s="1"/>
       <c r="AN89" s="83"/>
     </row>
-    <row r="90" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A90" s="22" t="s">
         <v>362</v>
       </c>
@@ -22295,7 +22291,7 @@
       <c r="AM90" s="1"/>
       <c r="AN90" s="83"/>
     </row>
-    <row r="91" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A91" s="22" t="s">
         <v>364</v>
       </c>
@@ -22388,7 +22384,7 @@
       <c r="AM91" s="1"/>
       <c r="AN91" s="83"/>
     </row>
-    <row r="92" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A92" s="22" t="s">
         <v>367</v>
       </c>
@@ -22481,7 +22477,7 @@
       <c r="AM92" s="1"/>
       <c r="AN92" s="83"/>
     </row>
-    <row r="93" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A93" s="22" t="s">
         <v>370</v>
       </c>
@@ -22572,7 +22568,7 @@
       <c r="AM93" s="1"/>
       <c r="AN93" s="83"/>
     </row>
-    <row r="94" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A94" s="22" t="s">
         <v>372</v>
       </c>
@@ -22665,7 +22661,7 @@
       <c r="AM94" s="1"/>
       <c r="AN94" s="83"/>
     </row>
-    <row r="95" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A95" s="15" t="s">
         <v>375</v>
       </c>
@@ -22758,7 +22754,7 @@
       <c r="AM95" s="1"/>
       <c r="AN95" s="83"/>
     </row>
-    <row r="96" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A96" s="22" t="s">
         <v>378</v>
       </c>
@@ -22871,7 +22867,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="97" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A97" s="22" t="s">
         <v>381</v>
       </c>
@@ -22958,7 +22954,7 @@
       <c r="AM97" s="1"/>
       <c r="AN97" s="83"/>
     </row>
-    <row r="98" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A98" s="3" t="s">
         <v>382</v>
       </c>
@@ -23053,7 +23049,7 @@
       <c r="AM98" s="1"/>
       <c r="AN98" s="83"/>
     </row>
-    <row r="99" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A99" s="22" t="s">
         <v>386</v>
       </c>
@@ -23148,7 +23144,7 @@
       <c r="AM99" s="1"/>
       <c r="AN99" s="83"/>
     </row>
-    <row r="100" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A100" s="22" t="s">
         <v>388</v>
       </c>
@@ -23241,7 +23237,7 @@
       <c r="AM100" s="1"/>
       <c r="AN100" s="83"/>
     </row>
-    <row r="101" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A101" s="22" t="s">
         <v>391</v>
       </c>
@@ -23334,7 +23330,7 @@
       <c r="AM101" s="1"/>
       <c r="AN101" s="83"/>
     </row>
-    <row r="102" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A102" s="22" t="s">
         <v>394</v>
       </c>
@@ -23423,7 +23419,7 @@
       <c r="AM102" s="1"/>
       <c r="AN102" s="83"/>
     </row>
-    <row r="103" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A103" s="22" t="s">
         <v>397</v>
       </c>
@@ -23516,7 +23512,7 @@
       <c r="AM103" s="1"/>
       <c r="AN103" s="83"/>
     </row>
-    <row r="104" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A104" s="22" t="s">
         <v>398</v>
       </c>
@@ -23611,7 +23607,7 @@
       <c r="AM104" s="1"/>
       <c r="AN104" s="83"/>
     </row>
-    <row r="105" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A105" s="22" t="s">
         <v>400</v>
       </c>
@@ -23698,7 +23694,7 @@
       <c r="AM105" s="1"/>
       <c r="AN105" s="83"/>
     </row>
-    <row r="106" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A106" s="22" t="s">
         <v>402</v>
       </c>
@@ -23791,7 +23787,7 @@
       <c r="AM106" s="1"/>
       <c r="AN106" s="83"/>
     </row>
-    <row r="107" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A107" s="15" t="s">
         <v>404</v>
       </c>
@@ -23878,7 +23874,7 @@
       <c r="AM107" s="1"/>
       <c r="AN107" s="83"/>
     </row>
-    <row r="108" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A108" s="22" t="s">
         <v>406</v>
       </c>
@@ -23969,7 +23965,7 @@
       <c r="AM108" s="1"/>
       <c r="AN108" s="83"/>
     </row>
-    <row r="109" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A109" s="22" t="s">
         <v>408</v>
       </c>
@@ -24062,7 +24058,7 @@
       <c r="AM109" s="1"/>
       <c r="AN109" s="83"/>
     </row>
-    <row r="110" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A110" s="22" t="s">
         <v>410</v>
       </c>
@@ -24177,7 +24173,7 @@
       </c>
       <c r="AN110" s="83"/>
     </row>
-    <row r="111" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A111" s="22" t="s">
         <v>414</v>
       </c>
@@ -24272,7 +24268,7 @@
       <c r="AM111" s="1"/>
       <c r="AN111" s="83"/>
     </row>
-    <row r="112" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A112" s="22" t="s">
         <v>416</v>
       </c>
@@ -24387,7 +24383,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="113" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A113" s="22" t="s">
         <v>419</v>
       </c>
@@ -24476,7 +24472,7 @@
       <c r="AM113" s="1"/>
       <c r="AN113" s="83"/>
     </row>
-    <row r="114" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A114" s="22" t="s">
         <v>423</v>
       </c>
@@ -24563,7 +24559,7 @@
       <c r="AM114" s="1"/>
       <c r="AN114" s="83"/>
     </row>
-    <row r="115" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A115" s="3" t="s">
         <v>424</v>
       </c>
@@ -24656,7 +24652,7 @@
       <c r="AM115" s="1"/>
       <c r="AN115" s="83"/>
     </row>
-    <row r="116" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A116" s="22" t="s">
         <v>426</v>
       </c>
@@ -24741,7 +24737,7 @@
       <c r="AM116" s="1"/>
       <c r="AN116" s="83"/>
     </row>
-    <row r="117" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A117" s="22" t="s">
         <v>428</v>
       </c>
@@ -24836,7 +24832,7 @@
       <c r="AM117" s="1"/>
       <c r="AN117" s="83"/>
     </row>
-    <row r="118" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A118" s="22" t="s">
         <v>430</v>
       </c>
@@ -24929,7 +24925,7 @@
       <c r="AM118" s="1"/>
       <c r="AN118" s="83"/>
     </row>
-    <row r="119" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A119" s="22" t="s">
         <v>432</v>
       </c>
@@ -25020,7 +25016,7 @@
       <c r="AM119" s="1"/>
       <c r="AN119" s="83"/>
     </row>
-    <row r="120" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A120" s="15" t="s">
         <v>434</v>
       </c>
@@ -25105,7 +25101,7 @@
       <c r="AM120" s="1"/>
       <c r="AN120" s="83"/>
     </row>
-    <row r="121" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A121" s="22" t="s">
         <v>435</v>
       </c>
@@ -25196,7 +25192,7 @@
       <c r="AM121" s="1"/>
       <c r="AN121" s="83"/>
     </row>
-    <row r="122" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A122" s="15" t="s">
         <v>437</v>
       </c>
@@ -25283,7 +25279,7 @@
       <c r="AM122" s="1"/>
       <c r="AN122" s="83"/>
     </row>
-    <row r="123" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A123" s="22" t="s">
         <v>438</v>
       </c>
@@ -25394,7 +25390,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="124" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A124" s="22" t="s">
         <v>440</v>
       </c>
@@ -25479,7 +25475,7 @@
       <c r="AM124" s="1"/>
       <c r="AN124" s="83"/>
     </row>
-    <row r="125" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A125" s="22" t="s">
         <v>441</v>
       </c>
@@ -25574,7 +25570,7 @@
       <c r="AM125" s="1"/>
       <c r="AN125" s="83"/>
     </row>
-    <row r="126" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A126" s="22" t="s">
         <v>443</v>
       </c>
@@ -25663,7 +25659,7 @@
       <c r="AM126" s="1"/>
       <c r="AN126" s="83"/>
     </row>
-    <row r="127" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A127" s="22" t="s">
         <v>446</v>
       </c>
@@ -25756,7 +25752,7 @@
       <c r="AM127" s="1"/>
       <c r="AN127" s="83"/>
     </row>
-    <row r="128" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A128" s="22" t="s">
         <v>448</v>
       </c>
@@ -25845,7 +25841,7 @@
       <c r="AM128" s="1"/>
       <c r="AN128" s="83"/>
     </row>
-    <row r="129" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A129" s="15" t="s">
         <v>451</v>
       </c>
@@ -25938,7 +25934,7 @@
       <c r="AM129" s="1"/>
       <c r="AN129" s="83"/>
     </row>
-    <row r="130" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A130" s="22" t="s">
         <v>453</v>
       </c>
@@ -26021,7 +26017,7 @@
       <c r="AM130" s="1"/>
       <c r="AN130" s="83"/>
     </row>
-    <row r="131" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A131" s="22" t="s">
         <v>454</v>
       </c>
@@ -26104,7 +26100,7 @@
       <c r="AM131" s="1"/>
       <c r="AN131" s="83"/>
     </row>
-    <row r="132" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A132" s="22" t="s">
         <v>455</v>
       </c>
@@ -26197,7 +26193,7 @@
       <c r="AM132" s="1"/>
       <c r="AN132" s="83"/>
     </row>
-    <row r="133" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A133" s="22" t="s">
         <v>457</v>
       </c>
@@ -26292,7 +26288,7 @@
       <c r="AM133" s="1"/>
       <c r="AN133" s="83"/>
     </row>
-    <row r="134" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A134" s="22" t="s">
         <v>459</v>
       </c>
@@ -26383,7 +26379,7 @@
       <c r="AM134" s="1"/>
       <c r="AN134" s="83"/>
     </row>
-    <row r="135" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A135" s="15" t="s">
         <v>461</v>
       </c>
@@ -26472,7 +26468,7 @@
       <c r="AM135" s="1"/>
       <c r="AN135" s="83"/>
     </row>
-    <row r="136" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A136" s="22" t="s">
         <v>463</v>
       </c>
@@ -26563,7 +26559,7 @@
       <c r="AM136" s="1"/>
       <c r="AN136" s="83"/>
     </row>
-    <row r="137" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A137" s="15" t="s">
         <v>465</v>
       </c>
@@ -26648,7 +26644,7 @@
       <c r="AM137" s="1"/>
       <c r="AN137" s="83"/>
     </row>
-    <row r="138" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A138" s="22" t="s">
         <v>467</v>
       </c>
@@ -26739,7 +26735,7 @@
       <c r="AM138" s="1"/>
       <c r="AN138" s="83"/>
     </row>
-    <row r="139" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A139" s="15" t="s">
         <v>468</v>
       </c>
@@ -26826,7 +26822,7 @@
       <c r="AM139" s="1"/>
       <c r="AN139" s="83"/>
     </row>
-    <row r="140" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A140" s="22" t="s">
         <v>471</v>
       </c>
@@ -26917,7 +26913,7 @@
       <c r="AM140" s="1"/>
       <c r="AN140" s="83"/>
     </row>
-    <row r="141" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A141" s="22" t="s">
         <v>474</v>
       </c>
@@ -27002,7 +26998,7 @@
       <c r="AM141" s="1"/>
       <c r="AN141" s="83"/>
     </row>
-    <row r="142" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A142" s="15" t="s">
         <v>475</v>
       </c>
@@ -27093,7 +27089,7 @@
       <c r="AM142" s="1"/>
       <c r="AN142" s="83"/>
     </row>
-    <row r="143" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A143" s="15" t="s">
         <v>477</v>
       </c>
@@ -27180,7 +27176,7 @@
       <c r="AM143" s="1"/>
       <c r="AN143" s="83"/>
     </row>
-    <row r="144" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A144" s="15" t="s">
         <v>480</v>
       </c>
@@ -27275,7 +27271,7 @@
       <c r="AM144" s="1"/>
       <c r="AN144" s="83"/>
     </row>
-    <row r="145" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A145" s="15" t="s">
         <v>482</v>
       </c>
@@ -27362,7 +27358,7 @@
       <c r="AM145" s="1"/>
       <c r="AN145" s="83"/>
     </row>
-    <row r="146" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A146" s="15" t="s">
         <v>483</v>
       </c>
@@ -27447,7 +27443,7 @@
       <c r="AM146" s="1"/>
       <c r="AN146" s="83"/>
     </row>
-    <row r="147" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A147" s="15" t="s">
         <v>484</v>
       </c>
@@ -27528,7 +27524,7 @@
       <c r="AM147" s="1"/>
       <c r="AN147" s="83"/>
     </row>
-    <row r="148" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A148" s="15" t="s">
         <v>485</v>
       </c>
@@ -27621,7 +27617,7 @@
       <c r="AM148" s="1"/>
       <c r="AN148" s="83"/>
     </row>
-    <row r="149" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A149" s="15" t="s">
         <v>487</v>
       </c>
@@ -27712,7 +27708,7 @@
       <c r="AM149" s="1"/>
       <c r="AN149" s="83"/>
     </row>
-    <row r="150" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A150" s="15" t="s">
         <v>489</v>
       </c>
@@ -27793,7 +27789,7 @@
       <c r="AM150" s="1"/>
       <c r="AN150" s="83"/>
     </row>
-    <row r="151" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A151" s="15" t="s">
         <v>490</v>
       </c>
@@ -27880,7 +27876,7 @@
       <c r="AM151" s="1"/>
       <c r="AN151" s="83"/>
     </row>
-    <row r="152" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A152" s="15" t="s">
         <v>492</v>
       </c>
@@ -27971,7 +27967,7 @@
       <c r="AM152" s="1"/>
       <c r="AN152" s="83"/>
     </row>
-    <row r="153" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A153" s="15" t="s">
         <v>495</v>
       </c>
@@ -28058,7 +28054,7 @@
       <c r="AM153" s="1"/>
       <c r="AN153" s="83"/>
     </row>
-    <row r="154" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A154" s="15" t="s">
         <v>497</v>
       </c>
@@ -28145,7 +28141,7 @@
       <c r="AM154" s="1"/>
       <c r="AN154" s="83"/>
     </row>
-    <row r="155" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A155" s="15" t="s">
         <v>499</v>
       </c>
@@ -28232,7 +28228,7 @@
       <c r="AM155" s="1"/>
       <c r="AN155" s="83"/>
     </row>
-    <row r="156" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A156" s="15" t="s">
         <v>501</v>
       </c>
@@ -28321,7 +28317,7 @@
       <c r="AM156" s="1"/>
       <c r="AN156" s="83"/>
     </row>
-    <row r="157" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A157" s="15" t="s">
         <v>504</v>
       </c>
@@ -28408,7 +28404,7 @@
       <c r="AM157" s="1"/>
       <c r="AN157" s="83"/>
     </row>
-    <row r="158" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A158" s="15" t="s">
         <v>506</v>
       </c>
@@ -28495,7 +28491,7 @@
       <c r="AM158" s="1"/>
       <c r="AN158" s="83"/>
     </row>
-    <row r="159" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A159" s="15" t="s">
         <v>508</v>
       </c>
@@ -28584,7 +28580,7 @@
       <c r="AM159" s="1"/>
       <c r="AN159" s="83"/>
     </row>
-    <row r="160" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A160" s="15" t="s">
         <v>510</v>
       </c>
@@ -28671,7 +28667,7 @@
       <c r="AM160" s="1"/>
       <c r="AN160" s="83"/>
     </row>
-    <row r="161" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A161" s="15" t="s">
         <v>512</v>
       </c>
@@ -28758,7 +28754,7 @@
       <c r="AM161" s="1"/>
       <c r="AN161" s="83"/>
     </row>
-    <row r="162" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A162" s="15" t="s">
         <v>514</v>
       </c>
@@ -28849,7 +28845,7 @@
       <c r="AM162" s="1"/>
       <c r="AN162" s="83"/>
     </row>
-    <row r="163" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A163" s="15" t="s">
         <v>517</v>
       </c>
@@ -28936,7 +28932,7 @@
       <c r="AM163" s="1"/>
       <c r="AN163" s="83"/>
     </row>
-    <row r="164" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A164" s="15" t="s">
         <v>519</v>
       </c>
@@ -29023,7 +29019,7 @@
       <c r="AM164" s="1"/>
       <c r="AN164" s="83"/>
     </row>
-    <row r="165" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A165" s="15" t="s">
         <v>521</v>
       </c>
@@ -29112,7 +29108,7 @@
       <c r="AM165" s="1"/>
       <c r="AN165" s="83"/>
     </row>
-    <row r="166" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A166" s="15" t="s">
         <v>523</v>
       </c>
@@ -29201,7 +29197,7 @@
       <c r="AM166" s="1"/>
       <c r="AN166" s="83"/>
     </row>
-    <row r="167" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A167" s="15" t="s">
         <v>525</v>
       </c>
@@ -29290,7 +29286,7 @@
       <c r="AM167" s="1"/>
       <c r="AN167" s="83"/>
     </row>
-    <row r="168" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A168" s="15" t="s">
         <v>527</v>
       </c>
@@ -29379,7 +29375,7 @@
       <c r="AM168" s="1"/>
       <c r="AN168" s="83"/>
     </row>
-    <row r="169" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A169" s="15" t="s">
         <v>529</v>
       </c>
@@ -29466,7 +29462,7 @@
       <c r="AM169" s="1"/>
       <c r="AN169" s="83"/>
     </row>
-    <row r="170" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A170" s="15" t="s">
         <v>531</v>
       </c>
@@ -29555,7 +29551,7 @@
       <c r="AM170" s="1"/>
       <c r="AN170" s="83"/>
     </row>
-    <row r="171" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A171" s="15" t="s">
         <v>533</v>
       </c>
@@ -29644,7 +29640,7 @@
       <c r="AM171" s="1"/>
       <c r="AN171" s="83"/>
     </row>
-    <row r="172" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A172" s="15" t="s">
         <v>535</v>
       </c>
@@ -29731,7 +29727,7 @@
       <c r="AM172" s="1"/>
       <c r="AN172" s="83"/>
     </row>
-    <row r="173" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A173" s="15" t="s">
         <v>537</v>
       </c>
@@ -29820,7 +29816,7 @@
       <c r="AM173" s="1"/>
       <c r="AN173" s="83"/>
     </row>
-    <row r="174" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A174" s="15" t="s">
         <v>539</v>
       </c>
@@ -29909,7 +29905,7 @@
       <c r="AM174" s="1"/>
       <c r="AN174" s="83"/>
     </row>
-    <row r="175" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A175" s="15" t="s">
         <v>541</v>
       </c>
@@ -29982,7 +29978,7 @@
       <c r="AM175" s="1"/>
       <c r="AN175" s="83"/>
     </row>
-    <row r="176" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A176" s="15" t="s">
         <v>542</v>
       </c>
@@ -30069,7 +30065,7 @@
       <c r="AM176" s="1"/>
       <c r="AN176" s="83"/>
     </row>
-    <row r="177" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A177" s="15" t="s">
         <v>545</v>
       </c>
@@ -30154,7 +30150,7 @@
       <c r="AM177" s="1"/>
       <c r="AN177" s="83"/>
     </row>
-    <row r="178" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A178" s="15" t="s">
         <v>547</v>
       </c>
@@ -30245,7 +30241,7 @@
       <c r="AM178" s="1"/>
       <c r="AN178" s="83"/>
     </row>
-    <row r="179" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A179" s="15" t="s">
         <v>548</v>
       </c>
@@ -30332,7 +30328,7 @@
       <c r="AM179" s="1"/>
       <c r="AN179" s="83"/>
     </row>
-    <row r="180" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A180" s="15" t="s">
         <v>552</v>
       </c>
@@ -30447,7 +30443,7 @@
         <v>46204</v>
       </c>
     </row>
-    <row r="181" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A181" s="15" t="s">
         <v>557</v>
       </c>
@@ -30562,7 +30558,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="182" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A182" s="15" t="s">
         <v>562</v>
       </c>
@@ -30653,7 +30649,7 @@
       <c r="AM182" s="1"/>
       <c r="AN182" s="83"/>
     </row>
-    <row r="183" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A183" s="15" t="s">
         <v>564</v>
       </c>
@@ -30742,7 +30738,7 @@
       <c r="AM183" s="1"/>
       <c r="AN183" s="83"/>
     </row>
-    <row r="184" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A184" s="15" t="s">
         <v>565</v>
       </c>
@@ -30831,7 +30827,7 @@
       <c r="AM184" s="1"/>
       <c r="AN184" s="83"/>
     </row>
-    <row r="185" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A185" s="15" t="s">
         <v>567</v>
       </c>
@@ -30918,7 +30914,7 @@
       <c r="AM185" s="1"/>
       <c r="AN185" s="83"/>
     </row>
-    <row r="186" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A186" s="15" t="s">
         <v>570</v>
       </c>
@@ -31005,7 +31001,7 @@
       <c r="AM186" s="1"/>
       <c r="AN186" s="83"/>
     </row>
-    <row r="187" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A187" s="15" t="s">
         <v>572</v>
       </c>
@@ -31092,7 +31088,7 @@
       <c r="AM187" s="1"/>
       <c r="AN187" s="83"/>
     </row>
-    <row r="188" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A188" s="15" t="s">
         <v>575</v>
       </c>
@@ -31179,7 +31175,7 @@
       <c r="AM188" s="1"/>
       <c r="AN188" s="83"/>
     </row>
-    <row r="189" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A189" s="15" t="s">
         <v>578</v>
       </c>
@@ -31266,7 +31262,7 @@
       <c r="AM189" s="1"/>
       <c r="AN189" s="83"/>
     </row>
-    <row r="190" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A190" s="15" t="s">
         <v>580</v>
       </c>
@@ -31353,7 +31349,7 @@
       <c r="AM190" s="1"/>
       <c r="AN190" s="83"/>
     </row>
-    <row r="191" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A191" s="15" t="s">
         <v>582</v>
       </c>
@@ -31434,7 +31430,7 @@
       <c r="AM191" s="1"/>
       <c r="AN191" s="83"/>
     </row>
-    <row r="192" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A192" s="15" t="s">
         <v>584</v>
       </c>
@@ -31521,7 +31517,7 @@
       <c r="AM192" s="1"/>
       <c r="AN192" s="83"/>
     </row>
-    <row r="193" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A193" s="15" t="s">
         <v>586</v>
       </c>
@@ -31610,7 +31606,7 @@
       <c r="AM193" s="1"/>
       <c r="AN193" s="83"/>
     </row>
-    <row r="194" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A194" s="15" t="s">
         <v>589</v>
       </c>
@@ -31697,7 +31693,7 @@
       <c r="AM194" s="1"/>
       <c r="AN194" s="83"/>
     </row>
-    <row r="195" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A195" s="15" t="s">
         <v>592</v>
       </c>
@@ -31784,7 +31780,7 @@
       <c r="AM195" s="1"/>
       <c r="AN195" s="83"/>
     </row>
-    <row r="196" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A196" s="15" t="s">
         <v>595</v>
       </c>
@@ -31873,7 +31869,7 @@
       <c r="AM196" s="1"/>
       <c r="AN196" s="83"/>
     </row>
-    <row r="197" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A197" s="15" t="s">
         <v>599</v>
       </c>
@@ -31962,7 +31958,7 @@
       <c r="AM197" s="1"/>
       <c r="AN197" s="83"/>
     </row>
-    <row r="198" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A198" s="15" t="s">
         <v>601</v>
       </c>
@@ -32051,7 +32047,7 @@
       <c r="AM198" s="1"/>
       <c r="AN198" s="83"/>
     </row>
-    <row r="199" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A199" s="15" t="s">
         <v>603</v>
       </c>
@@ -32138,7 +32134,7 @@
       <c r="AM199" s="1"/>
       <c r="AN199" s="83"/>
     </row>
-    <row r="200" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A200" s="15" t="s">
         <v>605</v>
       </c>
@@ -32225,7 +32221,7 @@
       <c r="AM200" s="1"/>
       <c r="AN200" s="83"/>
     </row>
-    <row r="201" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A201" s="15" t="s">
         <v>607</v>
       </c>
@@ -32312,7 +32308,7 @@
       <c r="AM201" s="1"/>
       <c r="AN201" s="83"/>
     </row>
-    <row r="202" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A202" s="15" t="s">
         <v>610</v>
       </c>
@@ -32403,7 +32399,7 @@
       <c r="AM202" s="1"/>
       <c r="AN202" s="83"/>
     </row>
-    <row r="203" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A203" s="15" t="s">
         <v>611</v>
       </c>
@@ -32490,7 +32486,7 @@
       <c r="AM203" s="1"/>
       <c r="AN203" s="83"/>
     </row>
-    <row r="204" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A204" s="15" t="s">
         <v>612</v>
       </c>
@@ -32577,7 +32573,7 @@
       <c r="AM204" s="1"/>
       <c r="AN204" s="83"/>
     </row>
-    <row r="205" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A205" s="15" t="s">
         <v>614</v>
       </c>
@@ -32666,7 +32662,7 @@
       <c r="AM205" s="1"/>
       <c r="AN205" s="83"/>
     </row>
-    <row r="206" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A206" s="15" t="s">
         <v>615</v>
       </c>
@@ -32759,7 +32755,7 @@
       <c r="AM206" s="1"/>
       <c r="AN206" s="83"/>
     </row>
-    <row r="207" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A207" s="15" t="s">
         <v>616</v>
       </c>
@@ -32846,7 +32842,7 @@
       <c r="AM207" s="1"/>
       <c r="AN207" s="83"/>
     </row>
-    <row r="208" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A208" s="15" t="s">
         <v>619</v>
       </c>
@@ -32935,7 +32931,7 @@
       <c r="AM208" s="1"/>
       <c r="AN208" s="83"/>
     </row>
-    <row r="209" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A209" s="15" t="s">
         <v>621</v>
       </c>
@@ -33022,7 +33018,7 @@
       <c r="AM209" s="1"/>
       <c r="AN209" s="83"/>
     </row>
-    <row r="210" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A210" s="15" t="s">
         <v>623</v>
       </c>
@@ -33109,7 +33105,7 @@
       <c r="AM210" s="1"/>
       <c r="AN210" s="83"/>
     </row>
-    <row r="211" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A211" s="15" t="s">
         <v>625</v>
       </c>
@@ -33196,7 +33192,7 @@
       <c r="AM211" s="1"/>
       <c r="AN211" s="83"/>
     </row>
-    <row r="212" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A212" s="15" t="s">
         <v>627</v>
       </c>
@@ -33285,7 +33281,7 @@
       <c r="AM212" s="1"/>
       <c r="AN212" s="83"/>
     </row>
-    <row r="213" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A213" s="15" t="s">
         <v>629</v>
       </c>
@@ -33372,7 +33368,7 @@
       <c r="AM213" s="1"/>
       <c r="AN213" s="83"/>
     </row>
-    <row r="214" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A214" s="15" t="s">
         <v>631</v>
       </c>
@@ -33459,7 +33455,7 @@
       <c r="AM214" s="1"/>
       <c r="AN214" s="83"/>
     </row>
-    <row r="215" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A215" s="15" t="s">
         <v>634</v>
       </c>
@@ -33548,7 +33544,7 @@
       <c r="AM215" s="1"/>
       <c r="AN215" s="83"/>
     </row>
-    <row r="216" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A216" s="15" t="s">
         <v>637</v>
       </c>
@@ -33633,7 +33629,7 @@
       <c r="AM216" s="1"/>
       <c r="AN216" s="83"/>
     </row>
-    <row r="217" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A217" s="15" t="s">
         <v>639</v>
       </c>
@@ -33720,7 +33716,7 @@
       <c r="AM217" s="1"/>
       <c r="AN217" s="83"/>
     </row>
-    <row r="218" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A218" s="15" t="s">
         <v>642</v>
       </c>
@@ -33805,7 +33801,7 @@
       <c r="AM218" s="1"/>
       <c r="AN218" s="83"/>
     </row>
-    <row r="219" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A219" s="15" t="s">
         <v>644</v>
       </c>
@@ -33890,7 +33886,7 @@
       <c r="AM219" s="1"/>
       <c r="AN219" s="83"/>
     </row>
-    <row r="220" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A220" s="15" t="s">
         <v>646</v>
       </c>
@@ -33971,7 +33967,7 @@
       <c r="AM220" s="1"/>
       <c r="AN220" s="83"/>
     </row>
-    <row r="221" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A221" s="15" t="s">
         <v>647</v>
       </c>
@@ -34056,7 +34052,7 @@
       <c r="AM221" s="1"/>
       <c r="AN221" s="83"/>
     </row>
-    <row r="222" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A222" s="15" t="s">
         <v>650</v>
       </c>
@@ -34141,7 +34137,7 @@
       <c r="AM222" s="1"/>
       <c r="AN222" s="83"/>
     </row>
-    <row r="223" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A223" s="15" t="s">
         <v>653</v>
       </c>
@@ -34226,7 +34222,7 @@
       <c r="AM223" s="1"/>
       <c r="AN223" s="83"/>
     </row>
-    <row r="224" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A224" s="15" t="s">
         <v>655</v>
       </c>
@@ -34315,7 +34311,7 @@
       <c r="AM224" s="1"/>
       <c r="AN224" s="83"/>
     </row>
-    <row r="225" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A225" s="15" t="s">
         <v>657</v>
       </c>
@@ -34398,7 +34394,7 @@
       <c r="AM225" s="1"/>
       <c r="AN225" s="83"/>
     </row>
-    <row r="226" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A226" s="15" t="s">
         <v>659</v>
       </c>
@@ -34485,7 +34481,7 @@
       <c r="AM226" s="1"/>
       <c r="AN226" s="83"/>
     </row>
-    <row r="227" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A227" s="15" t="s">
         <v>661</v>
       </c>
@@ -34572,7 +34568,7 @@
       <c r="AM227" s="1"/>
       <c r="AN227" s="83"/>
     </row>
-    <row r="228" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A228" s="15" t="s">
         <v>664</v>
       </c>
@@ -34657,7 +34653,7 @@
       <c r="AM228" s="1"/>
       <c r="AN228" s="83"/>
     </row>
-    <row r="229" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A229" s="15" t="s">
         <v>666</v>
       </c>
@@ -34740,7 +34736,7 @@
       <c r="AM229" s="1"/>
       <c r="AN229" s="83"/>
     </row>
-    <row r="230" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A230" s="15" t="s">
         <v>667</v>
       </c>
@@ -34825,7 +34821,7 @@
       <c r="AM230" s="1"/>
       <c r="AN230" s="83"/>
     </row>
-    <row r="231" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A231" s="15" t="s">
         <v>669</v>
       </c>
@@ -34910,7 +34906,7 @@
       <c r="AM231" s="1"/>
       <c r="AN231" s="83"/>
     </row>
-    <row r="232" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A232" s="15" t="s">
         <v>671</v>
       </c>
@@ -34991,7 +34987,7 @@
       <c r="AM232" s="1"/>
       <c r="AN232" s="83"/>
     </row>
-    <row r="233" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A233" s="15" t="s">
         <v>672</v>
       </c>
@@ -35076,7 +35072,7 @@
       <c r="AM233" s="1"/>
       <c r="AN233" s="83"/>
     </row>
-    <row r="234" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A234" s="15" t="s">
         <v>674</v>
       </c>
@@ -35165,7 +35161,7 @@
       <c r="AM234" s="1"/>
       <c r="AN234" s="83"/>
     </row>
-    <row r="235" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A235" s="15" t="s">
         <v>675</v>
       </c>
@@ -35252,7 +35248,7 @@
       <c r="AM235" s="1"/>
       <c r="AN235" s="83"/>
     </row>
-    <row r="236" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A236" s="15" t="s">
         <v>678</v>
       </c>
@@ -35339,7 +35335,7 @@
       <c r="AM236" s="1"/>
       <c r="AN236" s="83"/>
     </row>
-    <row r="237" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A237" s="15" t="s">
         <v>680</v>
       </c>
@@ -35426,7 +35422,7 @@
       <c r="AM237" s="1"/>
       <c r="AN237" s="83"/>
     </row>
-    <row r="238" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A238" s="15" t="s">
         <v>683</v>
       </c>
@@ -35517,7 +35513,7 @@
       <c r="AM238" s="1"/>
       <c r="AN238" s="83"/>
     </row>
-    <row r="239" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A239" s="15" t="s">
         <v>686</v>
       </c>
@@ -35608,7 +35604,7 @@
       <c r="AM239" s="1"/>
       <c r="AN239" s="83"/>
     </row>
-    <row r="240" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A240" s="15" t="s">
         <v>688</v>
       </c>
@@ -35699,7 +35695,7 @@
       <c r="AM240" s="1"/>
       <c r="AN240" s="83"/>
     </row>
-    <row r="241" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A241" s="15" t="s">
         <v>690</v>
       </c>
@@ -35788,7 +35784,7 @@
       <c r="AM241" s="1"/>
       <c r="AN241" s="83"/>
     </row>
-    <row r="242" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A242" s="15" t="s">
         <v>692</v>
       </c>
@@ -35875,7 +35871,7 @@
       <c r="AM242" s="1"/>
       <c r="AN242" s="83"/>
     </row>
-    <row r="243" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A243" s="15" t="s">
         <v>694</v>
       </c>
@@ -35968,7 +35964,7 @@
       <c r="AM243" s="1"/>
       <c r="AN243" s="83"/>
     </row>
-    <row r="244" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A244" s="15" t="s">
         <v>696</v>
       </c>
@@ -36055,7 +36051,7 @@
       <c r="AM244" s="1"/>
       <c r="AN244" s="83"/>
     </row>
-    <row r="245" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A245" s="15" t="s">
         <v>698</v>
       </c>
@@ -36140,7 +36136,7 @@
       <c r="AM245" s="1"/>
       <c r="AN245" s="83"/>
     </row>
-    <row r="246" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A246" s="15" t="s">
         <v>700</v>
       </c>
@@ -36227,7 +36223,7 @@
       <c r="AM246" s="1"/>
       <c r="AN246" s="83"/>
     </row>
-    <row r="247" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A247" s="15" t="s">
         <v>702</v>
       </c>
@@ -36314,7 +36310,7 @@
       <c r="AM247" s="1"/>
       <c r="AN247" s="83"/>
     </row>
-    <row r="248" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A248" s="15" t="s">
         <v>704</v>
       </c>
@@ -36401,7 +36397,7 @@
       <c r="AM248" s="1"/>
       <c r="AN248" s="83"/>
     </row>
-    <row r="249" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A249" s="15" t="s">
         <v>706</v>
       </c>
@@ -36488,7 +36484,7 @@
       <c r="AM249" s="1"/>
       <c r="AN249" s="83"/>
     </row>
-    <row r="250" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A250" s="15" t="s">
         <v>708</v>
       </c>
@@ -36577,7 +36573,7 @@
       <c r="AM250" s="1"/>
       <c r="AN250" s="83"/>
     </row>
-    <row r="251" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A251" s="15" t="s">
         <v>709</v>
       </c>
@@ -36662,7 +36658,7 @@
       <c r="AM251" s="1"/>
       <c r="AN251" s="83"/>
     </row>
-    <row r="252" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A252" s="15" t="s">
         <v>711</v>
       </c>
@@ -36747,7 +36743,7 @@
       <c r="AM252" s="1"/>
       <c r="AN252" s="83"/>
     </row>
-    <row r="253" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A253" s="15" t="s">
         <v>713</v>
       </c>
@@ -36832,7 +36828,7 @@
       <c r="AM253" s="1"/>
       <c r="AN253" s="83"/>
     </row>
-    <row r="254" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A254" s="15" t="s">
         <v>715</v>
       </c>
@@ -36917,7 +36913,7 @@
       <c r="AM254" s="1"/>
       <c r="AN254" s="83"/>
     </row>
-    <row r="255" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A255" s="15" t="s">
         <v>717</v>
       </c>
@@ -37004,7 +37000,7 @@
       <c r="AM255" s="1"/>
       <c r="AN255" s="83"/>
     </row>
-    <row r="256" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A256" s="15" t="s">
         <v>719</v>
       </c>
@@ -37093,7 +37089,7 @@
       <c r="AM256" s="1"/>
       <c r="AN256" s="83"/>
     </row>
-    <row r="257" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A257" s="15" t="s">
         <v>721</v>
       </c>
@@ -37180,7 +37176,7 @@
       <c r="AM257" s="1"/>
       <c r="AN257" s="83"/>
     </row>
-    <row r="258" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A258" s="15" t="s">
         <v>723</v>
       </c>
@@ -37267,7 +37263,7 @@
       <c r="AM258" s="1"/>
       <c r="AN258" s="83"/>
     </row>
-    <row r="259" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A259" s="15" t="s">
         <v>725</v>
       </c>
@@ -37354,7 +37350,7 @@
       <c r="AM259" s="1"/>
       <c r="AN259" s="83"/>
     </row>
-    <row r="260" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A260" s="15" t="s">
         <v>727</v>
       </c>
@@ -37439,7 +37435,7 @@
       <c r="AM260" s="1"/>
       <c r="AN260" s="83"/>
     </row>
-    <row r="261" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A261" s="15" t="s">
         <v>728</v>
       </c>
@@ -37520,7 +37516,7 @@
       <c r="AM261" s="1"/>
       <c r="AN261" s="83"/>
     </row>
-    <row r="262" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A262" s="15" t="s">
         <v>729</v>
       </c>
@@ -37601,7 +37597,7 @@
       <c r="AM262" s="1"/>
       <c r="AN262" s="83"/>
     </row>
-    <row r="263" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A263" s="15" t="s">
         <v>730</v>
       </c>
@@ -37678,7 +37674,7 @@
       <c r="AM263" s="1"/>
       <c r="AN263" s="83"/>
     </row>
-    <row r="264" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A264" s="15" t="s">
         <v>732</v>
       </c>
@@ -37759,7 +37755,7 @@
       <c r="AM264" s="1"/>
       <c r="AN264" s="83"/>
     </row>
-    <row r="265" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A265" s="15" t="s">
         <v>733</v>
       </c>
@@ -37836,7 +37832,7 @@
       <c r="AM265" s="1"/>
       <c r="AN265" s="83"/>
     </row>
-    <row r="266" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A266" s="15" t="s">
         <v>734</v>
       </c>
@@ -37917,7 +37913,7 @@
       <c r="AM266" s="1"/>
       <c r="AN266" s="83"/>
     </row>
-    <row r="267" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A267" s="15" t="s">
         <v>735</v>
       </c>
@@ -38000,7 +37996,7 @@
       <c r="AM267" s="1"/>
       <c r="AN267" s="83"/>
     </row>
-    <row r="268" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A268" s="15" t="s">
         <v>736</v>
       </c>
@@ -38081,7 +38077,7 @@
       <c r="AM268" s="1"/>
       <c r="AN268" s="83"/>
     </row>
-    <row r="269" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A269" s="15" t="s">
         <v>738</v>
       </c>
@@ -38162,7 +38158,7 @@
       <c r="AM269" s="1"/>
       <c r="AN269" s="83"/>
     </row>
-    <row r="270" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A270" s="15" t="s">
         <v>739</v>
       </c>
@@ -38243,7 +38239,7 @@
       <c r="AM270" s="1"/>
       <c r="AN270" s="83"/>
     </row>
-    <row r="271" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A271" s="15" t="s">
         <v>740</v>
       </c>
@@ -38324,7 +38320,7 @@
       <c r="AM271" s="1"/>
       <c r="AN271" s="83"/>
     </row>
-    <row r="272" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A272" s="31" t="s">
         <v>741</v>
       </c>
@@ -38405,7 +38401,7 @@
       <c r="AM272" s="1"/>
       <c r="AN272" s="83"/>
     </row>
-    <row r="273" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A273" s="15" t="s">
         <v>742</v>
       </c>
@@ -38488,7 +38484,7 @@
       <c r="AM273" s="1"/>
       <c r="AN273" s="83"/>
     </row>
-    <row r="274" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A274" s="15" t="s">
         <v>743</v>
       </c>
@@ -38569,7 +38565,7 @@
       <c r="AM274" s="1"/>
       <c r="AN274" s="83"/>
     </row>
-    <row r="275" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A275" s="15" t="s">
         <v>744</v>
       </c>
@@ -38650,7 +38646,7 @@
       <c r="AM275" s="1"/>
       <c r="AN275" s="83"/>
     </row>
-    <row r="276" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A276" s="15" t="s">
         <v>745</v>
       </c>
@@ -38731,7 +38727,7 @@
       <c r="AM276" s="1"/>
       <c r="AN276" s="83"/>
     </row>
-    <row r="277" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A277" s="15" t="s">
         <v>746</v>
       </c>
@@ -38812,7 +38808,7 @@
       <c r="AM277" s="1"/>
       <c r="AN277" s="83"/>
     </row>
-    <row r="278" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A278" s="15" t="s">
         <v>747</v>
       </c>
@@ -38893,7 +38889,7 @@
       <c r="AM278" s="1"/>
       <c r="AN278" s="83"/>
     </row>
-    <row r="279" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:40" s="26" customFormat="1" ht="20.45">
       <c r="A279" s="22" t="s">
         <v>748</v>
       </c>
@@ -39010,7 +39006,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="280" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:40" s="26" customFormat="1" ht="20.45">
       <c r="A280" s="22" t="s">
         <v>758</v>
       </c>
@@ -39125,7 +39121,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="281" spans="1:40" s="26" customFormat="1" ht="122.4" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:40" s="26" customFormat="1" ht="122.45">
       <c r="A281" s="22" t="s">
         <v>760</v>
       </c>
@@ -39242,7 +39238,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="282" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:40" s="26" customFormat="1">
       <c r="A282" s="22" t="s">
         <v>768</v>
       </c>
@@ -39355,7 +39351,7 @@
       <c r="AM282" s="1"/>
       <c r="AN282" s="83"/>
     </row>
-    <row r="283" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:40" s="26" customFormat="1">
       <c r="A283" s="22" t="s">
         <v>562</v>
       </c>
@@ -39470,7 +39466,7 @@
         <v>46235</v>
       </c>
     </row>
-    <row r="284" spans="1:40" s="26" customFormat="1" ht="81.599999999999994" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:40" s="26" customFormat="1" ht="81.599999999999994">
       <c r="A284" s="22" t="s">
         <v>778</v>
       </c>
@@ -39585,7 +39581,7 @@
       </c>
       <c r="AN284" s="83"/>
     </row>
-    <row r="285" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:40" s="26" customFormat="1">
       <c r="A285" s="22" t="s">
         <v>782</v>
       </c>
@@ -39700,7 +39696,7 @@
       </c>
       <c r="AN285" s="83"/>
     </row>
-    <row r="286" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:40" s="26" customFormat="1">
       <c r="A286" s="22" t="s">
         <v>786</v>
       </c>
@@ -39815,7 +39811,7 @@
       </c>
       <c r="AN286" s="83"/>
     </row>
-    <row r="287" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:40" s="26" customFormat="1" ht="20.45">
       <c r="A287" s="22" t="s">
         <v>790</v>
       </c>
@@ -39930,7 +39926,7 @@
       </c>
       <c r="AN287" s="83"/>
     </row>
-    <row r="288" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:40" s="26" customFormat="1">
       <c r="A288" s="22" t="s">
         <v>792</v>
       </c>
@@ -40045,7 +40041,7 @@
       </c>
       <c r="AN288" s="83"/>
     </row>
-    <row r="289" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:40" s="26" customFormat="1">
       <c r="A289" s="22" t="s">
         <v>795</v>
       </c>
@@ -40160,7 +40156,7 @@
       </c>
       <c r="AN289" s="83"/>
     </row>
-    <row r="290" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:40" s="26" customFormat="1">
       <c r="A290" s="22" t="s">
         <v>207</v>
       </c>
@@ -40257,7 +40253,7 @@
       </c>
       <c r="AN290" s="83"/>
     </row>
-    <row r="291" spans="1:40" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:40" s="26" customFormat="1" ht="30.6">
       <c r="A291" s="22" t="s">
         <v>804</v>
       </c>
@@ -40370,7 +40366,7 @@
       </c>
       <c r="AN291" s="83"/>
     </row>
-    <row r="292" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:40" s="26" customFormat="1">
       <c r="A292" s="22" t="s">
         <v>809</v>
       </c>
@@ -40465,7 +40461,7 @@
       <c r="AM292" s="1"/>
       <c r="AN292" s="83"/>
     </row>
-    <row r="293" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:40" s="26" customFormat="1">
       <c r="A293" s="22" t="s">
         <v>812</v>
       </c>
@@ -40554,7 +40550,7 @@
       <c r="AM293" s="1"/>
       <c r="AN293" s="83"/>
     </row>
-    <row r="294" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:40" s="26" customFormat="1">
       <c r="A294" s="22" t="s">
         <v>815</v>
       </c>
@@ -40645,7 +40641,7 @@
       <c r="AM294" s="1"/>
       <c r="AN294" s="83"/>
     </row>
-    <row r="295" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:40" s="26" customFormat="1">
       <c r="A295" s="22" t="s">
         <v>817</v>
       </c>
@@ -40730,7 +40726,7 @@
       <c r="AM295" s="1"/>
       <c r="AN295" s="83"/>
     </row>
-    <row r="296" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:40" s="26" customFormat="1">
       <c r="A296" s="22" t="s">
         <v>821</v>
       </c>
@@ -40821,7 +40817,7 @@
       <c r="AM296" s="1"/>
       <c r="AN296" s="83"/>
     </row>
-    <row r="297" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:40" s="26" customFormat="1">
       <c r="A297" s="22" t="s">
         <v>728</v>
       </c>
@@ -40912,7 +40908,7 @@
       </c>
       <c r="AN297" s="83"/>
     </row>
-    <row r="298" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:40" s="26" customFormat="1">
       <c r="A298" s="22" t="s">
         <v>156</v>
       </c>
@@ -41001,7 +40997,7 @@
       <c r="AM298" s="1"/>
       <c r="AN298" s="83"/>
     </row>
-    <row r="299" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:40" s="26" customFormat="1">
       <c r="A299" s="22" t="s">
         <v>828</v>
       </c>
@@ -41092,7 +41088,7 @@
       <c r="AM299" s="1"/>
       <c r="AN299" s="83"/>
     </row>
-    <row r="300" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:40" s="26" customFormat="1">
       <c r="A300" s="22" t="s">
         <v>829</v>
       </c>
@@ -41181,7 +41177,7 @@
       <c r="AM300" s="1"/>
       <c r="AN300" s="83"/>
     </row>
-    <row r="301" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:40" s="26" customFormat="1">
       <c r="A301" s="22" t="s">
         <v>391</v>
       </c>
@@ -41272,7 +41268,7 @@
       <c r="AM301" s="1"/>
       <c r="AN301" s="83"/>
     </row>
-    <row r="302" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:40" s="26" customFormat="1">
       <c r="A302" s="22" t="s">
         <v>266</v>
       </c>
@@ -41361,7 +41357,7 @@
       <c r="AM302" s="1"/>
       <c r="AN302" s="83"/>
     </row>
-    <row r="303" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:40" s="26" customFormat="1">
       <c r="A303" s="22" t="s">
         <v>836</v>
       </c>
@@ -41452,7 +41448,7 @@
       <c r="AM303" s="1"/>
       <c r="AN303" s="83"/>
     </row>
-    <row r="304" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:40" s="26" customFormat="1">
       <c r="A304" s="22" t="s">
         <v>839</v>
       </c>
@@ -41543,7 +41539,7 @@
       <c r="AM304" s="1"/>
       <c r="AN304" s="83"/>
     </row>
-    <row r="305" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:40" s="26" customFormat="1">
       <c r="A305" s="22" t="s">
         <v>53</v>
       </c>
@@ -41634,7 +41630,7 @@
       <c r="AM305" s="1"/>
       <c r="AN305" s="83"/>
     </row>
-    <row r="306" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:40" s="26" customFormat="1">
       <c r="A306" s="22" t="s">
         <v>843</v>
       </c>
@@ -41717,7 +41713,7 @@
       <c r="AM306" s="1"/>
       <c r="AN306" s="83"/>
     </row>
-    <row r="307" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:40" s="26" customFormat="1">
       <c r="A307" s="22" t="s">
         <v>845</v>
       </c>
@@ -41808,7 +41804,7 @@
       <c r="AM307" s="1"/>
       <c r="AN307" s="83"/>
     </row>
-    <row r="308" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:40" s="26" customFormat="1">
       <c r="A308" s="22" t="s">
         <v>847</v>
       </c>
@@ -41897,7 +41893,7 @@
       <c r="AM308" s="1"/>
       <c r="AN308" s="83"/>
     </row>
-    <row r="309" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:40" s="26" customFormat="1">
       <c r="A309" s="22" t="s">
         <v>848</v>
       </c>
@@ -41988,7 +41984,7 @@
       <c r="AM309" s="1"/>
       <c r="AN309" s="83"/>
     </row>
-    <row r="310" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:40" s="26" customFormat="1">
       <c r="A310" s="22" t="s">
         <v>650</v>
       </c>
@@ -42073,7 +42069,7 @@
       <c r="AM310" s="1"/>
       <c r="AN310" s="83"/>
     </row>
-    <row r="311" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:40" s="26" customFormat="1">
       <c r="A311" s="22" t="s">
         <v>739</v>
       </c>
@@ -42164,7 +42160,7 @@
       <c r="AM311" s="1"/>
       <c r="AN311" s="83"/>
     </row>
-    <row r="312" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:40" s="26" customFormat="1">
       <c r="A312" s="22" t="s">
         <v>118</v>
       </c>
@@ -42253,7 +42249,7 @@
       <c r="AM312" s="1"/>
       <c r="AN312" s="83"/>
     </row>
-    <row r="313" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:40" s="26" customFormat="1">
       <c r="A313" s="22">
         <v>98451</v>
       </c>
@@ -42326,7 +42322,7 @@
       <c r="AM313" s="1"/>
       <c r="AN313" s="83"/>
     </row>
-    <row r="314" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:40" s="26" customFormat="1">
       <c r="A314" s="22" t="s">
         <v>854</v>
       </c>
@@ -42421,7 +42417,7 @@
       <c r="AM314" s="1"/>
       <c r="AN314" s="83"/>
     </row>
-    <row r="315" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:40" s="26" customFormat="1">
       <c r="A315" s="22" t="s">
         <v>857</v>
       </c>
@@ -42512,7 +42508,7 @@
       <c r="AM315" s="1"/>
       <c r="AN315" s="83"/>
     </row>
-    <row r="316" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:40" s="26" customFormat="1">
       <c r="A316" s="3" t="s">
         <v>859</v>
       </c>
@@ -42599,7 +42595,7 @@
       <c r="AM316" s="1"/>
       <c r="AN316" s="83"/>
     </row>
-    <row r="317" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:40" s="26" customFormat="1">
       <c r="A317" s="22" t="s">
         <v>644</v>
       </c>
@@ -42684,7 +42680,7 @@
       <c r="AM317" s="1"/>
       <c r="AN317" s="83"/>
     </row>
-    <row r="318" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:40" s="26" customFormat="1">
       <c r="A318" s="22" t="s">
         <v>862</v>
       </c>
@@ -42775,7 +42771,7 @@
       <c r="AM318" s="1"/>
       <c r="AN318" s="83"/>
     </row>
-    <row r="319" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:40" s="26" customFormat="1">
       <c r="A319" s="22" t="s">
         <v>864</v>
       </c>
@@ -42870,7 +42866,7 @@
       <c r="AM319" s="1"/>
       <c r="AN319" s="83"/>
     </row>
-    <row r="320" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:40" s="26" customFormat="1">
       <c r="A320" s="22" t="s">
         <v>325</v>
       </c>
@@ -42959,7 +42955,7 @@
       <c r="AM320" s="1"/>
       <c r="AN320" s="83"/>
     </row>
-    <row r="321" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:40" s="26" customFormat="1">
       <c r="A321" s="22" t="s">
         <v>866</v>
       </c>
@@ -43040,7 +43036,7 @@
       <c r="AM321" s="1"/>
       <c r="AN321" s="83"/>
     </row>
-    <row r="322" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:40" s="26" customFormat="1">
       <c r="A322" s="3" t="s">
         <v>868</v>
       </c>
@@ -43127,7 +43123,7 @@
       <c r="AM322" s="1"/>
       <c r="AN322" s="83"/>
     </row>
-    <row r="323" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:40" s="26" customFormat="1">
       <c r="A323" s="22" t="s">
         <v>869</v>
       </c>
@@ -43214,7 +43210,7 @@
       <c r="AM323" s="1"/>
       <c r="AN323" s="83"/>
     </row>
-    <row r="324" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:40" s="26" customFormat="1">
       <c r="A324" s="22" t="s">
         <v>870</v>
       </c>
@@ -43297,7 +43293,7 @@
       <c r="AM324" s="1"/>
       <c r="AN324" s="83"/>
     </row>
-    <row r="325" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:40" s="26" customFormat="1">
       <c r="A325" s="22" t="s">
         <v>132</v>
       </c>
@@ -43386,7 +43382,7 @@
       <c r="AM325" s="1"/>
       <c r="AN325" s="83"/>
     </row>
-    <row r="326" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:40" s="26" customFormat="1">
       <c r="A326" s="3" t="s">
         <v>874</v>
       </c>
@@ -43475,7 +43471,7 @@
       <c r="AM326" s="1"/>
       <c r="AN326" s="83"/>
     </row>
-    <row r="327" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:40" s="26" customFormat="1">
       <c r="A327" s="22" t="s">
         <v>646</v>
       </c>
@@ -43560,7 +43556,7 @@
       <c r="AM327" s="1"/>
       <c r="AN327" s="83"/>
     </row>
-    <row r="328" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:40" s="26" customFormat="1">
       <c r="A328" s="3" t="s">
         <v>876</v>
       </c>
@@ -43647,7 +43643,7 @@
       <c r="AM328" s="1"/>
       <c r="AN328" s="83"/>
     </row>
-    <row r="329" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:40" s="26" customFormat="1">
       <c r="A329" s="3" t="s">
         <v>877</v>
       </c>
@@ -43734,7 +43730,7 @@
       <c r="AM329" s="1"/>
       <c r="AN329" s="83"/>
     </row>
-    <row r="330" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:40" s="26" customFormat="1">
       <c r="A330" s="3" t="s">
         <v>878</v>
       </c>
@@ -43821,7 +43817,7 @@
       <c r="AM330" s="1"/>
       <c r="AN330" s="83"/>
     </row>
-    <row r="331" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:40" s="26" customFormat="1">
       <c r="A331" s="3" t="s">
         <v>880</v>
       </c>
@@ -43904,7 +43900,7 @@
       <c r="AM331" s="1"/>
       <c r="AN331" s="83"/>
     </row>
-    <row r="332" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:40" s="26" customFormat="1">
       <c r="A332" s="3" t="s">
         <v>883</v>
       </c>
@@ -43987,7 +43983,7 @@
       <c r="AM332" s="1"/>
       <c r="AN332" s="83"/>
     </row>
-    <row r="333" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:40" s="26" customFormat="1">
       <c r="A333" s="3" t="s">
         <v>886</v>
       </c>
@@ -44074,7 +44070,7 @@
       <c r="AM333" s="1"/>
       <c r="AN333" s="83"/>
     </row>
-    <row r="334" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:40" s="26" customFormat="1">
       <c r="A334" s="22" t="s">
         <v>887</v>
       </c>
@@ -44165,7 +44161,7 @@
       <c r="AM334" s="1"/>
       <c r="AN334" s="83"/>
     </row>
-    <row r="335" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:40" s="26" customFormat="1">
       <c r="A335" s="22" t="s">
         <v>890</v>
       </c>
@@ -44248,7 +44244,7 @@
       <c r="AM335" s="1"/>
       <c r="AN335" s="83"/>
     </row>
-    <row r="336" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:40" s="26" customFormat="1">
       <c r="A336" s="3" t="s">
         <v>275</v>
       </c>
@@ -44325,7 +44321,7 @@
       <c r="AM336" s="1"/>
       <c r="AN336" s="83"/>
     </row>
-    <row r="337" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:40" s="26" customFormat="1">
       <c r="A337" s="22" t="s">
         <v>892</v>
       </c>
@@ -44416,7 +44412,7 @@
       <c r="AM337" s="1"/>
       <c r="AN337" s="83"/>
     </row>
-    <row r="338" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:40" s="26" customFormat="1">
       <c r="A338" s="3" t="s">
         <v>664</v>
       </c>
@@ -44499,7 +44495,7 @@
       <c r="AM338" s="1"/>
       <c r="AN338" s="83"/>
     </row>
-    <row r="339" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:40" s="26" customFormat="1">
       <c r="A339" s="22" t="s">
         <v>895</v>
       </c>
@@ -44582,7 +44578,7 @@
       <c r="AM339" s="1"/>
       <c r="AN339" s="83"/>
     </row>
-    <row r="340" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:40" s="26" customFormat="1">
       <c r="A340" s="3" t="s">
         <v>898</v>
       </c>
@@ -44665,7 +44661,7 @@
       <c r="AM340" s="1"/>
       <c r="AN340" s="83"/>
     </row>
-    <row r="341" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:40" s="26" customFormat="1">
       <c r="A341" s="22" t="s">
         <v>900</v>
       </c>
@@ -44748,7 +44744,7 @@
       <c r="AM341" s="1"/>
       <c r="AN341" s="83"/>
     </row>
-    <row r="342" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:40" s="26" customFormat="1">
       <c r="A342" s="22" t="s">
         <v>902</v>
       </c>
@@ -44831,7 +44827,7 @@
       <c r="AM342" s="1"/>
       <c r="AN342" s="83"/>
     </row>
-    <row r="343" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:40" s="26" customFormat="1">
       <c r="A343" s="3" t="s">
         <v>904</v>
       </c>
@@ -44920,7 +44916,7 @@
       <c r="AM343" s="1"/>
       <c r="AN343" s="83"/>
     </row>
-    <row r="344" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:40" s="26" customFormat="1">
       <c r="A344" s="22" t="s">
         <v>905</v>
       </c>
@@ -45007,7 +45003,7 @@
       <c r="AM344" s="1"/>
       <c r="AN344" s="83"/>
     </row>
-    <row r="345" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:40" s="26" customFormat="1">
       <c r="A345" s="3" t="s">
         <v>907</v>
       </c>
@@ -45094,7 +45090,7 @@
       <c r="AM345" s="1"/>
       <c r="AN345" s="83"/>
     </row>
-    <row r="346" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:40" s="26" customFormat="1">
       <c r="A346" s="3" t="s">
         <v>655</v>
       </c>
@@ -45181,7 +45177,7 @@
       <c r="AM346" s="1"/>
       <c r="AN346" s="83"/>
     </row>
-    <row r="347" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:40" s="26" customFormat="1">
       <c r="A347" s="22" t="s">
         <v>909</v>
       </c>
@@ -45260,7 +45256,7 @@
       <c r="AM347" s="1"/>
       <c r="AN347" s="83"/>
     </row>
-    <row r="348" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:40" s="26" customFormat="1">
       <c r="A348" s="3" t="s">
         <v>912</v>
       </c>
@@ -45347,7 +45343,7 @@
       <c r="AM348" s="1"/>
       <c r="AN348" s="83"/>
     </row>
-    <row r="349" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:40" s="26" customFormat="1">
       <c r="A349" s="22" t="s">
         <v>913</v>
       </c>
@@ -45434,7 +45430,7 @@
       <c r="AM349" s="1"/>
       <c r="AN349" s="83"/>
     </row>
-    <row r="350" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:40" s="26" customFormat="1">
       <c r="A350" s="3" t="s">
         <v>915</v>
       </c>
@@ -45517,7 +45513,7 @@
       <c r="AM350" s="1"/>
       <c r="AN350" s="83"/>
     </row>
-    <row r="351" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:40" s="26" customFormat="1">
       <c r="A351" s="22" t="s">
         <v>917</v>
       </c>
@@ -45608,7 +45604,7 @@
       <c r="AM351" s="1"/>
       <c r="AN351" s="83"/>
     </row>
-    <row r="352" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:40" s="26" customFormat="1">
       <c r="A352" s="22" t="s">
         <v>918</v>
       </c>
@@ -45691,7 +45687,7 @@
       <c r="AM352" s="1"/>
       <c r="AN352" s="83"/>
     </row>
-    <row r="353" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:40" s="26" customFormat="1">
       <c r="A353" s="3" t="s">
         <v>920</v>
       </c>
@@ -45778,7 +45774,7 @@
       <c r="AM353" s="1"/>
       <c r="AN353" s="83"/>
     </row>
-    <row r="354" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:40" s="26" customFormat="1">
       <c r="A354" s="3" t="s">
         <v>921</v>
       </c>
@@ -45861,7 +45857,7 @@
       <c r="AM354" s="1"/>
       <c r="AN354" s="83"/>
     </row>
-    <row r="355" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:40" s="26" customFormat="1">
       <c r="A355" s="22" t="s">
         <v>922</v>
       </c>
@@ -45952,7 +45948,7 @@
       <c r="AM355" s="1"/>
       <c r="AN355" s="83"/>
     </row>
-    <row r="356" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:40" s="26" customFormat="1">
       <c r="A356" s="3" t="s">
         <v>394</v>
       </c>
@@ -46035,7 +46031,7 @@
       <c r="AM356" s="1"/>
       <c r="AN356" s="83"/>
     </row>
-    <row r="357" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:40" s="26" customFormat="1">
       <c r="A357" s="22" t="s">
         <v>923</v>
       </c>
@@ -46118,7 +46114,7 @@
       <c r="AM357" s="1"/>
       <c r="AN357" s="83"/>
     </row>
-    <row r="358" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:40" s="26" customFormat="1">
       <c r="A358" s="22" t="s">
         <v>927</v>
       </c>
@@ -46201,7 +46197,7 @@
       <c r="AM358" s="1"/>
       <c r="AN358" s="83"/>
     </row>
-    <row r="359" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:40" s="26" customFormat="1">
       <c r="A359" s="3" t="s">
         <v>928</v>
       </c>
@@ -46288,7 +46284,7 @@
       <c r="AM359" s="1"/>
       <c r="AN359" s="83"/>
     </row>
-    <row r="360" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:40" s="26" customFormat="1">
       <c r="A360" s="22" t="s">
         <v>929</v>
       </c>
@@ -46379,7 +46375,7 @@
       <c r="AM360" s="1"/>
       <c r="AN360" s="83"/>
     </row>
-    <row r="361" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:40" s="26" customFormat="1">
       <c r="A361" s="3" t="s">
         <v>370</v>
       </c>
@@ -46462,7 +46458,7 @@
       <c r="AM361" s="1"/>
       <c r="AN361" s="83"/>
     </row>
-    <row r="362" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:40" s="26" customFormat="1">
       <c r="A362" s="3" t="s">
         <v>930</v>
       </c>
@@ -46549,7 +46545,7 @@
       <c r="AM362" s="1"/>
       <c r="AN362" s="83"/>
     </row>
-    <row r="363" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:40" s="26" customFormat="1">
       <c r="A363" s="22" t="s">
         <v>932</v>
       </c>
@@ -46632,7 +46628,7 @@
       <c r="AM363" s="1"/>
       <c r="AN363" s="83"/>
     </row>
-    <row r="364" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:40" s="26" customFormat="1">
       <c r="A364" s="3" t="s">
         <v>659</v>
       </c>
@@ -46715,7 +46711,7 @@
       <c r="AM364" s="1"/>
       <c r="AN364" s="83"/>
     </row>
-    <row r="365" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:40" s="26" customFormat="1">
       <c r="A365" s="22" t="s">
         <v>933</v>
       </c>
@@ -46798,7 +46794,7 @@
       <c r="AM365" s="1"/>
       <c r="AN365" s="83"/>
     </row>
-    <row r="366" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:40" s="26" customFormat="1">
       <c r="A366" s="3" t="s">
         <v>934</v>
       </c>
@@ -46881,7 +46877,7 @@
       <c r="AM366" s="1"/>
       <c r="AN366" s="83"/>
     </row>
-    <row r="367" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:40" s="26" customFormat="1">
       <c r="A367" s="3" t="s">
         <v>740</v>
       </c>
@@ -46964,7 +46960,7 @@
       <c r="AM367" s="1"/>
       <c r="AN367" s="83"/>
     </row>
-    <row r="368" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:40" s="26" customFormat="1">
       <c r="A368" s="3" t="s">
         <v>674</v>
       </c>
@@ -47047,7 +47043,7 @@
       <c r="AM368" s="1"/>
       <c r="AN368" s="83"/>
     </row>
-    <row r="369" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:40" s="26" customFormat="1">
       <c r="A369" s="3" t="s">
         <v>938</v>
       </c>
@@ -47130,7 +47126,7 @@
       <c r="AM369" s="1"/>
       <c r="AN369" s="83"/>
     </row>
-    <row r="370" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:40" s="26" customFormat="1">
       <c r="A370" s="22" t="s">
         <v>940</v>
       </c>
@@ -47213,7 +47209,7 @@
       <c r="AM370" s="1"/>
       <c r="AN370" s="83"/>
     </row>
-    <row r="371" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:40" s="26" customFormat="1">
       <c r="A371" s="22" t="s">
         <v>943</v>
       </c>
@@ -47296,7 +47292,7 @@
       <c r="AM371" s="1"/>
       <c r="AN371" s="83"/>
     </row>
-    <row r="372" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:40" s="26" customFormat="1">
       <c r="A372" s="22" t="s">
         <v>945</v>
       </c>
@@ -47379,7 +47375,7 @@
       <c r="AM372" s="1"/>
       <c r="AN372" s="83"/>
     </row>
-    <row r="373" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:40" s="26" customFormat="1">
       <c r="A373" s="3" t="s">
         <v>946</v>
       </c>
@@ -47462,7 +47458,7 @@
       <c r="AM373" s="1"/>
       <c r="AN373" s="83"/>
     </row>
-    <row r="374" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:40" s="26" customFormat="1">
       <c r="A374" s="3" t="s">
         <v>948</v>
       </c>
@@ -47545,7 +47541,7 @@
       <c r="AM374" s="1"/>
       <c r="AN374" s="83"/>
     </row>
-    <row r="375" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:40" s="26" customFormat="1">
       <c r="A375" s="22" t="s">
         <v>949</v>
       </c>
@@ -47628,7 +47624,7 @@
       <c r="AM375" s="1"/>
       <c r="AN375" s="83"/>
     </row>
-    <row r="376" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:40" s="26" customFormat="1">
       <c r="A376" s="3" t="s">
         <v>950</v>
       </c>
@@ -47711,7 +47707,7 @@
       <c r="AM376" s="1"/>
       <c r="AN376" s="83"/>
     </row>
-    <row r="377" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:40" s="26" customFormat="1">
       <c r="A377" s="22" t="s">
         <v>951</v>
       </c>
@@ -47794,7 +47790,7 @@
       <c r="AM377" s="1"/>
       <c r="AN377" s="83"/>
     </row>
-    <row r="378" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:40" s="26" customFormat="1">
       <c r="A378" s="22" t="s">
         <v>953</v>
       </c>
@@ -47877,7 +47873,7 @@
       <c r="AM378" s="1"/>
       <c r="AN378" s="83"/>
     </row>
-    <row r="379" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:40" s="26" customFormat="1">
       <c r="A379" s="22" t="s">
         <v>956</v>
       </c>
@@ -47960,7 +47956,7 @@
       <c r="AM379" s="1"/>
       <c r="AN379" s="83"/>
     </row>
-    <row r="380" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:40" s="26" customFormat="1">
       <c r="A380" s="22" t="s">
         <v>958</v>
       </c>
@@ -48043,7 +48039,7 @@
       <c r="AM380" s="1"/>
       <c r="AN380" s="83"/>
     </row>
-    <row r="381" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:40" s="26" customFormat="1">
       <c r="A381" s="22" t="s">
         <v>962</v>
       </c>
@@ -48130,7 +48126,7 @@
       <c r="AM381" s="1"/>
       <c r="AN381" s="83"/>
     </row>
-    <row r="382" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:40" s="26" customFormat="1">
       <c r="A382" s="3" t="s">
         <v>964</v>
       </c>
@@ -48209,7 +48205,7 @@
       <c r="AM382" s="1"/>
       <c r="AN382" s="83"/>
     </row>
-    <row r="383" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:40" s="26" customFormat="1">
       <c r="A383" s="22" t="s">
         <v>966</v>
       </c>
@@ -48292,7 +48288,7 @@
       <c r="AM383" s="1"/>
       <c r="AN383" s="83"/>
     </row>
-    <row r="384" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:40" s="26" customFormat="1">
       <c r="A384" s="22" t="s">
         <v>323</v>
       </c>
@@ -48375,7 +48371,7 @@
       <c r="AM384" s="1"/>
       <c r="AN384" s="83"/>
     </row>
-    <row r="385" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:40" s="26" customFormat="1">
       <c r="A385" s="3" t="s">
         <v>967</v>
       </c>
@@ -48462,7 +48458,7 @@
       <c r="AM385" s="1"/>
       <c r="AN385" s="83"/>
     </row>
-    <row r="386" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:40" s="26" customFormat="1">
       <c r="A386" s="22" t="s">
         <v>471</v>
       </c>
@@ -48545,7 +48541,7 @@
       <c r="AM386" s="1"/>
       <c r="AN386" s="83"/>
     </row>
-    <row r="387" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:40" s="26" customFormat="1">
       <c r="A387" s="22" t="s">
         <v>316</v>
       </c>
@@ -48628,7 +48624,7 @@
       <c r="AM387" s="1"/>
       <c r="AN387" s="83"/>
     </row>
-    <row r="388" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:40" s="26" customFormat="1">
       <c r="A388" s="3" t="s">
         <v>971</v>
       </c>
@@ -48711,7 +48707,7 @@
       <c r="AM388" s="1"/>
       <c r="AN388" s="83"/>
     </row>
-    <row r="389" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:40" s="26" customFormat="1">
       <c r="A389" s="22" t="s">
         <v>972</v>
       </c>
@@ -48802,7 +48798,7 @@
       <c r="AM389" s="1"/>
       <c r="AN389" s="83"/>
     </row>
-    <row r="390" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:40" s="26" customFormat="1">
       <c r="A390" s="22" t="s">
         <v>973</v>
       </c>
@@ -48893,7 +48889,7 @@
       <c r="AM390" s="1"/>
       <c r="AN390" s="83"/>
     </row>
-    <row r="391" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:40" s="26" customFormat="1">
       <c r="A391" s="22" t="s">
         <v>974</v>
       </c>
@@ -48976,7 +48972,7 @@
       <c r="AM391" s="1"/>
       <c r="AN391" s="83"/>
     </row>
-    <row r="392" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:40" s="26" customFormat="1">
       <c r="A392" s="22" t="s">
         <v>975</v>
       </c>
@@ -49059,7 +49055,7 @@
       <c r="AM392" s="1"/>
       <c r="AN392" s="83"/>
     </row>
-    <row r="393" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:40" s="26" customFormat="1">
       <c r="A393" s="22" t="s">
         <v>977</v>
       </c>
@@ -49150,7 +49146,7 @@
       <c r="AM393" s="1"/>
       <c r="AN393" s="83"/>
     </row>
-    <row r="394" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:40" s="26" customFormat="1">
       <c r="A394" s="22" t="s">
         <v>446</v>
       </c>
@@ -49233,7 +49229,7 @@
       <c r="AM394" s="1"/>
       <c r="AN394" s="83"/>
     </row>
-    <row r="395" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:40" s="26" customFormat="1">
       <c r="A395" s="22" t="s">
         <v>979</v>
       </c>
@@ -49324,7 +49320,7 @@
       <c r="AM395" s="1"/>
       <c r="AN395" s="83"/>
     </row>
-    <row r="396" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:40" s="26" customFormat="1">
       <c r="A396" s="22" t="s">
         <v>482</v>
       </c>
@@ -49407,7 +49403,7 @@
       <c r="AM396" s="1"/>
       <c r="AN396" s="83"/>
     </row>
-    <row r="397" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:40" s="26" customFormat="1">
       <c r="A397" s="22" t="s">
         <v>982</v>
       </c>
@@ -49490,7 +49486,7 @@
       <c r="AM397" s="1"/>
       <c r="AN397" s="83"/>
     </row>
-    <row r="398" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:40" s="26" customFormat="1">
       <c r="A398" s="22" t="s">
         <v>983</v>
       </c>
@@ -49573,7 +49569,7 @@
       <c r="AM398" s="1"/>
       <c r="AN398" s="83"/>
     </row>
-    <row r="399" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:40" s="26" customFormat="1">
       <c r="A399" s="22" t="s">
         <v>985</v>
       </c>
@@ -49656,7 +49652,7 @@
       <c r="AM399" s="1"/>
       <c r="AN399" s="83"/>
     </row>
-    <row r="400" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:40" s="26" customFormat="1">
       <c r="A400" s="3" t="s">
         <v>986</v>
       </c>
@@ -49739,7 +49735,7 @@
       <c r="AM400" s="1"/>
       <c r="AN400" s="83"/>
     </row>
-    <row r="401" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:40" s="26" customFormat="1">
       <c r="A401" s="3" t="s">
         <v>987</v>
       </c>
@@ -49826,7 +49822,7 @@
       <c r="AM401" s="1"/>
       <c r="AN401" s="83"/>
     </row>
-    <row r="402" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:40" s="26" customFormat="1">
       <c r="A402" s="22" t="s">
         <v>988</v>
       </c>
@@ -49909,7 +49905,7 @@
       <c r="AM402" s="1"/>
       <c r="AN402" s="83"/>
     </row>
-    <row r="403" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:40" s="26" customFormat="1">
       <c r="A403" s="22" t="s">
         <v>989</v>
       </c>
@@ -49992,7 +49988,7 @@
       <c r="AM403" s="1"/>
       <c r="AN403" s="83"/>
     </row>
-    <row r="404" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:40" s="26" customFormat="1">
       <c r="A404" s="22" t="s">
         <v>992</v>
       </c>
@@ -50081,7 +50077,7 @@
       <c r="AM404" s="1"/>
       <c r="AN404" s="83"/>
     </row>
-    <row r="405" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:40" s="26" customFormat="1">
       <c r="A405" s="22" t="s">
         <v>993</v>
       </c>
@@ -50172,7 +50168,7 @@
       <c r="AM405" s="1"/>
       <c r="AN405" s="83"/>
     </row>
-    <row r="406" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:40" s="26" customFormat="1">
       <c r="A406" s="3" t="s">
         <v>995</v>
       </c>
@@ -50259,7 +50255,7 @@
       <c r="AM406" s="1"/>
       <c r="AN406" s="83"/>
     </row>
-    <row r="407" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:40" s="26" customFormat="1">
       <c r="A407" s="22" t="s">
         <v>997</v>
       </c>
@@ -50350,7 +50346,7 @@
       <c r="AM407" s="1"/>
       <c r="AN407" s="83"/>
     </row>
-    <row r="408" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:40" s="26" customFormat="1">
       <c r="A408" s="22" t="s">
         <v>999</v>
       </c>
@@ -50433,7 +50429,7 @@
       <c r="AM408" s="1"/>
       <c r="AN408" s="83"/>
     </row>
-    <row r="409" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:40" s="26" customFormat="1">
       <c r="A409" s="22" t="s">
         <v>1001</v>
       </c>
@@ -50516,7 +50512,7 @@
       <c r="AM409" s="1"/>
       <c r="AN409" s="83"/>
     </row>
-    <row r="410" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:40" s="26" customFormat="1">
       <c r="A410" s="22" t="s">
         <v>1003</v>
       </c>
@@ -50599,7 +50595,7 @@
       <c r="AM410" s="1"/>
       <c r="AN410" s="83"/>
     </row>
-    <row r="411" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:40" s="26" customFormat="1">
       <c r="A411" s="22" t="s">
         <v>414</v>
       </c>
@@ -50682,7 +50678,7 @@
       <c r="AM411" s="1"/>
       <c r="AN411" s="83"/>
     </row>
-    <row r="412" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:40" s="26" customFormat="1">
       <c r="A412" s="22" t="s">
         <v>1005</v>
       </c>
@@ -50765,7 +50761,7 @@
       <c r="AM412" s="1"/>
       <c r="AN412" s="83"/>
     </row>
-    <row r="413" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:40" s="26" customFormat="1">
       <c r="A413" s="22" t="s">
         <v>1006</v>
       </c>
@@ -50848,7 +50844,7 @@
       <c r="AM413" s="1"/>
       <c r="AN413" s="83"/>
     </row>
-    <row r="414" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:40" s="26" customFormat="1">
       <c r="A414" s="22" t="s">
         <v>1008</v>
       </c>
@@ -50931,7 +50927,7 @@
       <c r="AM414" s="1"/>
       <c r="AN414" s="83"/>
     </row>
-    <row r="415" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:40" s="26" customFormat="1">
       <c r="A415" s="22" t="s">
         <v>1010</v>
       </c>
@@ -51020,7 +51016,7 @@
       <c r="AM415" s="1"/>
       <c r="AN415" s="83"/>
     </row>
-    <row r="416" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:40" s="26" customFormat="1">
       <c r="A416" s="22" t="s">
         <v>1011</v>
       </c>
@@ -51111,7 +51107,7 @@
       <c r="AM416" s="1"/>
       <c r="AN416" s="83"/>
     </row>
-    <row r="417" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:40" s="26" customFormat="1">
       <c r="A417" s="22" t="s">
         <v>1012</v>
       </c>
@@ -51202,7 +51198,7 @@
       <c r="AM417" s="1"/>
       <c r="AN417" s="83"/>
     </row>
-    <row r="418" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:40" s="26" customFormat="1">
       <c r="A418" s="22" t="s">
         <v>1013</v>
       </c>
@@ -51291,7 +51287,7 @@
       <c r="AM418" s="1"/>
       <c r="AN418" s="83"/>
     </row>
-    <row r="419" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:40" s="26" customFormat="1">
       <c r="A419" s="22" t="s">
         <v>1014</v>
       </c>
@@ -51382,7 +51378,7 @@
       <c r="AM419" s="1"/>
       <c r="AN419" s="83"/>
     </row>
-    <row r="420" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:40" s="26" customFormat="1">
       <c r="A420" s="22" t="s">
         <v>1015</v>
       </c>
@@ -51465,7 +51461,7 @@
       <c r="AM420" s="1"/>
       <c r="AN420" s="83"/>
     </row>
-    <row r="421" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:40" s="26" customFormat="1">
       <c r="A421" s="22" t="s">
         <v>1017</v>
       </c>
@@ -51548,7 +51544,7 @@
       <c r="AM421" s="1"/>
       <c r="AN421" s="83"/>
     </row>
-    <row r="422" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:40" s="26" customFormat="1">
       <c r="A422" s="22" t="s">
         <v>1019</v>
       </c>
@@ -51631,7 +51627,7 @@
       <c r="AM422" s="1"/>
       <c r="AN422" s="83"/>
     </row>
-    <row r="423" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:40" s="26" customFormat="1">
       <c r="A423" s="22" t="s">
         <v>1021</v>
       </c>
@@ -51714,7 +51710,7 @@
       <c r="AM423" s="1"/>
       <c r="AN423" s="83"/>
     </row>
-    <row r="424" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:40" s="26" customFormat="1">
       <c r="A424" s="22" t="s">
         <v>1024</v>
       </c>
@@ -51797,7 +51793,7 @@
       <c r="AM424" s="1"/>
       <c r="AN424" s="83"/>
     </row>
-    <row r="425" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:40" s="26" customFormat="1">
       <c r="A425" s="22" t="s">
         <v>1026</v>
       </c>
@@ -51880,7 +51876,7 @@
       <c r="AM425" s="1"/>
       <c r="AN425" s="83"/>
     </row>
-    <row r="426" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:40" s="26" customFormat="1">
       <c r="A426" s="22" t="s">
         <v>1028</v>
       </c>
@@ -51963,7 +51959,7 @@
       <c r="AM426" s="1"/>
       <c r="AN426" s="83"/>
     </row>
-    <row r="427" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:40" s="26" customFormat="1">
       <c r="A427" s="22" t="s">
         <v>1029</v>
       </c>
@@ -52046,7 +52042,7 @@
       <c r="AM427" s="1"/>
       <c r="AN427" s="83"/>
     </row>
-    <row r="428" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:40" s="26" customFormat="1">
       <c r="A428" s="22" t="s">
         <v>1030</v>
       </c>
@@ -52129,7 +52125,7 @@
       <c r="AM428" s="1"/>
       <c r="AN428" s="83"/>
     </row>
-    <row r="429" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:40" s="26" customFormat="1">
       <c r="A429" s="22" t="s">
         <v>1032</v>
       </c>
@@ -52212,7 +52208,7 @@
       <c r="AM429" s="1"/>
       <c r="AN429" s="83"/>
     </row>
-    <row r="430" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:40" s="26" customFormat="1">
       <c r="A430" s="22" t="s">
         <v>1034</v>
       </c>
@@ -52295,7 +52291,7 @@
       <c r="AM430" s="1"/>
       <c r="AN430" s="83"/>
     </row>
-    <row r="431" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:40" s="26" customFormat="1">
       <c r="A431" s="22" t="s">
         <v>1036</v>
       </c>
@@ -52378,7 +52374,7 @@
       <c r="AM431" s="1"/>
       <c r="AN431" s="83"/>
     </row>
-    <row r="432" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:40" s="26" customFormat="1">
       <c r="A432" s="22" t="s">
         <v>642</v>
       </c>
@@ -52461,7 +52457,7 @@
       <c r="AM432" s="1"/>
       <c r="AN432" s="83"/>
     </row>
-    <row r="433" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:40" s="26" customFormat="1">
       <c r="A433" s="22" t="s">
         <v>1041</v>
       </c>
@@ -52544,7 +52540,7 @@
       <c r="AM433" s="1"/>
       <c r="AN433" s="83"/>
     </row>
-    <row r="434" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:40" s="26" customFormat="1">
       <c r="A434" s="22" t="s">
         <v>1043</v>
       </c>
@@ -52627,7 +52623,7 @@
       <c r="AM434" s="1"/>
       <c r="AN434" s="83"/>
     </row>
-    <row r="435" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:40" s="26" customFormat="1">
       <c r="A435" s="22" t="s">
         <v>1044</v>
       </c>
@@ -52710,7 +52706,7 @@
       <c r="AM435" s="1"/>
       <c r="AN435" s="83"/>
     </row>
-    <row r="436" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:40" s="26" customFormat="1">
       <c r="A436" s="22" t="s">
         <v>1046</v>
       </c>
@@ -52793,7 +52789,7 @@
       <c r="AM436" s="1"/>
       <c r="AN436" s="83"/>
     </row>
-    <row r="437" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:40" s="26" customFormat="1">
       <c r="A437" s="22" t="s">
         <v>1048</v>
       </c>
@@ -52876,7 +52872,7 @@
       <c r="AM437" s="1"/>
       <c r="AN437" s="83"/>
     </row>
-    <row r="438" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:40" s="26" customFormat="1">
       <c r="A438" s="22" t="s">
         <v>398</v>
       </c>
@@ -52959,7 +52955,7 @@
       <c r="AM438" s="1"/>
       <c r="AN438" s="83"/>
     </row>
-    <row r="439" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:40" s="26" customFormat="1">
       <c r="A439" s="22" t="s">
         <v>745</v>
       </c>
@@ -53042,7 +53038,7 @@
       <c r="AM439" s="1"/>
       <c r="AN439" s="83"/>
     </row>
-    <row r="440" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:40" s="26" customFormat="1">
       <c r="A440" s="22" t="s">
         <v>1053</v>
       </c>
@@ -53125,7 +53121,7 @@
       <c r="AM440" s="1"/>
       <c r="AN440" s="83"/>
     </row>
-    <row r="441" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:40" s="26" customFormat="1">
       <c r="A441" s="22" t="s">
         <v>1054</v>
       </c>
@@ -53208,7 +53204,7 @@
       <c r="AM441" s="1"/>
       <c r="AN441" s="83"/>
     </row>
-    <row r="442" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:40" s="26" customFormat="1">
       <c r="A442" s="22" t="s">
         <v>1055</v>
       </c>
@@ -53291,7 +53287,7 @@
       <c r="AM442" s="1"/>
       <c r="AN442" s="83"/>
     </row>
-    <row r="443" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:40" s="26" customFormat="1">
       <c r="A443" s="22" t="s">
         <v>1057</v>
       </c>
@@ -53374,7 +53370,7 @@
       <c r="AM443" s="1"/>
       <c r="AN443" s="83"/>
     </row>
-    <row r="444" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:40" s="26" customFormat="1">
       <c r="A444" s="22" t="s">
         <v>1059</v>
       </c>
@@ -53457,7 +53453,7 @@
       <c r="AM444" s="1"/>
       <c r="AN444" s="83"/>
     </row>
-    <row r="445" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:40" s="26" customFormat="1">
       <c r="A445" s="22" t="s">
         <v>1062</v>
       </c>
@@ -53540,7 +53536,7 @@
       <c r="AM445" s="1"/>
       <c r="AN445" s="83"/>
     </row>
-    <row r="446" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:40" s="26" customFormat="1">
       <c r="A446" s="22" t="s">
         <v>1063</v>
       </c>
@@ -53623,7 +53619,7 @@
       <c r="AM446" s="1"/>
       <c r="AN446" s="83"/>
     </row>
-    <row r="447" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:40" s="26" customFormat="1">
       <c r="A447" s="3" t="s">
         <v>653</v>
       </c>
@@ -53698,7 +53694,7 @@
       <c r="AM447" s="1"/>
       <c r="AN447" s="83"/>
     </row>
-    <row r="448" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:40" s="26" customFormat="1">
       <c r="A448" s="3" t="s">
         <v>1064</v>
       </c>
@@ -53781,7 +53777,7 @@
       <c r="AM448" s="1"/>
       <c r="AN448" s="83"/>
     </row>
-    <row r="449" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:40" s="26" customFormat="1">
       <c r="A449" s="3" t="s">
         <v>1065</v>
       </c>
@@ -53864,7 +53860,7 @@
       <c r="AM449" s="1"/>
       <c r="AN449" s="83"/>
     </row>
-    <row r="450" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:40" s="26" customFormat="1">
       <c r="A450" s="3" t="s">
         <v>1066</v>
       </c>
@@ -53947,7 +53943,7 @@
       <c r="AM450" s="1"/>
       <c r="AN450" s="83"/>
     </row>
-    <row r="451" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:40" s="26" customFormat="1">
       <c r="A451" s="3" t="s">
         <v>1067</v>
       </c>
@@ -54030,7 +54026,7 @@
       <c r="AM451" s="1"/>
       <c r="AN451" s="83"/>
     </row>
-    <row r="452" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:40" s="26" customFormat="1">
       <c r="A452" s="3" t="s">
         <v>1068</v>
       </c>
@@ -54113,7 +54109,7 @@
       <c r="AM452" s="1"/>
       <c r="AN452" s="83"/>
     </row>
-    <row r="453" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:40" s="26" customFormat="1">
       <c r="A453" s="3" t="s">
         <v>1069</v>
       </c>
@@ -54196,7 +54192,7 @@
       <c r="AM453" s="1"/>
       <c r="AN453" s="83"/>
     </row>
-    <row r="454" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:40" s="26" customFormat="1">
       <c r="A454" s="3" t="s">
         <v>1070</v>
       </c>
@@ -54279,7 +54275,7 @@
       <c r="AM454" s="1"/>
       <c r="AN454" s="83"/>
     </row>
-    <row r="455" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:40" s="26" customFormat="1">
       <c r="A455" s="3" t="s">
         <v>1071</v>
       </c>
@@ -54362,7 +54358,7 @@
       <c r="AM455" s="1"/>
       <c r="AN455" s="83"/>
     </row>
-    <row r="456" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:40" s="26" customFormat="1">
       <c r="A456" s="3" t="s">
         <v>1072</v>
       </c>
@@ -54445,7 +54441,7 @@
       <c r="AM456" s="1"/>
       <c r="AN456" s="83"/>
     </row>
-    <row r="457" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:40" s="26" customFormat="1">
       <c r="A457" s="3" t="s">
         <v>1074</v>
       </c>
@@ -54528,7 +54524,7 @@
       <c r="AM457" s="1"/>
       <c r="AN457" s="83"/>
     </row>
-    <row r="458" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:40" s="26" customFormat="1">
       <c r="A458" s="3" t="s">
         <v>1075</v>
       </c>
@@ -54611,7 +54607,7 @@
       <c r="AM458" s="1"/>
       <c r="AN458" s="83"/>
     </row>
-    <row r="459" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:40" s="26" customFormat="1">
       <c r="A459" s="3" t="s">
         <v>1076</v>
       </c>
@@ -54694,7 +54690,7 @@
       <c r="AM459" s="1"/>
       <c r="AN459" s="83"/>
     </row>
-    <row r="460" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:40" s="26" customFormat="1">
       <c r="A460" s="3" t="s">
         <v>1078</v>
       </c>
@@ -54777,7 +54773,7 @@
       <c r="AM460" s="1"/>
       <c r="AN460" s="83"/>
     </row>
-    <row r="461" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:40" s="26" customFormat="1">
       <c r="A461" s="3" t="s">
         <v>1079</v>
       </c>
@@ -54860,7 +54856,7 @@
       <c r="AM461" s="1"/>
       <c r="AN461" s="83"/>
     </row>
-    <row r="462" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:40" s="26" customFormat="1">
       <c r="A462" s="3" t="s">
         <v>1080</v>
       </c>
@@ -54943,7 +54939,7 @@
       <c r="AM462" s="1"/>
       <c r="AN462" s="83"/>
     </row>
-    <row r="463" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:40" s="26" customFormat="1">
       <c r="A463" s="3" t="s">
         <v>1081</v>
       </c>
@@ -55030,7 +55026,7 @@
       <c r="AM463" s="1"/>
       <c r="AN463" s="83"/>
     </row>
-    <row r="464" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:40" s="26" customFormat="1">
       <c r="A464" s="3" t="s">
         <v>1082</v>
       </c>
@@ -55113,7 +55109,7 @@
       <c r="AM464" s="1"/>
       <c r="AN464" s="83"/>
     </row>
-    <row r="465" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:40" s="26" customFormat="1">
       <c r="A465" s="3" t="s">
         <v>1083</v>
       </c>
@@ -55196,7 +55192,7 @@
       <c r="AM465" s="1"/>
       <c r="AN465" s="83"/>
     </row>
-    <row r="466" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:40" s="26" customFormat="1">
       <c r="A466" s="3" t="s">
         <v>1084</v>
       </c>
@@ -55279,7 +55275,7 @@
       <c r="AM466" s="1"/>
       <c r="AN466" s="83"/>
     </row>
-    <row r="467" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:40" s="26" customFormat="1">
       <c r="A467" s="3" t="s">
         <v>1086</v>
       </c>
@@ -55362,7 +55358,7 @@
       <c r="AM467" s="1"/>
       <c r="AN467" s="83"/>
     </row>
-    <row r="468" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:40" s="26" customFormat="1">
       <c r="A468" s="3" t="s">
         <v>1088</v>
       </c>
@@ -55445,7 +55441,7 @@
       <c r="AM468" s="1"/>
       <c r="AN468" s="83"/>
     </row>
-    <row r="469" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:40" s="26" customFormat="1">
       <c r="A469" s="3" t="s">
         <v>1090</v>
       </c>
@@ -55528,7 +55524,7 @@
       <c r="AM469" s="1"/>
       <c r="AN469" s="83"/>
     </row>
-    <row r="470" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:40" s="26" customFormat="1">
       <c r="A470" s="3" t="s">
         <v>1091</v>
       </c>
@@ -55611,7 +55607,7 @@
       <c r="AM470" s="1"/>
       <c r="AN470" s="83"/>
     </row>
-    <row r="471" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:40" s="26" customFormat="1">
       <c r="A471" s="3" t="s">
         <v>1092</v>
       </c>
@@ -55694,7 +55690,7 @@
       <c r="AM471" s="1"/>
       <c r="AN471" s="83"/>
     </row>
-    <row r="472" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:40" s="26" customFormat="1">
       <c r="A472" s="3" t="s">
         <v>1093</v>
       </c>
@@ -55777,7 +55773,7 @@
       <c r="AM472" s="1"/>
       <c r="AN472" s="83"/>
     </row>
-    <row r="473" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:40" s="26" customFormat="1">
       <c r="A473" s="3" t="s">
         <v>1095</v>
       </c>
@@ -55860,7 +55856,7 @@
       <c r="AM473" s="1"/>
       <c r="AN473" s="83"/>
     </row>
-    <row r="474" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:40" s="26" customFormat="1">
       <c r="A474" s="3" t="s">
         <v>1097</v>
       </c>
@@ -55943,7 +55939,7 @@
       <c r="AM474" s="1"/>
       <c r="AN474" s="83"/>
     </row>
-    <row r="475" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:40" s="26" customFormat="1">
       <c r="A475" s="3" t="s">
         <v>1099</v>
       </c>
@@ -56026,7 +56022,7 @@
       <c r="AM475" s="1"/>
       <c r="AN475" s="83"/>
     </row>
-    <row r="476" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:40" s="26" customFormat="1">
       <c r="A476" s="3" t="s">
         <v>1101</v>
       </c>
@@ -56109,7 +56105,7 @@
       <c r="AM476" s="1"/>
       <c r="AN476" s="83"/>
     </row>
-    <row r="477" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:40" s="26" customFormat="1">
       <c r="A477" s="3" t="s">
         <v>1103</v>
       </c>
@@ -56196,7 +56192,7 @@
       <c r="AM477" s="1"/>
       <c r="AN477" s="83"/>
     </row>
-    <row r="478" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:40" s="26" customFormat="1">
       <c r="A478" s="3" t="s">
         <v>1104</v>
       </c>
@@ -56283,7 +56279,7 @@
       <c r="AM478" s="1"/>
       <c r="AN478" s="83"/>
     </row>
-    <row r="479" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:40" s="26" customFormat="1">
       <c r="A479" s="3" t="s">
         <v>1105</v>
       </c>
@@ -56370,7 +56366,7 @@
       <c r="AM479" s="1"/>
       <c r="AN479" s="83"/>
     </row>
-    <row r="480" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:40" s="26" customFormat="1">
       <c r="A480" s="3" t="s">
         <v>1106</v>
       </c>
@@ -56453,7 +56449,7 @@
       <c r="AM480" s="1"/>
       <c r="AN480" s="83"/>
     </row>
-    <row r="481" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:40" s="26" customFormat="1">
       <c r="A481" s="3" t="s">
         <v>1108</v>
       </c>
@@ -56536,7 +56532,7 @@
       <c r="AM481" s="1"/>
       <c r="AN481" s="83"/>
     </row>
-    <row r="482" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:40" s="26" customFormat="1">
       <c r="A482" s="3" t="s">
         <v>1109</v>
       </c>
@@ -56619,7 +56615,7 @@
       <c r="AM482" s="1"/>
       <c r="AN482" s="83"/>
     </row>
-    <row r="483" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:40" s="26" customFormat="1">
       <c r="A483" s="3" t="s">
         <v>1110</v>
       </c>
@@ -56706,7 +56702,7 @@
       <c r="AM483" s="1"/>
       <c r="AN483" s="83"/>
     </row>
-    <row r="484" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:40" s="26" customFormat="1">
       <c r="A484" s="3" t="s">
         <v>1111</v>
       </c>
@@ -56793,7 +56789,7 @@
       <c r="AM484" s="1"/>
       <c r="AN484" s="83"/>
     </row>
-    <row r="485" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:40" s="26" customFormat="1">
       <c r="A485" s="3" t="s">
         <v>1112</v>
       </c>
@@ -56876,7 +56872,7 @@
       <c r="AM485" s="1"/>
       <c r="AN485" s="83"/>
     </row>
-    <row r="486" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:40" s="26" customFormat="1">
       <c r="A486" s="22" t="s">
         <v>1114</v>
       </c>
@@ -56959,7 +56955,7 @@
       <c r="AM486" s="1"/>
       <c r="AN486" s="83"/>
     </row>
-    <row r="487" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:40" s="26" customFormat="1">
       <c r="A487" s="22" t="s">
         <v>1115</v>
       </c>
@@ -57042,7 +57038,7 @@
       <c r="AM487" s="1"/>
       <c r="AN487" s="83"/>
     </row>
-    <row r="488" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:40" s="26" customFormat="1">
       <c r="A488" s="22" t="s">
         <v>1117</v>
       </c>
@@ -57125,7 +57121,7 @@
       <c r="AM488" s="1"/>
       <c r="AN488" s="83"/>
     </row>
-    <row r="489" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:40" s="26" customFormat="1">
       <c r="A489" s="22" t="s">
         <v>1118</v>
       </c>
@@ -57208,7 +57204,7 @@
       <c r="AM489" s="1"/>
       <c r="AN489" s="83"/>
     </row>
-    <row r="490" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:40" s="26" customFormat="1">
       <c r="A490" s="22" t="s">
         <v>1119</v>
       </c>
@@ -57291,7 +57287,7 @@
       <c r="AM490" s="1"/>
       <c r="AN490" s="83"/>
     </row>
-    <row r="491" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:40" s="26" customFormat="1">
       <c r="A491" s="22" t="s">
         <v>1120</v>
       </c>
@@ -57382,7 +57378,7 @@
       <c r="AM491" s="1"/>
       <c r="AN491" s="83"/>
     </row>
-    <row r="492" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:40" s="26" customFormat="1">
       <c r="A492" s="22" t="s">
         <v>453</v>
       </c>
@@ -57461,7 +57457,7 @@
       <c r="AM492" s="1"/>
       <c r="AN492" s="83"/>
     </row>
-    <row r="493" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:40" s="26" customFormat="1">
       <c r="A493" s="22" t="s">
         <v>1123</v>
       </c>
@@ -57530,7 +57526,7 @@
       <c r="AM493" s="1"/>
       <c r="AN493" s="83"/>
     </row>
-    <row r="494" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:40" s="26" customFormat="1">
       <c r="A494" s="22" t="s">
         <v>1125</v>
       </c>
@@ -57599,7 +57595,7 @@
       <c r="AM494" s="1"/>
       <c r="AN494" s="83"/>
     </row>
-    <row r="495" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:40" s="26" customFormat="1">
       <c r="A495" s="22" t="s">
         <v>1126</v>
       </c>
@@ -57668,7 +57664,7 @@
       <c r="AM495" s="1"/>
       <c r="AN495" s="83"/>
     </row>
-    <row r="496" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:40" s="26" customFormat="1">
       <c r="A496" s="22" t="s">
         <v>1127</v>
       </c>
@@ -57737,7 +57733,7 @@
       <c r="AM496" s="1"/>
       <c r="AN496" s="83"/>
     </row>
-    <row r="497" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:41" s="26" customFormat="1">
       <c r="A497" s="22" t="s">
         <v>1128</v>
       </c>
@@ -57806,7 +57802,7 @@
       <c r="AM497" s="1"/>
       <c r="AN497" s="83"/>
     </row>
-    <row r="498" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:41" s="26" customFormat="1" ht="20.45" hidden="1">
       <c r="A498" s="19" t="s">
         <v>1129</v>
       </c>
@@ -57921,7 +57917,7 @@
       </c>
       <c r="AO498" s="81"/>
     </row>
-    <row r="499" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A499" s="19" t="s">
         <v>1136</v>
       </c>
@@ -58036,7 +58032,7 @@
       </c>
       <c r="AO499" s="81"/>
     </row>
-    <row r="500" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A500" s="19" t="s">
         <v>1141</v>
       </c>
@@ -58149,7 +58145,7 @@
       </c>
       <c r="AO500" s="81"/>
     </row>
-    <row r="501" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A501" s="19" t="s">
         <v>1147</v>
       </c>
@@ -58264,7 +58260,7 @@
       </c>
       <c r="AO501" s="81"/>
     </row>
-    <row r="502" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:41" s="26" customFormat="1" ht="20.45" hidden="1">
       <c r="A502" s="19" t="s">
         <v>1150</v>
       </c>
@@ -58379,7 +58375,7 @@
       </c>
       <c r="AO502" s="81"/>
     </row>
-    <row r="503" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A503" s="19" t="s">
         <v>1154</v>
       </c>
@@ -58494,7 +58490,7 @@
       </c>
       <c r="AO503" s="81"/>
     </row>
-    <row r="504" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A504" s="19" t="s">
         <v>1158</v>
       </c>
@@ -58596,7 +58592,7 @@
       <c r="AN504" s="83"/>
       <c r="AO504" s="81"/>
     </row>
-    <row r="505" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A505" s="19" t="s">
         <v>1162</v>
       </c>
@@ -58711,7 +58707,7 @@
       </c>
       <c r="AO505" s="81"/>
     </row>
-    <row r="506" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A506" s="19" t="s">
         <v>1166</v>
       </c>
@@ -58826,7 +58822,7 @@
       </c>
       <c r="AO506" s="81"/>
     </row>
-    <row r="507" spans="1:41" s="26" customFormat="1" ht="30.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:41" s="26" customFormat="1" ht="30.6" hidden="1">
       <c r="A507" s="19" t="s">
         <v>1169</v>
       </c>
@@ -58941,7 +58937,7 @@
       </c>
       <c r="AO507" s="81"/>
     </row>
-    <row r="508" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A508" s="19" t="s">
         <v>1172</v>
       </c>
@@ -59046,7 +59042,7 @@
       <c r="AN508" s="83"/>
       <c r="AO508" s="81"/>
     </row>
-    <row r="509" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A509" s="19" t="s">
         <v>1174</v>
       </c>
@@ -59161,7 +59157,7 @@
       </c>
       <c r="AO509" s="81"/>
     </row>
-    <row r="510" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A510" s="19" t="s">
         <v>1177</v>
       </c>
@@ -59267,7 +59263,7 @@
       </c>
       <c r="AO510" s="81"/>
     </row>
-    <row r="511" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A511" s="19" t="s">
         <v>1179</v>
       </c>
@@ -59370,7 +59366,7 @@
       <c r="AN511" s="83"/>
       <c r="AO511" s="81"/>
     </row>
-    <row r="512" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A512" s="19" t="s">
         <v>1181</v>
       </c>
@@ -59485,7 +59481,7 @@
       </c>
       <c r="AO512" s="81"/>
     </row>
-    <row r="513" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:41" s="26" customFormat="1" ht="20.45" hidden="1">
       <c r="A513" s="19" t="s">
         <v>1184</v>
       </c>
@@ -59600,7 +59596,7 @@
       </c>
       <c r="AO513" s="81"/>
     </row>
-    <row r="514" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A514" s="19" t="s">
         <v>1187</v>
       </c>
@@ -59715,7 +59711,7 @@
       </c>
       <c r="AO514" s="81"/>
     </row>
-    <row r="515" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A515" s="19" t="s">
         <v>1190</v>
       </c>
@@ -59830,7 +59826,7 @@
       </c>
       <c r="AO515" s="81"/>
     </row>
-    <row r="516" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A516" s="19" t="s">
         <v>1193</v>
       </c>
@@ -59943,7 +59939,7 @@
       </c>
       <c r="AO516" s="81"/>
     </row>
-    <row r="517" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:41" s="26" customFormat="1" ht="20.45" hidden="1">
       <c r="A517" s="19" t="s">
         <v>388</v>
       </c>
@@ -60058,7 +60054,7 @@
       </c>
       <c r="AO517" s="81"/>
     </row>
-    <row r="518" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:41" s="26" customFormat="1">
       <c r="A518" s="19" t="s">
         <v>1198</v>
       </c>
@@ -60142,7 +60138,7 @@
       </c>
       <c r="AO518" s="81"/>
     </row>
-    <row r="519" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:41" s="26" customFormat="1">
       <c r="A519" s="19" t="s">
         <v>1199</v>
       </c>
@@ -60164,7 +60160,9 @@
       <c r="O519" s="6"/>
       <c r="P519" s="6"/>
       <c r="Q519" s="27"/>
-      <c r="R519" s="28"/>
+      <c r="R519" s="28" t="s">
+        <v>151</v>
+      </c>
       <c r="S519" s="6"/>
       <c r="T519" s="1"/>
       <c r="U519" s="1"/>
@@ -60210,7 +60208,7 @@
       </c>
       <c r="AO519" s="81"/>
     </row>
-    <row r="520" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A520" s="19" t="s">
         <v>1200</v>
       </c>
@@ -60325,7 +60323,7 @@
       </c>
       <c r="AO520" s="81"/>
     </row>
-    <row r="521" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A521" s="19" t="s">
         <v>1205</v>
       </c>
@@ -60436,7 +60434,7 @@
       </c>
       <c r="AO521" s="81"/>
     </row>
-    <row r="522" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:41" s="26" customFormat="1" ht="20.45" hidden="1">
       <c r="A522" s="19" t="s">
         <v>1207</v>
       </c>
@@ -60551,7 +60549,7 @@
       </c>
       <c r="AO522" s="81"/>
     </row>
-    <row r="523" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A523" s="19" t="s">
         <v>1210</v>
       </c>
@@ -60656,7 +60654,7 @@
       <c r="AN523" s="83"/>
       <c r="AO523" s="81"/>
     </row>
-    <row r="524" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A524" s="19" t="s">
         <v>1214</v>
       </c>
@@ -60769,7 +60767,7 @@
       </c>
       <c r="AO524" s="81"/>
     </row>
-    <row r="525" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A525" s="19" t="s">
         <v>1218</v>
       </c>
@@ -60870,7 +60868,7 @@
       <c r="AN525" s="83"/>
       <c r="AO525" s="81"/>
     </row>
-    <row r="526" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A526" s="19" t="s">
         <v>1221</v>
       </c>
@@ -60985,7 +60983,7 @@
       </c>
       <c r="AO526" s="81"/>
     </row>
-    <row r="527" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A527" s="19" t="s">
         <v>1224</v>
       </c>
@@ -61100,7 +61098,7 @@
       </c>
       <c r="AO527" s="81"/>
     </row>
-    <row r="528" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A528" s="19" t="s">
         <v>1228</v>
       </c>
@@ -61215,7 +61213,7 @@
       </c>
       <c r="AO528" s="81"/>
     </row>
-    <row r="529" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:41" s="26" customFormat="1" ht="20.45" hidden="1">
       <c r="A529" s="19" t="s">
         <v>1231</v>
       </c>
@@ -61331,7 +61329,7 @@
       </c>
       <c r="AO529" s="81"/>
     </row>
-    <row r="530" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A530" s="19" t="s">
         <v>723</v>
       </c>
@@ -61431,7 +61429,7 @@
       <c r="AN530" s="83"/>
       <c r="AO530" s="81"/>
     </row>
-    <row r="531" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A531" s="19" t="s">
         <v>1234</v>
       </c>
@@ -61544,7 +61542,7 @@
       </c>
       <c r="AO531" s="81"/>
     </row>
-    <row r="532" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A532" s="19" t="s">
         <v>1237</v>
       </c>
@@ -61648,7 +61646,7 @@
       <c r="AN532" s="83"/>
       <c r="AO532" s="81"/>
     </row>
-    <row r="533" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A533" s="19" t="s">
         <v>1239</v>
       </c>
@@ -61752,7 +61750,7 @@
       <c r="AN533" s="83"/>
       <c r="AO533" s="81"/>
     </row>
-    <row r="534" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A534" s="19" t="s">
         <v>1241</v>
       </c>
@@ -61867,7 +61865,7 @@
       </c>
       <c r="AO534" s="81"/>
     </row>
-    <row r="535" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A535" s="19" t="s">
         <v>1245</v>
       </c>
@@ -61978,7 +61976,7 @@
       <c r="AN535" s="83"/>
       <c r="AO535" s="81"/>
     </row>
-    <row r="536" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A536" s="19" t="s">
         <v>1247</v>
       </c>
@@ -62082,7 +62080,7 @@
       <c r="AN536" s="83"/>
       <c r="AO536" s="81"/>
     </row>
-    <row r="537" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A537" s="19" t="s">
         <v>734</v>
       </c>
@@ -62195,7 +62193,7 @@
       </c>
       <c r="AO537" s="81"/>
     </row>
-    <row r="538" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A538" s="19" t="s">
         <v>1251</v>
       </c>
@@ -62307,7 +62305,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="539" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A539" s="19" t="s">
         <v>1253</v>
       </c>
@@ -62421,7 +62419,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="540" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A540" s="19" t="s">
         <v>1256</v>
       </c>
@@ -62524,7 +62522,7 @@
       <c r="AM540" s="1"/>
       <c r="AN540" s="83"/>
     </row>
-    <row r="541" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A541" s="19" t="s">
         <v>719</v>
       </c>
@@ -62623,7 +62621,7 @@
       <c r="AM541" s="1"/>
       <c r="AN541" s="83"/>
     </row>
-    <row r="542" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A542" s="19" t="s">
         <v>1259</v>
       </c>
@@ -62737,7 +62735,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="543" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A543" s="19" t="s">
         <v>1261</v>
       </c>
@@ -62840,7 +62838,7 @@
       <c r="AM543" s="1"/>
       <c r="AN543" s="83"/>
     </row>
-    <row r="544" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A544" s="19" t="s">
         <v>1263</v>
       </c>
@@ -62954,7 +62952,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="545" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A545" s="19" t="s">
         <v>1266</v>
       </c>
@@ -63068,7 +63066,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="546" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A546" s="19" t="s">
         <v>1268</v>
       </c>
@@ -63182,7 +63180,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="547" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A547" s="19" t="s">
         <v>1270</v>
       </c>
@@ -63285,7 +63283,7 @@
       <c r="AM547" s="1"/>
       <c r="AN547" s="83"/>
     </row>
-    <row r="548" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A548" s="19" t="s">
         <v>1271</v>
       </c>
@@ -63399,7 +63397,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="549" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A549" s="19" t="s">
         <v>1274</v>
       </c>
@@ -63502,7 +63500,7 @@
       <c r="AM549" s="1"/>
       <c r="AN549" s="83"/>
     </row>
-    <row r="550" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A550" s="19" t="s">
         <v>1275</v>
       </c>
@@ -63605,7 +63603,7 @@
       <c r="AM550" s="1"/>
       <c r="AN550" s="83"/>
     </row>
-    <row r="551" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A551" s="19" t="s">
         <v>1277</v>
       </c>
@@ -63708,7 +63706,7 @@
       <c r="AM551" s="1"/>
       <c r="AN551" s="83"/>
     </row>
-    <row r="552" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A552" s="19" t="s">
         <v>738</v>
       </c>
@@ -63809,7 +63807,7 @@
       <c r="AM552" s="1"/>
       <c r="AN552" s="83"/>
     </row>
-    <row r="553" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A553" s="19" t="s">
         <v>1278</v>
       </c>
@@ -63923,7 +63921,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="554" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A554" s="19" t="s">
         <v>1282</v>
       </c>
@@ -64026,7 +64024,7 @@
       <c r="AM554" s="1"/>
       <c r="AN554" s="83"/>
     </row>
-    <row r="555" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A555" s="19" t="s">
         <v>1283</v>
       </c>
@@ -64127,7 +64125,7 @@
       <c r="AM555" s="1"/>
       <c r="AN555" s="83"/>
     </row>
-    <row r="556" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A556" s="19" t="s">
         <v>1284</v>
       </c>
@@ -64241,7 +64239,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="557" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A557" s="19" t="s">
         <v>1287</v>
       </c>
@@ -64344,7 +64342,7 @@
       <c r="AM557" s="1"/>
       <c r="AN557" s="83"/>
     </row>
-    <row r="558" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A558" s="19" t="s">
         <v>1289</v>
       </c>
@@ -64445,7 +64443,7 @@
       <c r="AM558" s="1"/>
       <c r="AN558" s="83"/>
     </row>
-    <row r="559" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A559" s="19" t="s">
         <v>1291</v>
       </c>
@@ -64546,7 +64544,7 @@
       <c r="AM559" s="1"/>
       <c r="AN559" s="83"/>
     </row>
-    <row r="560" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A560" s="19" t="s">
         <v>1293</v>
       </c>
@@ -64658,7 +64656,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="561" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A561" s="19" t="s">
         <v>586</v>
       </c>
@@ -64761,7 +64759,7 @@
       <c r="AM561" s="1"/>
       <c r="AN561" s="83"/>
     </row>
-    <row r="562" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A562" s="19" t="s">
         <v>1296</v>
       </c>
@@ -64875,7 +64873,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="563" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A563" s="19" t="s">
         <v>1298</v>
       </c>
@@ -64989,7 +64987,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="564" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A564" s="19" t="s">
         <v>1301</v>
       </c>
@@ -65101,7 +65099,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="565" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A565" s="19" t="s">
         <v>1304</v>
       </c>
@@ -65202,7 +65200,7 @@
       <c r="AM565" s="1"/>
       <c r="AN565" s="83"/>
     </row>
-    <row r="566" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A566" s="19" t="s">
         <v>1306</v>
       </c>
@@ -65305,7 +65303,7 @@
       <c r="AM566" s="1"/>
       <c r="AN566" s="83"/>
     </row>
-    <row r="567" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A567" s="32" t="s">
         <v>1308</v>
       </c>
@@ -65406,7 +65404,7 @@
       <c r="AM567" s="1"/>
       <c r="AN567" s="83"/>
     </row>
-    <row r="568" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A568" s="19" t="s">
         <v>1310</v>
       </c>
@@ -65509,7 +65507,7 @@
       <c r="AM568" s="1"/>
       <c r="AN568" s="83"/>
     </row>
-    <row r="569" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A569" s="19" t="s">
         <v>1312</v>
       </c>
@@ -65623,7 +65621,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="570" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A570" s="19" t="s">
         <v>1315</v>
       </c>
@@ -65724,7 +65722,7 @@
       <c r="AM570" s="1"/>
       <c r="AN570" s="83"/>
     </row>
-    <row r="571" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A571" s="19" t="s">
         <v>1317</v>
       </c>
@@ -65825,7 +65823,7 @@
       <c r="AM571" s="1"/>
       <c r="AN571" s="83"/>
     </row>
-    <row r="572" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A572" s="19" t="s">
         <v>1318</v>
       </c>
@@ -65926,7 +65924,7 @@
       <c r="AM572" s="1"/>
       <c r="AN572" s="83"/>
     </row>
-    <row r="573" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A573" s="19" t="s">
         <v>1320</v>
       </c>
@@ -66029,7 +66027,7 @@
       <c r="AM573" s="1"/>
       <c r="AN573" s="83"/>
     </row>
-    <row r="574" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A574" s="19" t="s">
         <v>1322</v>
       </c>
@@ -66132,7 +66130,7 @@
       <c r="AM574" s="1"/>
       <c r="AN574" s="83"/>
     </row>
-    <row r="575" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A575" s="19" t="s">
         <v>1325</v>
       </c>
@@ -66235,7 +66233,7 @@
       <c r="AM575" s="1"/>
       <c r="AN575" s="83"/>
     </row>
-    <row r="576" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A576" s="19" t="s">
         <v>1327</v>
       </c>
@@ -66338,7 +66336,7 @@
       <c r="AM576" s="1"/>
       <c r="AN576" s="83"/>
     </row>
-    <row r="577" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A577" s="19" t="s">
         <v>1329</v>
       </c>
@@ -66441,7 +66439,7 @@
       <c r="AM577" s="1"/>
       <c r="AN577" s="83"/>
     </row>
-    <row r="578" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A578" s="19" t="s">
         <v>1331</v>
       </c>
@@ -66542,7 +66540,7 @@
       <c r="AM578" s="1"/>
       <c r="AN578" s="83"/>
     </row>
-    <row r="579" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A579" s="19" t="s">
         <v>1332</v>
       </c>
@@ -66645,7 +66643,7 @@
       <c r="AM579" s="1"/>
       <c r="AN579" s="83"/>
     </row>
-    <row r="580" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A580" s="19" t="s">
         <v>1334</v>
       </c>
@@ -66748,7 +66746,7 @@
       <c r="AM580" s="1"/>
       <c r="AN580" s="83"/>
     </row>
-    <row r="581" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A581" s="19" t="s">
         <v>1335</v>
       </c>
@@ -66851,7 +66849,7 @@
       <c r="AM581" s="1"/>
       <c r="AN581" s="83"/>
     </row>
-    <row r="582" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A582" s="19" t="s">
         <v>1337</v>
       </c>
@@ -66954,7 +66952,7 @@
       <c r="AM582" s="1"/>
       <c r="AN582" s="83"/>
     </row>
-    <row r="583" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A583" s="19" t="s">
         <v>1339</v>
       </c>
@@ -67017,7 +67015,7 @@
       <c r="AM583" s="1"/>
       <c r="AN583" s="83"/>
     </row>
-    <row r="584" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A584" s="19" t="s">
         <v>1340</v>
       </c>
@@ -67120,7 +67118,7 @@
       <c r="AM584" s="1"/>
       <c r="AN584" s="83"/>
     </row>
-    <row r="585" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A585" s="19" t="s">
         <v>1342</v>
       </c>
@@ -67223,7 +67221,7 @@
       <c r="AM585" s="1"/>
       <c r="AN585" s="83"/>
     </row>
-    <row r="586" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A586" s="19" t="s">
         <v>1344</v>
       </c>
@@ -67326,7 +67324,7 @@
       <c r="AM586" s="1"/>
       <c r="AN586" s="83"/>
     </row>
-    <row r="587" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A587" s="19" t="s">
         <v>1346</v>
       </c>
@@ -67425,7 +67423,7 @@
       <c r="AM587" s="1"/>
       <c r="AN587" s="83"/>
     </row>
-    <row r="588" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A588" s="19" t="s">
         <v>299</v>
       </c>
@@ -67524,7 +67522,7 @@
       <c r="AM588" s="1"/>
       <c r="AN588" s="83"/>
     </row>
-    <row r="589" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A589" s="19" t="s">
         <v>1349</v>
       </c>
@@ -67627,7 +67625,7 @@
       <c r="AM589" s="1"/>
       <c r="AN589" s="83"/>
     </row>
-    <row r="590" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A590" s="19" t="s">
         <v>1351</v>
       </c>
@@ -67730,7 +67728,7 @@
       <c r="AM590" s="1"/>
       <c r="AN590" s="83"/>
     </row>
-    <row r="591" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A591" s="22" t="s">
         <v>1353</v>
       </c>
@@ -67805,7 +67803,7 @@
       <c r="AM591" s="1"/>
       <c r="AN591" s="83"/>
     </row>
-    <row r="592" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A592" s="22" t="s">
         <v>1356</v>
       </c>
@@ -67878,7 +67876,7 @@
       <c r="AM592" s="1"/>
       <c r="AN592" s="83"/>
     </row>
-    <row r="593" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A593" s="22" t="s">
         <v>1359</v>
       </c>
@@ -67951,7 +67949,7 @@
       <c r="AM593" s="1"/>
       <c r="AN593" s="83"/>
     </row>
-    <row r="594" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A594" s="22" t="s">
         <v>1360</v>
       </c>
@@ -68024,7 +68022,7 @@
       <c r="AM594" s="1"/>
       <c r="AN594" s="83"/>
     </row>
-    <row r="595" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A595" s="22" t="s">
         <v>647</v>
       </c>
@@ -68097,7 +68095,7 @@
       <c r="AM595" s="1"/>
       <c r="AN595" s="83"/>
     </row>
-    <row r="596" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A596" s="22" t="s">
         <v>1363</v>
       </c>
@@ -68170,7 +68168,7 @@
       <c r="AM596" s="1"/>
       <c r="AN596" s="83"/>
     </row>
-    <row r="597" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A597" s="22" t="s">
         <v>1364</v>
       </c>
@@ -68243,7 +68241,7 @@
       <c r="AM597" s="1"/>
       <c r="AN597" s="83"/>
     </row>
-    <row r="598" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A598" s="22" t="s">
         <v>1365</v>
       </c>
@@ -68316,7 +68314,7 @@
       <c r="AM598" s="1"/>
       <c r="AN598" s="83"/>
     </row>
-    <row r="599" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A599" s="22" t="s">
         <v>1368</v>
       </c>
@@ -68389,7 +68387,7 @@
       <c r="AM599" s="1"/>
       <c r="AN599" s="83"/>
     </row>
-    <row r="600" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A600" s="22" t="s">
         <v>1369</v>
       </c>
@@ -68462,7 +68460,7 @@
       <c r="AM600" s="1"/>
       <c r="AN600" s="83"/>
     </row>
-    <row r="601" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A601" s="22" t="s">
         <v>1371</v>
       </c>
@@ -68535,7 +68533,7 @@
       <c r="AM601" s="1"/>
       <c r="AN601" s="83"/>
     </row>
-    <row r="602" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A602" s="22" t="s">
         <v>868</v>
       </c>
@@ -68608,7 +68606,7 @@
       <c r="AM602" s="1"/>
       <c r="AN602" s="83"/>
     </row>
-    <row r="603" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A603" s="22" t="s">
         <v>1373</v>
       </c>
@@ -68681,7 +68679,7 @@
       <c r="AM603" s="1"/>
       <c r="AN603" s="83"/>
     </row>
-    <row r="604" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A604" s="22" t="s">
         <v>1374</v>
       </c>
@@ -68754,7 +68752,7 @@
       <c r="AM604" s="1"/>
       <c r="AN604" s="83"/>
     </row>
-    <row r="605" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A605" s="22" t="s">
         <v>655</v>
       </c>
@@ -68827,7 +68825,7 @@
       <c r="AM605" s="1"/>
       <c r="AN605" s="83"/>
     </row>
-    <row r="606" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A606" s="22" t="s">
         <v>275</v>
       </c>
@@ -68902,7 +68900,7 @@
       <c r="AM606" s="1"/>
       <c r="AN606" s="83"/>
     </row>
-    <row r="607" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A607" s="22" t="s">
         <v>1377</v>
       </c>
@@ -68975,7 +68973,7 @@
       <c r="AM607" s="1"/>
       <c r="AN607" s="83"/>
     </row>
-    <row r="608" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A608" s="22" t="s">
         <v>1378</v>
       </c>
@@ -69048,7 +69046,7 @@
       <c r="AM608" s="1"/>
       <c r="AN608" s="83"/>
     </row>
-    <row r="609" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A609" s="22" t="s">
         <v>378</v>
       </c>
@@ -69121,7 +69119,7 @@
       <c r="AM609" s="1"/>
       <c r="AN609" s="83"/>
     </row>
-    <row r="610" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A610" s="22" t="s">
         <v>370</v>
       </c>
@@ -69194,7 +69192,7 @@
       <c r="AM610" s="1"/>
       <c r="AN610" s="83"/>
     </row>
-    <row r="611" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A611" s="22" t="s">
         <v>1379</v>
       </c>
@@ -69267,7 +69265,7 @@
       <c r="AM611" s="1"/>
       <c r="AN611" s="83"/>
     </row>
-    <row r="612" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A612" s="22" t="s">
         <v>1380</v>
       </c>
@@ -69340,7 +69338,7 @@
       <c r="AM612" s="1"/>
       <c r="AN612" s="83"/>
     </row>
-    <row r="613" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A613" s="22" t="s">
         <v>1381</v>
       </c>
@@ -69413,7 +69411,7 @@
       <c r="AM613" s="1"/>
       <c r="AN613" s="83"/>
     </row>
-    <row r="614" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A614" s="22" t="s">
         <v>1383</v>
       </c>
@@ -69486,7 +69484,7 @@
       <c r="AM614" s="1"/>
       <c r="AN614" s="83"/>
     </row>
-    <row r="615" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A615" s="22" t="s">
         <v>672</v>
       </c>
@@ -69559,7 +69557,7 @@
       <c r="AM615" s="1"/>
       <c r="AN615" s="83"/>
     </row>
-    <row r="616" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A616" s="22" t="s">
         <v>1384</v>
       </c>
@@ -69632,7 +69630,7 @@
       <c r="AM616" s="1"/>
       <c r="AN616" s="83"/>
     </row>
-    <row r="617" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A617" s="22" t="s">
         <v>1386</v>
       </c>
@@ -69705,7 +69703,7 @@
       <c r="AM617" s="1"/>
       <c r="AN617" s="83"/>
     </row>
-    <row r="618" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A618" s="22" t="s">
         <v>880</v>
       </c>
@@ -69778,7 +69776,7 @@
       <c r="AM618" s="1"/>
       <c r="AN618" s="83"/>
     </row>
-    <row r="619" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A619" s="22" t="s">
         <v>907</v>
       </c>
@@ -69851,7 +69849,7 @@
       <c r="AM619" s="1"/>
       <c r="AN619" s="83"/>
     </row>
-    <row r="620" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A620" s="22" t="s">
         <v>877</v>
       </c>
@@ -69924,7 +69922,7 @@
       <c r="AM620" s="1"/>
       <c r="AN620" s="83"/>
     </row>
-    <row r="621" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A621" s="22" t="s">
         <v>1389</v>
       </c>
@@ -69997,7 +69995,7 @@
       <c r="AM621" s="1"/>
       <c r="AN621" s="83"/>
     </row>
-    <row r="622" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A622" s="22" t="s">
         <v>1390</v>
       </c>
@@ -70070,7 +70068,7 @@
       <c r="AM622" s="1"/>
       <c r="AN622" s="83"/>
     </row>
-    <row r="623" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A623" s="22" t="s">
         <v>859</v>
       </c>
@@ -70143,7 +70141,7 @@
       <c r="AM623" s="1"/>
       <c r="AN623" s="83"/>
     </row>
-    <row r="624" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A624" s="22" t="s">
         <v>1392</v>
       </c>
@@ -70216,7 +70214,7 @@
       <c r="AM624" s="1"/>
       <c r="AN624" s="83"/>
     </row>
-    <row r="625" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A625" s="22" t="s">
         <v>1393</v>
       </c>
@@ -70289,7 +70287,7 @@
       <c r="AM625" s="1"/>
       <c r="AN625" s="83"/>
     </row>
-    <row r="626" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A626" s="22" t="s">
         <v>406</v>
       </c>
@@ -70362,7 +70360,7 @@
       <c r="AM626" s="1"/>
       <c r="AN626" s="83"/>
     </row>
-    <row r="627" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A627" s="22" t="s">
         <v>1396</v>
       </c>
@@ -70435,7 +70433,7 @@
       <c r="AM627" s="1"/>
       <c r="AN627" s="83"/>
     </row>
-    <row r="628" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A628" s="22" t="s">
         <v>921</v>
       </c>
@@ -70508,7 +70506,7 @@
       <c r="AM628" s="1"/>
       <c r="AN628" s="83"/>
     </row>
-    <row r="629" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A629" s="22" t="s">
         <v>1398</v>
       </c>
@@ -70581,7 +70579,7 @@
       <c r="AM629" s="1"/>
       <c r="AN629" s="83"/>
     </row>
-    <row r="630" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A630" s="22" t="s">
         <v>892</v>
       </c>
@@ -70654,7 +70652,7 @@
       <c r="AM630" s="1"/>
       <c r="AN630" s="83"/>
     </row>
-    <row r="631" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A631" s="22" t="s">
         <v>1400</v>
       </c>
@@ -70727,7 +70725,7 @@
       <c r="AM631" s="1"/>
       <c r="AN631" s="83"/>
     </row>
-    <row r="632" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A632" s="22" t="s">
         <v>1401</v>
       </c>
@@ -70800,7 +70798,7 @@
       <c r="AM632" s="1"/>
       <c r="AN632" s="83"/>
     </row>
-    <row r="633" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A633" s="22" t="s">
         <v>1403</v>
       </c>
@@ -70873,7 +70871,7 @@
       <c r="AM633" s="1"/>
       <c r="AN633" s="83"/>
     </row>
-    <row r="634" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A634" s="22" t="s">
         <v>1404</v>
       </c>
@@ -70946,7 +70944,7 @@
       <c r="AM634" s="1"/>
       <c r="AN634" s="83"/>
     </row>
-    <row r="635" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A635" s="22" t="s">
         <v>1405</v>
       </c>
@@ -71019,7 +71017,7 @@
       <c r="AM635" s="1"/>
       <c r="AN635" s="83"/>
     </row>
-    <row r="636" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A636" s="22" t="s">
         <v>1406</v>
       </c>
@@ -71092,7 +71090,7 @@
       <c r="AM636" s="1"/>
       <c r="AN636" s="83"/>
     </row>
-    <row r="637" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A637" s="22" t="s">
         <v>1407</v>
       </c>
@@ -71165,7 +71163,7 @@
       <c r="AM637" s="1"/>
       <c r="AN637" s="83"/>
     </row>
-    <row r="638" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A638" s="22" t="s">
         <v>1409</v>
       </c>
@@ -71238,7 +71236,7 @@
       <c r="AM638" s="1"/>
       <c r="AN638" s="83"/>
     </row>
-    <row r="639" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A639" s="22" t="s">
         <v>1410</v>
       </c>
@@ -71311,7 +71309,7 @@
       <c r="AM639" s="1"/>
       <c r="AN639" s="83"/>
     </row>
-    <row r="640" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A640" s="22" t="s">
         <v>1411</v>
       </c>
@@ -71384,7 +71382,7 @@
       <c r="AM640" s="1"/>
       <c r="AN640" s="83"/>
     </row>
-    <row r="641" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A641" s="22" t="s">
         <v>898</v>
       </c>
@@ -71457,7 +71455,7 @@
       <c r="AM641" s="1"/>
       <c r="AN641" s="83"/>
     </row>
-    <row r="642" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A642" s="22" t="s">
         <v>967</v>
       </c>
@@ -71530,7 +71528,7 @@
       <c r="AM642" s="1"/>
       <c r="AN642" s="83"/>
     </row>
-    <row r="643" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A643" s="22" t="s">
         <v>1412</v>
       </c>
@@ -71603,7 +71601,7 @@
       <c r="AM643" s="1"/>
       <c r="AN643" s="83"/>
     </row>
-    <row r="644" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A644" s="22" t="s">
         <v>1414</v>
       </c>
@@ -71676,7 +71674,7 @@
       <c r="AM644" s="1"/>
       <c r="AN644" s="83"/>
     </row>
-    <row r="645" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A645" s="22" t="s">
         <v>874</v>
       </c>
@@ -71749,7 +71747,7 @@
       <c r="AM645" s="1"/>
       <c r="AN645" s="83"/>
     </row>
-    <row r="646" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A646" s="22" t="s">
         <v>1415</v>
       </c>
@@ -71822,7 +71820,7 @@
       <c r="AM646" s="1"/>
       <c r="AN646" s="83"/>
     </row>
-    <row r="647" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A647" s="22" t="s">
         <v>946</v>
       </c>
@@ -71895,7 +71893,7 @@
       <c r="AM647" s="1"/>
       <c r="AN647" s="83"/>
     </row>
-    <row r="648" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A648" s="22" t="s">
         <v>1416</v>
       </c>
@@ -71968,7 +71966,7 @@
       <c r="AM648" s="1"/>
       <c r="AN648" s="83"/>
     </row>
-    <row r="649" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A649" s="22" t="s">
         <v>97</v>
       </c>
@@ -72043,7 +72041,7 @@
       <c r="AM649" s="1"/>
       <c r="AN649" s="83"/>
     </row>
-    <row r="650" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A650" s="22" t="s">
         <v>1419</v>
       </c>
@@ -72116,7 +72114,7 @@
       <c r="AM650" s="1"/>
       <c r="AN650" s="83"/>
     </row>
-    <row r="651" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A651" s="22" t="s">
         <v>1420</v>
       </c>
@@ -72187,7 +72185,7 @@
       <c r="AM651" s="1"/>
       <c r="AN651" s="83"/>
     </row>
-    <row r="652" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A652" s="22" t="s">
         <v>650</v>
       </c>
@@ -72260,7 +72258,7 @@
       <c r="AM652" s="1"/>
       <c r="AN652" s="83"/>
     </row>
-    <row r="653" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A653" s="22" t="s">
         <v>1421</v>
       </c>
@@ -72333,7 +72331,7 @@
       <c r="AM653" s="1"/>
       <c r="AN653" s="83"/>
     </row>
-    <row r="654" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A654" s="22" t="s">
         <v>1423</v>
       </c>
@@ -72406,7 +72404,7 @@
       <c r="AM654" s="1"/>
       <c r="AN654" s="83"/>
     </row>
-    <row r="655" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A655" s="22" t="s">
         <v>1424</v>
       </c>
@@ -72479,7 +72477,7 @@
       <c r="AM655" s="1"/>
       <c r="AN655" s="83"/>
     </row>
-    <row r="656" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A656" s="22" t="s">
         <v>1426</v>
       </c>
@@ -72552,7 +72550,7 @@
       <c r="AM656" s="1"/>
       <c r="AN656" s="83"/>
     </row>
-    <row r="657" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A657" s="22" t="s">
         <v>1427</v>
       </c>
@@ -72625,7 +72623,7 @@
       <c r="AM657" s="1"/>
       <c r="AN657" s="83"/>
     </row>
-    <row r="658" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A658" s="22" t="s">
         <v>1428</v>
       </c>
@@ -72698,7 +72696,7 @@
       <c r="AM658" s="1"/>
       <c r="AN658" s="83"/>
     </row>
-    <row r="659" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A659" s="22" t="s">
         <v>1429</v>
       </c>
@@ -72771,7 +72769,7 @@
       <c r="AM659" s="1"/>
       <c r="AN659" s="83"/>
     </row>
-    <row r="660" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A660" s="22" t="s">
         <v>1430</v>
       </c>
@@ -72844,7 +72842,7 @@
       <c r="AM660" s="1"/>
       <c r="AN660" s="83"/>
     </row>
-    <row r="661" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A661" s="22" t="s">
         <v>1431</v>
       </c>
@@ -72917,7 +72915,7 @@
       <c r="AM661" s="1"/>
       <c r="AN661" s="83"/>
     </row>
-    <row r="662" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A662" s="22" t="s">
         <v>1432</v>
       </c>
@@ -72990,7 +72988,7 @@
       <c r="AM662" s="1"/>
       <c r="AN662" s="83"/>
     </row>
-    <row r="663" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A663" s="22" t="s">
         <v>966</v>
       </c>
@@ -73063,7 +73061,7 @@
       <c r="AM663" s="1"/>
       <c r="AN663" s="83"/>
     </row>
-    <row r="664" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A664" s="22" t="s">
         <v>578</v>
       </c>
@@ -73146,7 +73144,7 @@
       <c r="AM664" s="1"/>
       <c r="AN664" s="83"/>
     </row>
-    <row r="665" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A665" s="22" t="s">
         <v>1435</v>
       </c>
@@ -73219,7 +73217,7 @@
       <c r="AM665" s="1"/>
       <c r="AN665" s="83"/>
     </row>
-    <row r="666" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A666" s="22" t="s">
         <v>1437</v>
       </c>
@@ -73292,7 +73290,7 @@
       <c r="AM666" s="1"/>
       <c r="AN666" s="83"/>
     </row>
-    <row r="667" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A667" s="22" t="s">
         <v>1439</v>
       </c>
@@ -73365,7 +73363,7 @@
       <c r="AM667" s="1"/>
       <c r="AN667" s="83"/>
     </row>
-    <row r="668" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A668" s="22" t="s">
         <v>1441</v>
       </c>
@@ -73438,7 +73436,7 @@
       <c r="AM668" s="1"/>
       <c r="AN668" s="83"/>
     </row>
-    <row r="669" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A669" s="22" t="s">
         <v>1442</v>
       </c>
@@ -73511,7 +73509,7 @@
       <c r="AM669" s="1"/>
       <c r="AN669" s="83"/>
     </row>
-    <row r="670" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A670" s="22" t="s">
         <v>1443</v>
       </c>
@@ -73584,7 +73582,7 @@
       <c r="AM670" s="1"/>
       <c r="AN670" s="83"/>
     </row>
-    <row r="671" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A671" s="22" t="s">
         <v>1445</v>
       </c>
@@ -73657,7 +73655,7 @@
       <c r="AM671" s="1"/>
       <c r="AN671" s="83"/>
     </row>
-    <row r="672" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A672" s="22" t="s">
         <v>1447</v>
       </c>
@@ -73730,7 +73728,7 @@
       <c r="AM672" s="1"/>
       <c r="AN672" s="83"/>
     </row>
-    <row r="673" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A673" s="22" t="s">
         <v>1448</v>
       </c>
@@ -73803,7 +73801,7 @@
       <c r="AM673" s="1"/>
       <c r="AN673" s="83"/>
     </row>
-    <row r="674" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A674" s="22" t="s">
         <v>1449</v>
       </c>
@@ -73874,7 +73872,7 @@
       <c r="AM674" s="1"/>
       <c r="AN674" s="83"/>
     </row>
-    <row r="675" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A675" s="22" t="s">
         <v>1450</v>
       </c>
@@ -73947,7 +73945,7 @@
       <c r="AM675" s="1"/>
       <c r="AN675" s="83"/>
     </row>
-    <row r="676" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A676" s="22" t="s">
         <v>1451</v>
       </c>
@@ -74020,7 +74018,7 @@
       <c r="AM676" s="1"/>
       <c r="AN676" s="83"/>
     </row>
-    <row r="677" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A677" s="22" t="s">
         <v>1452</v>
       </c>
@@ -74093,7 +74091,7 @@
       <c r="AM677" s="1"/>
       <c r="AN677" s="83"/>
     </row>
-    <row r="678" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A678" s="22" t="s">
         <v>1453</v>
       </c>
@@ -74166,7 +74164,7 @@
       <c r="AM678" s="1"/>
       <c r="AN678" s="83"/>
     </row>
-    <row r="679" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A679" s="22" t="s">
         <v>1454</v>
       </c>
@@ -74239,7 +74237,7 @@
       <c r="AM679" s="1"/>
       <c r="AN679" s="83"/>
     </row>
-    <row r="680" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A680" s="22" t="s">
         <v>1455</v>
       </c>
@@ -74312,7 +74310,7 @@
       <c r="AM680" s="1"/>
       <c r="AN680" s="83"/>
     </row>
-    <row r="681" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A681" s="22" t="s">
         <v>870</v>
       </c>
@@ -74385,7 +74383,7 @@
       <c r="AM681" s="1"/>
       <c r="AN681" s="83"/>
     </row>
-    <row r="682" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A682" s="22" t="s">
         <v>1456</v>
       </c>
@@ -74458,7 +74456,7 @@
       <c r="AM682" s="1"/>
       <c r="AN682" s="83"/>
     </row>
-    <row r="683" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A683" s="22" t="s">
         <v>1457</v>
       </c>
@@ -74531,7 +74529,7 @@
       <c r="AM683" s="1"/>
       <c r="AN683" s="83"/>
     </row>
-    <row r="684" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A684" s="22" t="s">
         <v>1458</v>
       </c>
@@ -74604,7 +74602,7 @@
       <c r="AM684" s="1"/>
       <c r="AN684" s="83"/>
     </row>
-    <row r="685" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A685" s="22" t="s">
         <v>1459</v>
       </c>
@@ -74677,7 +74675,7 @@
       <c r="AM685" s="1"/>
       <c r="AN685" s="83"/>
     </row>
-    <row r="686" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A686" s="22" t="s">
         <v>1460</v>
       </c>
@@ -74750,7 +74748,7 @@
       <c r="AM686" s="1"/>
       <c r="AN686" s="83"/>
     </row>
-    <row r="687" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A687" s="22" t="s">
         <v>1461</v>
       </c>
@@ -74823,7 +74821,7 @@
       <c r="AM687" s="1"/>
       <c r="AN687" s="83"/>
     </row>
-    <row r="688" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A688" s="22" t="s">
         <v>1462</v>
       </c>
@@ -74896,7 +74894,7 @@
       <c r="AM688" s="1"/>
       <c r="AN688" s="83"/>
     </row>
-    <row r="689" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A689" s="22" t="s">
         <v>1463</v>
       </c>
@@ -74969,7 +74967,7 @@
       <c r="AM689" s="1"/>
       <c r="AN689" s="83"/>
     </row>
-    <row r="690" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A690" s="22" t="s">
         <v>1464</v>
       </c>
@@ -75042,7 +75040,7 @@
       <c r="AM690" s="1"/>
       <c r="AN690" s="83"/>
     </row>
-    <row r="691" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A691" s="22" t="s">
         <v>1465</v>
       </c>
@@ -75115,7 +75113,7 @@
       <c r="AM691" s="1"/>
       <c r="AN691" s="83"/>
     </row>
-    <row r="692" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A692" s="22" t="s">
         <v>1466</v>
       </c>
@@ -75188,7 +75186,7 @@
       <c r="AM692" s="1"/>
       <c r="AN692" s="83"/>
     </row>
-    <row r="693" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A693" s="22" t="s">
         <v>1467</v>
       </c>
@@ -75261,7 +75259,7 @@
       <c r="AM693" s="1"/>
       <c r="AN693" s="83"/>
     </row>
-    <row r="694" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A694" s="22" t="s">
         <v>1468</v>
       </c>
@@ -75334,7 +75332,7 @@
       <c r="AM694" s="1"/>
       <c r="AN694" s="83"/>
     </row>
-    <row r="695" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A695" s="22" t="s">
         <v>1469</v>
       </c>
@@ -75407,7 +75405,7 @@
       <c r="AM695" s="1"/>
       <c r="AN695" s="83"/>
     </row>
-    <row r="696" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A696" s="22" t="s">
         <v>1470</v>
       </c>
@@ -75480,7 +75478,7 @@
       <c r="AM696" s="1"/>
       <c r="AN696" s="83"/>
     </row>
-    <row r="697" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A697" s="22" t="s">
         <v>1081</v>
       </c>
@@ -75553,7 +75551,7 @@
       <c r="AM697" s="1"/>
       <c r="AN697" s="83"/>
     </row>
-    <row r="698" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A698" s="22" t="s">
         <v>1472</v>
       </c>
@@ -75626,7 +75624,7 @@
       <c r="AM698" s="1"/>
       <c r="AN698" s="83"/>
     </row>
-    <row r="699" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A699" s="22" t="s">
         <v>1473</v>
       </c>
@@ -75699,7 +75697,7 @@
       <c r="AM699" s="1"/>
       <c r="AN699" s="83"/>
     </row>
-    <row r="700" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A700" s="22" t="s">
         <v>1474</v>
       </c>
@@ -75772,7 +75770,7 @@
       <c r="AM700" s="1"/>
       <c r="AN700" s="83"/>
     </row>
-    <row r="701" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A701" s="22" t="s">
         <v>1475</v>
       </c>
@@ -75845,7 +75843,7 @@
       <c r="AM701" s="1"/>
       <c r="AN701" s="83"/>
     </row>
-    <row r="702" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A702" s="22" t="s">
         <v>1476</v>
       </c>
@@ -75918,7 +75916,7 @@
       <c r="AM702" s="1"/>
       <c r="AN702" s="83"/>
     </row>
-    <row r="703" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A703" s="22" t="s">
         <v>1477</v>
       </c>
@@ -75991,7 +75989,7 @@
       <c r="AM703" s="1"/>
       <c r="AN703" s="83"/>
     </row>
-    <row r="704" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A704" s="22" t="s">
         <v>1109</v>
       </c>
@@ -76064,7 +76062,7 @@
       <c r="AM704" s="1"/>
       <c r="AN704" s="83"/>
     </row>
-    <row r="705" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A705" s="22" t="s">
         <v>1478</v>
       </c>
@@ -76137,7 +76135,7 @@
       <c r="AM705" s="1"/>
       <c r="AN705" s="83"/>
     </row>
-    <row r="706" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A706" s="22" t="s">
         <v>1479</v>
       </c>
@@ -76210,7 +76208,7 @@
       <c r="AM706" s="1"/>
       <c r="AN706" s="83"/>
     </row>
-    <row r="707" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A707" s="22" t="s">
         <v>1480</v>
       </c>
@@ -76283,7 +76281,7 @@
       <c r="AM707" s="1"/>
       <c r="AN707" s="83"/>
     </row>
-    <row r="708" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A708" s="22" t="s">
         <v>1481</v>
       </c>
@@ -76356,7 +76354,7 @@
       <c r="AM708" s="1"/>
       <c r="AN708" s="83"/>
     </row>
-    <row r="709" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A709" s="22" t="s">
         <v>1482</v>
       </c>
@@ -76429,7 +76427,7 @@
       <c r="AM709" s="1"/>
       <c r="AN709" s="83"/>
     </row>
-    <row r="710" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A710" s="22" t="s">
         <v>1483</v>
       </c>
@@ -76502,7 +76500,7 @@
       <c r="AM710" s="1"/>
       <c r="AN710" s="83"/>
     </row>
-    <row r="711" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:40" s="26" customFormat="1">
       <c r="A711" s="39"/>
       <c r="B711" s="40"/>
       <c r="C711" s="40"/>
@@ -76564,28 +76562,28 @@
       <c r="AM711" s="46"/>
       <c r="AN711" s="83"/>
     </row>
-    <row r="716" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:40">
       <c r="AA716" s="73"/>
       <c r="AB716" s="73"/>
       <c r="AC716" s="73"/>
       <c r="AN716" s="94"/>
     </row>
-    <row r="717" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:40">
       <c r="Z717" s="73"/>
       <c r="AA717" s="73"/>
       <c r="AB717" s="73"/>
       <c r="AC717" s="73"/>
       <c r="AN717" s="94"/>
     </row>
-    <row r="718" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:40">
       <c r="Z718" s="73"/>
       <c r="AA718" s="73"/>
       <c r="AB718" s="73"/>
     </row>
-    <row r="719" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:40">
       <c r="Z719" s="73"/>
     </row>
-    <row r="720" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:40">
       <c r="Z720" s="73"/>
       <c r="AA720" s="73"/>
       <c r="AB720" s="73"/>
@@ -76664,18 +76662,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D813743-8135-4F32-BACA-A0CD44F9427F}">
   <dimension ref="A1:F44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" s="69" t="s">
         <v>1485</v>
       </c>
@@ -76695,7 +76693,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>755</v>
       </c>
@@ -76720,7 +76718,7 @@
         <v>88880.437499999985</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>49</v>
       </c>
@@ -76745,13 +76743,13 @@
         <v>256393.97999999995</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>151</v>
       </c>
       <c r="B4" s="50">
         <f>COUNTIF(Controle!$R$4:$R$711,A4)</f>
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="52">
         <f>SUMIF(Controle!$R$4:$R$711,Formulas!A4,Controle!$Y$4:$Y$711)</f>
@@ -76767,10 +76765,10 @@
       </c>
       <c r="F4" s="66">
         <f>SUMIF(Controle!$R:$R,Formulas!A4,Controle!$AK:$AK)</f>
-        <v>133836.72333333336</v>
+        <v>136436.7233333333</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>187</v>
       </c>
@@ -76795,13 +76793,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" s="53" t="s">
         <v>1491</v>
       </c>
       <c r="B6" s="54">
         <f>SUM(B2:B5)</f>
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C6" s="55">
         <f t="shared" ref="C6:F6" si="1">SUM(C2:C5)</f>
@@ -76817,10 +76815,10 @@
       </c>
       <c r="F6" s="67">
         <f t="shared" si="1"/>
-        <v>479111.14083333325</v>
+        <v>481711.14083333325</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="A9" s="69" t="s">
         <v>1492</v>
       </c>
@@ -76837,7 +76835,7 @@
         <v>1496</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="A10" s="47" t="s">
         <v>764</v>
       </c>
@@ -76858,7 +76856,7 @@
         <v>163307.73333333334</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6">
       <c r="A11" s="47" t="s">
         <v>1133</v>
       </c>
@@ -76879,7 +76877,7 @@
         <v>101921.69083333333</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12" s="47" t="s">
         <v>752</v>
       </c>
@@ -76900,7 +76898,7 @@
         <v>33682.781666666669</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" s="47" t="s">
         <v>92</v>
       </c>
@@ -76921,7 +76919,7 @@
         <v>110026.7025</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="A14" s="47" t="s">
         <v>73</v>
       </c>
@@ -76942,7 +76940,7 @@
         <v>14192.72</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="A15" s="47" t="s">
         <v>45</v>
       </c>
@@ -76963,7 +76961,7 @@
         <v>18301.009999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="A16" s="47" t="s">
         <v>82</v>
       </c>
@@ -76984,7 +76982,7 @@
         <v>8786.4108333333334</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="A17" s="47" t="s">
         <v>1145</v>
       </c>
@@ -77005,7 +77003,7 @@
         <v>17038.2366666667</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18" s="47" t="s">
         <v>841</v>
       </c>
@@ -77026,7 +77024,7 @@
         <v>3342.1949999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19" s="47" t="s">
         <v>237</v>
       </c>
@@ -77047,7 +77045,7 @@
         <v>1642.21</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20" s="47" t="s">
         <v>1161</v>
       </c>
@@ -77068,7 +77066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21" s="47" t="s">
         <v>872</v>
       </c>
@@ -77089,7 +77087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5">
       <c r="A22" s="47" t="s">
         <v>356</v>
       </c>
@@ -77110,7 +77108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="A23" s="47" t="s">
         <v>223</v>
       </c>
@@ -77131,7 +77129,7 @@
         <v>4586.75</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5">
       <c r="A24" s="47" t="s">
         <v>1362</v>
       </c>
@@ -77152,7 +77150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5">
       <c r="A25" s="47" t="s">
         <v>220</v>
       </c>
@@ -77173,7 +77171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5">
       <c r="A26" s="47" t="s">
         <v>1220</v>
       </c>
@@ -77194,7 +77192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5">
       <c r="A27" s="47" t="s">
         <v>318</v>
       </c>
@@ -77215,7 +77213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5">
       <c r="A28" s="47" t="s">
         <v>349</v>
       </c>
@@ -77236,7 +77234,7 @@
         <v>1311.99</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5">
       <c r="A29" s="47" t="s">
         <v>253</v>
       </c>
@@ -77257,7 +77255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5">
       <c r="A30" s="47" t="s">
         <v>303</v>
       </c>
@@ -77278,7 +77276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5">
       <c r="A31" s="47" t="s">
         <v>879</v>
       </c>
@@ -77299,7 +77297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5">
       <c r="A32" s="47" t="s">
         <v>1358</v>
       </c>
@@ -77320,7 +77318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5">
       <c r="A33" s="47" t="s">
         <v>897</v>
       </c>
@@ -77341,7 +77339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5">
       <c r="A34" s="47" t="s">
         <v>1367</v>
       </c>
@@ -77362,7 +77360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5">
       <c r="A35" s="47" t="s">
         <v>925</v>
       </c>
@@ -77383,7 +77381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5">
       <c r="A36" s="47" t="s">
         <v>149</v>
       </c>
@@ -77404,7 +77402,7 @@
         <v>238.71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5">
       <c r="A37" s="47" t="s">
         <v>939</v>
       </c>
@@ -77425,7 +77423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5">
       <c r="A38" s="47" t="s">
         <v>1395</v>
       </c>
@@ -77446,7 +77444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5">
       <c r="A39" s="47" t="s">
         <v>1417</v>
       </c>
@@ -77467,7 +77465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5">
       <c r="A40" s="47"/>
       <c r="B40">
         <f>COUNTIF(Controle!L:L,Formulas!A41)</f>
@@ -77486,7 +77484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5">
       <c r="A41" s="47">
         <v>0</v>
       </c>
@@ -77507,7 +77505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5">
       <c r="A42" s="59" t="s">
         <v>1491</v>
       </c>
@@ -77528,12 +77526,12 @@
         <v>478379.14083333343</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5">
       <c r="A43" s="47"/>
       <c r="C43" s="57"/>
       <c r="D43" s="48"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5">
       <c r="A44" s="47"/>
     </row>
   </sheetData>
@@ -77551,14 +77549,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f5ab1930-d403-4c69-b2cd-8cc48f527d10" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c06ce65c-ed18-47f4-a957-afd315448c9c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -77757,54 +77753,24 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f5ab1930-d403-4c69-b2cd-8cc48f527d10" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c06ce65c-ed18-47f4-a957-afd315448c9c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE495743-F761-4961-A762-7A3D120C6961}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="c06ce65c-ed18-47f4-a957-afd315448c9c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f5ab1930-d403-4c69-b2cd-8cc48f527d10"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AE26D3A-03CC-4B3D-9F98-6F77A1AEA74E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59443FB2-AD94-4FFF-8817-F253987A64A5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c06ce65c-ed18-47f4-a957-afd315448c9c"/>
-    <ds:schemaRef ds:uri="f5ab1930-d403-4c69-b2cd-8cc48f527d10"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59443FB2-AD94-4FFF-8817-F253987A64A5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AE26D3A-03CC-4B3D-9F98-6F77A1AEA74E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE495743-F761-4961-A762-7A3D120C6961}"/>
 </file>
--- a/data/dados_atuais.xlsx
+++ b/data/dados_atuais.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="EsteLivro"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,15 +10,15 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2079" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{757586D1-4CE9-47A5-905B-B68F9CB661D8}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3696" yWindow="3696" windowWidth="17280" windowHeight="8880" xr2:uid="{3E398004-7492-4AA0-94C2-EA9B761AAA49}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E398004-7492-4AA0-94C2-EA9B761AAA49}"/>
   </bookViews>
   <sheets>
     <sheet name="Controle" sheetId="1" r:id="rId1"/>
     <sheet name="Formulas" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Controle!$A$2:$AN$711</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Formulas!$A$9:$D$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Controle!$A$2:$AN$711</definedName>
     <definedName name="_FiltrarBaseDados" localSheetId="0" hidden="1">Controle!$A$2:$AL$710</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -213,17 +213,17 @@
     </comment>
     <comment ref="A555" authorId="3" shapeId="0" xr:uid="{33C328EB-7B56-47E9-A787-F392CA006902}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentário encadeado]
+Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
+Comentário:
     Utilizando material 1,60x417</t>
       </text>
     </comment>
     <comment ref="A564" authorId="4" shapeId="0" xr:uid="{C01DA7E7-015C-4D77-8E50-06C386F35AF3}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentário encadeado]
+Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
+Comentário:
     Temos na Fitametal 
 BOZ0070TJ1350 - 10249kg</t>
       </text>
@@ -254,17 +254,17 @@
     </comment>
     <comment ref="A574" authorId="6" shapeId="0" xr:uid="{67F1D739-35C9-474A-BA1D-BDA6C83EF4A4}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentário encadeado]
+Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
+Comentário:
     CORTAR SLEETER DE MATERIAL SEMELHANTE DEVIDO AO BAIXO VOLUME TEMOS O MESMO MATERIAL COM OUTRAS LARGURAS</t>
       </text>
     </comment>
     <comment ref="A575" authorId="7" shapeId="0" xr:uid="{9641E501-4748-445C-B1A5-D0E296582A82}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentário encadeado]
+Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
+Comentário:
     Usar material BOZ0060HU1000 como material alternativo</t>
       </text>
     </comment>
@@ -5033,7 +5033,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
     <numFmt numFmtId="166" formatCode="mmmm\,\ yyyy;@"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -13063,6 +13063,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
+<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Eric da Silva Maia" id="{D9E3AE94-B136-43DC-991E-9F5A8D1687A6}" userId="S::eric.maia@delga.com.br::43e774bf-1d7b-4030-aa96-fdc0a837fc3b" providerId="AD"/>
@@ -13407,49 +13411,49 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA437EE-405D-4A43-9EB9-23F1BEB36011}">
   <sheetPr codeName="Folha1"/>
   <dimension ref="A1:AO720"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" customWidth="1"/>
-    <col min="7" max="7" width="28.5703125" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" customWidth="1"/>
-    <col min="11" max="11" width="21.42578125" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" customWidth="1"/>
-    <col min="13" max="13" width="23.5703125" customWidth="1"/>
-    <col min="14" max="14" width="32.42578125" customWidth="1"/>
-    <col min="15" max="15" width="8.5703125" customWidth="1"/>
-    <col min="16" max="16" width="10.42578125" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="12.42578125" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" customWidth="1"/>
+    <col min="7" max="7" width="28.5546875" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" customWidth="1"/>
+    <col min="10" max="10" width="9.5546875" customWidth="1"/>
+    <col min="11" max="11" width="21.44140625" customWidth="1"/>
+    <col min="12" max="12" width="20.44140625" customWidth="1"/>
+    <col min="13" max="13" width="23.5546875" customWidth="1"/>
+    <col min="14" max="14" width="32.44140625" customWidth="1"/>
+    <col min="15" max="15" width="8.5546875" customWidth="1"/>
+    <col min="16" max="16" width="10.44140625" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="12.44140625" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="11.5546875" customWidth="1"/>
     <col min="19" max="19" width="15" customWidth="1"/>
-    <col min="20" max="20" width="15.5703125" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="16.42578125" hidden="1" customWidth="1"/>
-    <col min="22" max="24" width="15.42578125" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="15.42578125" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.5546875" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="16.44140625" hidden="1" customWidth="1"/>
+    <col min="22" max="24" width="15.44140625" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="15.44140625" customWidth="1"/>
+    <col min="26" max="26" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="13" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.85546875" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="24.140625" customWidth="1"/>
-    <col min="37" max="37" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" hidden="1" customWidth="1"/>
-    <col min="39" max="39" width="91.140625" customWidth="1"/>
-    <col min="40" max="40" width="28.28515625" style="50" customWidth="1"/>
+    <col min="34" max="34" width="12.88671875" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="24.109375" customWidth="1"/>
+    <col min="37" max="37" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.88671875" hidden="1" customWidth="1"/>
+    <col min="39" max="39" width="91.109375" customWidth="1"/>
+    <col min="40" max="40" width="28.33203125" style="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="151.35" customHeight="1"/>
-    <row r="2" spans="1:40" ht="30.6">
+    <row r="1" spans="1:40" ht="151.35" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:40" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A2" s="39" t="s">
         <v>0</v>
       </c>
@@ -13571,7 +13575,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:40" hidden="1">
+    <row r="3" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>40</v>
       </c>
@@ -13686,7 +13690,7 @@
       </c>
       <c r="AN3" s="83"/>
     </row>
-    <row r="4" spans="1:40" s="26" customFormat="1" ht="132.6" hidden="1">
+    <row r="4" spans="1:40" s="26" customFormat="1" ht="132.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
         <v>53</v>
       </c>
@@ -13803,7 +13807,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="5" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="5" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
         <v>63</v>
       </c>
@@ -13920,7 +13924,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="6" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="6" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
         <v>70</v>
       </c>
@@ -14029,7 +14033,7 @@
       </c>
       <c r="AN6" s="83"/>
     </row>
-    <row r="7" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="7" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="22" t="s">
         <v>78</v>
       </c>
@@ -14144,7 +14148,7 @@
       </c>
       <c r="AN7" s="83"/>
     </row>
-    <row r="8" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="8" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
         <v>85</v>
       </c>
@@ -14241,7 +14245,7 @@
       <c r="AM8" s="1"/>
       <c r="AN8" s="83"/>
     </row>
-    <row r="9" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
+    <row r="9" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
         <v>90</v>
       </c>
@@ -14358,7 +14362,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="10" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="10" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>97</v>
       </c>
@@ -14475,7 +14479,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="11" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="11" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="22" t="s">
         <v>103</v>
       </c>
@@ -14588,7 +14592,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="12" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="12" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
         <v>108</v>
       </c>
@@ -14685,7 +14689,7 @@
       <c r="AM12" s="1"/>
       <c r="AN12" s="83"/>
     </row>
-    <row r="13" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
+    <row r="13" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="22" t="s">
         <v>111</v>
       </c>
@@ -14784,7 +14788,7 @@
       <c r="AM13" s="1"/>
       <c r="AN13" s="83"/>
     </row>
-    <row r="14" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
+    <row r="14" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
         <v>115</v>
       </c>
@@ -14889,7 +14893,7 @@
       <c r="AM14" s="1"/>
       <c r="AN14" s="83"/>
     </row>
-    <row r="15" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="15" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="22" t="s">
         <v>118</v>
       </c>
@@ -14982,7 +14986,7 @@
       <c r="AM15" s="1"/>
       <c r="AN15" s="83"/>
     </row>
-    <row r="16" spans="1:40" s="26" customFormat="1" ht="30.6" hidden="1">
+    <row r="16" spans="1:40" s="26" customFormat="1" ht="30.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
         <v>122</v>
       </c>
@@ -15099,7 +15103,7 @@
         <v>46235</v>
       </c>
     </row>
-    <row r="17" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
+    <row r="17" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="22" t="s">
         <v>127</v>
       </c>
@@ -15196,7 +15200,7 @@
       <c r="AM17" s="1"/>
       <c r="AN17" s="83"/>
     </row>
-    <row r="18" spans="1:40" s="26" customFormat="1" ht="51" hidden="1">
+    <row r="18" spans="1:40" s="26" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
         <v>132</v>
       </c>
@@ -15293,7 +15297,7 @@
       <c r="AM18" s="1"/>
       <c r="AN18" s="83"/>
     </row>
-    <row r="19" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="19" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="22" t="s">
         <v>137</v>
       </c>
@@ -15392,7 +15396,7 @@
       </c>
       <c r="AN19" s="83"/>
     </row>
-    <row r="20" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="20" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
         <v>142</v>
       </c>
@@ -15489,7 +15493,7 @@
       <c r="AM20" s="1"/>
       <c r="AN20" s="83"/>
     </row>
-    <row r="21" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="21" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="22" t="s">
         <v>147</v>
       </c>
@@ -15604,7 +15608,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="22" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="22" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
         <v>154</v>
       </c>
@@ -15697,7 +15701,7 @@
       <c r="AM22" s="1"/>
       <c r="AN22" s="83"/>
     </row>
-    <row r="23" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="23" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="22" t="s">
         <v>156</v>
       </c>
@@ -15812,7 +15816,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="24" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="24" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
         <v>160</v>
       </c>
@@ -15905,7 +15909,7 @@
       <c r="AM24" s="1"/>
       <c r="AN24" s="83"/>
     </row>
-    <row r="25" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="25" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="22" t="s">
         <v>161</v>
       </c>
@@ -15998,7 +16002,7 @@
       <c r="AM25" s="1"/>
       <c r="AN25" s="83"/>
     </row>
-    <row r="26" spans="1:40" s="26" customFormat="1" ht="30.6" hidden="1">
+    <row r="26" spans="1:40" s="26" customFormat="1" ht="30.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
         <v>163</v>
       </c>
@@ -16093,7 +16097,7 @@
       <c r="AM26" s="1"/>
       <c r="AN26" s="83"/>
     </row>
-    <row r="27" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="27" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="22" t="s">
         <v>166</v>
       </c>
@@ -16186,7 +16190,7 @@
       <c r="AM27" s="1"/>
       <c r="AN27" s="83"/>
     </row>
-    <row r="28" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="28" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="22" t="s">
         <v>169</v>
       </c>
@@ -16281,7 +16285,7 @@
       <c r="AM28" s="62"/>
       <c r="AN28" s="83"/>
     </row>
-    <row r="29" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="29" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="22" t="s">
         <v>172</v>
       </c>
@@ -16376,7 +16380,7 @@
       <c r="AM29" s="1"/>
       <c r="AN29" s="83"/>
     </row>
-    <row r="30" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="30" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
         <v>175</v>
       </c>
@@ -16469,7 +16473,7 @@
       <c r="AM30" s="1"/>
       <c r="AN30" s="83"/>
     </row>
-    <row r="31" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="31" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="22" t="s">
         <v>179</v>
       </c>
@@ -16556,7 +16560,7 @@
       <c r="AM31" s="1"/>
       <c r="AN31" s="83"/>
     </row>
-    <row r="32" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="32" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
         <v>181</v>
       </c>
@@ -16673,7 +16677,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="33" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="33" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="22" t="s">
         <v>184</v>
       </c>
@@ -16788,7 +16792,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="34" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="34" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
         <v>190</v>
       </c>
@@ -16881,7 +16885,7 @@
       <c r="AM34" s="1"/>
       <c r="AN34" s="83"/>
     </row>
-    <row r="35" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="35" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="22" t="s">
         <v>194</v>
       </c>
@@ -16998,7 +17002,7 @@
         <v>46235</v>
       </c>
     </row>
-    <row r="36" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="36" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="22" t="s">
         <v>200</v>
       </c>
@@ -17093,7 +17097,7 @@
       <c r="AM36" s="1"/>
       <c r="AN36" s="83"/>
     </row>
-    <row r="37" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="37" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="22" t="s">
         <v>201</v>
       </c>
@@ -17180,7 +17184,7 @@
       <c r="AM37" s="1"/>
       <c r="AN37" s="83"/>
     </row>
-    <row r="38" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="38" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="22" t="s">
         <v>204</v>
       </c>
@@ -17281,7 +17285,7 @@
       <c r="AM38" s="1"/>
       <c r="AN38" s="83"/>
     </row>
-    <row r="39" spans="1:40" s="26" customFormat="1" ht="71.45" hidden="1">
+    <row r="39" spans="1:40" s="26" customFormat="1" ht="71.400000000000006" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="22" t="s">
         <v>207</v>
       </c>
@@ -17400,7 +17404,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="40" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="40" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
         <v>211</v>
       </c>
@@ -17493,7 +17497,7 @@
       <c r="AM40" s="1"/>
       <c r="AN40" s="83"/>
     </row>
-    <row r="41" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="41" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="22" t="s">
         <v>214</v>
       </c>
@@ -17586,7 +17590,7 @@
       <c r="AM41" s="1"/>
       <c r="AN41" s="83"/>
     </row>
-    <row r="42" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="42" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>217</v>
       </c>
@@ -17679,7 +17683,7 @@
       <c r="AM42" s="1"/>
       <c r="AN42" s="83"/>
     </row>
-    <row r="43" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="43" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="22" t="s">
         <v>221</v>
       </c>
@@ -17772,7 +17776,7 @@
       <c r="AM43" s="1"/>
       <c r="AN43" s="83"/>
     </row>
-    <row r="44" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="44" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="22" t="s">
         <v>225</v>
       </c>
@@ -17889,7 +17893,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="45" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="45" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="22" t="s">
         <v>230</v>
       </c>
@@ -18002,7 +18006,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="46" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="46" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="22" t="s">
         <v>234</v>
       </c>
@@ -18095,7 +18099,7 @@
       <c r="AM46" s="1"/>
       <c r="AN46" s="83"/>
     </row>
-    <row r="47" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="47" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="22" t="s">
         <v>241</v>
       </c>
@@ -18188,7 +18192,7 @@
       <c r="AM47" s="1"/>
       <c r="AN47" s="83"/>
     </row>
-    <row r="48" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="48" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="22" t="s">
         <v>244</v>
       </c>
@@ -18281,7 +18285,7 @@
       <c r="AM48" s="1"/>
       <c r="AN48" s="83"/>
     </row>
-    <row r="49" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="49" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="22" t="s">
         <v>246</v>
       </c>
@@ -18374,7 +18378,7 @@
       <c r="AM49" s="1"/>
       <c r="AN49" s="83"/>
     </row>
-    <row r="50" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="50" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="22" t="s">
         <v>248</v>
       </c>
@@ -18467,7 +18471,7 @@
       <c r="AM50" s="1"/>
       <c r="AN50" s="83"/>
     </row>
-    <row r="51" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="51" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="22" t="s">
         <v>251</v>
       </c>
@@ -18560,7 +18564,7 @@
       <c r="AM51" s="1"/>
       <c r="AN51" s="83"/>
     </row>
-    <row r="52" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="52" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="22" t="s">
         <v>254</v>
       </c>
@@ -18653,7 +18657,7 @@
       <c r="AM52" s="1"/>
       <c r="AN52" s="83"/>
     </row>
-    <row r="53" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="53" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="22" t="s">
         <v>257</v>
       </c>
@@ -18746,7 +18750,7 @@
       <c r="AM53" s="1"/>
       <c r="AN53" s="83"/>
     </row>
-    <row r="54" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="54" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="22" t="s">
         <v>259</v>
       </c>
@@ -18839,7 +18843,7 @@
       <c r="AM54" s="1"/>
       <c r="AN54" s="83"/>
     </row>
-    <row r="55" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="55" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="22" t="s">
         <v>263</v>
       </c>
@@ -18932,7 +18936,7 @@
       <c r="AM55" s="1"/>
       <c r="AN55" s="83"/>
     </row>
-    <row r="56" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="56" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="22" t="s">
         <v>266</v>
       </c>
@@ -19049,7 +19053,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="57" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="57" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="22" t="s">
         <v>270</v>
       </c>
@@ -19142,7 +19146,7 @@
       <c r="AM57" s="1"/>
       <c r="AN57" s="83"/>
     </row>
-    <row r="58" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="58" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="22" t="s">
         <v>271</v>
       </c>
@@ -19235,7 +19239,7 @@
       <c r="AM58" s="1"/>
       <c r="AN58" s="83"/>
     </row>
-    <row r="59" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="59" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="22" t="s">
         <v>273</v>
       </c>
@@ -19328,7 +19332,7 @@
       <c r="AM59" s="1"/>
       <c r="AN59" s="83"/>
     </row>
-    <row r="60" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
+    <row r="60" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="22" t="s">
         <v>275</v>
       </c>
@@ -19439,7 +19443,7 @@
       </c>
       <c r="AN60" s="83"/>
     </row>
-    <row r="61" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="61" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="22" t="s">
         <v>281</v>
       </c>
@@ -19552,7 +19556,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="62" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="62" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="22" t="s">
         <v>287</v>
       </c>
@@ -19645,7 +19649,7 @@
       <c r="AM62" s="1"/>
       <c r="AN62" s="83"/>
     </row>
-    <row r="63" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="63" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="22" t="s">
         <v>289</v>
       </c>
@@ -19738,7 +19742,7 @@
       <c r="AM63" s="1"/>
       <c r="AN63" s="83"/>
     </row>
-    <row r="64" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="64" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="22" t="s">
         <v>292</v>
       </c>
@@ -19831,7 +19835,7 @@
       <c r="AM64" s="1"/>
       <c r="AN64" s="83"/>
     </row>
-    <row r="65" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="65" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="22" t="s">
         <v>294</v>
       </c>
@@ -19926,7 +19930,7 @@
       <c r="AM65" s="1"/>
       <c r="AN65" s="83"/>
     </row>
-    <row r="66" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="66" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="22" t="s">
         <v>296</v>
       </c>
@@ -20021,7 +20025,7 @@
       <c r="AM66" s="1"/>
       <c r="AN66" s="83"/>
     </row>
-    <row r="67" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="67" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="22" t="s">
         <v>298</v>
       </c>
@@ -20110,7 +20114,7 @@
       <c r="AM67" s="1"/>
       <c r="AN67" s="83"/>
     </row>
-    <row r="68" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="68" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="22" t="s">
         <v>299</v>
       </c>
@@ -20203,7 +20207,7 @@
       <c r="AM68" s="1"/>
       <c r="AN68" s="83"/>
     </row>
-    <row r="69" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="69" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="22" t="s">
         <v>301</v>
       </c>
@@ -20298,7 +20302,7 @@
       <c r="AM69" s="1"/>
       <c r="AN69" s="83"/>
     </row>
-    <row r="70" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="70" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="22" t="s">
         <v>304</v>
       </c>
@@ -20391,7 +20395,7 @@
       <c r="AM70" s="1"/>
       <c r="AN70" s="83"/>
     </row>
-    <row r="71" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="71" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="22" t="s">
         <v>306</v>
       </c>
@@ -20484,7 +20488,7 @@
       <c r="AM71" s="1"/>
       <c r="AN71" s="83"/>
     </row>
-    <row r="72" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="72" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="22" t="s">
         <v>309</v>
       </c>
@@ -20579,7 +20583,7 @@
       <c r="AM72" s="1"/>
       <c r="AN72" s="83"/>
     </row>
-    <row r="73" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="73" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="22" t="s">
         <v>312</v>
       </c>
@@ -20672,7 +20676,7 @@
       <c r="AM73" s="1"/>
       <c r="AN73" s="83"/>
     </row>
-    <row r="74" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="74" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="22" t="s">
         <v>314</v>
       </c>
@@ -20765,7 +20769,7 @@
       <c r="AM74" s="1"/>
       <c r="AN74" s="83"/>
     </row>
-    <row r="75" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="75" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="22" t="s">
         <v>316</v>
       </c>
@@ -20856,7 +20860,7 @@
       <c r="AM75" s="1"/>
       <c r="AN75" s="83"/>
     </row>
-    <row r="76" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="76" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="22" t="s">
         <v>319</v>
       </c>
@@ -20949,7 +20953,7 @@
       <c r="AM76" s="1"/>
       <c r="AN76" s="83"/>
     </row>
-    <row r="77" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="77" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="22" t="s">
         <v>323</v>
       </c>
@@ -21040,7 +21044,7 @@
       <c r="AM77" s="1"/>
       <c r="AN77" s="83"/>
     </row>
-    <row r="78" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="78" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="22" t="s">
         <v>325</v>
       </c>
@@ -21153,7 +21157,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="79" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="79" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="22" t="s">
         <v>329</v>
       </c>
@@ -21246,7 +21250,7 @@
       <c r="AM79" s="1"/>
       <c r="AN79" s="83"/>
     </row>
-    <row r="80" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="80" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="22" t="s">
         <v>332</v>
       </c>
@@ -21359,7 +21363,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="81" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="81" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="22" t="s">
         <v>336</v>
       </c>
@@ -21454,7 +21458,7 @@
       <c r="AM81" s="1"/>
       <c r="AN81" s="83"/>
     </row>
-    <row r="82" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="82" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="22" t="s">
         <v>338</v>
       </c>
@@ -21547,7 +21551,7 @@
       <c r="AM82" s="1"/>
       <c r="AN82" s="83"/>
     </row>
-    <row r="83" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="83" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="22" t="s">
         <v>340</v>
       </c>
@@ -21640,7 +21644,7 @@
       <c r="AM83" s="1"/>
       <c r="AN83" s="83"/>
     </row>
-    <row r="84" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="84" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="22" t="s">
         <v>342</v>
       </c>
@@ -21735,7 +21739,7 @@
       <c r="AM84" s="1"/>
       <c r="AN84" s="83"/>
     </row>
-    <row r="85" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="85" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="22" t="s">
         <v>345</v>
       </c>
@@ -21828,7 +21832,7 @@
       <c r="AM85" s="1"/>
       <c r="AN85" s="83"/>
     </row>
-    <row r="86" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="86" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="22" t="s">
         <v>347</v>
       </c>
@@ -21917,7 +21921,7 @@
       <c r="AM86" s="1"/>
       <c r="AN86" s="83"/>
     </row>
-    <row r="87" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="87" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="22" t="s">
         <v>352</v>
       </c>
@@ -22010,7 +22014,7 @@
       <c r="AM87" s="1"/>
       <c r="AN87" s="83"/>
     </row>
-    <row r="88" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="88" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="22" t="s">
         <v>354</v>
       </c>
@@ -22105,7 +22109,7 @@
       <c r="AM88" s="1"/>
       <c r="AN88" s="83"/>
     </row>
-    <row r="89" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="89" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="22" t="s">
         <v>359</v>
       </c>
@@ -22198,7 +22202,7 @@
       <c r="AM89" s="1"/>
       <c r="AN89" s="83"/>
     </row>
-    <row r="90" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="90" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="22" t="s">
         <v>362</v>
       </c>
@@ -22291,7 +22295,7 @@
       <c r="AM90" s="1"/>
       <c r="AN90" s="83"/>
     </row>
-    <row r="91" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="91" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="22" t="s">
         <v>364</v>
       </c>
@@ -22384,7 +22388,7 @@
       <c r="AM91" s="1"/>
       <c r="AN91" s="83"/>
     </row>
-    <row r="92" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="92" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="22" t="s">
         <v>367</v>
       </c>
@@ -22477,7 +22481,7 @@
       <c r="AM92" s="1"/>
       <c r="AN92" s="83"/>
     </row>
-    <row r="93" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="93" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="22" t="s">
         <v>370</v>
       </c>
@@ -22568,7 +22572,7 @@
       <c r="AM93" s="1"/>
       <c r="AN93" s="83"/>
     </row>
-    <row r="94" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="94" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="22" t="s">
         <v>372</v>
       </c>
@@ -22661,7 +22665,7 @@
       <c r="AM94" s="1"/>
       <c r="AN94" s="83"/>
     </row>
-    <row r="95" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="95" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="15" t="s">
         <v>375</v>
       </c>
@@ -22754,7 +22758,7 @@
       <c r="AM95" s="1"/>
       <c r="AN95" s="83"/>
     </row>
-    <row r="96" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="96" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="22" t="s">
         <v>378</v>
       </c>
@@ -22867,7 +22871,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="97" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="97" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="22" t="s">
         <v>381</v>
       </c>
@@ -22954,7 +22958,7 @@
       <c r="AM97" s="1"/>
       <c r="AN97" s="83"/>
     </row>
-    <row r="98" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="98" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>382</v>
       </c>
@@ -23049,7 +23053,7 @@
       <c r="AM98" s="1"/>
       <c r="AN98" s="83"/>
     </row>
-    <row r="99" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="99" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="22" t="s">
         <v>386</v>
       </c>
@@ -23144,7 +23148,7 @@
       <c r="AM99" s="1"/>
       <c r="AN99" s="83"/>
     </row>
-    <row r="100" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="100" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="22" t="s">
         <v>388</v>
       </c>
@@ -23237,7 +23241,7 @@
       <c r="AM100" s="1"/>
       <c r="AN100" s="83"/>
     </row>
-    <row r="101" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="101" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="22" t="s">
         <v>391</v>
       </c>
@@ -23330,7 +23334,7 @@
       <c r="AM101" s="1"/>
       <c r="AN101" s="83"/>
     </row>
-    <row r="102" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="102" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="22" t="s">
         <v>394</v>
       </c>
@@ -23419,7 +23423,7 @@
       <c r="AM102" s="1"/>
       <c r="AN102" s="83"/>
     </row>
-    <row r="103" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="103" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="22" t="s">
         <v>397</v>
       </c>
@@ -23512,7 +23516,7 @@
       <c r="AM103" s="1"/>
       <c r="AN103" s="83"/>
     </row>
-    <row r="104" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="104" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="22" t="s">
         <v>398</v>
       </c>
@@ -23607,7 +23611,7 @@
       <c r="AM104" s="1"/>
       <c r="AN104" s="83"/>
     </row>
-    <row r="105" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="105" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="22" t="s">
         <v>400</v>
       </c>
@@ -23694,7 +23698,7 @@
       <c r="AM105" s="1"/>
       <c r="AN105" s="83"/>
     </row>
-    <row r="106" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="106" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="22" t="s">
         <v>402</v>
       </c>
@@ -23787,7 +23791,7 @@
       <c r="AM106" s="1"/>
       <c r="AN106" s="83"/>
     </row>
-    <row r="107" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="107" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="15" t="s">
         <v>404</v>
       </c>
@@ -23874,7 +23878,7 @@
       <c r="AM107" s="1"/>
       <c r="AN107" s="83"/>
     </row>
-    <row r="108" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="108" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="22" t="s">
         <v>406</v>
       </c>
@@ -23965,7 +23969,7 @@
       <c r="AM108" s="1"/>
       <c r="AN108" s="83"/>
     </row>
-    <row r="109" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="109" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="22" t="s">
         <v>408</v>
       </c>
@@ -24058,7 +24062,7 @@
       <c r="AM109" s="1"/>
       <c r="AN109" s="83"/>
     </row>
-    <row r="110" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="110" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="22" t="s">
         <v>410</v>
       </c>
@@ -24173,7 +24177,7 @@
       </c>
       <c r="AN110" s="83"/>
     </row>
-    <row r="111" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="111" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="22" t="s">
         <v>414</v>
       </c>
@@ -24268,7 +24272,7 @@
       <c r="AM111" s="1"/>
       <c r="AN111" s="83"/>
     </row>
-    <row r="112" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="112" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="22" t="s">
         <v>416</v>
       </c>
@@ -24383,7 +24387,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="113" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="113" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="22" t="s">
         <v>419</v>
       </c>
@@ -24472,7 +24476,7 @@
       <c r="AM113" s="1"/>
       <c r="AN113" s="83"/>
     </row>
-    <row r="114" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="114" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="22" t="s">
         <v>423</v>
       </c>
@@ -24559,7 +24563,7 @@
       <c r="AM114" s="1"/>
       <c r="AN114" s="83"/>
     </row>
-    <row r="115" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="115" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>424</v>
       </c>
@@ -24652,7 +24656,7 @@
       <c r="AM115" s="1"/>
       <c r="AN115" s="83"/>
     </row>
-    <row r="116" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="116" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="22" t="s">
         <v>426</v>
       </c>
@@ -24737,7 +24741,7 @@
       <c r="AM116" s="1"/>
       <c r="AN116" s="83"/>
     </row>
-    <row r="117" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="117" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="22" t="s">
         <v>428</v>
       </c>
@@ -24832,7 +24836,7 @@
       <c r="AM117" s="1"/>
       <c r="AN117" s="83"/>
     </row>
-    <row r="118" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="118" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="22" t="s">
         <v>430</v>
       </c>
@@ -24925,7 +24929,7 @@
       <c r="AM118" s="1"/>
       <c r="AN118" s="83"/>
     </row>
-    <row r="119" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="119" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="22" t="s">
         <v>432</v>
       </c>
@@ -25016,7 +25020,7 @@
       <c r="AM119" s="1"/>
       <c r="AN119" s="83"/>
     </row>
-    <row r="120" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="120" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="15" t="s">
         <v>434</v>
       </c>
@@ -25101,7 +25105,7 @@
       <c r="AM120" s="1"/>
       <c r="AN120" s="83"/>
     </row>
-    <row r="121" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="121" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="22" t="s">
         <v>435</v>
       </c>
@@ -25192,7 +25196,7 @@
       <c r="AM121" s="1"/>
       <c r="AN121" s="83"/>
     </row>
-    <row r="122" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="122" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="15" t="s">
         <v>437</v>
       </c>
@@ -25279,7 +25283,7 @@
       <c r="AM122" s="1"/>
       <c r="AN122" s="83"/>
     </row>
-    <row r="123" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="123" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="22" t="s">
         <v>438</v>
       </c>
@@ -25390,7 +25394,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="124" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="124" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="22" t="s">
         <v>440</v>
       </c>
@@ -25475,7 +25479,7 @@
       <c r="AM124" s="1"/>
       <c r="AN124" s="83"/>
     </row>
-    <row r="125" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="125" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="22" t="s">
         <v>441</v>
       </c>
@@ -25570,7 +25574,7 @@
       <c r="AM125" s="1"/>
       <c r="AN125" s="83"/>
     </row>
-    <row r="126" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="126" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="22" t="s">
         <v>443</v>
       </c>
@@ -25659,7 +25663,7 @@
       <c r="AM126" s="1"/>
       <c r="AN126" s="83"/>
     </row>
-    <row r="127" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="127" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="22" t="s">
         <v>446</v>
       </c>
@@ -25752,7 +25756,7 @@
       <c r="AM127" s="1"/>
       <c r="AN127" s="83"/>
     </row>
-    <row r="128" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="128" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="22" t="s">
         <v>448</v>
       </c>
@@ -25841,7 +25845,7 @@
       <c r="AM128" s="1"/>
       <c r="AN128" s="83"/>
     </row>
-    <row r="129" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="129" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="15" t="s">
         <v>451</v>
       </c>
@@ -25934,7 +25938,7 @@
       <c r="AM129" s="1"/>
       <c r="AN129" s="83"/>
     </row>
-    <row r="130" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="130" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="22" t="s">
         <v>453</v>
       </c>
@@ -26017,7 +26021,7 @@
       <c r="AM130" s="1"/>
       <c r="AN130" s="83"/>
     </row>
-    <row r="131" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="131" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="22" t="s">
         <v>454</v>
       </c>
@@ -26100,7 +26104,7 @@
       <c r="AM131" s="1"/>
       <c r="AN131" s="83"/>
     </row>
-    <row r="132" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="132" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="22" t="s">
         <v>455</v>
       </c>
@@ -26193,7 +26197,7 @@
       <c r="AM132" s="1"/>
       <c r="AN132" s="83"/>
     </row>
-    <row r="133" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="133" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="22" t="s">
         <v>457</v>
       </c>
@@ -26288,7 +26292,7 @@
       <c r="AM133" s="1"/>
       <c r="AN133" s="83"/>
     </row>
-    <row r="134" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="134" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="22" t="s">
         <v>459</v>
       </c>
@@ -26379,7 +26383,7 @@
       <c r="AM134" s="1"/>
       <c r="AN134" s="83"/>
     </row>
-    <row r="135" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="135" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="15" t="s">
         <v>461</v>
       </c>
@@ -26468,7 +26472,7 @@
       <c r="AM135" s="1"/>
       <c r="AN135" s="83"/>
     </row>
-    <row r="136" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="136" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="22" t="s">
         <v>463</v>
       </c>
@@ -26559,7 +26563,7 @@
       <c r="AM136" s="1"/>
       <c r="AN136" s="83"/>
     </row>
-    <row r="137" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="137" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="15" t="s">
         <v>465</v>
       </c>
@@ -26644,7 +26648,7 @@
       <c r="AM137" s="1"/>
       <c r="AN137" s="83"/>
     </row>
-    <row r="138" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="138" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="22" t="s">
         <v>467</v>
       </c>
@@ -26735,7 +26739,7 @@
       <c r="AM138" s="1"/>
       <c r="AN138" s="83"/>
     </row>
-    <row r="139" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="139" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="15" t="s">
         <v>468</v>
       </c>
@@ -26822,7 +26826,7 @@
       <c r="AM139" s="1"/>
       <c r="AN139" s="83"/>
     </row>
-    <row r="140" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="140" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="22" t="s">
         <v>471</v>
       </c>
@@ -26913,7 +26917,7 @@
       <c r="AM140" s="1"/>
       <c r="AN140" s="83"/>
     </row>
-    <row r="141" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="141" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="22" t="s">
         <v>474</v>
       </c>
@@ -26998,7 +27002,7 @@
       <c r="AM141" s="1"/>
       <c r="AN141" s="83"/>
     </row>
-    <row r="142" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="142" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="15" t="s">
         <v>475</v>
       </c>
@@ -27089,7 +27093,7 @@
       <c r="AM142" s="1"/>
       <c r="AN142" s="83"/>
     </row>
-    <row r="143" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="143" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="15" t="s">
         <v>477</v>
       </c>
@@ -27176,7 +27180,7 @@
       <c r="AM143" s="1"/>
       <c r="AN143" s="83"/>
     </row>
-    <row r="144" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="144" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="15" t="s">
         <v>480</v>
       </c>
@@ -27271,7 +27275,7 @@
       <c r="AM144" s="1"/>
       <c r="AN144" s="83"/>
     </row>
-    <row r="145" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="145" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="15" t="s">
         <v>482</v>
       </c>
@@ -27358,7 +27362,7 @@
       <c r="AM145" s="1"/>
       <c r="AN145" s="83"/>
     </row>
-    <row r="146" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="146" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="15" t="s">
         <v>483</v>
       </c>
@@ -27443,7 +27447,7 @@
       <c r="AM146" s="1"/>
       <c r="AN146" s="83"/>
     </row>
-    <row r="147" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="147" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="15" t="s">
         <v>484</v>
       </c>
@@ -27524,7 +27528,7 @@
       <c r="AM147" s="1"/>
       <c r="AN147" s="83"/>
     </row>
-    <row r="148" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="148" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="15" t="s">
         <v>485</v>
       </c>
@@ -27617,7 +27621,7 @@
       <c r="AM148" s="1"/>
       <c r="AN148" s="83"/>
     </row>
-    <row r="149" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="149" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="15" t="s">
         <v>487</v>
       </c>
@@ -27708,7 +27712,7 @@
       <c r="AM149" s="1"/>
       <c r="AN149" s="83"/>
     </row>
-    <row r="150" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="150" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="15" t="s">
         <v>489</v>
       </c>
@@ -27789,7 +27793,7 @@
       <c r="AM150" s="1"/>
       <c r="AN150" s="83"/>
     </row>
-    <row r="151" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="151" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="15" t="s">
         <v>490</v>
       </c>
@@ -27876,7 +27880,7 @@
       <c r="AM151" s="1"/>
       <c r="AN151" s="83"/>
     </row>
-    <row r="152" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="152" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="15" t="s">
         <v>492</v>
       </c>
@@ -27967,7 +27971,7 @@
       <c r="AM152" s="1"/>
       <c r="AN152" s="83"/>
     </row>
-    <row r="153" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="153" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="15" t="s">
         <v>495</v>
       </c>
@@ -28054,7 +28058,7 @@
       <c r="AM153" s="1"/>
       <c r="AN153" s="83"/>
     </row>
-    <row r="154" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="154" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="15" t="s">
         <v>497</v>
       </c>
@@ -28141,7 +28145,7 @@
       <c r="AM154" s="1"/>
       <c r="AN154" s="83"/>
     </row>
-    <row r="155" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="155" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="15" t="s">
         <v>499</v>
       </c>
@@ -28228,7 +28232,7 @@
       <c r="AM155" s="1"/>
       <c r="AN155" s="83"/>
     </row>
-    <row r="156" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="156" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="15" t="s">
         <v>501</v>
       </c>
@@ -28317,7 +28321,7 @@
       <c r="AM156" s="1"/>
       <c r="AN156" s="83"/>
     </row>
-    <row r="157" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="157" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="15" t="s">
         <v>504</v>
       </c>
@@ -28404,7 +28408,7 @@
       <c r="AM157" s="1"/>
       <c r="AN157" s="83"/>
     </row>
-    <row r="158" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="158" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="15" t="s">
         <v>506</v>
       </c>
@@ -28491,7 +28495,7 @@
       <c r="AM158" s="1"/>
       <c r="AN158" s="83"/>
     </row>
-    <row r="159" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="159" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="15" t="s">
         <v>508</v>
       </c>
@@ -28580,7 +28584,7 @@
       <c r="AM159" s="1"/>
       <c r="AN159" s="83"/>
     </row>
-    <row r="160" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="160" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="15" t="s">
         <v>510</v>
       </c>
@@ -28667,7 +28671,7 @@
       <c r="AM160" s="1"/>
       <c r="AN160" s="83"/>
     </row>
-    <row r="161" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="161" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="15" t="s">
         <v>512</v>
       </c>
@@ -28754,7 +28758,7 @@
       <c r="AM161" s="1"/>
       <c r="AN161" s="83"/>
     </row>
-    <row r="162" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="162" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="15" t="s">
         <v>514</v>
       </c>
@@ -28845,7 +28849,7 @@
       <c r="AM162" s="1"/>
       <c r="AN162" s="83"/>
     </row>
-    <row r="163" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="163" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="15" t="s">
         <v>517</v>
       </c>
@@ -28932,7 +28936,7 @@
       <c r="AM163" s="1"/>
       <c r="AN163" s="83"/>
     </row>
-    <row r="164" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="164" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="15" t="s">
         <v>519</v>
       </c>
@@ -29019,7 +29023,7 @@
       <c r="AM164" s="1"/>
       <c r="AN164" s="83"/>
     </row>
-    <row r="165" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="165" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="15" t="s">
         <v>521</v>
       </c>
@@ -29108,7 +29112,7 @@
       <c r="AM165" s="1"/>
       <c r="AN165" s="83"/>
     </row>
-    <row r="166" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="166" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="15" t="s">
         <v>523</v>
       </c>
@@ -29197,7 +29201,7 @@
       <c r="AM166" s="1"/>
       <c r="AN166" s="83"/>
     </row>
-    <row r="167" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="167" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="15" t="s">
         <v>525</v>
       </c>
@@ -29286,7 +29290,7 @@
       <c r="AM167" s="1"/>
       <c r="AN167" s="83"/>
     </row>
-    <row r="168" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="168" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="15" t="s">
         <v>527</v>
       </c>
@@ -29375,7 +29379,7 @@
       <c r="AM168" s="1"/>
       <c r="AN168" s="83"/>
     </row>
-    <row r="169" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="169" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="15" t="s">
         <v>529</v>
       </c>
@@ -29462,7 +29466,7 @@
       <c r="AM169" s="1"/>
       <c r="AN169" s="83"/>
     </row>
-    <row r="170" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="170" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="15" t="s">
         <v>531</v>
       </c>
@@ -29551,7 +29555,7 @@
       <c r="AM170" s="1"/>
       <c r="AN170" s="83"/>
     </row>
-    <row r="171" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="171" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="15" t="s">
         <v>533</v>
       </c>
@@ -29640,7 +29644,7 @@
       <c r="AM171" s="1"/>
       <c r="AN171" s="83"/>
     </row>
-    <row r="172" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="172" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="15" t="s">
         <v>535</v>
       </c>
@@ -29727,7 +29731,7 @@
       <c r="AM172" s="1"/>
       <c r="AN172" s="83"/>
     </row>
-    <row r="173" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="173" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="15" t="s">
         <v>537</v>
       </c>
@@ -29816,7 +29820,7 @@
       <c r="AM173" s="1"/>
       <c r="AN173" s="83"/>
     </row>
-    <row r="174" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="174" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="15" t="s">
         <v>539</v>
       </c>
@@ -29905,7 +29909,7 @@
       <c r="AM174" s="1"/>
       <c r="AN174" s="83"/>
     </row>
-    <row r="175" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="175" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="15" t="s">
         <v>541</v>
       </c>
@@ -29978,7 +29982,7 @@
       <c r="AM175" s="1"/>
       <c r="AN175" s="83"/>
     </row>
-    <row r="176" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="176" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="15" t="s">
         <v>542</v>
       </c>
@@ -30065,7 +30069,7 @@
       <c r="AM176" s="1"/>
       <c r="AN176" s="83"/>
     </row>
-    <row r="177" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="177" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="15" t="s">
         <v>545</v>
       </c>
@@ -30150,7 +30154,7 @@
       <c r="AM177" s="1"/>
       <c r="AN177" s="83"/>
     </row>
-    <row r="178" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="178" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="15" t="s">
         <v>547</v>
       </c>
@@ -30241,7 +30245,7 @@
       <c r="AM178" s="1"/>
       <c r="AN178" s="83"/>
     </row>
-    <row r="179" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="179" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="15" t="s">
         <v>548</v>
       </c>
@@ -30328,7 +30332,7 @@
       <c r="AM179" s="1"/>
       <c r="AN179" s="83"/>
     </row>
-    <row r="180" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="180" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="15" t="s">
         <v>552</v>
       </c>
@@ -30443,7 +30447,7 @@
         <v>46204</v>
       </c>
     </row>
-    <row r="181" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="181" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="15" t="s">
         <v>557</v>
       </c>
@@ -30558,7 +30562,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="182" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="182" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="15" t="s">
         <v>562</v>
       </c>
@@ -30649,7 +30653,7 @@
       <c r="AM182" s="1"/>
       <c r="AN182" s="83"/>
     </row>
-    <row r="183" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="183" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="15" t="s">
         <v>564</v>
       </c>
@@ -30738,7 +30742,7 @@
       <c r="AM183" s="1"/>
       <c r="AN183" s="83"/>
     </row>
-    <row r="184" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="184" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="15" t="s">
         <v>565</v>
       </c>
@@ -30827,7 +30831,7 @@
       <c r="AM184" s="1"/>
       <c r="AN184" s="83"/>
     </row>
-    <row r="185" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="185" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="15" t="s">
         <v>567</v>
       </c>
@@ -30914,7 +30918,7 @@
       <c r="AM185" s="1"/>
       <c r="AN185" s="83"/>
     </row>
-    <row r="186" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="186" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="15" t="s">
         <v>570</v>
       </c>
@@ -31001,7 +31005,7 @@
       <c r="AM186" s="1"/>
       <c r="AN186" s="83"/>
     </row>
-    <row r="187" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="187" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="15" t="s">
         <v>572</v>
       </c>
@@ -31088,7 +31092,7 @@
       <c r="AM187" s="1"/>
       <c r="AN187" s="83"/>
     </row>
-    <row r="188" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="188" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="15" t="s">
         <v>575</v>
       </c>
@@ -31175,7 +31179,7 @@
       <c r="AM188" s="1"/>
       <c r="AN188" s="83"/>
     </row>
-    <row r="189" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="189" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="15" t="s">
         <v>578</v>
       </c>
@@ -31262,7 +31266,7 @@
       <c r="AM189" s="1"/>
       <c r="AN189" s="83"/>
     </row>
-    <row r="190" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="190" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="15" t="s">
         <v>580</v>
       </c>
@@ -31349,7 +31353,7 @@
       <c r="AM190" s="1"/>
       <c r="AN190" s="83"/>
     </row>
-    <row r="191" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="191" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="15" t="s">
         <v>582</v>
       </c>
@@ -31430,7 +31434,7 @@
       <c r="AM191" s="1"/>
       <c r="AN191" s="83"/>
     </row>
-    <row r="192" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="192" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="15" t="s">
         <v>584</v>
       </c>
@@ -31517,7 +31521,7 @@
       <c r="AM192" s="1"/>
       <c r="AN192" s="83"/>
     </row>
-    <row r="193" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="193" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="15" t="s">
         <v>586</v>
       </c>
@@ -31606,7 +31610,7 @@
       <c r="AM193" s="1"/>
       <c r="AN193" s="83"/>
     </row>
-    <row r="194" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="194" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="15" t="s">
         <v>589</v>
       </c>
@@ -31693,7 +31697,7 @@
       <c r="AM194" s="1"/>
       <c r="AN194" s="83"/>
     </row>
-    <row r="195" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="195" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="15" t="s">
         <v>592</v>
       </c>
@@ -31780,7 +31784,7 @@
       <c r="AM195" s="1"/>
       <c r="AN195" s="83"/>
     </row>
-    <row r="196" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="196" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="15" t="s">
         <v>595</v>
       </c>
@@ -31869,7 +31873,7 @@
       <c r="AM196" s="1"/>
       <c r="AN196" s="83"/>
     </row>
-    <row r="197" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="197" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="15" t="s">
         <v>599</v>
       </c>
@@ -31958,7 +31962,7 @@
       <c r="AM197" s="1"/>
       <c r="AN197" s="83"/>
     </row>
-    <row r="198" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="198" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="15" t="s">
         <v>601</v>
       </c>
@@ -32047,7 +32051,7 @@
       <c r="AM198" s="1"/>
       <c r="AN198" s="83"/>
     </row>
-    <row r="199" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="199" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="15" t="s">
         <v>603</v>
       </c>
@@ -32134,7 +32138,7 @@
       <c r="AM199" s="1"/>
       <c r="AN199" s="83"/>
     </row>
-    <row r="200" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="200" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="15" t="s">
         <v>605</v>
       </c>
@@ -32221,7 +32225,7 @@
       <c r="AM200" s="1"/>
       <c r="AN200" s="83"/>
     </row>
-    <row r="201" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="201" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="15" t="s">
         <v>607</v>
       </c>
@@ -32308,7 +32312,7 @@
       <c r="AM201" s="1"/>
       <c r="AN201" s="83"/>
     </row>
-    <row r="202" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="202" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="15" t="s">
         <v>610</v>
       </c>
@@ -32399,7 +32403,7 @@
       <c r="AM202" s="1"/>
       <c r="AN202" s="83"/>
     </row>
-    <row r="203" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="203" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="15" t="s">
         <v>611</v>
       </c>
@@ -32486,7 +32490,7 @@
       <c r="AM203" s="1"/>
       <c r="AN203" s="83"/>
     </row>
-    <row r="204" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="204" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="15" t="s">
         <v>612</v>
       </c>
@@ -32573,7 +32577,7 @@
       <c r="AM204" s="1"/>
       <c r="AN204" s="83"/>
     </row>
-    <row r="205" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="205" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="15" t="s">
         <v>614</v>
       </c>
@@ -32662,7 +32666,7 @@
       <c r="AM205" s="1"/>
       <c r="AN205" s="83"/>
     </row>
-    <row r="206" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="206" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="15" t="s">
         <v>615</v>
       </c>
@@ -32755,7 +32759,7 @@
       <c r="AM206" s="1"/>
       <c r="AN206" s="83"/>
     </row>
-    <row r="207" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="207" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="15" t="s">
         <v>616</v>
       </c>
@@ -32842,7 +32846,7 @@
       <c r="AM207" s="1"/>
       <c r="AN207" s="83"/>
     </row>
-    <row r="208" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="208" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="15" t="s">
         <v>619</v>
       </c>
@@ -32931,7 +32935,7 @@
       <c r="AM208" s="1"/>
       <c r="AN208" s="83"/>
     </row>
-    <row r="209" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="209" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="15" t="s">
         <v>621</v>
       </c>
@@ -33018,7 +33022,7 @@
       <c r="AM209" s="1"/>
       <c r="AN209" s="83"/>
     </row>
-    <row r="210" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="210" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="15" t="s">
         <v>623</v>
       </c>
@@ -33105,7 +33109,7 @@
       <c r="AM210" s="1"/>
       <c r="AN210" s="83"/>
     </row>
-    <row r="211" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="211" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="15" t="s">
         <v>625</v>
       </c>
@@ -33192,7 +33196,7 @@
       <c r="AM211" s="1"/>
       <c r="AN211" s="83"/>
     </row>
-    <row r="212" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="212" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="15" t="s">
         <v>627</v>
       </c>
@@ -33281,7 +33285,7 @@
       <c r="AM212" s="1"/>
       <c r="AN212" s="83"/>
     </row>
-    <row r="213" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="213" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="15" t="s">
         <v>629</v>
       </c>
@@ -33368,7 +33372,7 @@
       <c r="AM213" s="1"/>
       <c r="AN213" s="83"/>
     </row>
-    <row r="214" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="214" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="15" t="s">
         <v>631</v>
       </c>
@@ -33455,7 +33459,7 @@
       <c r="AM214" s="1"/>
       <c r="AN214" s="83"/>
     </row>
-    <row r="215" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="215" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="15" t="s">
         <v>634</v>
       </c>
@@ -33544,7 +33548,7 @@
       <c r="AM215" s="1"/>
       <c r="AN215" s="83"/>
     </row>
-    <row r="216" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="216" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="15" t="s">
         <v>637</v>
       </c>
@@ -33629,7 +33633,7 @@
       <c r="AM216" s="1"/>
       <c r="AN216" s="83"/>
     </row>
-    <row r="217" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="217" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="15" t="s">
         <v>639</v>
       </c>
@@ -33716,7 +33720,7 @@
       <c r="AM217" s="1"/>
       <c r="AN217" s="83"/>
     </row>
-    <row r="218" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="218" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="15" t="s">
         <v>642</v>
       </c>
@@ -33801,7 +33805,7 @@
       <c r="AM218" s="1"/>
       <c r="AN218" s="83"/>
     </row>
-    <row r="219" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="219" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="15" t="s">
         <v>644</v>
       </c>
@@ -33886,7 +33890,7 @@
       <c r="AM219" s="1"/>
       <c r="AN219" s="83"/>
     </row>
-    <row r="220" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="220" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="15" t="s">
         <v>646</v>
       </c>
@@ -33967,7 +33971,7 @@
       <c r="AM220" s="1"/>
       <c r="AN220" s="83"/>
     </row>
-    <row r="221" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="221" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="15" t="s">
         <v>647</v>
       </c>
@@ -34052,7 +34056,7 @@
       <c r="AM221" s="1"/>
       <c r="AN221" s="83"/>
     </row>
-    <row r="222" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="222" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="15" t="s">
         <v>650</v>
       </c>
@@ -34137,7 +34141,7 @@
       <c r="AM222" s="1"/>
       <c r="AN222" s="83"/>
     </row>
-    <row r="223" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="223" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="15" t="s">
         <v>653</v>
       </c>
@@ -34222,7 +34226,7 @@
       <c r="AM223" s="1"/>
       <c r="AN223" s="83"/>
     </row>
-    <row r="224" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="224" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="15" t="s">
         <v>655</v>
       </c>
@@ -34311,7 +34315,7 @@
       <c r="AM224" s="1"/>
       <c r="AN224" s="83"/>
     </row>
-    <row r="225" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="225" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="15" t="s">
         <v>657</v>
       </c>
@@ -34394,7 +34398,7 @@
       <c r="AM225" s="1"/>
       <c r="AN225" s="83"/>
     </row>
-    <row r="226" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="226" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="15" t="s">
         <v>659</v>
       </c>
@@ -34481,7 +34485,7 @@
       <c r="AM226" s="1"/>
       <c r="AN226" s="83"/>
     </row>
-    <row r="227" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="227" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="15" t="s">
         <v>661</v>
       </c>
@@ -34568,7 +34572,7 @@
       <c r="AM227" s="1"/>
       <c r="AN227" s="83"/>
     </row>
-    <row r="228" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="228" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="15" t="s">
         <v>664</v>
       </c>
@@ -34653,7 +34657,7 @@
       <c r="AM228" s="1"/>
       <c r="AN228" s="83"/>
     </row>
-    <row r="229" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="229" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="15" t="s">
         <v>666</v>
       </c>
@@ -34736,7 +34740,7 @@
       <c r="AM229" s="1"/>
       <c r="AN229" s="83"/>
     </row>
-    <row r="230" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="230" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="15" t="s">
         <v>667</v>
       </c>
@@ -34821,7 +34825,7 @@
       <c r="AM230" s="1"/>
       <c r="AN230" s="83"/>
     </row>
-    <row r="231" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="231" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="15" t="s">
         <v>669</v>
       </c>
@@ -34906,7 +34910,7 @@
       <c r="AM231" s="1"/>
       <c r="AN231" s="83"/>
     </row>
-    <row r="232" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="232" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="15" t="s">
         <v>671</v>
       </c>
@@ -34987,7 +34991,7 @@
       <c r="AM232" s="1"/>
       <c r="AN232" s="83"/>
     </row>
-    <row r="233" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="233" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="15" t="s">
         <v>672</v>
       </c>
@@ -35072,7 +35076,7 @@
       <c r="AM233" s="1"/>
       <c r="AN233" s="83"/>
     </row>
-    <row r="234" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="234" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="15" t="s">
         <v>674</v>
       </c>
@@ -35161,7 +35165,7 @@
       <c r="AM234" s="1"/>
       <c r="AN234" s="83"/>
     </row>
-    <row r="235" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="235" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="15" t="s">
         <v>675</v>
       </c>
@@ -35248,7 +35252,7 @@
       <c r="AM235" s="1"/>
       <c r="AN235" s="83"/>
     </row>
-    <row r="236" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="236" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="15" t="s">
         <v>678</v>
       </c>
@@ -35335,7 +35339,7 @@
       <c r="AM236" s="1"/>
       <c r="AN236" s="83"/>
     </row>
-    <row r="237" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="237" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="15" t="s">
         <v>680</v>
       </c>
@@ -35422,7 +35426,7 @@
       <c r="AM237" s="1"/>
       <c r="AN237" s="83"/>
     </row>
-    <row r="238" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="238" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="15" t="s">
         <v>683</v>
       </c>
@@ -35513,7 +35517,7 @@
       <c r="AM238" s="1"/>
       <c r="AN238" s="83"/>
     </row>
-    <row r="239" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="239" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="15" t="s">
         <v>686</v>
       </c>
@@ -35604,7 +35608,7 @@
       <c r="AM239" s="1"/>
       <c r="AN239" s="83"/>
     </row>
-    <row r="240" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="240" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="15" t="s">
         <v>688</v>
       </c>
@@ -35695,7 +35699,7 @@
       <c r="AM240" s="1"/>
       <c r="AN240" s="83"/>
     </row>
-    <row r="241" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="241" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="15" t="s">
         <v>690</v>
       </c>
@@ -35784,7 +35788,7 @@
       <c r="AM241" s="1"/>
       <c r="AN241" s="83"/>
     </row>
-    <row r="242" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="242" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="15" t="s">
         <v>692</v>
       </c>
@@ -35871,7 +35875,7 @@
       <c r="AM242" s="1"/>
       <c r="AN242" s="83"/>
     </row>
-    <row r="243" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="243" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="15" t="s">
         <v>694</v>
       </c>
@@ -35964,7 +35968,7 @@
       <c r="AM243" s="1"/>
       <c r="AN243" s="83"/>
     </row>
-    <row r="244" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="244" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="15" t="s">
         <v>696</v>
       </c>
@@ -36051,7 +36055,7 @@
       <c r="AM244" s="1"/>
       <c r="AN244" s="83"/>
     </row>
-    <row r="245" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="245" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="15" t="s">
         <v>698</v>
       </c>
@@ -36136,7 +36140,7 @@
       <c r="AM245" s="1"/>
       <c r="AN245" s="83"/>
     </row>
-    <row r="246" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="246" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="15" t="s">
         <v>700</v>
       </c>
@@ -36223,7 +36227,7 @@
       <c r="AM246" s="1"/>
       <c r="AN246" s="83"/>
     </row>
-    <row r="247" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="247" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="15" t="s">
         <v>702</v>
       </c>
@@ -36310,7 +36314,7 @@
       <c r="AM247" s="1"/>
       <c r="AN247" s="83"/>
     </row>
-    <row r="248" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="248" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="15" t="s">
         <v>704</v>
       </c>
@@ -36397,7 +36401,7 @@
       <c r="AM248" s="1"/>
       <c r="AN248" s="83"/>
     </row>
-    <row r="249" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="249" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="15" t="s">
         <v>706</v>
       </c>
@@ -36484,7 +36488,7 @@
       <c r="AM249" s="1"/>
       <c r="AN249" s="83"/>
     </row>
-    <row r="250" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="250" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="15" t="s">
         <v>708</v>
       </c>
@@ -36573,7 +36577,7 @@
       <c r="AM250" s="1"/>
       <c r="AN250" s="83"/>
     </row>
-    <row r="251" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="251" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="15" t="s">
         <v>709</v>
       </c>
@@ -36658,7 +36662,7 @@
       <c r="AM251" s="1"/>
       <c r="AN251" s="83"/>
     </row>
-    <row r="252" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="252" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="15" t="s">
         <v>711</v>
       </c>
@@ -36743,7 +36747,7 @@
       <c r="AM252" s="1"/>
       <c r="AN252" s="83"/>
     </row>
-    <row r="253" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="253" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="15" t="s">
         <v>713</v>
       </c>
@@ -36828,7 +36832,7 @@
       <c r="AM253" s="1"/>
       <c r="AN253" s="83"/>
     </row>
-    <row r="254" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="254" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="15" t="s">
         <v>715</v>
       </c>
@@ -36913,7 +36917,7 @@
       <c r="AM254" s="1"/>
       <c r="AN254" s="83"/>
     </row>
-    <row r="255" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="255" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="15" t="s">
         <v>717</v>
       </c>
@@ -37000,7 +37004,7 @@
       <c r="AM255" s="1"/>
       <c r="AN255" s="83"/>
     </row>
-    <row r="256" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="256" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="15" t="s">
         <v>719</v>
       </c>
@@ -37089,7 +37093,7 @@
       <c r="AM256" s="1"/>
       <c r="AN256" s="83"/>
     </row>
-    <row r="257" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="257" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="15" t="s">
         <v>721</v>
       </c>
@@ -37176,7 +37180,7 @@
       <c r="AM257" s="1"/>
       <c r="AN257" s="83"/>
     </row>
-    <row r="258" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="258" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="15" t="s">
         <v>723</v>
       </c>
@@ -37263,7 +37267,7 @@
       <c r="AM258" s="1"/>
       <c r="AN258" s="83"/>
     </row>
-    <row r="259" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="259" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="15" t="s">
         <v>725</v>
       </c>
@@ -37350,7 +37354,7 @@
       <c r="AM259" s="1"/>
       <c r="AN259" s="83"/>
     </row>
-    <row r="260" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="260" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="15" t="s">
         <v>727</v>
       </c>
@@ -37435,7 +37439,7 @@
       <c r="AM260" s="1"/>
       <c r="AN260" s="83"/>
     </row>
-    <row r="261" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="261" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="15" t="s">
         <v>728</v>
       </c>
@@ -37516,7 +37520,7 @@
       <c r="AM261" s="1"/>
       <c r="AN261" s="83"/>
     </row>
-    <row r="262" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="262" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="15" t="s">
         <v>729</v>
       </c>
@@ -37597,7 +37601,7 @@
       <c r="AM262" s="1"/>
       <c r="AN262" s="83"/>
     </row>
-    <row r="263" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="263" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="15" t="s">
         <v>730</v>
       </c>
@@ -37674,7 +37678,7 @@
       <c r="AM263" s="1"/>
       <c r="AN263" s="83"/>
     </row>
-    <row r="264" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="264" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="15" t="s">
         <v>732</v>
       </c>
@@ -37755,7 +37759,7 @@
       <c r="AM264" s="1"/>
       <c r="AN264" s="83"/>
     </row>
-    <row r="265" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="265" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="15" t="s">
         <v>733</v>
       </c>
@@ -37832,7 +37836,7 @@
       <c r="AM265" s="1"/>
       <c r="AN265" s="83"/>
     </row>
-    <row r="266" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="266" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="15" t="s">
         <v>734</v>
       </c>
@@ -37913,7 +37917,7 @@
       <c r="AM266" s="1"/>
       <c r="AN266" s="83"/>
     </row>
-    <row r="267" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="267" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="15" t="s">
         <v>735</v>
       </c>
@@ -37996,7 +38000,7 @@
       <c r="AM267" s="1"/>
       <c r="AN267" s="83"/>
     </row>
-    <row r="268" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="268" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="15" t="s">
         <v>736</v>
       </c>
@@ -38077,7 +38081,7 @@
       <c r="AM268" s="1"/>
       <c r="AN268" s="83"/>
     </row>
-    <row r="269" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="269" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="15" t="s">
         <v>738</v>
       </c>
@@ -38158,7 +38162,7 @@
       <c r="AM269" s="1"/>
       <c r="AN269" s="83"/>
     </row>
-    <row r="270" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="270" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="15" t="s">
         <v>739</v>
       </c>
@@ -38239,7 +38243,7 @@
       <c r="AM270" s="1"/>
       <c r="AN270" s="83"/>
     </row>
-    <row r="271" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="271" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="15" t="s">
         <v>740</v>
       </c>
@@ -38320,7 +38324,7 @@
       <c r="AM271" s="1"/>
       <c r="AN271" s="83"/>
     </row>
-    <row r="272" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="272" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="31" t="s">
         <v>741</v>
       </c>
@@ -38401,7 +38405,7 @@
       <c r="AM272" s="1"/>
       <c r="AN272" s="83"/>
     </row>
-    <row r="273" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="273" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="15" t="s">
         <v>742</v>
       </c>
@@ -38484,7 +38488,7 @@
       <c r="AM273" s="1"/>
       <c r="AN273" s="83"/>
     </row>
-    <row r="274" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="274" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="15" t="s">
         <v>743</v>
       </c>
@@ -38565,7 +38569,7 @@
       <c r="AM274" s="1"/>
       <c r="AN274" s="83"/>
     </row>
-    <row r="275" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="275" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="15" t="s">
         <v>744</v>
       </c>
@@ -38646,7 +38650,7 @@
       <c r="AM275" s="1"/>
       <c r="AN275" s="83"/>
     </row>
-    <row r="276" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="276" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="15" t="s">
         <v>745</v>
       </c>
@@ -38727,7 +38731,7 @@
       <c r="AM276" s="1"/>
       <c r="AN276" s="83"/>
     </row>
-    <row r="277" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="277" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="15" t="s">
         <v>746</v>
       </c>
@@ -38808,7 +38812,7 @@
       <c r="AM277" s="1"/>
       <c r="AN277" s="83"/>
     </row>
-    <row r="278" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="278" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="15" t="s">
         <v>747</v>
       </c>
@@ -38889,7 +38893,7 @@
       <c r="AM278" s="1"/>
       <c r="AN278" s="83"/>
     </row>
-    <row r="279" spans="1:40" s="26" customFormat="1" ht="20.45">
+    <row r="279" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A279" s="22" t="s">
         <v>748</v>
       </c>
@@ -39006,7 +39010,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="280" spans="1:40" s="26" customFormat="1" ht="20.45">
+    <row r="280" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A280" s="22" t="s">
         <v>758</v>
       </c>
@@ -39121,7 +39125,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="281" spans="1:40" s="26" customFormat="1" ht="122.45">
+    <row r="281" spans="1:40" s="26" customFormat="1" ht="122.4" x14ac:dyDescent="0.3">
       <c r="A281" s="22" t="s">
         <v>760</v>
       </c>
@@ -39238,7 +39242,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="282" spans="1:40" s="26" customFormat="1">
+    <row r="282" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A282" s="22" t="s">
         <v>768</v>
       </c>
@@ -39351,7 +39355,7 @@
       <c r="AM282" s="1"/>
       <c r="AN282" s="83"/>
     </row>
-    <row r="283" spans="1:40" s="26" customFormat="1">
+    <row r="283" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A283" s="22" t="s">
         <v>562</v>
       </c>
@@ -39466,7 +39470,7 @@
         <v>46235</v>
       </c>
     </row>
-    <row r="284" spans="1:40" s="26" customFormat="1" ht="81.599999999999994">
+    <row r="284" spans="1:40" s="26" customFormat="1" ht="81.599999999999994" x14ac:dyDescent="0.3">
       <c r="A284" s="22" t="s">
         <v>778</v>
       </c>
@@ -39581,7 +39585,7 @@
       </c>
       <c r="AN284" s="83"/>
     </row>
-    <row r="285" spans="1:40" s="26" customFormat="1">
+    <row r="285" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A285" s="22" t="s">
         <v>782</v>
       </c>
@@ -39696,7 +39700,7 @@
       </c>
       <c r="AN285" s="83"/>
     </row>
-    <row r="286" spans="1:40" s="26" customFormat="1">
+    <row r="286" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A286" s="22" t="s">
         <v>786</v>
       </c>
@@ -39811,7 +39815,7 @@
       </c>
       <c r="AN286" s="83"/>
     </row>
-    <row r="287" spans="1:40" s="26" customFormat="1" ht="20.45">
+    <row r="287" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A287" s="22" t="s">
         <v>790</v>
       </c>
@@ -39926,7 +39930,7 @@
       </c>
       <c r="AN287" s="83"/>
     </row>
-    <row r="288" spans="1:40" s="26" customFormat="1">
+    <row r="288" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A288" s="22" t="s">
         <v>792</v>
       </c>
@@ -40041,7 +40045,7 @@
       </c>
       <c r="AN288" s="83"/>
     </row>
-    <row r="289" spans="1:40" s="26" customFormat="1">
+    <row r="289" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A289" s="22" t="s">
         <v>795</v>
       </c>
@@ -40156,7 +40160,7 @@
       </c>
       <c r="AN289" s="83"/>
     </row>
-    <row r="290" spans="1:40" s="26" customFormat="1">
+    <row r="290" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A290" s="22" t="s">
         <v>207</v>
       </c>
@@ -40253,7 +40257,7 @@
       </c>
       <c r="AN290" s="83"/>
     </row>
-    <row r="291" spans="1:40" s="26" customFormat="1" ht="30.6">
+    <row r="291" spans="1:40" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A291" s="22" t="s">
         <v>804</v>
       </c>
@@ -40366,7 +40370,7 @@
       </c>
       <c r="AN291" s="83"/>
     </row>
-    <row r="292" spans="1:40" s="26" customFormat="1">
+    <row r="292" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A292" s="22" t="s">
         <v>809</v>
       </c>
@@ -40461,7 +40465,7 @@
       <c r="AM292" s="1"/>
       <c r="AN292" s="83"/>
     </row>
-    <row r="293" spans="1:40" s="26" customFormat="1">
+    <row r="293" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A293" s="22" t="s">
         <v>812</v>
       </c>
@@ -40550,7 +40554,7 @@
       <c r="AM293" s="1"/>
       <c r="AN293" s="83"/>
     </row>
-    <row r="294" spans="1:40" s="26" customFormat="1">
+    <row r="294" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A294" s="22" t="s">
         <v>815</v>
       </c>
@@ -40641,7 +40645,7 @@
       <c r="AM294" s="1"/>
       <c r="AN294" s="83"/>
     </row>
-    <row r="295" spans="1:40" s="26" customFormat="1">
+    <row r="295" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A295" s="22" t="s">
         <v>817</v>
       </c>
@@ -40726,7 +40730,7 @@
       <c r="AM295" s="1"/>
       <c r="AN295" s="83"/>
     </row>
-    <row r="296" spans="1:40" s="26" customFormat="1">
+    <row r="296" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A296" s="22" t="s">
         <v>821</v>
       </c>
@@ -40817,7 +40821,7 @@
       <c r="AM296" s="1"/>
       <c r="AN296" s="83"/>
     </row>
-    <row r="297" spans="1:40" s="26" customFormat="1">
+    <row r="297" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A297" s="22" t="s">
         <v>728</v>
       </c>
@@ -40908,7 +40912,7 @@
       </c>
       <c r="AN297" s="83"/>
     </row>
-    <row r="298" spans="1:40" s="26" customFormat="1">
+    <row r="298" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A298" s="22" t="s">
         <v>156</v>
       </c>
@@ -40997,7 +41001,7 @@
       <c r="AM298" s="1"/>
       <c r="AN298" s="83"/>
     </row>
-    <row r="299" spans="1:40" s="26" customFormat="1">
+    <row r="299" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A299" s="22" t="s">
         <v>828</v>
       </c>
@@ -41088,7 +41092,7 @@
       <c r="AM299" s="1"/>
       <c r="AN299" s="83"/>
     </row>
-    <row r="300" spans="1:40" s="26" customFormat="1">
+    <row r="300" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A300" s="22" t="s">
         <v>829</v>
       </c>
@@ -41177,7 +41181,7 @@
       <c r="AM300" s="1"/>
       <c r="AN300" s="83"/>
     </row>
-    <row r="301" spans="1:40" s="26" customFormat="1">
+    <row r="301" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A301" s="22" t="s">
         <v>391</v>
       </c>
@@ -41268,7 +41272,7 @@
       <c r="AM301" s="1"/>
       <c r="AN301" s="83"/>
     </row>
-    <row r="302" spans="1:40" s="26" customFormat="1">
+    <row r="302" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A302" s="22" t="s">
         <v>266</v>
       </c>
@@ -41357,7 +41361,7 @@
       <c r="AM302" s="1"/>
       <c r="AN302" s="83"/>
     </row>
-    <row r="303" spans="1:40" s="26" customFormat="1">
+    <row r="303" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A303" s="22" t="s">
         <v>836</v>
       </c>
@@ -41448,7 +41452,7 @@
       <c r="AM303" s="1"/>
       <c r="AN303" s="83"/>
     </row>
-    <row r="304" spans="1:40" s="26" customFormat="1">
+    <row r="304" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A304" s="22" t="s">
         <v>839</v>
       </c>
@@ -41539,7 +41543,7 @@
       <c r="AM304" s="1"/>
       <c r="AN304" s="83"/>
     </row>
-    <row r="305" spans="1:40" s="26" customFormat="1">
+    <row r="305" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A305" s="22" t="s">
         <v>53</v>
       </c>
@@ -41630,7 +41634,7 @@
       <c r="AM305" s="1"/>
       <c r="AN305" s="83"/>
     </row>
-    <row r="306" spans="1:40" s="26" customFormat="1">
+    <row r="306" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A306" s="22" t="s">
         <v>843</v>
       </c>
@@ -41713,7 +41717,7 @@
       <c r="AM306" s="1"/>
       <c r="AN306" s="83"/>
     </row>
-    <row r="307" spans="1:40" s="26" customFormat="1">
+    <row r="307" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A307" s="22" t="s">
         <v>845</v>
       </c>
@@ -41804,7 +41808,7 @@
       <c r="AM307" s="1"/>
       <c r="AN307" s="83"/>
     </row>
-    <row r="308" spans="1:40" s="26" customFormat="1">
+    <row r="308" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A308" s="22" t="s">
         <v>847</v>
       </c>
@@ -41893,7 +41897,7 @@
       <c r="AM308" s="1"/>
       <c r="AN308" s="83"/>
     </row>
-    <row r="309" spans="1:40" s="26" customFormat="1">
+    <row r="309" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A309" s="22" t="s">
         <v>848</v>
       </c>
@@ -41984,7 +41988,7 @@
       <c r="AM309" s="1"/>
       <c r="AN309" s="83"/>
     </row>
-    <row r="310" spans="1:40" s="26" customFormat="1">
+    <row r="310" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A310" s="22" t="s">
         <v>650</v>
       </c>
@@ -42069,7 +42073,7 @@
       <c r="AM310" s="1"/>
       <c r="AN310" s="83"/>
     </row>
-    <row r="311" spans="1:40" s="26" customFormat="1">
+    <row r="311" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A311" s="22" t="s">
         <v>739</v>
       </c>
@@ -42160,7 +42164,7 @@
       <c r="AM311" s="1"/>
       <c r="AN311" s="83"/>
     </row>
-    <row r="312" spans="1:40" s="26" customFormat="1">
+    <row r="312" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A312" s="22" t="s">
         <v>118</v>
       </c>
@@ -42249,7 +42253,7 @@
       <c r="AM312" s="1"/>
       <c r="AN312" s="83"/>
     </row>
-    <row r="313" spans="1:40" s="26" customFormat="1">
+    <row r="313" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A313" s="22">
         <v>98451</v>
       </c>
@@ -42322,7 +42326,7 @@
       <c r="AM313" s="1"/>
       <c r="AN313" s="83"/>
     </row>
-    <row r="314" spans="1:40" s="26" customFormat="1">
+    <row r="314" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A314" s="22" t="s">
         <v>854</v>
       </c>
@@ -42417,7 +42421,7 @@
       <c r="AM314" s="1"/>
       <c r="AN314" s="83"/>
     </row>
-    <row r="315" spans="1:40" s="26" customFormat="1">
+    <row r="315" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A315" s="22" t="s">
         <v>857</v>
       </c>
@@ -42508,7 +42512,7 @@
       <c r="AM315" s="1"/>
       <c r="AN315" s="83"/>
     </row>
-    <row r="316" spans="1:40" s="26" customFormat="1">
+    <row r="316" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A316" s="3" t="s">
         <v>859</v>
       </c>
@@ -42595,7 +42599,7 @@
       <c r="AM316" s="1"/>
       <c r="AN316" s="83"/>
     </row>
-    <row r="317" spans="1:40" s="26" customFormat="1">
+    <row r="317" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A317" s="22" t="s">
         <v>644</v>
       </c>
@@ -42680,7 +42684,7 @@
       <c r="AM317" s="1"/>
       <c r="AN317" s="83"/>
     </row>
-    <row r="318" spans="1:40" s="26" customFormat="1">
+    <row r="318" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A318" s="22" t="s">
         <v>862</v>
       </c>
@@ -42771,7 +42775,7 @@
       <c r="AM318" s="1"/>
       <c r="AN318" s="83"/>
     </row>
-    <row r="319" spans="1:40" s="26" customFormat="1">
+    <row r="319" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A319" s="22" t="s">
         <v>864</v>
       </c>
@@ -42866,7 +42870,7 @@
       <c r="AM319" s="1"/>
       <c r="AN319" s="83"/>
     </row>
-    <row r="320" spans="1:40" s="26" customFormat="1">
+    <row r="320" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A320" s="22" t="s">
         <v>325</v>
       </c>
@@ -42955,7 +42959,7 @@
       <c r="AM320" s="1"/>
       <c r="AN320" s="83"/>
     </row>
-    <row r="321" spans="1:40" s="26" customFormat="1">
+    <row r="321" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A321" s="22" t="s">
         <v>866</v>
       </c>
@@ -43036,7 +43040,7 @@
       <c r="AM321" s="1"/>
       <c r="AN321" s="83"/>
     </row>
-    <row r="322" spans="1:40" s="26" customFormat="1">
+    <row r="322" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A322" s="3" t="s">
         <v>868</v>
       </c>
@@ -43123,7 +43127,7 @@
       <c r="AM322" s="1"/>
       <c r="AN322" s="83"/>
     </row>
-    <row r="323" spans="1:40" s="26" customFormat="1">
+    <row r="323" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A323" s="22" t="s">
         <v>869</v>
       </c>
@@ -43210,7 +43214,7 @@
       <c r="AM323" s="1"/>
       <c r="AN323" s="83"/>
     </row>
-    <row r="324" spans="1:40" s="26" customFormat="1">
+    <row r="324" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A324" s="22" t="s">
         <v>870</v>
       </c>
@@ -43293,7 +43297,7 @@
       <c r="AM324" s="1"/>
       <c r="AN324" s="83"/>
     </row>
-    <row r="325" spans="1:40" s="26" customFormat="1">
+    <row r="325" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A325" s="22" t="s">
         <v>132</v>
       </c>
@@ -43382,7 +43386,7 @@
       <c r="AM325" s="1"/>
       <c r="AN325" s="83"/>
     </row>
-    <row r="326" spans="1:40" s="26" customFormat="1">
+    <row r="326" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A326" s="3" t="s">
         <v>874</v>
       </c>
@@ -43471,7 +43475,7 @@
       <c r="AM326" s="1"/>
       <c r="AN326" s="83"/>
     </row>
-    <row r="327" spans="1:40" s="26" customFormat="1">
+    <row r="327" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A327" s="22" t="s">
         <v>646</v>
       </c>
@@ -43556,7 +43560,7 @@
       <c r="AM327" s="1"/>
       <c r="AN327" s="83"/>
     </row>
-    <row r="328" spans="1:40" s="26" customFormat="1">
+    <row r="328" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A328" s="3" t="s">
         <v>876</v>
       </c>
@@ -43643,7 +43647,7 @@
       <c r="AM328" s="1"/>
       <c r="AN328" s="83"/>
     </row>
-    <row r="329" spans="1:40" s="26" customFormat="1">
+    <row r="329" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
         <v>877</v>
       </c>
@@ -43730,7 +43734,7 @@
       <c r="AM329" s="1"/>
       <c r="AN329" s="83"/>
     </row>
-    <row r="330" spans="1:40" s="26" customFormat="1">
+    <row r="330" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A330" s="3" t="s">
         <v>878</v>
       </c>
@@ -43817,7 +43821,7 @@
       <c r="AM330" s="1"/>
       <c r="AN330" s="83"/>
     </row>
-    <row r="331" spans="1:40" s="26" customFormat="1">
+    <row r="331" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
         <v>880</v>
       </c>
@@ -43900,7 +43904,7 @@
       <c r="AM331" s="1"/>
       <c r="AN331" s="83"/>
     </row>
-    <row r="332" spans="1:40" s="26" customFormat="1">
+    <row r="332" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A332" s="3" t="s">
         <v>883</v>
       </c>
@@ -43983,7 +43987,7 @@
       <c r="AM332" s="1"/>
       <c r="AN332" s="83"/>
     </row>
-    <row r="333" spans="1:40" s="26" customFormat="1">
+    <row r="333" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
         <v>886</v>
       </c>
@@ -44070,7 +44074,7 @@
       <c r="AM333" s="1"/>
       <c r="AN333" s="83"/>
     </row>
-    <row r="334" spans="1:40" s="26" customFormat="1">
+    <row r="334" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A334" s="22" t="s">
         <v>887</v>
       </c>
@@ -44161,7 +44165,7 @@
       <c r="AM334" s="1"/>
       <c r="AN334" s="83"/>
     </row>
-    <row r="335" spans="1:40" s="26" customFormat="1">
+    <row r="335" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A335" s="22" t="s">
         <v>890</v>
       </c>
@@ -44244,7 +44248,7 @@
       <c r="AM335" s="1"/>
       <c r="AN335" s="83"/>
     </row>
-    <row r="336" spans="1:40" s="26" customFormat="1">
+    <row r="336" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A336" s="3" t="s">
         <v>275</v>
       </c>
@@ -44321,7 +44325,7 @@
       <c r="AM336" s="1"/>
       <c r="AN336" s="83"/>
     </row>
-    <row r="337" spans="1:40" s="26" customFormat="1">
+    <row r="337" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A337" s="22" t="s">
         <v>892</v>
       </c>
@@ -44412,7 +44416,7 @@
       <c r="AM337" s="1"/>
       <c r="AN337" s="83"/>
     </row>
-    <row r="338" spans="1:40" s="26" customFormat="1">
+    <row r="338" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A338" s="3" t="s">
         <v>664</v>
       </c>
@@ -44495,7 +44499,7 @@
       <c r="AM338" s="1"/>
       <c r="AN338" s="83"/>
     </row>
-    <row r="339" spans="1:40" s="26" customFormat="1">
+    <row r="339" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A339" s="22" t="s">
         <v>895</v>
       </c>
@@ -44578,7 +44582,7 @@
       <c r="AM339" s="1"/>
       <c r="AN339" s="83"/>
     </row>
-    <row r="340" spans="1:40" s="26" customFormat="1">
+    <row r="340" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A340" s="3" t="s">
         <v>898</v>
       </c>
@@ -44661,7 +44665,7 @@
       <c r="AM340" s="1"/>
       <c r="AN340" s="83"/>
     </row>
-    <row r="341" spans="1:40" s="26" customFormat="1">
+    <row r="341" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A341" s="22" t="s">
         <v>900</v>
       </c>
@@ -44744,7 +44748,7 @@
       <c r="AM341" s="1"/>
       <c r="AN341" s="83"/>
     </row>
-    <row r="342" spans="1:40" s="26" customFormat="1">
+    <row r="342" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A342" s="22" t="s">
         <v>902</v>
       </c>
@@ -44827,7 +44831,7 @@
       <c r="AM342" s="1"/>
       <c r="AN342" s="83"/>
     </row>
-    <row r="343" spans="1:40" s="26" customFormat="1">
+    <row r="343" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
         <v>904</v>
       </c>
@@ -44916,7 +44920,7 @@
       <c r="AM343" s="1"/>
       <c r="AN343" s="83"/>
     </row>
-    <row r="344" spans="1:40" s="26" customFormat="1">
+    <row r="344" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A344" s="22" t="s">
         <v>905</v>
       </c>
@@ -45003,7 +45007,7 @@
       <c r="AM344" s="1"/>
       <c r="AN344" s="83"/>
     </row>
-    <row r="345" spans="1:40" s="26" customFormat="1">
+    <row r="345" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
         <v>907</v>
       </c>
@@ -45090,7 +45094,7 @@
       <c r="AM345" s="1"/>
       <c r="AN345" s="83"/>
     </row>
-    <row r="346" spans="1:40" s="26" customFormat="1">
+    <row r="346" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A346" s="3" t="s">
         <v>655</v>
       </c>
@@ -45177,7 +45181,7 @@
       <c r="AM346" s="1"/>
       <c r="AN346" s="83"/>
     </row>
-    <row r="347" spans="1:40" s="26" customFormat="1">
+    <row r="347" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A347" s="22" t="s">
         <v>909</v>
       </c>
@@ -45256,7 +45260,7 @@
       <c r="AM347" s="1"/>
       <c r="AN347" s="83"/>
     </row>
-    <row r="348" spans="1:40" s="26" customFormat="1">
+    <row r="348" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A348" s="3" t="s">
         <v>912</v>
       </c>
@@ -45343,7 +45347,7 @@
       <c r="AM348" s="1"/>
       <c r="AN348" s="83"/>
     </row>
-    <row r="349" spans="1:40" s="26" customFormat="1">
+    <row r="349" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A349" s="22" t="s">
         <v>913</v>
       </c>
@@ -45430,7 +45434,7 @@
       <c r="AM349" s="1"/>
       <c r="AN349" s="83"/>
     </row>
-    <row r="350" spans="1:40" s="26" customFormat="1">
+    <row r="350" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A350" s="3" t="s">
         <v>915</v>
       </c>
@@ -45513,7 +45517,7 @@
       <c r="AM350" s="1"/>
       <c r="AN350" s="83"/>
     </row>
-    <row r="351" spans="1:40" s="26" customFormat="1">
+    <row r="351" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A351" s="22" t="s">
         <v>917</v>
       </c>
@@ -45604,7 +45608,7 @@
       <c r="AM351" s="1"/>
       <c r="AN351" s="83"/>
     </row>
-    <row r="352" spans="1:40" s="26" customFormat="1">
+    <row r="352" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A352" s="22" t="s">
         <v>918</v>
       </c>
@@ -45687,7 +45691,7 @@
       <c r="AM352" s="1"/>
       <c r="AN352" s="83"/>
     </row>
-    <row r="353" spans="1:40" s="26" customFormat="1">
+    <row r="353" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
         <v>920</v>
       </c>
@@ -45774,7 +45778,7 @@
       <c r="AM353" s="1"/>
       <c r="AN353" s="83"/>
     </row>
-    <row r="354" spans="1:40" s="26" customFormat="1">
+    <row r="354" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A354" s="3" t="s">
         <v>921</v>
       </c>
@@ -45857,7 +45861,7 @@
       <c r="AM354" s="1"/>
       <c r="AN354" s="83"/>
     </row>
-    <row r="355" spans="1:40" s="26" customFormat="1">
+    <row r="355" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A355" s="22" t="s">
         <v>922</v>
       </c>
@@ -45948,7 +45952,7 @@
       <c r="AM355" s="1"/>
       <c r="AN355" s="83"/>
     </row>
-    <row r="356" spans="1:40" s="26" customFormat="1">
+    <row r="356" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A356" s="3" t="s">
         <v>394</v>
       </c>
@@ -46031,7 +46035,7 @@
       <c r="AM356" s="1"/>
       <c r="AN356" s="83"/>
     </row>
-    <row r="357" spans="1:40" s="26" customFormat="1">
+    <row r="357" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A357" s="22" t="s">
         <v>923</v>
       </c>
@@ -46114,7 +46118,7 @@
       <c r="AM357" s="1"/>
       <c r="AN357" s="83"/>
     </row>
-    <row r="358" spans="1:40" s="26" customFormat="1">
+    <row r="358" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A358" s="22" t="s">
         <v>927</v>
       </c>
@@ -46197,7 +46201,7 @@
       <c r="AM358" s="1"/>
       <c r="AN358" s="83"/>
     </row>
-    <row r="359" spans="1:40" s="26" customFormat="1">
+    <row r="359" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
         <v>928</v>
       </c>
@@ -46284,7 +46288,7 @@
       <c r="AM359" s="1"/>
       <c r="AN359" s="83"/>
     </row>
-    <row r="360" spans="1:40" s="26" customFormat="1">
+    <row r="360" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A360" s="22" t="s">
         <v>929</v>
       </c>
@@ -46375,7 +46379,7 @@
       <c r="AM360" s="1"/>
       <c r="AN360" s="83"/>
     </row>
-    <row r="361" spans="1:40" s="26" customFormat="1">
+    <row r="361" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
         <v>370</v>
       </c>
@@ -46458,7 +46462,7 @@
       <c r="AM361" s="1"/>
       <c r="AN361" s="83"/>
     </row>
-    <row r="362" spans="1:40" s="26" customFormat="1">
+    <row r="362" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A362" s="3" t="s">
         <v>930</v>
       </c>
@@ -46545,7 +46549,7 @@
       <c r="AM362" s="1"/>
       <c r="AN362" s="83"/>
     </row>
-    <row r="363" spans="1:40" s="26" customFormat="1">
+    <row r="363" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A363" s="22" t="s">
         <v>932</v>
       </c>
@@ -46628,7 +46632,7 @@
       <c r="AM363" s="1"/>
       <c r="AN363" s="83"/>
     </row>
-    <row r="364" spans="1:40" s="26" customFormat="1">
+    <row r="364" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A364" s="3" t="s">
         <v>659</v>
       </c>
@@ -46711,7 +46715,7 @@
       <c r="AM364" s="1"/>
       <c r="AN364" s="83"/>
     </row>
-    <row r="365" spans="1:40" s="26" customFormat="1">
+    <row r="365" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A365" s="22" t="s">
         <v>933</v>
       </c>
@@ -46794,7 +46798,7 @@
       <c r="AM365" s="1"/>
       <c r="AN365" s="83"/>
     </row>
-    <row r="366" spans="1:40" s="26" customFormat="1">
+    <row r="366" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A366" s="3" t="s">
         <v>934</v>
       </c>
@@ -46877,7 +46881,7 @@
       <c r="AM366" s="1"/>
       <c r="AN366" s="83"/>
     </row>
-    <row r="367" spans="1:40" s="26" customFormat="1">
+    <row r="367" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
         <v>740</v>
       </c>
@@ -46960,7 +46964,7 @@
       <c r="AM367" s="1"/>
       <c r="AN367" s="83"/>
     </row>
-    <row r="368" spans="1:40" s="26" customFormat="1">
+    <row r="368" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A368" s="3" t="s">
         <v>674</v>
       </c>
@@ -47043,7 +47047,7 @@
       <c r="AM368" s="1"/>
       <c r="AN368" s="83"/>
     </row>
-    <row r="369" spans="1:40" s="26" customFormat="1">
+    <row r="369" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
         <v>938</v>
       </c>
@@ -47126,7 +47130,7 @@
       <c r="AM369" s="1"/>
       <c r="AN369" s="83"/>
     </row>
-    <row r="370" spans="1:40" s="26" customFormat="1">
+    <row r="370" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A370" s="22" t="s">
         <v>940</v>
       </c>
@@ -47209,7 +47213,7 @@
       <c r="AM370" s="1"/>
       <c r="AN370" s="83"/>
     </row>
-    <row r="371" spans="1:40" s="26" customFormat="1">
+    <row r="371" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A371" s="22" t="s">
         <v>943</v>
       </c>
@@ -47292,7 +47296,7 @@
       <c r="AM371" s="1"/>
       <c r="AN371" s="83"/>
     </row>
-    <row r="372" spans="1:40" s="26" customFormat="1">
+    <row r="372" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A372" s="22" t="s">
         <v>945</v>
       </c>
@@ -47375,7 +47379,7 @@
       <c r="AM372" s="1"/>
       <c r="AN372" s="83"/>
     </row>
-    <row r="373" spans="1:40" s="26" customFormat="1">
+    <row r="373" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
         <v>946</v>
       </c>
@@ -47458,7 +47462,7 @@
       <c r="AM373" s="1"/>
       <c r="AN373" s="83"/>
     </row>
-    <row r="374" spans="1:40" s="26" customFormat="1">
+    <row r="374" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A374" s="3" t="s">
         <v>948</v>
       </c>
@@ -47541,7 +47545,7 @@
       <c r="AM374" s="1"/>
       <c r="AN374" s="83"/>
     </row>
-    <row r="375" spans="1:40" s="26" customFormat="1">
+    <row r="375" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A375" s="22" t="s">
         <v>949</v>
       </c>
@@ -47624,7 +47628,7 @@
       <c r="AM375" s="1"/>
       <c r="AN375" s="83"/>
     </row>
-    <row r="376" spans="1:40" s="26" customFormat="1">
+    <row r="376" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A376" s="3" t="s">
         <v>950</v>
       </c>
@@ -47707,7 +47711,7 @@
       <c r="AM376" s="1"/>
       <c r="AN376" s="83"/>
     </row>
-    <row r="377" spans="1:40" s="26" customFormat="1">
+    <row r="377" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A377" s="22" t="s">
         <v>951</v>
       </c>
@@ -47790,7 +47794,7 @@
       <c r="AM377" s="1"/>
       <c r="AN377" s="83"/>
     </row>
-    <row r="378" spans="1:40" s="26" customFormat="1">
+    <row r="378" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A378" s="22" t="s">
         <v>953</v>
       </c>
@@ -47873,7 +47877,7 @@
       <c r="AM378" s="1"/>
       <c r="AN378" s="83"/>
     </row>
-    <row r="379" spans="1:40" s="26" customFormat="1">
+    <row r="379" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A379" s="22" t="s">
         <v>956</v>
       </c>
@@ -47956,7 +47960,7 @@
       <c r="AM379" s="1"/>
       <c r="AN379" s="83"/>
     </row>
-    <row r="380" spans="1:40" s="26" customFormat="1">
+    <row r="380" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A380" s="22" t="s">
         <v>958</v>
       </c>
@@ -48039,7 +48043,7 @@
       <c r="AM380" s="1"/>
       <c r="AN380" s="83"/>
     </row>
-    <row r="381" spans="1:40" s="26" customFormat="1">
+    <row r="381" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A381" s="22" t="s">
         <v>962</v>
       </c>
@@ -48126,7 +48130,7 @@
       <c r="AM381" s="1"/>
       <c r="AN381" s="83"/>
     </row>
-    <row r="382" spans="1:40" s="26" customFormat="1">
+    <row r="382" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A382" s="3" t="s">
         <v>964</v>
       </c>
@@ -48205,7 +48209,7 @@
       <c r="AM382" s="1"/>
       <c r="AN382" s="83"/>
     </row>
-    <row r="383" spans="1:40" s="26" customFormat="1">
+    <row r="383" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A383" s="22" t="s">
         <v>966</v>
       </c>
@@ -48288,7 +48292,7 @@
       <c r="AM383" s="1"/>
       <c r="AN383" s="83"/>
     </row>
-    <row r="384" spans="1:40" s="26" customFormat="1">
+    <row r="384" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A384" s="22" t="s">
         <v>323</v>
       </c>
@@ -48371,7 +48375,7 @@
       <c r="AM384" s="1"/>
       <c r="AN384" s="83"/>
     </row>
-    <row r="385" spans="1:40" s="26" customFormat="1">
+    <row r="385" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
         <v>967</v>
       </c>
@@ -48458,7 +48462,7 @@
       <c r="AM385" s="1"/>
       <c r="AN385" s="83"/>
     </row>
-    <row r="386" spans="1:40" s="26" customFormat="1">
+    <row r="386" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A386" s="22" t="s">
         <v>471</v>
       </c>
@@ -48541,7 +48545,7 @@
       <c r="AM386" s="1"/>
       <c r="AN386" s="83"/>
     </row>
-    <row r="387" spans="1:40" s="26" customFormat="1">
+    <row r="387" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A387" s="22" t="s">
         <v>316</v>
       </c>
@@ -48624,7 +48628,7 @@
       <c r="AM387" s="1"/>
       <c r="AN387" s="83"/>
     </row>
-    <row r="388" spans="1:40" s="26" customFormat="1">
+    <row r="388" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A388" s="3" t="s">
         <v>971</v>
       </c>
@@ -48707,7 +48711,7 @@
       <c r="AM388" s="1"/>
       <c r="AN388" s="83"/>
     </row>
-    <row r="389" spans="1:40" s="26" customFormat="1">
+    <row r="389" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A389" s="22" t="s">
         <v>972</v>
       </c>
@@ -48798,7 +48802,7 @@
       <c r="AM389" s="1"/>
       <c r="AN389" s="83"/>
     </row>
-    <row r="390" spans="1:40" s="26" customFormat="1">
+    <row r="390" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A390" s="22" t="s">
         <v>973</v>
       </c>
@@ -48889,7 +48893,7 @@
       <c r="AM390" s="1"/>
       <c r="AN390" s="83"/>
     </row>
-    <row r="391" spans="1:40" s="26" customFormat="1">
+    <row r="391" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A391" s="22" t="s">
         <v>974</v>
       </c>
@@ -48972,7 +48976,7 @@
       <c r="AM391" s="1"/>
       <c r="AN391" s="83"/>
     </row>
-    <row r="392" spans="1:40" s="26" customFormat="1">
+    <row r="392" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A392" s="22" t="s">
         <v>975</v>
       </c>
@@ -49055,7 +49059,7 @@
       <c r="AM392" s="1"/>
       <c r="AN392" s="83"/>
     </row>
-    <row r="393" spans="1:40" s="26" customFormat="1">
+    <row r="393" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A393" s="22" t="s">
         <v>977</v>
       </c>
@@ -49146,7 +49150,7 @@
       <c r="AM393" s="1"/>
       <c r="AN393" s="83"/>
     </row>
-    <row r="394" spans="1:40" s="26" customFormat="1">
+    <row r="394" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A394" s="22" t="s">
         <v>446</v>
       </c>
@@ -49229,7 +49233,7 @@
       <c r="AM394" s="1"/>
       <c r="AN394" s="83"/>
     </row>
-    <row r="395" spans="1:40" s="26" customFormat="1">
+    <row r="395" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A395" s="22" t="s">
         <v>979</v>
       </c>
@@ -49320,7 +49324,7 @@
       <c r="AM395" s="1"/>
       <c r="AN395" s="83"/>
     </row>
-    <row r="396" spans="1:40" s="26" customFormat="1">
+    <row r="396" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A396" s="22" t="s">
         <v>482</v>
       </c>
@@ -49403,7 +49407,7 @@
       <c r="AM396" s="1"/>
       <c r="AN396" s="83"/>
     </row>
-    <row r="397" spans="1:40" s="26" customFormat="1">
+    <row r="397" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A397" s="22" t="s">
         <v>982</v>
       </c>
@@ -49486,7 +49490,7 @@
       <c r="AM397" s="1"/>
       <c r="AN397" s="83"/>
     </row>
-    <row r="398" spans="1:40" s="26" customFormat="1">
+    <row r="398" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A398" s="22" t="s">
         <v>983</v>
       </c>
@@ -49569,7 +49573,7 @@
       <c r="AM398" s="1"/>
       <c r="AN398" s="83"/>
     </row>
-    <row r="399" spans="1:40" s="26" customFormat="1">
+    <row r="399" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A399" s="22" t="s">
         <v>985</v>
       </c>
@@ -49652,7 +49656,7 @@
       <c r="AM399" s="1"/>
       <c r="AN399" s="83"/>
     </row>
-    <row r="400" spans="1:40" s="26" customFormat="1">
+    <row r="400" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A400" s="3" t="s">
         <v>986</v>
       </c>
@@ -49735,7 +49739,7 @@
       <c r="AM400" s="1"/>
       <c r="AN400" s="83"/>
     </row>
-    <row r="401" spans="1:40" s="26" customFormat="1">
+    <row r="401" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
         <v>987</v>
       </c>
@@ -49822,7 +49826,7 @@
       <c r="AM401" s="1"/>
       <c r="AN401" s="83"/>
     </row>
-    <row r="402" spans="1:40" s="26" customFormat="1">
+    <row r="402" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A402" s="22" t="s">
         <v>988</v>
       </c>
@@ -49905,7 +49909,7 @@
       <c r="AM402" s="1"/>
       <c r="AN402" s="83"/>
     </row>
-    <row r="403" spans="1:40" s="26" customFormat="1">
+    <row r="403" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A403" s="22" t="s">
         <v>989</v>
       </c>
@@ -49988,7 +49992,7 @@
       <c r="AM403" s="1"/>
       <c r="AN403" s="83"/>
     </row>
-    <row r="404" spans="1:40" s="26" customFormat="1">
+    <row r="404" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A404" s="22" t="s">
         <v>992</v>
       </c>
@@ -50077,7 +50081,7 @@
       <c r="AM404" s="1"/>
       <c r="AN404" s="83"/>
     </row>
-    <row r="405" spans="1:40" s="26" customFormat="1">
+    <row r="405" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A405" s="22" t="s">
         <v>993</v>
       </c>
@@ -50168,7 +50172,7 @@
       <c r="AM405" s="1"/>
       <c r="AN405" s="83"/>
     </row>
-    <row r="406" spans="1:40" s="26" customFormat="1">
+    <row r="406" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A406" s="3" t="s">
         <v>995</v>
       </c>
@@ -50255,7 +50259,7 @@
       <c r="AM406" s="1"/>
       <c r="AN406" s="83"/>
     </row>
-    <row r="407" spans="1:40" s="26" customFormat="1">
+    <row r="407" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A407" s="22" t="s">
         <v>997</v>
       </c>
@@ -50346,7 +50350,7 @@
       <c r="AM407" s="1"/>
       <c r="AN407" s="83"/>
     </row>
-    <row r="408" spans="1:40" s="26" customFormat="1">
+    <row r="408" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A408" s="22" t="s">
         <v>999</v>
       </c>
@@ -50429,7 +50433,7 @@
       <c r="AM408" s="1"/>
       <c r="AN408" s="83"/>
     </row>
-    <row r="409" spans="1:40" s="26" customFormat="1">
+    <row r="409" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A409" s="22" t="s">
         <v>1001</v>
       </c>
@@ -50512,7 +50516,7 @@
       <c r="AM409" s="1"/>
       <c r="AN409" s="83"/>
     </row>
-    <row r="410" spans="1:40" s="26" customFormat="1">
+    <row r="410" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A410" s="22" t="s">
         <v>1003</v>
       </c>
@@ -50595,7 +50599,7 @@
       <c r="AM410" s="1"/>
       <c r="AN410" s="83"/>
     </row>
-    <row r="411" spans="1:40" s="26" customFormat="1">
+    <row r="411" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A411" s="22" t="s">
         <v>414</v>
       </c>
@@ -50678,7 +50682,7 @@
       <c r="AM411" s="1"/>
       <c r="AN411" s="83"/>
     </row>
-    <row r="412" spans="1:40" s="26" customFormat="1">
+    <row r="412" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A412" s="22" t="s">
         <v>1005</v>
       </c>
@@ -50761,7 +50765,7 @@
       <c r="AM412" s="1"/>
       <c r="AN412" s="83"/>
     </row>
-    <row r="413" spans="1:40" s="26" customFormat="1">
+    <row r="413" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A413" s="22" t="s">
         <v>1006</v>
       </c>
@@ -50844,7 +50848,7 @@
       <c r="AM413" s="1"/>
       <c r="AN413" s="83"/>
     </row>
-    <row r="414" spans="1:40" s="26" customFormat="1">
+    <row r="414" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A414" s="22" t="s">
         <v>1008</v>
       </c>
@@ -50927,7 +50931,7 @@
       <c r="AM414" s="1"/>
       <c r="AN414" s="83"/>
     </row>
-    <row r="415" spans="1:40" s="26" customFormat="1">
+    <row r="415" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A415" s="22" t="s">
         <v>1010</v>
       </c>
@@ -51016,7 +51020,7 @@
       <c r="AM415" s="1"/>
       <c r="AN415" s="83"/>
     </row>
-    <row r="416" spans="1:40" s="26" customFormat="1">
+    <row r="416" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A416" s="22" t="s">
         <v>1011</v>
       </c>
@@ -51107,7 +51111,7 @@
       <c r="AM416" s="1"/>
       <c r="AN416" s="83"/>
     </row>
-    <row r="417" spans="1:40" s="26" customFormat="1">
+    <row r="417" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A417" s="22" t="s">
         <v>1012</v>
       </c>
@@ -51198,7 +51202,7 @@
       <c r="AM417" s="1"/>
       <c r="AN417" s="83"/>
     </row>
-    <row r="418" spans="1:40" s="26" customFormat="1">
+    <row r="418" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A418" s="22" t="s">
         <v>1013</v>
       </c>
@@ -51287,7 +51291,7 @@
       <c r="AM418" s="1"/>
       <c r="AN418" s="83"/>
     </row>
-    <row r="419" spans="1:40" s="26" customFormat="1">
+    <row r="419" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A419" s="22" t="s">
         <v>1014</v>
       </c>
@@ -51378,7 +51382,7 @@
       <c r="AM419" s="1"/>
       <c r="AN419" s="83"/>
     </row>
-    <row r="420" spans="1:40" s="26" customFormat="1">
+    <row r="420" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A420" s="22" t="s">
         <v>1015</v>
       </c>
@@ -51461,7 +51465,7 @@
       <c r="AM420" s="1"/>
       <c r="AN420" s="83"/>
     </row>
-    <row r="421" spans="1:40" s="26" customFormat="1">
+    <row r="421" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A421" s="22" t="s">
         <v>1017</v>
       </c>
@@ -51544,7 +51548,7 @@
       <c r="AM421" s="1"/>
       <c r="AN421" s="83"/>
     </row>
-    <row r="422" spans="1:40" s="26" customFormat="1">
+    <row r="422" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A422" s="22" t="s">
         <v>1019</v>
       </c>
@@ -51627,7 +51631,7 @@
       <c r="AM422" s="1"/>
       <c r="AN422" s="83"/>
     </row>
-    <row r="423" spans="1:40" s="26" customFormat="1">
+    <row r="423" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A423" s="22" t="s">
         <v>1021</v>
       </c>
@@ -51710,7 +51714,7 @@
       <c r="AM423" s="1"/>
       <c r="AN423" s="83"/>
     </row>
-    <row r="424" spans="1:40" s="26" customFormat="1">
+    <row r="424" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A424" s="22" t="s">
         <v>1024</v>
       </c>
@@ -51793,7 +51797,7 @@
       <c r="AM424" s="1"/>
       <c r="AN424" s="83"/>
     </row>
-    <row r="425" spans="1:40" s="26" customFormat="1">
+    <row r="425" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A425" s="22" t="s">
         <v>1026</v>
       </c>
@@ -51876,7 +51880,7 @@
       <c r="AM425" s="1"/>
       <c r="AN425" s="83"/>
     </row>
-    <row r="426" spans="1:40" s="26" customFormat="1">
+    <row r="426" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A426" s="22" t="s">
         <v>1028</v>
       </c>
@@ -51959,7 +51963,7 @@
       <c r="AM426" s="1"/>
       <c r="AN426" s="83"/>
     </row>
-    <row r="427" spans="1:40" s="26" customFormat="1">
+    <row r="427" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A427" s="22" t="s">
         <v>1029</v>
       </c>
@@ -52042,7 +52046,7 @@
       <c r="AM427" s="1"/>
       <c r="AN427" s="83"/>
     </row>
-    <row r="428" spans="1:40" s="26" customFormat="1">
+    <row r="428" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A428" s="22" t="s">
         <v>1030</v>
       </c>
@@ -52125,7 +52129,7 @@
       <c r="AM428" s="1"/>
       <c r="AN428" s="83"/>
     </row>
-    <row r="429" spans="1:40" s="26" customFormat="1">
+    <row r="429" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A429" s="22" t="s">
         <v>1032</v>
       </c>
@@ -52208,7 +52212,7 @@
       <c r="AM429" s="1"/>
       <c r="AN429" s="83"/>
     </row>
-    <row r="430" spans="1:40" s="26" customFormat="1">
+    <row r="430" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A430" s="22" t="s">
         <v>1034</v>
       </c>
@@ -52291,7 +52295,7 @@
       <c r="AM430" s="1"/>
       <c r="AN430" s="83"/>
     </row>
-    <row r="431" spans="1:40" s="26" customFormat="1">
+    <row r="431" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A431" s="22" t="s">
         <v>1036</v>
       </c>
@@ -52374,7 +52378,7 @@
       <c r="AM431" s="1"/>
       <c r="AN431" s="83"/>
     </row>
-    <row r="432" spans="1:40" s="26" customFormat="1">
+    <row r="432" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A432" s="22" t="s">
         <v>642</v>
       </c>
@@ -52457,7 +52461,7 @@
       <c r="AM432" s="1"/>
       <c r="AN432" s="83"/>
     </row>
-    <row r="433" spans="1:40" s="26" customFormat="1">
+    <row r="433" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A433" s="22" t="s">
         <v>1041</v>
       </c>
@@ -52540,7 +52544,7 @@
       <c r="AM433" s="1"/>
       <c r="AN433" s="83"/>
     </row>
-    <row r="434" spans="1:40" s="26" customFormat="1">
+    <row r="434" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A434" s="22" t="s">
         <v>1043</v>
       </c>
@@ -52623,7 +52627,7 @@
       <c r="AM434" s="1"/>
       <c r="AN434" s="83"/>
     </row>
-    <row r="435" spans="1:40" s="26" customFormat="1">
+    <row r="435" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A435" s="22" t="s">
         <v>1044</v>
       </c>
@@ -52706,7 +52710,7 @@
       <c r="AM435" s="1"/>
       <c r="AN435" s="83"/>
     </row>
-    <row r="436" spans="1:40" s="26" customFormat="1">
+    <row r="436" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A436" s="22" t="s">
         <v>1046</v>
       </c>
@@ -52789,7 +52793,7 @@
       <c r="AM436" s="1"/>
       <c r="AN436" s="83"/>
     </row>
-    <row r="437" spans="1:40" s="26" customFormat="1">
+    <row r="437" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A437" s="22" t="s">
         <v>1048</v>
       </c>
@@ -52872,7 +52876,7 @@
       <c r="AM437" s="1"/>
       <c r="AN437" s="83"/>
     </row>
-    <row r="438" spans="1:40" s="26" customFormat="1">
+    <row r="438" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A438" s="22" t="s">
         <v>398</v>
       </c>
@@ -52955,7 +52959,7 @@
       <c r="AM438" s="1"/>
       <c r="AN438" s="83"/>
     </row>
-    <row r="439" spans="1:40" s="26" customFormat="1">
+    <row r="439" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A439" s="22" t="s">
         <v>745</v>
       </c>
@@ -53038,7 +53042,7 @@
       <c r="AM439" s="1"/>
       <c r="AN439" s="83"/>
     </row>
-    <row r="440" spans="1:40" s="26" customFormat="1">
+    <row r="440" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A440" s="22" t="s">
         <v>1053</v>
       </c>
@@ -53121,7 +53125,7 @@
       <c r="AM440" s="1"/>
       <c r="AN440" s="83"/>
     </row>
-    <row r="441" spans="1:40" s="26" customFormat="1">
+    <row r="441" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A441" s="22" t="s">
         <v>1054</v>
       </c>
@@ -53204,7 +53208,7 @@
       <c r="AM441" s="1"/>
       <c r="AN441" s="83"/>
     </row>
-    <row r="442" spans="1:40" s="26" customFormat="1">
+    <row r="442" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A442" s="22" t="s">
         <v>1055</v>
       </c>
@@ -53287,7 +53291,7 @@
       <c r="AM442" s="1"/>
       <c r="AN442" s="83"/>
     </row>
-    <row r="443" spans="1:40" s="26" customFormat="1">
+    <row r="443" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A443" s="22" t="s">
         <v>1057</v>
       </c>
@@ -53370,7 +53374,7 @@
       <c r="AM443" s="1"/>
       <c r="AN443" s="83"/>
     </row>
-    <row r="444" spans="1:40" s="26" customFormat="1">
+    <row r="444" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A444" s="22" t="s">
         <v>1059</v>
       </c>
@@ -53453,7 +53457,7 @@
       <c r="AM444" s="1"/>
       <c r="AN444" s="83"/>
     </row>
-    <row r="445" spans="1:40" s="26" customFormat="1">
+    <row r="445" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A445" s="22" t="s">
         <v>1062</v>
       </c>
@@ -53536,7 +53540,7 @@
       <c r="AM445" s="1"/>
       <c r="AN445" s="83"/>
     </row>
-    <row r="446" spans="1:40" s="26" customFormat="1">
+    <row r="446" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A446" s="22" t="s">
         <v>1063</v>
       </c>
@@ -53619,7 +53623,7 @@
       <c r="AM446" s="1"/>
       <c r="AN446" s="83"/>
     </row>
-    <row r="447" spans="1:40" s="26" customFormat="1">
+    <row r="447" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A447" s="3" t="s">
         <v>653</v>
       </c>
@@ -53694,7 +53698,7 @@
       <c r="AM447" s="1"/>
       <c r="AN447" s="83"/>
     </row>
-    <row r="448" spans="1:40" s="26" customFormat="1">
+    <row r="448" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A448" s="3" t="s">
         <v>1064</v>
       </c>
@@ -53777,7 +53781,7 @@
       <c r="AM448" s="1"/>
       <c r="AN448" s="83"/>
     </row>
-    <row r="449" spans="1:40" s="26" customFormat="1">
+    <row r="449" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A449" s="3" t="s">
         <v>1065</v>
       </c>
@@ -53860,7 +53864,7 @@
       <c r="AM449" s="1"/>
       <c r="AN449" s="83"/>
     </row>
-    <row r="450" spans="1:40" s="26" customFormat="1">
+    <row r="450" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A450" s="3" t="s">
         <v>1066</v>
       </c>
@@ -53943,7 +53947,7 @@
       <c r="AM450" s="1"/>
       <c r="AN450" s="83"/>
     </row>
-    <row r="451" spans="1:40" s="26" customFormat="1">
+    <row r="451" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A451" s="3" t="s">
         <v>1067</v>
       </c>
@@ -54026,7 +54030,7 @@
       <c r="AM451" s="1"/>
       <c r="AN451" s="83"/>
     </row>
-    <row r="452" spans="1:40" s="26" customFormat="1">
+    <row r="452" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A452" s="3" t="s">
         <v>1068</v>
       </c>
@@ -54109,7 +54113,7 @@
       <c r="AM452" s="1"/>
       <c r="AN452" s="83"/>
     </row>
-    <row r="453" spans="1:40" s="26" customFormat="1">
+    <row r="453" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A453" s="3" t="s">
         <v>1069</v>
       </c>
@@ -54192,7 +54196,7 @@
       <c r="AM453" s="1"/>
       <c r="AN453" s="83"/>
     </row>
-    <row r="454" spans="1:40" s="26" customFormat="1">
+    <row r="454" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A454" s="3" t="s">
         <v>1070</v>
       </c>
@@ -54275,7 +54279,7 @@
       <c r="AM454" s="1"/>
       <c r="AN454" s="83"/>
     </row>
-    <row r="455" spans="1:40" s="26" customFormat="1">
+    <row r="455" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A455" s="3" t="s">
         <v>1071</v>
       </c>
@@ -54358,7 +54362,7 @@
       <c r="AM455" s="1"/>
       <c r="AN455" s="83"/>
     </row>
-    <row r="456" spans="1:40" s="26" customFormat="1">
+    <row r="456" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A456" s="3" t="s">
         <v>1072</v>
       </c>
@@ -54441,7 +54445,7 @@
       <c r="AM456" s="1"/>
       <c r="AN456" s="83"/>
     </row>
-    <row r="457" spans="1:40" s="26" customFormat="1">
+    <row r="457" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A457" s="3" t="s">
         <v>1074</v>
       </c>
@@ -54524,7 +54528,7 @@
       <c r="AM457" s="1"/>
       <c r="AN457" s="83"/>
     </row>
-    <row r="458" spans="1:40" s="26" customFormat="1">
+    <row r="458" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A458" s="3" t="s">
         <v>1075</v>
       </c>
@@ -54607,7 +54611,7 @@
       <c r="AM458" s="1"/>
       <c r="AN458" s="83"/>
     </row>
-    <row r="459" spans="1:40" s="26" customFormat="1">
+    <row r="459" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A459" s="3" t="s">
         <v>1076</v>
       </c>
@@ -54690,7 +54694,7 @@
       <c r="AM459" s="1"/>
       <c r="AN459" s="83"/>
     </row>
-    <row r="460" spans="1:40" s="26" customFormat="1">
+    <row r="460" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A460" s="3" t="s">
         <v>1078</v>
       </c>
@@ -54773,7 +54777,7 @@
       <c r="AM460" s="1"/>
       <c r="AN460" s="83"/>
     </row>
-    <row r="461" spans="1:40" s="26" customFormat="1">
+    <row r="461" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A461" s="3" t="s">
         <v>1079</v>
       </c>
@@ -54856,7 +54860,7 @@
       <c r="AM461" s="1"/>
       <c r="AN461" s="83"/>
     </row>
-    <row r="462" spans="1:40" s="26" customFormat="1">
+    <row r="462" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A462" s="3" t="s">
         <v>1080</v>
       </c>
@@ -54939,7 +54943,7 @@
       <c r="AM462" s="1"/>
       <c r="AN462" s="83"/>
     </row>
-    <row r="463" spans="1:40" s="26" customFormat="1">
+    <row r="463" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A463" s="3" t="s">
         <v>1081</v>
       </c>
@@ -55026,7 +55030,7 @@
       <c r="AM463" s="1"/>
       <c r="AN463" s="83"/>
     </row>
-    <row r="464" spans="1:40" s="26" customFormat="1">
+    <row r="464" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A464" s="3" t="s">
         <v>1082</v>
       </c>
@@ -55109,7 +55113,7 @@
       <c r="AM464" s="1"/>
       <c r="AN464" s="83"/>
     </row>
-    <row r="465" spans="1:40" s="26" customFormat="1">
+    <row r="465" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A465" s="3" t="s">
         <v>1083</v>
       </c>
@@ -55192,7 +55196,7 @@
       <c r="AM465" s="1"/>
       <c r="AN465" s="83"/>
     </row>
-    <row r="466" spans="1:40" s="26" customFormat="1">
+    <row r="466" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A466" s="3" t="s">
         <v>1084</v>
       </c>
@@ -55275,7 +55279,7 @@
       <c r="AM466" s="1"/>
       <c r="AN466" s="83"/>
     </row>
-    <row r="467" spans="1:40" s="26" customFormat="1">
+    <row r="467" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A467" s="3" t="s">
         <v>1086</v>
       </c>
@@ -55358,7 +55362,7 @@
       <c r="AM467" s="1"/>
       <c r="AN467" s="83"/>
     </row>
-    <row r="468" spans="1:40" s="26" customFormat="1">
+    <row r="468" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A468" s="3" t="s">
         <v>1088</v>
       </c>
@@ -55441,7 +55445,7 @@
       <c r="AM468" s="1"/>
       <c r="AN468" s="83"/>
     </row>
-    <row r="469" spans="1:40" s="26" customFormat="1">
+    <row r="469" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A469" s="3" t="s">
         <v>1090</v>
       </c>
@@ -55524,7 +55528,7 @@
       <c r="AM469" s="1"/>
       <c r="AN469" s="83"/>
     </row>
-    <row r="470" spans="1:40" s="26" customFormat="1">
+    <row r="470" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A470" s="3" t="s">
         <v>1091</v>
       </c>
@@ -55607,7 +55611,7 @@
       <c r="AM470" s="1"/>
       <c r="AN470" s="83"/>
     </row>
-    <row r="471" spans="1:40" s="26" customFormat="1">
+    <row r="471" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A471" s="3" t="s">
         <v>1092</v>
       </c>
@@ -55690,7 +55694,7 @@
       <c r="AM471" s="1"/>
       <c r="AN471" s="83"/>
     </row>
-    <row r="472" spans="1:40" s="26" customFormat="1">
+    <row r="472" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A472" s="3" t="s">
         <v>1093</v>
       </c>
@@ -55773,7 +55777,7 @@
       <c r="AM472" s="1"/>
       <c r="AN472" s="83"/>
     </row>
-    <row r="473" spans="1:40" s="26" customFormat="1">
+    <row r="473" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A473" s="3" t="s">
         <v>1095</v>
       </c>
@@ -55856,7 +55860,7 @@
       <c r="AM473" s="1"/>
       <c r="AN473" s="83"/>
     </row>
-    <row r="474" spans="1:40" s="26" customFormat="1">
+    <row r="474" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A474" s="3" t="s">
         <v>1097</v>
       </c>
@@ -55939,7 +55943,7 @@
       <c r="AM474" s="1"/>
       <c r="AN474" s="83"/>
     </row>
-    <row r="475" spans="1:40" s="26" customFormat="1">
+    <row r="475" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A475" s="3" t="s">
         <v>1099</v>
       </c>
@@ -56022,7 +56026,7 @@
       <c r="AM475" s="1"/>
       <c r="AN475" s="83"/>
     </row>
-    <row r="476" spans="1:40" s="26" customFormat="1">
+    <row r="476" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A476" s="3" t="s">
         <v>1101</v>
       </c>
@@ -56105,7 +56109,7 @@
       <c r="AM476" s="1"/>
       <c r="AN476" s="83"/>
     </row>
-    <row r="477" spans="1:40" s="26" customFormat="1">
+    <row r="477" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A477" s="3" t="s">
         <v>1103</v>
       </c>
@@ -56192,7 +56196,7 @@
       <c r="AM477" s="1"/>
       <c r="AN477" s="83"/>
     </row>
-    <row r="478" spans="1:40" s="26" customFormat="1">
+    <row r="478" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A478" s="3" t="s">
         <v>1104</v>
       </c>
@@ -56279,7 +56283,7 @@
       <c r="AM478" s="1"/>
       <c r="AN478" s="83"/>
     </row>
-    <row r="479" spans="1:40" s="26" customFormat="1">
+    <row r="479" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A479" s="3" t="s">
         <v>1105</v>
       </c>
@@ -56366,7 +56370,7 @@
       <c r="AM479" s="1"/>
       <c r="AN479" s="83"/>
     </row>
-    <row r="480" spans="1:40" s="26" customFormat="1">
+    <row r="480" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A480" s="3" t="s">
         <v>1106</v>
       </c>
@@ -56449,7 +56453,7 @@
       <c r="AM480" s="1"/>
       <c r="AN480" s="83"/>
     </row>
-    <row r="481" spans="1:40" s="26" customFormat="1">
+    <row r="481" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A481" s="3" t="s">
         <v>1108</v>
       </c>
@@ -56532,7 +56536,7 @@
       <c r="AM481" s="1"/>
       <c r="AN481" s="83"/>
     </row>
-    <row r="482" spans="1:40" s="26" customFormat="1">
+    <row r="482" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A482" s="3" t="s">
         <v>1109</v>
       </c>
@@ -56615,7 +56619,7 @@
       <c r="AM482" s="1"/>
       <c r="AN482" s="83"/>
     </row>
-    <row r="483" spans="1:40" s="26" customFormat="1">
+    <row r="483" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A483" s="3" t="s">
         <v>1110</v>
       </c>
@@ -56702,7 +56706,7 @@
       <c r="AM483" s="1"/>
       <c r="AN483" s="83"/>
     </row>
-    <row r="484" spans="1:40" s="26" customFormat="1">
+    <row r="484" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A484" s="3" t="s">
         <v>1111</v>
       </c>
@@ -56789,7 +56793,7 @@
       <c r="AM484" s="1"/>
       <c r="AN484" s="83"/>
     </row>
-    <row r="485" spans="1:40" s="26" customFormat="1">
+    <row r="485" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A485" s="3" t="s">
         <v>1112</v>
       </c>
@@ -56872,7 +56876,7 @@
       <c r="AM485" s="1"/>
       <c r="AN485" s="83"/>
     </row>
-    <row r="486" spans="1:40" s="26" customFormat="1">
+    <row r="486" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A486" s="22" t="s">
         <v>1114</v>
       </c>
@@ -56955,7 +56959,7 @@
       <c r="AM486" s="1"/>
       <c r="AN486" s="83"/>
     </row>
-    <row r="487" spans="1:40" s="26" customFormat="1">
+    <row r="487" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A487" s="22" t="s">
         <v>1115</v>
       </c>
@@ -57038,7 +57042,7 @@
       <c r="AM487" s="1"/>
       <c r="AN487" s="83"/>
     </row>
-    <row r="488" spans="1:40" s="26" customFormat="1">
+    <row r="488" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A488" s="22" t="s">
         <v>1117</v>
       </c>
@@ -57121,7 +57125,7 @@
       <c r="AM488" s="1"/>
       <c r="AN488" s="83"/>
     </row>
-    <row r="489" spans="1:40" s="26" customFormat="1">
+    <row r="489" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A489" s="22" t="s">
         <v>1118</v>
       </c>
@@ -57204,7 +57208,7 @@
       <c r="AM489" s="1"/>
       <c r="AN489" s="83"/>
     </row>
-    <row r="490" spans="1:40" s="26" customFormat="1">
+    <row r="490" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A490" s="22" t="s">
         <v>1119</v>
       </c>
@@ -57287,7 +57291,7 @@
       <c r="AM490" s="1"/>
       <c r="AN490" s="83"/>
     </row>
-    <row r="491" spans="1:40" s="26" customFormat="1">
+    <row r="491" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A491" s="22" t="s">
         <v>1120</v>
       </c>
@@ -57378,7 +57382,7 @@
       <c r="AM491" s="1"/>
       <c r="AN491" s="83"/>
     </row>
-    <row r="492" spans="1:40" s="26" customFormat="1">
+    <row r="492" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A492" s="22" t="s">
         <v>453</v>
       </c>
@@ -57457,7 +57461,7 @@
       <c r="AM492" s="1"/>
       <c r="AN492" s="83"/>
     </row>
-    <row r="493" spans="1:40" s="26" customFormat="1">
+    <row r="493" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A493" s="22" t="s">
         <v>1123</v>
       </c>
@@ -57526,7 +57530,7 @@
       <c r="AM493" s="1"/>
       <c r="AN493" s="83"/>
     </row>
-    <row r="494" spans="1:40" s="26" customFormat="1">
+    <row r="494" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A494" s="22" t="s">
         <v>1125</v>
       </c>
@@ -57595,7 +57599,7 @@
       <c r="AM494" s="1"/>
       <c r="AN494" s="83"/>
     </row>
-    <row r="495" spans="1:40" s="26" customFormat="1">
+    <row r="495" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A495" s="22" t="s">
         <v>1126</v>
       </c>
@@ -57664,7 +57668,7 @@
       <c r="AM495" s="1"/>
       <c r="AN495" s="83"/>
     </row>
-    <row r="496" spans="1:40" s="26" customFormat="1">
+    <row r="496" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A496" s="22" t="s">
         <v>1127</v>
       </c>
@@ -57733,7 +57737,7 @@
       <c r="AM496" s="1"/>
       <c r="AN496" s="83"/>
     </row>
-    <row r="497" spans="1:41" s="26" customFormat="1">
+    <row r="497" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A497" s="22" t="s">
         <v>1128</v>
       </c>
@@ -57802,7 +57806,7 @@
       <c r="AM497" s="1"/>
       <c r="AN497" s="83"/>
     </row>
-    <row r="498" spans="1:41" s="26" customFormat="1" ht="20.45" hidden="1">
+    <row r="498" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" s="19" t="s">
         <v>1129</v>
       </c>
@@ -57917,7 +57921,7 @@
       </c>
       <c r="AO498" s="81"/>
     </row>
-    <row r="499" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="499" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" s="19" t="s">
         <v>1136</v>
       </c>
@@ -58032,7 +58036,7 @@
       </c>
       <c r="AO499" s="81"/>
     </row>
-    <row r="500" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="500" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" s="19" t="s">
         <v>1141</v>
       </c>
@@ -58145,7 +58149,7 @@
       </c>
       <c r="AO500" s="81"/>
     </row>
-    <row r="501" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="501" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" s="19" t="s">
         <v>1147</v>
       </c>
@@ -58260,7 +58264,7 @@
       </c>
       <c r="AO501" s="81"/>
     </row>
-    <row r="502" spans="1:41" s="26" customFormat="1" ht="20.45" hidden="1">
+    <row r="502" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" s="19" t="s">
         <v>1150</v>
       </c>
@@ -58375,7 +58379,7 @@
       </c>
       <c r="AO502" s="81"/>
     </row>
-    <row r="503" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="503" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" s="19" t="s">
         <v>1154</v>
       </c>
@@ -58490,7 +58494,7 @@
       </c>
       <c r="AO503" s="81"/>
     </row>
-    <row r="504" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="504" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" s="19" t="s">
         <v>1158</v>
       </c>
@@ -58592,7 +58596,7 @@
       <c r="AN504" s="83"/>
       <c r="AO504" s="81"/>
     </row>
-    <row r="505" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="505" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" s="19" t="s">
         <v>1162</v>
       </c>
@@ -58707,7 +58711,7 @@
       </c>
       <c r="AO505" s="81"/>
     </row>
-    <row r="506" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="506" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" s="19" t="s">
         <v>1166</v>
       </c>
@@ -58822,7 +58826,7 @@
       </c>
       <c r="AO506" s="81"/>
     </row>
-    <row r="507" spans="1:41" s="26" customFormat="1" ht="30.6" hidden="1">
+    <row r="507" spans="1:41" s="26" customFormat="1" ht="30.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" s="19" t="s">
         <v>1169</v>
       </c>
@@ -58937,7 +58941,7 @@
       </c>
       <c r="AO507" s="81"/>
     </row>
-    <row r="508" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="508" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" s="19" t="s">
         <v>1172</v>
       </c>
@@ -59042,7 +59046,7 @@
       <c r="AN508" s="83"/>
       <c r="AO508" s="81"/>
     </row>
-    <row r="509" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="509" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" s="19" t="s">
         <v>1174</v>
       </c>
@@ -59157,7 +59161,7 @@
       </c>
       <c r="AO509" s="81"/>
     </row>
-    <row r="510" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="510" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" s="19" t="s">
         <v>1177</v>
       </c>
@@ -59263,7 +59267,7 @@
       </c>
       <c r="AO510" s="81"/>
     </row>
-    <row r="511" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="511" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" s="19" t="s">
         <v>1179</v>
       </c>
@@ -59366,7 +59370,7 @@
       <c r="AN511" s="83"/>
       <c r="AO511" s="81"/>
     </row>
-    <row r="512" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="512" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" s="19" t="s">
         <v>1181</v>
       </c>
@@ -59481,7 +59485,7 @@
       </c>
       <c r="AO512" s="81"/>
     </row>
-    <row r="513" spans="1:41" s="26" customFormat="1" ht="20.45" hidden="1">
+    <row r="513" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" s="19" t="s">
         <v>1184</v>
       </c>
@@ -59596,7 +59600,7 @@
       </c>
       <c r="AO513" s="81"/>
     </row>
-    <row r="514" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="514" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" s="19" t="s">
         <v>1187</v>
       </c>
@@ -59711,7 +59715,7 @@
       </c>
       <c r="AO514" s="81"/>
     </row>
-    <row r="515" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="515" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" s="19" t="s">
         <v>1190</v>
       </c>
@@ -59826,7 +59830,7 @@
       </c>
       <c r="AO515" s="81"/>
     </row>
-    <row r="516" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="516" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="19" t="s">
         <v>1193</v>
       </c>
@@ -59939,7 +59943,7 @@
       </c>
       <c r="AO516" s="81"/>
     </row>
-    <row r="517" spans="1:41" s="26" customFormat="1" ht="20.45" hidden="1">
+    <row r="517" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" s="19" t="s">
         <v>388</v>
       </c>
@@ -60054,7 +60058,7 @@
       </c>
       <c r="AO517" s="81"/>
     </row>
-    <row r="518" spans="1:41" s="26" customFormat="1">
+    <row r="518" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A518" s="19" t="s">
         <v>1198</v>
       </c>
@@ -60138,7 +60142,7 @@
       </c>
       <c r="AO518" s="81"/>
     </row>
-    <row r="519" spans="1:41" s="26" customFormat="1">
+    <row r="519" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A519" s="19" t="s">
         <v>1199</v>
       </c>
@@ -60208,7 +60212,7 @@
       </c>
       <c r="AO519" s="81"/>
     </row>
-    <row r="520" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="520" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" s="19" t="s">
         <v>1200</v>
       </c>
@@ -60323,7 +60327,7 @@
       </c>
       <c r="AO520" s="81"/>
     </row>
-    <row r="521" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="521" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" s="19" t="s">
         <v>1205</v>
       </c>
@@ -60434,7 +60438,7 @@
       </c>
       <c r="AO521" s="81"/>
     </row>
-    <row r="522" spans="1:41" s="26" customFormat="1" ht="20.45" hidden="1">
+    <row r="522" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" s="19" t="s">
         <v>1207</v>
       </c>
@@ -60549,7 +60553,7 @@
       </c>
       <c r="AO522" s="81"/>
     </row>
-    <row r="523" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="523" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" s="19" t="s">
         <v>1210</v>
       </c>
@@ -60654,7 +60658,7 @@
       <c r="AN523" s="83"/>
       <c r="AO523" s="81"/>
     </row>
-    <row r="524" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="524" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" s="19" t="s">
         <v>1214</v>
       </c>
@@ -60767,7 +60771,7 @@
       </c>
       <c r="AO524" s="81"/>
     </row>
-    <row r="525" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="525" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" s="19" t="s">
         <v>1218</v>
       </c>
@@ -60868,7 +60872,7 @@
       <c r="AN525" s="83"/>
       <c r="AO525" s="81"/>
     </row>
-    <row r="526" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="526" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" s="19" t="s">
         <v>1221</v>
       </c>
@@ -60983,7 +60987,7 @@
       </c>
       <c r="AO526" s="81"/>
     </row>
-    <row r="527" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="527" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" s="19" t="s">
         <v>1224</v>
       </c>
@@ -61098,7 +61102,7 @@
       </c>
       <c r="AO527" s="81"/>
     </row>
-    <row r="528" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="528" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" s="19" t="s">
         <v>1228</v>
       </c>
@@ -61213,7 +61217,7 @@
       </c>
       <c r="AO528" s="81"/>
     </row>
-    <row r="529" spans="1:41" s="26" customFormat="1" ht="20.45" hidden="1">
+    <row r="529" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="19" t="s">
         <v>1231</v>
       </c>
@@ -61329,7 +61333,7 @@
       </c>
       <c r="AO529" s="81"/>
     </row>
-    <row r="530" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="530" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" s="19" t="s">
         <v>723</v>
       </c>
@@ -61429,7 +61433,7 @@
       <c r="AN530" s="83"/>
       <c r="AO530" s="81"/>
     </row>
-    <row r="531" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="531" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" s="19" t="s">
         <v>1234</v>
       </c>
@@ -61542,7 +61546,7 @@
       </c>
       <c r="AO531" s="81"/>
     </row>
-    <row r="532" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="532" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" s="19" t="s">
         <v>1237</v>
       </c>
@@ -61646,7 +61650,7 @@
       <c r="AN532" s="83"/>
       <c r="AO532" s="81"/>
     </row>
-    <row r="533" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="533" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" s="19" t="s">
         <v>1239</v>
       </c>
@@ -61750,7 +61754,7 @@
       <c r="AN533" s="83"/>
       <c r="AO533" s="81"/>
     </row>
-    <row r="534" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="534" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" s="19" t="s">
         <v>1241</v>
       </c>
@@ -61865,7 +61869,7 @@
       </c>
       <c r="AO534" s="81"/>
     </row>
-    <row r="535" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="535" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" s="19" t="s">
         <v>1245</v>
       </c>
@@ -61976,7 +61980,7 @@
       <c r="AN535" s="83"/>
       <c r="AO535" s="81"/>
     </row>
-    <row r="536" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="536" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" s="19" t="s">
         <v>1247</v>
       </c>
@@ -62080,7 +62084,7 @@
       <c r="AN536" s="83"/>
       <c r="AO536" s="81"/>
     </row>
-    <row r="537" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="537" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" s="19" t="s">
         <v>734</v>
       </c>
@@ -62193,7 +62197,7 @@
       </c>
       <c r="AO537" s="81"/>
     </row>
-    <row r="538" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="538" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" s="19" t="s">
         <v>1251</v>
       </c>
@@ -62305,7 +62309,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="539" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="539" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" s="19" t="s">
         <v>1253</v>
       </c>
@@ -62419,7 +62423,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="540" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="540" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" s="19" t="s">
         <v>1256</v>
       </c>
@@ -62522,7 +62526,7 @@
       <c r="AM540" s="1"/>
       <c r="AN540" s="83"/>
     </row>
-    <row r="541" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="541" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" s="19" t="s">
         <v>719</v>
       </c>
@@ -62621,7 +62625,7 @@
       <c r="AM541" s="1"/>
       <c r="AN541" s="83"/>
     </row>
-    <row r="542" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="542" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" s="19" t="s">
         <v>1259</v>
       </c>
@@ -62735,7 +62739,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="543" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="543" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" s="19" t="s">
         <v>1261</v>
       </c>
@@ -62838,7 +62842,7 @@
       <c r="AM543" s="1"/>
       <c r="AN543" s="83"/>
     </row>
-    <row r="544" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="544" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" s="19" t="s">
         <v>1263</v>
       </c>
@@ -62952,7 +62956,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="545" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="545" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="19" t="s">
         <v>1266</v>
       </c>
@@ -63066,7 +63070,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="546" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="546" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="19" t="s">
         <v>1268</v>
       </c>
@@ -63180,7 +63184,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="547" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="547" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" s="19" t="s">
         <v>1270</v>
       </c>
@@ -63283,7 +63287,7 @@
       <c r="AM547" s="1"/>
       <c r="AN547" s="83"/>
     </row>
-    <row r="548" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="548" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="19" t="s">
         <v>1271</v>
       </c>
@@ -63397,7 +63401,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="549" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="549" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="19" t="s">
         <v>1274</v>
       </c>
@@ -63500,7 +63504,7 @@
       <c r="AM549" s="1"/>
       <c r="AN549" s="83"/>
     </row>
-    <row r="550" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="550" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="19" t="s">
         <v>1275</v>
       </c>
@@ -63603,7 +63607,7 @@
       <c r="AM550" s="1"/>
       <c r="AN550" s="83"/>
     </row>
-    <row r="551" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="551" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" s="19" t="s">
         <v>1277</v>
       </c>
@@ -63706,7 +63710,7 @@
       <c r="AM551" s="1"/>
       <c r="AN551" s="83"/>
     </row>
-    <row r="552" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="552" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" s="19" t="s">
         <v>738</v>
       </c>
@@ -63807,7 +63811,7 @@
       <c r="AM552" s="1"/>
       <c r="AN552" s="83"/>
     </row>
-    <row r="553" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="553" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="19" t="s">
         <v>1278</v>
       </c>
@@ -63921,7 +63925,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="554" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="554" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" s="19" t="s">
         <v>1282</v>
       </c>
@@ -64024,7 +64028,7 @@
       <c r="AM554" s="1"/>
       <c r="AN554" s="83"/>
     </row>
-    <row r="555" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="555" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" s="19" t="s">
         <v>1283</v>
       </c>
@@ -64125,7 +64129,7 @@
       <c r="AM555" s="1"/>
       <c r="AN555" s="83"/>
     </row>
-    <row r="556" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="556" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" s="19" t="s">
         <v>1284</v>
       </c>
@@ -64239,7 +64243,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="557" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="557" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="19" t="s">
         <v>1287</v>
       </c>
@@ -64342,7 +64346,7 @@
       <c r="AM557" s="1"/>
       <c r="AN557" s="83"/>
     </row>
-    <row r="558" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="558" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="19" t="s">
         <v>1289</v>
       </c>
@@ -64443,7 +64447,7 @@
       <c r="AM558" s="1"/>
       <c r="AN558" s="83"/>
     </row>
-    <row r="559" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="559" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" s="19" t="s">
         <v>1291</v>
       </c>
@@ -64544,7 +64548,7 @@
       <c r="AM559" s="1"/>
       <c r="AN559" s="83"/>
     </row>
-    <row r="560" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="560" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" s="19" t="s">
         <v>1293</v>
       </c>
@@ -64656,7 +64660,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="561" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="561" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" s="19" t="s">
         <v>586</v>
       </c>
@@ -64759,7 +64763,7 @@
       <c r="AM561" s="1"/>
       <c r="AN561" s="83"/>
     </row>
-    <row r="562" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="562" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" s="19" t="s">
         <v>1296</v>
       </c>
@@ -64873,7 +64877,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="563" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="563" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" s="19" t="s">
         <v>1298</v>
       </c>
@@ -64987,7 +64991,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="564" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="564" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="19" t="s">
         <v>1301</v>
       </c>
@@ -65099,7 +65103,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="565" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="565" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="19" t="s">
         <v>1304</v>
       </c>
@@ -65200,7 +65204,7 @@
       <c r="AM565" s="1"/>
       <c r="AN565" s="83"/>
     </row>
-    <row r="566" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="566" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="19" t="s">
         <v>1306</v>
       </c>
@@ -65303,7 +65307,7 @@
       <c r="AM566" s="1"/>
       <c r="AN566" s="83"/>
     </row>
-    <row r="567" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="567" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" s="32" t="s">
         <v>1308</v>
       </c>
@@ -65404,7 +65408,7 @@
       <c r="AM567" s="1"/>
       <c r="AN567" s="83"/>
     </row>
-    <row r="568" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="568" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" s="19" t="s">
         <v>1310</v>
       </c>
@@ -65507,7 +65511,7 @@
       <c r="AM568" s="1"/>
       <c r="AN568" s="83"/>
     </row>
-    <row r="569" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="569" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" s="19" t="s">
         <v>1312</v>
       </c>
@@ -65621,7 +65625,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="570" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="570" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" s="19" t="s">
         <v>1315</v>
       </c>
@@ -65722,7 +65726,7 @@
       <c r="AM570" s="1"/>
       <c r="AN570" s="83"/>
     </row>
-    <row r="571" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="571" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="19" t="s">
         <v>1317</v>
       </c>
@@ -65823,7 +65827,7 @@
       <c r="AM571" s="1"/>
       <c r="AN571" s="83"/>
     </row>
-    <row r="572" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="572" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" s="19" t="s">
         <v>1318</v>
       </c>
@@ -65924,7 +65928,7 @@
       <c r="AM572" s="1"/>
       <c r="AN572" s="83"/>
     </row>
-    <row r="573" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="573" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" s="19" t="s">
         <v>1320</v>
       </c>
@@ -66027,7 +66031,7 @@
       <c r="AM573" s="1"/>
       <c r="AN573" s="83"/>
     </row>
-    <row r="574" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="574" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="19" t="s">
         <v>1322</v>
       </c>
@@ -66130,7 +66134,7 @@
       <c r="AM574" s="1"/>
       <c r="AN574" s="83"/>
     </row>
-    <row r="575" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="575" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" s="19" t="s">
         <v>1325</v>
       </c>
@@ -66233,7 +66237,7 @@
       <c r="AM575" s="1"/>
       <c r="AN575" s="83"/>
     </row>
-    <row r="576" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="576" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" s="19" t="s">
         <v>1327</v>
       </c>
@@ -66336,7 +66340,7 @@
       <c r="AM576" s="1"/>
       <c r="AN576" s="83"/>
     </row>
-    <row r="577" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="577" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" s="19" t="s">
         <v>1329</v>
       </c>
@@ -66439,7 +66443,7 @@
       <c r="AM577" s="1"/>
       <c r="AN577" s="83"/>
     </row>
-    <row r="578" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="578" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" s="19" t="s">
         <v>1331</v>
       </c>
@@ -66540,7 +66544,7 @@
       <c r="AM578" s="1"/>
       <c r="AN578" s="83"/>
     </row>
-    <row r="579" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="579" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579" s="19" t="s">
         <v>1332</v>
       </c>
@@ -66643,7 +66647,7 @@
       <c r="AM579" s="1"/>
       <c r="AN579" s="83"/>
     </row>
-    <row r="580" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="580" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" s="19" t="s">
         <v>1334</v>
       </c>
@@ -66746,7 +66750,7 @@
       <c r="AM580" s="1"/>
       <c r="AN580" s="83"/>
     </row>
-    <row r="581" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="581" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" s="19" t="s">
         <v>1335</v>
       </c>
@@ -66849,7 +66853,7 @@
       <c r="AM581" s="1"/>
       <c r="AN581" s="83"/>
     </row>
-    <row r="582" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="582" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582" s="19" t="s">
         <v>1337</v>
       </c>
@@ -66952,7 +66956,7 @@
       <c r="AM582" s="1"/>
       <c r="AN582" s="83"/>
     </row>
-    <row r="583" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="583" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="19" t="s">
         <v>1339</v>
       </c>
@@ -67015,7 +67019,7 @@
       <c r="AM583" s="1"/>
       <c r="AN583" s="83"/>
     </row>
-    <row r="584" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="584" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="19" t="s">
         <v>1340</v>
       </c>
@@ -67118,7 +67122,7 @@
       <c r="AM584" s="1"/>
       <c r="AN584" s="83"/>
     </row>
-    <row r="585" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="585" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" s="19" t="s">
         <v>1342</v>
       </c>
@@ -67221,7 +67225,7 @@
       <c r="AM585" s="1"/>
       <c r="AN585" s="83"/>
     </row>
-    <row r="586" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="586" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" s="19" t="s">
         <v>1344</v>
       </c>
@@ -67324,7 +67328,7 @@
       <c r="AM586" s="1"/>
       <c r="AN586" s="83"/>
     </row>
-    <row r="587" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="587" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" s="19" t="s">
         <v>1346</v>
       </c>
@@ -67423,7 +67427,7 @@
       <c r="AM587" s="1"/>
       <c r="AN587" s="83"/>
     </row>
-    <row r="588" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="588" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" s="19" t="s">
         <v>299</v>
       </c>
@@ -67522,7 +67526,7 @@
       <c r="AM588" s="1"/>
       <c r="AN588" s="83"/>
     </row>
-    <row r="589" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="589" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" s="19" t="s">
         <v>1349</v>
       </c>
@@ -67625,7 +67629,7 @@
       <c r="AM589" s="1"/>
       <c r="AN589" s="83"/>
     </row>
-    <row r="590" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="590" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" s="19" t="s">
         <v>1351</v>
       </c>
@@ -67728,7 +67732,7 @@
       <c r="AM590" s="1"/>
       <c r="AN590" s="83"/>
     </row>
-    <row r="591" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="591" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591" s="22" t="s">
         <v>1353</v>
       </c>
@@ -67803,7 +67807,7 @@
       <c r="AM591" s="1"/>
       <c r="AN591" s="83"/>
     </row>
-    <row r="592" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="592" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592" s="22" t="s">
         <v>1356</v>
       </c>
@@ -67876,7 +67880,7 @@
       <c r="AM592" s="1"/>
       <c r="AN592" s="83"/>
     </row>
-    <row r="593" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="593" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" s="22" t="s">
         <v>1359</v>
       </c>
@@ -67949,7 +67953,7 @@
       <c r="AM593" s="1"/>
       <c r="AN593" s="83"/>
     </row>
-    <row r="594" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="594" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" s="22" t="s">
         <v>1360</v>
       </c>
@@ -68022,7 +68026,7 @@
       <c r="AM594" s="1"/>
       <c r="AN594" s="83"/>
     </row>
-    <row r="595" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="595" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="22" t="s">
         <v>647</v>
       </c>
@@ -68095,7 +68099,7 @@
       <c r="AM595" s="1"/>
       <c r="AN595" s="83"/>
     </row>
-    <row r="596" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="596" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="22" t="s">
         <v>1363</v>
       </c>
@@ -68168,7 +68172,7 @@
       <c r="AM596" s="1"/>
       <c r="AN596" s="83"/>
     </row>
-    <row r="597" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="597" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" s="22" t="s">
         <v>1364</v>
       </c>
@@ -68241,7 +68245,7 @@
       <c r="AM597" s="1"/>
       <c r="AN597" s="83"/>
     </row>
-    <row r="598" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="598" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" s="22" t="s">
         <v>1365</v>
       </c>
@@ -68314,7 +68318,7 @@
       <c r="AM598" s="1"/>
       <c r="AN598" s="83"/>
     </row>
-    <row r="599" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="599" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="22" t="s">
         <v>1368</v>
       </c>
@@ -68387,7 +68391,7 @@
       <c r="AM599" s="1"/>
       <c r="AN599" s="83"/>
     </row>
-    <row r="600" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="600" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" s="22" t="s">
         <v>1369</v>
       </c>
@@ -68460,7 +68464,7 @@
       <c r="AM600" s="1"/>
       <c r="AN600" s="83"/>
     </row>
-    <row r="601" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="601" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" s="22" t="s">
         <v>1371</v>
       </c>
@@ -68533,7 +68537,7 @@
       <c r="AM601" s="1"/>
       <c r="AN601" s="83"/>
     </row>
-    <row r="602" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="602" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" s="22" t="s">
         <v>868</v>
       </c>
@@ -68606,7 +68610,7 @@
       <c r="AM602" s="1"/>
       <c r="AN602" s="83"/>
     </row>
-    <row r="603" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="603" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603" s="22" t="s">
         <v>1373</v>
       </c>
@@ -68679,7 +68683,7 @@
       <c r="AM603" s="1"/>
       <c r="AN603" s="83"/>
     </row>
-    <row r="604" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="604" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604" s="22" t="s">
         <v>1374</v>
       </c>
@@ -68752,7 +68756,7 @@
       <c r="AM604" s="1"/>
       <c r="AN604" s="83"/>
     </row>
-    <row r="605" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="605" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605" s="22" t="s">
         <v>655</v>
       </c>
@@ -68825,7 +68829,7 @@
       <c r="AM605" s="1"/>
       <c r="AN605" s="83"/>
     </row>
-    <row r="606" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="606" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606" s="22" t="s">
         <v>275</v>
       </c>
@@ -68900,7 +68904,7 @@
       <c r="AM606" s="1"/>
       <c r="AN606" s="83"/>
     </row>
-    <row r="607" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="607" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607" s="22" t="s">
         <v>1377</v>
       </c>
@@ -68973,7 +68977,7 @@
       <c r="AM607" s="1"/>
       <c r="AN607" s="83"/>
     </row>
-    <row r="608" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="608" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608" s="22" t="s">
         <v>1378</v>
       </c>
@@ -69046,7 +69050,7 @@
       <c r="AM608" s="1"/>
       <c r="AN608" s="83"/>
     </row>
-    <row r="609" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="609" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609" s="22" t="s">
         <v>378</v>
       </c>
@@ -69119,7 +69123,7 @@
       <c r="AM609" s="1"/>
       <c r="AN609" s="83"/>
     </row>
-    <row r="610" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="610" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610" s="22" t="s">
         <v>370</v>
       </c>
@@ -69192,7 +69196,7 @@
       <c r="AM610" s="1"/>
       <c r="AN610" s="83"/>
     </row>
-    <row r="611" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="611" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611" s="22" t="s">
         <v>1379</v>
       </c>
@@ -69265,7 +69269,7 @@
       <c r="AM611" s="1"/>
       <c r="AN611" s="83"/>
     </row>
-    <row r="612" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="612" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612" s="22" t="s">
         <v>1380</v>
       </c>
@@ -69338,7 +69342,7 @@
       <c r="AM612" s="1"/>
       <c r="AN612" s="83"/>
     </row>
-    <row r="613" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="613" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613" s="22" t="s">
         <v>1381</v>
       </c>
@@ -69411,7 +69415,7 @@
       <c r="AM613" s="1"/>
       <c r="AN613" s="83"/>
     </row>
-    <row r="614" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="614" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614" s="22" t="s">
         <v>1383</v>
       </c>
@@ -69484,7 +69488,7 @@
       <c r="AM614" s="1"/>
       <c r="AN614" s="83"/>
     </row>
-    <row r="615" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="615" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615" s="22" t="s">
         <v>672</v>
       </c>
@@ -69557,7 +69561,7 @@
       <c r="AM615" s="1"/>
       <c r="AN615" s="83"/>
     </row>
-    <row r="616" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="616" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616" s="22" t="s">
         <v>1384</v>
       </c>
@@ -69630,7 +69634,7 @@
       <c r="AM616" s="1"/>
       <c r="AN616" s="83"/>
     </row>
-    <row r="617" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="617" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617" s="22" t="s">
         <v>1386</v>
       </c>
@@ -69703,7 +69707,7 @@
       <c r="AM617" s="1"/>
       <c r="AN617" s="83"/>
     </row>
-    <row r="618" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="618" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618" s="22" t="s">
         <v>880</v>
       </c>
@@ -69776,7 +69780,7 @@
       <c r="AM618" s="1"/>
       <c r="AN618" s="83"/>
     </row>
-    <row r="619" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="619" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619" s="22" t="s">
         <v>907</v>
       </c>
@@ -69849,7 +69853,7 @@
       <c r="AM619" s="1"/>
       <c r="AN619" s="83"/>
     </row>
-    <row r="620" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="620" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620" s="22" t="s">
         <v>877</v>
       </c>
@@ -69922,7 +69926,7 @@
       <c r="AM620" s="1"/>
       <c r="AN620" s="83"/>
     </row>
-    <row r="621" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="621" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621" s="22" t="s">
         <v>1389</v>
       </c>
@@ -69995,7 +69999,7 @@
       <c r="AM621" s="1"/>
       <c r="AN621" s="83"/>
     </row>
-    <row r="622" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="622" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622" s="22" t="s">
         <v>1390</v>
       </c>
@@ -70068,7 +70072,7 @@
       <c r="AM622" s="1"/>
       <c r="AN622" s="83"/>
     </row>
-    <row r="623" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="623" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" s="22" t="s">
         <v>859</v>
       </c>
@@ -70141,7 +70145,7 @@
       <c r="AM623" s="1"/>
       <c r="AN623" s="83"/>
     </row>
-    <row r="624" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="624" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" s="22" t="s">
         <v>1392</v>
       </c>
@@ -70214,7 +70218,7 @@
       <c r="AM624" s="1"/>
       <c r="AN624" s="83"/>
     </row>
-    <row r="625" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="625" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" s="22" t="s">
         <v>1393</v>
       </c>
@@ -70287,7 +70291,7 @@
       <c r="AM625" s="1"/>
       <c r="AN625" s="83"/>
     </row>
-    <row r="626" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="626" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626" s="22" t="s">
         <v>406</v>
       </c>
@@ -70360,7 +70364,7 @@
       <c r="AM626" s="1"/>
       <c r="AN626" s="83"/>
     </row>
-    <row r="627" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="627" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A627" s="22" t="s">
         <v>1396</v>
       </c>
@@ -70433,7 +70437,7 @@
       <c r="AM627" s="1"/>
       <c r="AN627" s="83"/>
     </row>
-    <row r="628" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="628" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628" s="22" t="s">
         <v>921</v>
       </c>
@@ -70506,7 +70510,7 @@
       <c r="AM628" s="1"/>
       <c r="AN628" s="83"/>
     </row>
-    <row r="629" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="629" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629" s="22" t="s">
         <v>1398</v>
       </c>
@@ -70579,7 +70583,7 @@
       <c r="AM629" s="1"/>
       <c r="AN629" s="83"/>
     </row>
-    <row r="630" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="630" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" s="22" t="s">
         <v>892</v>
       </c>
@@ -70652,7 +70656,7 @@
       <c r="AM630" s="1"/>
       <c r="AN630" s="83"/>
     </row>
-    <row r="631" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="631" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631" s="22" t="s">
         <v>1400</v>
       </c>
@@ -70725,7 +70729,7 @@
       <c r="AM631" s="1"/>
       <c r="AN631" s="83"/>
     </row>
-    <row r="632" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="632" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632" s="22" t="s">
         <v>1401</v>
       </c>
@@ -70798,7 +70802,7 @@
       <c r="AM632" s="1"/>
       <c r="AN632" s="83"/>
     </row>
-    <row r="633" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="633" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633" s="22" t="s">
         <v>1403</v>
       </c>
@@ -70871,7 +70875,7 @@
       <c r="AM633" s="1"/>
       <c r="AN633" s="83"/>
     </row>
-    <row r="634" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="634" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634" s="22" t="s">
         <v>1404</v>
       </c>
@@ -70944,7 +70948,7 @@
       <c r="AM634" s="1"/>
       <c r="AN634" s="83"/>
     </row>
-    <row r="635" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="635" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635" s="22" t="s">
         <v>1405</v>
       </c>
@@ -71017,7 +71021,7 @@
       <c r="AM635" s="1"/>
       <c r="AN635" s="83"/>
     </row>
-    <row r="636" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="636" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636" s="22" t="s">
         <v>1406</v>
       </c>
@@ -71090,7 +71094,7 @@
       <c r="AM636" s="1"/>
       <c r="AN636" s="83"/>
     </row>
-    <row r="637" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="637" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637" s="22" t="s">
         <v>1407</v>
       </c>
@@ -71163,7 +71167,7 @@
       <c r="AM637" s="1"/>
       <c r="AN637" s="83"/>
     </row>
-    <row r="638" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="638" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638" s="22" t="s">
         <v>1409</v>
       </c>
@@ -71236,7 +71240,7 @@
       <c r="AM638" s="1"/>
       <c r="AN638" s="83"/>
     </row>
-    <row r="639" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="639" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639" s="22" t="s">
         <v>1410</v>
       </c>
@@ -71309,7 +71313,7 @@
       <c r="AM639" s="1"/>
       <c r="AN639" s="83"/>
     </row>
-    <row r="640" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="640" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" s="22" t="s">
         <v>1411</v>
       </c>
@@ -71382,7 +71386,7 @@
       <c r="AM640" s="1"/>
       <c r="AN640" s="83"/>
     </row>
-    <row r="641" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="641" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" s="22" t="s">
         <v>898</v>
       </c>
@@ -71455,7 +71459,7 @@
       <c r="AM641" s="1"/>
       <c r="AN641" s="83"/>
     </row>
-    <row r="642" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="642" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" s="22" t="s">
         <v>967</v>
       </c>
@@ -71528,7 +71532,7 @@
       <c r="AM642" s="1"/>
       <c r="AN642" s="83"/>
     </row>
-    <row r="643" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="643" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" s="22" t="s">
         <v>1412</v>
       </c>
@@ -71601,7 +71605,7 @@
       <c r="AM643" s="1"/>
       <c r="AN643" s="83"/>
     </row>
-    <row r="644" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="644" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644" s="22" t="s">
         <v>1414</v>
       </c>
@@ -71674,7 +71678,7 @@
       <c r="AM644" s="1"/>
       <c r="AN644" s="83"/>
     </row>
-    <row r="645" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="645" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645" s="22" t="s">
         <v>874</v>
       </c>
@@ -71747,7 +71751,7 @@
       <c r="AM645" s="1"/>
       <c r="AN645" s="83"/>
     </row>
-    <row r="646" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="646" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646" s="22" t="s">
         <v>1415</v>
       </c>
@@ -71820,7 +71824,7 @@
       <c r="AM646" s="1"/>
       <c r="AN646" s="83"/>
     </row>
-    <row r="647" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="647" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647" s="22" t="s">
         <v>946</v>
       </c>
@@ -71893,7 +71897,7 @@
       <c r="AM647" s="1"/>
       <c r="AN647" s="83"/>
     </row>
-    <row r="648" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="648" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648" s="22" t="s">
         <v>1416</v>
       </c>
@@ -71966,7 +71970,7 @@
       <c r="AM648" s="1"/>
       <c r="AN648" s="83"/>
     </row>
-    <row r="649" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="649" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649" s="22" t="s">
         <v>97</v>
       </c>
@@ -72041,7 +72045,7 @@
       <c r="AM649" s="1"/>
       <c r="AN649" s="83"/>
     </row>
-    <row r="650" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="650" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650" s="22" t="s">
         <v>1419</v>
       </c>
@@ -72114,7 +72118,7 @@
       <c r="AM650" s="1"/>
       <c r="AN650" s="83"/>
     </row>
-    <row r="651" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="651" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651" s="22" t="s">
         <v>1420</v>
       </c>
@@ -72185,7 +72189,7 @@
       <c r="AM651" s="1"/>
       <c r="AN651" s="83"/>
     </row>
-    <row r="652" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="652" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A652" s="22" t="s">
         <v>650</v>
       </c>
@@ -72258,7 +72262,7 @@
       <c r="AM652" s="1"/>
       <c r="AN652" s="83"/>
     </row>
-    <row r="653" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="653" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653" s="22" t="s">
         <v>1421</v>
       </c>
@@ -72331,7 +72335,7 @@
       <c r="AM653" s="1"/>
       <c r="AN653" s="83"/>
     </row>
-    <row r="654" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="654" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654" s="22" t="s">
         <v>1423</v>
       </c>
@@ -72404,7 +72408,7 @@
       <c r="AM654" s="1"/>
       <c r="AN654" s="83"/>
     </row>
-    <row r="655" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="655" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655" s="22" t="s">
         <v>1424</v>
       </c>
@@ -72477,7 +72481,7 @@
       <c r="AM655" s="1"/>
       <c r="AN655" s="83"/>
     </row>
-    <row r="656" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="656" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A656" s="22" t="s">
         <v>1426</v>
       </c>
@@ -72550,7 +72554,7 @@
       <c r="AM656" s="1"/>
       <c r="AN656" s="83"/>
     </row>
-    <row r="657" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="657" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A657" s="22" t="s">
         <v>1427</v>
       </c>
@@ -72623,7 +72627,7 @@
       <c r="AM657" s="1"/>
       <c r="AN657" s="83"/>
     </row>
-    <row r="658" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="658" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A658" s="22" t="s">
         <v>1428</v>
       </c>
@@ -72696,7 +72700,7 @@
       <c r="AM658" s="1"/>
       <c r="AN658" s="83"/>
     </row>
-    <row r="659" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="659" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A659" s="22" t="s">
         <v>1429</v>
       </c>
@@ -72769,7 +72773,7 @@
       <c r="AM659" s="1"/>
       <c r="AN659" s="83"/>
     </row>
-    <row r="660" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="660" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660" s="22" t="s">
         <v>1430</v>
       </c>
@@ -72842,7 +72846,7 @@
       <c r="AM660" s="1"/>
       <c r="AN660" s="83"/>
     </row>
-    <row r="661" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="661" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A661" s="22" t="s">
         <v>1431</v>
       </c>
@@ -72915,7 +72919,7 @@
       <c r="AM661" s="1"/>
       <c r="AN661" s="83"/>
     </row>
-    <row r="662" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="662" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662" s="22" t="s">
         <v>1432</v>
       </c>
@@ -72988,7 +72992,7 @@
       <c r="AM662" s="1"/>
       <c r="AN662" s="83"/>
     </row>
-    <row r="663" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="663" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663" s="22" t="s">
         <v>966</v>
       </c>
@@ -73061,7 +73065,7 @@
       <c r="AM663" s="1"/>
       <c r="AN663" s="83"/>
     </row>
-    <row r="664" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="664" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664" s="22" t="s">
         <v>578</v>
       </c>
@@ -73144,7 +73148,7 @@
       <c r="AM664" s="1"/>
       <c r="AN664" s="83"/>
     </row>
-    <row r="665" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="665" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665" s="22" t="s">
         <v>1435</v>
       </c>
@@ -73217,7 +73221,7 @@
       <c r="AM665" s="1"/>
       <c r="AN665" s="83"/>
     </row>
-    <row r="666" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="666" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A666" s="22" t="s">
         <v>1437</v>
       </c>
@@ -73290,7 +73294,7 @@
       <c r="AM666" s="1"/>
       <c r="AN666" s="83"/>
     </row>
-    <row r="667" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="667" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A667" s="22" t="s">
         <v>1439</v>
       </c>
@@ -73363,7 +73367,7 @@
       <c r="AM667" s="1"/>
       <c r="AN667" s="83"/>
     </row>
-    <row r="668" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="668" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A668" s="22" t="s">
         <v>1441</v>
       </c>
@@ -73436,7 +73440,7 @@
       <c r="AM668" s="1"/>
       <c r="AN668" s="83"/>
     </row>
-    <row r="669" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="669" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A669" s="22" t="s">
         <v>1442</v>
       </c>
@@ -73509,7 +73513,7 @@
       <c r="AM669" s="1"/>
       <c r="AN669" s="83"/>
     </row>
-    <row r="670" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="670" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A670" s="22" t="s">
         <v>1443</v>
       </c>
@@ -73582,7 +73586,7 @@
       <c r="AM670" s="1"/>
       <c r="AN670" s="83"/>
     </row>
-    <row r="671" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="671" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A671" s="22" t="s">
         <v>1445</v>
       </c>
@@ -73655,7 +73659,7 @@
       <c r="AM671" s="1"/>
       <c r="AN671" s="83"/>
     </row>
-    <row r="672" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="672" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A672" s="22" t="s">
         <v>1447</v>
       </c>
@@ -73728,7 +73732,7 @@
       <c r="AM672" s="1"/>
       <c r="AN672" s="83"/>
     </row>
-    <row r="673" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="673" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A673" s="22" t="s">
         <v>1448</v>
       </c>
@@ -73801,7 +73805,7 @@
       <c r="AM673" s="1"/>
       <c r="AN673" s="83"/>
     </row>
-    <row r="674" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="674" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A674" s="22" t="s">
         <v>1449</v>
       </c>
@@ -73872,7 +73876,7 @@
       <c r="AM674" s="1"/>
       <c r="AN674" s="83"/>
     </row>
-    <row r="675" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="675" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A675" s="22" t="s">
         <v>1450</v>
       </c>
@@ -73945,7 +73949,7 @@
       <c r="AM675" s="1"/>
       <c r="AN675" s="83"/>
     </row>
-    <row r="676" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="676" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A676" s="22" t="s">
         <v>1451</v>
       </c>
@@ -74018,7 +74022,7 @@
       <c r="AM676" s="1"/>
       <c r="AN676" s="83"/>
     </row>
-    <row r="677" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="677" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A677" s="22" t="s">
         <v>1452</v>
       </c>
@@ -74091,7 +74095,7 @@
       <c r="AM677" s="1"/>
       <c r="AN677" s="83"/>
     </row>
-    <row r="678" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="678" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A678" s="22" t="s">
         <v>1453</v>
       </c>
@@ -74164,7 +74168,7 @@
       <c r="AM678" s="1"/>
       <c r="AN678" s="83"/>
     </row>
-    <row r="679" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="679" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A679" s="22" t="s">
         <v>1454</v>
       </c>
@@ -74237,7 +74241,7 @@
       <c r="AM679" s="1"/>
       <c r="AN679" s="83"/>
     </row>
-    <row r="680" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="680" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A680" s="22" t="s">
         <v>1455</v>
       </c>
@@ -74310,7 +74314,7 @@
       <c r="AM680" s="1"/>
       <c r="AN680" s="83"/>
     </row>
-    <row r="681" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="681" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A681" s="22" t="s">
         <v>870</v>
       </c>
@@ -74383,7 +74387,7 @@
       <c r="AM681" s="1"/>
       <c r="AN681" s="83"/>
     </row>
-    <row r="682" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="682" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A682" s="22" t="s">
         <v>1456</v>
       </c>
@@ -74456,7 +74460,7 @@
       <c r="AM682" s="1"/>
       <c r="AN682" s="83"/>
     </row>
-    <row r="683" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="683" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A683" s="22" t="s">
         <v>1457</v>
       </c>
@@ -74529,7 +74533,7 @@
       <c r="AM683" s="1"/>
       <c r="AN683" s="83"/>
     </row>
-    <row r="684" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="684" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A684" s="22" t="s">
         <v>1458</v>
       </c>
@@ -74602,7 +74606,7 @@
       <c r="AM684" s="1"/>
       <c r="AN684" s="83"/>
     </row>
-    <row r="685" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="685" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A685" s="22" t="s">
         <v>1459</v>
       </c>
@@ -74675,7 +74679,7 @@
       <c r="AM685" s="1"/>
       <c r="AN685" s="83"/>
     </row>
-    <row r="686" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="686" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A686" s="22" t="s">
         <v>1460</v>
       </c>
@@ -74748,7 +74752,7 @@
       <c r="AM686" s="1"/>
       <c r="AN686" s="83"/>
     </row>
-    <row r="687" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="687" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A687" s="22" t="s">
         <v>1461</v>
       </c>
@@ -74821,7 +74825,7 @@
       <c r="AM687" s="1"/>
       <c r="AN687" s="83"/>
     </row>
-    <row r="688" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="688" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A688" s="22" t="s">
         <v>1462</v>
       </c>
@@ -74894,7 +74898,7 @@
       <c r="AM688" s="1"/>
       <c r="AN688" s="83"/>
     </row>
-    <row r="689" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="689" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A689" s="22" t="s">
         <v>1463</v>
       </c>
@@ -74967,7 +74971,7 @@
       <c r="AM689" s="1"/>
       <c r="AN689" s="83"/>
     </row>
-    <row r="690" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="690" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A690" s="22" t="s">
         <v>1464</v>
       </c>
@@ -75040,7 +75044,7 @@
       <c r="AM690" s="1"/>
       <c r="AN690" s="83"/>
     </row>
-    <row r="691" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="691" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A691" s="22" t="s">
         <v>1465</v>
       </c>
@@ -75113,7 +75117,7 @@
       <c r="AM691" s="1"/>
       <c r="AN691" s="83"/>
     </row>
-    <row r="692" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="692" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A692" s="22" t="s">
         <v>1466</v>
       </c>
@@ -75186,7 +75190,7 @@
       <c r="AM692" s="1"/>
       <c r="AN692" s="83"/>
     </row>
-    <row r="693" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="693" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A693" s="22" t="s">
         <v>1467</v>
       </c>
@@ -75259,7 +75263,7 @@
       <c r="AM693" s="1"/>
       <c r="AN693" s="83"/>
     </row>
-    <row r="694" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="694" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A694" s="22" t="s">
         <v>1468</v>
       </c>
@@ -75332,7 +75336,7 @@
       <c r="AM694" s="1"/>
       <c r="AN694" s="83"/>
     </row>
-    <row r="695" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="695" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A695" s="22" t="s">
         <v>1469</v>
       </c>
@@ -75405,7 +75409,7 @@
       <c r="AM695" s="1"/>
       <c r="AN695" s="83"/>
     </row>
-    <row r="696" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="696" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A696" s="22" t="s">
         <v>1470</v>
       </c>
@@ -75478,7 +75482,7 @@
       <c r="AM696" s="1"/>
       <c r="AN696" s="83"/>
     </row>
-    <row r="697" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="697" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A697" s="22" t="s">
         <v>1081</v>
       </c>
@@ -75551,7 +75555,7 @@
       <c r="AM697" s="1"/>
       <c r="AN697" s="83"/>
     </row>
-    <row r="698" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="698" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A698" s="22" t="s">
         <v>1472</v>
       </c>
@@ -75624,7 +75628,7 @@
       <c r="AM698" s="1"/>
       <c r="AN698" s="83"/>
     </row>
-    <row r="699" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="699" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A699" s="22" t="s">
         <v>1473</v>
       </c>
@@ -75697,7 +75701,7 @@
       <c r="AM699" s="1"/>
       <c r="AN699" s="83"/>
     </row>
-    <row r="700" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="700" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A700" s="22" t="s">
         <v>1474</v>
       </c>
@@ -75770,7 +75774,7 @@
       <c r="AM700" s="1"/>
       <c r="AN700" s="83"/>
     </row>
-    <row r="701" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="701" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A701" s="22" t="s">
         <v>1475</v>
       </c>
@@ -75843,7 +75847,7 @@
       <c r="AM701" s="1"/>
       <c r="AN701" s="83"/>
     </row>
-    <row r="702" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="702" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A702" s="22" t="s">
         <v>1476</v>
       </c>
@@ -75916,7 +75920,7 @@
       <c r="AM702" s="1"/>
       <c r="AN702" s="83"/>
     </row>
-    <row r="703" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="703" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A703" s="22" t="s">
         <v>1477</v>
       </c>
@@ -75989,7 +75993,7 @@
       <c r="AM703" s="1"/>
       <c r="AN703" s="83"/>
     </row>
-    <row r="704" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="704" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A704" s="22" t="s">
         <v>1109</v>
       </c>
@@ -76062,7 +76066,7 @@
       <c r="AM704" s="1"/>
       <c r="AN704" s="83"/>
     </row>
-    <row r="705" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="705" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A705" s="22" t="s">
         <v>1478</v>
       </c>
@@ -76135,7 +76139,7 @@
       <c r="AM705" s="1"/>
       <c r="AN705" s="83"/>
     </row>
-    <row r="706" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="706" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A706" s="22" t="s">
         <v>1479</v>
       </c>
@@ -76208,7 +76212,7 @@
       <c r="AM706" s="1"/>
       <c r="AN706" s="83"/>
     </row>
-    <row r="707" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="707" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A707" s="22" t="s">
         <v>1480</v>
       </c>
@@ -76281,7 +76285,7 @@
       <c r="AM707" s="1"/>
       <c r="AN707" s="83"/>
     </row>
-    <row r="708" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="708" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A708" s="22" t="s">
         <v>1481</v>
       </c>
@@ -76354,7 +76358,7 @@
       <c r="AM708" s="1"/>
       <c r="AN708" s="83"/>
     </row>
-    <row r="709" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="709" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A709" s="22" t="s">
         <v>1482</v>
       </c>
@@ -76427,7 +76431,7 @@
       <c r="AM709" s="1"/>
       <c r="AN709" s="83"/>
     </row>
-    <row r="710" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="710" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A710" s="22" t="s">
         <v>1483</v>
       </c>
@@ -76500,7 +76504,7 @@
       <c r="AM710" s="1"/>
       <c r="AN710" s="83"/>
     </row>
-    <row r="711" spans="1:40" s="26" customFormat="1">
+    <row r="711" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A711" s="39"/>
       <c r="B711" s="40"/>
       <c r="C711" s="40"/>
@@ -76562,28 +76566,28 @@
       <c r="AM711" s="46"/>
       <c r="AN711" s="83"/>
     </row>
-    <row r="716" spans="1:40">
+    <row r="716" spans="1:40" x14ac:dyDescent="0.3">
       <c r="AA716" s="73"/>
       <c r="AB716" s="73"/>
       <c r="AC716" s="73"/>
       <c r="AN716" s="94"/>
     </row>
-    <row r="717" spans="1:40">
+    <row r="717" spans="1:40" x14ac:dyDescent="0.3">
       <c r="Z717" s="73"/>
       <c r="AA717" s="73"/>
       <c r="AB717" s="73"/>
       <c r="AC717" s="73"/>
       <c r="AN717" s="94"/>
     </row>
-    <row r="718" spans="1:40">
+    <row r="718" spans="1:40" x14ac:dyDescent="0.3">
       <c r="Z718" s="73"/>
       <c r="AA718" s="73"/>
       <c r="AB718" s="73"/>
     </row>
-    <row r="719" spans="1:40">
+    <row r="719" spans="1:40" x14ac:dyDescent="0.3">
       <c r="Z719" s="73"/>
     </row>
-    <row r="720" spans="1:40">
+    <row r="720" spans="1:40" x14ac:dyDescent="0.3">
       <c r="Z720" s="73"/>
       <c r="AA720" s="73"/>
       <c r="AB720" s="73"/>
@@ -76662,18 +76666,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D813743-8135-4F32-BACA-A0CD44F9427F}">
   <dimension ref="A1:F44"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="21.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="69" t="s">
         <v>1485</v>
       </c>
@@ -76693,7 +76697,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>755</v>
       </c>
@@ -76718,7 +76722,7 @@
         <v>88880.437499999985</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>49</v>
       </c>
@@ -76743,7 +76747,7 @@
         <v>256393.97999999995</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>151</v>
       </c>
@@ -76768,7 +76772,7 @@
         <v>136436.7233333333</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>187</v>
       </c>
@@ -76793,7 +76797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="53" t="s">
         <v>1491</v>
       </c>
@@ -76818,7 +76822,7 @@
         <v>481711.14083333325</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="69" t="s">
         <v>1492</v>
       </c>
@@ -76835,7 +76839,7 @@
         <v>1496</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
         <v>764</v>
       </c>
@@ -76856,7 +76860,7 @@
         <v>163307.73333333334</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="47" t="s">
         <v>1133</v>
       </c>
@@ -76877,7 +76881,7 @@
         <v>101921.69083333333</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="47" t="s">
         <v>752</v>
       </c>
@@ -76898,7 +76902,7 @@
         <v>33682.781666666669</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="47" t="s">
         <v>92</v>
       </c>
@@ -76919,7 +76923,7 @@
         <v>110026.7025</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="47" t="s">
         <v>73</v>
       </c>
@@ -76940,7 +76944,7 @@
         <v>14192.72</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="47" t="s">
         <v>45</v>
       </c>
@@ -76961,7 +76965,7 @@
         <v>18301.009999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="47" t="s">
         <v>82</v>
       </c>
@@ -76982,7 +76986,7 @@
         <v>8786.4108333333334</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="47" t="s">
         <v>1145</v>
       </c>
@@ -77003,7 +77007,7 @@
         <v>17038.2366666667</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="47" t="s">
         <v>841</v>
       </c>
@@ -77024,7 +77028,7 @@
         <v>3342.1949999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="47" t="s">
         <v>237</v>
       </c>
@@ -77045,7 +77049,7 @@
         <v>1642.21</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="47" t="s">
         <v>1161</v>
       </c>
@@ -77066,7 +77070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="47" t="s">
         <v>872</v>
       </c>
@@ -77087,7 +77091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="47" t="s">
         <v>356</v>
       </c>
@@ -77108,7 +77112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="47" t="s">
         <v>223</v>
       </c>
@@ -77129,7 +77133,7 @@
         <v>4586.75</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="47" t="s">
         <v>1362</v>
       </c>
@@ -77150,7 +77154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="47" t="s">
         <v>220</v>
       </c>
@@ -77171,7 +77175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="47" t="s">
         <v>1220</v>
       </c>
@@ -77192,7 +77196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="47" t="s">
         <v>318</v>
       </c>
@@ -77213,7 +77217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="47" t="s">
         <v>349</v>
       </c>
@@ -77234,7 +77238,7 @@
         <v>1311.99</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="47" t="s">
         <v>253</v>
       </c>
@@ -77255,7 +77259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="47" t="s">
         <v>303</v>
       </c>
@@ -77276,7 +77280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="47" t="s">
         <v>879</v>
       </c>
@@ -77297,7 +77301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="47" t="s">
         <v>1358</v>
       </c>
@@ -77318,7 +77322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="47" t="s">
         <v>897</v>
       </c>
@@ -77339,7 +77343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="47" t="s">
         <v>1367</v>
       </c>
@@ -77360,7 +77364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="47" t="s">
         <v>925</v>
       </c>
@@ -77381,7 +77385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="47" t="s">
         <v>149</v>
       </c>
@@ -77402,7 +77406,7 @@
         <v>238.71</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="47" t="s">
         <v>939</v>
       </c>
@@ -77423,7 +77427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="47" t="s">
         <v>1395</v>
       </c>
@@ -77444,7 +77448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="47" t="s">
         <v>1417</v>
       </c>
@@ -77465,7 +77469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="47"/>
       <c r="B40">
         <f>COUNTIF(Controle!L:L,Formulas!A41)</f>
@@ -77484,7 +77488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="47">
         <v>0</v>
       </c>
@@ -77505,7 +77509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="59" t="s">
         <v>1491</v>
       </c>
@@ -77526,12 +77530,12 @@
         <v>478379.14083333343</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="47"/>
       <c r="C43" s="57"/>
       <c r="D43" s="48"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="47"/>
     </row>
   </sheetData>
@@ -77549,12 +77553,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f5ab1930-d403-4c69-b2cd-8cc48f527d10" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c06ce65c-ed18-47f4-a957-afd315448c9c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -77753,24 +77759,54 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f5ab1930-d403-4c69-b2cd-8cc48f527d10" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c06ce65c-ed18-47f4-a957-afd315448c9c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AE26D3A-03CC-4B3D-9F98-6F77A1AEA74E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE495743-F761-4961-A762-7A3D120C6961}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="c06ce65c-ed18-47f4-a957-afd315448c9c"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f5ab1930-d403-4c69-b2cd-8cc48f527d10"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59443FB2-AD94-4FFF-8817-F253987A64A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59443FB2-AD94-4FFF-8817-F253987A64A5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c06ce65c-ed18-47f4-a957-afd315448c9c"/>
+    <ds:schemaRef ds:uri="f5ab1930-d403-4c69-b2cd-8cc48f527d10"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE495743-F761-4961-A762-7A3D120C6961}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AE26D3A-03CC-4B3D-9F98-6F77A1AEA74E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/dados_atuais.xlsx
+++ b/data/dados_atuais.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
   <workbookPr codeName="EsteLivro"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delgadiadema.sharepoint.com/sites/GestoEstratgica/Documentos Compartilhados/Controle Master/BSW/Novo controle (Em processo)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2079" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{757586D1-4CE9-47A5-905B-B68F9CB661D8}"/>
+  <xr:revisionPtr revIDLastSave="2080" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{988EE322-C98C-46BB-BB0D-97A8CB95C0B3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E398004-7492-4AA0-94C2-EA9B761AAA49}"/>
   </bookViews>
@@ -213,17 +213,17 @@
     </comment>
     <comment ref="A555" authorId="3" shapeId="0" xr:uid="{33C328EB-7B56-47E9-A787-F392CA006902}">
       <text>
-        <t>[Comentário encadeado]
-Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
-Comentário:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Utilizando material 1,60x417</t>
       </text>
     </comment>
     <comment ref="A564" authorId="4" shapeId="0" xr:uid="{C01DA7E7-015C-4D77-8E50-06C386F35AF3}">
       <text>
-        <t>[Comentário encadeado]
-Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
-Comentário:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Temos na Fitametal 
 BOZ0070TJ1350 - 10249kg</t>
       </text>
@@ -254,17 +254,17 @@
     </comment>
     <comment ref="A574" authorId="6" shapeId="0" xr:uid="{67F1D739-35C9-474A-BA1D-BDA6C83EF4A4}">
       <text>
-        <t>[Comentário encadeado]
-Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
-Comentário:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     CORTAR SLEETER DE MATERIAL SEMELHANTE DEVIDO AO BAIXO VOLUME TEMOS O MESMO MATERIAL COM OUTRAS LARGURAS</t>
       </text>
     </comment>
     <comment ref="A575" authorId="7" shapeId="0" xr:uid="{9641E501-4748-445C-B1A5-D0E296582A82}">
       <text>
-        <t>[Comentário encadeado]
-Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
-Comentário:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Usar material BOZ0060HU1000 como material alternativo</t>
       </text>
     </comment>
@@ -5033,7 +5033,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
     <numFmt numFmtId="166" formatCode="mmmm\,\ yyyy;@"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -13063,10 +13063,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
-</file>
-
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Eric da Silva Maia" id="{D9E3AE94-B136-43DC-991E-9F5A8D1687A6}" userId="S::eric.maia@delga.com.br::43e774bf-1d7b-4030-aa96-fdc0a837fc3b" providerId="AD"/>
@@ -13409,51 +13405,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA437EE-405D-4A43-9EB9-23F1BEB36011}">
-  <sheetPr codeName="Folha1"/>
+  <sheetPr codeName="Folha1" filterMode="1"/>
   <dimension ref="A1:AO720"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" customWidth="1"/>
-    <col min="7" max="7" width="28.5546875" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" customWidth="1"/>
-    <col min="9" max="9" width="10.109375" customWidth="1"/>
-    <col min="10" max="10" width="9.5546875" customWidth="1"/>
-    <col min="11" max="11" width="21.44140625" customWidth="1"/>
-    <col min="12" max="12" width="20.44140625" customWidth="1"/>
-    <col min="13" max="13" width="23.5546875" customWidth="1"/>
-    <col min="14" max="14" width="32.44140625" customWidth="1"/>
-    <col min="15" max="15" width="8.5546875" customWidth="1"/>
-    <col min="16" max="16" width="10.44140625" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="12.44140625" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5546875" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="7" max="7" width="28.5703125" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" customWidth="1"/>
+    <col min="9" max="9" width="10.140625" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" customWidth="1"/>
+    <col min="11" max="11" width="21.42578125" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" customWidth="1"/>
+    <col min="13" max="13" width="23.5703125" customWidth="1"/>
+    <col min="14" max="14" width="32.42578125" customWidth="1"/>
+    <col min="15" max="15" width="8.5703125" customWidth="1"/>
+    <col min="16" max="16" width="10.42578125" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="12.42578125" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="11.5703125" customWidth="1"/>
     <col min="19" max="19" width="15" customWidth="1"/>
-    <col min="20" max="20" width="15.5546875" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="16.44140625" hidden="1" customWidth="1"/>
-    <col min="22" max="24" width="15.44140625" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="15.44140625" customWidth="1"/>
-    <col min="26" max="26" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.5703125" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="16.42578125" hidden="1" customWidth="1"/>
+    <col min="22" max="24" width="15.42578125" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="15.42578125" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="13" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.88671875" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="24.109375" customWidth="1"/>
-    <col min="37" max="37" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.88671875" hidden="1" customWidth="1"/>
-    <col min="39" max="39" width="91.109375" customWidth="1"/>
-    <col min="40" max="40" width="28.33203125" style="50" customWidth="1"/>
+    <col min="34" max="34" width="12.85546875" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="24.140625" customWidth="1"/>
+    <col min="37" max="37" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.85546875" hidden="1" customWidth="1"/>
+    <col min="39" max="39" width="91.140625" customWidth="1"/>
+    <col min="40" max="40" width="28.28515625" style="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="151.35" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:40" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:40" ht="151.35" customHeight="1"/>
+    <row r="2" spans="1:40" ht="30.6">
       <c r="A2" s="39" t="s">
         <v>0</v>
       </c>
@@ -13575,7 +13571,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:40" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:40" hidden="1">
       <c r="A3" s="22" t="s">
         <v>40</v>
       </c>
@@ -13690,7 +13686,7 @@
       </c>
       <c r="AN3" s="83"/>
     </row>
-    <row r="4" spans="1:40" s="26" customFormat="1" ht="132.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:40" s="26" customFormat="1" ht="132.6" hidden="1">
       <c r="A4" s="22" t="s">
         <v>53</v>
       </c>
@@ -13807,7 +13803,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="5" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A5" s="22" t="s">
         <v>63</v>
       </c>
@@ -13924,7 +13920,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="6" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A6" s="22" t="s">
         <v>70</v>
       </c>
@@ -14033,7 +14029,7 @@
       </c>
       <c r="AN6" s="83"/>
     </row>
-    <row r="7" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A7" s="22" t="s">
         <v>78</v>
       </c>
@@ -14148,7 +14144,7 @@
       </c>
       <c r="AN7" s="83"/>
     </row>
-    <row r="8" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A8" s="22" t="s">
         <v>85</v>
       </c>
@@ -14245,7 +14241,7 @@
       <c r="AM8" s="1"/>
       <c r="AN8" s="83"/>
     </row>
-    <row r="9" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
       <c r="A9" s="22" t="s">
         <v>90</v>
       </c>
@@ -14362,7 +14358,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="10" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A10" s="3" t="s">
         <v>97</v>
       </c>
@@ -14479,7 +14475,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="11" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A11" s="22" t="s">
         <v>103</v>
       </c>
@@ -14592,7 +14588,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="12" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A12" s="22" t="s">
         <v>108</v>
       </c>
@@ -14689,7 +14685,7 @@
       <c r="AM12" s="1"/>
       <c r="AN12" s="83"/>
     </row>
-    <row r="13" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
       <c r="A13" s="22" t="s">
         <v>111</v>
       </c>
@@ -14788,7 +14784,7 @@
       <c r="AM13" s="1"/>
       <c r="AN13" s="83"/>
     </row>
-    <row r="14" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
       <c r="A14" s="22" t="s">
         <v>115</v>
       </c>
@@ -14893,7 +14889,7 @@
       <c r="AM14" s="1"/>
       <c r="AN14" s="83"/>
     </row>
-    <row r="15" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A15" s="22" t="s">
         <v>118</v>
       </c>
@@ -14986,7 +14982,7 @@
       <c r="AM15" s="1"/>
       <c r="AN15" s="83"/>
     </row>
-    <row r="16" spans="1:40" s="26" customFormat="1" ht="30.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:40" s="26" customFormat="1" ht="30.6" hidden="1">
       <c r="A16" s="22" t="s">
         <v>122</v>
       </c>
@@ -15103,7 +15099,7 @@
         <v>46235</v>
       </c>
     </row>
-    <row r="17" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
       <c r="A17" s="22" t="s">
         <v>127</v>
       </c>
@@ -15200,7 +15196,7 @@
       <c r="AM17" s="1"/>
       <c r="AN17" s="83"/>
     </row>
-    <row r="18" spans="1:40" s="26" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:40" s="26" customFormat="1" ht="51" hidden="1">
       <c r="A18" s="22" t="s">
         <v>132</v>
       </c>
@@ -15297,7 +15293,7 @@
       <c r="AM18" s="1"/>
       <c r="AN18" s="83"/>
     </row>
-    <row r="19" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A19" s="22" t="s">
         <v>137</v>
       </c>
@@ -15396,7 +15392,7 @@
       </c>
       <c r="AN19" s="83"/>
     </row>
-    <row r="20" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A20" s="22" t="s">
         <v>142</v>
       </c>
@@ -15493,7 +15489,7 @@
       <c r="AM20" s="1"/>
       <c r="AN20" s="83"/>
     </row>
-    <row r="21" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A21" s="22" t="s">
         <v>147</v>
       </c>
@@ -15608,7 +15604,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="22" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A22" s="22" t="s">
         <v>154</v>
       </c>
@@ -15701,7 +15697,7 @@
       <c r="AM22" s="1"/>
       <c r="AN22" s="83"/>
     </row>
-    <row r="23" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A23" s="22" t="s">
         <v>156</v>
       </c>
@@ -15816,7 +15812,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="24" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A24" s="22" t="s">
         <v>160</v>
       </c>
@@ -15909,7 +15905,7 @@
       <c r="AM24" s="1"/>
       <c r="AN24" s="83"/>
     </row>
-    <row r="25" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A25" s="22" t="s">
         <v>161</v>
       </c>
@@ -16002,7 +15998,7 @@
       <c r="AM25" s="1"/>
       <c r="AN25" s="83"/>
     </row>
-    <row r="26" spans="1:40" s="26" customFormat="1" ht="30.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:40" s="26" customFormat="1" ht="30.6" hidden="1">
       <c r="A26" s="22" t="s">
         <v>163</v>
       </c>
@@ -16097,7 +16093,7 @@
       <c r="AM26" s="1"/>
       <c r="AN26" s="83"/>
     </row>
-    <row r="27" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A27" s="22" t="s">
         <v>166</v>
       </c>
@@ -16190,7 +16186,7 @@
       <c r="AM27" s="1"/>
       <c r="AN27" s="83"/>
     </row>
-    <row r="28" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A28" s="22" t="s">
         <v>169</v>
       </c>
@@ -16285,7 +16281,7 @@
       <c r="AM28" s="62"/>
       <c r="AN28" s="83"/>
     </row>
-    <row r="29" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A29" s="22" t="s">
         <v>172</v>
       </c>
@@ -16380,7 +16376,7 @@
       <c r="AM29" s="1"/>
       <c r="AN29" s="83"/>
     </row>
-    <row r="30" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A30" s="22" t="s">
         <v>175</v>
       </c>
@@ -16473,7 +16469,7 @@
       <c r="AM30" s="1"/>
       <c r="AN30" s="83"/>
     </row>
-    <row r="31" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A31" s="22" t="s">
         <v>179</v>
       </c>
@@ -16560,7 +16556,7 @@
       <c r="AM31" s="1"/>
       <c r="AN31" s="83"/>
     </row>
-    <row r="32" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A32" s="22" t="s">
         <v>181</v>
       </c>
@@ -16677,7 +16673,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="33" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A33" s="22" t="s">
         <v>184</v>
       </c>
@@ -16792,7 +16788,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="34" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A34" s="22" t="s">
         <v>190</v>
       </c>
@@ -16885,7 +16881,7 @@
       <c r="AM34" s="1"/>
       <c r="AN34" s="83"/>
     </row>
-    <row r="35" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A35" s="22" t="s">
         <v>194</v>
       </c>
@@ -17002,7 +16998,7 @@
         <v>46235</v>
       </c>
     </row>
-    <row r="36" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A36" s="22" t="s">
         <v>200</v>
       </c>
@@ -17097,7 +17093,7 @@
       <c r="AM36" s="1"/>
       <c r="AN36" s="83"/>
     </row>
-    <row r="37" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A37" s="22" t="s">
         <v>201</v>
       </c>
@@ -17184,7 +17180,7 @@
       <c r="AM37" s="1"/>
       <c r="AN37" s="83"/>
     </row>
-    <row r="38" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A38" s="22" t="s">
         <v>204</v>
       </c>
@@ -17285,7 +17281,7 @@
       <c r="AM38" s="1"/>
       <c r="AN38" s="83"/>
     </row>
-    <row r="39" spans="1:40" s="26" customFormat="1" ht="71.400000000000006" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:40" s="26" customFormat="1" ht="71.45" hidden="1">
       <c r="A39" s="22" t="s">
         <v>207</v>
       </c>
@@ -17404,7 +17400,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="40" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A40" s="22" t="s">
         <v>211</v>
       </c>
@@ -17497,7 +17493,7 @@
       <c r="AM40" s="1"/>
       <c r="AN40" s="83"/>
     </row>
-    <row r="41" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A41" s="22" t="s">
         <v>214</v>
       </c>
@@ -17590,7 +17586,7 @@
       <c r="AM41" s="1"/>
       <c r="AN41" s="83"/>
     </row>
-    <row r="42" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A42" s="22" t="s">
         <v>217</v>
       </c>
@@ -17683,7 +17679,7 @@
       <c r="AM42" s="1"/>
       <c r="AN42" s="83"/>
     </row>
-    <row r="43" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A43" s="22" t="s">
         <v>221</v>
       </c>
@@ -17776,7 +17772,7 @@
       <c r="AM43" s="1"/>
       <c r="AN43" s="83"/>
     </row>
-    <row r="44" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A44" s="22" t="s">
         <v>225</v>
       </c>
@@ -17893,7 +17889,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="45" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A45" s="22" t="s">
         <v>230</v>
       </c>
@@ -18006,7 +18002,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="46" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A46" s="22" t="s">
         <v>234</v>
       </c>
@@ -18099,7 +18095,7 @@
       <c r="AM46" s="1"/>
       <c r="AN46" s="83"/>
     </row>
-    <row r="47" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A47" s="22" t="s">
         <v>241</v>
       </c>
@@ -18192,7 +18188,7 @@
       <c r="AM47" s="1"/>
       <c r="AN47" s="83"/>
     </row>
-    <row r="48" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A48" s="22" t="s">
         <v>244</v>
       </c>
@@ -18285,7 +18281,7 @@
       <c r="AM48" s="1"/>
       <c r="AN48" s="83"/>
     </row>
-    <row r="49" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A49" s="22" t="s">
         <v>246</v>
       </c>
@@ -18378,7 +18374,7 @@
       <c r="AM49" s="1"/>
       <c r="AN49" s="83"/>
     </row>
-    <row r="50" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A50" s="22" t="s">
         <v>248</v>
       </c>
@@ -18471,7 +18467,7 @@
       <c r="AM50" s="1"/>
       <c r="AN50" s="83"/>
     </row>
-    <row r="51" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A51" s="22" t="s">
         <v>251</v>
       </c>
@@ -18564,7 +18560,7 @@
       <c r="AM51" s="1"/>
       <c r="AN51" s="83"/>
     </row>
-    <row r="52" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A52" s="22" t="s">
         <v>254</v>
       </c>
@@ -18657,7 +18653,7 @@
       <c r="AM52" s="1"/>
       <c r="AN52" s="83"/>
     </row>
-    <row r="53" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A53" s="22" t="s">
         <v>257</v>
       </c>
@@ -18750,7 +18746,7 @@
       <c r="AM53" s="1"/>
       <c r="AN53" s="83"/>
     </row>
-    <row r="54" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A54" s="22" t="s">
         <v>259</v>
       </c>
@@ -18843,7 +18839,7 @@
       <c r="AM54" s="1"/>
       <c r="AN54" s="83"/>
     </row>
-    <row r="55" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A55" s="22" t="s">
         <v>263</v>
       </c>
@@ -18936,7 +18932,7 @@
       <c r="AM55" s="1"/>
       <c r="AN55" s="83"/>
     </row>
-    <row r="56" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A56" s="22" t="s">
         <v>266</v>
       </c>
@@ -19053,7 +19049,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="57" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A57" s="22" t="s">
         <v>270</v>
       </c>
@@ -19146,7 +19142,7 @@
       <c r="AM57" s="1"/>
       <c r="AN57" s="83"/>
     </row>
-    <row r="58" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A58" s="22" t="s">
         <v>271</v>
       </c>
@@ -19239,7 +19235,7 @@
       <c r="AM58" s="1"/>
       <c r="AN58" s="83"/>
     </row>
-    <row r="59" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A59" s="22" t="s">
         <v>273</v>
       </c>
@@ -19332,7 +19328,7 @@
       <c r="AM59" s="1"/>
       <c r="AN59" s="83"/>
     </row>
-    <row r="60" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
       <c r="A60" s="22" t="s">
         <v>275</v>
       </c>
@@ -19443,7 +19439,7 @@
       </c>
       <c r="AN60" s="83"/>
     </row>
-    <row r="61" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A61" s="22" t="s">
         <v>281</v>
       </c>
@@ -19556,7 +19552,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="62" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A62" s="22" t="s">
         <v>287</v>
       </c>
@@ -19649,7 +19645,7 @@
       <c r="AM62" s="1"/>
       <c r="AN62" s="83"/>
     </row>
-    <row r="63" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A63" s="22" t="s">
         <v>289</v>
       </c>
@@ -19742,7 +19738,7 @@
       <c r="AM63" s="1"/>
       <c r="AN63" s="83"/>
     </row>
-    <row r="64" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A64" s="22" t="s">
         <v>292</v>
       </c>
@@ -19835,7 +19831,7 @@
       <c r="AM64" s="1"/>
       <c r="AN64" s="83"/>
     </row>
-    <row r="65" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A65" s="22" t="s">
         <v>294</v>
       </c>
@@ -19930,7 +19926,7 @@
       <c r="AM65" s="1"/>
       <c r="AN65" s="83"/>
     </row>
-    <row r="66" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A66" s="22" t="s">
         <v>296</v>
       </c>
@@ -20025,7 +20021,7 @@
       <c r="AM66" s="1"/>
       <c r="AN66" s="83"/>
     </row>
-    <row r="67" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A67" s="22" t="s">
         <v>298</v>
       </c>
@@ -20114,7 +20110,7 @@
       <c r="AM67" s="1"/>
       <c r="AN67" s="83"/>
     </row>
-    <row r="68" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A68" s="22" t="s">
         <v>299</v>
       </c>
@@ -20207,7 +20203,7 @@
       <c r="AM68" s="1"/>
       <c r="AN68" s="83"/>
     </row>
-    <row r="69" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A69" s="22" t="s">
         <v>301</v>
       </c>
@@ -20302,7 +20298,7 @@
       <c r="AM69" s="1"/>
       <c r="AN69" s="83"/>
     </row>
-    <row r="70" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A70" s="22" t="s">
         <v>304</v>
       </c>
@@ -20395,7 +20391,7 @@
       <c r="AM70" s="1"/>
       <c r="AN70" s="83"/>
     </row>
-    <row r="71" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A71" s="22" t="s">
         <v>306</v>
       </c>
@@ -20488,7 +20484,7 @@
       <c r="AM71" s="1"/>
       <c r="AN71" s="83"/>
     </row>
-    <row r="72" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A72" s="22" t="s">
         <v>309</v>
       </c>
@@ -20583,7 +20579,7 @@
       <c r="AM72" s="1"/>
       <c r="AN72" s="83"/>
     </row>
-    <row r="73" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A73" s="22" t="s">
         <v>312</v>
       </c>
@@ -20676,7 +20672,7 @@
       <c r="AM73" s="1"/>
       <c r="AN73" s="83"/>
     </row>
-    <row r="74" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A74" s="22" t="s">
         <v>314</v>
       </c>
@@ -20769,7 +20765,7 @@
       <c r="AM74" s="1"/>
       <c r="AN74" s="83"/>
     </row>
-    <row r="75" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A75" s="22" t="s">
         <v>316</v>
       </c>
@@ -20860,7 +20856,7 @@
       <c r="AM75" s="1"/>
       <c r="AN75" s="83"/>
     </row>
-    <row r="76" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A76" s="22" t="s">
         <v>319</v>
       </c>
@@ -20953,7 +20949,7 @@
       <c r="AM76" s="1"/>
       <c r="AN76" s="83"/>
     </row>
-    <row r="77" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A77" s="22" t="s">
         <v>323</v>
       </c>
@@ -21044,7 +21040,7 @@
       <c r="AM77" s="1"/>
       <c r="AN77" s="83"/>
     </row>
-    <row r="78" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A78" s="22" t="s">
         <v>325</v>
       </c>
@@ -21157,7 +21153,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="79" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A79" s="22" t="s">
         <v>329</v>
       </c>
@@ -21250,7 +21246,7 @@
       <c r="AM79" s="1"/>
       <c r="AN79" s="83"/>
     </row>
-    <row r="80" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A80" s="22" t="s">
         <v>332</v>
       </c>
@@ -21363,7 +21359,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="81" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A81" s="22" t="s">
         <v>336</v>
       </c>
@@ -21458,7 +21454,7 @@
       <c r="AM81" s="1"/>
       <c r="AN81" s="83"/>
     </row>
-    <row r="82" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A82" s="22" t="s">
         <v>338</v>
       </c>
@@ -21551,7 +21547,7 @@
       <c r="AM82" s="1"/>
       <c r="AN82" s="83"/>
     </row>
-    <row r="83" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A83" s="22" t="s">
         <v>340</v>
       </c>
@@ -21644,7 +21640,7 @@
       <c r="AM83" s="1"/>
       <c r="AN83" s="83"/>
     </row>
-    <row r="84" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A84" s="22" t="s">
         <v>342</v>
       </c>
@@ -21739,7 +21735,7 @@
       <c r="AM84" s="1"/>
       <c r="AN84" s="83"/>
     </row>
-    <row r="85" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A85" s="22" t="s">
         <v>345</v>
       </c>
@@ -21832,7 +21828,7 @@
       <c r="AM85" s="1"/>
       <c r="AN85" s="83"/>
     </row>
-    <row r="86" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A86" s="22" t="s">
         <v>347</v>
       </c>
@@ -21921,7 +21917,7 @@
       <c r="AM86" s="1"/>
       <c r="AN86" s="83"/>
     </row>
-    <row r="87" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A87" s="22" t="s">
         <v>352</v>
       </c>
@@ -22014,7 +22010,7 @@
       <c r="AM87" s="1"/>
       <c r="AN87" s="83"/>
     </row>
-    <row r="88" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A88" s="22" t="s">
         <v>354</v>
       </c>
@@ -22109,7 +22105,7 @@
       <c r="AM88" s="1"/>
       <c r="AN88" s="83"/>
     </row>
-    <row r="89" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A89" s="22" t="s">
         <v>359</v>
       </c>
@@ -22202,7 +22198,7 @@
       <c r="AM89" s="1"/>
       <c r="AN89" s="83"/>
     </row>
-    <row r="90" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A90" s="22" t="s">
         <v>362</v>
       </c>
@@ -22295,7 +22291,7 @@
       <c r="AM90" s="1"/>
       <c r="AN90" s="83"/>
     </row>
-    <row r="91" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A91" s="22" t="s">
         <v>364</v>
       </c>
@@ -22388,7 +22384,7 @@
       <c r="AM91" s="1"/>
       <c r="AN91" s="83"/>
     </row>
-    <row r="92" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A92" s="22" t="s">
         <v>367</v>
       </c>
@@ -22481,7 +22477,7 @@
       <c r="AM92" s="1"/>
       <c r="AN92" s="83"/>
     </row>
-    <row r="93" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A93" s="22" t="s">
         <v>370</v>
       </c>
@@ -22572,7 +22568,7 @@
       <c r="AM93" s="1"/>
       <c r="AN93" s="83"/>
     </row>
-    <row r="94" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A94" s="22" t="s">
         <v>372</v>
       </c>
@@ -22665,7 +22661,7 @@
       <c r="AM94" s="1"/>
       <c r="AN94" s="83"/>
     </row>
-    <row r="95" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A95" s="15" t="s">
         <v>375</v>
       </c>
@@ -22758,7 +22754,7 @@
       <c r="AM95" s="1"/>
       <c r="AN95" s="83"/>
     </row>
-    <row r="96" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A96" s="22" t="s">
         <v>378</v>
       </c>
@@ -22871,7 +22867,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="97" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A97" s="22" t="s">
         <v>381</v>
       </c>
@@ -22958,7 +22954,7 @@
       <c r="AM97" s="1"/>
       <c r="AN97" s="83"/>
     </row>
-    <row r="98" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A98" s="3" t="s">
         <v>382</v>
       </c>
@@ -23053,7 +23049,7 @@
       <c r="AM98" s="1"/>
       <c r="AN98" s="83"/>
     </row>
-    <row r="99" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A99" s="22" t="s">
         <v>386</v>
       </c>
@@ -23148,7 +23144,7 @@
       <c r="AM99" s="1"/>
       <c r="AN99" s="83"/>
     </row>
-    <row r="100" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A100" s="22" t="s">
         <v>388</v>
       </c>
@@ -23241,7 +23237,7 @@
       <c r="AM100" s="1"/>
       <c r="AN100" s="83"/>
     </row>
-    <row r="101" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A101" s="22" t="s">
         <v>391</v>
       </c>
@@ -23334,7 +23330,7 @@
       <c r="AM101" s="1"/>
       <c r="AN101" s="83"/>
     </row>
-    <row r="102" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A102" s="22" t="s">
         <v>394</v>
       </c>
@@ -23423,7 +23419,7 @@
       <c r="AM102" s="1"/>
       <c r="AN102" s="83"/>
     </row>
-    <row r="103" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A103" s="22" t="s">
         <v>397</v>
       </c>
@@ -23516,7 +23512,7 @@
       <c r="AM103" s="1"/>
       <c r="AN103" s="83"/>
     </row>
-    <row r="104" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A104" s="22" t="s">
         <v>398</v>
       </c>
@@ -23611,7 +23607,7 @@
       <c r="AM104" s="1"/>
       <c r="AN104" s="83"/>
     </row>
-    <row r="105" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A105" s="22" t="s">
         <v>400</v>
       </c>
@@ -23698,7 +23694,7 @@
       <c r="AM105" s="1"/>
       <c r="AN105" s="83"/>
     </row>
-    <row r="106" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A106" s="22" t="s">
         <v>402</v>
       </c>
@@ -23791,7 +23787,7 @@
       <c r="AM106" s="1"/>
       <c r="AN106" s="83"/>
     </row>
-    <row r="107" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A107" s="15" t="s">
         <v>404</v>
       </c>
@@ -23878,7 +23874,7 @@
       <c r="AM107" s="1"/>
       <c r="AN107" s="83"/>
     </row>
-    <row r="108" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A108" s="22" t="s">
         <v>406</v>
       </c>
@@ -23969,7 +23965,7 @@
       <c r="AM108" s="1"/>
       <c r="AN108" s="83"/>
     </row>
-    <row r="109" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A109" s="22" t="s">
         <v>408</v>
       </c>
@@ -24062,7 +24058,7 @@
       <c r="AM109" s="1"/>
       <c r="AN109" s="83"/>
     </row>
-    <row r="110" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A110" s="22" t="s">
         <v>410</v>
       </c>
@@ -24177,7 +24173,7 @@
       </c>
       <c r="AN110" s="83"/>
     </row>
-    <row r="111" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A111" s="22" t="s">
         <v>414</v>
       </c>
@@ -24272,7 +24268,7 @@
       <c r="AM111" s="1"/>
       <c r="AN111" s="83"/>
     </row>
-    <row r="112" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A112" s="22" t="s">
         <v>416</v>
       </c>
@@ -24387,7 +24383,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="113" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A113" s="22" t="s">
         <v>419</v>
       </c>
@@ -24476,7 +24472,7 @@
       <c r="AM113" s="1"/>
       <c r="AN113" s="83"/>
     </row>
-    <row r="114" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A114" s="22" t="s">
         <v>423</v>
       </c>
@@ -24563,7 +24559,7 @@
       <c r="AM114" s="1"/>
       <c r="AN114" s="83"/>
     </row>
-    <row r="115" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A115" s="3" t="s">
         <v>424</v>
       </c>
@@ -24656,7 +24652,7 @@
       <c r="AM115" s="1"/>
       <c r="AN115" s="83"/>
     </row>
-    <row r="116" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A116" s="22" t="s">
         <v>426</v>
       </c>
@@ -24741,7 +24737,7 @@
       <c r="AM116" s="1"/>
       <c r="AN116" s="83"/>
     </row>
-    <row r="117" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A117" s="22" t="s">
         <v>428</v>
       </c>
@@ -24836,7 +24832,7 @@
       <c r="AM117" s="1"/>
       <c r="AN117" s="83"/>
     </row>
-    <row r="118" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A118" s="22" t="s">
         <v>430</v>
       </c>
@@ -24929,7 +24925,7 @@
       <c r="AM118" s="1"/>
       <c r="AN118" s="83"/>
     </row>
-    <row r="119" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A119" s="22" t="s">
         <v>432</v>
       </c>
@@ -25020,7 +25016,7 @@
       <c r="AM119" s="1"/>
       <c r="AN119" s="83"/>
     </row>
-    <row r="120" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A120" s="15" t="s">
         <v>434</v>
       </c>
@@ -25105,7 +25101,7 @@
       <c r="AM120" s="1"/>
       <c r="AN120" s="83"/>
     </row>
-    <row r="121" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A121" s="22" t="s">
         <v>435</v>
       </c>
@@ -25196,7 +25192,7 @@
       <c r="AM121" s="1"/>
       <c r="AN121" s="83"/>
     </row>
-    <row r="122" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A122" s="15" t="s">
         <v>437</v>
       </c>
@@ -25283,7 +25279,7 @@
       <c r="AM122" s="1"/>
       <c r="AN122" s="83"/>
     </row>
-    <row r="123" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A123" s="22" t="s">
         <v>438</v>
       </c>
@@ -25394,7 +25390,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="124" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A124" s="22" t="s">
         <v>440</v>
       </c>
@@ -25479,7 +25475,7 @@
       <c r="AM124" s="1"/>
       <c r="AN124" s="83"/>
     </row>
-    <row r="125" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A125" s="22" t="s">
         <v>441</v>
       </c>
@@ -25574,7 +25570,7 @@
       <c r="AM125" s="1"/>
       <c r="AN125" s="83"/>
     </row>
-    <row r="126" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A126" s="22" t="s">
         <v>443</v>
       </c>
@@ -25663,7 +25659,7 @@
       <c r="AM126" s="1"/>
       <c r="AN126" s="83"/>
     </row>
-    <row r="127" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A127" s="22" t="s">
         <v>446</v>
       </c>
@@ -25756,7 +25752,7 @@
       <c r="AM127" s="1"/>
       <c r="AN127" s="83"/>
     </row>
-    <row r="128" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A128" s="22" t="s">
         <v>448</v>
       </c>
@@ -25845,7 +25841,7 @@
       <c r="AM128" s="1"/>
       <c r="AN128" s="83"/>
     </row>
-    <row r="129" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A129" s="15" t="s">
         <v>451</v>
       </c>
@@ -25938,7 +25934,7 @@
       <c r="AM129" s="1"/>
       <c r="AN129" s="83"/>
     </row>
-    <row r="130" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A130" s="22" t="s">
         <v>453</v>
       </c>
@@ -26021,7 +26017,7 @@
       <c r="AM130" s="1"/>
       <c r="AN130" s="83"/>
     </row>
-    <row r="131" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A131" s="22" t="s">
         <v>454</v>
       </c>
@@ -26104,7 +26100,7 @@
       <c r="AM131" s="1"/>
       <c r="AN131" s="83"/>
     </row>
-    <row r="132" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A132" s="22" t="s">
         <v>455</v>
       </c>
@@ -26197,7 +26193,7 @@
       <c r="AM132" s="1"/>
       <c r="AN132" s="83"/>
     </row>
-    <row r="133" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A133" s="22" t="s">
         <v>457</v>
       </c>
@@ -26292,7 +26288,7 @@
       <c r="AM133" s="1"/>
       <c r="AN133" s="83"/>
     </row>
-    <row r="134" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A134" s="22" t="s">
         <v>459</v>
       </c>
@@ -26383,7 +26379,7 @@
       <c r="AM134" s="1"/>
       <c r="AN134" s="83"/>
     </row>
-    <row r="135" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A135" s="15" t="s">
         <v>461</v>
       </c>
@@ -26472,7 +26468,7 @@
       <c r="AM135" s="1"/>
       <c r="AN135" s="83"/>
     </row>
-    <row r="136" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A136" s="22" t="s">
         <v>463</v>
       </c>
@@ -26563,7 +26559,7 @@
       <c r="AM136" s="1"/>
       <c r="AN136" s="83"/>
     </row>
-    <row r="137" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A137" s="15" t="s">
         <v>465</v>
       </c>
@@ -26648,7 +26644,7 @@
       <c r="AM137" s="1"/>
       <c r="AN137" s="83"/>
     </row>
-    <row r="138" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A138" s="22" t="s">
         <v>467</v>
       </c>
@@ -26739,7 +26735,7 @@
       <c r="AM138" s="1"/>
       <c r="AN138" s="83"/>
     </row>
-    <row r="139" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A139" s="15" t="s">
         <v>468</v>
       </c>
@@ -26826,7 +26822,7 @@
       <c r="AM139" s="1"/>
       <c r="AN139" s="83"/>
     </row>
-    <row r="140" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A140" s="22" t="s">
         <v>471</v>
       </c>
@@ -26917,7 +26913,7 @@
       <c r="AM140" s="1"/>
       <c r="AN140" s="83"/>
     </row>
-    <row r="141" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A141" s="22" t="s">
         <v>474</v>
       </c>
@@ -27002,7 +26998,7 @@
       <c r="AM141" s="1"/>
       <c r="AN141" s="83"/>
     </row>
-    <row r="142" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A142" s="15" t="s">
         <v>475</v>
       </c>
@@ -27093,7 +27089,7 @@
       <c r="AM142" s="1"/>
       <c r="AN142" s="83"/>
     </row>
-    <row r="143" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A143" s="15" t="s">
         <v>477</v>
       </c>
@@ -27180,7 +27176,7 @@
       <c r="AM143" s="1"/>
       <c r="AN143" s="83"/>
     </row>
-    <row r="144" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A144" s="15" t="s">
         <v>480</v>
       </c>
@@ -27275,7 +27271,7 @@
       <c r="AM144" s="1"/>
       <c r="AN144" s="83"/>
     </row>
-    <row r="145" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A145" s="15" t="s">
         <v>482</v>
       </c>
@@ -27362,7 +27358,7 @@
       <c r="AM145" s="1"/>
       <c r="AN145" s="83"/>
     </row>
-    <row r="146" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A146" s="15" t="s">
         <v>483</v>
       </c>
@@ -27447,7 +27443,7 @@
       <c r="AM146" s="1"/>
       <c r="AN146" s="83"/>
     </row>
-    <row r="147" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A147" s="15" t="s">
         <v>484</v>
       </c>
@@ -27528,7 +27524,7 @@
       <c r="AM147" s="1"/>
       <c r="AN147" s="83"/>
     </row>
-    <row r="148" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A148" s="15" t="s">
         <v>485</v>
       </c>
@@ -27621,7 +27617,7 @@
       <c r="AM148" s="1"/>
       <c r="AN148" s="83"/>
     </row>
-    <row r="149" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A149" s="15" t="s">
         <v>487</v>
       </c>
@@ -27712,7 +27708,7 @@
       <c r="AM149" s="1"/>
       <c r="AN149" s="83"/>
     </row>
-    <row r="150" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A150" s="15" t="s">
         <v>489</v>
       </c>
@@ -27793,7 +27789,7 @@
       <c r="AM150" s="1"/>
       <c r="AN150" s="83"/>
     </row>
-    <row r="151" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A151" s="15" t="s">
         <v>490</v>
       </c>
@@ -27880,7 +27876,7 @@
       <c r="AM151" s="1"/>
       <c r="AN151" s="83"/>
     </row>
-    <row r="152" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A152" s="15" t="s">
         <v>492</v>
       </c>
@@ -27971,7 +27967,7 @@
       <c r="AM152" s="1"/>
       <c r="AN152" s="83"/>
     </row>
-    <row r="153" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A153" s="15" t="s">
         <v>495</v>
       </c>
@@ -28058,7 +28054,7 @@
       <c r="AM153" s="1"/>
       <c r="AN153" s="83"/>
     </row>
-    <row r="154" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A154" s="15" t="s">
         <v>497</v>
       </c>
@@ -28145,7 +28141,7 @@
       <c r="AM154" s="1"/>
       <c r="AN154" s="83"/>
     </row>
-    <row r="155" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A155" s="15" t="s">
         <v>499</v>
       </c>
@@ -28232,7 +28228,7 @@
       <c r="AM155" s="1"/>
       <c r="AN155" s="83"/>
     </row>
-    <row r="156" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A156" s="15" t="s">
         <v>501</v>
       </c>
@@ -28321,7 +28317,7 @@
       <c r="AM156" s="1"/>
       <c r="AN156" s="83"/>
     </row>
-    <row r="157" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A157" s="15" t="s">
         <v>504</v>
       </c>
@@ -28408,7 +28404,7 @@
       <c r="AM157" s="1"/>
       <c r="AN157" s="83"/>
     </row>
-    <row r="158" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A158" s="15" t="s">
         <v>506</v>
       </c>
@@ -28495,7 +28491,7 @@
       <c r="AM158" s="1"/>
       <c r="AN158" s="83"/>
     </row>
-    <row r="159" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A159" s="15" t="s">
         <v>508</v>
       </c>
@@ -28584,7 +28580,7 @@
       <c r="AM159" s="1"/>
       <c r="AN159" s="83"/>
     </row>
-    <row r="160" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A160" s="15" t="s">
         <v>510</v>
       </c>
@@ -28671,7 +28667,7 @@
       <c r="AM160" s="1"/>
       <c r="AN160" s="83"/>
     </row>
-    <row r="161" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A161" s="15" t="s">
         <v>512</v>
       </c>
@@ -28758,7 +28754,7 @@
       <c r="AM161" s="1"/>
       <c r="AN161" s="83"/>
     </row>
-    <row r="162" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A162" s="15" t="s">
         <v>514</v>
       </c>
@@ -28849,7 +28845,7 @@
       <c r="AM162" s="1"/>
       <c r="AN162" s="83"/>
     </row>
-    <row r="163" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A163" s="15" t="s">
         <v>517</v>
       </c>
@@ -28936,7 +28932,7 @@
       <c r="AM163" s="1"/>
       <c r="AN163" s="83"/>
     </row>
-    <row r="164" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A164" s="15" t="s">
         <v>519</v>
       </c>
@@ -29023,7 +29019,7 @@
       <c r="AM164" s="1"/>
       <c r="AN164" s="83"/>
     </row>
-    <row r="165" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A165" s="15" t="s">
         <v>521</v>
       </c>
@@ -29112,7 +29108,7 @@
       <c r="AM165" s="1"/>
       <c r="AN165" s="83"/>
     </row>
-    <row r="166" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A166" s="15" t="s">
         <v>523</v>
       </c>
@@ -29201,7 +29197,7 @@
       <c r="AM166" s="1"/>
       <c r="AN166" s="83"/>
     </row>
-    <row r="167" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A167" s="15" t="s">
         <v>525</v>
       </c>
@@ -29290,7 +29286,7 @@
       <c r="AM167" s="1"/>
       <c r="AN167" s="83"/>
     </row>
-    <row r="168" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A168" s="15" t="s">
         <v>527</v>
       </c>
@@ -29379,7 +29375,7 @@
       <c r="AM168" s="1"/>
       <c r="AN168" s="83"/>
     </row>
-    <row r="169" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A169" s="15" t="s">
         <v>529</v>
       </c>
@@ -29466,7 +29462,7 @@
       <c r="AM169" s="1"/>
       <c r="AN169" s="83"/>
     </row>
-    <row r="170" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A170" s="15" t="s">
         <v>531</v>
       </c>
@@ -29555,7 +29551,7 @@
       <c r="AM170" s="1"/>
       <c r="AN170" s="83"/>
     </row>
-    <row r="171" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A171" s="15" t="s">
         <v>533</v>
       </c>
@@ -29644,7 +29640,7 @@
       <c r="AM171" s="1"/>
       <c r="AN171" s="83"/>
     </row>
-    <row r="172" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A172" s="15" t="s">
         <v>535</v>
       </c>
@@ -29731,7 +29727,7 @@
       <c r="AM172" s="1"/>
       <c r="AN172" s="83"/>
     </row>
-    <row r="173" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A173" s="15" t="s">
         <v>537</v>
       </c>
@@ -29820,7 +29816,7 @@
       <c r="AM173" s="1"/>
       <c r="AN173" s="83"/>
     </row>
-    <row r="174" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A174" s="15" t="s">
         <v>539</v>
       </c>
@@ -29909,7 +29905,7 @@
       <c r="AM174" s="1"/>
       <c r="AN174" s="83"/>
     </row>
-    <row r="175" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A175" s="15" t="s">
         <v>541</v>
       </c>
@@ -29982,7 +29978,7 @@
       <c r="AM175" s="1"/>
       <c r="AN175" s="83"/>
     </row>
-    <row r="176" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A176" s="15" t="s">
         <v>542</v>
       </c>
@@ -30069,7 +30065,7 @@
       <c r="AM176" s="1"/>
       <c r="AN176" s="83"/>
     </row>
-    <row r="177" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A177" s="15" t="s">
         <v>545</v>
       </c>
@@ -30154,7 +30150,7 @@
       <c r="AM177" s="1"/>
       <c r="AN177" s="83"/>
     </row>
-    <row r="178" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A178" s="15" t="s">
         <v>547</v>
       </c>
@@ -30245,7 +30241,7 @@
       <c r="AM178" s="1"/>
       <c r="AN178" s="83"/>
     </row>
-    <row r="179" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A179" s="15" t="s">
         <v>548</v>
       </c>
@@ -30332,7 +30328,7 @@
       <c r="AM179" s="1"/>
       <c r="AN179" s="83"/>
     </row>
-    <row r="180" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A180" s="15" t="s">
         <v>552</v>
       </c>
@@ -30447,7 +30443,7 @@
         <v>46204</v>
       </c>
     </row>
-    <row r="181" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A181" s="15" t="s">
         <v>557</v>
       </c>
@@ -30562,7 +30558,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="182" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A182" s="15" t="s">
         <v>562</v>
       </c>
@@ -30653,7 +30649,7 @@
       <c r="AM182" s="1"/>
       <c r="AN182" s="83"/>
     </row>
-    <row r="183" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A183" s="15" t="s">
         <v>564</v>
       </c>
@@ -30742,7 +30738,7 @@
       <c r="AM183" s="1"/>
       <c r="AN183" s="83"/>
     </row>
-    <row r="184" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A184" s="15" t="s">
         <v>565</v>
       </c>
@@ -30831,7 +30827,7 @@
       <c r="AM184" s="1"/>
       <c r="AN184" s="83"/>
     </row>
-    <row r="185" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A185" s="15" t="s">
         <v>567</v>
       </c>
@@ -30918,7 +30914,7 @@
       <c r="AM185" s="1"/>
       <c r="AN185" s="83"/>
     </row>
-    <row r="186" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A186" s="15" t="s">
         <v>570</v>
       </c>
@@ -31005,7 +31001,7 @@
       <c r="AM186" s="1"/>
       <c r="AN186" s="83"/>
     </row>
-    <row r="187" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A187" s="15" t="s">
         <v>572</v>
       </c>
@@ -31092,7 +31088,7 @@
       <c r="AM187" s="1"/>
       <c r="AN187" s="83"/>
     </row>
-    <row r="188" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A188" s="15" t="s">
         <v>575</v>
       </c>
@@ -31179,7 +31175,7 @@
       <c r="AM188" s="1"/>
       <c r="AN188" s="83"/>
     </row>
-    <row r="189" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A189" s="15" t="s">
         <v>578</v>
       </c>
@@ -31266,7 +31262,7 @@
       <c r="AM189" s="1"/>
       <c r="AN189" s="83"/>
     </row>
-    <row r="190" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A190" s="15" t="s">
         <v>580</v>
       </c>
@@ -31353,7 +31349,7 @@
       <c r="AM190" s="1"/>
       <c r="AN190" s="83"/>
     </row>
-    <row r="191" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A191" s="15" t="s">
         <v>582</v>
       </c>
@@ -31434,7 +31430,7 @@
       <c r="AM191" s="1"/>
       <c r="AN191" s="83"/>
     </row>
-    <row r="192" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A192" s="15" t="s">
         <v>584</v>
       </c>
@@ -31521,7 +31517,7 @@
       <c r="AM192" s="1"/>
       <c r="AN192" s="83"/>
     </row>
-    <row r="193" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A193" s="15" t="s">
         <v>586</v>
       </c>
@@ -31610,7 +31606,7 @@
       <c r="AM193" s="1"/>
       <c r="AN193" s="83"/>
     </row>
-    <row r="194" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A194" s="15" t="s">
         <v>589</v>
       </c>
@@ -31697,7 +31693,7 @@
       <c r="AM194" s="1"/>
       <c r="AN194" s="83"/>
     </row>
-    <row r="195" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A195" s="15" t="s">
         <v>592</v>
       </c>
@@ -31784,7 +31780,7 @@
       <c r="AM195" s="1"/>
       <c r="AN195" s="83"/>
     </row>
-    <row r="196" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A196" s="15" t="s">
         <v>595</v>
       </c>
@@ -31873,7 +31869,7 @@
       <c r="AM196" s="1"/>
       <c r="AN196" s="83"/>
     </row>
-    <row r="197" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A197" s="15" t="s">
         <v>599</v>
       </c>
@@ -31962,7 +31958,7 @@
       <c r="AM197" s="1"/>
       <c r="AN197" s="83"/>
     </row>
-    <row r="198" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A198" s="15" t="s">
         <v>601</v>
       </c>
@@ -32051,7 +32047,7 @@
       <c r="AM198" s="1"/>
       <c r="AN198" s="83"/>
     </row>
-    <row r="199" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A199" s="15" t="s">
         <v>603</v>
       </c>
@@ -32138,7 +32134,7 @@
       <c r="AM199" s="1"/>
       <c r="AN199" s="83"/>
     </row>
-    <row r="200" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A200" s="15" t="s">
         <v>605</v>
       </c>
@@ -32225,7 +32221,7 @@
       <c r="AM200" s="1"/>
       <c r="AN200" s="83"/>
     </row>
-    <row r="201" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A201" s="15" t="s">
         <v>607</v>
       </c>
@@ -32312,7 +32308,7 @@
       <c r="AM201" s="1"/>
       <c r="AN201" s="83"/>
     </row>
-    <row r="202" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A202" s="15" t="s">
         <v>610</v>
       </c>
@@ -32403,7 +32399,7 @@
       <c r="AM202" s="1"/>
       <c r="AN202" s="83"/>
     </row>
-    <row r="203" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A203" s="15" t="s">
         <v>611</v>
       </c>
@@ -32490,7 +32486,7 @@
       <c r="AM203" s="1"/>
       <c r="AN203" s="83"/>
     </row>
-    <row r="204" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A204" s="15" t="s">
         <v>612</v>
       </c>
@@ -32577,7 +32573,7 @@
       <c r="AM204" s="1"/>
       <c r="AN204" s="83"/>
     </row>
-    <row r="205" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A205" s="15" t="s">
         <v>614</v>
       </c>
@@ -32666,7 +32662,7 @@
       <c r="AM205" s="1"/>
       <c r="AN205" s="83"/>
     </row>
-    <row r="206" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A206" s="15" t="s">
         <v>615</v>
       </c>
@@ -32759,7 +32755,7 @@
       <c r="AM206" s="1"/>
       <c r="AN206" s="83"/>
     </row>
-    <row r="207" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A207" s="15" t="s">
         <v>616</v>
       </c>
@@ -32846,7 +32842,7 @@
       <c r="AM207" s="1"/>
       <c r="AN207" s="83"/>
     </row>
-    <row r="208" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A208" s="15" t="s">
         <v>619</v>
       </c>
@@ -32935,7 +32931,7 @@
       <c r="AM208" s="1"/>
       <c r="AN208" s="83"/>
     </row>
-    <row r="209" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A209" s="15" t="s">
         <v>621</v>
       </c>
@@ -33022,7 +33018,7 @@
       <c r="AM209" s="1"/>
       <c r="AN209" s="83"/>
     </row>
-    <row r="210" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A210" s="15" t="s">
         <v>623</v>
       </c>
@@ -33109,7 +33105,7 @@
       <c r="AM210" s="1"/>
       <c r="AN210" s="83"/>
     </row>
-    <row r="211" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A211" s="15" t="s">
         <v>625</v>
       </c>
@@ -33196,7 +33192,7 @@
       <c r="AM211" s="1"/>
       <c r="AN211" s="83"/>
     </row>
-    <row r="212" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A212" s="15" t="s">
         <v>627</v>
       </c>
@@ -33285,7 +33281,7 @@
       <c r="AM212" s="1"/>
       <c r="AN212" s="83"/>
     </row>
-    <row r="213" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A213" s="15" t="s">
         <v>629</v>
       </c>
@@ -33372,7 +33368,7 @@
       <c r="AM213" s="1"/>
       <c r="AN213" s="83"/>
     </row>
-    <row r="214" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A214" s="15" t="s">
         <v>631</v>
       </c>
@@ -33459,7 +33455,7 @@
       <c r="AM214" s="1"/>
       <c r="AN214" s="83"/>
     </row>
-    <row r="215" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A215" s="15" t="s">
         <v>634</v>
       </c>
@@ -33548,7 +33544,7 @@
       <c r="AM215" s="1"/>
       <c r="AN215" s="83"/>
     </row>
-    <row r="216" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A216" s="15" t="s">
         <v>637</v>
       </c>
@@ -33633,7 +33629,7 @@
       <c r="AM216" s="1"/>
       <c r="AN216" s="83"/>
     </row>
-    <row r="217" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A217" s="15" t="s">
         <v>639</v>
       </c>
@@ -33720,7 +33716,7 @@
       <c r="AM217" s="1"/>
       <c r="AN217" s="83"/>
     </row>
-    <row r="218" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A218" s="15" t="s">
         <v>642</v>
       </c>
@@ -33805,7 +33801,7 @@
       <c r="AM218" s="1"/>
       <c r="AN218" s="83"/>
     </row>
-    <row r="219" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A219" s="15" t="s">
         <v>644</v>
       </c>
@@ -33890,7 +33886,7 @@
       <c r="AM219" s="1"/>
       <c r="AN219" s="83"/>
     </row>
-    <row r="220" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A220" s="15" t="s">
         <v>646</v>
       </c>
@@ -33971,7 +33967,7 @@
       <c r="AM220" s="1"/>
       <c r="AN220" s="83"/>
     </row>
-    <row r="221" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A221" s="15" t="s">
         <v>647</v>
       </c>
@@ -34056,7 +34052,7 @@
       <c r="AM221" s="1"/>
       <c r="AN221" s="83"/>
     </row>
-    <row r="222" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A222" s="15" t="s">
         <v>650</v>
       </c>
@@ -34141,7 +34137,7 @@
       <c r="AM222" s="1"/>
       <c r="AN222" s="83"/>
     </row>
-    <row r="223" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A223" s="15" t="s">
         <v>653</v>
       </c>
@@ -34226,7 +34222,7 @@
       <c r="AM223" s="1"/>
       <c r="AN223" s="83"/>
     </row>
-    <row r="224" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A224" s="15" t="s">
         <v>655</v>
       </c>
@@ -34315,7 +34311,7 @@
       <c r="AM224" s="1"/>
       <c r="AN224" s="83"/>
     </row>
-    <row r="225" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A225" s="15" t="s">
         <v>657</v>
       </c>
@@ -34398,7 +34394,7 @@
       <c r="AM225" s="1"/>
       <c r="AN225" s="83"/>
     </row>
-    <row r="226" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A226" s="15" t="s">
         <v>659</v>
       </c>
@@ -34485,7 +34481,7 @@
       <c r="AM226" s="1"/>
       <c r="AN226" s="83"/>
     </row>
-    <row r="227" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A227" s="15" t="s">
         <v>661</v>
       </c>
@@ -34572,7 +34568,7 @@
       <c r="AM227" s="1"/>
       <c r="AN227" s="83"/>
     </row>
-    <row r="228" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A228" s="15" t="s">
         <v>664</v>
       </c>
@@ -34657,7 +34653,7 @@
       <c r="AM228" s="1"/>
       <c r="AN228" s="83"/>
     </row>
-    <row r="229" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A229" s="15" t="s">
         <v>666</v>
       </c>
@@ -34740,7 +34736,7 @@
       <c r="AM229" s="1"/>
       <c r="AN229" s="83"/>
     </row>
-    <row r="230" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A230" s="15" t="s">
         <v>667</v>
       </c>
@@ -34825,7 +34821,7 @@
       <c r="AM230" s="1"/>
       <c r="AN230" s="83"/>
     </row>
-    <row r="231" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A231" s="15" t="s">
         <v>669</v>
       </c>
@@ -34910,7 +34906,7 @@
       <c r="AM231" s="1"/>
       <c r="AN231" s="83"/>
     </row>
-    <row r="232" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A232" s="15" t="s">
         <v>671</v>
       </c>
@@ -34991,7 +34987,7 @@
       <c r="AM232" s="1"/>
       <c r="AN232" s="83"/>
     </row>
-    <row r="233" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A233" s="15" t="s">
         <v>672</v>
       </c>
@@ -35076,7 +35072,7 @@
       <c r="AM233" s="1"/>
       <c r="AN233" s="83"/>
     </row>
-    <row r="234" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A234" s="15" t="s">
         <v>674</v>
       </c>
@@ -35165,7 +35161,7 @@
       <c r="AM234" s="1"/>
       <c r="AN234" s="83"/>
     </row>
-    <row r="235" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A235" s="15" t="s">
         <v>675</v>
       </c>
@@ -35252,7 +35248,7 @@
       <c r="AM235" s="1"/>
       <c r="AN235" s="83"/>
     </row>
-    <row r="236" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A236" s="15" t="s">
         <v>678</v>
       </c>
@@ -35339,7 +35335,7 @@
       <c r="AM236" s="1"/>
       <c r="AN236" s="83"/>
     </row>
-    <row r="237" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A237" s="15" t="s">
         <v>680</v>
       </c>
@@ -35426,7 +35422,7 @@
       <c r="AM237" s="1"/>
       <c r="AN237" s="83"/>
     </row>
-    <row r="238" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A238" s="15" t="s">
         <v>683</v>
       </c>
@@ -35517,7 +35513,7 @@
       <c r="AM238" s="1"/>
       <c r="AN238" s="83"/>
     </row>
-    <row r="239" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A239" s="15" t="s">
         <v>686</v>
       </c>
@@ -35608,7 +35604,7 @@
       <c r="AM239" s="1"/>
       <c r="AN239" s="83"/>
     </row>
-    <row r="240" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A240" s="15" t="s">
         <v>688</v>
       </c>
@@ -35699,7 +35695,7 @@
       <c r="AM240" s="1"/>
       <c r="AN240" s="83"/>
     </row>
-    <row r="241" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A241" s="15" t="s">
         <v>690</v>
       </c>
@@ -35788,7 +35784,7 @@
       <c r="AM241" s="1"/>
       <c r="AN241" s="83"/>
     </row>
-    <row r="242" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A242" s="15" t="s">
         <v>692</v>
       </c>
@@ -35875,7 +35871,7 @@
       <c r="AM242" s="1"/>
       <c r="AN242" s="83"/>
     </row>
-    <row r="243" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A243" s="15" t="s">
         <v>694</v>
       </c>
@@ -35968,7 +35964,7 @@
       <c r="AM243" s="1"/>
       <c r="AN243" s="83"/>
     </row>
-    <row r="244" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A244" s="15" t="s">
         <v>696</v>
       </c>
@@ -36055,7 +36051,7 @@
       <c r="AM244" s="1"/>
       <c r="AN244" s="83"/>
     </row>
-    <row r="245" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A245" s="15" t="s">
         <v>698</v>
       </c>
@@ -36140,7 +36136,7 @@
       <c r="AM245" s="1"/>
       <c r="AN245" s="83"/>
     </row>
-    <row r="246" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A246" s="15" t="s">
         <v>700</v>
       </c>
@@ -36227,7 +36223,7 @@
       <c r="AM246" s="1"/>
       <c r="AN246" s="83"/>
     </row>
-    <row r="247" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A247" s="15" t="s">
         <v>702</v>
       </c>
@@ -36314,7 +36310,7 @@
       <c r="AM247" s="1"/>
       <c r="AN247" s="83"/>
     </row>
-    <row r="248" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A248" s="15" t="s">
         <v>704</v>
       </c>
@@ -36401,7 +36397,7 @@
       <c r="AM248" s="1"/>
       <c r="AN248" s="83"/>
     </row>
-    <row r="249" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A249" s="15" t="s">
         <v>706</v>
       </c>
@@ -36488,7 +36484,7 @@
       <c r="AM249" s="1"/>
       <c r="AN249" s="83"/>
     </row>
-    <row r="250" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A250" s="15" t="s">
         <v>708</v>
       </c>
@@ -36577,7 +36573,7 @@
       <c r="AM250" s="1"/>
       <c r="AN250" s="83"/>
     </row>
-    <row r="251" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A251" s="15" t="s">
         <v>709</v>
       </c>
@@ -36662,7 +36658,7 @@
       <c r="AM251" s="1"/>
       <c r="AN251" s="83"/>
     </row>
-    <row r="252" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A252" s="15" t="s">
         <v>711</v>
       </c>
@@ -36747,7 +36743,7 @@
       <c r="AM252" s="1"/>
       <c r="AN252" s="83"/>
     </row>
-    <row r="253" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A253" s="15" t="s">
         <v>713</v>
       </c>
@@ -36832,7 +36828,7 @@
       <c r="AM253" s="1"/>
       <c r="AN253" s="83"/>
     </row>
-    <row r="254" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A254" s="15" t="s">
         <v>715</v>
       </c>
@@ -36917,7 +36913,7 @@
       <c r="AM254" s="1"/>
       <c r="AN254" s="83"/>
     </row>
-    <row r="255" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A255" s="15" t="s">
         <v>717</v>
       </c>
@@ -37004,7 +37000,7 @@
       <c r="AM255" s="1"/>
       <c r="AN255" s="83"/>
     </row>
-    <row r="256" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A256" s="15" t="s">
         <v>719</v>
       </c>
@@ -37093,7 +37089,7 @@
       <c r="AM256" s="1"/>
       <c r="AN256" s="83"/>
     </row>
-    <row r="257" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A257" s="15" t="s">
         <v>721</v>
       </c>
@@ -37180,7 +37176,7 @@
       <c r="AM257" s="1"/>
       <c r="AN257" s="83"/>
     </row>
-    <row r="258" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A258" s="15" t="s">
         <v>723</v>
       </c>
@@ -37267,7 +37263,7 @@
       <c r="AM258" s="1"/>
       <c r="AN258" s="83"/>
     </row>
-    <row r="259" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A259" s="15" t="s">
         <v>725</v>
       </c>
@@ -37354,7 +37350,7 @@
       <c r="AM259" s="1"/>
       <c r="AN259" s="83"/>
     </row>
-    <row r="260" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A260" s="15" t="s">
         <v>727</v>
       </c>
@@ -37439,7 +37435,7 @@
       <c r="AM260" s="1"/>
       <c r="AN260" s="83"/>
     </row>
-    <row r="261" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A261" s="15" t="s">
         <v>728</v>
       </c>
@@ -37520,7 +37516,7 @@
       <c r="AM261" s="1"/>
       <c r="AN261" s="83"/>
     </row>
-    <row r="262" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A262" s="15" t="s">
         <v>729</v>
       </c>
@@ -37601,7 +37597,7 @@
       <c r="AM262" s="1"/>
       <c r="AN262" s="83"/>
     </row>
-    <row r="263" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A263" s="15" t="s">
         <v>730</v>
       </c>
@@ -37678,7 +37674,7 @@
       <c r="AM263" s="1"/>
       <c r="AN263" s="83"/>
     </row>
-    <row r="264" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A264" s="15" t="s">
         <v>732</v>
       </c>
@@ -37759,7 +37755,7 @@
       <c r="AM264" s="1"/>
       <c r="AN264" s="83"/>
     </row>
-    <row r="265" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A265" s="15" t="s">
         <v>733</v>
       </c>
@@ -37836,7 +37832,7 @@
       <c r="AM265" s="1"/>
       <c r="AN265" s="83"/>
     </row>
-    <row r="266" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A266" s="15" t="s">
         <v>734</v>
       </c>
@@ -37917,7 +37913,7 @@
       <c r="AM266" s="1"/>
       <c r="AN266" s="83"/>
     </row>
-    <row r="267" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A267" s="15" t="s">
         <v>735</v>
       </c>
@@ -38000,7 +37996,7 @@
       <c r="AM267" s="1"/>
       <c r="AN267" s="83"/>
     </row>
-    <row r="268" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A268" s="15" t="s">
         <v>736</v>
       </c>
@@ -38081,7 +38077,7 @@
       <c r="AM268" s="1"/>
       <c r="AN268" s="83"/>
     </row>
-    <row r="269" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A269" s="15" t="s">
         <v>738</v>
       </c>
@@ -38162,7 +38158,7 @@
       <c r="AM269" s="1"/>
       <c r="AN269" s="83"/>
     </row>
-    <row r="270" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A270" s="15" t="s">
         <v>739</v>
       </c>
@@ -38243,7 +38239,7 @@
       <c r="AM270" s="1"/>
       <c r="AN270" s="83"/>
     </row>
-    <row r="271" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A271" s="15" t="s">
         <v>740</v>
       </c>
@@ -38324,7 +38320,7 @@
       <c r="AM271" s="1"/>
       <c r="AN271" s="83"/>
     </row>
-    <row r="272" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A272" s="31" t="s">
         <v>741</v>
       </c>
@@ -38405,7 +38401,7 @@
       <c r="AM272" s="1"/>
       <c r="AN272" s="83"/>
     </row>
-    <row r="273" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A273" s="15" t="s">
         <v>742</v>
       </c>
@@ -38488,7 +38484,7 @@
       <c r="AM273" s="1"/>
       <c r="AN273" s="83"/>
     </row>
-    <row r="274" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A274" s="15" t="s">
         <v>743</v>
       </c>
@@ -38569,7 +38565,7 @@
       <c r="AM274" s="1"/>
       <c r="AN274" s="83"/>
     </row>
-    <row r="275" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A275" s="15" t="s">
         <v>744</v>
       </c>
@@ -38650,7 +38646,7 @@
       <c r="AM275" s="1"/>
       <c r="AN275" s="83"/>
     </row>
-    <row r="276" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A276" s="15" t="s">
         <v>745</v>
       </c>
@@ -38731,7 +38727,7 @@
       <c r="AM276" s="1"/>
       <c r="AN276" s="83"/>
     </row>
-    <row r="277" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A277" s="15" t="s">
         <v>746</v>
       </c>
@@ -38812,7 +38808,7 @@
       <c r="AM277" s="1"/>
       <c r="AN277" s="83"/>
     </row>
-    <row r="278" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A278" s="15" t="s">
         <v>747</v>
       </c>
@@ -38893,7 +38889,7 @@
       <c r="AM278" s="1"/>
       <c r="AN278" s="83"/>
     </row>
-    <row r="279" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
       <c r="A279" s="22" t="s">
         <v>748</v>
       </c>
@@ -39010,7 +39006,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="280" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
       <c r="A280" s="22" t="s">
         <v>758</v>
       </c>
@@ -39125,7 +39121,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="281" spans="1:40" s="26" customFormat="1" ht="122.4" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:40" s="26" customFormat="1" ht="122.45" hidden="1">
       <c r="A281" s="22" t="s">
         <v>760</v>
       </c>
@@ -39242,7 +39238,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="282" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A282" s="22" t="s">
         <v>768</v>
       </c>
@@ -39355,7 +39351,7 @@
       <c r="AM282" s="1"/>
       <c r="AN282" s="83"/>
     </row>
-    <row r="283" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A283" s="22" t="s">
         <v>562</v>
       </c>
@@ -39470,7 +39466,7 @@
         <v>46235</v>
       </c>
     </row>
-    <row r="284" spans="1:40" s="26" customFormat="1" ht="81.599999999999994" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:40" s="26" customFormat="1" ht="81.599999999999994" hidden="1">
       <c r="A284" s="22" t="s">
         <v>778</v>
       </c>
@@ -39585,7 +39581,7 @@
       </c>
       <c r="AN284" s="83"/>
     </row>
-    <row r="285" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A285" s="22" t="s">
         <v>782</v>
       </c>
@@ -39700,7 +39696,7 @@
       </c>
       <c r="AN285" s="83"/>
     </row>
-    <row r="286" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A286" s="22" t="s">
         <v>786</v>
       </c>
@@ -39815,7 +39811,7 @@
       </c>
       <c r="AN286" s="83"/>
     </row>
-    <row r="287" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
       <c r="A287" s="22" t="s">
         <v>790</v>
       </c>
@@ -39930,7 +39926,7 @@
       </c>
       <c r="AN287" s="83"/>
     </row>
-    <row r="288" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A288" s="22" t="s">
         <v>792</v>
       </c>
@@ -40045,7 +40041,7 @@
       </c>
       <c r="AN288" s="83"/>
     </row>
-    <row r="289" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A289" s="22" t="s">
         <v>795</v>
       </c>
@@ -40160,7 +40156,7 @@
       </c>
       <c r="AN289" s="83"/>
     </row>
-    <row r="290" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A290" s="22" t="s">
         <v>207</v>
       </c>
@@ -40257,7 +40253,7 @@
       </c>
       <c r="AN290" s="83"/>
     </row>
-    <row r="291" spans="1:40" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:40" s="26" customFormat="1" ht="30.6" hidden="1">
       <c r="A291" s="22" t="s">
         <v>804</v>
       </c>
@@ -40370,7 +40366,7 @@
       </c>
       <c r="AN291" s="83"/>
     </row>
-    <row r="292" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A292" s="22" t="s">
         <v>809</v>
       </c>
@@ -40465,7 +40461,7 @@
       <c r="AM292" s="1"/>
       <c r="AN292" s="83"/>
     </row>
-    <row r="293" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A293" s="22" t="s">
         <v>812</v>
       </c>
@@ -40554,7 +40550,7 @@
       <c r="AM293" s="1"/>
       <c r="AN293" s="83"/>
     </row>
-    <row r="294" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A294" s="22" t="s">
         <v>815</v>
       </c>
@@ -40645,7 +40641,7 @@
       <c r="AM294" s="1"/>
       <c r="AN294" s="83"/>
     </row>
-    <row r="295" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A295" s="22" t="s">
         <v>817</v>
       </c>
@@ -40730,7 +40726,7 @@
       <c r="AM295" s="1"/>
       <c r="AN295" s="83"/>
     </row>
-    <row r="296" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A296" s="22" t="s">
         <v>821</v>
       </c>
@@ -40821,7 +40817,7 @@
       <c r="AM296" s="1"/>
       <c r="AN296" s="83"/>
     </row>
-    <row r="297" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A297" s="22" t="s">
         <v>728</v>
       </c>
@@ -40912,7 +40908,7 @@
       </c>
       <c r="AN297" s="83"/>
     </row>
-    <row r="298" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A298" s="22" t="s">
         <v>156</v>
       </c>
@@ -41001,7 +40997,7 @@
       <c r="AM298" s="1"/>
       <c r="AN298" s="83"/>
     </row>
-    <row r="299" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A299" s="22" t="s">
         <v>828</v>
       </c>
@@ -41092,7 +41088,7 @@
       <c r="AM299" s="1"/>
       <c r="AN299" s="83"/>
     </row>
-    <row r="300" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A300" s="22" t="s">
         <v>829</v>
       </c>
@@ -41181,7 +41177,7 @@
       <c r="AM300" s="1"/>
       <c r="AN300" s="83"/>
     </row>
-    <row r="301" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A301" s="22" t="s">
         <v>391</v>
       </c>
@@ -41272,7 +41268,7 @@
       <c r="AM301" s="1"/>
       <c r="AN301" s="83"/>
     </row>
-    <row r="302" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A302" s="22" t="s">
         <v>266</v>
       </c>
@@ -41361,7 +41357,7 @@
       <c r="AM302" s="1"/>
       <c r="AN302" s="83"/>
     </row>
-    <row r="303" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A303" s="22" t="s">
         <v>836</v>
       </c>
@@ -41452,7 +41448,7 @@
       <c r="AM303" s="1"/>
       <c r="AN303" s="83"/>
     </row>
-    <row r="304" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A304" s="22" t="s">
         <v>839</v>
       </c>
@@ -41543,7 +41539,7 @@
       <c r="AM304" s="1"/>
       <c r="AN304" s="83"/>
     </row>
-    <row r="305" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A305" s="22" t="s">
         <v>53</v>
       </c>
@@ -41634,7 +41630,7 @@
       <c r="AM305" s="1"/>
       <c r="AN305" s="83"/>
     </row>
-    <row r="306" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A306" s="22" t="s">
         <v>843</v>
       </c>
@@ -41717,7 +41713,7 @@
       <c r="AM306" s="1"/>
       <c r="AN306" s="83"/>
     </row>
-    <row r="307" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A307" s="22" t="s">
         <v>845</v>
       </c>
@@ -41808,7 +41804,7 @@
       <c r="AM307" s="1"/>
       <c r="AN307" s="83"/>
     </row>
-    <row r="308" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A308" s="22" t="s">
         <v>847</v>
       </c>
@@ -41897,7 +41893,7 @@
       <c r="AM308" s="1"/>
       <c r="AN308" s="83"/>
     </row>
-    <row r="309" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A309" s="22" t="s">
         <v>848</v>
       </c>
@@ -41988,7 +41984,7 @@
       <c r="AM309" s="1"/>
       <c r="AN309" s="83"/>
     </row>
-    <row r="310" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A310" s="22" t="s">
         <v>650</v>
       </c>
@@ -42073,7 +42069,7 @@
       <c r="AM310" s="1"/>
       <c r="AN310" s="83"/>
     </row>
-    <row r="311" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A311" s="22" t="s">
         <v>739</v>
       </c>
@@ -42164,7 +42160,7 @@
       <c r="AM311" s="1"/>
       <c r="AN311" s="83"/>
     </row>
-    <row r="312" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A312" s="22" t="s">
         <v>118</v>
       </c>
@@ -42253,7 +42249,7 @@
       <c r="AM312" s="1"/>
       <c r="AN312" s="83"/>
     </row>
-    <row r="313" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A313" s="22">
         <v>98451</v>
       </c>
@@ -42326,7 +42322,7 @@
       <c r="AM313" s="1"/>
       <c r="AN313" s="83"/>
     </row>
-    <row r="314" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A314" s="22" t="s">
         <v>854</v>
       </c>
@@ -42421,7 +42417,7 @@
       <c r="AM314" s="1"/>
       <c r="AN314" s="83"/>
     </row>
-    <row r="315" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A315" s="22" t="s">
         <v>857</v>
       </c>
@@ -42512,7 +42508,7 @@
       <c r="AM315" s="1"/>
       <c r="AN315" s="83"/>
     </row>
-    <row r="316" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A316" s="3" t="s">
         <v>859</v>
       </c>
@@ -42599,7 +42595,7 @@
       <c r="AM316" s="1"/>
       <c r="AN316" s="83"/>
     </row>
-    <row r="317" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A317" s="22" t="s">
         <v>644</v>
       </c>
@@ -42684,7 +42680,7 @@
       <c r="AM317" s="1"/>
       <c r="AN317" s="83"/>
     </row>
-    <row r="318" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A318" s="22" t="s">
         <v>862</v>
       </c>
@@ -42775,7 +42771,7 @@
       <c r="AM318" s="1"/>
       <c r="AN318" s="83"/>
     </row>
-    <row r="319" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A319" s="22" t="s">
         <v>864</v>
       </c>
@@ -42870,7 +42866,7 @@
       <c r="AM319" s="1"/>
       <c r="AN319" s="83"/>
     </row>
-    <row r="320" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A320" s="22" t="s">
         <v>325</v>
       </c>
@@ -42959,7 +42955,7 @@
       <c r="AM320" s="1"/>
       <c r="AN320" s="83"/>
     </row>
-    <row r="321" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A321" s="22" t="s">
         <v>866</v>
       </c>
@@ -43040,7 +43036,7 @@
       <c r="AM321" s="1"/>
       <c r="AN321" s="83"/>
     </row>
-    <row r="322" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A322" s="3" t="s">
         <v>868</v>
       </c>
@@ -43127,7 +43123,7 @@
       <c r="AM322" s="1"/>
       <c r="AN322" s="83"/>
     </row>
-    <row r="323" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A323" s="22" t="s">
         <v>869</v>
       </c>
@@ -43214,7 +43210,7 @@
       <c r="AM323" s="1"/>
       <c r="AN323" s="83"/>
     </row>
-    <row r="324" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A324" s="22" t="s">
         <v>870</v>
       </c>
@@ -43297,7 +43293,7 @@
       <c r="AM324" s="1"/>
       <c r="AN324" s="83"/>
     </row>
-    <row r="325" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A325" s="22" t="s">
         <v>132</v>
       </c>
@@ -43386,7 +43382,7 @@
       <c r="AM325" s="1"/>
       <c r="AN325" s="83"/>
     </row>
-    <row r="326" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A326" s="3" t="s">
         <v>874</v>
       </c>
@@ -43475,7 +43471,7 @@
       <c r="AM326" s="1"/>
       <c r="AN326" s="83"/>
     </row>
-    <row r="327" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A327" s="22" t="s">
         <v>646</v>
       </c>
@@ -43560,7 +43556,7 @@
       <c r="AM327" s="1"/>
       <c r="AN327" s="83"/>
     </row>
-    <row r="328" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A328" s="3" t="s">
         <v>876</v>
       </c>
@@ -43647,7 +43643,7 @@
       <c r="AM328" s="1"/>
       <c r="AN328" s="83"/>
     </row>
-    <row r="329" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A329" s="3" t="s">
         <v>877</v>
       </c>
@@ -43734,7 +43730,7 @@
       <c r="AM329" s="1"/>
       <c r="AN329" s="83"/>
     </row>
-    <row r="330" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A330" s="3" t="s">
         <v>878</v>
       </c>
@@ -43821,7 +43817,7 @@
       <c r="AM330" s="1"/>
       <c r="AN330" s="83"/>
     </row>
-    <row r="331" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A331" s="3" t="s">
         <v>880</v>
       </c>
@@ -43904,7 +43900,7 @@
       <c r="AM331" s="1"/>
       <c r="AN331" s="83"/>
     </row>
-    <row r="332" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A332" s="3" t="s">
         <v>883</v>
       </c>
@@ -43987,7 +43983,7 @@
       <c r="AM332" s="1"/>
       <c r="AN332" s="83"/>
     </row>
-    <row r="333" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A333" s="3" t="s">
         <v>886</v>
       </c>
@@ -44074,7 +44070,7 @@
       <c r="AM333" s="1"/>
       <c r="AN333" s="83"/>
     </row>
-    <row r="334" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A334" s="22" t="s">
         <v>887</v>
       </c>
@@ -44165,7 +44161,7 @@
       <c r="AM334" s="1"/>
       <c r="AN334" s="83"/>
     </row>
-    <row r="335" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A335" s="22" t="s">
         <v>890</v>
       </c>
@@ -44248,7 +44244,7 @@
       <c r="AM335" s="1"/>
       <c r="AN335" s="83"/>
     </row>
-    <row r="336" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A336" s="3" t="s">
         <v>275</v>
       </c>
@@ -44325,7 +44321,7 @@
       <c r="AM336" s="1"/>
       <c r="AN336" s="83"/>
     </row>
-    <row r="337" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A337" s="22" t="s">
         <v>892</v>
       </c>
@@ -44416,7 +44412,7 @@
       <c r="AM337" s="1"/>
       <c r="AN337" s="83"/>
     </row>
-    <row r="338" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A338" s="3" t="s">
         <v>664</v>
       </c>
@@ -44499,7 +44495,7 @@
       <c r="AM338" s="1"/>
       <c r="AN338" s="83"/>
     </row>
-    <row r="339" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A339" s="22" t="s">
         <v>895</v>
       </c>
@@ -44582,7 +44578,7 @@
       <c r="AM339" s="1"/>
       <c r="AN339" s="83"/>
     </row>
-    <row r="340" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A340" s="3" t="s">
         <v>898</v>
       </c>
@@ -44665,7 +44661,7 @@
       <c r="AM340" s="1"/>
       <c r="AN340" s="83"/>
     </row>
-    <row r="341" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A341" s="22" t="s">
         <v>900</v>
       </c>
@@ -44748,7 +44744,7 @@
       <c r="AM341" s="1"/>
       <c r="AN341" s="83"/>
     </row>
-    <row r="342" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A342" s="22" t="s">
         <v>902</v>
       </c>
@@ -44831,7 +44827,7 @@
       <c r="AM342" s="1"/>
       <c r="AN342" s="83"/>
     </row>
-    <row r="343" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A343" s="3" t="s">
         <v>904</v>
       </c>
@@ -44920,7 +44916,7 @@
       <c r="AM343" s="1"/>
       <c r="AN343" s="83"/>
     </row>
-    <row r="344" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A344" s="22" t="s">
         <v>905</v>
       </c>
@@ -45007,7 +45003,7 @@
       <c r="AM344" s="1"/>
       <c r="AN344" s="83"/>
     </row>
-    <row r="345" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A345" s="3" t="s">
         <v>907</v>
       </c>
@@ -45094,7 +45090,7 @@
       <c r="AM345" s="1"/>
       <c r="AN345" s="83"/>
     </row>
-    <row r="346" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A346" s="3" t="s">
         <v>655</v>
       </c>
@@ -45181,7 +45177,7 @@
       <c r="AM346" s="1"/>
       <c r="AN346" s="83"/>
     </row>
-    <row r="347" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A347" s="22" t="s">
         <v>909</v>
       </c>
@@ -45260,7 +45256,7 @@
       <c r="AM347" s="1"/>
       <c r="AN347" s="83"/>
     </row>
-    <row r="348" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A348" s="3" t="s">
         <v>912</v>
       </c>
@@ -45347,7 +45343,7 @@
       <c r="AM348" s="1"/>
       <c r="AN348" s="83"/>
     </row>
-    <row r="349" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A349" s="22" t="s">
         <v>913</v>
       </c>
@@ -45434,7 +45430,7 @@
       <c r="AM349" s="1"/>
       <c r="AN349" s="83"/>
     </row>
-    <row r="350" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A350" s="3" t="s">
         <v>915</v>
       </c>
@@ -45517,7 +45513,7 @@
       <c r="AM350" s="1"/>
       <c r="AN350" s="83"/>
     </row>
-    <row r="351" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A351" s="22" t="s">
         <v>917</v>
       </c>
@@ -45608,7 +45604,7 @@
       <c r="AM351" s="1"/>
       <c r="AN351" s="83"/>
     </row>
-    <row r="352" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A352" s="22" t="s">
         <v>918</v>
       </c>
@@ -45691,7 +45687,7 @@
       <c r="AM352" s="1"/>
       <c r="AN352" s="83"/>
     </row>
-    <row r="353" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A353" s="3" t="s">
         <v>920</v>
       </c>
@@ -45778,7 +45774,7 @@
       <c r="AM353" s="1"/>
       <c r="AN353" s="83"/>
     </row>
-    <row r="354" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A354" s="3" t="s">
         <v>921</v>
       </c>
@@ -45861,7 +45857,7 @@
       <c r="AM354" s="1"/>
       <c r="AN354" s="83"/>
     </row>
-    <row r="355" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A355" s="22" t="s">
         <v>922</v>
       </c>
@@ -45952,7 +45948,7 @@
       <c r="AM355" s="1"/>
       <c r="AN355" s="83"/>
     </row>
-    <row r="356" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A356" s="3" t="s">
         <v>394</v>
       </c>
@@ -46035,7 +46031,7 @@
       <c r="AM356" s="1"/>
       <c r="AN356" s="83"/>
     </row>
-    <row r="357" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A357" s="22" t="s">
         <v>923</v>
       </c>
@@ -46118,7 +46114,7 @@
       <c r="AM357" s="1"/>
       <c r="AN357" s="83"/>
     </row>
-    <row r="358" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A358" s="22" t="s">
         <v>927</v>
       </c>
@@ -46201,7 +46197,7 @@
       <c r="AM358" s="1"/>
       <c r="AN358" s="83"/>
     </row>
-    <row r="359" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A359" s="3" t="s">
         <v>928</v>
       </c>
@@ -46288,7 +46284,7 @@
       <c r="AM359" s="1"/>
       <c r="AN359" s="83"/>
     </row>
-    <row r="360" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A360" s="22" t="s">
         <v>929</v>
       </c>
@@ -46379,7 +46375,7 @@
       <c r="AM360" s="1"/>
       <c r="AN360" s="83"/>
     </row>
-    <row r="361" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A361" s="3" t="s">
         <v>370</v>
       </c>
@@ -46462,7 +46458,7 @@
       <c r="AM361" s="1"/>
       <c r="AN361" s="83"/>
     </row>
-    <row r="362" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A362" s="3" t="s">
         <v>930</v>
       </c>
@@ -46549,7 +46545,7 @@
       <c r="AM362" s="1"/>
       <c r="AN362" s="83"/>
     </row>
-    <row r="363" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A363" s="22" t="s">
         <v>932</v>
       </c>
@@ -46632,7 +46628,7 @@
       <c r="AM363" s="1"/>
       <c r="AN363" s="83"/>
     </row>
-    <row r="364" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A364" s="3" t="s">
         <v>659</v>
       </c>
@@ -46715,7 +46711,7 @@
       <c r="AM364" s="1"/>
       <c r="AN364" s="83"/>
     </row>
-    <row r="365" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A365" s="22" t="s">
         <v>933</v>
       </c>
@@ -46798,7 +46794,7 @@
       <c r="AM365" s="1"/>
       <c r="AN365" s="83"/>
     </row>
-    <row r="366" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A366" s="3" t="s">
         <v>934</v>
       </c>
@@ -46881,7 +46877,7 @@
       <c r="AM366" s="1"/>
       <c r="AN366" s="83"/>
     </row>
-    <row r="367" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A367" s="3" t="s">
         <v>740</v>
       </c>
@@ -46964,7 +46960,7 @@
       <c r="AM367" s="1"/>
       <c r="AN367" s="83"/>
     </row>
-    <row r="368" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A368" s="3" t="s">
         <v>674</v>
       </c>
@@ -47047,7 +47043,7 @@
       <c r="AM368" s="1"/>
       <c r="AN368" s="83"/>
     </row>
-    <row r="369" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A369" s="3" t="s">
         <v>938</v>
       </c>
@@ -47130,7 +47126,7 @@
       <c r="AM369" s="1"/>
       <c r="AN369" s="83"/>
     </row>
-    <row r="370" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A370" s="22" t="s">
         <v>940</v>
       </c>
@@ -47213,7 +47209,7 @@
       <c r="AM370" s="1"/>
       <c r="AN370" s="83"/>
     </row>
-    <row r="371" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A371" s="22" t="s">
         <v>943</v>
       </c>
@@ -47296,7 +47292,7 @@
       <c r="AM371" s="1"/>
       <c r="AN371" s="83"/>
     </row>
-    <row r="372" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A372" s="22" t="s">
         <v>945</v>
       </c>
@@ -47379,7 +47375,7 @@
       <c r="AM372" s="1"/>
       <c r="AN372" s="83"/>
     </row>
-    <row r="373" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A373" s="3" t="s">
         <v>946</v>
       </c>
@@ -47462,7 +47458,7 @@
       <c r="AM373" s="1"/>
       <c r="AN373" s="83"/>
     </row>
-    <row r="374" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A374" s="3" t="s">
         <v>948</v>
       </c>
@@ -47545,7 +47541,7 @@
       <c r="AM374" s="1"/>
       <c r="AN374" s="83"/>
     </row>
-    <row r="375" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A375" s="22" t="s">
         <v>949</v>
       </c>
@@ -47628,7 +47624,7 @@
       <c r="AM375" s="1"/>
       <c r="AN375" s="83"/>
     </row>
-    <row r="376" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A376" s="3" t="s">
         <v>950</v>
       </c>
@@ -47711,7 +47707,7 @@
       <c r="AM376" s="1"/>
       <c r="AN376" s="83"/>
     </row>
-    <row r="377" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A377" s="22" t="s">
         <v>951</v>
       </c>
@@ -47794,7 +47790,7 @@
       <c r="AM377" s="1"/>
       <c r="AN377" s="83"/>
     </row>
-    <row r="378" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A378" s="22" t="s">
         <v>953</v>
       </c>
@@ -47877,7 +47873,7 @@
       <c r="AM378" s="1"/>
       <c r="AN378" s="83"/>
     </row>
-    <row r="379" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A379" s="22" t="s">
         <v>956</v>
       </c>
@@ -47960,7 +47956,7 @@
       <c r="AM379" s="1"/>
       <c r="AN379" s="83"/>
     </row>
-    <row r="380" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A380" s="22" t="s">
         <v>958</v>
       </c>
@@ -48043,7 +48039,7 @@
       <c r="AM380" s="1"/>
       <c r="AN380" s="83"/>
     </row>
-    <row r="381" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A381" s="22" t="s">
         <v>962</v>
       </c>
@@ -48130,7 +48126,7 @@
       <c r="AM381" s="1"/>
       <c r="AN381" s="83"/>
     </row>
-    <row r="382" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A382" s="3" t="s">
         <v>964</v>
       </c>
@@ -48209,7 +48205,7 @@
       <c r="AM382" s="1"/>
       <c r="AN382" s="83"/>
     </row>
-    <row r="383" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A383" s="22" t="s">
         <v>966</v>
       </c>
@@ -48292,7 +48288,7 @@
       <c r="AM383" s="1"/>
       <c r="AN383" s="83"/>
     </row>
-    <row r="384" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A384" s="22" t="s">
         <v>323</v>
       </c>
@@ -48375,7 +48371,7 @@
       <c r="AM384" s="1"/>
       <c r="AN384" s="83"/>
     </row>
-    <row r="385" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A385" s="3" t="s">
         <v>967</v>
       </c>
@@ -48462,7 +48458,7 @@
       <c r="AM385" s="1"/>
       <c r="AN385" s="83"/>
     </row>
-    <row r="386" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A386" s="22" t="s">
         <v>471</v>
       </c>
@@ -48545,7 +48541,7 @@
       <c r="AM386" s="1"/>
       <c r="AN386" s="83"/>
     </row>
-    <row r="387" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A387" s="22" t="s">
         <v>316</v>
       </c>
@@ -48628,7 +48624,7 @@
       <c r="AM387" s="1"/>
       <c r="AN387" s="83"/>
     </row>
-    <row r="388" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A388" s="3" t="s">
         <v>971</v>
       </c>
@@ -48711,7 +48707,7 @@
       <c r="AM388" s="1"/>
       <c r="AN388" s="83"/>
     </row>
-    <row r="389" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A389" s="22" t="s">
         <v>972</v>
       </c>
@@ -48802,7 +48798,7 @@
       <c r="AM389" s="1"/>
       <c r="AN389" s="83"/>
     </row>
-    <row r="390" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A390" s="22" t="s">
         <v>973</v>
       </c>
@@ -48893,7 +48889,7 @@
       <c r="AM390" s="1"/>
       <c r="AN390" s="83"/>
     </row>
-    <row r="391" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A391" s="22" t="s">
         <v>974</v>
       </c>
@@ -48976,7 +48972,7 @@
       <c r="AM391" s="1"/>
       <c r="AN391" s="83"/>
     </row>
-    <row r="392" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A392" s="22" t="s">
         <v>975</v>
       </c>
@@ -49059,7 +49055,7 @@
       <c r="AM392" s="1"/>
       <c r="AN392" s="83"/>
     </row>
-    <row r="393" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A393" s="22" t="s">
         <v>977</v>
       </c>
@@ -49150,7 +49146,7 @@
       <c r="AM393" s="1"/>
       <c r="AN393" s="83"/>
     </row>
-    <row r="394" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A394" s="22" t="s">
         <v>446</v>
       </c>
@@ -49233,7 +49229,7 @@
       <c r="AM394" s="1"/>
       <c r="AN394" s="83"/>
     </row>
-    <row r="395" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A395" s="22" t="s">
         <v>979</v>
       </c>
@@ -49324,7 +49320,7 @@
       <c r="AM395" s="1"/>
       <c r="AN395" s="83"/>
     </row>
-    <row r="396" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A396" s="22" t="s">
         <v>482</v>
       </c>
@@ -49407,7 +49403,7 @@
       <c r="AM396" s="1"/>
       <c r="AN396" s="83"/>
     </row>
-    <row r="397" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A397" s="22" t="s">
         <v>982</v>
       </c>
@@ -49490,7 +49486,7 @@
       <c r="AM397" s="1"/>
       <c r="AN397" s="83"/>
     </row>
-    <row r="398" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A398" s="22" t="s">
         <v>983</v>
       </c>
@@ -49573,7 +49569,7 @@
       <c r="AM398" s="1"/>
       <c r="AN398" s="83"/>
     </row>
-    <row r="399" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A399" s="22" t="s">
         <v>985</v>
       </c>
@@ -49656,7 +49652,7 @@
       <c r="AM399" s="1"/>
       <c r="AN399" s="83"/>
     </row>
-    <row r="400" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A400" s="3" t="s">
         <v>986</v>
       </c>
@@ -49739,7 +49735,7 @@
       <c r="AM400" s="1"/>
       <c r="AN400" s="83"/>
     </row>
-    <row r="401" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A401" s="3" t="s">
         <v>987</v>
       </c>
@@ -49826,7 +49822,7 @@
       <c r="AM401" s="1"/>
       <c r="AN401" s="83"/>
     </row>
-    <row r="402" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A402" s="22" t="s">
         <v>988</v>
       </c>
@@ -49909,7 +49905,7 @@
       <c r="AM402" s="1"/>
       <c r="AN402" s="83"/>
     </row>
-    <row r="403" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A403" s="22" t="s">
         <v>989</v>
       </c>
@@ -49992,7 +49988,7 @@
       <c r="AM403" s="1"/>
       <c r="AN403" s="83"/>
     </row>
-    <row r="404" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A404" s="22" t="s">
         <v>992</v>
       </c>
@@ -50081,7 +50077,7 @@
       <c r="AM404" s="1"/>
       <c r="AN404" s="83"/>
     </row>
-    <row r="405" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A405" s="22" t="s">
         <v>993</v>
       </c>
@@ -50172,7 +50168,7 @@
       <c r="AM405" s="1"/>
       <c r="AN405" s="83"/>
     </row>
-    <row r="406" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A406" s="3" t="s">
         <v>995</v>
       </c>
@@ -50259,7 +50255,7 @@
       <c r="AM406" s="1"/>
       <c r="AN406" s="83"/>
     </row>
-    <row r="407" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A407" s="22" t="s">
         <v>997</v>
       </c>
@@ -50350,7 +50346,7 @@
       <c r="AM407" s="1"/>
       <c r="AN407" s="83"/>
     </row>
-    <row r="408" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A408" s="22" t="s">
         <v>999</v>
       </c>
@@ -50433,7 +50429,7 @@
       <c r="AM408" s="1"/>
       <c r="AN408" s="83"/>
     </row>
-    <row r="409" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A409" s="22" t="s">
         <v>1001</v>
       </c>
@@ -50516,7 +50512,7 @@
       <c r="AM409" s="1"/>
       <c r="AN409" s="83"/>
     </row>
-    <row r="410" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A410" s="22" t="s">
         <v>1003</v>
       </c>
@@ -50599,7 +50595,7 @@
       <c r="AM410" s="1"/>
       <c r="AN410" s="83"/>
     </row>
-    <row r="411" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A411" s="22" t="s">
         <v>414</v>
       </c>
@@ -50682,7 +50678,7 @@
       <c r="AM411" s="1"/>
       <c r="AN411" s="83"/>
     </row>
-    <row r="412" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A412" s="22" t="s">
         <v>1005</v>
       </c>
@@ -50765,7 +50761,7 @@
       <c r="AM412" s="1"/>
       <c r="AN412" s="83"/>
     </row>
-    <row r="413" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A413" s="22" t="s">
         <v>1006</v>
       </c>
@@ -50848,7 +50844,7 @@
       <c r="AM413" s="1"/>
       <c r="AN413" s="83"/>
     </row>
-    <row r="414" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A414" s="22" t="s">
         <v>1008</v>
       </c>
@@ -50931,7 +50927,7 @@
       <c r="AM414" s="1"/>
       <c r="AN414" s="83"/>
     </row>
-    <row r="415" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A415" s="22" t="s">
         <v>1010</v>
       </c>
@@ -51020,7 +51016,7 @@
       <c r="AM415" s="1"/>
       <c r="AN415" s="83"/>
     </row>
-    <row r="416" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A416" s="22" t="s">
         <v>1011</v>
       </c>
@@ -51111,7 +51107,7 @@
       <c r="AM416" s="1"/>
       <c r="AN416" s="83"/>
     </row>
-    <row r="417" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A417" s="22" t="s">
         <v>1012</v>
       </c>
@@ -51202,7 +51198,7 @@
       <c r="AM417" s="1"/>
       <c r="AN417" s="83"/>
     </row>
-    <row r="418" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A418" s="22" t="s">
         <v>1013</v>
       </c>
@@ -51291,7 +51287,7 @@
       <c r="AM418" s="1"/>
       <c r="AN418" s="83"/>
     </row>
-    <row r="419" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A419" s="22" t="s">
         <v>1014</v>
       </c>
@@ -51382,7 +51378,7 @@
       <c r="AM419" s="1"/>
       <c r="AN419" s="83"/>
     </row>
-    <row r="420" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A420" s="22" t="s">
         <v>1015</v>
       </c>
@@ -51465,7 +51461,7 @@
       <c r="AM420" s="1"/>
       <c r="AN420" s="83"/>
     </row>
-    <row r="421" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A421" s="22" t="s">
         <v>1017</v>
       </c>
@@ -51548,7 +51544,7 @@
       <c r="AM421" s="1"/>
       <c r="AN421" s="83"/>
     </row>
-    <row r="422" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A422" s="22" t="s">
         <v>1019</v>
       </c>
@@ -51631,7 +51627,7 @@
       <c r="AM422" s="1"/>
       <c r="AN422" s="83"/>
     </row>
-    <row r="423" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A423" s="22" t="s">
         <v>1021</v>
       </c>
@@ -51714,7 +51710,7 @@
       <c r="AM423" s="1"/>
       <c r="AN423" s="83"/>
     </row>
-    <row r="424" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A424" s="22" t="s">
         <v>1024</v>
       </c>
@@ -51797,7 +51793,7 @@
       <c r="AM424" s="1"/>
       <c r="AN424" s="83"/>
     </row>
-    <row r="425" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A425" s="22" t="s">
         <v>1026</v>
       </c>
@@ -51880,7 +51876,7 @@
       <c r="AM425" s="1"/>
       <c r="AN425" s="83"/>
     </row>
-    <row r="426" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A426" s="22" t="s">
         <v>1028</v>
       </c>
@@ -51963,7 +51959,7 @@
       <c r="AM426" s="1"/>
       <c r="AN426" s="83"/>
     </row>
-    <row r="427" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A427" s="22" t="s">
         <v>1029</v>
       </c>
@@ -52046,7 +52042,7 @@
       <c r="AM427" s="1"/>
       <c r="AN427" s="83"/>
     </row>
-    <row r="428" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A428" s="22" t="s">
         <v>1030</v>
       </c>
@@ -52129,7 +52125,7 @@
       <c r="AM428" s="1"/>
       <c r="AN428" s="83"/>
     </row>
-    <row r="429" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A429" s="22" t="s">
         <v>1032</v>
       </c>
@@ -52212,7 +52208,7 @@
       <c r="AM429" s="1"/>
       <c r="AN429" s="83"/>
     </row>
-    <row r="430" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A430" s="22" t="s">
         <v>1034</v>
       </c>
@@ -52295,7 +52291,7 @@
       <c r="AM430" s="1"/>
       <c r="AN430" s="83"/>
     </row>
-    <row r="431" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A431" s="22" t="s">
         <v>1036</v>
       </c>
@@ -52378,7 +52374,7 @@
       <c r="AM431" s="1"/>
       <c r="AN431" s="83"/>
     </row>
-    <row r="432" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A432" s="22" t="s">
         <v>642</v>
       </c>
@@ -52461,7 +52457,7 @@
       <c r="AM432" s="1"/>
       <c r="AN432" s="83"/>
     </row>
-    <row r="433" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A433" s="22" t="s">
         <v>1041</v>
       </c>
@@ -52544,7 +52540,7 @@
       <c r="AM433" s="1"/>
       <c r="AN433" s="83"/>
     </row>
-    <row r="434" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A434" s="22" t="s">
         <v>1043</v>
       </c>
@@ -52627,7 +52623,7 @@
       <c r="AM434" s="1"/>
       <c r="AN434" s="83"/>
     </row>
-    <row r="435" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A435" s="22" t="s">
         <v>1044</v>
       </c>
@@ -52710,7 +52706,7 @@
       <c r="AM435" s="1"/>
       <c r="AN435" s="83"/>
     </row>
-    <row r="436" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A436" s="22" t="s">
         <v>1046</v>
       </c>
@@ -52793,7 +52789,7 @@
       <c r="AM436" s="1"/>
       <c r="AN436" s="83"/>
     </row>
-    <row r="437" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A437" s="22" t="s">
         <v>1048</v>
       </c>
@@ -52876,7 +52872,7 @@
       <c r="AM437" s="1"/>
       <c r="AN437" s="83"/>
     </row>
-    <row r="438" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A438" s="22" t="s">
         <v>398</v>
       </c>
@@ -52959,7 +52955,7 @@
       <c r="AM438" s="1"/>
       <c r="AN438" s="83"/>
     </row>
-    <row r="439" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A439" s="22" t="s">
         <v>745</v>
       </c>
@@ -53042,7 +53038,7 @@
       <c r="AM439" s="1"/>
       <c r="AN439" s="83"/>
     </row>
-    <row r="440" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A440" s="22" t="s">
         <v>1053</v>
       </c>
@@ -53125,7 +53121,7 @@
       <c r="AM440" s="1"/>
       <c r="AN440" s="83"/>
     </row>
-    <row r="441" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A441" s="22" t="s">
         <v>1054</v>
       </c>
@@ -53208,7 +53204,7 @@
       <c r="AM441" s="1"/>
       <c r="AN441" s="83"/>
     </row>
-    <row r="442" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A442" s="22" t="s">
         <v>1055</v>
       </c>
@@ -53291,7 +53287,7 @@
       <c r="AM442" s="1"/>
       <c r="AN442" s="83"/>
     </row>
-    <row r="443" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A443" s="22" t="s">
         <v>1057</v>
       </c>
@@ -53374,7 +53370,7 @@
       <c r="AM443" s="1"/>
       <c r="AN443" s="83"/>
     </row>
-    <row r="444" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A444" s="22" t="s">
         <v>1059</v>
       </c>
@@ -53457,7 +53453,7 @@
       <c r="AM444" s="1"/>
       <c r="AN444" s="83"/>
     </row>
-    <row r="445" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A445" s="22" t="s">
         <v>1062</v>
       </c>
@@ -53540,7 +53536,7 @@
       <c r="AM445" s="1"/>
       <c r="AN445" s="83"/>
     </row>
-    <row r="446" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A446" s="22" t="s">
         <v>1063</v>
       </c>
@@ -53623,7 +53619,7 @@
       <c r="AM446" s="1"/>
       <c r="AN446" s="83"/>
     </row>
-    <row r="447" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A447" s="3" t="s">
         <v>653</v>
       </c>
@@ -53698,7 +53694,7 @@
       <c r="AM447" s="1"/>
       <c r="AN447" s="83"/>
     </row>
-    <row r="448" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A448" s="3" t="s">
         <v>1064</v>
       </c>
@@ -53781,7 +53777,7 @@
       <c r="AM448" s="1"/>
       <c r="AN448" s="83"/>
     </row>
-    <row r="449" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A449" s="3" t="s">
         <v>1065</v>
       </c>
@@ -53864,7 +53860,7 @@
       <c r="AM449" s="1"/>
       <c r="AN449" s="83"/>
     </row>
-    <row r="450" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A450" s="3" t="s">
         <v>1066</v>
       </c>
@@ -53947,7 +53943,7 @@
       <c r="AM450" s="1"/>
       <c r="AN450" s="83"/>
     </row>
-    <row r="451" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A451" s="3" t="s">
         <v>1067</v>
       </c>
@@ -54030,7 +54026,7 @@
       <c r="AM451" s="1"/>
       <c r="AN451" s="83"/>
     </row>
-    <row r="452" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A452" s="3" t="s">
         <v>1068</v>
       </c>
@@ -54113,7 +54109,7 @@
       <c r="AM452" s="1"/>
       <c r="AN452" s="83"/>
     </row>
-    <row r="453" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A453" s="3" t="s">
         <v>1069</v>
       </c>
@@ -54196,7 +54192,7 @@
       <c r="AM453" s="1"/>
       <c r="AN453" s="83"/>
     </row>
-    <row r="454" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A454" s="3" t="s">
         <v>1070</v>
       </c>
@@ -54279,7 +54275,7 @@
       <c r="AM454" s="1"/>
       <c r="AN454" s="83"/>
     </row>
-    <row r="455" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A455" s="3" t="s">
         <v>1071</v>
       </c>
@@ -54362,7 +54358,7 @@
       <c r="AM455" s="1"/>
       <c r="AN455" s="83"/>
     </row>
-    <row r="456" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A456" s="3" t="s">
         <v>1072</v>
       </c>
@@ -54445,7 +54441,7 @@
       <c r="AM456" s="1"/>
       <c r="AN456" s="83"/>
     </row>
-    <row r="457" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A457" s="3" t="s">
         <v>1074</v>
       </c>
@@ -54528,7 +54524,7 @@
       <c r="AM457" s="1"/>
       <c r="AN457" s="83"/>
     </row>
-    <row r="458" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A458" s="3" t="s">
         <v>1075</v>
       </c>
@@ -54611,7 +54607,7 @@
       <c r="AM458" s="1"/>
       <c r="AN458" s="83"/>
     </row>
-    <row r="459" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A459" s="3" t="s">
         <v>1076</v>
       </c>
@@ -54694,7 +54690,7 @@
       <c r="AM459" s="1"/>
       <c r="AN459" s="83"/>
     </row>
-    <row r="460" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A460" s="3" t="s">
         <v>1078</v>
       </c>
@@ -54777,7 +54773,7 @@
       <c r="AM460" s="1"/>
       <c r="AN460" s="83"/>
     </row>
-    <row r="461" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A461" s="3" t="s">
         <v>1079</v>
       </c>
@@ -54860,7 +54856,7 @@
       <c r="AM461" s="1"/>
       <c r="AN461" s="83"/>
     </row>
-    <row r="462" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A462" s="3" t="s">
         <v>1080</v>
       </c>
@@ -54943,7 +54939,7 @@
       <c r="AM462" s="1"/>
       <c r="AN462" s="83"/>
     </row>
-    <row r="463" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A463" s="3" t="s">
         <v>1081</v>
       </c>
@@ -55030,7 +55026,7 @@
       <c r="AM463" s="1"/>
       <c r="AN463" s="83"/>
     </row>
-    <row r="464" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A464" s="3" t="s">
         <v>1082</v>
       </c>
@@ -55113,7 +55109,7 @@
       <c r="AM464" s="1"/>
       <c r="AN464" s="83"/>
     </row>
-    <row r="465" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A465" s="3" t="s">
         <v>1083</v>
       </c>
@@ -55196,7 +55192,7 @@
       <c r="AM465" s="1"/>
       <c r="AN465" s="83"/>
     </row>
-    <row r="466" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A466" s="3" t="s">
         <v>1084</v>
       </c>
@@ -55279,7 +55275,7 @@
       <c r="AM466" s="1"/>
       <c r="AN466" s="83"/>
     </row>
-    <row r="467" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A467" s="3" t="s">
         <v>1086</v>
       </c>
@@ -55362,7 +55358,7 @@
       <c r="AM467" s="1"/>
       <c r="AN467" s="83"/>
     </row>
-    <row r="468" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A468" s="3" t="s">
         <v>1088</v>
       </c>
@@ -55445,7 +55441,7 @@
       <c r="AM468" s="1"/>
       <c r="AN468" s="83"/>
     </row>
-    <row r="469" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A469" s="3" t="s">
         <v>1090</v>
       </c>
@@ -55528,7 +55524,7 @@
       <c r="AM469" s="1"/>
       <c r="AN469" s="83"/>
     </row>
-    <row r="470" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A470" s="3" t="s">
         <v>1091</v>
       </c>
@@ -55611,7 +55607,7 @@
       <c r="AM470" s="1"/>
       <c r="AN470" s="83"/>
     </row>
-    <row r="471" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A471" s="3" t="s">
         <v>1092</v>
       </c>
@@ -55694,7 +55690,7 @@
       <c r="AM471" s="1"/>
       <c r="AN471" s="83"/>
     </row>
-    <row r="472" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A472" s="3" t="s">
         <v>1093</v>
       </c>
@@ -55777,7 +55773,7 @@
       <c r="AM472" s="1"/>
       <c r="AN472" s="83"/>
     </row>
-    <row r="473" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A473" s="3" t="s">
         <v>1095</v>
       </c>
@@ -55860,7 +55856,7 @@
       <c r="AM473" s="1"/>
       <c r="AN473" s="83"/>
     </row>
-    <row r="474" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A474" s="3" t="s">
         <v>1097</v>
       </c>
@@ -55943,7 +55939,7 @@
       <c r="AM474" s="1"/>
       <c r="AN474" s="83"/>
     </row>
-    <row r="475" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A475" s="3" t="s">
         <v>1099</v>
       </c>
@@ -56026,7 +56022,7 @@
       <c r="AM475" s="1"/>
       <c r="AN475" s="83"/>
     </row>
-    <row r="476" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A476" s="3" t="s">
         <v>1101</v>
       </c>
@@ -56109,7 +56105,7 @@
       <c r="AM476" s="1"/>
       <c r="AN476" s="83"/>
     </row>
-    <row r="477" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A477" s="3" t="s">
         <v>1103</v>
       </c>
@@ -56196,7 +56192,7 @@
       <c r="AM477" s="1"/>
       <c r="AN477" s="83"/>
     </row>
-    <row r="478" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A478" s="3" t="s">
         <v>1104</v>
       </c>
@@ -56283,7 +56279,7 @@
       <c r="AM478" s="1"/>
       <c r="AN478" s="83"/>
     </row>
-    <row r="479" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A479" s="3" t="s">
         <v>1105</v>
       </c>
@@ -56370,7 +56366,7 @@
       <c r="AM479" s="1"/>
       <c r="AN479" s="83"/>
     </row>
-    <row r="480" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A480" s="3" t="s">
         <v>1106</v>
       </c>
@@ -56453,7 +56449,7 @@
       <c r="AM480" s="1"/>
       <c r="AN480" s="83"/>
     </row>
-    <row r="481" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A481" s="3" t="s">
         <v>1108</v>
       </c>
@@ -56536,7 +56532,7 @@
       <c r="AM481" s="1"/>
       <c r="AN481" s="83"/>
     </row>
-    <row r="482" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A482" s="3" t="s">
         <v>1109</v>
       </c>
@@ -56619,7 +56615,7 @@
       <c r="AM482" s="1"/>
       <c r="AN482" s="83"/>
     </row>
-    <row r="483" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A483" s="3" t="s">
         <v>1110</v>
       </c>
@@ -56706,7 +56702,7 @@
       <c r="AM483" s="1"/>
       <c r="AN483" s="83"/>
     </row>
-    <row r="484" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A484" s="3" t="s">
         <v>1111</v>
       </c>
@@ -56793,7 +56789,7 @@
       <c r="AM484" s="1"/>
       <c r="AN484" s="83"/>
     </row>
-    <row r="485" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A485" s="3" t="s">
         <v>1112</v>
       </c>
@@ -56876,7 +56872,7 @@
       <c r="AM485" s="1"/>
       <c r="AN485" s="83"/>
     </row>
-    <row r="486" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A486" s="22" t="s">
         <v>1114</v>
       </c>
@@ -56959,7 +56955,7 @@
       <c r="AM486" s="1"/>
       <c r="AN486" s="83"/>
     </row>
-    <row r="487" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A487" s="22" t="s">
         <v>1115</v>
       </c>
@@ -57042,7 +57038,7 @@
       <c r="AM487" s="1"/>
       <c r="AN487" s="83"/>
     </row>
-    <row r="488" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A488" s="22" t="s">
         <v>1117</v>
       </c>
@@ -57125,7 +57121,7 @@
       <c r="AM488" s="1"/>
       <c r="AN488" s="83"/>
     </row>
-    <row r="489" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A489" s="22" t="s">
         <v>1118</v>
       </c>
@@ -57208,7 +57204,7 @@
       <c r="AM489" s="1"/>
       <c r="AN489" s="83"/>
     </row>
-    <row r="490" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A490" s="22" t="s">
         <v>1119</v>
       </c>
@@ -57291,7 +57287,7 @@
       <c r="AM490" s="1"/>
       <c r="AN490" s="83"/>
     </row>
-    <row r="491" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A491" s="22" t="s">
         <v>1120</v>
       </c>
@@ -57382,7 +57378,7 @@
       <c r="AM491" s="1"/>
       <c r="AN491" s="83"/>
     </row>
-    <row r="492" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A492" s="22" t="s">
         <v>453</v>
       </c>
@@ -57461,7 +57457,7 @@
       <c r="AM492" s="1"/>
       <c r="AN492" s="83"/>
     </row>
-    <row r="493" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A493" s="22" t="s">
         <v>1123</v>
       </c>
@@ -57530,7 +57526,7 @@
       <c r="AM493" s="1"/>
       <c r="AN493" s="83"/>
     </row>
-    <row r="494" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A494" s="22" t="s">
         <v>1125</v>
       </c>
@@ -57599,7 +57595,7 @@
       <c r="AM494" s="1"/>
       <c r="AN494" s="83"/>
     </row>
-    <row r="495" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A495" s="22" t="s">
         <v>1126</v>
       </c>
@@ -57668,7 +57664,7 @@
       <c r="AM495" s="1"/>
       <c r="AN495" s="83"/>
     </row>
-    <row r="496" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A496" s="22" t="s">
         <v>1127</v>
       </c>
@@ -57737,7 +57733,7 @@
       <c r="AM496" s="1"/>
       <c r="AN496" s="83"/>
     </row>
-    <row r="497" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:41" s="26" customFormat="1" hidden="1">
       <c r="A497" s="22" t="s">
         <v>1128</v>
       </c>
@@ -57806,7 +57802,7 @@
       <c r="AM497" s="1"/>
       <c r="AN497" s="83"/>
     </row>
-    <row r="498" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:41" s="26" customFormat="1" ht="20.45">
       <c r="A498" s="19" t="s">
         <v>1129</v>
       </c>
@@ -57921,7 +57917,7 @@
       </c>
       <c r="AO498" s="81"/>
     </row>
-    <row r="499" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:41" s="26" customFormat="1">
       <c r="A499" s="19" t="s">
         <v>1136</v>
       </c>
@@ -58036,7 +58032,7 @@
       </c>
       <c r="AO499" s="81"/>
     </row>
-    <row r="500" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:41" s="26" customFormat="1">
       <c r="A500" s="19" t="s">
         <v>1141</v>
       </c>
@@ -58149,7 +58145,7 @@
       </c>
       <c r="AO500" s="81"/>
     </row>
-    <row r="501" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:41" s="26" customFormat="1">
       <c r="A501" s="19" t="s">
         <v>1147</v>
       </c>
@@ -58264,7 +58260,7 @@
       </c>
       <c r="AO501" s="81"/>
     </row>
-    <row r="502" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:41" s="26" customFormat="1" ht="20.45">
       <c r="A502" s="19" t="s">
         <v>1150</v>
       </c>
@@ -58379,7 +58375,7 @@
       </c>
       <c r="AO502" s="81"/>
     </row>
-    <row r="503" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:41" s="26" customFormat="1">
       <c r="A503" s="19" t="s">
         <v>1154</v>
       </c>
@@ -58494,7 +58490,7 @@
       </c>
       <c r="AO503" s="81"/>
     </row>
-    <row r="504" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:41" s="26" customFormat="1">
       <c r="A504" s="19" t="s">
         <v>1158</v>
       </c>
@@ -58596,7 +58592,7 @@
       <c r="AN504" s="83"/>
       <c r="AO504" s="81"/>
     </row>
-    <row r="505" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:41" s="26" customFormat="1">
       <c r="A505" s="19" t="s">
         <v>1162</v>
       </c>
@@ -58711,7 +58707,7 @@
       </c>
       <c r="AO505" s="81"/>
     </row>
-    <row r="506" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:41" s="26" customFormat="1">
       <c r="A506" s="19" t="s">
         <v>1166</v>
       </c>
@@ -58826,7 +58822,7 @@
       </c>
       <c r="AO506" s="81"/>
     </row>
-    <row r="507" spans="1:41" s="26" customFormat="1" ht="30.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:41" s="26" customFormat="1" ht="30.6">
       <c r="A507" s="19" t="s">
         <v>1169</v>
       </c>
@@ -58941,7 +58937,7 @@
       </c>
       <c r="AO507" s="81"/>
     </row>
-    <row r="508" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:41" s="26" customFormat="1">
       <c r="A508" s="19" t="s">
         <v>1172</v>
       </c>
@@ -59046,7 +59042,7 @@
       <c r="AN508" s="83"/>
       <c r="AO508" s="81"/>
     </row>
-    <row r="509" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:41" s="26" customFormat="1">
       <c r="A509" s="19" t="s">
         <v>1174</v>
       </c>
@@ -59161,7 +59157,7 @@
       </c>
       <c r="AO509" s="81"/>
     </row>
-    <row r="510" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:41" s="26" customFormat="1">
       <c r="A510" s="19" t="s">
         <v>1177</v>
       </c>
@@ -59267,7 +59263,7 @@
       </c>
       <c r="AO510" s="81"/>
     </row>
-    <row r="511" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:41" s="26" customFormat="1">
       <c r="A511" s="19" t="s">
         <v>1179</v>
       </c>
@@ -59370,7 +59366,7 @@
       <c r="AN511" s="83"/>
       <c r="AO511" s="81"/>
     </row>
-    <row r="512" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:41" s="26" customFormat="1">
       <c r="A512" s="19" t="s">
         <v>1181</v>
       </c>
@@ -59485,7 +59481,7 @@
       </c>
       <c r="AO512" s="81"/>
     </row>
-    <row r="513" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:41" s="26" customFormat="1" ht="20.45">
       <c r="A513" s="19" t="s">
         <v>1184</v>
       </c>
@@ -59600,7 +59596,7 @@
       </c>
       <c r="AO513" s="81"/>
     </row>
-    <row r="514" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:41" s="26" customFormat="1">
       <c r="A514" s="19" t="s">
         <v>1187</v>
       </c>
@@ -59715,7 +59711,7 @@
       </c>
       <c r="AO514" s="81"/>
     </row>
-    <row r="515" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:41" s="26" customFormat="1">
       <c r="A515" s="19" t="s">
         <v>1190</v>
       </c>
@@ -59830,7 +59826,7 @@
       </c>
       <c r="AO515" s="81"/>
     </row>
-    <row r="516" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:41" s="26" customFormat="1">
       <c r="A516" s="19" t="s">
         <v>1193</v>
       </c>
@@ -59943,7 +59939,7 @@
       </c>
       <c r="AO516" s="81"/>
     </row>
-    <row r="517" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:41" s="26" customFormat="1" ht="20.45">
       <c r="A517" s="19" t="s">
         <v>388</v>
       </c>
@@ -60058,7 +60054,7 @@
       </c>
       <c r="AO517" s="81"/>
     </row>
-    <row r="518" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:41" s="26" customFormat="1">
       <c r="A518" s="19" t="s">
         <v>1198</v>
       </c>
@@ -60142,7 +60138,7 @@
       </c>
       <c r="AO518" s="81"/>
     </row>
-    <row r="519" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:41" s="26" customFormat="1">
       <c r="A519" s="19" t="s">
         <v>1199</v>
       </c>
@@ -60212,7 +60208,7 @@
       </c>
       <c r="AO519" s="81"/>
     </row>
-    <row r="520" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:41" s="26" customFormat="1">
       <c r="A520" s="19" t="s">
         <v>1200</v>
       </c>
@@ -60327,7 +60323,7 @@
       </c>
       <c r="AO520" s="81"/>
     </row>
-    <row r="521" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:41" s="26" customFormat="1">
       <c r="A521" s="19" t="s">
         <v>1205</v>
       </c>
@@ -60438,7 +60434,7 @@
       </c>
       <c r="AO521" s="81"/>
     </row>
-    <row r="522" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:41" s="26" customFormat="1" ht="20.45">
       <c r="A522" s="19" t="s">
         <v>1207</v>
       </c>
@@ -60553,7 +60549,7 @@
       </c>
       <c r="AO522" s="81"/>
     </row>
-    <row r="523" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:41" s="26" customFormat="1">
       <c r="A523" s="19" t="s">
         <v>1210</v>
       </c>
@@ -60658,7 +60654,7 @@
       <c r="AN523" s="83"/>
       <c r="AO523" s="81"/>
     </row>
-    <row r="524" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:41" s="26" customFormat="1">
       <c r="A524" s="19" t="s">
         <v>1214</v>
       </c>
@@ -60771,7 +60767,7 @@
       </c>
       <c r="AO524" s="81"/>
     </row>
-    <row r="525" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:41" s="26" customFormat="1">
       <c r="A525" s="19" t="s">
         <v>1218</v>
       </c>
@@ -60872,7 +60868,7 @@
       <c r="AN525" s="83"/>
       <c r="AO525" s="81"/>
     </row>
-    <row r="526" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:41" s="26" customFormat="1">
       <c r="A526" s="19" t="s">
         <v>1221</v>
       </c>
@@ -60987,7 +60983,7 @@
       </c>
       <c r="AO526" s="81"/>
     </row>
-    <row r="527" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:41" s="26" customFormat="1">
       <c r="A527" s="19" t="s">
         <v>1224</v>
       </c>
@@ -61102,7 +61098,7 @@
       </c>
       <c r="AO527" s="81"/>
     </row>
-    <row r="528" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:41" s="26" customFormat="1">
       <c r="A528" s="19" t="s">
         <v>1228</v>
       </c>
@@ -61217,7 +61213,7 @@
       </c>
       <c r="AO528" s="81"/>
     </row>
-    <row r="529" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:41" s="26" customFormat="1" ht="20.45">
       <c r="A529" s="19" t="s">
         <v>1231</v>
       </c>
@@ -61333,7 +61329,7 @@
       </c>
       <c r="AO529" s="81"/>
     </row>
-    <row r="530" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:41" s="26" customFormat="1">
       <c r="A530" s="19" t="s">
         <v>723</v>
       </c>
@@ -61433,7 +61429,7 @@
       <c r="AN530" s="83"/>
       <c r="AO530" s="81"/>
     </row>
-    <row r="531" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:41" s="26" customFormat="1">
       <c r="A531" s="19" t="s">
         <v>1234</v>
       </c>
@@ -61546,7 +61542,7 @@
       </c>
       <c r="AO531" s="81"/>
     </row>
-    <row r="532" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:41" s="26" customFormat="1">
       <c r="A532" s="19" t="s">
         <v>1237</v>
       </c>
@@ -61650,7 +61646,7 @@
       <c r="AN532" s="83"/>
       <c r="AO532" s="81"/>
     </row>
-    <row r="533" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:41" s="26" customFormat="1">
       <c r="A533" s="19" t="s">
         <v>1239</v>
       </c>
@@ -61754,7 +61750,7 @@
       <c r="AN533" s="83"/>
       <c r="AO533" s="81"/>
     </row>
-    <row r="534" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:41" s="26" customFormat="1">
       <c r="A534" s="19" t="s">
         <v>1241</v>
       </c>
@@ -61869,7 +61865,7 @@
       </c>
       <c r="AO534" s="81"/>
     </row>
-    <row r="535" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:41" s="26" customFormat="1">
       <c r="A535" s="19" t="s">
         <v>1245</v>
       </c>
@@ -61980,7 +61976,7 @@
       <c r="AN535" s="83"/>
       <c r="AO535" s="81"/>
     </row>
-    <row r="536" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:41" s="26" customFormat="1">
       <c r="A536" s="19" t="s">
         <v>1247</v>
       </c>
@@ -62084,7 +62080,7 @@
       <c r="AN536" s="83"/>
       <c r="AO536" s="81"/>
     </row>
-    <row r="537" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:41" s="26" customFormat="1">
       <c r="A537" s="19" t="s">
         <v>734</v>
       </c>
@@ -62197,7 +62193,7 @@
       </c>
       <c r="AO537" s="81"/>
     </row>
-    <row r="538" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:41" s="26" customFormat="1">
       <c r="A538" s="19" t="s">
         <v>1251</v>
       </c>
@@ -62309,7 +62305,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="539" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:41" s="26" customFormat="1">
       <c r="A539" s="19" t="s">
         <v>1253</v>
       </c>
@@ -62423,7 +62419,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="540" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:41" s="26" customFormat="1">
       <c r="A540" s="19" t="s">
         <v>1256</v>
       </c>
@@ -62526,7 +62522,7 @@
       <c r="AM540" s="1"/>
       <c r="AN540" s="83"/>
     </row>
-    <row r="541" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:41" s="26" customFormat="1">
       <c r="A541" s="19" t="s">
         <v>719</v>
       </c>
@@ -62625,7 +62621,7 @@
       <c r="AM541" s="1"/>
       <c r="AN541" s="83"/>
     </row>
-    <row r="542" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:41" s="26" customFormat="1">
       <c r="A542" s="19" t="s">
         <v>1259</v>
       </c>
@@ -62739,7 +62735,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="543" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:41" s="26" customFormat="1">
       <c r="A543" s="19" t="s">
         <v>1261</v>
       </c>
@@ -62842,7 +62838,7 @@
       <c r="AM543" s="1"/>
       <c r="AN543" s="83"/>
     </row>
-    <row r="544" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:41" s="26" customFormat="1">
       <c r="A544" s="19" t="s">
         <v>1263</v>
       </c>
@@ -62956,7 +62952,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="545" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:40" s="26" customFormat="1">
       <c r="A545" s="19" t="s">
         <v>1266</v>
       </c>
@@ -63070,7 +63066,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="546" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:40" s="26" customFormat="1">
       <c r="A546" s="19" t="s">
         <v>1268</v>
       </c>
@@ -63184,7 +63180,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="547" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:40" s="26" customFormat="1">
       <c r="A547" s="19" t="s">
         <v>1270</v>
       </c>
@@ -63287,7 +63283,7 @@
       <c r="AM547" s="1"/>
       <c r="AN547" s="83"/>
     </row>
-    <row r="548" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:40" s="26" customFormat="1">
       <c r="A548" s="19" t="s">
         <v>1271</v>
       </c>
@@ -63401,7 +63397,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="549" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:40" s="26" customFormat="1">
       <c r="A549" s="19" t="s">
         <v>1274</v>
       </c>
@@ -63504,7 +63500,7 @@
       <c r="AM549" s="1"/>
       <c r="AN549" s="83"/>
     </row>
-    <row r="550" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:40" s="26" customFormat="1">
       <c r="A550" s="19" t="s">
         <v>1275</v>
       </c>
@@ -63607,7 +63603,7 @@
       <c r="AM550" s="1"/>
       <c r="AN550" s="83"/>
     </row>
-    <row r="551" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:40" s="26" customFormat="1">
       <c r="A551" s="19" t="s">
         <v>1277</v>
       </c>
@@ -63710,7 +63706,7 @@
       <c r="AM551" s="1"/>
       <c r="AN551" s="83"/>
     </row>
-    <row r="552" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:40" s="26" customFormat="1">
       <c r="A552" s="19" t="s">
         <v>738</v>
       </c>
@@ -63811,7 +63807,7 @@
       <c r="AM552" s="1"/>
       <c r="AN552" s="83"/>
     </row>
-    <row r="553" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:40" s="26" customFormat="1">
       <c r="A553" s="19" t="s">
         <v>1278</v>
       </c>
@@ -63925,7 +63921,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="554" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:40" s="26" customFormat="1">
       <c r="A554" s="19" t="s">
         <v>1282</v>
       </c>
@@ -64028,7 +64024,7 @@
       <c r="AM554" s="1"/>
       <c r="AN554" s="83"/>
     </row>
-    <row r="555" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:40" s="26" customFormat="1">
       <c r="A555" s="19" t="s">
         <v>1283</v>
       </c>
@@ -64129,7 +64125,7 @@
       <c r="AM555" s="1"/>
       <c r="AN555" s="83"/>
     </row>
-    <row r="556" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:40" s="26" customFormat="1">
       <c r="A556" s="19" t="s">
         <v>1284</v>
       </c>
@@ -64243,7 +64239,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="557" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:40" s="26" customFormat="1">
       <c r="A557" s="19" t="s">
         <v>1287</v>
       </c>
@@ -64346,7 +64342,7 @@
       <c r="AM557" s="1"/>
       <c r="AN557" s="83"/>
     </row>
-    <row r="558" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:40" s="26" customFormat="1">
       <c r="A558" s="19" t="s">
         <v>1289</v>
       </c>
@@ -64447,7 +64443,7 @@
       <c r="AM558" s="1"/>
       <c r="AN558" s="83"/>
     </row>
-    <row r="559" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:40" s="26" customFormat="1">
       <c r="A559" s="19" t="s">
         <v>1291</v>
       </c>
@@ -64548,7 +64544,7 @@
       <c r="AM559" s="1"/>
       <c r="AN559" s="83"/>
     </row>
-    <row r="560" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:40" s="26" customFormat="1">
       <c r="A560" s="19" t="s">
         <v>1293</v>
       </c>
@@ -64660,7 +64656,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="561" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:40" s="26" customFormat="1">
       <c r="A561" s="19" t="s">
         <v>586</v>
       </c>
@@ -64763,7 +64759,7 @@
       <c r="AM561" s="1"/>
       <c r="AN561" s="83"/>
     </row>
-    <row r="562" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:40" s="26" customFormat="1">
       <c r="A562" s="19" t="s">
         <v>1296</v>
       </c>
@@ -64877,7 +64873,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="563" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:40" s="26" customFormat="1">
       <c r="A563" s="19" t="s">
         <v>1298</v>
       </c>
@@ -64991,7 +64987,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="564" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:40" s="26" customFormat="1">
       <c r="A564" s="19" t="s">
         <v>1301</v>
       </c>
@@ -65103,7 +65099,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="565" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:40" s="26" customFormat="1">
       <c r="A565" s="19" t="s">
         <v>1304</v>
       </c>
@@ -65204,7 +65200,7 @@
       <c r="AM565" s="1"/>
       <c r="AN565" s="83"/>
     </row>
-    <row r="566" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:40" s="26" customFormat="1">
       <c r="A566" s="19" t="s">
         <v>1306</v>
       </c>
@@ -65307,7 +65303,7 @@
       <c r="AM566" s="1"/>
       <c r="AN566" s="83"/>
     </row>
-    <row r="567" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:40" s="26" customFormat="1">
       <c r="A567" s="32" t="s">
         <v>1308</v>
       </c>
@@ -65408,7 +65404,7 @@
       <c r="AM567" s="1"/>
       <c r="AN567" s="83"/>
     </row>
-    <row r="568" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:40" s="26" customFormat="1">
       <c r="A568" s="19" t="s">
         <v>1310</v>
       </c>
@@ -65511,7 +65507,7 @@
       <c r="AM568" s="1"/>
       <c r="AN568" s="83"/>
     </row>
-    <row r="569" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:40" s="26" customFormat="1">
       <c r="A569" s="19" t="s">
         <v>1312</v>
       </c>
@@ -65625,7 +65621,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="570" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:40" s="26" customFormat="1">
       <c r="A570" s="19" t="s">
         <v>1315</v>
       </c>
@@ -65726,7 +65722,7 @@
       <c r="AM570" s="1"/>
       <c r="AN570" s="83"/>
     </row>
-    <row r="571" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:40" s="26" customFormat="1">
       <c r="A571" s="19" t="s">
         <v>1317</v>
       </c>
@@ -65827,7 +65823,7 @@
       <c r="AM571" s="1"/>
       <c r="AN571" s="83"/>
     </row>
-    <row r="572" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:40" s="26" customFormat="1">
       <c r="A572" s="19" t="s">
         <v>1318</v>
       </c>
@@ -65928,7 +65924,7 @@
       <c r="AM572" s="1"/>
       <c r="AN572" s="83"/>
     </row>
-    <row r="573" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:40" s="26" customFormat="1">
       <c r="A573" s="19" t="s">
         <v>1320</v>
       </c>
@@ -66031,7 +66027,7 @@
       <c r="AM573" s="1"/>
       <c r="AN573" s="83"/>
     </row>
-    <row r="574" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:40" s="26" customFormat="1">
       <c r="A574" s="19" t="s">
         <v>1322</v>
       </c>
@@ -66134,7 +66130,7 @@
       <c r="AM574" s="1"/>
       <c r="AN574" s="83"/>
     </row>
-    <row r="575" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:40" s="26" customFormat="1">
       <c r="A575" s="19" t="s">
         <v>1325</v>
       </c>
@@ -66237,7 +66233,7 @@
       <c r="AM575" s="1"/>
       <c r="AN575" s="83"/>
     </row>
-    <row r="576" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:40" s="26" customFormat="1">
       <c r="A576" s="19" t="s">
         <v>1327</v>
       </c>
@@ -66340,7 +66336,7 @@
       <c r="AM576" s="1"/>
       <c r="AN576" s="83"/>
     </row>
-    <row r="577" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:40" s="26" customFormat="1">
       <c r="A577" s="19" t="s">
         <v>1329</v>
       </c>
@@ -66443,7 +66439,7 @@
       <c r="AM577" s="1"/>
       <c r="AN577" s="83"/>
     </row>
-    <row r="578" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:40" s="26" customFormat="1">
       <c r="A578" s="19" t="s">
         <v>1331</v>
       </c>
@@ -66544,7 +66540,7 @@
       <c r="AM578" s="1"/>
       <c r="AN578" s="83"/>
     </row>
-    <row r="579" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:40" s="26" customFormat="1">
       <c r="A579" s="19" t="s">
         <v>1332</v>
       </c>
@@ -66647,7 +66643,7 @@
       <c r="AM579" s="1"/>
       <c r="AN579" s="83"/>
     </row>
-    <row r="580" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:40" s="26" customFormat="1">
       <c r="A580" s="19" t="s">
         <v>1334</v>
       </c>
@@ -66750,7 +66746,7 @@
       <c r="AM580" s="1"/>
       <c r="AN580" s="83"/>
     </row>
-    <row r="581" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:40" s="26" customFormat="1">
       <c r="A581" s="19" t="s">
         <v>1335</v>
       </c>
@@ -66853,7 +66849,7 @@
       <c r="AM581" s="1"/>
       <c r="AN581" s="83"/>
     </row>
-    <row r="582" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:40" s="26" customFormat="1">
       <c r="A582" s="19" t="s">
         <v>1337</v>
       </c>
@@ -66956,7 +66952,7 @@
       <c r="AM582" s="1"/>
       <c r="AN582" s="83"/>
     </row>
-    <row r="583" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A583" s="19" t="s">
         <v>1339</v>
       </c>
@@ -67019,7 +67015,7 @@
       <c r="AM583" s="1"/>
       <c r="AN583" s="83"/>
     </row>
-    <row r="584" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:40" s="26" customFormat="1">
       <c r="A584" s="19" t="s">
         <v>1340</v>
       </c>
@@ -67122,7 +67118,7 @@
       <c r="AM584" s="1"/>
       <c r="AN584" s="83"/>
     </row>
-    <row r="585" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:40" s="26" customFormat="1">
       <c r="A585" s="19" t="s">
         <v>1342</v>
       </c>
@@ -67225,7 +67221,7 @@
       <c r="AM585" s="1"/>
       <c r="AN585" s="83"/>
     </row>
-    <row r="586" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:40" s="26" customFormat="1">
       <c r="A586" s="19" t="s">
         <v>1344</v>
       </c>
@@ -67328,7 +67324,7 @@
       <c r="AM586" s="1"/>
       <c r="AN586" s="83"/>
     </row>
-    <row r="587" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:40" s="26" customFormat="1">
       <c r="A587" s="19" t="s">
         <v>1346</v>
       </c>
@@ -67427,7 +67423,7 @@
       <c r="AM587" s="1"/>
       <c r="AN587" s="83"/>
     </row>
-    <row r="588" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:40" s="26" customFormat="1">
       <c r="A588" s="19" t="s">
         <v>299</v>
       </c>
@@ -67526,7 +67522,7 @@
       <c r="AM588" s="1"/>
       <c r="AN588" s="83"/>
     </row>
-    <row r="589" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:40" s="26" customFormat="1">
       <c r="A589" s="19" t="s">
         <v>1349</v>
       </c>
@@ -67629,7 +67625,7 @@
       <c r="AM589" s="1"/>
       <c r="AN589" s="83"/>
     </row>
-    <row r="590" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:40" s="26" customFormat="1">
       <c r="A590" s="19" t="s">
         <v>1351</v>
       </c>
@@ -67732,7 +67728,7 @@
       <c r="AM590" s="1"/>
       <c r="AN590" s="83"/>
     </row>
-    <row r="591" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A591" s="22" t="s">
         <v>1353</v>
       </c>
@@ -67807,7 +67803,7 @@
       <c r="AM591" s="1"/>
       <c r="AN591" s="83"/>
     </row>
-    <row r="592" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A592" s="22" t="s">
         <v>1356</v>
       </c>
@@ -67880,7 +67876,7 @@
       <c r="AM592" s="1"/>
       <c r="AN592" s="83"/>
     </row>
-    <row r="593" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A593" s="22" t="s">
         <v>1359</v>
       </c>
@@ -67953,7 +67949,7 @@
       <c r="AM593" s="1"/>
       <c r="AN593" s="83"/>
     </row>
-    <row r="594" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A594" s="22" t="s">
         <v>1360</v>
       </c>
@@ -68026,7 +68022,7 @@
       <c r="AM594" s="1"/>
       <c r="AN594" s="83"/>
     </row>
-    <row r="595" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A595" s="22" t="s">
         <v>647</v>
       </c>
@@ -68099,7 +68095,7 @@
       <c r="AM595" s="1"/>
       <c r="AN595" s="83"/>
     </row>
-    <row r="596" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A596" s="22" t="s">
         <v>1363</v>
       </c>
@@ -68172,7 +68168,7 @@
       <c r="AM596" s="1"/>
       <c r="AN596" s="83"/>
     </row>
-    <row r="597" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A597" s="22" t="s">
         <v>1364</v>
       </c>
@@ -68245,7 +68241,7 @@
       <c r="AM597" s="1"/>
       <c r="AN597" s="83"/>
     </row>
-    <row r="598" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A598" s="22" t="s">
         <v>1365</v>
       </c>
@@ -68318,7 +68314,7 @@
       <c r="AM598" s="1"/>
       <c r="AN598" s="83"/>
     </row>
-    <row r="599" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A599" s="22" t="s">
         <v>1368</v>
       </c>
@@ -68391,7 +68387,7 @@
       <c r="AM599" s="1"/>
       <c r="AN599" s="83"/>
     </row>
-    <row r="600" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A600" s="22" t="s">
         <v>1369</v>
       </c>
@@ -68464,7 +68460,7 @@
       <c r="AM600" s="1"/>
       <c r="AN600" s="83"/>
     </row>
-    <row r="601" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A601" s="22" t="s">
         <v>1371</v>
       </c>
@@ -68537,7 +68533,7 @@
       <c r="AM601" s="1"/>
       <c r="AN601" s="83"/>
     </row>
-    <row r="602" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A602" s="22" t="s">
         <v>868</v>
       </c>
@@ -68610,7 +68606,7 @@
       <c r="AM602" s="1"/>
       <c r="AN602" s="83"/>
     </row>
-    <row r="603" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A603" s="22" t="s">
         <v>1373</v>
       </c>
@@ -68683,7 +68679,7 @@
       <c r="AM603" s="1"/>
       <c r="AN603" s="83"/>
     </row>
-    <row r="604" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A604" s="22" t="s">
         <v>1374</v>
       </c>
@@ -68756,7 +68752,7 @@
       <c r="AM604" s="1"/>
       <c r="AN604" s="83"/>
     </row>
-    <row r="605" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A605" s="22" t="s">
         <v>655</v>
       </c>
@@ -68829,7 +68825,7 @@
       <c r="AM605" s="1"/>
       <c r="AN605" s="83"/>
     </row>
-    <row r="606" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A606" s="22" t="s">
         <v>275</v>
       </c>
@@ -68904,7 +68900,7 @@
       <c r="AM606" s="1"/>
       <c r="AN606" s="83"/>
     </row>
-    <row r="607" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A607" s="22" t="s">
         <v>1377</v>
       </c>
@@ -68977,7 +68973,7 @@
       <c r="AM607" s="1"/>
       <c r="AN607" s="83"/>
     </row>
-    <row r="608" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A608" s="22" t="s">
         <v>1378</v>
       </c>
@@ -69050,7 +69046,7 @@
       <c r="AM608" s="1"/>
       <c r="AN608" s="83"/>
     </row>
-    <row r="609" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A609" s="22" t="s">
         <v>378</v>
       </c>
@@ -69123,7 +69119,7 @@
       <c r="AM609" s="1"/>
       <c r="AN609" s="83"/>
     </row>
-    <row r="610" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A610" s="22" t="s">
         <v>370</v>
       </c>
@@ -69196,7 +69192,7 @@
       <c r="AM610" s="1"/>
       <c r="AN610" s="83"/>
     </row>
-    <row r="611" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A611" s="22" t="s">
         <v>1379</v>
       </c>
@@ -69269,7 +69265,7 @@
       <c r="AM611" s="1"/>
       <c r="AN611" s="83"/>
     </row>
-    <row r="612" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A612" s="22" t="s">
         <v>1380</v>
       </c>
@@ -69342,7 +69338,7 @@
       <c r="AM612" s="1"/>
       <c r="AN612" s="83"/>
     </row>
-    <row r="613" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A613" s="22" t="s">
         <v>1381</v>
       </c>
@@ -69415,7 +69411,7 @@
       <c r="AM613" s="1"/>
       <c r="AN613" s="83"/>
     </row>
-    <row r="614" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A614" s="22" t="s">
         <v>1383</v>
       </c>
@@ -69488,7 +69484,7 @@
       <c r="AM614" s="1"/>
       <c r="AN614" s="83"/>
     </row>
-    <row r="615" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A615" s="22" t="s">
         <v>672</v>
       </c>
@@ -69561,7 +69557,7 @@
       <c r="AM615" s="1"/>
       <c r="AN615" s="83"/>
     </row>
-    <row r="616" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A616" s="22" t="s">
         <v>1384</v>
       </c>
@@ -69634,7 +69630,7 @@
       <c r="AM616" s="1"/>
       <c r="AN616" s="83"/>
     </row>
-    <row r="617" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A617" s="22" t="s">
         <v>1386</v>
       </c>
@@ -69707,7 +69703,7 @@
       <c r="AM617" s="1"/>
       <c r="AN617" s="83"/>
     </row>
-    <row r="618" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A618" s="22" t="s">
         <v>880</v>
       </c>
@@ -69780,7 +69776,7 @@
       <c r="AM618" s="1"/>
       <c r="AN618" s="83"/>
     </row>
-    <row r="619" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A619" s="22" t="s">
         <v>907</v>
       </c>
@@ -69853,7 +69849,7 @@
       <c r="AM619" s="1"/>
       <c r="AN619" s="83"/>
     </row>
-    <row r="620" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A620" s="22" t="s">
         <v>877</v>
       </c>
@@ -69926,7 +69922,7 @@
       <c r="AM620" s="1"/>
       <c r="AN620" s="83"/>
     </row>
-    <row r="621" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A621" s="22" t="s">
         <v>1389</v>
       </c>
@@ -69999,7 +69995,7 @@
       <c r="AM621" s="1"/>
       <c r="AN621" s="83"/>
     </row>
-    <row r="622" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A622" s="22" t="s">
         <v>1390</v>
       </c>
@@ -70072,7 +70068,7 @@
       <c r="AM622" s="1"/>
       <c r="AN622" s="83"/>
     </row>
-    <row r="623" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A623" s="22" t="s">
         <v>859</v>
       </c>
@@ -70145,7 +70141,7 @@
       <c r="AM623" s="1"/>
       <c r="AN623" s="83"/>
     </row>
-    <row r="624" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A624" s="22" t="s">
         <v>1392</v>
       </c>
@@ -70218,7 +70214,7 @@
       <c r="AM624" s="1"/>
       <c r="AN624" s="83"/>
     </row>
-    <row r="625" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A625" s="22" t="s">
         <v>1393</v>
       </c>
@@ -70291,7 +70287,7 @@
       <c r="AM625" s="1"/>
       <c r="AN625" s="83"/>
     </row>
-    <row r="626" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A626" s="22" t="s">
         <v>406</v>
       </c>
@@ -70364,7 +70360,7 @@
       <c r="AM626" s="1"/>
       <c r="AN626" s="83"/>
     </row>
-    <row r="627" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A627" s="22" t="s">
         <v>1396</v>
       </c>
@@ -70437,7 +70433,7 @@
       <c r="AM627" s="1"/>
       <c r="AN627" s="83"/>
     </row>
-    <row r="628" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A628" s="22" t="s">
         <v>921</v>
       </c>
@@ -70510,7 +70506,7 @@
       <c r="AM628" s="1"/>
       <c r="AN628" s="83"/>
     </row>
-    <row r="629" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A629" s="22" t="s">
         <v>1398</v>
       </c>
@@ -70583,7 +70579,7 @@
       <c r="AM629" s="1"/>
       <c r="AN629" s="83"/>
     </row>
-    <row r="630" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A630" s="22" t="s">
         <v>892</v>
       </c>
@@ -70656,7 +70652,7 @@
       <c r="AM630" s="1"/>
       <c r="AN630" s="83"/>
     </row>
-    <row r="631" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A631" s="22" t="s">
         <v>1400</v>
       </c>
@@ -70729,7 +70725,7 @@
       <c r="AM631" s="1"/>
       <c r="AN631" s="83"/>
     </row>
-    <row r="632" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A632" s="22" t="s">
         <v>1401</v>
       </c>
@@ -70802,7 +70798,7 @@
       <c r="AM632" s="1"/>
       <c r="AN632" s="83"/>
     </row>
-    <row r="633" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A633" s="22" t="s">
         <v>1403</v>
       </c>
@@ -70875,7 +70871,7 @@
       <c r="AM633" s="1"/>
       <c r="AN633" s="83"/>
     </row>
-    <row r="634" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A634" s="22" t="s">
         <v>1404</v>
       </c>
@@ -70948,7 +70944,7 @@
       <c r="AM634" s="1"/>
       <c r="AN634" s="83"/>
     </row>
-    <row r="635" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A635" s="22" t="s">
         <v>1405</v>
       </c>
@@ -71021,7 +71017,7 @@
       <c r="AM635" s="1"/>
       <c r="AN635" s="83"/>
     </row>
-    <row r="636" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A636" s="22" t="s">
         <v>1406</v>
       </c>
@@ -71094,7 +71090,7 @@
       <c r="AM636" s="1"/>
       <c r="AN636" s="83"/>
     </row>
-    <row r="637" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A637" s="22" t="s">
         <v>1407</v>
       </c>
@@ -71167,7 +71163,7 @@
       <c r="AM637" s="1"/>
       <c r="AN637" s="83"/>
     </row>
-    <row r="638" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A638" s="22" t="s">
         <v>1409</v>
       </c>
@@ -71240,7 +71236,7 @@
       <c r="AM638" s="1"/>
       <c r="AN638" s="83"/>
     </row>
-    <row r="639" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A639" s="22" t="s">
         <v>1410</v>
       </c>
@@ -71313,7 +71309,7 @@
       <c r="AM639" s="1"/>
       <c r="AN639" s="83"/>
     </row>
-    <row r="640" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A640" s="22" t="s">
         <v>1411</v>
       </c>
@@ -71386,7 +71382,7 @@
       <c r="AM640" s="1"/>
       <c r="AN640" s="83"/>
     </row>
-    <row r="641" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A641" s="22" t="s">
         <v>898</v>
       </c>
@@ -71459,7 +71455,7 @@
       <c r="AM641" s="1"/>
       <c r="AN641" s="83"/>
     </row>
-    <row r="642" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A642" s="22" t="s">
         <v>967</v>
       </c>
@@ -71532,7 +71528,7 @@
       <c r="AM642" s="1"/>
       <c r="AN642" s="83"/>
     </row>
-    <row r="643" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A643" s="22" t="s">
         <v>1412</v>
       </c>
@@ -71605,7 +71601,7 @@
       <c r="AM643" s="1"/>
       <c r="AN643" s="83"/>
     </row>
-    <row r="644" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A644" s="22" t="s">
         <v>1414</v>
       </c>
@@ -71678,7 +71674,7 @@
       <c r="AM644" s="1"/>
       <c r="AN644" s="83"/>
     </row>
-    <row r="645" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A645" s="22" t="s">
         <v>874</v>
       </c>
@@ -71751,7 +71747,7 @@
       <c r="AM645" s="1"/>
       <c r="AN645" s="83"/>
     </row>
-    <row r="646" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A646" s="22" t="s">
         <v>1415</v>
       </c>
@@ -71824,7 +71820,7 @@
       <c r="AM646" s="1"/>
       <c r="AN646" s="83"/>
     </row>
-    <row r="647" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A647" s="22" t="s">
         <v>946</v>
       </c>
@@ -71897,7 +71893,7 @@
       <c r="AM647" s="1"/>
       <c r="AN647" s="83"/>
     </row>
-    <row r="648" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A648" s="22" t="s">
         <v>1416</v>
       </c>
@@ -71970,7 +71966,7 @@
       <c r="AM648" s="1"/>
       <c r="AN648" s="83"/>
     </row>
-    <row r="649" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A649" s="22" t="s">
         <v>97</v>
       </c>
@@ -72045,7 +72041,7 @@
       <c r="AM649" s="1"/>
       <c r="AN649" s="83"/>
     </row>
-    <row r="650" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A650" s="22" t="s">
         <v>1419</v>
       </c>
@@ -72118,7 +72114,7 @@
       <c r="AM650" s="1"/>
       <c r="AN650" s="83"/>
     </row>
-    <row r="651" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A651" s="22" t="s">
         <v>1420</v>
       </c>
@@ -72189,7 +72185,7 @@
       <c r="AM651" s="1"/>
       <c r="AN651" s="83"/>
     </row>
-    <row r="652" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A652" s="22" t="s">
         <v>650</v>
       </c>
@@ -72262,7 +72258,7 @@
       <c r="AM652" s="1"/>
       <c r="AN652" s="83"/>
     </row>
-    <row r="653" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A653" s="22" t="s">
         <v>1421</v>
       </c>
@@ -72335,7 +72331,7 @@
       <c r="AM653" s="1"/>
       <c r="AN653" s="83"/>
     </row>
-    <row r="654" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A654" s="22" t="s">
         <v>1423</v>
       </c>
@@ -72408,7 +72404,7 @@
       <c r="AM654" s="1"/>
       <c r="AN654" s="83"/>
     </row>
-    <row r="655" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A655" s="22" t="s">
         <v>1424</v>
       </c>
@@ -72481,7 +72477,7 @@
       <c r="AM655" s="1"/>
       <c r="AN655" s="83"/>
     </row>
-    <row r="656" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A656" s="22" t="s">
         <v>1426</v>
       </c>
@@ -72554,7 +72550,7 @@
       <c r="AM656" s="1"/>
       <c r="AN656" s="83"/>
     </row>
-    <row r="657" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A657" s="22" t="s">
         <v>1427</v>
       </c>
@@ -72627,7 +72623,7 @@
       <c r="AM657" s="1"/>
       <c r="AN657" s="83"/>
     </row>
-    <row r="658" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A658" s="22" t="s">
         <v>1428</v>
       </c>
@@ -72700,7 +72696,7 @@
       <c r="AM658" s="1"/>
       <c r="AN658" s="83"/>
     </row>
-    <row r="659" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A659" s="22" t="s">
         <v>1429</v>
       </c>
@@ -72773,7 +72769,7 @@
       <c r="AM659" s="1"/>
       <c r="AN659" s="83"/>
     </row>
-    <row r="660" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A660" s="22" t="s">
         <v>1430</v>
       </c>
@@ -72846,7 +72842,7 @@
       <c r="AM660" s="1"/>
       <c r="AN660" s="83"/>
     </row>
-    <row r="661" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A661" s="22" t="s">
         <v>1431</v>
       </c>
@@ -72919,7 +72915,7 @@
       <c r="AM661" s="1"/>
       <c r="AN661" s="83"/>
     </row>
-    <row r="662" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A662" s="22" t="s">
         <v>1432</v>
       </c>
@@ -72992,7 +72988,7 @@
       <c r="AM662" s="1"/>
       <c r="AN662" s="83"/>
     </row>
-    <row r="663" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A663" s="22" t="s">
         <v>966</v>
       </c>
@@ -73065,7 +73061,7 @@
       <c r="AM663" s="1"/>
       <c r="AN663" s="83"/>
     </row>
-    <row r="664" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A664" s="22" t="s">
         <v>578</v>
       </c>
@@ -73148,7 +73144,7 @@
       <c r="AM664" s="1"/>
       <c r="AN664" s="83"/>
     </row>
-    <row r="665" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A665" s="22" t="s">
         <v>1435</v>
       </c>
@@ -73221,7 +73217,7 @@
       <c r="AM665" s="1"/>
       <c r="AN665" s="83"/>
     </row>
-    <row r="666" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A666" s="22" t="s">
         <v>1437</v>
       </c>
@@ -73294,7 +73290,7 @@
       <c r="AM666" s="1"/>
       <c r="AN666" s="83"/>
     </row>
-    <row r="667" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A667" s="22" t="s">
         <v>1439</v>
       </c>
@@ -73367,7 +73363,7 @@
       <c r="AM667" s="1"/>
       <c r="AN667" s="83"/>
     </row>
-    <row r="668" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A668" s="22" t="s">
         <v>1441</v>
       </c>
@@ -73440,7 +73436,7 @@
       <c r="AM668" s="1"/>
       <c r="AN668" s="83"/>
     </row>
-    <row r="669" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A669" s="22" t="s">
         <v>1442</v>
       </c>
@@ -73513,7 +73509,7 @@
       <c r="AM669" s="1"/>
       <c r="AN669" s="83"/>
     </row>
-    <row r="670" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A670" s="22" t="s">
         <v>1443</v>
       </c>
@@ -73586,7 +73582,7 @@
       <c r="AM670" s="1"/>
       <c r="AN670" s="83"/>
     </row>
-    <row r="671" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A671" s="22" t="s">
         <v>1445</v>
       </c>
@@ -73659,7 +73655,7 @@
       <c r="AM671" s="1"/>
       <c r="AN671" s="83"/>
     </row>
-    <row r="672" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A672" s="22" t="s">
         <v>1447</v>
       </c>
@@ -73732,7 +73728,7 @@
       <c r="AM672" s="1"/>
       <c r="AN672" s="83"/>
     </row>
-    <row r="673" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A673" s="22" t="s">
         <v>1448</v>
       </c>
@@ -73805,7 +73801,7 @@
       <c r="AM673" s="1"/>
       <c r="AN673" s="83"/>
     </row>
-    <row r="674" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A674" s="22" t="s">
         <v>1449</v>
       </c>
@@ -73876,7 +73872,7 @@
       <c r="AM674" s="1"/>
       <c r="AN674" s="83"/>
     </row>
-    <row r="675" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A675" s="22" t="s">
         <v>1450</v>
       </c>
@@ -73949,7 +73945,7 @@
       <c r="AM675" s="1"/>
       <c r="AN675" s="83"/>
     </row>
-    <row r="676" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A676" s="22" t="s">
         <v>1451</v>
       </c>
@@ -74022,7 +74018,7 @@
       <c r="AM676" s="1"/>
       <c r="AN676" s="83"/>
     </row>
-    <row r="677" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A677" s="22" t="s">
         <v>1452</v>
       </c>
@@ -74095,7 +74091,7 @@
       <c r="AM677" s="1"/>
       <c r="AN677" s="83"/>
     </row>
-    <row r="678" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A678" s="22" t="s">
         <v>1453</v>
       </c>
@@ -74168,7 +74164,7 @@
       <c r="AM678" s="1"/>
       <c r="AN678" s="83"/>
     </row>
-    <row r="679" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A679" s="22" t="s">
         <v>1454</v>
       </c>
@@ -74241,7 +74237,7 @@
       <c r="AM679" s="1"/>
       <c r="AN679" s="83"/>
     </row>
-    <row r="680" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A680" s="22" t="s">
         <v>1455</v>
       </c>
@@ -74314,7 +74310,7 @@
       <c r="AM680" s="1"/>
       <c r="AN680" s="83"/>
     </row>
-    <row r="681" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A681" s="22" t="s">
         <v>870</v>
       </c>
@@ -74387,7 +74383,7 @@
       <c r="AM681" s="1"/>
       <c r="AN681" s="83"/>
     </row>
-    <row r="682" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A682" s="22" t="s">
         <v>1456</v>
       </c>
@@ -74460,7 +74456,7 @@
       <c r="AM682" s="1"/>
       <c r="AN682" s="83"/>
     </row>
-    <row r="683" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A683" s="22" t="s">
         <v>1457</v>
       </c>
@@ -74533,7 +74529,7 @@
       <c r="AM683" s="1"/>
       <c r="AN683" s="83"/>
     </row>
-    <row r="684" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A684" s="22" t="s">
         <v>1458</v>
       </c>
@@ -74606,7 +74602,7 @@
       <c r="AM684" s="1"/>
       <c r="AN684" s="83"/>
     </row>
-    <row r="685" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A685" s="22" t="s">
         <v>1459</v>
       </c>
@@ -74679,7 +74675,7 @@
       <c r="AM685" s="1"/>
       <c r="AN685" s="83"/>
     </row>
-    <row r="686" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A686" s="22" t="s">
         <v>1460</v>
       </c>
@@ -74752,7 +74748,7 @@
       <c r="AM686" s="1"/>
       <c r="AN686" s="83"/>
     </row>
-    <row r="687" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A687" s="22" t="s">
         <v>1461</v>
       </c>
@@ -74825,7 +74821,7 @@
       <c r="AM687" s="1"/>
       <c r="AN687" s="83"/>
     </row>
-    <row r="688" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A688" s="22" t="s">
         <v>1462</v>
       </c>
@@ -74898,7 +74894,7 @@
       <c r="AM688" s="1"/>
       <c r="AN688" s="83"/>
     </row>
-    <row r="689" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A689" s="22" t="s">
         <v>1463</v>
       </c>
@@ -74971,7 +74967,7 @@
       <c r="AM689" s="1"/>
       <c r="AN689" s="83"/>
     </row>
-    <row r="690" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A690" s="22" t="s">
         <v>1464</v>
       </c>
@@ -75044,7 +75040,7 @@
       <c r="AM690" s="1"/>
       <c r="AN690" s="83"/>
     </row>
-    <row r="691" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A691" s="22" t="s">
         <v>1465</v>
       </c>
@@ -75117,7 +75113,7 @@
       <c r="AM691" s="1"/>
       <c r="AN691" s="83"/>
     </row>
-    <row r="692" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A692" s="22" t="s">
         <v>1466</v>
       </c>
@@ -75190,7 +75186,7 @@
       <c r="AM692" s="1"/>
       <c r="AN692" s="83"/>
     </row>
-    <row r="693" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A693" s="22" t="s">
         <v>1467</v>
       </c>
@@ -75263,7 +75259,7 @@
       <c r="AM693" s="1"/>
       <c r="AN693" s="83"/>
     </row>
-    <row r="694" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A694" s="22" t="s">
         <v>1468</v>
       </c>
@@ -75336,7 +75332,7 @@
       <c r="AM694" s="1"/>
       <c r="AN694" s="83"/>
     </row>
-    <row r="695" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A695" s="22" t="s">
         <v>1469</v>
       </c>
@@ -75409,7 +75405,7 @@
       <c r="AM695" s="1"/>
       <c r="AN695" s="83"/>
     </row>
-    <row r="696" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A696" s="22" t="s">
         <v>1470</v>
       </c>
@@ -75482,7 +75478,7 @@
       <c r="AM696" s="1"/>
       <c r="AN696" s="83"/>
     </row>
-    <row r="697" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A697" s="22" t="s">
         <v>1081</v>
       </c>
@@ -75555,7 +75551,7 @@
       <c r="AM697" s="1"/>
       <c r="AN697" s="83"/>
     </row>
-    <row r="698" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A698" s="22" t="s">
         <v>1472</v>
       </c>
@@ -75628,7 +75624,7 @@
       <c r="AM698" s="1"/>
       <c r="AN698" s="83"/>
     </row>
-    <row r="699" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A699" s="22" t="s">
         <v>1473</v>
       </c>
@@ -75701,7 +75697,7 @@
       <c r="AM699" s="1"/>
       <c r="AN699" s="83"/>
     </row>
-    <row r="700" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A700" s="22" t="s">
         <v>1474</v>
       </c>
@@ -75774,7 +75770,7 @@
       <c r="AM700" s="1"/>
       <c r="AN700" s="83"/>
     </row>
-    <row r="701" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A701" s="22" t="s">
         <v>1475</v>
       </c>
@@ -75847,7 +75843,7 @@
       <c r="AM701" s="1"/>
       <c r="AN701" s="83"/>
     </row>
-    <row r="702" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A702" s="22" t="s">
         <v>1476</v>
       </c>
@@ -75920,7 +75916,7 @@
       <c r="AM702" s="1"/>
       <c r="AN702" s="83"/>
     </row>
-    <row r="703" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A703" s="22" t="s">
         <v>1477</v>
       </c>
@@ -75993,7 +75989,7 @@
       <c r="AM703" s="1"/>
       <c r="AN703" s="83"/>
     </row>
-    <row r="704" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A704" s="22" t="s">
         <v>1109</v>
       </c>
@@ -76066,7 +76062,7 @@
       <c r="AM704" s="1"/>
       <c r="AN704" s="83"/>
     </row>
-    <row r="705" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A705" s="22" t="s">
         <v>1478</v>
       </c>
@@ -76139,7 +76135,7 @@
       <c r="AM705" s="1"/>
       <c r="AN705" s="83"/>
     </row>
-    <row r="706" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A706" s="22" t="s">
         <v>1479</v>
       </c>
@@ -76212,7 +76208,7 @@
       <c r="AM706" s="1"/>
       <c r="AN706" s="83"/>
     </row>
-    <row r="707" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A707" s="22" t="s">
         <v>1480</v>
       </c>
@@ -76285,7 +76281,7 @@
       <c r="AM707" s="1"/>
       <c r="AN707" s="83"/>
     </row>
-    <row r="708" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A708" s="22" t="s">
         <v>1481</v>
       </c>
@@ -76358,7 +76354,7 @@
       <c r="AM708" s="1"/>
       <c r="AN708" s="83"/>
     </row>
-    <row r="709" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A709" s="22" t="s">
         <v>1482</v>
       </c>
@@ -76431,7 +76427,7 @@
       <c r="AM709" s="1"/>
       <c r="AN709" s="83"/>
     </row>
-    <row r="710" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:40" s="26" customFormat="1" hidden="1">
       <c r="A710" s="22" t="s">
         <v>1483</v>
       </c>
@@ -76504,7 +76500,7 @@
       <c r="AM710" s="1"/>
       <c r="AN710" s="83"/>
     </row>
-    <row r="711" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:40" s="26" customFormat="1">
       <c r="A711" s="39"/>
       <c r="B711" s="40"/>
       <c r="C711" s="40"/>
@@ -76566,34 +76562,40 @@
       <c r="AM711" s="46"/>
       <c r="AN711" s="83"/>
     </row>
-    <row r="716" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:40">
       <c r="AA716" s="73"/>
       <c r="AB716" s="73"/>
       <c r="AC716" s="73"/>
       <c r="AN716" s="94"/>
     </row>
-    <row r="717" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:40">
       <c r="Z717" s="73"/>
       <c r="AA717" s="73"/>
       <c r="AB717" s="73"/>
       <c r="AC717" s="73"/>
       <c r="AN717" s="94"/>
     </row>
-    <row r="718" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:40">
       <c r="Z718" s="73"/>
       <c r="AA718" s="73"/>
       <c r="AB718" s="73"/>
     </row>
-    <row r="719" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:40">
       <c r="Z719" s="73"/>
     </row>
-    <row r="720" spans="1:40" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:40">
       <c r="Z720" s="73"/>
       <c r="AA720" s="73"/>
       <c r="AB720" s="73"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AN711" xr:uid="{2AA437EE-405D-4A43-9EB9-23F1BEB36011}"/>
+  <autoFilter ref="A2:AN710" xr:uid="{2AA437EE-405D-4A43-9EB9-23F1BEB36011}">
+    <filterColumn colId="17">
+      <filters>
+        <filter val="Jarinu"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="A193:A213 A4:A95 A97:A118">
     <cfRule type="duplicateValues" dxfId="4" priority="12"/>
   </conditionalFormatting>
@@ -76666,18 +76668,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D813743-8135-4F32-BACA-A0CD44F9427F}">
   <dimension ref="A1:F44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" s="69" t="s">
         <v>1485</v>
       </c>
@@ -76697,7 +76699,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>755</v>
       </c>
@@ -76722,7 +76724,7 @@
         <v>88880.437499999985</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>49</v>
       </c>
@@ -76747,7 +76749,7 @@
         <v>256393.97999999995</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>151</v>
       </c>
@@ -76772,7 +76774,7 @@
         <v>136436.7233333333</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>187</v>
       </c>
@@ -76797,7 +76799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6">
       <c r="A6" s="53" t="s">
         <v>1491</v>
       </c>
@@ -76822,7 +76824,7 @@
         <v>481711.14083333325</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6">
       <c r="A9" s="69" t="s">
         <v>1492</v>
       </c>
@@ -76839,7 +76841,7 @@
         <v>1496</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6">
       <c r="A10" s="47" t="s">
         <v>764</v>
       </c>
@@ -76860,7 +76862,7 @@
         <v>163307.73333333334</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6">
       <c r="A11" s="47" t="s">
         <v>1133</v>
       </c>
@@ -76881,7 +76883,7 @@
         <v>101921.69083333333</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6">
       <c r="A12" s="47" t="s">
         <v>752</v>
       </c>
@@ -76902,7 +76904,7 @@
         <v>33682.781666666669</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6">
       <c r="A13" s="47" t="s">
         <v>92</v>
       </c>
@@ -76923,7 +76925,7 @@
         <v>110026.7025</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6">
       <c r="A14" s="47" t="s">
         <v>73</v>
       </c>
@@ -76944,7 +76946,7 @@
         <v>14192.72</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6">
       <c r="A15" s="47" t="s">
         <v>45</v>
       </c>
@@ -76965,7 +76967,7 @@
         <v>18301.009999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6">
       <c r="A16" s="47" t="s">
         <v>82</v>
       </c>
@@ -76986,7 +76988,7 @@
         <v>8786.4108333333334</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5">
       <c r="A17" s="47" t="s">
         <v>1145</v>
       </c>
@@ -77007,7 +77009,7 @@
         <v>17038.2366666667</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5">
       <c r="A18" s="47" t="s">
         <v>841</v>
       </c>
@@ -77028,7 +77030,7 @@
         <v>3342.1949999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5">
       <c r="A19" s="47" t="s">
         <v>237</v>
       </c>
@@ -77049,7 +77051,7 @@
         <v>1642.21</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5">
       <c r="A20" s="47" t="s">
         <v>1161</v>
       </c>
@@ -77070,7 +77072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5">
       <c r="A21" s="47" t="s">
         <v>872</v>
       </c>
@@ -77091,7 +77093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5">
       <c r="A22" s="47" t="s">
         <v>356</v>
       </c>
@@ -77112,7 +77114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5">
       <c r="A23" s="47" t="s">
         <v>223</v>
       </c>
@@ -77133,7 +77135,7 @@
         <v>4586.75</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5">
       <c r="A24" s="47" t="s">
         <v>1362</v>
       </c>
@@ -77154,7 +77156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5">
       <c r="A25" s="47" t="s">
         <v>220</v>
       </c>
@@ -77175,7 +77177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5">
       <c r="A26" s="47" t="s">
         <v>1220</v>
       </c>
@@ -77196,7 +77198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5">
       <c r="A27" s="47" t="s">
         <v>318</v>
       </c>
@@ -77217,7 +77219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5">
       <c r="A28" s="47" t="s">
         <v>349</v>
       </c>
@@ -77238,7 +77240,7 @@
         <v>1311.99</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5">
       <c r="A29" s="47" t="s">
         <v>253</v>
       </c>
@@ -77259,7 +77261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5">
       <c r="A30" s="47" t="s">
         <v>303</v>
       </c>
@@ -77280,7 +77282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5">
       <c r="A31" s="47" t="s">
         <v>879</v>
       </c>
@@ -77301,7 +77303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5">
       <c r="A32" s="47" t="s">
         <v>1358</v>
       </c>
@@ -77322,7 +77324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5">
       <c r="A33" s="47" t="s">
         <v>897</v>
       </c>
@@ -77343,7 +77345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5">
       <c r="A34" s="47" t="s">
         <v>1367</v>
       </c>
@@ -77364,7 +77366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5">
       <c r="A35" s="47" t="s">
         <v>925</v>
       </c>
@@ -77385,7 +77387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5">
       <c r="A36" s="47" t="s">
         <v>149</v>
       </c>
@@ -77406,7 +77408,7 @@
         <v>238.71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5">
       <c r="A37" s="47" t="s">
         <v>939</v>
       </c>
@@ -77427,7 +77429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5">
       <c r="A38" s="47" t="s">
         <v>1395</v>
       </c>
@@ -77448,7 +77450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5">
       <c r="A39" s="47" t="s">
         <v>1417</v>
       </c>
@@ -77469,7 +77471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5">
       <c r="A40" s="47"/>
       <c r="B40">
         <f>COUNTIF(Controle!L:L,Formulas!A41)</f>
@@ -77488,7 +77490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5">
       <c r="A41" s="47">
         <v>0</v>
       </c>
@@ -77509,7 +77511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5">
       <c r="A42" s="59" t="s">
         <v>1491</v>
       </c>
@@ -77530,12 +77532,12 @@
         <v>478379.14083333343</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5">
       <c r="A43" s="47"/>
       <c r="C43" s="57"/>
       <c r="D43" s="48"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5">
       <c r="A44" s="47"/>
     </row>
   </sheetData>
@@ -77553,14 +77555,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f5ab1930-d403-4c69-b2cd-8cc48f527d10" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c06ce65c-ed18-47f4-a957-afd315448c9c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -77759,54 +77759,24 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f5ab1930-d403-4c69-b2cd-8cc48f527d10" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c06ce65c-ed18-47f4-a957-afd315448c9c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE495743-F761-4961-A762-7A3D120C6961}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="c06ce65c-ed18-47f4-a957-afd315448c9c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f5ab1930-d403-4c69-b2cd-8cc48f527d10"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AE26D3A-03CC-4B3D-9F98-6F77A1AEA74E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59443FB2-AD94-4FFF-8817-F253987A64A5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c06ce65c-ed18-47f4-a957-afd315448c9c"/>
-    <ds:schemaRef ds:uri="f5ab1930-d403-4c69-b2cd-8cc48f527d10"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59443FB2-AD94-4FFF-8817-F253987A64A5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AE26D3A-03CC-4B3D-9F98-6F77A1AEA74E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE495743-F761-4961-A762-7A3D120C6961}"/>
 </file>
--- a/data/dados_atuais.xlsx
+++ b/data/dados_atuais.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="EsteLivro"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delgadiadema.sharepoint.com/sites/GestoEstratgica/Documentos Compartilhados/Controle Master/BSW/Novo controle (Em processo)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2080" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{988EE322-C98C-46BB-BB0D-97A8CB95C0B3}"/>
+  <xr:revisionPtr revIDLastSave="2108" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{168F0F45-6497-47F3-9ED0-64BF8C3F1EC5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E398004-7492-4AA0-94C2-EA9B761AAA49}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Formulas" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Controle!$A$2:$AN$711</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Controle!$A$2:$AN$710</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Formulas!$A$9:$D$41</definedName>
     <definedName name="_FiltrarBaseDados" localSheetId="0" hidden="1">Controle!$A$2:$AL$710</definedName>
   </definedNames>
@@ -213,17 +213,17 @@
     </comment>
     <comment ref="A555" authorId="3" shapeId="0" xr:uid="{33C328EB-7B56-47E9-A787-F392CA006902}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentário encadeado]
+Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
+Comentário:
     Utilizando material 1,60x417</t>
       </text>
     </comment>
     <comment ref="A564" authorId="4" shapeId="0" xr:uid="{C01DA7E7-015C-4D77-8E50-06C386F35AF3}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentário encadeado]
+Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
+Comentário:
     Temos na Fitametal 
 BOZ0070TJ1350 - 10249kg</t>
       </text>
@@ -254,17 +254,17 @@
     </comment>
     <comment ref="A574" authorId="6" shapeId="0" xr:uid="{67F1D739-35C9-474A-BA1D-BDA6C83EF4A4}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentário encadeado]
+Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
+Comentário:
     CORTAR SLEETER DE MATERIAL SEMELHANTE DEVIDO AO BAIXO VOLUME TEMOS O MESMO MATERIAL COM OUTRAS LARGURAS</t>
       </text>
     </comment>
     <comment ref="A575" authorId="7" shapeId="0" xr:uid="{9641E501-4748-445C-B1A5-D0E296582A82}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentário encadeado]
+Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
+Comentário:
     Usar material BOZ0060HU1000 como material alternativo</t>
       </text>
     </comment>
@@ -322,7 +322,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7119" uniqueCount="1497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7134" uniqueCount="1504">
   <si>
     <t>Código
 Bobina Mâe</t>
@@ -5021,6 +5021,27 @@
   <si>
     <t>Ganho por usina</t>
   </si>
+  <si>
+    <t>Reduzir 20mm no passo do blank, de 900 para 880 (10mm/peça). Aguardando validação da controladoria.</t>
+  </si>
+  <si>
+    <t>Processo terceirizado.</t>
+  </si>
+  <si>
+    <t>DA000503Z</t>
+  </si>
+  <si>
+    <t>Reduzir 20mm no passo do blank, de 240 para 220 (10mm/peça). Aguardando validação da controladoria.</t>
+  </si>
+  <si>
+    <t>Material em análise (Thiago Cardoso). Aguardando produção do produto para acompanhamento.</t>
+  </si>
+  <si>
+    <t>Material em análise (Izaias Claro). Aguardando produção do produto para acompanhamento.</t>
+  </si>
+  <si>
+    <t>Material em análise (Edson Lupis). Aguardando produção do produto para acompanhamento.</t>
+  </si>
 </sst>
 </file>
 
@@ -5033,7 +5054,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
     <numFmt numFmtId="166" formatCode="mmmm\,\ yyyy;@"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5268,7 +5289,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5525,6 +5546,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5856,7 +5880,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.68370795014214703</c:v>
+                  <c:v>0.69079740726203986</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6774,7 +6798,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.48576787436869623</c:v>
+                  <c:v>0.50880756061198085</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8100,7 +8124,7 @@
                   <c:v>1307.4815842</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>678.6992884</c:v>
+                  <c:v>710.88959879999993</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1118.2558657600009</c:v>
@@ -13407,49 +13431,49 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA437EE-405D-4A43-9EB9-23F1BEB36011}">
   <sheetPr codeName="Folha1" filterMode="1"/>
   <dimension ref="A1:AO720"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" customWidth="1"/>
-    <col min="7" max="7" width="28.5703125" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" customWidth="1"/>
-    <col min="11" max="11" width="21.42578125" customWidth="1"/>
-    <col min="12" max="12" width="20.42578125" customWidth="1"/>
-    <col min="13" max="13" width="23.5703125" customWidth="1"/>
-    <col min="14" max="14" width="32.42578125" customWidth="1"/>
-    <col min="15" max="15" width="8.5703125" customWidth="1"/>
-    <col min="16" max="16" width="10.42578125" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="12.42578125" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" customWidth="1"/>
+    <col min="7" max="7" width="28.5546875" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" customWidth="1"/>
+    <col min="10" max="10" width="9.5546875" customWidth="1"/>
+    <col min="11" max="11" width="21.44140625" customWidth="1"/>
+    <col min="12" max="12" width="20.44140625" customWidth="1"/>
+    <col min="13" max="13" width="23.5546875" customWidth="1"/>
+    <col min="14" max="14" width="32.44140625" customWidth="1"/>
+    <col min="15" max="15" width="8.5546875" customWidth="1"/>
+    <col min="16" max="16" width="10.44140625" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="12.44140625" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="11.5546875" customWidth="1"/>
     <col min="19" max="19" width="15" customWidth="1"/>
-    <col min="20" max="20" width="15.5703125" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="16.42578125" hidden="1" customWidth="1"/>
-    <col min="22" max="24" width="15.42578125" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="15.42578125" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.5546875" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="16.44140625" hidden="1" customWidth="1"/>
+    <col min="22" max="24" width="15.44140625" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="15.44140625" customWidth="1"/>
+    <col min="26" max="26" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="13" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.85546875" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="24.140625" customWidth="1"/>
-    <col min="37" max="37" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" hidden="1" customWidth="1"/>
-    <col min="39" max="39" width="91.140625" customWidth="1"/>
-    <col min="40" max="40" width="28.28515625" style="50" customWidth="1"/>
+    <col min="34" max="34" width="12.88671875" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="24.109375" customWidth="1"/>
+    <col min="37" max="37" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.88671875" hidden="1" customWidth="1"/>
+    <col min="39" max="39" width="91.109375" customWidth="1"/>
+    <col min="40" max="40" width="28.33203125" style="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="151.35" customHeight="1"/>
-    <row r="2" spans="1:40" ht="30.6">
+    <row r="1" spans="1:40" ht="151.35" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:40" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A2" s="39" t="s">
         <v>0</v>
       </c>
@@ -13571,7 +13595,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:40" hidden="1">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>40</v>
       </c>
@@ -13686,7 +13710,7 @@
       </c>
       <c r="AN3" s="83"/>
     </row>
-    <row r="4" spans="1:40" s="26" customFormat="1" ht="132.6" hidden="1">
+    <row r="4" spans="1:40" s="26" customFormat="1" ht="132.6" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
         <v>53</v>
       </c>
@@ -13803,7 +13827,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="5" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="5" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
         <v>63</v>
       </c>
@@ -13920,7 +13944,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="6" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="6" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
         <v>70</v>
       </c>
@@ -14029,7 +14053,7 @@
       </c>
       <c r="AN6" s="83"/>
     </row>
-    <row r="7" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="7" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="22" t="s">
         <v>78</v>
       </c>
@@ -14144,7 +14168,7 @@
       </c>
       <c r="AN7" s="83"/>
     </row>
-    <row r="8" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="8" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
         <v>85</v>
       </c>
@@ -14238,10 +14262,12 @@
         <v>0</v>
       </c>
       <c r="AL8" s="1"/>
-      <c r="AM8" s="1"/>
+      <c r="AM8" s="1" t="s">
+        <v>1498</v>
+      </c>
       <c r="AN8" s="83"/>
     </row>
-    <row r="9" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
+    <row r="9" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
         <v>90</v>
       </c>
@@ -14358,7 +14384,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="10" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="10" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>97</v>
       </c>
@@ -14475,7 +14501,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="11" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="11" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="22" t="s">
         <v>103</v>
       </c>
@@ -14588,7 +14614,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="12" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="12" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
         <v>108</v>
       </c>
@@ -14657,20 +14683,34 @@
         <f t="shared" si="0"/>
         <v>32.190310400000001</v>
       </c>
-      <c r="Z12" s="10"/>
-      <c r="AA12" s="10"/>
-      <c r="AB12" s="10"/>
-      <c r="AC12" s="10"/>
-      <c r="AD12" s="10"/>
-      <c r="AE12" s="10"/>
-      <c r="AF12" s="10"/>
+      <c r="Z12" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA12" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB12" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC12" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD12" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE12" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF12" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="AG12" s="38">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AH12" s="51" t="str">
+        <v>1</v>
+      </c>
+      <c r="AH12" s="51">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>32.190310400000001</v>
       </c>
       <c r="AI12" s="64">
         <v>2</v>
@@ -14678,14 +14718,18 @@
       <c r="AJ12" s="87" t="s">
         <v>110</v>
       </c>
-      <c r="AK12" s="65">
+      <c r="AK12" s="95">
         <v>0</v>
       </c>
       <c r="AL12" s="1"/>
-      <c r="AM12" s="1"/>
-      <c r="AN12" s="83"/>
+      <c r="AM12" s="1" t="s">
+        <v>1497</v>
+      </c>
+      <c r="AN12" s="83">
+        <v>46204</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
+    <row r="13" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A13" s="22" t="s">
         <v>111</v>
       </c>
@@ -14781,10 +14825,12 @@
         <v>0</v>
       </c>
       <c r="AL13" s="1"/>
-      <c r="AM13" s="1"/>
+      <c r="AM13" s="1" t="s">
+        <v>1503</v>
+      </c>
       <c r="AN13" s="83"/>
     </row>
-    <row r="14" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
+    <row r="14" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
         <v>115</v>
       </c>
@@ -14863,14 +14909,16 @@
       <c r="AC14" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AD14" s="10"/>
+      <c r="AD14" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="AE14" s="10"/>
       <c r="AF14" s="10" t="s">
         <v>50</v>
       </c>
       <c r="AG14" s="38">
         <f t="shared" si="1"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AH14" s="51" t="str">
         <f t="shared" si="2"/>
@@ -14882,14 +14930,18 @@
       <c r="AJ14" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="AK14" s="65">
+      <c r="AK14" s="95">
         <v>0</v>
       </c>
       <c r="AL14" s="1"/>
-      <c r="AM14" s="1"/>
-      <c r="AN14" s="83"/>
+      <c r="AM14" s="1" t="s">
+        <v>1500</v>
+      </c>
+      <c r="AN14" s="83">
+        <v>46204</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="15" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="22" t="s">
         <v>118</v>
       </c>
@@ -14973,16 +15025,22 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="AI15" s="64"/>
-      <c r="AJ15" s="86"/>
+      <c r="AI15" s="64">
+        <v>1</v>
+      </c>
+      <c r="AJ15" s="86" t="s">
+        <v>1499</v>
+      </c>
       <c r="AK15" s="65">
         <v>0</v>
       </c>
       <c r="AL15" s="1"/>
-      <c r="AM15" s="1"/>
+      <c r="AM15" s="1" t="s">
+        <v>1502</v>
+      </c>
       <c r="AN15" s="83"/>
     </row>
-    <row r="16" spans="1:40" s="26" customFormat="1" ht="30.6" hidden="1">
+    <row r="16" spans="1:40" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
         <v>122</v>
       </c>
@@ -15099,7 +15157,7 @@
         <v>46235</v>
       </c>
     </row>
-    <row r="17" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
+    <row r="17" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A17" s="22" t="s">
         <v>127</v>
       </c>
@@ -15193,10 +15251,12 @@
         <v>0</v>
       </c>
       <c r="AL17" s="1"/>
-      <c r="AM17" s="1"/>
+      <c r="AM17" s="1" t="s">
+        <v>1501</v>
+      </c>
       <c r="AN17" s="83"/>
     </row>
-    <row r="18" spans="1:40" s="26" customFormat="1" ht="51" hidden="1">
+    <row r="18" spans="1:40" s="26" customFormat="1" ht="51" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
         <v>132</v>
       </c>
@@ -15293,7 +15353,7 @@
       <c r="AM18" s="1"/>
       <c r="AN18" s="83"/>
     </row>
-    <row r="19" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="19" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="22" t="s">
         <v>137</v>
       </c>
@@ -15392,7 +15452,7 @@
       </c>
       <c r="AN19" s="83"/>
     </row>
-    <row r="20" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="20" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
         <v>142</v>
       </c>
@@ -15489,7 +15549,7 @@
       <c r="AM20" s="1"/>
       <c r="AN20" s="83"/>
     </row>
-    <row r="21" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="21" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="22" t="s">
         <v>147</v>
       </c>
@@ -15604,7 +15664,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="22" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="22" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
         <v>154</v>
       </c>
@@ -15697,7 +15757,7 @@
       <c r="AM22" s="1"/>
       <c r="AN22" s="83"/>
     </row>
-    <row r="23" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="23" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="22" t="s">
         <v>156</v>
       </c>
@@ -15812,7 +15872,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="24" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="24" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
         <v>160</v>
       </c>
@@ -15905,7 +15965,7 @@
       <c r="AM24" s="1"/>
       <c r="AN24" s="83"/>
     </row>
-    <row r="25" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="25" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="22" t="s">
         <v>161</v>
       </c>
@@ -15998,7 +16058,7 @@
       <c r="AM25" s="1"/>
       <c r="AN25" s="83"/>
     </row>
-    <row r="26" spans="1:40" s="26" customFormat="1" ht="30.6" hidden="1">
+    <row r="26" spans="1:40" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
         <v>163</v>
       </c>
@@ -16093,7 +16153,7 @@
       <c r="AM26" s="1"/>
       <c r="AN26" s="83"/>
     </row>
-    <row r="27" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="27" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="22" t="s">
         <v>166</v>
       </c>
@@ -16186,7 +16246,7 @@
       <c r="AM27" s="1"/>
       <c r="AN27" s="83"/>
     </row>
-    <row r="28" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="28" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="22" t="s">
         <v>169</v>
       </c>
@@ -16281,7 +16341,7 @@
       <c r="AM28" s="62"/>
       <c r="AN28" s="83"/>
     </row>
-    <row r="29" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="29" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="22" t="s">
         <v>172</v>
       </c>
@@ -16376,7 +16436,7 @@
       <c r="AM29" s="1"/>
       <c r="AN29" s="83"/>
     </row>
-    <row r="30" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="30" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
         <v>175</v>
       </c>
@@ -16469,7 +16529,7 @@
       <c r="AM30" s="1"/>
       <c r="AN30" s="83"/>
     </row>
-    <row r="31" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="31" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="22" t="s">
         <v>179</v>
       </c>
@@ -16556,7 +16616,7 @@
       <c r="AM31" s="1"/>
       <c r="AN31" s="83"/>
     </row>
-    <row r="32" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="32" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
         <v>181</v>
       </c>
@@ -16673,7 +16733,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="33" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="33" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="22" t="s">
         <v>184</v>
       </c>
@@ -16788,7 +16848,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="34" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="34" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
         <v>190</v>
       </c>
@@ -16881,7 +16941,7 @@
       <c r="AM34" s="1"/>
       <c r="AN34" s="83"/>
     </row>
-    <row r="35" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="35" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="22" t="s">
         <v>194</v>
       </c>
@@ -16998,7 +17058,7 @@
         <v>46235</v>
       </c>
     </row>
-    <row r="36" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="36" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="22" t="s">
         <v>200</v>
       </c>
@@ -17093,7 +17153,7 @@
       <c r="AM36" s="1"/>
       <c r="AN36" s="83"/>
     </row>
-    <row r="37" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="37" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="22" t="s">
         <v>201</v>
       </c>
@@ -17180,7 +17240,7 @@
       <c r="AM37" s="1"/>
       <c r="AN37" s="83"/>
     </row>
-    <row r="38" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="38" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="22" t="s">
         <v>204</v>
       </c>
@@ -17281,7 +17341,7 @@
       <c r="AM38" s="1"/>
       <c r="AN38" s="83"/>
     </row>
-    <row r="39" spans="1:40" s="26" customFormat="1" ht="71.45" hidden="1">
+    <row r="39" spans="1:40" s="26" customFormat="1" ht="71.400000000000006" x14ac:dyDescent="0.3">
       <c r="A39" s="22" t="s">
         <v>207</v>
       </c>
@@ -17400,7 +17460,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="40" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="40" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
         <v>211</v>
       </c>
@@ -17493,7 +17553,7 @@
       <c r="AM40" s="1"/>
       <c r="AN40" s="83"/>
     </row>
-    <row r="41" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="41" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="22" t="s">
         <v>214</v>
       </c>
@@ -17586,7 +17646,7 @@
       <c r="AM41" s="1"/>
       <c r="AN41" s="83"/>
     </row>
-    <row r="42" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="42" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>217</v>
       </c>
@@ -17679,7 +17739,7 @@
       <c r="AM42" s="1"/>
       <c r="AN42" s="83"/>
     </row>
-    <row r="43" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="43" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="22" t="s">
         <v>221</v>
       </c>
@@ -17772,7 +17832,7 @@
       <c r="AM43" s="1"/>
       <c r="AN43" s="83"/>
     </row>
-    <row r="44" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="44" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="22" t="s">
         <v>225</v>
       </c>
@@ -17889,7 +17949,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="45" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="45" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="22" t="s">
         <v>230</v>
       </c>
@@ -18002,7 +18062,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="46" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="46" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="22" t="s">
         <v>234</v>
       </c>
@@ -18095,7 +18155,7 @@
       <c r="AM46" s="1"/>
       <c r="AN46" s="83"/>
     </row>
-    <row r="47" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="47" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="22" t="s">
         <v>241</v>
       </c>
@@ -18188,7 +18248,7 @@
       <c r="AM47" s="1"/>
       <c r="AN47" s="83"/>
     </row>
-    <row r="48" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="48" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="22" t="s">
         <v>244</v>
       </c>
@@ -18281,7 +18341,7 @@
       <c r="AM48" s="1"/>
       <c r="AN48" s="83"/>
     </row>
-    <row r="49" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="49" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="22" t="s">
         <v>246</v>
       </c>
@@ -18374,7 +18434,7 @@
       <c r="AM49" s="1"/>
       <c r="AN49" s="83"/>
     </row>
-    <row r="50" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="50" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="22" t="s">
         <v>248</v>
       </c>
@@ -18467,7 +18527,7 @@
       <c r="AM50" s="1"/>
       <c r="AN50" s="83"/>
     </row>
-    <row r="51" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="51" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="22" t="s">
         <v>251</v>
       </c>
@@ -18560,7 +18620,7 @@
       <c r="AM51" s="1"/>
       <c r="AN51" s="83"/>
     </row>
-    <row r="52" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="52" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="22" t="s">
         <v>254</v>
       </c>
@@ -18653,7 +18713,7 @@
       <c r="AM52" s="1"/>
       <c r="AN52" s="83"/>
     </row>
-    <row r="53" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="53" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="22" t="s">
         <v>257</v>
       </c>
@@ -18746,7 +18806,7 @@
       <c r="AM53" s="1"/>
       <c r="AN53" s="83"/>
     </row>
-    <row r="54" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="54" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="22" t="s">
         <v>259</v>
       </c>
@@ -18839,7 +18899,7 @@
       <c r="AM54" s="1"/>
       <c r="AN54" s="83"/>
     </row>
-    <row r="55" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="55" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="22" t="s">
         <v>263</v>
       </c>
@@ -18932,7 +18992,7 @@
       <c r="AM55" s="1"/>
       <c r="AN55" s="83"/>
     </row>
-    <row r="56" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="56" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="22" t="s">
         <v>266</v>
       </c>
@@ -19049,7 +19109,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="57" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="57" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="22" t="s">
         <v>270</v>
       </c>
@@ -19142,7 +19202,7 @@
       <c r="AM57" s="1"/>
       <c r="AN57" s="83"/>
     </row>
-    <row r="58" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="58" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="22" t="s">
         <v>271</v>
       </c>
@@ -19235,7 +19295,7 @@
       <c r="AM58" s="1"/>
       <c r="AN58" s="83"/>
     </row>
-    <row r="59" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="59" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="22" t="s">
         <v>273</v>
       </c>
@@ -19328,7 +19388,7 @@
       <c r="AM59" s="1"/>
       <c r="AN59" s="83"/>
     </row>
-    <row r="60" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
+    <row r="60" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A60" s="22" t="s">
         <v>275</v>
       </c>
@@ -19439,7 +19499,7 @@
       </c>
       <c r="AN60" s="83"/>
     </row>
-    <row r="61" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="61" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="22" t="s">
         <v>281</v>
       </c>
@@ -19552,7 +19612,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="62" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="62" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="22" t="s">
         <v>287</v>
       </c>
@@ -19645,7 +19705,7 @@
       <c r="AM62" s="1"/>
       <c r="AN62" s="83"/>
     </row>
-    <row r="63" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="63" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="22" t="s">
         <v>289</v>
       </c>
@@ -19738,7 +19798,7 @@
       <c r="AM63" s="1"/>
       <c r="AN63" s="83"/>
     </row>
-    <row r="64" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="64" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="22" t="s">
         <v>292</v>
       </c>
@@ -19831,7 +19891,7 @@
       <c r="AM64" s="1"/>
       <c r="AN64" s="83"/>
     </row>
-    <row r="65" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="65" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="22" t="s">
         <v>294</v>
       </c>
@@ -19926,7 +19986,7 @@
       <c r="AM65" s="1"/>
       <c r="AN65" s="83"/>
     </row>
-    <row r="66" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="66" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="22" t="s">
         <v>296</v>
       </c>
@@ -20021,7 +20081,7 @@
       <c r="AM66" s="1"/>
       <c r="AN66" s="83"/>
     </row>
-    <row r="67" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="67" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="22" t="s">
         <v>298</v>
       </c>
@@ -20110,7 +20170,7 @@
       <c r="AM67" s="1"/>
       <c r="AN67" s="83"/>
     </row>
-    <row r="68" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="68" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="22" t="s">
         <v>299</v>
       </c>
@@ -20203,7 +20263,7 @@
       <c r="AM68" s="1"/>
       <c r="AN68" s="83"/>
     </row>
-    <row r="69" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="69" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="22" t="s">
         <v>301</v>
       </c>
@@ -20298,7 +20358,7 @@
       <c r="AM69" s="1"/>
       <c r="AN69" s="83"/>
     </row>
-    <row r="70" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="70" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="22" t="s">
         <v>304</v>
       </c>
@@ -20391,7 +20451,7 @@
       <c r="AM70" s="1"/>
       <c r="AN70" s="83"/>
     </row>
-    <row r="71" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="71" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="22" t="s">
         <v>306</v>
       </c>
@@ -20484,7 +20544,7 @@
       <c r="AM71" s="1"/>
       <c r="AN71" s="83"/>
     </row>
-    <row r="72" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="72" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="22" t="s">
         <v>309</v>
       </c>
@@ -20579,7 +20639,7 @@
       <c r="AM72" s="1"/>
       <c r="AN72" s="83"/>
     </row>
-    <row r="73" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="73" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="22" t="s">
         <v>312</v>
       </c>
@@ -20672,7 +20732,7 @@
       <c r="AM73" s="1"/>
       <c r="AN73" s="83"/>
     </row>
-    <row r="74" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="74" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="22" t="s">
         <v>314</v>
       </c>
@@ -20765,7 +20825,7 @@
       <c r="AM74" s="1"/>
       <c r="AN74" s="83"/>
     </row>
-    <row r="75" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="75" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="22" t="s">
         <v>316</v>
       </c>
@@ -20856,7 +20916,7 @@
       <c r="AM75" s="1"/>
       <c r="AN75" s="83"/>
     </row>
-    <row r="76" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="76" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="22" t="s">
         <v>319</v>
       </c>
@@ -20949,7 +21009,7 @@
       <c r="AM76" s="1"/>
       <c r="AN76" s="83"/>
     </row>
-    <row r="77" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="77" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="22" t="s">
         <v>323</v>
       </c>
@@ -21040,7 +21100,7 @@
       <c r="AM77" s="1"/>
       <c r="AN77" s="83"/>
     </row>
-    <row r="78" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="78" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="22" t="s">
         <v>325</v>
       </c>
@@ -21153,7 +21213,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="79" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="79" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" s="22" t="s">
         <v>329</v>
       </c>
@@ -21246,7 +21306,7 @@
       <c r="AM79" s="1"/>
       <c r="AN79" s="83"/>
     </row>
-    <row r="80" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="80" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A80" s="22" t="s">
         <v>332</v>
       </c>
@@ -21359,7 +21419,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="81" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="81" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A81" s="22" t="s">
         <v>336</v>
       </c>
@@ -21454,7 +21514,7 @@
       <c r="AM81" s="1"/>
       <c r="AN81" s="83"/>
     </row>
-    <row r="82" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="82" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="22" t="s">
         <v>338</v>
       </c>
@@ -21547,7 +21607,7 @@
       <c r="AM82" s="1"/>
       <c r="AN82" s="83"/>
     </row>
-    <row r="83" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="83" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A83" s="22" t="s">
         <v>340</v>
       </c>
@@ -21640,7 +21700,7 @@
       <c r="AM83" s="1"/>
       <c r="AN83" s="83"/>
     </row>
-    <row r="84" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="84" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A84" s="22" t="s">
         <v>342</v>
       </c>
@@ -21735,7 +21795,7 @@
       <c r="AM84" s="1"/>
       <c r="AN84" s="83"/>
     </row>
-    <row r="85" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="85" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="22" t="s">
         <v>345</v>
       </c>
@@ -21828,7 +21888,7 @@
       <c r="AM85" s="1"/>
       <c r="AN85" s="83"/>
     </row>
-    <row r="86" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="86" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="22" t="s">
         <v>347</v>
       </c>
@@ -21917,7 +21977,7 @@
       <c r="AM86" s="1"/>
       <c r="AN86" s="83"/>
     </row>
-    <row r="87" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="87" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="22" t="s">
         <v>352</v>
       </c>
@@ -22010,7 +22070,7 @@
       <c r="AM87" s="1"/>
       <c r="AN87" s="83"/>
     </row>
-    <row r="88" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="88" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A88" s="22" t="s">
         <v>354</v>
       </c>
@@ -22105,7 +22165,7 @@
       <c r="AM88" s="1"/>
       <c r="AN88" s="83"/>
     </row>
-    <row r="89" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="89" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="22" t="s">
         <v>359</v>
       </c>
@@ -22198,7 +22258,7 @@
       <c r="AM89" s="1"/>
       <c r="AN89" s="83"/>
     </row>
-    <row r="90" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="90" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A90" s="22" t="s">
         <v>362</v>
       </c>
@@ -22291,7 +22351,7 @@
       <c r="AM90" s="1"/>
       <c r="AN90" s="83"/>
     </row>
-    <row r="91" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="91" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A91" s="22" t="s">
         <v>364</v>
       </c>
@@ -22384,7 +22444,7 @@
       <c r="AM91" s="1"/>
       <c r="AN91" s="83"/>
     </row>
-    <row r="92" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="92" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A92" s="22" t="s">
         <v>367</v>
       </c>
@@ -22477,7 +22537,7 @@
       <c r="AM92" s="1"/>
       <c r="AN92" s="83"/>
     </row>
-    <row r="93" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="93" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A93" s="22" t="s">
         <v>370</v>
       </c>
@@ -22568,7 +22628,7 @@
       <c r="AM93" s="1"/>
       <c r="AN93" s="83"/>
     </row>
-    <row r="94" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="94" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A94" s="22" t="s">
         <v>372</v>
       </c>
@@ -22661,7 +22721,7 @@
       <c r="AM94" s="1"/>
       <c r="AN94" s="83"/>
     </row>
-    <row r="95" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="95" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A95" s="15" t="s">
         <v>375</v>
       </c>
@@ -22754,7 +22814,7 @@
       <c r="AM95" s="1"/>
       <c r="AN95" s="83"/>
     </row>
-    <row r="96" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="96" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A96" s="22" t="s">
         <v>378</v>
       </c>
@@ -22867,7 +22927,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="97" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="97" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A97" s="22" t="s">
         <v>381</v>
       </c>
@@ -22954,7 +23014,7 @@
       <c r="AM97" s="1"/>
       <c r="AN97" s="83"/>
     </row>
-    <row r="98" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="98" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>382</v>
       </c>
@@ -23049,7 +23109,7 @@
       <c r="AM98" s="1"/>
       <c r="AN98" s="83"/>
     </row>
-    <row r="99" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="99" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A99" s="22" t="s">
         <v>386</v>
       </c>
@@ -23144,7 +23204,7 @@
       <c r="AM99" s="1"/>
       <c r="AN99" s="83"/>
     </row>
-    <row r="100" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="100" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="22" t="s">
         <v>388</v>
       </c>
@@ -23237,7 +23297,7 @@
       <c r="AM100" s="1"/>
       <c r="AN100" s="83"/>
     </row>
-    <row r="101" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="101" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A101" s="22" t="s">
         <v>391</v>
       </c>
@@ -23330,7 +23390,7 @@
       <c r="AM101" s="1"/>
       <c r="AN101" s="83"/>
     </row>
-    <row r="102" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="102" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A102" s="22" t="s">
         <v>394</v>
       </c>
@@ -23419,7 +23479,7 @@
       <c r="AM102" s="1"/>
       <c r="AN102" s="83"/>
     </row>
-    <row r="103" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="103" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A103" s="22" t="s">
         <v>397</v>
       </c>
@@ -23512,7 +23572,7 @@
       <c r="AM103" s="1"/>
       <c r="AN103" s="83"/>
     </row>
-    <row r="104" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="104" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A104" s="22" t="s">
         <v>398</v>
       </c>
@@ -23607,7 +23667,7 @@
       <c r="AM104" s="1"/>
       <c r="AN104" s="83"/>
     </row>
-    <row r="105" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="105" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A105" s="22" t="s">
         <v>400</v>
       </c>
@@ -23694,7 +23754,7 @@
       <c r="AM105" s="1"/>
       <c r="AN105" s="83"/>
     </row>
-    <row r="106" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="106" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A106" s="22" t="s">
         <v>402</v>
       </c>
@@ -23787,7 +23847,7 @@
       <c r="AM106" s="1"/>
       <c r="AN106" s="83"/>
     </row>
-    <row r="107" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="107" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A107" s="15" t="s">
         <v>404</v>
       </c>
@@ -23874,7 +23934,7 @@
       <c r="AM107" s="1"/>
       <c r="AN107" s="83"/>
     </row>
-    <row r="108" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="108" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A108" s="22" t="s">
         <v>406</v>
       </c>
@@ -23965,7 +24025,7 @@
       <c r="AM108" s="1"/>
       <c r="AN108" s="83"/>
     </row>
-    <row r="109" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="109" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A109" s="22" t="s">
         <v>408</v>
       </c>
@@ -24058,7 +24118,7 @@
       <c r="AM109" s="1"/>
       <c r="AN109" s="83"/>
     </row>
-    <row r="110" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="110" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A110" s="22" t="s">
         <v>410</v>
       </c>
@@ -24173,7 +24233,7 @@
       </c>
       <c r="AN110" s="83"/>
     </row>
-    <row r="111" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="111" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A111" s="22" t="s">
         <v>414</v>
       </c>
@@ -24268,7 +24328,7 @@
       <c r="AM111" s="1"/>
       <c r="AN111" s="83"/>
     </row>
-    <row r="112" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="112" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A112" s="22" t="s">
         <v>416</v>
       </c>
@@ -24383,7 +24443,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="113" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="113" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A113" s="22" t="s">
         <v>419</v>
       </c>
@@ -24472,7 +24532,7 @@
       <c r="AM113" s="1"/>
       <c r="AN113" s="83"/>
     </row>
-    <row r="114" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="114" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A114" s="22" t="s">
         <v>423</v>
       </c>
@@ -24559,7 +24619,7 @@
       <c r="AM114" s="1"/>
       <c r="AN114" s="83"/>
     </row>
-    <row r="115" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="115" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>424</v>
       </c>
@@ -24652,7 +24712,7 @@
       <c r="AM115" s="1"/>
       <c r="AN115" s="83"/>
     </row>
-    <row r="116" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="116" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A116" s="22" t="s">
         <v>426</v>
       </c>
@@ -24737,7 +24797,7 @@
       <c r="AM116" s="1"/>
       <c r="AN116" s="83"/>
     </row>
-    <row r="117" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="117" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A117" s="22" t="s">
         <v>428</v>
       </c>
@@ -24832,7 +24892,7 @@
       <c r="AM117" s="1"/>
       <c r="AN117" s="83"/>
     </row>
-    <row r="118" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="118" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A118" s="22" t="s">
         <v>430</v>
       </c>
@@ -24925,7 +24985,7 @@
       <c r="AM118" s="1"/>
       <c r="AN118" s="83"/>
     </row>
-    <row r="119" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="119" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A119" s="22" t="s">
         <v>432</v>
       </c>
@@ -25016,7 +25076,7 @@
       <c r="AM119" s="1"/>
       <c r="AN119" s="83"/>
     </row>
-    <row r="120" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="120" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A120" s="15" t="s">
         <v>434</v>
       </c>
@@ -25101,7 +25161,7 @@
       <c r="AM120" s="1"/>
       <c r="AN120" s="83"/>
     </row>
-    <row r="121" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="121" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A121" s="22" t="s">
         <v>435</v>
       </c>
@@ -25192,7 +25252,7 @@
       <c r="AM121" s="1"/>
       <c r="AN121" s="83"/>
     </row>
-    <row r="122" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="122" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A122" s="15" t="s">
         <v>437</v>
       </c>
@@ -25279,7 +25339,7 @@
       <c r="AM122" s="1"/>
       <c r="AN122" s="83"/>
     </row>
-    <row r="123" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="123" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A123" s="22" t="s">
         <v>438</v>
       </c>
@@ -25390,7 +25450,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="124" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="124" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A124" s="22" t="s">
         <v>440</v>
       </c>
@@ -25475,7 +25535,7 @@
       <c r="AM124" s="1"/>
       <c r="AN124" s="83"/>
     </row>
-    <row r="125" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="125" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A125" s="22" t="s">
         <v>441</v>
       </c>
@@ -25570,7 +25630,7 @@
       <c r="AM125" s="1"/>
       <c r="AN125" s="83"/>
     </row>
-    <row r="126" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="126" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A126" s="22" t="s">
         <v>443</v>
       </c>
@@ -25659,7 +25719,7 @@
       <c r="AM126" s="1"/>
       <c r="AN126" s="83"/>
     </row>
-    <row r="127" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="127" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A127" s="22" t="s">
         <v>446</v>
       </c>
@@ -25752,7 +25812,7 @@
       <c r="AM127" s="1"/>
       <c r="AN127" s="83"/>
     </row>
-    <row r="128" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="128" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A128" s="22" t="s">
         <v>448</v>
       </c>
@@ -25841,7 +25901,7 @@
       <c r="AM128" s="1"/>
       <c r="AN128" s="83"/>
     </row>
-    <row r="129" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="129" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A129" s="15" t="s">
         <v>451</v>
       </c>
@@ -25934,7 +25994,7 @@
       <c r="AM129" s="1"/>
       <c r="AN129" s="83"/>
     </row>
-    <row r="130" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="130" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A130" s="22" t="s">
         <v>453</v>
       </c>
@@ -26017,7 +26077,7 @@
       <c r="AM130" s="1"/>
       <c r="AN130" s="83"/>
     </row>
-    <row r="131" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="131" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A131" s="22" t="s">
         <v>454</v>
       </c>
@@ -26100,7 +26160,7 @@
       <c r="AM131" s="1"/>
       <c r="AN131" s="83"/>
     </row>
-    <row r="132" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="132" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A132" s="22" t="s">
         <v>455</v>
       </c>
@@ -26193,7 +26253,7 @@
       <c r="AM132" s="1"/>
       <c r="AN132" s="83"/>
     </row>
-    <row r="133" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="133" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A133" s="22" t="s">
         <v>457</v>
       </c>
@@ -26288,7 +26348,7 @@
       <c r="AM133" s="1"/>
       <c r="AN133" s="83"/>
     </row>
-    <row r="134" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="134" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A134" s="22" t="s">
         <v>459</v>
       </c>
@@ -26379,7 +26439,7 @@
       <c r="AM134" s="1"/>
       <c r="AN134" s="83"/>
     </row>
-    <row r="135" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="135" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A135" s="15" t="s">
         <v>461</v>
       </c>
@@ -26468,7 +26528,7 @@
       <c r="AM135" s="1"/>
       <c r="AN135" s="83"/>
     </row>
-    <row r="136" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="136" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A136" s="22" t="s">
         <v>463</v>
       </c>
@@ -26559,7 +26619,7 @@
       <c r="AM136" s="1"/>
       <c r="AN136" s="83"/>
     </row>
-    <row r="137" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="137" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A137" s="15" t="s">
         <v>465</v>
       </c>
@@ -26644,7 +26704,7 @@
       <c r="AM137" s="1"/>
       <c r="AN137" s="83"/>
     </row>
-    <row r="138" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="138" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A138" s="22" t="s">
         <v>467</v>
       </c>
@@ -26735,7 +26795,7 @@
       <c r="AM138" s="1"/>
       <c r="AN138" s="83"/>
     </row>
-    <row r="139" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="139" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A139" s="15" t="s">
         <v>468</v>
       </c>
@@ -26822,7 +26882,7 @@
       <c r="AM139" s="1"/>
       <c r="AN139" s="83"/>
     </row>
-    <row r="140" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="140" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A140" s="22" t="s">
         <v>471</v>
       </c>
@@ -26913,7 +26973,7 @@
       <c r="AM140" s="1"/>
       <c r="AN140" s="83"/>
     </row>
-    <row r="141" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="141" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A141" s="22" t="s">
         <v>474</v>
       </c>
@@ -26998,7 +27058,7 @@
       <c r="AM141" s="1"/>
       <c r="AN141" s="83"/>
     </row>
-    <row r="142" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="142" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A142" s="15" t="s">
         <v>475</v>
       </c>
@@ -27089,7 +27149,7 @@
       <c r="AM142" s="1"/>
       <c r="AN142" s="83"/>
     </row>
-    <row r="143" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="143" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A143" s="15" t="s">
         <v>477</v>
       </c>
@@ -27176,7 +27236,7 @@
       <c r="AM143" s="1"/>
       <c r="AN143" s="83"/>
     </row>
-    <row r="144" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="144" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A144" s="15" t="s">
         <v>480</v>
       </c>
@@ -27271,7 +27331,7 @@
       <c r="AM144" s="1"/>
       <c r="AN144" s="83"/>
     </row>
-    <row r="145" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="145" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A145" s="15" t="s">
         <v>482</v>
       </c>
@@ -27358,7 +27418,7 @@
       <c r="AM145" s="1"/>
       <c r="AN145" s="83"/>
     </row>
-    <row r="146" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="146" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A146" s="15" t="s">
         <v>483</v>
       </c>
@@ -27443,7 +27503,7 @@
       <c r="AM146" s="1"/>
       <c r="AN146" s="83"/>
     </row>
-    <row r="147" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="147" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A147" s="15" t="s">
         <v>484</v>
       </c>
@@ -27524,7 +27584,7 @@
       <c r="AM147" s="1"/>
       <c r="AN147" s="83"/>
     </row>
-    <row r="148" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="148" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A148" s="15" t="s">
         <v>485</v>
       </c>
@@ -27617,7 +27677,7 @@
       <c r="AM148" s="1"/>
       <c r="AN148" s="83"/>
     </row>
-    <row r="149" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="149" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A149" s="15" t="s">
         <v>487</v>
       </c>
@@ -27708,7 +27768,7 @@
       <c r="AM149" s="1"/>
       <c r="AN149" s="83"/>
     </row>
-    <row r="150" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="150" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A150" s="15" t="s">
         <v>489</v>
       </c>
@@ -27789,7 +27849,7 @@
       <c r="AM150" s="1"/>
       <c r="AN150" s="83"/>
     </row>
-    <row r="151" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="151" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A151" s="15" t="s">
         <v>490</v>
       </c>
@@ -27876,7 +27936,7 @@
       <c r="AM151" s="1"/>
       <c r="AN151" s="83"/>
     </row>
-    <row r="152" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="152" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A152" s="15" t="s">
         <v>492</v>
       </c>
@@ -27967,7 +28027,7 @@
       <c r="AM152" s="1"/>
       <c r="AN152" s="83"/>
     </row>
-    <row r="153" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="153" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A153" s="15" t="s">
         <v>495</v>
       </c>
@@ -28054,7 +28114,7 @@
       <c r="AM153" s="1"/>
       <c r="AN153" s="83"/>
     </row>
-    <row r="154" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="154" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A154" s="15" t="s">
         <v>497</v>
       </c>
@@ -28141,7 +28201,7 @@
       <c r="AM154" s="1"/>
       <c r="AN154" s="83"/>
     </row>
-    <row r="155" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="155" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A155" s="15" t="s">
         <v>499</v>
       </c>
@@ -28228,7 +28288,7 @@
       <c r="AM155" s="1"/>
       <c r="AN155" s="83"/>
     </row>
-    <row r="156" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="156" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A156" s="15" t="s">
         <v>501</v>
       </c>
@@ -28317,7 +28377,7 @@
       <c r="AM156" s="1"/>
       <c r="AN156" s="83"/>
     </row>
-    <row r="157" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="157" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A157" s="15" t="s">
         <v>504</v>
       </c>
@@ -28404,7 +28464,7 @@
       <c r="AM157" s="1"/>
       <c r="AN157" s="83"/>
     </row>
-    <row r="158" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="158" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A158" s="15" t="s">
         <v>506</v>
       </c>
@@ -28491,7 +28551,7 @@
       <c r="AM158" s="1"/>
       <c r="AN158" s="83"/>
     </row>
-    <row r="159" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="159" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A159" s="15" t="s">
         <v>508</v>
       </c>
@@ -28580,7 +28640,7 @@
       <c r="AM159" s="1"/>
       <c r="AN159" s="83"/>
     </row>
-    <row r="160" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="160" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A160" s="15" t="s">
         <v>510</v>
       </c>
@@ -28667,7 +28727,7 @@
       <c r="AM160" s="1"/>
       <c r="AN160" s="83"/>
     </row>
-    <row r="161" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="161" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A161" s="15" t="s">
         <v>512</v>
       </c>
@@ -28754,7 +28814,7 @@
       <c r="AM161" s="1"/>
       <c r="AN161" s="83"/>
     </row>
-    <row r="162" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="162" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A162" s="15" t="s">
         <v>514</v>
       </c>
@@ -28845,7 +28905,7 @@
       <c r="AM162" s="1"/>
       <c r="AN162" s="83"/>
     </row>
-    <row r="163" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="163" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A163" s="15" t="s">
         <v>517</v>
       </c>
@@ -28932,7 +28992,7 @@
       <c r="AM163" s="1"/>
       <c r="AN163" s="83"/>
     </row>
-    <row r="164" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="164" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A164" s="15" t="s">
         <v>519</v>
       </c>
@@ -29019,7 +29079,7 @@
       <c r="AM164" s="1"/>
       <c r="AN164" s="83"/>
     </row>
-    <row r="165" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="165" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A165" s="15" t="s">
         <v>521</v>
       </c>
@@ -29108,7 +29168,7 @@
       <c r="AM165" s="1"/>
       <c r="AN165" s="83"/>
     </row>
-    <row r="166" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="166" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A166" s="15" t="s">
         <v>523</v>
       </c>
@@ -29197,7 +29257,7 @@
       <c r="AM166" s="1"/>
       <c r="AN166" s="83"/>
     </row>
-    <row r="167" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="167" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A167" s="15" t="s">
         <v>525</v>
       </c>
@@ -29286,7 +29346,7 @@
       <c r="AM167" s="1"/>
       <c r="AN167" s="83"/>
     </row>
-    <row r="168" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="168" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A168" s="15" t="s">
         <v>527</v>
       </c>
@@ -29375,7 +29435,7 @@
       <c r="AM168" s="1"/>
       <c r="AN168" s="83"/>
     </row>
-    <row r="169" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="169" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A169" s="15" t="s">
         <v>529</v>
       </c>
@@ -29462,7 +29522,7 @@
       <c r="AM169" s="1"/>
       <c r="AN169" s="83"/>
     </row>
-    <row r="170" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="170" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A170" s="15" t="s">
         <v>531</v>
       </c>
@@ -29551,7 +29611,7 @@
       <c r="AM170" s="1"/>
       <c r="AN170" s="83"/>
     </row>
-    <row r="171" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="171" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A171" s="15" t="s">
         <v>533</v>
       </c>
@@ -29640,7 +29700,7 @@
       <c r="AM171" s="1"/>
       <c r="AN171" s="83"/>
     </row>
-    <row r="172" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="172" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A172" s="15" t="s">
         <v>535</v>
       </c>
@@ -29727,7 +29787,7 @@
       <c r="AM172" s="1"/>
       <c r="AN172" s="83"/>
     </row>
-    <row r="173" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="173" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A173" s="15" t="s">
         <v>537</v>
       </c>
@@ -29816,7 +29876,7 @@
       <c r="AM173" s="1"/>
       <c r="AN173" s="83"/>
     </row>
-    <row r="174" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="174" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A174" s="15" t="s">
         <v>539</v>
       </c>
@@ -29905,7 +29965,7 @@
       <c r="AM174" s="1"/>
       <c r="AN174" s="83"/>
     </row>
-    <row r="175" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="175" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A175" s="15" t="s">
         <v>541</v>
       </c>
@@ -29978,7 +30038,7 @@
       <c r="AM175" s="1"/>
       <c r="AN175" s="83"/>
     </row>
-    <row r="176" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="176" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A176" s="15" t="s">
         <v>542</v>
       </c>
@@ -30065,7 +30125,7 @@
       <c r="AM176" s="1"/>
       <c r="AN176" s="83"/>
     </row>
-    <row r="177" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="177" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A177" s="15" t="s">
         <v>545</v>
       </c>
@@ -30150,7 +30210,7 @@
       <c r="AM177" s="1"/>
       <c r="AN177" s="83"/>
     </row>
-    <row r="178" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="178" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A178" s="15" t="s">
         <v>547</v>
       </c>
@@ -30241,7 +30301,7 @@
       <c r="AM178" s="1"/>
       <c r="AN178" s="83"/>
     </row>
-    <row r="179" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="179" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A179" s="15" t="s">
         <v>548</v>
       </c>
@@ -30328,7 +30388,7 @@
       <c r="AM179" s="1"/>
       <c r="AN179" s="83"/>
     </row>
-    <row r="180" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="180" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A180" s="15" t="s">
         <v>552</v>
       </c>
@@ -30443,7 +30503,7 @@
         <v>46204</v>
       </c>
     </row>
-    <row r="181" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="181" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A181" s="15" t="s">
         <v>557</v>
       </c>
@@ -30558,7 +30618,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="182" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="182" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A182" s="15" t="s">
         <v>562</v>
       </c>
@@ -30649,7 +30709,7 @@
       <c r="AM182" s="1"/>
       <c r="AN182" s="83"/>
     </row>
-    <row r="183" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="183" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A183" s="15" t="s">
         <v>564</v>
       </c>
@@ -30738,7 +30798,7 @@
       <c r="AM183" s="1"/>
       <c r="AN183" s="83"/>
     </row>
-    <row r="184" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="184" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A184" s="15" t="s">
         <v>565</v>
       </c>
@@ -30827,7 +30887,7 @@
       <c r="AM184" s="1"/>
       <c r="AN184" s="83"/>
     </row>
-    <row r="185" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="185" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A185" s="15" t="s">
         <v>567</v>
       </c>
@@ -30914,7 +30974,7 @@
       <c r="AM185" s="1"/>
       <c r="AN185" s="83"/>
     </row>
-    <row r="186" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="186" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A186" s="15" t="s">
         <v>570</v>
       </c>
@@ -31001,7 +31061,7 @@
       <c r="AM186" s="1"/>
       <c r="AN186" s="83"/>
     </row>
-    <row r="187" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="187" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A187" s="15" t="s">
         <v>572</v>
       </c>
@@ -31088,7 +31148,7 @@
       <c r="AM187" s="1"/>
       <c r="AN187" s="83"/>
     </row>
-    <row r="188" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="188" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A188" s="15" t="s">
         <v>575</v>
       </c>
@@ -31175,7 +31235,7 @@
       <c r="AM188" s="1"/>
       <c r="AN188" s="83"/>
     </row>
-    <row r="189" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="189" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A189" s="15" t="s">
         <v>578</v>
       </c>
@@ -31262,7 +31322,7 @@
       <c r="AM189" s="1"/>
       <c r="AN189" s="83"/>
     </row>
-    <row r="190" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="190" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A190" s="15" t="s">
         <v>580</v>
       </c>
@@ -31349,7 +31409,7 @@
       <c r="AM190" s="1"/>
       <c r="AN190" s="83"/>
     </row>
-    <row r="191" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="191" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A191" s="15" t="s">
         <v>582</v>
       </c>
@@ -31430,7 +31490,7 @@
       <c r="AM191" s="1"/>
       <c r="AN191" s="83"/>
     </row>
-    <row r="192" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="192" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A192" s="15" t="s">
         <v>584</v>
       </c>
@@ -31517,7 +31577,7 @@
       <c r="AM192" s="1"/>
       <c r="AN192" s="83"/>
     </row>
-    <row r="193" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="193" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A193" s="15" t="s">
         <v>586</v>
       </c>
@@ -31606,7 +31666,7 @@
       <c r="AM193" s="1"/>
       <c r="AN193" s="83"/>
     </row>
-    <row r="194" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="194" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A194" s="15" t="s">
         <v>589</v>
       </c>
@@ -31693,7 +31753,7 @@
       <c r="AM194" s="1"/>
       <c r="AN194" s="83"/>
     </row>
-    <row r="195" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="195" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A195" s="15" t="s">
         <v>592</v>
       </c>
@@ -31780,7 +31840,7 @@
       <c r="AM195" s="1"/>
       <c r="AN195" s="83"/>
     </row>
-    <row r="196" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="196" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A196" s="15" t="s">
         <v>595</v>
       </c>
@@ -31869,7 +31929,7 @@
       <c r="AM196" s="1"/>
       <c r="AN196" s="83"/>
     </row>
-    <row r="197" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="197" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A197" s="15" t="s">
         <v>599</v>
       </c>
@@ -31958,7 +32018,7 @@
       <c r="AM197" s="1"/>
       <c r="AN197" s="83"/>
     </row>
-    <row r="198" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="198" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A198" s="15" t="s">
         <v>601</v>
       </c>
@@ -32047,7 +32107,7 @@
       <c r="AM198" s="1"/>
       <c r="AN198" s="83"/>
     </row>
-    <row r="199" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="199" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A199" s="15" t="s">
         <v>603</v>
       </c>
@@ -32134,7 +32194,7 @@
       <c r="AM199" s="1"/>
       <c r="AN199" s="83"/>
     </row>
-    <row r="200" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="200" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A200" s="15" t="s">
         <v>605</v>
       </c>
@@ -32221,7 +32281,7 @@
       <c r="AM200" s="1"/>
       <c r="AN200" s="83"/>
     </row>
-    <row r="201" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="201" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A201" s="15" t="s">
         <v>607</v>
       </c>
@@ -32308,7 +32368,7 @@
       <c r="AM201" s="1"/>
       <c r="AN201" s="83"/>
     </row>
-    <row r="202" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="202" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A202" s="15" t="s">
         <v>610</v>
       </c>
@@ -32399,7 +32459,7 @@
       <c r="AM202" s="1"/>
       <c r="AN202" s="83"/>
     </row>
-    <row r="203" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="203" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A203" s="15" t="s">
         <v>611</v>
       </c>
@@ -32486,7 +32546,7 @@
       <c r="AM203" s="1"/>
       <c r="AN203" s="83"/>
     </row>
-    <row r="204" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="204" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A204" s="15" t="s">
         <v>612</v>
       </c>
@@ -32573,7 +32633,7 @@
       <c r="AM204" s="1"/>
       <c r="AN204" s="83"/>
     </row>
-    <row r="205" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="205" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A205" s="15" t="s">
         <v>614</v>
       </c>
@@ -32662,7 +32722,7 @@
       <c r="AM205" s="1"/>
       <c r="AN205" s="83"/>
     </row>
-    <row r="206" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="206" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A206" s="15" t="s">
         <v>615</v>
       </c>
@@ -32755,7 +32815,7 @@
       <c r="AM206" s="1"/>
       <c r="AN206" s="83"/>
     </row>
-    <row r="207" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="207" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A207" s="15" t="s">
         <v>616</v>
       </c>
@@ -32842,7 +32902,7 @@
       <c r="AM207" s="1"/>
       <c r="AN207" s="83"/>
     </row>
-    <row r="208" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="208" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A208" s="15" t="s">
         <v>619</v>
       </c>
@@ -32931,7 +32991,7 @@
       <c r="AM208" s="1"/>
       <c r="AN208" s="83"/>
     </row>
-    <row r="209" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="209" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A209" s="15" t="s">
         <v>621</v>
       </c>
@@ -33018,7 +33078,7 @@
       <c r="AM209" s="1"/>
       <c r="AN209" s="83"/>
     </row>
-    <row r="210" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="210" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A210" s="15" t="s">
         <v>623</v>
       </c>
@@ -33105,7 +33165,7 @@
       <c r="AM210" s="1"/>
       <c r="AN210" s="83"/>
     </row>
-    <row r="211" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="211" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A211" s="15" t="s">
         <v>625</v>
       </c>
@@ -33192,7 +33252,7 @@
       <c r="AM211" s="1"/>
       <c r="AN211" s="83"/>
     </row>
-    <row r="212" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="212" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A212" s="15" t="s">
         <v>627</v>
       </c>
@@ -33281,7 +33341,7 @@
       <c r="AM212" s="1"/>
       <c r="AN212" s="83"/>
     </row>
-    <row r="213" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="213" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A213" s="15" t="s">
         <v>629</v>
       </c>
@@ -33368,7 +33428,7 @@
       <c r="AM213" s="1"/>
       <c r="AN213" s="83"/>
     </row>
-    <row r="214" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="214" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A214" s="15" t="s">
         <v>631</v>
       </c>
@@ -33455,7 +33515,7 @@
       <c r="AM214" s="1"/>
       <c r="AN214" s="83"/>
     </row>
-    <row r="215" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="215" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A215" s="15" t="s">
         <v>634</v>
       </c>
@@ -33544,7 +33604,7 @@
       <c r="AM215" s="1"/>
       <c r="AN215" s="83"/>
     </row>
-    <row r="216" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="216" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A216" s="15" t="s">
         <v>637</v>
       </c>
@@ -33629,7 +33689,7 @@
       <c r="AM216" s="1"/>
       <c r="AN216" s="83"/>
     </row>
-    <row r="217" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="217" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A217" s="15" t="s">
         <v>639</v>
       </c>
@@ -33716,7 +33776,7 @@
       <c r="AM217" s="1"/>
       <c r="AN217" s="83"/>
     </row>
-    <row r="218" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="218" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A218" s="15" t="s">
         <v>642</v>
       </c>
@@ -33801,7 +33861,7 @@
       <c r="AM218" s="1"/>
       <c r="AN218" s="83"/>
     </row>
-    <row r="219" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="219" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A219" s="15" t="s">
         <v>644</v>
       </c>
@@ -33886,7 +33946,7 @@
       <c r="AM219" s="1"/>
       <c r="AN219" s="83"/>
     </row>
-    <row r="220" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="220" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A220" s="15" t="s">
         <v>646</v>
       </c>
@@ -33967,7 +34027,7 @@
       <c r="AM220" s="1"/>
       <c r="AN220" s="83"/>
     </row>
-    <row r="221" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="221" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A221" s="15" t="s">
         <v>647</v>
       </c>
@@ -34052,7 +34112,7 @@
       <c r="AM221" s="1"/>
       <c r="AN221" s="83"/>
     </row>
-    <row r="222" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="222" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A222" s="15" t="s">
         <v>650</v>
       </c>
@@ -34137,7 +34197,7 @@
       <c r="AM222" s="1"/>
       <c r="AN222" s="83"/>
     </row>
-    <row r="223" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="223" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A223" s="15" t="s">
         <v>653</v>
       </c>
@@ -34222,7 +34282,7 @@
       <c r="AM223" s="1"/>
       <c r="AN223" s="83"/>
     </row>
-    <row r="224" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="224" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A224" s="15" t="s">
         <v>655</v>
       </c>
@@ -34311,7 +34371,7 @@
       <c r="AM224" s="1"/>
       <c r="AN224" s="83"/>
     </row>
-    <row r="225" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="225" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A225" s="15" t="s">
         <v>657</v>
       </c>
@@ -34394,7 +34454,7 @@
       <c r="AM225" s="1"/>
       <c r="AN225" s="83"/>
     </row>
-    <row r="226" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="226" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A226" s="15" t="s">
         <v>659</v>
       </c>
@@ -34481,7 +34541,7 @@
       <c r="AM226" s="1"/>
       <c r="AN226" s="83"/>
     </row>
-    <row r="227" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="227" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A227" s="15" t="s">
         <v>661</v>
       </c>
@@ -34568,7 +34628,7 @@
       <c r="AM227" s="1"/>
       <c r="AN227" s="83"/>
     </row>
-    <row r="228" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="228" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A228" s="15" t="s">
         <v>664</v>
       </c>
@@ -34653,7 +34713,7 @@
       <c r="AM228" s="1"/>
       <c r="AN228" s="83"/>
     </row>
-    <row r="229" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="229" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A229" s="15" t="s">
         <v>666</v>
       </c>
@@ -34736,7 +34796,7 @@
       <c r="AM229" s="1"/>
       <c r="AN229" s="83"/>
     </row>
-    <row r="230" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="230" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A230" s="15" t="s">
         <v>667</v>
       </c>
@@ -34821,7 +34881,7 @@
       <c r="AM230" s="1"/>
       <c r="AN230" s="83"/>
     </row>
-    <row r="231" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="231" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A231" s="15" t="s">
         <v>669</v>
       </c>
@@ -34906,7 +34966,7 @@
       <c r="AM231" s="1"/>
       <c r="AN231" s="83"/>
     </row>
-    <row r="232" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="232" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A232" s="15" t="s">
         <v>671</v>
       </c>
@@ -34987,7 +35047,7 @@
       <c r="AM232" s="1"/>
       <c r="AN232" s="83"/>
     </row>
-    <row r="233" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="233" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A233" s="15" t="s">
         <v>672</v>
       </c>
@@ -35072,7 +35132,7 @@
       <c r="AM233" s="1"/>
       <c r="AN233" s="83"/>
     </row>
-    <row r="234" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="234" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A234" s="15" t="s">
         <v>674</v>
       </c>
@@ -35161,7 +35221,7 @@
       <c r="AM234" s="1"/>
       <c r="AN234" s="83"/>
     </row>
-    <row r="235" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="235" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A235" s="15" t="s">
         <v>675</v>
       </c>
@@ -35248,7 +35308,7 @@
       <c r="AM235" s="1"/>
       <c r="AN235" s="83"/>
     </row>
-    <row r="236" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="236" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A236" s="15" t="s">
         <v>678</v>
       </c>
@@ -35335,7 +35395,7 @@
       <c r="AM236" s="1"/>
       <c r="AN236" s="83"/>
     </row>
-    <row r="237" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="237" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A237" s="15" t="s">
         <v>680</v>
       </c>
@@ -35422,7 +35482,7 @@
       <c r="AM237" s="1"/>
       <c r="AN237" s="83"/>
     </row>
-    <row r="238" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="238" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A238" s="15" t="s">
         <v>683</v>
       </c>
@@ -35513,7 +35573,7 @@
       <c r="AM238" s="1"/>
       <c r="AN238" s="83"/>
     </row>
-    <row r="239" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="239" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A239" s="15" t="s">
         <v>686</v>
       </c>
@@ -35604,7 +35664,7 @@
       <c r="AM239" s="1"/>
       <c r="AN239" s="83"/>
     </row>
-    <row r="240" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="240" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A240" s="15" t="s">
         <v>688</v>
       </c>
@@ -35695,7 +35755,7 @@
       <c r="AM240" s="1"/>
       <c r="AN240" s="83"/>
     </row>
-    <row r="241" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="241" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A241" s="15" t="s">
         <v>690</v>
       </c>
@@ -35784,7 +35844,7 @@
       <c r="AM241" s="1"/>
       <c r="AN241" s="83"/>
     </row>
-    <row r="242" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="242" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A242" s="15" t="s">
         <v>692</v>
       </c>
@@ -35871,7 +35931,7 @@
       <c r="AM242" s="1"/>
       <c r="AN242" s="83"/>
     </row>
-    <row r="243" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="243" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A243" s="15" t="s">
         <v>694</v>
       </c>
@@ -35964,7 +36024,7 @@
       <c r="AM243" s="1"/>
       <c r="AN243" s="83"/>
     </row>
-    <row r="244" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="244" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A244" s="15" t="s">
         <v>696</v>
       </c>
@@ -36051,7 +36111,7 @@
       <c r="AM244" s="1"/>
       <c r="AN244" s="83"/>
     </row>
-    <row r="245" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="245" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A245" s="15" t="s">
         <v>698</v>
       </c>
@@ -36136,7 +36196,7 @@
       <c r="AM245" s="1"/>
       <c r="AN245" s="83"/>
     </row>
-    <row r="246" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="246" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A246" s="15" t="s">
         <v>700</v>
       </c>
@@ -36223,7 +36283,7 @@
       <c r="AM246" s="1"/>
       <c r="AN246" s="83"/>
     </row>
-    <row r="247" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="247" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A247" s="15" t="s">
         <v>702</v>
       </c>
@@ -36310,7 +36370,7 @@
       <c r="AM247" s="1"/>
       <c r="AN247" s="83"/>
     </row>
-    <row r="248" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="248" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A248" s="15" t="s">
         <v>704</v>
       </c>
@@ -36397,7 +36457,7 @@
       <c r="AM248" s="1"/>
       <c r="AN248" s="83"/>
     </row>
-    <row r="249" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="249" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A249" s="15" t="s">
         <v>706</v>
       </c>
@@ -36484,7 +36544,7 @@
       <c r="AM249" s="1"/>
       <c r="AN249" s="83"/>
     </row>
-    <row r="250" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="250" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A250" s="15" t="s">
         <v>708</v>
       </c>
@@ -36573,7 +36633,7 @@
       <c r="AM250" s="1"/>
       <c r="AN250" s="83"/>
     </row>
-    <row r="251" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="251" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A251" s="15" t="s">
         <v>709</v>
       </c>
@@ -36658,7 +36718,7 @@
       <c r="AM251" s="1"/>
       <c r="AN251" s="83"/>
     </row>
-    <row r="252" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="252" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A252" s="15" t="s">
         <v>711</v>
       </c>
@@ -36743,7 +36803,7 @@
       <c r="AM252" s="1"/>
       <c r="AN252" s="83"/>
     </row>
-    <row r="253" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="253" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A253" s="15" t="s">
         <v>713</v>
       </c>
@@ -36828,7 +36888,7 @@
       <c r="AM253" s="1"/>
       <c r="AN253" s="83"/>
     </row>
-    <row r="254" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="254" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A254" s="15" t="s">
         <v>715</v>
       </c>
@@ -36913,7 +36973,7 @@
       <c r="AM254" s="1"/>
       <c r="AN254" s="83"/>
     </row>
-    <row r="255" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="255" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A255" s="15" t="s">
         <v>717</v>
       </c>
@@ -37000,7 +37060,7 @@
       <c r="AM255" s="1"/>
       <c r="AN255" s="83"/>
     </row>
-    <row r="256" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="256" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A256" s="15" t="s">
         <v>719</v>
       </c>
@@ -37089,7 +37149,7 @@
       <c r="AM256" s="1"/>
       <c r="AN256" s="83"/>
     </row>
-    <row r="257" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="257" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A257" s="15" t="s">
         <v>721</v>
       </c>
@@ -37176,7 +37236,7 @@
       <c r="AM257" s="1"/>
       <c r="AN257" s="83"/>
     </row>
-    <row r="258" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="258" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A258" s="15" t="s">
         <v>723</v>
       </c>
@@ -37263,7 +37323,7 @@
       <c r="AM258" s="1"/>
       <c r="AN258" s="83"/>
     </row>
-    <row r="259" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="259" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A259" s="15" t="s">
         <v>725</v>
       </c>
@@ -37350,7 +37410,7 @@
       <c r="AM259" s="1"/>
       <c r="AN259" s="83"/>
     </row>
-    <row r="260" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="260" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A260" s="15" t="s">
         <v>727</v>
       </c>
@@ -37435,7 +37495,7 @@
       <c r="AM260" s="1"/>
       <c r="AN260" s="83"/>
     </row>
-    <row r="261" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="261" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A261" s="15" t="s">
         <v>728</v>
       </c>
@@ -37516,7 +37576,7 @@
       <c r="AM261" s="1"/>
       <c r="AN261" s="83"/>
     </row>
-    <row r="262" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="262" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A262" s="15" t="s">
         <v>729</v>
       </c>
@@ -37597,7 +37657,7 @@
       <c r="AM262" s="1"/>
       <c r="AN262" s="83"/>
     </row>
-    <row r="263" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="263" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A263" s="15" t="s">
         <v>730</v>
       </c>
@@ -37674,7 +37734,7 @@
       <c r="AM263" s="1"/>
       <c r="AN263" s="83"/>
     </row>
-    <row r="264" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="264" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A264" s="15" t="s">
         <v>732</v>
       </c>
@@ -37755,7 +37815,7 @@
       <c r="AM264" s="1"/>
       <c r="AN264" s="83"/>
     </row>
-    <row r="265" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="265" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A265" s="15" t="s">
         <v>733</v>
       </c>
@@ -37832,7 +37892,7 @@
       <c r="AM265" s="1"/>
       <c r="AN265" s="83"/>
     </row>
-    <row r="266" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="266" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A266" s="15" t="s">
         <v>734</v>
       </c>
@@ -37913,7 +37973,7 @@
       <c r="AM266" s="1"/>
       <c r="AN266" s="83"/>
     </row>
-    <row r="267" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="267" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A267" s="15" t="s">
         <v>735</v>
       </c>
@@ -37996,7 +38056,7 @@
       <c r="AM267" s="1"/>
       <c r="AN267" s="83"/>
     </row>
-    <row r="268" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="268" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A268" s="15" t="s">
         <v>736</v>
       </c>
@@ -38077,7 +38137,7 @@
       <c r="AM268" s="1"/>
       <c r="AN268" s="83"/>
     </row>
-    <row r="269" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="269" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A269" s="15" t="s">
         <v>738</v>
       </c>
@@ -38158,7 +38218,7 @@
       <c r="AM269" s="1"/>
       <c r="AN269" s="83"/>
     </row>
-    <row r="270" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="270" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A270" s="15" t="s">
         <v>739</v>
       </c>
@@ -38239,7 +38299,7 @@
       <c r="AM270" s="1"/>
       <c r="AN270" s="83"/>
     </row>
-    <row r="271" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="271" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A271" s="15" t="s">
         <v>740</v>
       </c>
@@ -38320,7 +38380,7 @@
       <c r="AM271" s="1"/>
       <c r="AN271" s="83"/>
     </row>
-    <row r="272" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="272" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A272" s="31" t="s">
         <v>741</v>
       </c>
@@ -38401,7 +38461,7 @@
       <c r="AM272" s="1"/>
       <c r="AN272" s="83"/>
     </row>
-    <row r="273" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="273" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A273" s="15" t="s">
         <v>742</v>
       </c>
@@ -38484,7 +38544,7 @@
       <c r="AM273" s="1"/>
       <c r="AN273" s="83"/>
     </row>
-    <row r="274" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="274" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A274" s="15" t="s">
         <v>743</v>
       </c>
@@ -38565,7 +38625,7 @@
       <c r="AM274" s="1"/>
       <c r="AN274" s="83"/>
     </row>
-    <row r="275" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="275" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A275" s="15" t="s">
         <v>744</v>
       </c>
@@ -38646,7 +38706,7 @@
       <c r="AM275" s="1"/>
       <c r="AN275" s="83"/>
     </row>
-    <row r="276" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="276" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A276" s="15" t="s">
         <v>745</v>
       </c>
@@ -38727,7 +38787,7 @@
       <c r="AM276" s="1"/>
       <c r="AN276" s="83"/>
     </row>
-    <row r="277" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="277" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A277" s="15" t="s">
         <v>746</v>
       </c>
@@ -38808,7 +38868,7 @@
       <c r="AM277" s="1"/>
       <c r="AN277" s="83"/>
     </row>
-    <row r="278" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="278" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A278" s="15" t="s">
         <v>747</v>
       </c>
@@ -38889,7 +38949,7 @@
       <c r="AM278" s="1"/>
       <c r="AN278" s="83"/>
     </row>
-    <row r="279" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
+    <row r="279" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="22" t="s">
         <v>748</v>
       </c>
@@ -39006,7 +39066,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="280" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
+    <row r="280" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="22" t="s">
         <v>758</v>
       </c>
@@ -39121,7 +39181,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="281" spans="1:40" s="26" customFormat="1" ht="122.45" hidden="1">
+    <row r="281" spans="1:40" s="26" customFormat="1" ht="122.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="22" t="s">
         <v>760</v>
       </c>
@@ -39238,7 +39298,7 @@
         <v>46266</v>
       </c>
     </row>
-    <row r="282" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="282" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="22" t="s">
         <v>768</v>
       </c>
@@ -39351,7 +39411,7 @@
       <c r="AM282" s="1"/>
       <c r="AN282" s="83"/>
     </row>
-    <row r="283" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="283" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="22" t="s">
         <v>562</v>
       </c>
@@ -39466,7 +39526,7 @@
         <v>46235</v>
       </c>
     </row>
-    <row r="284" spans="1:40" s="26" customFormat="1" ht="81.599999999999994" hidden="1">
+    <row r="284" spans="1:40" s="26" customFormat="1" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="22" t="s">
         <v>778</v>
       </c>
@@ -39581,7 +39641,7 @@
       </c>
       <c r="AN284" s="83"/>
     </row>
-    <row r="285" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="285" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="22" t="s">
         <v>782</v>
       </c>
@@ -39696,7 +39756,7 @@
       </c>
       <c r="AN285" s="83"/>
     </row>
-    <row r="286" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="286" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="22" t="s">
         <v>786</v>
       </c>
@@ -39811,7 +39871,7 @@
       </c>
       <c r="AN286" s="83"/>
     </row>
-    <row r="287" spans="1:40" s="26" customFormat="1" ht="20.45" hidden="1">
+    <row r="287" spans="1:40" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="22" t="s">
         <v>790</v>
       </c>
@@ -39926,7 +39986,7 @@
       </c>
       <c r="AN287" s="83"/>
     </row>
-    <row r="288" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="288" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="22" t="s">
         <v>792</v>
       </c>
@@ -40041,7 +40101,7 @@
       </c>
       <c r="AN288" s="83"/>
     </row>
-    <row r="289" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="289" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="22" t="s">
         <v>795</v>
       </c>
@@ -40156,7 +40216,7 @@
       </c>
       <c r="AN289" s="83"/>
     </row>
-    <row r="290" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="290" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="22" t="s">
         <v>207</v>
       </c>
@@ -40253,7 +40313,7 @@
       </c>
       <c r="AN290" s="83"/>
     </row>
-    <row r="291" spans="1:40" s="26" customFormat="1" ht="30.6" hidden="1">
+    <row r="291" spans="1:40" s="26" customFormat="1" ht="30.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="22" t="s">
         <v>804</v>
       </c>
@@ -40366,7 +40426,7 @@
       </c>
       <c r="AN291" s="83"/>
     </row>
-    <row r="292" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="292" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="22" t="s">
         <v>809</v>
       </c>
@@ -40461,7 +40521,7 @@
       <c r="AM292" s="1"/>
       <c r="AN292" s="83"/>
     </row>
-    <row r="293" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="293" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="22" t="s">
         <v>812</v>
       </c>
@@ -40550,7 +40610,7 @@
       <c r="AM293" s="1"/>
       <c r="AN293" s="83"/>
     </row>
-    <row r="294" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="294" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="22" t="s">
         <v>815</v>
       </c>
@@ -40641,7 +40701,7 @@
       <c r="AM294" s="1"/>
       <c r="AN294" s="83"/>
     </row>
-    <row r="295" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="295" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="22" t="s">
         <v>817</v>
       </c>
@@ -40726,7 +40786,7 @@
       <c r="AM295" s="1"/>
       <c r="AN295" s="83"/>
     </row>
-    <row r="296" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="296" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="22" t="s">
         <v>821</v>
       </c>
@@ -40817,7 +40877,7 @@
       <c r="AM296" s="1"/>
       <c r="AN296" s="83"/>
     </row>
-    <row r="297" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="297" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="22" t="s">
         <v>728</v>
       </c>
@@ -40908,7 +40968,7 @@
       </c>
       <c r="AN297" s="83"/>
     </row>
-    <row r="298" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="298" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="22" t="s">
         <v>156</v>
       </c>
@@ -40997,7 +41057,7 @@
       <c r="AM298" s="1"/>
       <c r="AN298" s="83"/>
     </row>
-    <row r="299" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="299" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="22" t="s">
         <v>828</v>
       </c>
@@ -41088,7 +41148,7 @@
       <c r="AM299" s="1"/>
       <c r="AN299" s="83"/>
     </row>
-    <row r="300" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="300" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="22" t="s">
         <v>829</v>
       </c>
@@ -41177,7 +41237,7 @@
       <c r="AM300" s="1"/>
       <c r="AN300" s="83"/>
     </row>
-    <row r="301" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="301" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="22" t="s">
         <v>391</v>
       </c>
@@ -41268,7 +41328,7 @@
       <c r="AM301" s="1"/>
       <c r="AN301" s="83"/>
     </row>
-    <row r="302" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="302" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="22" t="s">
         <v>266</v>
       </c>
@@ -41357,7 +41417,7 @@
       <c r="AM302" s="1"/>
       <c r="AN302" s="83"/>
     </row>
-    <row r="303" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="303" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="22" t="s">
         <v>836</v>
       </c>
@@ -41448,7 +41508,7 @@
       <c r="AM303" s="1"/>
       <c r="AN303" s="83"/>
     </row>
-    <row r="304" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="304" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="22" t="s">
         <v>839</v>
       </c>
@@ -41539,7 +41599,7 @@
       <c r="AM304" s="1"/>
       <c r="AN304" s="83"/>
     </row>
-    <row r="305" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="305" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="22" t="s">
         <v>53</v>
       </c>
@@ -41630,7 +41690,7 @@
       <c r="AM305" s="1"/>
       <c r="AN305" s="83"/>
     </row>
-    <row r="306" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="306" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="22" t="s">
         <v>843</v>
       </c>
@@ -41713,7 +41773,7 @@
       <c r="AM306" s="1"/>
       <c r="AN306" s="83"/>
     </row>
-    <row r="307" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="307" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="22" t="s">
         <v>845</v>
       </c>
@@ -41804,7 +41864,7 @@
       <c r="AM307" s="1"/>
       <c r="AN307" s="83"/>
     </row>
-    <row r="308" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="308" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="22" t="s">
         <v>847</v>
       </c>
@@ -41893,7 +41953,7 @@
       <c r="AM308" s="1"/>
       <c r="AN308" s="83"/>
     </row>
-    <row r="309" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="309" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="22" t="s">
         <v>848</v>
       </c>
@@ -41984,7 +42044,7 @@
       <c r="AM309" s="1"/>
       <c r="AN309" s="83"/>
     </row>
-    <row r="310" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="310" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="22" t="s">
         <v>650</v>
       </c>
@@ -42069,7 +42129,7 @@
       <c r="AM310" s="1"/>
       <c r="AN310" s="83"/>
     </row>
-    <row r="311" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="311" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="22" t="s">
         <v>739</v>
       </c>
@@ -42160,7 +42220,7 @@
       <c r="AM311" s="1"/>
       <c r="AN311" s="83"/>
     </row>
-    <row r="312" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="312" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="22" t="s">
         <v>118</v>
       </c>
@@ -42249,7 +42309,7 @@
       <c r="AM312" s="1"/>
       <c r="AN312" s="83"/>
     </row>
-    <row r="313" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="313" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="22">
         <v>98451</v>
       </c>
@@ -42322,7 +42382,7 @@
       <c r="AM313" s="1"/>
       <c r="AN313" s="83"/>
     </row>
-    <row r="314" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="314" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="22" t="s">
         <v>854</v>
       </c>
@@ -42417,7 +42477,7 @@
       <c r="AM314" s="1"/>
       <c r="AN314" s="83"/>
     </row>
-    <row r="315" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="315" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="22" t="s">
         <v>857</v>
       </c>
@@ -42508,7 +42568,7 @@
       <c r="AM315" s="1"/>
       <c r="AN315" s="83"/>
     </row>
-    <row r="316" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="316" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="3" t="s">
         <v>859</v>
       </c>
@@ -42595,7 +42655,7 @@
       <c r="AM316" s="1"/>
       <c r="AN316" s="83"/>
     </row>
-    <row r="317" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="317" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="22" t="s">
         <v>644</v>
       </c>
@@ -42680,7 +42740,7 @@
       <c r="AM317" s="1"/>
       <c r="AN317" s="83"/>
     </row>
-    <row r="318" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="318" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="22" t="s">
         <v>862</v>
       </c>
@@ -42771,7 +42831,7 @@
       <c r="AM318" s="1"/>
       <c r="AN318" s="83"/>
     </row>
-    <row r="319" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="319" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="22" t="s">
         <v>864</v>
       </c>
@@ -42866,7 +42926,7 @@
       <c r="AM319" s="1"/>
       <c r="AN319" s="83"/>
     </row>
-    <row r="320" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="320" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="22" t="s">
         <v>325</v>
       </c>
@@ -42955,7 +43015,7 @@
       <c r="AM320" s="1"/>
       <c r="AN320" s="83"/>
     </row>
-    <row r="321" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="321" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="22" t="s">
         <v>866</v>
       </c>
@@ -43036,7 +43096,7 @@
       <c r="AM321" s="1"/>
       <c r="AN321" s="83"/>
     </row>
-    <row r="322" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="322" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="3" t="s">
         <v>868</v>
       </c>
@@ -43123,7 +43183,7 @@
       <c r="AM322" s="1"/>
       <c r="AN322" s="83"/>
     </row>
-    <row r="323" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="323" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="22" t="s">
         <v>869</v>
       </c>
@@ -43210,7 +43270,7 @@
       <c r="AM323" s="1"/>
       <c r="AN323" s="83"/>
     </row>
-    <row r="324" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="324" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="22" t="s">
         <v>870</v>
       </c>
@@ -43293,7 +43353,7 @@
       <c r="AM324" s="1"/>
       <c r="AN324" s="83"/>
     </row>
-    <row r="325" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="325" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="22" t="s">
         <v>132</v>
       </c>
@@ -43382,7 +43442,7 @@
       <c r="AM325" s="1"/>
       <c r="AN325" s="83"/>
     </row>
-    <row r="326" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="326" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="3" t="s">
         <v>874</v>
       </c>
@@ -43471,7 +43531,7 @@
       <c r="AM326" s="1"/>
       <c r="AN326" s="83"/>
     </row>
-    <row r="327" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="327" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="22" t="s">
         <v>646</v>
       </c>
@@ -43556,7 +43616,7 @@
       <c r="AM327" s="1"/>
       <c r="AN327" s="83"/>
     </row>
-    <row r="328" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="328" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="3" t="s">
         <v>876</v>
       </c>
@@ -43643,7 +43703,7 @@
       <c r="AM328" s="1"/>
       <c r="AN328" s="83"/>
     </row>
-    <row r="329" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="329" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
         <v>877</v>
       </c>
@@ -43730,7 +43790,7 @@
       <c r="AM329" s="1"/>
       <c r="AN329" s="83"/>
     </row>
-    <row r="330" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="330" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="3" t="s">
         <v>878</v>
       </c>
@@ -43817,7 +43877,7 @@
       <c r="AM330" s="1"/>
       <c r="AN330" s="83"/>
     </row>
-    <row r="331" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="331" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
         <v>880</v>
       </c>
@@ -43900,7 +43960,7 @@
       <c r="AM331" s="1"/>
       <c r="AN331" s="83"/>
     </row>
-    <row r="332" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="332" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="3" t="s">
         <v>883</v>
       </c>
@@ -43983,7 +44043,7 @@
       <c r="AM332" s="1"/>
       <c r="AN332" s="83"/>
     </row>
-    <row r="333" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="333" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
         <v>886</v>
       </c>
@@ -44070,7 +44130,7 @@
       <c r="AM333" s="1"/>
       <c r="AN333" s="83"/>
     </row>
-    <row r="334" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="334" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="22" t="s">
         <v>887</v>
       </c>
@@ -44161,7 +44221,7 @@
       <c r="AM334" s="1"/>
       <c r="AN334" s="83"/>
     </row>
-    <row r="335" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="335" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="22" t="s">
         <v>890</v>
       </c>
@@ -44244,7 +44304,7 @@
       <c r="AM335" s="1"/>
       <c r="AN335" s="83"/>
     </row>
-    <row r="336" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="336" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="3" t="s">
         <v>275</v>
       </c>
@@ -44321,7 +44381,7 @@
       <c r="AM336" s="1"/>
       <c r="AN336" s="83"/>
     </row>
-    <row r="337" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="337" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="22" t="s">
         <v>892</v>
       </c>
@@ -44412,7 +44472,7 @@
       <c r="AM337" s="1"/>
       <c r="AN337" s="83"/>
     </row>
-    <row r="338" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="338" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="3" t="s">
         <v>664</v>
       </c>
@@ -44495,7 +44555,7 @@
       <c r="AM338" s="1"/>
       <c r="AN338" s="83"/>
     </row>
-    <row r="339" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="339" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="22" t="s">
         <v>895</v>
       </c>
@@ -44578,7 +44638,7 @@
       <c r="AM339" s="1"/>
       <c r="AN339" s="83"/>
     </row>
-    <row r="340" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="340" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="3" t="s">
         <v>898</v>
       </c>
@@ -44661,7 +44721,7 @@
       <c r="AM340" s="1"/>
       <c r="AN340" s="83"/>
     </row>
-    <row r="341" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="341" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="22" t="s">
         <v>900</v>
       </c>
@@ -44744,7 +44804,7 @@
       <c r="AM341" s="1"/>
       <c r="AN341" s="83"/>
     </row>
-    <row r="342" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="342" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="22" t="s">
         <v>902</v>
       </c>
@@ -44827,7 +44887,7 @@
       <c r="AM342" s="1"/>
       <c r="AN342" s="83"/>
     </row>
-    <row r="343" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="343" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
         <v>904</v>
       </c>
@@ -44916,7 +44976,7 @@
       <c r="AM343" s="1"/>
       <c r="AN343" s="83"/>
     </row>
-    <row r="344" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="344" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="22" t="s">
         <v>905</v>
       </c>
@@ -45003,7 +45063,7 @@
       <c r="AM344" s="1"/>
       <c r="AN344" s="83"/>
     </row>
-    <row r="345" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="345" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
         <v>907</v>
       </c>
@@ -45090,7 +45150,7 @@
       <c r="AM345" s="1"/>
       <c r="AN345" s="83"/>
     </row>
-    <row r="346" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="346" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="3" t="s">
         <v>655</v>
       </c>
@@ -45177,7 +45237,7 @@
       <c r="AM346" s="1"/>
       <c r="AN346" s="83"/>
     </row>
-    <row r="347" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="347" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="22" t="s">
         <v>909</v>
       </c>
@@ -45256,7 +45316,7 @@
       <c r="AM347" s="1"/>
       <c r="AN347" s="83"/>
     </row>
-    <row r="348" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="348" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="3" t="s">
         <v>912</v>
       </c>
@@ -45343,7 +45403,7 @@
       <c r="AM348" s="1"/>
       <c r="AN348" s="83"/>
     </row>
-    <row r="349" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="349" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="22" t="s">
         <v>913</v>
       </c>
@@ -45430,7 +45490,7 @@
       <c r="AM349" s="1"/>
       <c r="AN349" s="83"/>
     </row>
-    <row r="350" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="350" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="3" t="s">
         <v>915</v>
       </c>
@@ -45513,7 +45573,7 @@
       <c r="AM350" s="1"/>
       <c r="AN350" s="83"/>
     </row>
-    <row r="351" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="351" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="22" t="s">
         <v>917</v>
       </c>
@@ -45604,7 +45664,7 @@
       <c r="AM351" s="1"/>
       <c r="AN351" s="83"/>
     </row>
-    <row r="352" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="352" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="22" t="s">
         <v>918</v>
       </c>
@@ -45687,7 +45747,7 @@
       <c r="AM352" s="1"/>
       <c r="AN352" s="83"/>
     </row>
-    <row r="353" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="353" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
         <v>920</v>
       </c>
@@ -45774,7 +45834,7 @@
       <c r="AM353" s="1"/>
       <c r="AN353" s="83"/>
     </row>
-    <row r="354" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="354" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="3" t="s">
         <v>921</v>
       </c>
@@ -45857,7 +45917,7 @@
       <c r="AM354" s="1"/>
       <c r="AN354" s="83"/>
     </row>
-    <row r="355" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="355" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="22" t="s">
         <v>922</v>
       </c>
@@ -45948,7 +46008,7 @@
       <c r="AM355" s="1"/>
       <c r="AN355" s="83"/>
     </row>
-    <row r="356" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="356" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="3" t="s">
         <v>394</v>
       </c>
@@ -46031,7 +46091,7 @@
       <c r="AM356" s="1"/>
       <c r="AN356" s="83"/>
     </row>
-    <row r="357" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="357" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="22" t="s">
         <v>923</v>
       </c>
@@ -46114,7 +46174,7 @@
       <c r="AM357" s="1"/>
       <c r="AN357" s="83"/>
     </row>
-    <row r="358" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="358" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="22" t="s">
         <v>927</v>
       </c>
@@ -46197,7 +46257,7 @@
       <c r="AM358" s="1"/>
       <c r="AN358" s="83"/>
     </row>
-    <row r="359" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="359" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
         <v>928</v>
       </c>
@@ -46284,7 +46344,7 @@
       <c r="AM359" s="1"/>
       <c r="AN359" s="83"/>
     </row>
-    <row r="360" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="360" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="22" t="s">
         <v>929</v>
       </c>
@@ -46375,7 +46435,7 @@
       <c r="AM360" s="1"/>
       <c r="AN360" s="83"/>
     </row>
-    <row r="361" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="361" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
         <v>370</v>
       </c>
@@ -46458,7 +46518,7 @@
       <c r="AM361" s="1"/>
       <c r="AN361" s="83"/>
     </row>
-    <row r="362" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="362" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="3" t="s">
         <v>930</v>
       </c>
@@ -46545,7 +46605,7 @@
       <c r="AM362" s="1"/>
       <c r="AN362" s="83"/>
     </row>
-    <row r="363" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="363" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="22" t="s">
         <v>932</v>
       </c>
@@ -46628,7 +46688,7 @@
       <c r="AM363" s="1"/>
       <c r="AN363" s="83"/>
     </row>
-    <row r="364" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="364" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="3" t="s">
         <v>659</v>
       </c>
@@ -46711,7 +46771,7 @@
       <c r="AM364" s="1"/>
       <c r="AN364" s="83"/>
     </row>
-    <row r="365" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="365" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="22" t="s">
         <v>933</v>
       </c>
@@ -46794,7 +46854,7 @@
       <c r="AM365" s="1"/>
       <c r="AN365" s="83"/>
     </row>
-    <row r="366" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="366" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="3" t="s">
         <v>934</v>
       </c>
@@ -46877,7 +46937,7 @@
       <c r="AM366" s="1"/>
       <c r="AN366" s="83"/>
     </row>
-    <row r="367" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="367" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
         <v>740</v>
       </c>
@@ -46960,7 +47020,7 @@
       <c r="AM367" s="1"/>
       <c r="AN367" s="83"/>
     </row>
-    <row r="368" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="368" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="3" t="s">
         <v>674</v>
       </c>
@@ -47043,7 +47103,7 @@
       <c r="AM368" s="1"/>
       <c r="AN368" s="83"/>
     </row>
-    <row r="369" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="369" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
         <v>938</v>
       </c>
@@ -47126,7 +47186,7 @@
       <c r="AM369" s="1"/>
       <c r="AN369" s="83"/>
     </row>
-    <row r="370" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="370" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="22" t="s">
         <v>940</v>
       </c>
@@ -47209,7 +47269,7 @@
       <c r="AM370" s="1"/>
       <c r="AN370" s="83"/>
     </row>
-    <row r="371" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="371" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="22" t="s">
         <v>943</v>
       </c>
@@ -47292,7 +47352,7 @@
       <c r="AM371" s="1"/>
       <c r="AN371" s="83"/>
     </row>
-    <row r="372" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="372" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="22" t="s">
         <v>945</v>
       </c>
@@ -47375,7 +47435,7 @@
       <c r="AM372" s="1"/>
       <c r="AN372" s="83"/>
     </row>
-    <row r="373" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="373" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
         <v>946</v>
       </c>
@@ -47458,7 +47518,7 @@
       <c r="AM373" s="1"/>
       <c r="AN373" s="83"/>
     </row>
-    <row r="374" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="374" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="3" t="s">
         <v>948</v>
       </c>
@@ -47541,7 +47601,7 @@
       <c r="AM374" s="1"/>
       <c r="AN374" s="83"/>
     </row>
-    <row r="375" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="375" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="22" t="s">
         <v>949</v>
       </c>
@@ -47624,7 +47684,7 @@
       <c r="AM375" s="1"/>
       <c r="AN375" s="83"/>
     </row>
-    <row r="376" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="376" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="3" t="s">
         <v>950</v>
       </c>
@@ -47707,7 +47767,7 @@
       <c r="AM376" s="1"/>
       <c r="AN376" s="83"/>
     </row>
-    <row r="377" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="377" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="22" t="s">
         <v>951</v>
       </c>
@@ -47790,7 +47850,7 @@
       <c r="AM377" s="1"/>
       <c r="AN377" s="83"/>
     </row>
-    <row r="378" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="378" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="22" t="s">
         <v>953</v>
       </c>
@@ -47873,7 +47933,7 @@
       <c r="AM378" s="1"/>
       <c r="AN378" s="83"/>
     </row>
-    <row r="379" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="379" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="22" t="s">
         <v>956</v>
       </c>
@@ -47956,7 +48016,7 @@
       <c r="AM379" s="1"/>
       <c r="AN379" s="83"/>
     </row>
-    <row r="380" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="380" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="22" t="s">
         <v>958</v>
       </c>
@@ -48039,7 +48099,7 @@
       <c r="AM380" s="1"/>
       <c r="AN380" s="83"/>
     </row>
-    <row r="381" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="381" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="22" t="s">
         <v>962</v>
       </c>
@@ -48126,7 +48186,7 @@
       <c r="AM381" s="1"/>
       <c r="AN381" s="83"/>
     </row>
-    <row r="382" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="382" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="3" t="s">
         <v>964</v>
       </c>
@@ -48205,7 +48265,7 @@
       <c r="AM382" s="1"/>
       <c r="AN382" s="83"/>
     </row>
-    <row r="383" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="383" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="22" t="s">
         <v>966</v>
       </c>
@@ -48288,7 +48348,7 @@
       <c r="AM383" s="1"/>
       <c r="AN383" s="83"/>
     </row>
-    <row r="384" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="384" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" s="22" t="s">
         <v>323</v>
       </c>
@@ -48371,7 +48431,7 @@
       <c r="AM384" s="1"/>
       <c r="AN384" s="83"/>
     </row>
-    <row r="385" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="385" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
         <v>967</v>
       </c>
@@ -48458,7 +48518,7 @@
       <c r="AM385" s="1"/>
       <c r="AN385" s="83"/>
     </row>
-    <row r="386" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="386" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="22" t="s">
         <v>471</v>
       </c>
@@ -48541,7 +48601,7 @@
       <c r="AM386" s="1"/>
       <c r="AN386" s="83"/>
     </row>
-    <row r="387" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="387" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="22" t="s">
         <v>316</v>
       </c>
@@ -48624,7 +48684,7 @@
       <c r="AM387" s="1"/>
       <c r="AN387" s="83"/>
     </row>
-    <row r="388" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="388" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="3" t="s">
         <v>971</v>
       </c>
@@ -48707,7 +48767,7 @@
       <c r="AM388" s="1"/>
       <c r="AN388" s="83"/>
     </row>
-    <row r="389" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="389" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="22" t="s">
         <v>972</v>
       </c>
@@ -48798,7 +48858,7 @@
       <c r="AM389" s="1"/>
       <c r="AN389" s="83"/>
     </row>
-    <row r="390" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="390" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="22" t="s">
         <v>973</v>
       </c>
@@ -48889,7 +48949,7 @@
       <c r="AM390" s="1"/>
       <c r="AN390" s="83"/>
     </row>
-    <row r="391" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="391" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="22" t="s">
         <v>974</v>
       </c>
@@ -48972,7 +49032,7 @@
       <c r="AM391" s="1"/>
       <c r="AN391" s="83"/>
     </row>
-    <row r="392" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="392" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="22" t="s">
         <v>975</v>
       </c>
@@ -49055,7 +49115,7 @@
       <c r="AM392" s="1"/>
       <c r="AN392" s="83"/>
     </row>
-    <row r="393" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="393" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="22" t="s">
         <v>977</v>
       </c>
@@ -49146,7 +49206,7 @@
       <c r="AM393" s="1"/>
       <c r="AN393" s="83"/>
     </row>
-    <row r="394" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="394" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="22" t="s">
         <v>446</v>
       </c>
@@ -49229,7 +49289,7 @@
       <c r="AM394" s="1"/>
       <c r="AN394" s="83"/>
     </row>
-    <row r="395" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="395" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="22" t="s">
         <v>979</v>
       </c>
@@ -49320,7 +49380,7 @@
       <c r="AM395" s="1"/>
       <c r="AN395" s="83"/>
     </row>
-    <row r="396" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="396" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="22" t="s">
         <v>482</v>
       </c>
@@ -49403,7 +49463,7 @@
       <c r="AM396" s="1"/>
       <c r="AN396" s="83"/>
     </row>
-    <row r="397" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="397" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="22" t="s">
         <v>982</v>
       </c>
@@ -49486,7 +49546,7 @@
       <c r="AM397" s="1"/>
       <c r="AN397" s="83"/>
     </row>
-    <row r="398" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="398" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="22" t="s">
         <v>983</v>
       </c>
@@ -49569,7 +49629,7 @@
       <c r="AM398" s="1"/>
       <c r="AN398" s="83"/>
     </row>
-    <row r="399" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="399" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="22" t="s">
         <v>985</v>
       </c>
@@ -49652,7 +49712,7 @@
       <c r="AM399" s="1"/>
       <c r="AN399" s="83"/>
     </row>
-    <row r="400" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="400" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="3" t="s">
         <v>986</v>
       </c>
@@ -49735,7 +49795,7 @@
       <c r="AM400" s="1"/>
       <c r="AN400" s="83"/>
     </row>
-    <row r="401" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="401" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
         <v>987</v>
       </c>
@@ -49822,7 +49882,7 @@
       <c r="AM401" s="1"/>
       <c r="AN401" s="83"/>
     </row>
-    <row r="402" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="402" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="22" t="s">
         <v>988</v>
       </c>
@@ -49905,7 +49965,7 @@
       <c r="AM402" s="1"/>
       <c r="AN402" s="83"/>
     </row>
-    <row r="403" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="403" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="22" t="s">
         <v>989</v>
       </c>
@@ -49988,7 +50048,7 @@
       <c r="AM403" s="1"/>
       <c r="AN403" s="83"/>
     </row>
-    <row r="404" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="404" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="22" t="s">
         <v>992</v>
       </c>
@@ -50077,7 +50137,7 @@
       <c r="AM404" s="1"/>
       <c r="AN404" s="83"/>
     </row>
-    <row r="405" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="405" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="22" t="s">
         <v>993</v>
       </c>
@@ -50168,7 +50228,7 @@
       <c r="AM405" s="1"/>
       <c r="AN405" s="83"/>
     </row>
-    <row r="406" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="406" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="3" t="s">
         <v>995</v>
       </c>
@@ -50255,7 +50315,7 @@
       <c r="AM406" s="1"/>
       <c r="AN406" s="83"/>
     </row>
-    <row r="407" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="407" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" s="22" t="s">
         <v>997</v>
       </c>
@@ -50346,7 +50406,7 @@
       <c r="AM407" s="1"/>
       <c r="AN407" s="83"/>
     </row>
-    <row r="408" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="408" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" s="22" t="s">
         <v>999</v>
       </c>
@@ -50429,7 +50489,7 @@
       <c r="AM408" s="1"/>
       <c r="AN408" s="83"/>
     </row>
-    <row r="409" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="409" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="22" t="s">
         <v>1001</v>
       </c>
@@ -50512,7 +50572,7 @@
       <c r="AM409" s="1"/>
       <c r="AN409" s="83"/>
     </row>
-    <row r="410" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="410" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="22" t="s">
         <v>1003</v>
       </c>
@@ -50595,7 +50655,7 @@
       <c r="AM410" s="1"/>
       <c r="AN410" s="83"/>
     </row>
-    <row r="411" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="411" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="22" t="s">
         <v>414</v>
       </c>
@@ -50678,7 +50738,7 @@
       <c r="AM411" s="1"/>
       <c r="AN411" s="83"/>
     </row>
-    <row r="412" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="412" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="22" t="s">
         <v>1005</v>
       </c>
@@ -50761,7 +50821,7 @@
       <c r="AM412" s="1"/>
       <c r="AN412" s="83"/>
     </row>
-    <row r="413" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="413" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="22" t="s">
         <v>1006</v>
       </c>
@@ -50844,7 +50904,7 @@
       <c r="AM413" s="1"/>
       <c r="AN413" s="83"/>
     </row>
-    <row r="414" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="414" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" s="22" t="s">
         <v>1008</v>
       </c>
@@ -50927,7 +50987,7 @@
       <c r="AM414" s="1"/>
       <c r="AN414" s="83"/>
     </row>
-    <row r="415" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="415" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" s="22" t="s">
         <v>1010</v>
       </c>
@@ -51016,7 +51076,7 @@
       <c r="AM415" s="1"/>
       <c r="AN415" s="83"/>
     </row>
-    <row r="416" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="416" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" s="22" t="s">
         <v>1011</v>
       </c>
@@ -51107,7 +51167,7 @@
       <c r="AM416" s="1"/>
       <c r="AN416" s="83"/>
     </row>
-    <row r="417" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="417" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="22" t="s">
         <v>1012</v>
       </c>
@@ -51198,7 +51258,7 @@
       <c r="AM417" s="1"/>
       <c r="AN417" s="83"/>
     </row>
-    <row r="418" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="418" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="22" t="s">
         <v>1013</v>
       </c>
@@ -51287,7 +51347,7 @@
       <c r="AM418" s="1"/>
       <c r="AN418" s="83"/>
     </row>
-    <row r="419" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="419" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="22" t="s">
         <v>1014</v>
       </c>
@@ -51378,7 +51438,7 @@
       <c r="AM419" s="1"/>
       <c r="AN419" s="83"/>
     </row>
-    <row r="420" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="420" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="22" t="s">
         <v>1015</v>
       </c>
@@ -51461,7 +51521,7 @@
       <c r="AM420" s="1"/>
       <c r="AN420" s="83"/>
     </row>
-    <row r="421" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="421" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="22" t="s">
         <v>1017</v>
       </c>
@@ -51544,7 +51604,7 @@
       <c r="AM421" s="1"/>
       <c r="AN421" s="83"/>
     </row>
-    <row r="422" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="422" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" s="22" t="s">
         <v>1019</v>
       </c>
@@ -51627,7 +51687,7 @@
       <c r="AM422" s="1"/>
       <c r="AN422" s="83"/>
     </row>
-    <row r="423" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="423" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="22" t="s">
         <v>1021</v>
       </c>
@@ -51710,7 +51770,7 @@
       <c r="AM423" s="1"/>
       <c r="AN423" s="83"/>
     </row>
-    <row r="424" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="424" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="22" t="s">
         <v>1024</v>
       </c>
@@ -51793,7 +51853,7 @@
       <c r="AM424" s="1"/>
       <c r="AN424" s="83"/>
     </row>
-    <row r="425" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="425" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" s="22" t="s">
         <v>1026</v>
       </c>
@@ -51876,7 +51936,7 @@
       <c r="AM425" s="1"/>
       <c r="AN425" s="83"/>
     </row>
-    <row r="426" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="426" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="22" t="s">
         <v>1028</v>
       </c>
@@ -51959,7 +52019,7 @@
       <c r="AM426" s="1"/>
       <c r="AN426" s="83"/>
     </row>
-    <row r="427" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="427" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="22" t="s">
         <v>1029</v>
       </c>
@@ -52042,7 +52102,7 @@
       <c r="AM427" s="1"/>
       <c r="AN427" s="83"/>
     </row>
-    <row r="428" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="428" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" s="22" t="s">
         <v>1030</v>
       </c>
@@ -52125,7 +52185,7 @@
       <c r="AM428" s="1"/>
       <c r="AN428" s="83"/>
     </row>
-    <row r="429" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="429" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" s="22" t="s">
         <v>1032</v>
       </c>
@@ -52208,7 +52268,7 @@
       <c r="AM429" s="1"/>
       <c r="AN429" s="83"/>
     </row>
-    <row r="430" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="430" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="22" t="s">
         <v>1034</v>
       </c>
@@ -52291,7 +52351,7 @@
       <c r="AM430" s="1"/>
       <c r="AN430" s="83"/>
     </row>
-    <row r="431" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="431" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" s="22" t="s">
         <v>1036</v>
       </c>
@@ -52374,7 +52434,7 @@
       <c r="AM431" s="1"/>
       <c r="AN431" s="83"/>
     </row>
-    <row r="432" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="432" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="22" t="s">
         <v>642</v>
       </c>
@@ -52457,7 +52517,7 @@
       <c r="AM432" s="1"/>
       <c r="AN432" s="83"/>
     </row>
-    <row r="433" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="433" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="22" t="s">
         <v>1041</v>
       </c>
@@ -52540,7 +52600,7 @@
       <c r="AM433" s="1"/>
       <c r="AN433" s="83"/>
     </row>
-    <row r="434" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="434" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="22" t="s">
         <v>1043</v>
       </c>
@@ -52623,7 +52683,7 @@
       <c r="AM434" s="1"/>
       <c r="AN434" s="83"/>
     </row>
-    <row r="435" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="435" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="22" t="s">
         <v>1044</v>
       </c>
@@ -52706,7 +52766,7 @@
       <c r="AM435" s="1"/>
       <c r="AN435" s="83"/>
     </row>
-    <row r="436" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="436" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="22" t="s">
         <v>1046</v>
       </c>
@@ -52789,7 +52849,7 @@
       <c r="AM436" s="1"/>
       <c r="AN436" s="83"/>
     </row>
-    <row r="437" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="437" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="22" t="s">
         <v>1048</v>
       </c>
@@ -52872,7 +52932,7 @@
       <c r="AM437" s="1"/>
       <c r="AN437" s="83"/>
     </row>
-    <row r="438" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="438" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="22" t="s">
         <v>398</v>
       </c>
@@ -52955,7 +53015,7 @@
       <c r="AM438" s="1"/>
       <c r="AN438" s="83"/>
     </row>
-    <row r="439" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="439" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="22" t="s">
         <v>745</v>
       </c>
@@ -53038,7 +53098,7 @@
       <c r="AM439" s="1"/>
       <c r="AN439" s="83"/>
     </row>
-    <row r="440" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="440" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="22" t="s">
         <v>1053</v>
       </c>
@@ -53121,7 +53181,7 @@
       <c r="AM440" s="1"/>
       <c r="AN440" s="83"/>
     </row>
-    <row r="441" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="441" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" s="22" t="s">
         <v>1054</v>
       </c>
@@ -53204,7 +53264,7 @@
       <c r="AM441" s="1"/>
       <c r="AN441" s="83"/>
     </row>
-    <row r="442" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="442" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" s="22" t="s">
         <v>1055</v>
       </c>
@@ -53287,7 +53347,7 @@
       <c r="AM442" s="1"/>
       <c r="AN442" s="83"/>
     </row>
-    <row r="443" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="443" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" s="22" t="s">
         <v>1057</v>
       </c>
@@ -53370,7 +53430,7 @@
       <c r="AM443" s="1"/>
       <c r="AN443" s="83"/>
     </row>
-    <row r="444" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="444" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="22" t="s">
         <v>1059</v>
       </c>
@@ -53453,7 +53513,7 @@
       <c r="AM444" s="1"/>
       <c r="AN444" s="83"/>
     </row>
-    <row r="445" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="445" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" s="22" t="s">
         <v>1062</v>
       </c>
@@ -53536,7 +53596,7 @@
       <c r="AM445" s="1"/>
       <c r="AN445" s="83"/>
     </row>
-    <row r="446" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="446" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="22" t="s">
         <v>1063</v>
       </c>
@@ -53619,7 +53679,7 @@
       <c r="AM446" s="1"/>
       <c r="AN446" s="83"/>
     </row>
-    <row r="447" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="447" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="3" t="s">
         <v>653</v>
       </c>
@@ -53694,7 +53754,7 @@
       <c r="AM447" s="1"/>
       <c r="AN447" s="83"/>
     </row>
-    <row r="448" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="448" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" s="3" t="s">
         <v>1064</v>
       </c>
@@ -53777,7 +53837,7 @@
       <c r="AM448" s="1"/>
       <c r="AN448" s="83"/>
     </row>
-    <row r="449" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="449" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" s="3" t="s">
         <v>1065</v>
       </c>
@@ -53860,7 +53920,7 @@
       <c r="AM449" s="1"/>
       <c r="AN449" s="83"/>
     </row>
-    <row r="450" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="450" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" s="3" t="s">
         <v>1066</v>
       </c>
@@ -53943,7 +54003,7 @@
       <c r="AM450" s="1"/>
       <c r="AN450" s="83"/>
     </row>
-    <row r="451" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="451" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" s="3" t="s">
         <v>1067</v>
       </c>
@@ -54026,7 +54086,7 @@
       <c r="AM451" s="1"/>
       <c r="AN451" s="83"/>
     </row>
-    <row r="452" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="452" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" s="3" t="s">
         <v>1068</v>
       </c>
@@ -54109,7 +54169,7 @@
       <c r="AM452" s="1"/>
       <c r="AN452" s="83"/>
     </row>
-    <row r="453" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="453" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" s="3" t="s">
         <v>1069</v>
       </c>
@@ -54192,7 +54252,7 @@
       <c r="AM453" s="1"/>
       <c r="AN453" s="83"/>
     </row>
-    <row r="454" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="454" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" s="3" t="s">
         <v>1070</v>
       </c>
@@ -54275,7 +54335,7 @@
       <c r="AM454" s="1"/>
       <c r="AN454" s="83"/>
     </row>
-    <row r="455" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="455" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" s="3" t="s">
         <v>1071</v>
       </c>
@@ -54358,7 +54418,7 @@
       <c r="AM455" s="1"/>
       <c r="AN455" s="83"/>
     </row>
-    <row r="456" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="456" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" s="3" t="s">
         <v>1072</v>
       </c>
@@ -54441,7 +54501,7 @@
       <c r="AM456" s="1"/>
       <c r="AN456" s="83"/>
     </row>
-    <row r="457" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="457" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" s="3" t="s">
         <v>1074</v>
       </c>
@@ -54524,7 +54584,7 @@
       <c r="AM457" s="1"/>
       <c r="AN457" s="83"/>
     </row>
-    <row r="458" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="458" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" s="3" t="s">
         <v>1075</v>
       </c>
@@ -54607,7 +54667,7 @@
       <c r="AM458" s="1"/>
       <c r="AN458" s="83"/>
     </row>
-    <row r="459" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="459" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="3" t="s">
         <v>1076</v>
       </c>
@@ -54690,7 +54750,7 @@
       <c r="AM459" s="1"/>
       <c r="AN459" s="83"/>
     </row>
-    <row r="460" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="460" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="3" t="s">
         <v>1078</v>
       </c>
@@ -54773,7 +54833,7 @@
       <c r="AM460" s="1"/>
       <c r="AN460" s="83"/>
     </row>
-    <row r="461" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="461" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="3" t="s">
         <v>1079</v>
       </c>
@@ -54856,7 +54916,7 @@
       <c r="AM461" s="1"/>
       <c r="AN461" s="83"/>
     </row>
-    <row r="462" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="462" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="3" t="s">
         <v>1080</v>
       </c>
@@ -54939,7 +54999,7 @@
       <c r="AM462" s="1"/>
       <c r="AN462" s="83"/>
     </row>
-    <row r="463" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="463" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="3" t="s">
         <v>1081</v>
       </c>
@@ -55026,7 +55086,7 @@
       <c r="AM463" s="1"/>
       <c r="AN463" s="83"/>
     </row>
-    <row r="464" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="464" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="3" t="s">
         <v>1082</v>
       </c>
@@ -55109,7 +55169,7 @@
       <c r="AM464" s="1"/>
       <c r="AN464" s="83"/>
     </row>
-    <row r="465" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="465" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="3" t="s">
         <v>1083</v>
       </c>
@@ -55192,7 +55252,7 @@
       <c r="AM465" s="1"/>
       <c r="AN465" s="83"/>
     </row>
-    <row r="466" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="466" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="3" t="s">
         <v>1084</v>
       </c>
@@ -55275,7 +55335,7 @@
       <c r="AM466" s="1"/>
       <c r="AN466" s="83"/>
     </row>
-    <row r="467" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="467" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="3" t="s">
         <v>1086</v>
       </c>
@@ -55358,7 +55418,7 @@
       <c r="AM467" s="1"/>
       <c r="AN467" s="83"/>
     </row>
-    <row r="468" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="468" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="3" t="s">
         <v>1088</v>
       </c>
@@ -55441,7 +55501,7 @@
       <c r="AM468" s="1"/>
       <c r="AN468" s="83"/>
     </row>
-    <row r="469" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="469" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" s="3" t="s">
         <v>1090</v>
       </c>
@@ -55524,7 +55584,7 @@
       <c r="AM469" s="1"/>
       <c r="AN469" s="83"/>
     </row>
-    <row r="470" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="470" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" s="3" t="s">
         <v>1091</v>
       </c>
@@ -55607,7 +55667,7 @@
       <c r="AM470" s="1"/>
       <c r="AN470" s="83"/>
     </row>
-    <row r="471" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="471" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="3" t="s">
         <v>1092</v>
       </c>
@@ -55690,7 +55750,7 @@
       <c r="AM471" s="1"/>
       <c r="AN471" s="83"/>
     </row>
-    <row r="472" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="472" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="3" t="s">
         <v>1093</v>
       </c>
@@ -55773,7 +55833,7 @@
       <c r="AM472" s="1"/>
       <c r="AN472" s="83"/>
     </row>
-    <row r="473" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="473" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="3" t="s">
         <v>1095</v>
       </c>
@@ -55856,7 +55916,7 @@
       <c r="AM473" s="1"/>
       <c r="AN473" s="83"/>
     </row>
-    <row r="474" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="474" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" s="3" t="s">
         <v>1097</v>
       </c>
@@ -55939,7 +55999,7 @@
       <c r="AM474" s="1"/>
       <c r="AN474" s="83"/>
     </row>
-    <row r="475" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="475" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" s="3" t="s">
         <v>1099</v>
       </c>
@@ -56022,7 +56082,7 @@
       <c r="AM475" s="1"/>
       <c r="AN475" s="83"/>
     </row>
-    <row r="476" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="476" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" s="3" t="s">
         <v>1101</v>
       </c>
@@ -56105,7 +56165,7 @@
       <c r="AM476" s="1"/>
       <c r="AN476" s="83"/>
     </row>
-    <row r="477" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="477" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" s="3" t="s">
         <v>1103</v>
       </c>
@@ -56192,7 +56252,7 @@
       <c r="AM477" s="1"/>
       <c r="AN477" s="83"/>
     </row>
-    <row r="478" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="478" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" s="3" t="s">
         <v>1104</v>
       </c>
@@ -56279,7 +56339,7 @@
       <c r="AM478" s="1"/>
       <c r="AN478" s="83"/>
     </row>
-    <row r="479" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="479" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" s="3" t="s">
         <v>1105</v>
       </c>
@@ -56366,7 +56426,7 @@
       <c r="AM479" s="1"/>
       <c r="AN479" s="83"/>
     </row>
-    <row r="480" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="480" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" s="3" t="s">
         <v>1106</v>
       </c>
@@ -56449,7 +56509,7 @@
       <c r="AM480" s="1"/>
       <c r="AN480" s="83"/>
     </row>
-    <row r="481" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="481" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" s="3" t="s">
         <v>1108</v>
       </c>
@@ -56532,7 +56592,7 @@
       <c r="AM481" s="1"/>
       <c r="AN481" s="83"/>
     </row>
-    <row r="482" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="482" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" s="3" t="s">
         <v>1109</v>
       </c>
@@ -56615,7 +56675,7 @@
       <c r="AM482" s="1"/>
       <c r="AN482" s="83"/>
     </row>
-    <row r="483" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="483" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" s="3" t="s">
         <v>1110</v>
       </c>
@@ -56702,7 +56762,7 @@
       <c r="AM483" s="1"/>
       <c r="AN483" s="83"/>
     </row>
-    <row r="484" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="484" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" s="3" t="s">
         <v>1111</v>
       </c>
@@ -56789,7 +56849,7 @@
       <c r="AM484" s="1"/>
       <c r="AN484" s="83"/>
     </row>
-    <row r="485" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="485" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="3" t="s">
         <v>1112</v>
       </c>
@@ -56872,7 +56932,7 @@
       <c r="AM485" s="1"/>
       <c r="AN485" s="83"/>
     </row>
-    <row r="486" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="486" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="22" t="s">
         <v>1114</v>
       </c>
@@ -56955,7 +57015,7 @@
       <c r="AM486" s="1"/>
       <c r="AN486" s="83"/>
     </row>
-    <row r="487" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="487" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" s="22" t="s">
         <v>1115</v>
       </c>
@@ -57038,7 +57098,7 @@
       <c r="AM487" s="1"/>
       <c r="AN487" s="83"/>
     </row>
-    <row r="488" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="488" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" s="22" t="s">
         <v>1117</v>
       </c>
@@ -57121,7 +57181,7 @@
       <c r="AM488" s="1"/>
       <c r="AN488" s="83"/>
     </row>
-    <row r="489" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="489" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" s="22" t="s">
         <v>1118</v>
       </c>
@@ -57204,7 +57264,7 @@
       <c r="AM489" s="1"/>
       <c r="AN489" s="83"/>
     </row>
-    <row r="490" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="490" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="22" t="s">
         <v>1119</v>
       </c>
@@ -57287,7 +57347,7 @@
       <c r="AM490" s="1"/>
       <c r="AN490" s="83"/>
     </row>
-    <row r="491" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="491" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" s="22" t="s">
         <v>1120</v>
       </c>
@@ -57378,7 +57438,7 @@
       <c r="AM491" s="1"/>
       <c r="AN491" s="83"/>
     </row>
-    <row r="492" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="492" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" s="22" t="s">
         <v>453</v>
       </c>
@@ -57457,7 +57517,7 @@
       <c r="AM492" s="1"/>
       <c r="AN492" s="83"/>
     </row>
-    <row r="493" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="493" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" s="22" t="s">
         <v>1123</v>
       </c>
@@ -57526,7 +57586,7 @@
       <c r="AM493" s="1"/>
       <c r="AN493" s="83"/>
     </row>
-    <row r="494" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="494" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494" s="22" t="s">
         <v>1125</v>
       </c>
@@ -57595,7 +57655,7 @@
       <c r="AM494" s="1"/>
       <c r="AN494" s="83"/>
     </row>
-    <row r="495" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="495" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495" s="22" t="s">
         <v>1126</v>
       </c>
@@ -57664,7 +57724,7 @@
       <c r="AM495" s="1"/>
       <c r="AN495" s="83"/>
     </row>
-    <row r="496" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="496" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" s="22" t="s">
         <v>1127</v>
       </c>
@@ -57733,7 +57793,7 @@
       <c r="AM496" s="1"/>
       <c r="AN496" s="83"/>
     </row>
-    <row r="497" spans="1:41" s="26" customFormat="1" hidden="1">
+    <row r="497" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497" s="22" t="s">
         <v>1128</v>
       </c>
@@ -57802,7 +57862,7 @@
       <c r="AM497" s="1"/>
       <c r="AN497" s="83"/>
     </row>
-    <row r="498" spans="1:41" s="26" customFormat="1" ht="20.45">
+    <row r="498" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" s="19" t="s">
         <v>1129</v>
       </c>
@@ -57917,7 +57977,7 @@
       </c>
       <c r="AO498" s="81"/>
     </row>
-    <row r="499" spans="1:41" s="26" customFormat="1">
+    <row r="499" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" s="19" t="s">
         <v>1136</v>
       </c>
@@ -58032,7 +58092,7 @@
       </c>
       <c r="AO499" s="81"/>
     </row>
-    <row r="500" spans="1:41" s="26" customFormat="1">
+    <row r="500" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" s="19" t="s">
         <v>1141</v>
       </c>
@@ -58145,7 +58205,7 @@
       </c>
       <c r="AO500" s="81"/>
     </row>
-    <row r="501" spans="1:41" s="26" customFormat="1">
+    <row r="501" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" s="19" t="s">
         <v>1147</v>
       </c>
@@ -58260,7 +58320,7 @@
       </c>
       <c r="AO501" s="81"/>
     </row>
-    <row r="502" spans="1:41" s="26" customFormat="1" ht="20.45">
+    <row r="502" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" s="19" t="s">
         <v>1150</v>
       </c>
@@ -58375,7 +58435,7 @@
       </c>
       <c r="AO502" s="81"/>
     </row>
-    <row r="503" spans="1:41" s="26" customFormat="1">
+    <row r="503" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" s="19" t="s">
         <v>1154</v>
       </c>
@@ -58490,7 +58550,7 @@
       </c>
       <c r="AO503" s="81"/>
     </row>
-    <row r="504" spans="1:41" s="26" customFormat="1">
+    <row r="504" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" s="19" t="s">
         <v>1158</v>
       </c>
@@ -58592,7 +58652,7 @@
       <c r="AN504" s="83"/>
       <c r="AO504" s="81"/>
     </row>
-    <row r="505" spans="1:41" s="26" customFormat="1">
+    <row r="505" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" s="19" t="s">
         <v>1162</v>
       </c>
@@ -58707,7 +58767,7 @@
       </c>
       <c r="AO505" s="81"/>
     </row>
-    <row r="506" spans="1:41" s="26" customFormat="1">
+    <row r="506" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" s="19" t="s">
         <v>1166</v>
       </c>
@@ -58822,7 +58882,7 @@
       </c>
       <c r="AO506" s="81"/>
     </row>
-    <row r="507" spans="1:41" s="26" customFormat="1" ht="30.6">
+    <row r="507" spans="1:41" s="26" customFormat="1" ht="30.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" s="19" t="s">
         <v>1169</v>
       </c>
@@ -58937,7 +58997,7 @@
       </c>
       <c r="AO507" s="81"/>
     </row>
-    <row r="508" spans="1:41" s="26" customFormat="1">
+    <row r="508" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" s="19" t="s">
         <v>1172</v>
       </c>
@@ -59042,7 +59102,7 @@
       <c r="AN508" s="83"/>
       <c r="AO508" s="81"/>
     </row>
-    <row r="509" spans="1:41" s="26" customFormat="1">
+    <row r="509" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" s="19" t="s">
         <v>1174</v>
       </c>
@@ -59157,7 +59217,7 @@
       </c>
       <c r="AO509" s="81"/>
     </row>
-    <row r="510" spans="1:41" s="26" customFormat="1">
+    <row r="510" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" s="19" t="s">
         <v>1177</v>
       </c>
@@ -59263,7 +59323,7 @@
       </c>
       <c r="AO510" s="81"/>
     </row>
-    <row r="511" spans="1:41" s="26" customFormat="1">
+    <row r="511" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" s="19" t="s">
         <v>1179</v>
       </c>
@@ -59366,7 +59426,7 @@
       <c r="AN511" s="83"/>
       <c r="AO511" s="81"/>
     </row>
-    <row r="512" spans="1:41" s="26" customFormat="1">
+    <row r="512" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" s="19" t="s">
         <v>1181</v>
       </c>
@@ -59481,7 +59541,7 @@
       </c>
       <c r="AO512" s="81"/>
     </row>
-    <row r="513" spans="1:41" s="26" customFormat="1" ht="20.45">
+    <row r="513" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" s="19" t="s">
         <v>1184</v>
       </c>
@@ -59596,7 +59656,7 @@
       </c>
       <c r="AO513" s="81"/>
     </row>
-    <row r="514" spans="1:41" s="26" customFormat="1">
+    <row r="514" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" s="19" t="s">
         <v>1187</v>
       </c>
@@ -59711,7 +59771,7 @@
       </c>
       <c r="AO514" s="81"/>
     </row>
-    <row r="515" spans="1:41" s="26" customFormat="1">
+    <row r="515" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" s="19" t="s">
         <v>1190</v>
       </c>
@@ -59826,7 +59886,7 @@
       </c>
       <c r="AO515" s="81"/>
     </row>
-    <row r="516" spans="1:41" s="26" customFormat="1">
+    <row r="516" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="19" t="s">
         <v>1193</v>
       </c>
@@ -59939,7 +59999,7 @@
       </c>
       <c r="AO516" s="81"/>
     </row>
-    <row r="517" spans="1:41" s="26" customFormat="1" ht="20.45">
+    <row r="517" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" s="19" t="s">
         <v>388</v>
       </c>
@@ -60054,7 +60114,7 @@
       </c>
       <c r="AO517" s="81"/>
     </row>
-    <row r="518" spans="1:41" s="26" customFormat="1">
+    <row r="518" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" s="19" t="s">
         <v>1198</v>
       </c>
@@ -60138,7 +60198,7 @@
       </c>
       <c r="AO518" s="81"/>
     </row>
-    <row r="519" spans="1:41" s="26" customFormat="1">
+    <row r="519" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519" s="19" t="s">
         <v>1199</v>
       </c>
@@ -60208,7 +60268,7 @@
       </c>
       <c r="AO519" s="81"/>
     </row>
-    <row r="520" spans="1:41" s="26" customFormat="1">
+    <row r="520" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" s="19" t="s">
         <v>1200</v>
       </c>
@@ -60323,7 +60383,7 @@
       </c>
       <c r="AO520" s="81"/>
     </row>
-    <row r="521" spans="1:41" s="26" customFormat="1">
+    <row r="521" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" s="19" t="s">
         <v>1205</v>
       </c>
@@ -60434,7 +60494,7 @@
       </c>
       <c r="AO521" s="81"/>
     </row>
-    <row r="522" spans="1:41" s="26" customFormat="1" ht="20.45">
+    <row r="522" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" s="19" t="s">
         <v>1207</v>
       </c>
@@ -60549,7 +60609,7 @@
       </c>
       <c r="AO522" s="81"/>
     </row>
-    <row r="523" spans="1:41" s="26" customFormat="1">
+    <row r="523" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" s="19" t="s">
         <v>1210</v>
       </c>
@@ -60654,7 +60714,7 @@
       <c r="AN523" s="83"/>
       <c r="AO523" s="81"/>
     </row>
-    <row r="524" spans="1:41" s="26" customFormat="1">
+    <row r="524" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" s="19" t="s">
         <v>1214</v>
       </c>
@@ -60767,7 +60827,7 @@
       </c>
       <c r="AO524" s="81"/>
     </row>
-    <row r="525" spans="1:41" s="26" customFormat="1">
+    <row r="525" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" s="19" t="s">
         <v>1218</v>
       </c>
@@ -60868,7 +60928,7 @@
       <c r="AN525" s="83"/>
       <c r="AO525" s="81"/>
     </row>
-    <row r="526" spans="1:41" s="26" customFormat="1">
+    <row r="526" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" s="19" t="s">
         <v>1221</v>
       </c>
@@ -60983,7 +61043,7 @@
       </c>
       <c r="AO526" s="81"/>
     </row>
-    <row r="527" spans="1:41" s="26" customFormat="1">
+    <row r="527" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" s="19" t="s">
         <v>1224</v>
       </c>
@@ -61098,7 +61158,7 @@
       </c>
       <c r="AO527" s="81"/>
     </row>
-    <row r="528" spans="1:41" s="26" customFormat="1">
+    <row r="528" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" s="19" t="s">
         <v>1228</v>
       </c>
@@ -61213,7 +61273,7 @@
       </c>
       <c r="AO528" s="81"/>
     </row>
-    <row r="529" spans="1:41" s="26" customFormat="1" ht="20.45">
+    <row r="529" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="19" t="s">
         <v>1231</v>
       </c>
@@ -61329,7 +61389,7 @@
       </c>
       <c r="AO529" s="81"/>
     </row>
-    <row r="530" spans="1:41" s="26" customFormat="1">
+    <row r="530" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" s="19" t="s">
         <v>723</v>
       </c>
@@ -61429,7 +61489,7 @@
       <c r="AN530" s="83"/>
       <c r="AO530" s="81"/>
     </row>
-    <row r="531" spans="1:41" s="26" customFormat="1">
+    <row r="531" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" s="19" t="s">
         <v>1234</v>
       </c>
@@ -61542,7 +61602,7 @@
       </c>
       <c r="AO531" s="81"/>
     </row>
-    <row r="532" spans="1:41" s="26" customFormat="1">
+    <row r="532" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" s="19" t="s">
         <v>1237</v>
       </c>
@@ -61646,7 +61706,7 @@
       <c r="AN532" s="83"/>
       <c r="AO532" s="81"/>
     </row>
-    <row r="533" spans="1:41" s="26" customFormat="1">
+    <row r="533" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" s="19" t="s">
         <v>1239</v>
       </c>
@@ -61750,7 +61810,7 @@
       <c r="AN533" s="83"/>
       <c r="AO533" s="81"/>
     </row>
-    <row r="534" spans="1:41" s="26" customFormat="1">
+    <row r="534" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" s="19" t="s">
         <v>1241</v>
       </c>
@@ -61865,7 +61925,7 @@
       </c>
       <c r="AO534" s="81"/>
     </row>
-    <row r="535" spans="1:41" s="26" customFormat="1">
+    <row r="535" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" s="19" t="s">
         <v>1245</v>
       </c>
@@ -61976,7 +62036,7 @@
       <c r="AN535" s="83"/>
       <c r="AO535" s="81"/>
     </row>
-    <row r="536" spans="1:41" s="26" customFormat="1">
+    <row r="536" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" s="19" t="s">
         <v>1247</v>
       </c>
@@ -62080,7 +62140,7 @@
       <c r="AN536" s="83"/>
       <c r="AO536" s="81"/>
     </row>
-    <row r="537" spans="1:41" s="26" customFormat="1">
+    <row r="537" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" s="19" t="s">
         <v>734</v>
       </c>
@@ -62193,7 +62253,7 @@
       </c>
       <c r="AO537" s="81"/>
     </row>
-    <row r="538" spans="1:41" s="26" customFormat="1">
+    <row r="538" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" s="19" t="s">
         <v>1251</v>
       </c>
@@ -62305,7 +62365,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="539" spans="1:41" s="26" customFormat="1">
+    <row r="539" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" s="19" t="s">
         <v>1253</v>
       </c>
@@ -62419,7 +62479,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="540" spans="1:41" s="26" customFormat="1">
+    <row r="540" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" s="19" t="s">
         <v>1256</v>
       </c>
@@ -62522,7 +62582,7 @@
       <c r="AM540" s="1"/>
       <c r="AN540" s="83"/>
     </row>
-    <row r="541" spans="1:41" s="26" customFormat="1">
+    <row r="541" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" s="19" t="s">
         <v>719</v>
       </c>
@@ -62621,7 +62681,7 @@
       <c r="AM541" s="1"/>
       <c r="AN541" s="83"/>
     </row>
-    <row r="542" spans="1:41" s="26" customFormat="1">
+    <row r="542" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" s="19" t="s">
         <v>1259</v>
       </c>
@@ -62735,7 +62795,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="543" spans="1:41" s="26" customFormat="1">
+    <row r="543" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" s="19" t="s">
         <v>1261</v>
       </c>
@@ -62838,7 +62898,7 @@
       <c r="AM543" s="1"/>
       <c r="AN543" s="83"/>
     </row>
-    <row r="544" spans="1:41" s="26" customFormat="1">
+    <row r="544" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" s="19" t="s">
         <v>1263</v>
       </c>
@@ -62952,7 +63012,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="545" spans="1:40" s="26" customFormat="1">
+    <row r="545" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="19" t="s">
         <v>1266</v>
       </c>
@@ -63066,7 +63126,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="546" spans="1:40" s="26" customFormat="1">
+    <row r="546" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="19" t="s">
         <v>1268</v>
       </c>
@@ -63180,7 +63240,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="547" spans="1:40" s="26" customFormat="1">
+    <row r="547" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" s="19" t="s">
         <v>1270</v>
       </c>
@@ -63283,7 +63343,7 @@
       <c r="AM547" s="1"/>
       <c r="AN547" s="83"/>
     </row>
-    <row r="548" spans="1:40" s="26" customFormat="1">
+    <row r="548" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="19" t="s">
         <v>1271</v>
       </c>
@@ -63397,7 +63457,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="549" spans="1:40" s="26" customFormat="1">
+    <row r="549" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="19" t="s">
         <v>1274</v>
       </c>
@@ -63500,7 +63560,7 @@
       <c r="AM549" s="1"/>
       <c r="AN549" s="83"/>
     </row>
-    <row r="550" spans="1:40" s="26" customFormat="1">
+    <row r="550" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="19" t="s">
         <v>1275</v>
       </c>
@@ -63603,7 +63663,7 @@
       <c r="AM550" s="1"/>
       <c r="AN550" s="83"/>
     </row>
-    <row r="551" spans="1:40" s="26" customFormat="1">
+    <row r="551" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" s="19" t="s">
         <v>1277</v>
       </c>
@@ -63706,7 +63766,7 @@
       <c r="AM551" s="1"/>
       <c r="AN551" s="83"/>
     </row>
-    <row r="552" spans="1:40" s="26" customFormat="1">
+    <row r="552" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" s="19" t="s">
         <v>738</v>
       </c>
@@ -63807,7 +63867,7 @@
       <c r="AM552" s="1"/>
       <c r="AN552" s="83"/>
     </row>
-    <row r="553" spans="1:40" s="26" customFormat="1">
+    <row r="553" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="19" t="s">
         <v>1278</v>
       </c>
@@ -63921,7 +63981,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="554" spans="1:40" s="26" customFormat="1">
+    <row r="554" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" s="19" t="s">
         <v>1282</v>
       </c>
@@ -64024,7 +64084,7 @@
       <c r="AM554" s="1"/>
       <c r="AN554" s="83"/>
     </row>
-    <row r="555" spans="1:40" s="26" customFormat="1">
+    <row r="555" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" s="19" t="s">
         <v>1283</v>
       </c>
@@ -64125,7 +64185,7 @@
       <c r="AM555" s="1"/>
       <c r="AN555" s="83"/>
     </row>
-    <row r="556" spans="1:40" s="26" customFormat="1">
+    <row r="556" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" s="19" t="s">
         <v>1284</v>
       </c>
@@ -64239,7 +64299,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="557" spans="1:40" s="26" customFormat="1">
+    <row r="557" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="19" t="s">
         <v>1287</v>
       </c>
@@ -64342,7 +64402,7 @@
       <c r="AM557" s="1"/>
       <c r="AN557" s="83"/>
     </row>
-    <row r="558" spans="1:40" s="26" customFormat="1">
+    <row r="558" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="19" t="s">
         <v>1289</v>
       </c>
@@ -64443,7 +64503,7 @@
       <c r="AM558" s="1"/>
       <c r="AN558" s="83"/>
     </row>
-    <row r="559" spans="1:40" s="26" customFormat="1">
+    <row r="559" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" s="19" t="s">
         <v>1291</v>
       </c>
@@ -64544,7 +64604,7 @@
       <c r="AM559" s="1"/>
       <c r="AN559" s="83"/>
     </row>
-    <row r="560" spans="1:40" s="26" customFormat="1">
+    <row r="560" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" s="19" t="s">
         <v>1293</v>
       </c>
@@ -64656,7 +64716,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="561" spans="1:40" s="26" customFormat="1">
+    <row r="561" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" s="19" t="s">
         <v>586</v>
       </c>
@@ -64759,7 +64819,7 @@
       <c r="AM561" s="1"/>
       <c r="AN561" s="83"/>
     </row>
-    <row r="562" spans="1:40" s="26" customFormat="1">
+    <row r="562" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" s="19" t="s">
         <v>1296</v>
       </c>
@@ -64873,7 +64933,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="563" spans="1:40" s="26" customFormat="1">
+    <row r="563" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" s="19" t="s">
         <v>1298</v>
       </c>
@@ -64987,7 +65047,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="564" spans="1:40" s="26" customFormat="1">
+    <row r="564" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="19" t="s">
         <v>1301</v>
       </c>
@@ -65099,7 +65159,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="565" spans="1:40" s="26" customFormat="1">
+    <row r="565" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="19" t="s">
         <v>1304</v>
       </c>
@@ -65200,7 +65260,7 @@
       <c r="AM565" s="1"/>
       <c r="AN565" s="83"/>
     </row>
-    <row r="566" spans="1:40" s="26" customFormat="1">
+    <row r="566" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="19" t="s">
         <v>1306</v>
       </c>
@@ -65303,7 +65363,7 @@
       <c r="AM566" s="1"/>
       <c r="AN566" s="83"/>
     </row>
-    <row r="567" spans="1:40" s="26" customFormat="1">
+    <row r="567" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" s="32" t="s">
         <v>1308</v>
       </c>
@@ -65404,7 +65464,7 @@
       <c r="AM567" s="1"/>
       <c r="AN567" s="83"/>
     </row>
-    <row r="568" spans="1:40" s="26" customFormat="1">
+    <row r="568" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" s="19" t="s">
         <v>1310</v>
       </c>
@@ -65507,7 +65567,7 @@
       <c r="AM568" s="1"/>
       <c r="AN568" s="83"/>
     </row>
-    <row r="569" spans="1:40" s="26" customFormat="1">
+    <row r="569" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" s="19" t="s">
         <v>1312</v>
       </c>
@@ -65621,7 +65681,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="570" spans="1:40" s="26" customFormat="1">
+    <row r="570" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" s="19" t="s">
         <v>1315</v>
       </c>
@@ -65722,7 +65782,7 @@
       <c r="AM570" s="1"/>
       <c r="AN570" s="83"/>
     </row>
-    <row r="571" spans="1:40" s="26" customFormat="1">
+    <row r="571" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="19" t="s">
         <v>1317</v>
       </c>
@@ -65823,7 +65883,7 @@
       <c r="AM571" s="1"/>
       <c r="AN571" s="83"/>
     </row>
-    <row r="572" spans="1:40" s="26" customFormat="1">
+    <row r="572" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" s="19" t="s">
         <v>1318</v>
       </c>
@@ -65924,7 +65984,7 @@
       <c r="AM572" s="1"/>
       <c r="AN572" s="83"/>
     </row>
-    <row r="573" spans="1:40" s="26" customFormat="1">
+    <row r="573" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" s="19" t="s">
         <v>1320</v>
       </c>
@@ -66027,7 +66087,7 @@
       <c r="AM573" s="1"/>
       <c r="AN573" s="83"/>
     </row>
-    <row r="574" spans="1:40" s="26" customFormat="1">
+    <row r="574" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="19" t="s">
         <v>1322</v>
       </c>
@@ -66130,7 +66190,7 @@
       <c r="AM574" s="1"/>
       <c r="AN574" s="83"/>
     </row>
-    <row r="575" spans="1:40" s="26" customFormat="1">
+    <row r="575" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" s="19" t="s">
         <v>1325</v>
       </c>
@@ -66233,7 +66293,7 @@
       <c r="AM575" s="1"/>
       <c r="AN575" s="83"/>
     </row>
-    <row r="576" spans="1:40" s="26" customFormat="1">
+    <row r="576" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" s="19" t="s">
         <v>1327</v>
       </c>
@@ -66336,7 +66396,7 @@
       <c r="AM576" s="1"/>
       <c r="AN576" s="83"/>
     </row>
-    <row r="577" spans="1:40" s="26" customFormat="1">
+    <row r="577" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" s="19" t="s">
         <v>1329</v>
       </c>
@@ -66439,7 +66499,7 @@
       <c r="AM577" s="1"/>
       <c r="AN577" s="83"/>
     </row>
-    <row r="578" spans="1:40" s="26" customFormat="1">
+    <row r="578" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" s="19" t="s">
         <v>1331</v>
       </c>
@@ -66540,7 +66600,7 @@
       <c r="AM578" s="1"/>
       <c r="AN578" s="83"/>
     </row>
-    <row r="579" spans="1:40" s="26" customFormat="1">
+    <row r="579" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579" s="19" t="s">
         <v>1332</v>
       </c>
@@ -66643,7 +66703,7 @@
       <c r="AM579" s="1"/>
       <c r="AN579" s="83"/>
     </row>
-    <row r="580" spans="1:40" s="26" customFormat="1">
+    <row r="580" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" s="19" t="s">
         <v>1334</v>
       </c>
@@ -66746,7 +66806,7 @@
       <c r="AM580" s="1"/>
       <c r="AN580" s="83"/>
     </row>
-    <row r="581" spans="1:40" s="26" customFormat="1">
+    <row r="581" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" s="19" t="s">
         <v>1335</v>
       </c>
@@ -66849,7 +66909,7 @@
       <c r="AM581" s="1"/>
       <c r="AN581" s="83"/>
     </row>
-    <row r="582" spans="1:40" s="26" customFormat="1">
+    <row r="582" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582" s="19" t="s">
         <v>1337</v>
       </c>
@@ -66952,7 +67012,7 @@
       <c r="AM582" s="1"/>
       <c r="AN582" s="83"/>
     </row>
-    <row r="583" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="583" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="19" t="s">
         <v>1339</v>
       </c>
@@ -67015,7 +67075,7 @@
       <c r="AM583" s="1"/>
       <c r="AN583" s="83"/>
     </row>
-    <row r="584" spans="1:40" s="26" customFormat="1">
+    <row r="584" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="19" t="s">
         <v>1340</v>
       </c>
@@ -67118,7 +67178,7 @@
       <c r="AM584" s="1"/>
       <c r="AN584" s="83"/>
     </row>
-    <row r="585" spans="1:40" s="26" customFormat="1">
+    <row r="585" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" s="19" t="s">
         <v>1342</v>
       </c>
@@ -67221,7 +67281,7 @@
       <c r="AM585" s="1"/>
       <c r="AN585" s="83"/>
     </row>
-    <row r="586" spans="1:40" s="26" customFormat="1">
+    <row r="586" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" s="19" t="s">
         <v>1344</v>
       </c>
@@ -67324,7 +67384,7 @@
       <c r="AM586" s="1"/>
       <c r="AN586" s="83"/>
     </row>
-    <row r="587" spans="1:40" s="26" customFormat="1">
+    <row r="587" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" s="19" t="s">
         <v>1346</v>
       </c>
@@ -67423,7 +67483,7 @@
       <c r="AM587" s="1"/>
       <c r="AN587" s="83"/>
     </row>
-    <row r="588" spans="1:40" s="26" customFormat="1">
+    <row r="588" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" s="19" t="s">
         <v>299</v>
       </c>
@@ -67522,7 +67582,7 @@
       <c r="AM588" s="1"/>
       <c r="AN588" s="83"/>
     </row>
-    <row r="589" spans="1:40" s="26" customFormat="1">
+    <row r="589" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" s="19" t="s">
         <v>1349</v>
       </c>
@@ -67625,7 +67685,7 @@
       <c r="AM589" s="1"/>
       <c r="AN589" s="83"/>
     </row>
-    <row r="590" spans="1:40" s="26" customFormat="1">
+    <row r="590" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" s="19" t="s">
         <v>1351</v>
       </c>
@@ -67728,7 +67788,7 @@
       <c r="AM590" s="1"/>
       <c r="AN590" s="83"/>
     </row>
-    <row r="591" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="591" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591" s="22" t="s">
         <v>1353</v>
       </c>
@@ -67803,7 +67863,7 @@
       <c r="AM591" s="1"/>
       <c r="AN591" s="83"/>
     </row>
-    <row r="592" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="592" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592" s="22" t="s">
         <v>1356</v>
       </c>
@@ -67876,7 +67936,7 @@
       <c r="AM592" s="1"/>
       <c r="AN592" s="83"/>
     </row>
-    <row r="593" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="593" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" s="22" t="s">
         <v>1359</v>
       </c>
@@ -67949,7 +68009,7 @@
       <c r="AM593" s="1"/>
       <c r="AN593" s="83"/>
     </row>
-    <row r="594" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="594" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" s="22" t="s">
         <v>1360</v>
       </c>
@@ -68022,7 +68082,7 @@
       <c r="AM594" s="1"/>
       <c r="AN594" s="83"/>
     </row>
-    <row r="595" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="595" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="22" t="s">
         <v>647</v>
       </c>
@@ -68095,7 +68155,7 @@
       <c r="AM595" s="1"/>
       <c r="AN595" s="83"/>
     </row>
-    <row r="596" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="596" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="22" t="s">
         <v>1363</v>
       </c>
@@ -68168,7 +68228,7 @@
       <c r="AM596" s="1"/>
       <c r="AN596" s="83"/>
     </row>
-    <row r="597" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="597" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" s="22" t="s">
         <v>1364</v>
       </c>
@@ -68241,7 +68301,7 @@
       <c r="AM597" s="1"/>
       <c r="AN597" s="83"/>
     </row>
-    <row r="598" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="598" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" s="22" t="s">
         <v>1365</v>
       </c>
@@ -68314,7 +68374,7 @@
       <c r="AM598" s="1"/>
       <c r="AN598" s="83"/>
     </row>
-    <row r="599" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="599" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="22" t="s">
         <v>1368</v>
       </c>
@@ -68387,7 +68447,7 @@
       <c r="AM599" s="1"/>
       <c r="AN599" s="83"/>
     </row>
-    <row r="600" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="600" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" s="22" t="s">
         <v>1369</v>
       </c>
@@ -68460,7 +68520,7 @@
       <c r="AM600" s="1"/>
       <c r="AN600" s="83"/>
     </row>
-    <row r="601" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="601" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" s="22" t="s">
         <v>1371</v>
       </c>
@@ -68533,7 +68593,7 @@
       <c r="AM601" s="1"/>
       <c r="AN601" s="83"/>
     </row>
-    <row r="602" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="602" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" s="22" t="s">
         <v>868</v>
       </c>
@@ -68606,7 +68666,7 @@
       <c r="AM602" s="1"/>
       <c r="AN602" s="83"/>
     </row>
-    <row r="603" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="603" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603" s="22" t="s">
         <v>1373</v>
       </c>
@@ -68679,7 +68739,7 @@
       <c r="AM603" s="1"/>
       <c r="AN603" s="83"/>
     </row>
-    <row r="604" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="604" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604" s="22" t="s">
         <v>1374</v>
       </c>
@@ -68752,7 +68812,7 @@
       <c r="AM604" s="1"/>
       <c r="AN604" s="83"/>
     </row>
-    <row r="605" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="605" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605" s="22" t="s">
         <v>655</v>
       </c>
@@ -68825,7 +68885,7 @@
       <c r="AM605" s="1"/>
       <c r="AN605" s="83"/>
     </row>
-    <row r="606" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="606" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606" s="22" t="s">
         <v>275</v>
       </c>
@@ -68900,7 +68960,7 @@
       <c r="AM606" s="1"/>
       <c r="AN606" s="83"/>
     </row>
-    <row r="607" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="607" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607" s="22" t="s">
         <v>1377</v>
       </c>
@@ -68973,7 +69033,7 @@
       <c r="AM607" s="1"/>
       <c r="AN607" s="83"/>
     </row>
-    <row r="608" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="608" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608" s="22" t="s">
         <v>1378</v>
       </c>
@@ -69046,7 +69106,7 @@
       <c r="AM608" s="1"/>
       <c r="AN608" s="83"/>
     </row>
-    <row r="609" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="609" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609" s="22" t="s">
         <v>378</v>
       </c>
@@ -69119,7 +69179,7 @@
       <c r="AM609" s="1"/>
       <c r="AN609" s="83"/>
     </row>
-    <row r="610" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="610" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610" s="22" t="s">
         <v>370</v>
       </c>
@@ -69192,7 +69252,7 @@
       <c r="AM610" s="1"/>
       <c r="AN610" s="83"/>
     </row>
-    <row r="611" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="611" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611" s="22" t="s">
         <v>1379</v>
       </c>
@@ -69265,7 +69325,7 @@
       <c r="AM611" s="1"/>
       <c r="AN611" s="83"/>
     </row>
-    <row r="612" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="612" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612" s="22" t="s">
         <v>1380</v>
       </c>
@@ -69338,7 +69398,7 @@
       <c r="AM612" s="1"/>
       <c r="AN612" s="83"/>
     </row>
-    <row r="613" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="613" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613" s="22" t="s">
         <v>1381</v>
       </c>
@@ -69411,7 +69471,7 @@
       <c r="AM613" s="1"/>
       <c r="AN613" s="83"/>
     </row>
-    <row r="614" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="614" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614" s="22" t="s">
         <v>1383</v>
       </c>
@@ -69484,7 +69544,7 @@
       <c r="AM614" s="1"/>
       <c r="AN614" s="83"/>
     </row>
-    <row r="615" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="615" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615" s="22" t="s">
         <v>672</v>
       </c>
@@ -69557,7 +69617,7 @@
       <c r="AM615" s="1"/>
       <c r="AN615" s="83"/>
     </row>
-    <row r="616" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="616" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616" s="22" t="s">
         <v>1384</v>
       </c>
@@ -69630,7 +69690,7 @@
       <c r="AM616" s="1"/>
       <c r="AN616" s="83"/>
     </row>
-    <row r="617" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="617" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617" s="22" t="s">
         <v>1386</v>
       </c>
@@ -69703,7 +69763,7 @@
       <c r="AM617" s="1"/>
       <c r="AN617" s="83"/>
     </row>
-    <row r="618" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="618" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618" s="22" t="s">
         <v>880</v>
       </c>
@@ -69776,7 +69836,7 @@
       <c r="AM618" s="1"/>
       <c r="AN618" s="83"/>
     </row>
-    <row r="619" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="619" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619" s="22" t="s">
         <v>907</v>
       </c>
@@ -69849,7 +69909,7 @@
       <c r="AM619" s="1"/>
       <c r="AN619" s="83"/>
     </row>
-    <row r="620" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="620" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620" s="22" t="s">
         <v>877</v>
       </c>
@@ -69922,7 +69982,7 @@
       <c r="AM620" s="1"/>
       <c r="AN620" s="83"/>
     </row>
-    <row r="621" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="621" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621" s="22" t="s">
         <v>1389</v>
       </c>
@@ -69995,7 +70055,7 @@
       <c r="AM621" s="1"/>
       <c r="AN621" s="83"/>
     </row>
-    <row r="622" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="622" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622" s="22" t="s">
         <v>1390</v>
       </c>
@@ -70068,7 +70128,7 @@
       <c r="AM622" s="1"/>
       <c r="AN622" s="83"/>
     </row>
-    <row r="623" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="623" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" s="22" t="s">
         <v>859</v>
       </c>
@@ -70141,7 +70201,7 @@
       <c r="AM623" s="1"/>
       <c r="AN623" s="83"/>
     </row>
-    <row r="624" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="624" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" s="22" t="s">
         <v>1392</v>
       </c>
@@ -70214,7 +70274,7 @@
       <c r="AM624" s="1"/>
       <c r="AN624" s="83"/>
     </row>
-    <row r="625" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="625" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" s="22" t="s">
         <v>1393</v>
       </c>
@@ -70287,7 +70347,7 @@
       <c r="AM625" s="1"/>
       <c r="AN625" s="83"/>
     </row>
-    <row r="626" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="626" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626" s="22" t="s">
         <v>406</v>
       </c>
@@ -70360,7 +70420,7 @@
       <c r="AM626" s="1"/>
       <c r="AN626" s="83"/>
     </row>
-    <row r="627" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="627" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A627" s="22" t="s">
         <v>1396</v>
       </c>
@@ -70433,7 +70493,7 @@
       <c r="AM627" s="1"/>
       <c r="AN627" s="83"/>
     </row>
-    <row r="628" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="628" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628" s="22" t="s">
         <v>921</v>
       </c>
@@ -70506,7 +70566,7 @@
       <c r="AM628" s="1"/>
       <c r="AN628" s="83"/>
     </row>
-    <row r="629" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="629" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629" s="22" t="s">
         <v>1398</v>
       </c>
@@ -70579,7 +70639,7 @@
       <c r="AM629" s="1"/>
       <c r="AN629" s="83"/>
     </row>
-    <row r="630" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="630" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" s="22" t="s">
         <v>892</v>
       </c>
@@ -70652,7 +70712,7 @@
       <c r="AM630" s="1"/>
       <c r="AN630" s="83"/>
     </row>
-    <row r="631" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="631" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631" s="22" t="s">
         <v>1400</v>
       </c>
@@ -70725,7 +70785,7 @@
       <c r="AM631" s="1"/>
       <c r="AN631" s="83"/>
     </row>
-    <row r="632" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="632" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632" s="22" t="s">
         <v>1401</v>
       </c>
@@ -70798,7 +70858,7 @@
       <c r="AM632" s="1"/>
       <c r="AN632" s="83"/>
     </row>
-    <row r="633" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="633" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633" s="22" t="s">
         <v>1403</v>
       </c>
@@ -70871,7 +70931,7 @@
       <c r="AM633" s="1"/>
       <c r="AN633" s="83"/>
     </row>
-    <row r="634" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="634" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634" s="22" t="s">
         <v>1404</v>
       </c>
@@ -70944,7 +71004,7 @@
       <c r="AM634" s="1"/>
       <c r="AN634" s="83"/>
     </row>
-    <row r="635" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="635" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635" s="22" t="s">
         <v>1405</v>
       </c>
@@ -71017,7 +71077,7 @@
       <c r="AM635" s="1"/>
       <c r="AN635" s="83"/>
     </row>
-    <row r="636" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="636" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636" s="22" t="s">
         <v>1406</v>
       </c>
@@ -71090,7 +71150,7 @@
       <c r="AM636" s="1"/>
       <c r="AN636" s="83"/>
     </row>
-    <row r="637" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="637" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637" s="22" t="s">
         <v>1407</v>
       </c>
@@ -71163,7 +71223,7 @@
       <c r="AM637" s="1"/>
       <c r="AN637" s="83"/>
     </row>
-    <row r="638" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="638" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638" s="22" t="s">
         <v>1409</v>
       </c>
@@ -71236,7 +71296,7 @@
       <c r="AM638" s="1"/>
       <c r="AN638" s="83"/>
     </row>
-    <row r="639" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="639" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639" s="22" t="s">
         <v>1410</v>
       </c>
@@ -71309,7 +71369,7 @@
       <c r="AM639" s="1"/>
       <c r="AN639" s="83"/>
     </row>
-    <row r="640" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="640" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" s="22" t="s">
         <v>1411</v>
       </c>
@@ -71382,7 +71442,7 @@
       <c r="AM640" s="1"/>
       <c r="AN640" s="83"/>
     </row>
-    <row r="641" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="641" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" s="22" t="s">
         <v>898</v>
       </c>
@@ -71455,7 +71515,7 @@
       <c r="AM641" s="1"/>
       <c r="AN641" s="83"/>
     </row>
-    <row r="642" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="642" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" s="22" t="s">
         <v>967</v>
       </c>
@@ -71528,7 +71588,7 @@
       <c r="AM642" s="1"/>
       <c r="AN642" s="83"/>
     </row>
-    <row r="643" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="643" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" s="22" t="s">
         <v>1412</v>
       </c>
@@ -71601,7 +71661,7 @@
       <c r="AM643" s="1"/>
       <c r="AN643" s="83"/>
     </row>
-    <row r="644" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="644" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644" s="22" t="s">
         <v>1414</v>
       </c>
@@ -71674,7 +71734,7 @@
       <c r="AM644" s="1"/>
       <c r="AN644" s="83"/>
     </row>
-    <row r="645" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="645" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645" s="22" t="s">
         <v>874</v>
       </c>
@@ -71747,7 +71807,7 @@
       <c r="AM645" s="1"/>
       <c r="AN645" s="83"/>
     </row>
-    <row r="646" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="646" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646" s="22" t="s">
         <v>1415</v>
       </c>
@@ -71820,7 +71880,7 @@
       <c r="AM646" s="1"/>
       <c r="AN646" s="83"/>
     </row>
-    <row r="647" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="647" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647" s="22" t="s">
         <v>946</v>
       </c>
@@ -71893,7 +71953,7 @@
       <c r="AM647" s="1"/>
       <c r="AN647" s="83"/>
     </row>
-    <row r="648" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="648" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648" s="22" t="s">
         <v>1416</v>
       </c>
@@ -71966,7 +72026,7 @@
       <c r="AM648" s="1"/>
       <c r="AN648" s="83"/>
     </row>
-    <row r="649" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="649" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649" s="22" t="s">
         <v>97</v>
       </c>
@@ -72041,7 +72101,7 @@
       <c r="AM649" s="1"/>
       <c r="AN649" s="83"/>
     </row>
-    <row r="650" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="650" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650" s="22" t="s">
         <v>1419</v>
       </c>
@@ -72114,7 +72174,7 @@
       <c r="AM650" s="1"/>
       <c r="AN650" s="83"/>
     </row>
-    <row r="651" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="651" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651" s="22" t="s">
         <v>1420</v>
       </c>
@@ -72185,7 +72245,7 @@
       <c r="AM651" s="1"/>
       <c r="AN651" s="83"/>
     </row>
-    <row r="652" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="652" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A652" s="22" t="s">
         <v>650</v>
       </c>
@@ -72258,7 +72318,7 @@
       <c r="AM652" s="1"/>
       <c r="AN652" s="83"/>
     </row>
-    <row r="653" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="653" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653" s="22" t="s">
         <v>1421</v>
       </c>
@@ -72331,7 +72391,7 @@
       <c r="AM653" s="1"/>
       <c r="AN653" s="83"/>
     </row>
-    <row r="654" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="654" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654" s="22" t="s">
         <v>1423</v>
       </c>
@@ -72404,7 +72464,7 @@
       <c r="AM654" s="1"/>
       <c r="AN654" s="83"/>
     </row>
-    <row r="655" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="655" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655" s="22" t="s">
         <v>1424</v>
       </c>
@@ -72477,7 +72537,7 @@
       <c r="AM655" s="1"/>
       <c r="AN655" s="83"/>
     </row>
-    <row r="656" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="656" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A656" s="22" t="s">
         <v>1426</v>
       </c>
@@ -72550,7 +72610,7 @@
       <c r="AM656" s="1"/>
       <c r="AN656" s="83"/>
     </row>
-    <row r="657" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="657" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A657" s="22" t="s">
         <v>1427</v>
       </c>
@@ -72623,7 +72683,7 @@
       <c r="AM657" s="1"/>
       <c r="AN657" s="83"/>
     </row>
-    <row r="658" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="658" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A658" s="22" t="s">
         <v>1428</v>
       </c>
@@ -72696,7 +72756,7 @@
       <c r="AM658" s="1"/>
       <c r="AN658" s="83"/>
     </row>
-    <row r="659" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="659" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A659" s="22" t="s">
         <v>1429</v>
       </c>
@@ -72769,7 +72829,7 @@
       <c r="AM659" s="1"/>
       <c r="AN659" s="83"/>
     </row>
-    <row r="660" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="660" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660" s="22" t="s">
         <v>1430</v>
       </c>
@@ -72842,7 +72902,7 @@
       <c r="AM660" s="1"/>
       <c r="AN660" s="83"/>
     </row>
-    <row r="661" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="661" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A661" s="22" t="s">
         <v>1431</v>
       </c>
@@ -72915,7 +72975,7 @@
       <c r="AM661" s="1"/>
       <c r="AN661" s="83"/>
     </row>
-    <row r="662" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="662" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662" s="22" t="s">
         <v>1432</v>
       </c>
@@ -72988,7 +73048,7 @@
       <c r="AM662" s="1"/>
       <c r="AN662" s="83"/>
     </row>
-    <row r="663" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="663" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663" s="22" t="s">
         <v>966</v>
       </c>
@@ -73061,7 +73121,7 @@
       <c r="AM663" s="1"/>
       <c r="AN663" s="83"/>
     </row>
-    <row r="664" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="664" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664" s="22" t="s">
         <v>578</v>
       </c>
@@ -73144,7 +73204,7 @@
       <c r="AM664" s="1"/>
       <c r="AN664" s="83"/>
     </row>
-    <row r="665" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="665" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665" s="22" t="s">
         <v>1435</v>
       </c>
@@ -73217,7 +73277,7 @@
       <c r="AM665" s="1"/>
       <c r="AN665" s="83"/>
     </row>
-    <row r="666" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="666" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A666" s="22" t="s">
         <v>1437</v>
       </c>
@@ -73290,7 +73350,7 @@
       <c r="AM666" s="1"/>
       <c r="AN666" s="83"/>
     </row>
-    <row r="667" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="667" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A667" s="22" t="s">
         <v>1439</v>
       </c>
@@ -73363,7 +73423,7 @@
       <c r="AM667" s="1"/>
       <c r="AN667" s="83"/>
     </row>
-    <row r="668" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="668" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A668" s="22" t="s">
         <v>1441</v>
       </c>
@@ -73436,7 +73496,7 @@
       <c r="AM668" s="1"/>
       <c r="AN668" s="83"/>
     </row>
-    <row r="669" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="669" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A669" s="22" t="s">
         <v>1442</v>
       </c>
@@ -73509,7 +73569,7 @@
       <c r="AM669" s="1"/>
       <c r="AN669" s="83"/>
     </row>
-    <row r="670" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="670" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A670" s="22" t="s">
         <v>1443</v>
       </c>
@@ -73582,7 +73642,7 @@
       <c r="AM670" s="1"/>
       <c r="AN670" s="83"/>
     </row>
-    <row r="671" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="671" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A671" s="22" t="s">
         <v>1445</v>
       </c>
@@ -73655,7 +73715,7 @@
       <c r="AM671" s="1"/>
       <c r="AN671" s="83"/>
     </row>
-    <row r="672" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="672" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A672" s="22" t="s">
         <v>1447</v>
       </c>
@@ -73728,7 +73788,7 @@
       <c r="AM672" s="1"/>
       <c r="AN672" s="83"/>
     </row>
-    <row r="673" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="673" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A673" s="22" t="s">
         <v>1448</v>
       </c>
@@ -73801,7 +73861,7 @@
       <c r="AM673" s="1"/>
       <c r="AN673" s="83"/>
     </row>
-    <row r="674" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="674" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A674" s="22" t="s">
         <v>1449</v>
       </c>
@@ -73872,7 +73932,7 @@
       <c r="AM674" s="1"/>
       <c r="AN674" s="83"/>
     </row>
-    <row r="675" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="675" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A675" s="22" t="s">
         <v>1450</v>
       </c>
@@ -73945,7 +74005,7 @@
       <c r="AM675" s="1"/>
       <c r="AN675" s="83"/>
     </row>
-    <row r="676" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="676" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A676" s="22" t="s">
         <v>1451</v>
       </c>
@@ -74018,7 +74078,7 @@
       <c r="AM676" s="1"/>
       <c r="AN676" s="83"/>
     </row>
-    <row r="677" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="677" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A677" s="22" t="s">
         <v>1452</v>
       </c>
@@ -74091,7 +74151,7 @@
       <c r="AM677" s="1"/>
       <c r="AN677" s="83"/>
     </row>
-    <row r="678" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="678" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A678" s="22" t="s">
         <v>1453</v>
       </c>
@@ -74164,7 +74224,7 @@
       <c r="AM678" s="1"/>
       <c r="AN678" s="83"/>
     </row>
-    <row r="679" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="679" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A679" s="22" t="s">
         <v>1454</v>
       </c>
@@ -74237,7 +74297,7 @@
       <c r="AM679" s="1"/>
       <c r="AN679" s="83"/>
     </row>
-    <row r="680" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="680" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A680" s="22" t="s">
         <v>1455</v>
       </c>
@@ -74310,7 +74370,7 @@
       <c r="AM680" s="1"/>
       <c r="AN680" s="83"/>
     </row>
-    <row r="681" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="681" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A681" s="22" t="s">
         <v>870</v>
       </c>
@@ -74383,7 +74443,7 @@
       <c r="AM681" s="1"/>
       <c r="AN681" s="83"/>
     </row>
-    <row r="682" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="682" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A682" s="22" t="s">
         <v>1456</v>
       </c>
@@ -74456,7 +74516,7 @@
       <c r="AM682" s="1"/>
       <c r="AN682" s="83"/>
     </row>
-    <row r="683" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="683" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A683" s="22" t="s">
         <v>1457</v>
       </c>
@@ -74529,7 +74589,7 @@
       <c r="AM683" s="1"/>
       <c r="AN683" s="83"/>
     </row>
-    <row r="684" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="684" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A684" s="22" t="s">
         <v>1458</v>
       </c>
@@ -74602,7 +74662,7 @@
       <c r="AM684" s="1"/>
       <c r="AN684" s="83"/>
     </row>
-    <row r="685" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="685" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A685" s="22" t="s">
         <v>1459</v>
       </c>
@@ -74675,7 +74735,7 @@
       <c r="AM685" s="1"/>
       <c r="AN685" s="83"/>
     </row>
-    <row r="686" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="686" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A686" s="22" t="s">
         <v>1460</v>
       </c>
@@ -74748,7 +74808,7 @@
       <c r="AM686" s="1"/>
       <c r="AN686" s="83"/>
     </row>
-    <row r="687" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="687" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A687" s="22" t="s">
         <v>1461</v>
       </c>
@@ -74821,7 +74881,7 @@
       <c r="AM687" s="1"/>
       <c r="AN687" s="83"/>
     </row>
-    <row r="688" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="688" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A688" s="22" t="s">
         <v>1462</v>
       </c>
@@ -74894,7 +74954,7 @@
       <c r="AM688" s="1"/>
       <c r="AN688" s="83"/>
     </row>
-    <row r="689" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="689" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A689" s="22" t="s">
         <v>1463</v>
       </c>
@@ -74967,7 +75027,7 @@
       <c r="AM689" s="1"/>
       <c r="AN689" s="83"/>
     </row>
-    <row r="690" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="690" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A690" s="22" t="s">
         <v>1464</v>
       </c>
@@ -75040,7 +75100,7 @@
       <c r="AM690" s="1"/>
       <c r="AN690" s="83"/>
     </row>
-    <row r="691" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="691" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A691" s="22" t="s">
         <v>1465</v>
       </c>
@@ -75113,7 +75173,7 @@
       <c r="AM691" s="1"/>
       <c r="AN691" s="83"/>
     </row>
-    <row r="692" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="692" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A692" s="22" t="s">
         <v>1466</v>
       </c>
@@ -75186,7 +75246,7 @@
       <c r="AM692" s="1"/>
       <c r="AN692" s="83"/>
     </row>
-    <row r="693" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="693" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A693" s="22" t="s">
         <v>1467</v>
       </c>
@@ -75259,7 +75319,7 @@
       <c r="AM693" s="1"/>
       <c r="AN693" s="83"/>
     </row>
-    <row r="694" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="694" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A694" s="22" t="s">
         <v>1468</v>
       </c>
@@ -75332,7 +75392,7 @@
       <c r="AM694" s="1"/>
       <c r="AN694" s="83"/>
     </row>
-    <row r="695" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="695" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A695" s="22" t="s">
         <v>1469</v>
       </c>
@@ -75405,7 +75465,7 @@
       <c r="AM695" s="1"/>
       <c r="AN695" s="83"/>
     </row>
-    <row r="696" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="696" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A696" s="22" t="s">
         <v>1470</v>
       </c>
@@ -75478,7 +75538,7 @@
       <c r="AM696" s="1"/>
       <c r="AN696" s="83"/>
     </row>
-    <row r="697" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="697" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A697" s="22" t="s">
         <v>1081</v>
       </c>
@@ -75551,7 +75611,7 @@
       <c r="AM697" s="1"/>
       <c r="AN697" s="83"/>
     </row>
-    <row r="698" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="698" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A698" s="22" t="s">
         <v>1472</v>
       </c>
@@ -75624,7 +75684,7 @@
       <c r="AM698" s="1"/>
       <c r="AN698" s="83"/>
     </row>
-    <row r="699" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="699" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A699" s="22" t="s">
         <v>1473</v>
       </c>
@@ -75697,7 +75757,7 @@
       <c r="AM699" s="1"/>
       <c r="AN699" s="83"/>
     </row>
-    <row r="700" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="700" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A700" s="22" t="s">
         <v>1474</v>
       </c>
@@ -75770,7 +75830,7 @@
       <c r="AM700" s="1"/>
       <c r="AN700" s="83"/>
     </row>
-    <row r="701" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="701" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A701" s="22" t="s">
         <v>1475</v>
       </c>
@@ -75843,7 +75903,7 @@
       <c r="AM701" s="1"/>
       <c r="AN701" s="83"/>
     </row>
-    <row r="702" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="702" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A702" s="22" t="s">
         <v>1476</v>
       </c>
@@ -75916,7 +75976,7 @@
       <c r="AM702" s="1"/>
       <c r="AN702" s="83"/>
     </row>
-    <row r="703" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="703" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A703" s="22" t="s">
         <v>1477</v>
       </c>
@@ -75989,7 +76049,7 @@
       <c r="AM703" s="1"/>
       <c r="AN703" s="83"/>
     </row>
-    <row r="704" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="704" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A704" s="22" t="s">
         <v>1109</v>
       </c>
@@ -76062,7 +76122,7 @@
       <c r="AM704" s="1"/>
       <c r="AN704" s="83"/>
     </row>
-    <row r="705" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="705" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A705" s="22" t="s">
         <v>1478</v>
       </c>
@@ -76135,7 +76195,7 @@
       <c r="AM705" s="1"/>
       <c r="AN705" s="83"/>
     </row>
-    <row r="706" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="706" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A706" s="22" t="s">
         <v>1479</v>
       </c>
@@ -76208,7 +76268,7 @@
       <c r="AM706" s="1"/>
       <c r="AN706" s="83"/>
     </row>
-    <row r="707" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="707" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A707" s="22" t="s">
         <v>1480</v>
       </c>
@@ -76281,7 +76341,7 @@
       <c r="AM707" s="1"/>
       <c r="AN707" s="83"/>
     </row>
-    <row r="708" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="708" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A708" s="22" t="s">
         <v>1481</v>
       </c>
@@ -76354,7 +76414,7 @@
       <c r="AM708" s="1"/>
       <c r="AN708" s="83"/>
     </row>
-    <row r="709" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="709" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A709" s="22" t="s">
         <v>1482</v>
       </c>
@@ -76427,7 +76487,7 @@
       <c r="AM709" s="1"/>
       <c r="AN709" s="83"/>
     </row>
-    <row r="710" spans="1:40" s="26" customFormat="1" hidden="1">
+    <row r="710" spans="1:40" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A710" s="22" t="s">
         <v>1483</v>
       </c>
@@ -76500,7 +76560,7 @@
       <c r="AM710" s="1"/>
       <c r="AN710" s="83"/>
     </row>
-    <row r="711" spans="1:40" s="26" customFormat="1">
+    <row r="711" spans="1:40" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A711" s="39"/>
       <c r="B711" s="40"/>
       <c r="C711" s="40"/>
@@ -76562,28 +76622,28 @@
       <c r="AM711" s="46"/>
       <c r="AN711" s="83"/>
     </row>
-    <row r="716" spans="1:40">
+    <row r="716" spans="1:40" x14ac:dyDescent="0.3">
       <c r="AA716" s="73"/>
       <c r="AB716" s="73"/>
       <c r="AC716" s="73"/>
       <c r="AN716" s="94"/>
     </row>
-    <row r="717" spans="1:40">
+    <row r="717" spans="1:40" x14ac:dyDescent="0.3">
       <c r="Z717" s="73"/>
       <c r="AA717" s="73"/>
       <c r="AB717" s="73"/>
       <c r="AC717" s="73"/>
       <c r="AN717" s="94"/>
     </row>
-    <row r="718" spans="1:40">
+    <row r="718" spans="1:40" x14ac:dyDescent="0.3">
       <c r="Z718" s="73"/>
       <c r="AA718" s="73"/>
       <c r="AB718" s="73"/>
     </row>
-    <row r="719" spans="1:40">
+    <row r="719" spans="1:40" x14ac:dyDescent="0.3">
       <c r="Z719" s="73"/>
     </row>
-    <row r="720" spans="1:40">
+    <row r="720" spans="1:40" x14ac:dyDescent="0.3">
       <c r="Z720" s="73"/>
       <c r="AA720" s="73"/>
       <c r="AB720" s="73"/>
@@ -76592,7 +76652,7 @@
   <autoFilter ref="A2:AN710" xr:uid="{2AA437EE-405D-4A43-9EB9-23F1BEB36011}">
     <filterColumn colId="17">
       <filters>
-        <filter val="Jarinu"/>
+        <filter val="Diadema"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -76668,18 +76728,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D813743-8135-4F32-BACA-A0CD44F9427F}">
   <dimension ref="A1:F44"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="21.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="69" t="s">
         <v>1485</v>
       </c>
@@ -76699,7 +76759,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>755</v>
       </c>
@@ -76724,7 +76784,7 @@
         <v>88880.437499999985</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>49</v>
       </c>
@@ -76738,18 +76798,18 @@
       </c>
       <c r="D3" s="52">
         <f>SUMIF(Controle!R:R,Formulas!A3,Controle!AH:AH)</f>
-        <v>678.6992884</v>
+        <v>710.88959879999993</v>
       </c>
       <c r="E3" s="49">
         <f t="shared" ref="E3:E5" si="0">D3/C3</f>
-        <v>0.48576787436869623</v>
+        <v>0.50880756061198085</v>
       </c>
       <c r="F3" s="66">
         <f>SUMIF(Controle!$R:$R,Formulas!A3,Controle!$AK:$AK)</f>
         <v>256393.97999999995</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>151</v>
       </c>
@@ -76774,7 +76834,7 @@
         <v>136436.7233333333</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>187</v>
       </c>
@@ -76799,7 +76859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="53" t="s">
         <v>1491</v>
       </c>
@@ -76813,18 +76873,18 @@
       </c>
       <c r="D6" s="55">
         <f t="shared" si="1"/>
-        <v>3104.4367383600011</v>
+        <v>3136.6270487600009</v>
       </c>
       <c r="E6" s="56">
         <f>D6/C6</f>
-        <v>0.68370795014214703</v>
+        <v>0.69079740726203986</v>
       </c>
       <c r="F6" s="67">
         <f t="shared" si="1"/>
         <v>481711.14083333325</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="69" t="s">
         <v>1492</v>
       </c>
@@ -76841,7 +76901,7 @@
         <v>1496</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
         <v>764</v>
       </c>
@@ -76862,7 +76922,7 @@
         <v>163307.73333333334</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="47" t="s">
         <v>1133</v>
       </c>
@@ -76883,7 +76943,7 @@
         <v>101921.69083333333</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="47" t="s">
         <v>752</v>
       </c>
@@ -76904,7 +76964,7 @@
         <v>33682.781666666669</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="47" t="s">
         <v>92</v>
       </c>
@@ -76925,7 +76985,7 @@
         <v>110026.7025</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="47" t="s">
         <v>73</v>
       </c>
@@ -76946,7 +77006,7 @@
         <v>14192.72</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="47" t="s">
         <v>45</v>
       </c>
@@ -76967,7 +77027,7 @@
         <v>18301.009999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="47" t="s">
         <v>82</v>
       </c>
@@ -76988,7 +77048,7 @@
         <v>8786.4108333333334</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="47" t="s">
         <v>1145</v>
       </c>
@@ -77009,7 +77069,7 @@
         <v>17038.2366666667</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="47" t="s">
         <v>841</v>
       </c>
@@ -77030,7 +77090,7 @@
         <v>3342.1949999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="47" t="s">
         <v>237</v>
       </c>
@@ -77051,7 +77111,7 @@
         <v>1642.21</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="47" t="s">
         <v>1161</v>
       </c>
@@ -77072,7 +77132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="47" t="s">
         <v>872</v>
       </c>
@@ -77093,7 +77153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="47" t="s">
         <v>356</v>
       </c>
@@ -77114,7 +77174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="47" t="s">
         <v>223</v>
       </c>
@@ -77135,7 +77195,7 @@
         <v>4586.75</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="47" t="s">
         <v>1362</v>
       </c>
@@ -77156,7 +77216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="47" t="s">
         <v>220</v>
       </c>
@@ -77177,7 +77237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="47" t="s">
         <v>1220</v>
       </c>
@@ -77198,7 +77258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="47" t="s">
         <v>318</v>
       </c>
@@ -77219,7 +77279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="47" t="s">
         <v>349</v>
       </c>
@@ -77240,7 +77300,7 @@
         <v>1311.99</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="47" t="s">
         <v>253</v>
       </c>
@@ -77261,7 +77321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="47" t="s">
         <v>303</v>
       </c>
@@ -77282,7 +77342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="47" t="s">
         <v>879</v>
       </c>
@@ -77303,7 +77363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="47" t="s">
         <v>1358</v>
       </c>
@@ -77324,7 +77384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="47" t="s">
         <v>897</v>
       </c>
@@ -77345,7 +77405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="47" t="s">
         <v>1367</v>
       </c>
@@ -77366,7 +77426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="47" t="s">
         <v>925</v>
       </c>
@@ -77387,7 +77447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="47" t="s">
         <v>149</v>
       </c>
@@ -77408,7 +77468,7 @@
         <v>238.71</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="47" t="s">
         <v>939</v>
       </c>
@@ -77429,7 +77489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="47" t="s">
         <v>1395</v>
       </c>
@@ -77450,7 +77510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="47" t="s">
         <v>1417</v>
       </c>
@@ -77471,7 +77531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="47"/>
       <c r="B40">
         <f>COUNTIF(Controle!L:L,Formulas!A41)</f>
@@ -77490,7 +77550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="47">
         <v>0</v>
       </c>
@@ -77511,7 +77571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="59" t="s">
         <v>1491</v>
       </c>
@@ -77532,12 +77592,12 @@
         <v>478379.14083333343</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="47"/>
       <c r="C43" s="57"/>
       <c r="D43" s="48"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="47"/>
     </row>
   </sheetData>
@@ -77555,12 +77615,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="f5ab1930-d403-4c69-b2cd-8cc48f527d10" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c06ce65c-ed18-47f4-a957-afd315448c9c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -77759,24 +77821,54 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="f5ab1930-d403-4c69-b2cd-8cc48f527d10" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c06ce65c-ed18-47f4-a957-afd315448c9c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AE26D3A-03CC-4B3D-9F98-6F77A1AEA74E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE495743-F761-4961-A762-7A3D120C6961}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c06ce65c-ed18-47f4-a957-afd315448c9c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="f5ab1930-d403-4c69-b2cd-8cc48f527d10"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59443FB2-AD94-4FFF-8817-F253987A64A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59443FB2-AD94-4FFF-8817-F253987A64A5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c06ce65c-ed18-47f4-a957-afd315448c9c"/>
+    <ds:schemaRef ds:uri="f5ab1930-d403-4c69-b2cd-8cc48f527d10"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE495743-F761-4961-A762-7A3D120C6961}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AE26D3A-03CC-4B3D-9F98-6F77A1AEA74E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/dados_atuais.xlsx
+++ b/data/dados_atuais.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delgadiadema.sharepoint.com/sites/GestoEstratgica/Documentos Compartilhados/Controle Master/BSW/Novo controle (Em processo)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2108" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{168F0F45-6497-47F3-9ED0-64BF8C3F1EC5}"/>
+  <xr:revisionPtr revIDLastSave="2121" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2C8DB98-9027-4611-BF89-9C238FB9BC56}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E398004-7492-4AA0-94C2-EA9B761AAA49}"/>
   </bookViews>
@@ -322,7 +322,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7134" uniqueCount="1504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7139" uniqueCount="1504">
   <si>
     <t>Código
 Bobina Mâe</t>
@@ -5037,10 +5037,10 @@
     <t>Material em análise (Thiago Cardoso). Aguardando produção do produto para acompanhamento.</t>
   </si>
   <si>
-    <t>Material em análise (Izaias Claro). Aguardando produção do produto para acompanhamento.</t>
-  </si>
-  <si>
     <t>Material em análise (Edson Lupis). Aguardando produção do produto para acompanhamento.</t>
+  </si>
+  <si>
+    <t>Material em análise (Izaias Claro). Possibilidade na redução da largura da bobina / chapa.</t>
   </si>
 </sst>
 </file>
@@ -14826,7 +14826,7 @@
       </c>
       <c r="AL13" s="1"/>
       <c r="AM13" s="1" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="AN13" s="83"/>
     </row>
@@ -15010,16 +15010,26 @@
         <f t="shared" si="0"/>
         <v>31.757323800000005</v>
       </c>
-      <c r="Z15" s="10"/>
+      <c r="Z15" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="AA15" s="10"/>
-      <c r="AB15" s="10"/>
-      <c r="AC15" s="10"/>
-      <c r="AD15" s="10"/>
+      <c r="AB15" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC15" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD15" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="AE15" s="10"/>
-      <c r="AF15" s="10"/>
+      <c r="AF15" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="AG15" s="38">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AH15" s="51" t="str">
         <f t="shared" si="2"/>
@@ -15036,7 +15046,7 @@
       </c>
       <c r="AL15" s="1"/>
       <c r="AM15" s="1" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="AN15" s="83"/>
     </row>

--- a/data/dados_atuais.xlsx
+++ b/data/dados_atuais.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="EsteLivro"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr codeName="EsteLivro" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delgadiadema.sharepoint.com/sites/GestoEstratgica/Documentos Compartilhados/Controle Master/BSW/Novo controle (Em processo)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2228" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CA87258-A579-4031-A157-959517B13604}"/>
+  <xr:revisionPtr revIDLastSave="2234" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E07EDBF8-507D-4903-B295-279546C99279}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E398004-7492-4AA0-94C2-EA9B761AAA49}"/>
   </bookViews>
@@ -321,7 +321,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7181" uniqueCount="1515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7185" uniqueCount="1515">
   <si>
     <t>Código
 Bobina Mâe</t>
@@ -13119,10 +13119,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
-</file>
-
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Eric da Silva Maia" id="{D9E3AE94-B136-43DC-991E-9F5A8D1687A6}" userId="S::eric.maia@delga.com.br::43e774bf-1d7b-4030-aa96-fdc0a837fc3b" providerId="AD"/>
@@ -13634,7 +13630,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:41" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>40</v>
       </c>
@@ -13750,7 +13746,7 @@
       <c r="AN3" s="82"/>
       <c r="AO3" s="82"/>
     </row>
-    <row r="4" spans="1:41" s="26" customFormat="1" ht="132.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:41" s="26" customFormat="1" ht="132.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
         <v>52</v>
       </c>
@@ -13870,7 +13866,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="5" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
         <v>62</v>
       </c>
@@ -13990,7 +13986,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="6" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
         <v>69</v>
       </c>
@@ -14100,7 +14096,7 @@
       <c r="AN6" s="82"/>
       <c r="AO6" s="82"/>
     </row>
-    <row r="7" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="22" t="s">
         <v>77</v>
       </c>
@@ -14216,7 +14212,7 @@
       <c r="AN7" s="82"/>
       <c r="AO7" s="82"/>
     </row>
-    <row r="8" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
         <v>84</v>
       </c>
@@ -14330,7 +14326,7 @@
       <c r="AN8" s="82"/>
       <c r="AO8" s="82"/>
     </row>
-    <row r="9" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
         <v>89</v>
       </c>
@@ -14450,7 +14446,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="10" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>96</v>
       </c>
@@ -14570,7 +14566,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="11" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="22" t="s">
         <v>102</v>
       </c>
@@ -14688,7 +14684,7 @@
       </c>
       <c r="AO11" s="82"/>
     </row>
-    <row r="12" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
         <v>107</v>
       </c>
@@ -14804,7 +14800,7 @@
       </c>
       <c r="AO12" s="82"/>
     </row>
-    <row r="13" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="22" t="s">
         <v>110</v>
       </c>
@@ -14903,7 +14899,7 @@
       <c r="AN13" s="82"/>
       <c r="AO13" s="82"/>
     </row>
-    <row r="14" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
         <v>114</v>
       </c>
@@ -15017,7 +15013,7 @@
       </c>
       <c r="AO14" s="82"/>
     </row>
-    <row r="15" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="22" t="s">
         <v>117</v>
       </c>
@@ -15127,7 +15123,7 @@
       <c r="AN15" s="82"/>
       <c r="AO15" s="82"/>
     </row>
-    <row r="16" spans="1:41" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:41" s="26" customFormat="1" ht="30.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
         <v>121</v>
       </c>
@@ -15245,7 +15241,7 @@
       </c>
       <c r="AO16" s="82"/>
     </row>
-    <row r="17" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="22" t="s">
         <v>126</v>
       </c>
@@ -15345,7 +15341,7 @@
       <c r="AN17" s="82"/>
       <c r="AO17" s="82"/>
     </row>
-    <row r="18" spans="1:41" s="26" customFormat="1" ht="51" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:41" s="26" customFormat="1" ht="51" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
         <v>131</v>
       </c>
@@ -15453,7 +15449,7 @@
       <c r="AN18" s="82"/>
       <c r="AO18" s="82"/>
     </row>
-    <row r="19" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="22" t="s">
         <v>136</v>
       </c>
@@ -15569,7 +15565,7 @@
       </c>
       <c r="AO19" s="82"/>
     </row>
-    <row r="20" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
         <v>141</v>
       </c>
@@ -15669,7 +15665,7 @@
       <c r="AN20" s="82"/>
       <c r="AO20" s="82"/>
     </row>
-    <row r="21" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="22" t="s">
         <v>146</v>
       </c>
@@ -15787,7 +15783,7 @@
       </c>
       <c r="AO21" s="82"/>
     </row>
-    <row r="22" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
         <v>153</v>
       </c>
@@ -15887,7 +15883,7 @@
       <c r="AN22" s="82"/>
       <c r="AO22" s="82"/>
     </row>
-    <row r="23" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="22" t="s">
         <v>155</v>
       </c>
@@ -16003,7 +15999,7 @@
       </c>
       <c r="AO23" s="82"/>
     </row>
-    <row r="24" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
         <v>159</v>
       </c>
@@ -16101,7 +16097,7 @@
       <c r="AN24" s="82"/>
       <c r="AO24" s="82"/>
     </row>
-    <row r="25" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="22" t="s">
         <v>160</v>
       </c>
@@ -16199,7 +16195,7 @@
       <c r="AN25" s="82"/>
       <c r="AO25" s="82"/>
     </row>
-    <row r="26" spans="1:41" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:41" s="26" customFormat="1" ht="30.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
         <v>162</v>
       </c>
@@ -16295,7 +16291,7 @@
       <c r="AN26" s="82"/>
       <c r="AO26" s="82"/>
     </row>
-    <row r="27" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="22" t="s">
         <v>165</v>
       </c>
@@ -16393,7 +16389,7 @@
       <c r="AN27" s="82"/>
       <c r="AO27" s="82"/>
     </row>
-    <row r="28" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="22" t="s">
         <v>168</v>
       </c>
@@ -16509,7 +16505,7 @@
       <c r="AN28" s="82"/>
       <c r="AO28" s="82"/>
     </row>
-    <row r="29" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="22" t="s">
         <v>171</v>
       </c>
@@ -16607,7 +16603,7 @@
       <c r="AN29" s="82"/>
       <c r="AO29" s="82"/>
     </row>
-    <row r="30" spans="1:41" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:41" s="26" customFormat="1" ht="30.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
         <v>174</v>
       </c>
@@ -16705,7 +16701,7 @@
       <c r="AN30" s="82"/>
       <c r="AO30" s="82"/>
     </row>
-    <row r="31" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="22" t="s">
         <v>178</v>
       </c>
@@ -16797,7 +16793,7 @@
       <c r="AN31" s="82"/>
       <c r="AO31" s="82"/>
     </row>
-    <row r="32" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
         <v>180</v>
       </c>
@@ -16915,7 +16911,7 @@
       </c>
       <c r="AO32" s="82"/>
     </row>
-    <row r="33" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="22" t="s">
         <v>183</v>
       </c>
@@ -17031,7 +17027,7 @@
       </c>
       <c r="AO33" s="82"/>
     </row>
-    <row r="34" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
         <v>189</v>
       </c>
@@ -17125,7 +17121,7 @@
       <c r="AN34" s="82"/>
       <c r="AO34" s="82"/>
     </row>
-    <row r="35" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="22" t="s">
         <v>193</v>
       </c>
@@ -17243,7 +17239,7 @@
       </c>
       <c r="AO35" s="82"/>
     </row>
-    <row r="36" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="22" t="s">
         <v>199</v>
       </c>
@@ -17339,7 +17335,7 @@
       <c r="AN36" s="82"/>
       <c r="AO36" s="82"/>
     </row>
-    <row r="37" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="22" t="s">
         <v>200</v>
       </c>
@@ -17427,7 +17423,7 @@
       <c r="AN37" s="82"/>
       <c r="AO37" s="82"/>
     </row>
-    <row r="38" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="22" t="s">
         <v>203</v>
       </c>
@@ -17529,7 +17525,7 @@
       <c r="AN38" s="82"/>
       <c r="AO38" s="82"/>
     </row>
-    <row r="39" spans="1:41" s="26" customFormat="1" ht="71.400000000000006" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:41" s="26" customFormat="1" ht="71.400000000000006" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="22" t="s">
         <v>206</v>
       </c>
@@ -17649,7 +17645,7 @@
       </c>
       <c r="AO39" s="82"/>
     </row>
-    <row r="40" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
         <v>210</v>
       </c>
@@ -17743,7 +17739,7 @@
       <c r="AN40" s="82"/>
       <c r="AO40" s="82"/>
     </row>
-    <row r="41" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="22" t="s">
         <v>213</v>
       </c>
@@ -17837,7 +17833,7 @@
       <c r="AN41" s="82"/>
       <c r="AO41" s="82"/>
     </row>
-    <row r="42" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>216</v>
       </c>
@@ -17931,7 +17927,7 @@
       <c r="AN42" s="82"/>
       <c r="AO42" s="82"/>
     </row>
-    <row r="43" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="22" t="s">
         <v>220</v>
       </c>
@@ -18025,7 +18021,7 @@
       <c r="AN43" s="82"/>
       <c r="AO43" s="82"/>
     </row>
-    <row r="44" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="22" t="s">
         <v>224</v>
       </c>
@@ -18143,7 +18139,7 @@
       </c>
       <c r="AO44" s="82"/>
     </row>
-    <row r="45" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="22" t="s">
         <v>229</v>
       </c>
@@ -18257,7 +18253,7 @@
       </c>
       <c r="AO45" s="82"/>
     </row>
-    <row r="46" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="22" t="s">
         <v>233</v>
       </c>
@@ -18351,7 +18347,7 @@
       <c r="AN46" s="82"/>
       <c r="AO46" s="82"/>
     </row>
-    <row r="47" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="22" t="s">
         <v>240</v>
       </c>
@@ -18445,7 +18441,7 @@
       <c r="AN47" s="82"/>
       <c r="AO47" s="82"/>
     </row>
-    <row r="48" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="22" t="s">
         <v>243</v>
       </c>
@@ -18539,7 +18535,7 @@
       <c r="AN48" s="82"/>
       <c r="AO48" s="82"/>
     </row>
-    <row r="49" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="22" t="s">
         <v>245</v>
       </c>
@@ -18633,7 +18629,7 @@
       <c r="AN49" s="82"/>
       <c r="AO49" s="82"/>
     </row>
-    <row r="50" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="22" t="s">
         <v>247</v>
       </c>
@@ -18727,7 +18723,7 @@
       <c r="AN50" s="82"/>
       <c r="AO50" s="82"/>
     </row>
-    <row r="51" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="22" t="s">
         <v>250</v>
       </c>
@@ -18821,7 +18817,7 @@
       <c r="AN51" s="82"/>
       <c r="AO51" s="82"/>
     </row>
-    <row r="52" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="22" t="s">
         <v>253</v>
       </c>
@@ -18915,7 +18911,7 @@
       <c r="AN52" s="82"/>
       <c r="AO52" s="82"/>
     </row>
-    <row r="53" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="22" t="s">
         <v>256</v>
       </c>
@@ -19009,7 +19005,7 @@
       <c r="AN53" s="82"/>
       <c r="AO53" s="82"/>
     </row>
-    <row r="54" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="22" t="s">
         <v>258</v>
       </c>
@@ -19103,7 +19099,7 @@
       <c r="AN54" s="82"/>
       <c r="AO54" s="82"/>
     </row>
-    <row r="55" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="22" t="s">
         <v>262</v>
       </c>
@@ -19197,7 +19193,7 @@
       <c r="AN55" s="82"/>
       <c r="AO55" s="82"/>
     </row>
-    <row r="56" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="22" t="s">
         <v>265</v>
       </c>
@@ -19315,7 +19311,7 @@
       </c>
       <c r="AO56" s="82"/>
     </row>
-    <row r="57" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="22" t="s">
         <v>269</v>
       </c>
@@ -19409,7 +19405,7 @@
       <c r="AN57" s="82"/>
       <c r="AO57" s="82"/>
     </row>
-    <row r="58" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="22" t="s">
         <v>270</v>
       </c>
@@ -19503,7 +19499,7 @@
       <c r="AN58" s="82"/>
       <c r="AO58" s="82"/>
     </row>
-    <row r="59" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="22" t="s">
         <v>272</v>
       </c>
@@ -19597,7 +19593,7 @@
       <c r="AN59" s="82"/>
       <c r="AO59" s="82"/>
     </row>
-    <row r="60" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="22" t="s">
         <v>274</v>
       </c>
@@ -19709,7 +19705,7 @@
       <c r="AN60" s="82"/>
       <c r="AO60" s="82"/>
     </row>
-    <row r="61" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="22" t="s">
         <v>280</v>
       </c>
@@ -19823,7 +19819,7 @@
       </c>
       <c r="AO61" s="82"/>
     </row>
-    <row r="62" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="22" t="s">
         <v>286</v>
       </c>
@@ -19917,7 +19913,7 @@
       <c r="AN62" s="82"/>
       <c r="AO62" s="82"/>
     </row>
-    <row r="63" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="22" t="s">
         <v>288</v>
       </c>
@@ -20011,7 +20007,7 @@
       <c r="AN63" s="82"/>
       <c r="AO63" s="82"/>
     </row>
-    <row r="64" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="22" t="s">
         <v>291</v>
       </c>
@@ -20105,7 +20101,7 @@
       <c r="AN64" s="82"/>
       <c r="AO64" s="82"/>
     </row>
-    <row r="65" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="22" t="s">
         <v>293</v>
       </c>
@@ -20201,7 +20197,7 @@
       <c r="AN65" s="82"/>
       <c r="AO65" s="82"/>
     </row>
-    <row r="66" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="22" t="s">
         <v>295</v>
       </c>
@@ -20297,7 +20293,7 @@
       <c r="AN66" s="82"/>
       <c r="AO66" s="82"/>
     </row>
-    <row r="67" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="22" t="s">
         <v>297</v>
       </c>
@@ -20387,7 +20383,7 @@
       <c r="AN67" s="82"/>
       <c r="AO67" s="82"/>
     </row>
-    <row r="68" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="22" t="s">
         <v>298</v>
       </c>
@@ -20481,7 +20477,7 @@
       <c r="AN68" s="82"/>
       <c r="AO68" s="82"/>
     </row>
-    <row r="69" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="22" t="s">
         <v>300</v>
       </c>
@@ -20577,7 +20573,7 @@
       <c r="AN69" s="82"/>
       <c r="AO69" s="82"/>
     </row>
-    <row r="70" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="22" t="s">
         <v>303</v>
       </c>
@@ -20671,7 +20667,7 @@
       <c r="AN70" s="82"/>
       <c r="AO70" s="82"/>
     </row>
-    <row r="71" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="22" t="s">
         <v>305</v>
       </c>
@@ -20765,7 +20761,7 @@
       <c r="AN71" s="82"/>
       <c r="AO71" s="82"/>
     </row>
-    <row r="72" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="22" t="s">
         <v>308</v>
       </c>
@@ -20861,7 +20857,7 @@
       <c r="AN72" s="82"/>
       <c r="AO72" s="82"/>
     </row>
-    <row r="73" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="22" t="s">
         <v>311</v>
       </c>
@@ -20955,7 +20951,7 @@
       <c r="AN73" s="82"/>
       <c r="AO73" s="82"/>
     </row>
-    <row r="74" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="22" t="s">
         <v>313</v>
       </c>
@@ -21049,7 +21045,7 @@
       <c r="AN74" s="82"/>
       <c r="AO74" s="82"/>
     </row>
-    <row r="75" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="22" t="s">
         <v>315</v>
       </c>
@@ -21141,7 +21137,7 @@
       <c r="AN75" s="82"/>
       <c r="AO75" s="82"/>
     </row>
-    <row r="76" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="22" t="s">
         <v>318</v>
       </c>
@@ -21235,7 +21231,7 @@
       <c r="AN76" s="82"/>
       <c r="AO76" s="82"/>
     </row>
-    <row r="77" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="22" t="s">
         <v>322</v>
       </c>
@@ -21327,7 +21323,7 @@
       <c r="AN77" s="82"/>
       <c r="AO77" s="82"/>
     </row>
-    <row r="78" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="22" t="s">
         <v>324</v>
       </c>
@@ -21441,7 +21437,7 @@
       </c>
       <c r="AO78" s="82"/>
     </row>
-    <row r="79" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="22" t="s">
         <v>328</v>
       </c>
@@ -21535,7 +21531,7 @@
       <c r="AN79" s="82"/>
       <c r="AO79" s="82"/>
     </row>
-    <row r="80" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="22" t="s">
         <v>331</v>
       </c>
@@ -21649,7 +21645,7 @@
       </c>
       <c r="AO80" s="82"/>
     </row>
-    <row r="81" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="22" t="s">
         <v>335</v>
       </c>
@@ -21745,7 +21741,7 @@
       <c r="AN81" s="82"/>
       <c r="AO81" s="82"/>
     </row>
-    <row r="82" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="22" t="s">
         <v>337</v>
       </c>
@@ -21839,7 +21835,7 @@
       <c r="AN82" s="82"/>
       <c r="AO82" s="82"/>
     </row>
-    <row r="83" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="22" t="s">
         <v>339</v>
       </c>
@@ -21933,7 +21929,7 @@
       <c r="AN83" s="82"/>
       <c r="AO83" s="82"/>
     </row>
-    <row r="84" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="22" t="s">
         <v>341</v>
       </c>
@@ -22029,7 +22025,7 @@
       <c r="AN84" s="82"/>
       <c r="AO84" s="82"/>
     </row>
-    <row r="85" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="22" t="s">
         <v>344</v>
       </c>
@@ -22123,7 +22119,7 @@
       <c r="AN85" s="82"/>
       <c r="AO85" s="82"/>
     </row>
-    <row r="86" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="22" t="s">
         <v>346</v>
       </c>
@@ -22213,7 +22209,7 @@
       <c r="AN86" s="82"/>
       <c r="AO86" s="82"/>
     </row>
-    <row r="87" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="22" t="s">
         <v>351</v>
       </c>
@@ -22307,7 +22303,7 @@
       <c r="AN87" s="82"/>
       <c r="AO87" s="82"/>
     </row>
-    <row r="88" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="22" t="s">
         <v>353</v>
       </c>
@@ -22403,7 +22399,7 @@
       <c r="AN88" s="82"/>
       <c r="AO88" s="82"/>
     </row>
-    <row r="89" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="22" t="s">
         <v>358</v>
       </c>
@@ -22497,7 +22493,7 @@
       <c r="AN89" s="82"/>
       <c r="AO89" s="82"/>
     </row>
-    <row r="90" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="22" t="s">
         <v>361</v>
       </c>
@@ -22591,7 +22587,7 @@
       <c r="AN90" s="82"/>
       <c r="AO90" s="82"/>
     </row>
-    <row r="91" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="22" t="s">
         <v>363</v>
       </c>
@@ -22685,7 +22681,7 @@
       <c r="AN91" s="82"/>
       <c r="AO91" s="82"/>
     </row>
-    <row r="92" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="22" t="s">
         <v>366</v>
       </c>
@@ -22779,7 +22775,7 @@
       <c r="AN92" s="82"/>
       <c r="AO92" s="82"/>
     </row>
-    <row r="93" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="22" t="s">
         <v>369</v>
       </c>
@@ -22871,7 +22867,7 @@
       <c r="AN93" s="82"/>
       <c r="AO93" s="82"/>
     </row>
-    <row r="94" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="22" t="s">
         <v>371</v>
       </c>
@@ -22965,7 +22961,7 @@
       <c r="AN94" s="82"/>
       <c r="AO94" s="82"/>
     </row>
-    <row r="95" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="15" t="s">
         <v>374</v>
       </c>
@@ -23059,7 +23055,7 @@
       <c r="AN95" s="82"/>
       <c r="AO95" s="82"/>
     </row>
-    <row r="96" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="22" t="s">
         <v>377</v>
       </c>
@@ -23173,7 +23169,7 @@
       </c>
       <c r="AO96" s="82"/>
     </row>
-    <row r="97" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="22" t="s">
         <v>380</v>
       </c>
@@ -23261,7 +23257,7 @@
       <c r="AN97" s="82"/>
       <c r="AO97" s="82"/>
     </row>
-    <row r="98" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>381</v>
       </c>
@@ -23357,7 +23353,7 @@
       <c r="AN98" s="82"/>
       <c r="AO98" s="82"/>
     </row>
-    <row r="99" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="22" t="s">
         <v>385</v>
       </c>
@@ -23453,7 +23449,7 @@
       <c r="AN99" s="82"/>
       <c r="AO99" s="82"/>
     </row>
-    <row r="100" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="22" t="s">
         <v>387</v>
       </c>
@@ -23547,7 +23543,7 @@
       <c r="AN100" s="82"/>
       <c r="AO100" s="82"/>
     </row>
-    <row r="101" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="22" t="s">
         <v>390</v>
       </c>
@@ -23641,7 +23637,7 @@
       <c r="AN101" s="82"/>
       <c r="AO101" s="82"/>
     </row>
-    <row r="102" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="22" t="s">
         <v>393</v>
       </c>
@@ -23731,7 +23727,7 @@
       <c r="AN102" s="82"/>
       <c r="AO102" s="82"/>
     </row>
-    <row r="103" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="22" t="s">
         <v>396</v>
       </c>
@@ -23825,7 +23821,7 @@
       <c r="AN103" s="82"/>
       <c r="AO103" s="82"/>
     </row>
-    <row r="104" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="22" t="s">
         <v>397</v>
       </c>
@@ -23921,7 +23917,7 @@
       <c r="AN104" s="82"/>
       <c r="AO104" s="82"/>
     </row>
-    <row r="105" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="22" t="s">
         <v>399</v>
       </c>
@@ -24009,7 +24005,7 @@
       <c r="AN105" s="82"/>
       <c r="AO105" s="82"/>
     </row>
-    <row r="106" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="22" t="s">
         <v>401</v>
       </c>
@@ -24103,7 +24099,7 @@
       <c r="AN106" s="82"/>
       <c r="AO106" s="82"/>
     </row>
-    <row r="107" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="15" t="s">
         <v>403</v>
       </c>
@@ -24191,7 +24187,7 @@
       <c r="AN107" s="82"/>
       <c r="AO107" s="82"/>
     </row>
-    <row r="108" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="22" t="s">
         <v>405</v>
       </c>
@@ -24283,7 +24279,7 @@
       <c r="AN108" s="82"/>
       <c r="AO108" s="82"/>
     </row>
-    <row r="109" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="22" t="s">
         <v>407</v>
       </c>
@@ -24377,7 +24373,7 @@
       <c r="AN109" s="82"/>
       <c r="AO109" s="82"/>
     </row>
-    <row r="110" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="22" t="s">
         <v>409</v>
       </c>
@@ -24493,7 +24489,7 @@
       <c r="AN110" s="82"/>
       <c r="AO110" s="82"/>
     </row>
-    <row r="111" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="22" t="s">
         <v>413</v>
       </c>
@@ -24589,7 +24585,7 @@
       <c r="AN111" s="82"/>
       <c r="AO111" s="82"/>
     </row>
-    <row r="112" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="22" t="s">
         <v>415</v>
       </c>
@@ -24705,7 +24701,7 @@
       </c>
       <c r="AO112" s="82"/>
     </row>
-    <row r="113" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="22" t="s">
         <v>418</v>
       </c>
@@ -24795,7 +24791,7 @@
       <c r="AN113" s="82"/>
       <c r="AO113" s="82"/>
     </row>
-    <row r="114" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="22" t="s">
         <v>422</v>
       </c>
@@ -24883,7 +24879,7 @@
       <c r="AN114" s="82"/>
       <c r="AO114" s="82"/>
     </row>
-    <row r="115" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>423</v>
       </c>
@@ -24977,7 +24973,7 @@
       <c r="AN115" s="82"/>
       <c r="AO115" s="82"/>
     </row>
-    <row r="116" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="22" t="s">
         <v>425</v>
       </c>
@@ -25063,7 +25059,7 @@
       <c r="AN116" s="82"/>
       <c r="AO116" s="82"/>
     </row>
-    <row r="117" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="22" t="s">
         <v>427</v>
       </c>
@@ -25159,7 +25155,7 @@
       <c r="AN117" s="82"/>
       <c r="AO117" s="82"/>
     </row>
-    <row r="118" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="22" t="s">
         <v>429</v>
       </c>
@@ -25253,7 +25249,7 @@
       <c r="AN118" s="82"/>
       <c r="AO118" s="82"/>
     </row>
-    <row r="119" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="22" t="s">
         <v>431</v>
       </c>
@@ -25345,7 +25341,7 @@
       <c r="AN119" s="82"/>
       <c r="AO119" s="82"/>
     </row>
-    <row r="120" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="15" t="s">
         <v>433</v>
       </c>
@@ -25431,7 +25427,7 @@
       <c r="AN120" s="82"/>
       <c r="AO120" s="82"/>
     </row>
-    <row r="121" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="22" t="s">
         <v>434</v>
       </c>
@@ -25523,7 +25519,7 @@
       <c r="AN121" s="82"/>
       <c r="AO121" s="82"/>
     </row>
-    <row r="122" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="15" t="s">
         <v>436</v>
       </c>
@@ -25611,7 +25607,7 @@
       <c r="AN122" s="82"/>
       <c r="AO122" s="82"/>
     </row>
-    <row r="123" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="22" t="s">
         <v>437</v>
       </c>
@@ -25723,7 +25719,7 @@
       </c>
       <c r="AO123" s="82"/>
     </row>
-    <row r="124" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="22" t="s">
         <v>439</v>
       </c>
@@ -25809,7 +25805,7 @@
       <c r="AN124" s="82"/>
       <c r="AO124" s="82"/>
     </row>
-    <row r="125" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="22" t="s">
         <v>440</v>
       </c>
@@ -25905,7 +25901,7 @@
       <c r="AN125" s="82"/>
       <c r="AO125" s="82"/>
     </row>
-    <row r="126" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="22" t="s">
         <v>442</v>
       </c>
@@ -25995,7 +25991,7 @@
       <c r="AN126" s="82"/>
       <c r="AO126" s="82"/>
     </row>
-    <row r="127" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="22" t="s">
         <v>445</v>
       </c>
@@ -26089,7 +26085,7 @@
       <c r="AN127" s="82"/>
       <c r="AO127" s="82"/>
     </row>
-    <row r="128" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="22" t="s">
         <v>447</v>
       </c>
@@ -26179,7 +26175,7 @@
       <c r="AN128" s="82"/>
       <c r="AO128" s="82"/>
     </row>
-    <row r="129" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="15" t="s">
         <v>450</v>
       </c>
@@ -26273,7 +26269,7 @@
       <c r="AN129" s="82"/>
       <c r="AO129" s="82"/>
     </row>
-    <row r="130" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="22" t="s">
         <v>452</v>
       </c>
@@ -26357,7 +26353,7 @@
       <c r="AN130" s="82"/>
       <c r="AO130" s="82"/>
     </row>
-    <row r="131" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="22" t="s">
         <v>453</v>
       </c>
@@ -26441,7 +26437,7 @@
       <c r="AN131" s="82"/>
       <c r="AO131" s="82"/>
     </row>
-    <row r="132" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="22" t="s">
         <v>454</v>
       </c>
@@ -26535,7 +26531,7 @@
       <c r="AN132" s="82"/>
       <c r="AO132" s="82"/>
     </row>
-    <row r="133" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="22" t="s">
         <v>456</v>
       </c>
@@ -26631,7 +26627,7 @@
       <c r="AN133" s="82"/>
       <c r="AO133" s="82"/>
     </row>
-    <row r="134" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="22" t="s">
         <v>458</v>
       </c>
@@ -26723,7 +26719,7 @@
       <c r="AN134" s="82"/>
       <c r="AO134" s="82"/>
     </row>
-    <row r="135" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="15" t="s">
         <v>460</v>
       </c>
@@ -26813,7 +26809,7 @@
       <c r="AN135" s="82"/>
       <c r="AO135" s="82"/>
     </row>
-    <row r="136" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="22" t="s">
         <v>462</v>
       </c>
@@ -26905,7 +26901,7 @@
       <c r="AN136" s="82"/>
       <c r="AO136" s="82"/>
     </row>
-    <row r="137" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="15" t="s">
         <v>464</v>
       </c>
@@ -26991,7 +26987,7 @@
       <c r="AN137" s="82"/>
       <c r="AO137" s="82"/>
     </row>
-    <row r="138" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="22" t="s">
         <v>466</v>
       </c>
@@ -27083,7 +27079,7 @@
       <c r="AN138" s="82"/>
       <c r="AO138" s="82"/>
     </row>
-    <row r="139" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="15" t="s">
         <v>467</v>
       </c>
@@ -27171,7 +27167,7 @@
       <c r="AN139" s="82"/>
       <c r="AO139" s="82"/>
     </row>
-    <row r="140" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="22" t="s">
         <v>470</v>
       </c>
@@ -27263,7 +27259,7 @@
       <c r="AN140" s="82"/>
       <c r="AO140" s="82"/>
     </row>
-    <row r="141" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="22" t="s">
         <v>473</v>
       </c>
@@ -27349,7 +27345,7 @@
       <c r="AN141" s="82"/>
       <c r="AO141" s="82"/>
     </row>
-    <row r="142" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="15" t="s">
         <v>474</v>
       </c>
@@ -27441,7 +27437,7 @@
       <c r="AN142" s="82"/>
       <c r="AO142" s="82"/>
     </row>
-    <row r="143" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="15" t="s">
         <v>476</v>
       </c>
@@ -27529,7 +27525,7 @@
       <c r="AN143" s="82"/>
       <c r="AO143" s="82"/>
     </row>
-    <row r="144" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="15" t="s">
         <v>479</v>
       </c>
@@ -27625,7 +27621,7 @@
       <c r="AN144" s="82"/>
       <c r="AO144" s="82"/>
     </row>
-    <row r="145" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="15" t="s">
         <v>481</v>
       </c>
@@ -27713,7 +27709,7 @@
       <c r="AN145" s="82"/>
       <c r="AO145" s="82"/>
     </row>
-    <row r="146" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="15" t="s">
         <v>482</v>
       </c>
@@ -27799,7 +27795,7 @@
       <c r="AN146" s="82"/>
       <c r="AO146" s="82"/>
     </row>
-    <row r="147" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="15" t="s">
         <v>483</v>
       </c>
@@ -27881,7 +27877,7 @@
       <c r="AN147" s="82"/>
       <c r="AO147" s="82"/>
     </row>
-    <row r="148" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="15" t="s">
         <v>484</v>
       </c>
@@ -27975,7 +27971,7 @@
       <c r="AN148" s="82"/>
       <c r="AO148" s="82"/>
     </row>
-    <row r="149" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="15" t="s">
         <v>486</v>
       </c>
@@ -28067,7 +28063,7 @@
       <c r="AN149" s="82"/>
       <c r="AO149" s="82"/>
     </row>
-    <row r="150" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="15" t="s">
         <v>488</v>
       </c>
@@ -28149,7 +28145,7 @@
       <c r="AN150" s="82"/>
       <c r="AO150" s="82"/>
     </row>
-    <row r="151" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="15" t="s">
         <v>489</v>
       </c>
@@ -28237,7 +28233,7 @@
       <c r="AN151" s="82"/>
       <c r="AO151" s="82"/>
     </row>
-    <row r="152" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="15" t="s">
         <v>491</v>
       </c>
@@ -28329,7 +28325,7 @@
       <c r="AN152" s="82"/>
       <c r="AO152" s="82"/>
     </row>
-    <row r="153" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="15" t="s">
         <v>494</v>
       </c>
@@ -28417,7 +28413,7 @@
       <c r="AN153" s="82"/>
       <c r="AO153" s="82"/>
     </row>
-    <row r="154" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="15" t="s">
         <v>496</v>
       </c>
@@ -28505,7 +28501,7 @@
       <c r="AN154" s="82"/>
       <c r="AO154" s="82"/>
     </row>
-    <row r="155" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="15" t="s">
         <v>498</v>
       </c>
@@ -28593,7 +28589,7 @@
       <c r="AN155" s="82"/>
       <c r="AO155" s="82"/>
     </row>
-    <row r="156" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="15" t="s">
         <v>500</v>
       </c>
@@ -28683,7 +28679,7 @@
       <c r="AN156" s="82"/>
       <c r="AO156" s="82"/>
     </row>
-    <row r="157" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="15" t="s">
         <v>503</v>
       </c>
@@ -28771,7 +28767,7 @@
       <c r="AN157" s="82"/>
       <c r="AO157" s="82"/>
     </row>
-    <row r="158" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="15" t="s">
         <v>505</v>
       </c>
@@ -28859,7 +28855,7 @@
       <c r="AN158" s="82"/>
       <c r="AO158" s="82"/>
     </row>
-    <row r="159" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="15" t="s">
         <v>507</v>
       </c>
@@ -28949,7 +28945,7 @@
       <c r="AN159" s="82"/>
       <c r="AO159" s="82"/>
     </row>
-    <row r="160" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="15" t="s">
         <v>509</v>
       </c>
@@ -29037,7 +29033,7 @@
       <c r="AN160" s="82"/>
       <c r="AO160" s="82"/>
     </row>
-    <row r="161" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="15" t="s">
         <v>511</v>
       </c>
@@ -29125,7 +29121,7 @@
       <c r="AN161" s="82"/>
       <c r="AO161" s="82"/>
     </row>
-    <row r="162" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="15" t="s">
         <v>513</v>
       </c>
@@ -29217,7 +29213,7 @@
       <c r="AN162" s="82"/>
       <c r="AO162" s="82"/>
     </row>
-    <row r="163" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="15" t="s">
         <v>516</v>
       </c>
@@ -29305,7 +29301,7 @@
       <c r="AN163" s="82"/>
       <c r="AO163" s="82"/>
     </row>
-    <row r="164" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="15" t="s">
         <v>518</v>
       </c>
@@ -29393,7 +29389,7 @@
       <c r="AN164" s="82"/>
       <c r="AO164" s="82"/>
     </row>
-    <row r="165" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="15" t="s">
         <v>520</v>
       </c>
@@ -29483,7 +29479,7 @@
       <c r="AN165" s="82"/>
       <c r="AO165" s="82"/>
     </row>
-    <row r="166" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="15" t="s">
         <v>522</v>
       </c>
@@ -29573,7 +29569,7 @@
       <c r="AN166" s="82"/>
       <c r="AO166" s="82"/>
     </row>
-    <row r="167" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="15" t="s">
         <v>524</v>
       </c>
@@ -29663,7 +29659,7 @@
       <c r="AN167" s="82"/>
       <c r="AO167" s="82"/>
     </row>
-    <row r="168" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="15" t="s">
         <v>526</v>
       </c>
@@ -29753,7 +29749,7 @@
       <c r="AN168" s="82"/>
       <c r="AO168" s="82"/>
     </row>
-    <row r="169" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="15" t="s">
         <v>528</v>
       </c>
@@ -29841,7 +29837,7 @@
       <c r="AN169" s="82"/>
       <c r="AO169" s="82"/>
     </row>
-    <row r="170" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="15" t="s">
         <v>530</v>
       </c>
@@ -29931,7 +29927,7 @@
       <c r="AN170" s="82"/>
       <c r="AO170" s="82"/>
     </row>
-    <row r="171" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="15" t="s">
         <v>532</v>
       </c>
@@ -30021,7 +30017,7 @@
       <c r="AN171" s="82"/>
       <c r="AO171" s="82"/>
     </row>
-    <row r="172" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="15" t="s">
         <v>534</v>
       </c>
@@ -30109,7 +30105,7 @@
       <c r="AN172" s="82"/>
       <c r="AO172" s="82"/>
     </row>
-    <row r="173" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="15" t="s">
         <v>536</v>
       </c>
@@ -30199,7 +30195,7 @@
       <c r="AN173" s="82"/>
       <c r="AO173" s="82"/>
     </row>
-    <row r="174" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="15" t="s">
         <v>538</v>
       </c>
@@ -30289,7 +30285,7 @@
       <c r="AN174" s="82"/>
       <c r="AO174" s="82"/>
     </row>
-    <row r="175" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="15" t="s">
         <v>540</v>
       </c>
@@ -30363,7 +30359,7 @@
       <c r="AN175" s="82"/>
       <c r="AO175" s="82"/>
     </row>
-    <row r="176" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="15" t="s">
         <v>541</v>
       </c>
@@ -30451,7 +30447,7 @@
       <c r="AN176" s="82"/>
       <c r="AO176" s="82"/>
     </row>
-    <row r="177" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="15" t="s">
         <v>544</v>
       </c>
@@ -30537,7 +30533,7 @@
       <c r="AN177" s="82"/>
       <c r="AO177" s="82"/>
     </row>
-    <row r="178" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="15" t="s">
         <v>546</v>
       </c>
@@ -30629,7 +30625,7 @@
       <c r="AN178" s="82"/>
       <c r="AO178" s="82"/>
     </row>
-    <row r="179" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="15" t="s">
         <v>547</v>
       </c>
@@ -30717,7 +30713,7 @@
       <c r="AN179" s="82"/>
       <c r="AO179" s="82"/>
     </row>
-    <row r="180" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="15" t="s">
         <v>551</v>
       </c>
@@ -30833,7 +30829,7 @@
       </c>
       <c r="AO180" s="82"/>
     </row>
-    <row r="181" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="15" t="s">
         <v>556</v>
       </c>
@@ -30949,7 +30945,7 @@
       </c>
       <c r="AO181" s="82"/>
     </row>
-    <row r="182" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="15" t="s">
         <v>561</v>
       </c>
@@ -31041,7 +31037,7 @@
       <c r="AN182" s="82"/>
       <c r="AO182" s="82"/>
     </row>
-    <row r="183" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="15" t="s">
         <v>563</v>
       </c>
@@ -31131,7 +31127,7 @@
       <c r="AN183" s="82"/>
       <c r="AO183" s="82"/>
     </row>
-    <row r="184" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="15" t="s">
         <v>564</v>
       </c>
@@ -31221,7 +31217,7 @@
       <c r="AN184" s="82"/>
       <c r="AO184" s="82"/>
     </row>
-    <row r="185" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="15" t="s">
         <v>566</v>
       </c>
@@ -31309,7 +31305,7 @@
       <c r="AN185" s="82"/>
       <c r="AO185" s="82"/>
     </row>
-    <row r="186" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="15" t="s">
         <v>569</v>
       </c>
@@ -31397,7 +31393,7 @@
       <c r="AN186" s="82"/>
       <c r="AO186" s="82"/>
     </row>
-    <row r="187" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="15" t="s">
         <v>571</v>
       </c>
@@ -31485,7 +31481,7 @@
       <c r="AN187" s="82"/>
       <c r="AO187" s="82"/>
     </row>
-    <row r="188" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="15" t="s">
         <v>574</v>
       </c>
@@ -31573,7 +31569,7 @@
       <c r="AN188" s="82"/>
       <c r="AO188" s="82"/>
     </row>
-    <row r="189" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="15" t="s">
         <v>577</v>
       </c>
@@ -31661,7 +31657,7 @@
       <c r="AN189" s="82"/>
       <c r="AO189" s="82"/>
     </row>
-    <row r="190" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="15" t="s">
         <v>579</v>
       </c>
@@ -31749,7 +31745,7 @@
       <c r="AN190" s="82"/>
       <c r="AO190" s="82"/>
     </row>
-    <row r="191" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="15" t="s">
         <v>581</v>
       </c>
@@ -31831,7 +31827,7 @@
       <c r="AN191" s="82"/>
       <c r="AO191" s="82"/>
     </row>
-    <row r="192" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="15" t="s">
         <v>583</v>
       </c>
@@ -31919,7 +31915,7 @@
       <c r="AN192" s="82"/>
       <c r="AO192" s="82"/>
     </row>
-    <row r="193" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="15" t="s">
         <v>585</v>
       </c>
@@ -32009,7 +32005,7 @@
       <c r="AN193" s="82"/>
       <c r="AO193" s="82"/>
     </row>
-    <row r="194" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="15" t="s">
         <v>588</v>
       </c>
@@ -32097,7 +32093,7 @@
       <c r="AN194" s="82"/>
       <c r="AO194" s="82"/>
     </row>
-    <row r="195" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="15" t="s">
         <v>591</v>
       </c>
@@ -32185,7 +32181,7 @@
       <c r="AN195" s="82"/>
       <c r="AO195" s="82"/>
     </row>
-    <row r="196" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="15" t="s">
         <v>594</v>
       </c>
@@ -32275,7 +32271,7 @@
       <c r="AN196" s="82"/>
       <c r="AO196" s="82"/>
     </row>
-    <row r="197" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="15" t="s">
         <v>598</v>
       </c>
@@ -32365,7 +32361,7 @@
       <c r="AN197" s="82"/>
       <c r="AO197" s="82"/>
     </row>
-    <row r="198" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="15" t="s">
         <v>600</v>
       </c>
@@ -32455,7 +32451,7 @@
       <c r="AN198" s="82"/>
       <c r="AO198" s="82"/>
     </row>
-    <row r="199" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="15" t="s">
         <v>602</v>
       </c>
@@ -32543,7 +32539,7 @@
       <c r="AN199" s="82"/>
       <c r="AO199" s="82"/>
     </row>
-    <row r="200" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="15" t="s">
         <v>604</v>
       </c>
@@ -32631,7 +32627,7 @@
       <c r="AN200" s="82"/>
       <c r="AO200" s="82"/>
     </row>
-    <row r="201" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="15" t="s">
         <v>606</v>
       </c>
@@ -32719,7 +32715,7 @@
       <c r="AN201" s="82"/>
       <c r="AO201" s="82"/>
     </row>
-    <row r="202" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="15" t="s">
         <v>609</v>
       </c>
@@ -32811,7 +32807,7 @@
       <c r="AN202" s="82"/>
       <c r="AO202" s="82"/>
     </row>
-    <row r="203" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="15" t="s">
         <v>610</v>
       </c>
@@ -32899,7 +32895,7 @@
       <c r="AN203" s="82"/>
       <c r="AO203" s="82"/>
     </row>
-    <row r="204" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="15" t="s">
         <v>611</v>
       </c>
@@ -32987,7 +32983,7 @@
       <c r="AN204" s="82"/>
       <c r="AO204" s="82"/>
     </row>
-    <row r="205" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="15" t="s">
         <v>613</v>
       </c>
@@ -33077,7 +33073,7 @@
       <c r="AN205" s="82"/>
       <c r="AO205" s="82"/>
     </row>
-    <row r="206" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="15" t="s">
         <v>614</v>
       </c>
@@ -33171,7 +33167,7 @@
       <c r="AN206" s="82"/>
       <c r="AO206" s="82"/>
     </row>
-    <row r="207" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="15" t="s">
         <v>615</v>
       </c>
@@ -33259,7 +33255,7 @@
       <c r="AN207" s="82"/>
       <c r="AO207" s="82"/>
     </row>
-    <row r="208" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="15" t="s">
         <v>618</v>
       </c>
@@ -33349,7 +33345,7 @@
       <c r="AN208" s="82"/>
       <c r="AO208" s="82"/>
     </row>
-    <row r="209" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="15" t="s">
         <v>620</v>
       </c>
@@ -33437,7 +33433,7 @@
       <c r="AN209" s="82"/>
       <c r="AO209" s="82"/>
     </row>
-    <row r="210" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="15" t="s">
         <v>622</v>
       </c>
@@ -33525,7 +33521,7 @@
       <c r="AN210" s="82"/>
       <c r="AO210" s="82"/>
     </row>
-    <row r="211" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="15" t="s">
         <v>624</v>
       </c>
@@ -33613,7 +33609,7 @@
       <c r="AN211" s="82"/>
       <c r="AO211" s="82"/>
     </row>
-    <row r="212" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="15" t="s">
         <v>626</v>
       </c>
@@ -33703,7 +33699,7 @@
       <c r="AN212" s="82"/>
       <c r="AO212" s="82"/>
     </row>
-    <row r="213" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="15" t="s">
         <v>628</v>
       </c>
@@ -33791,7 +33787,7 @@
       <c r="AN213" s="82"/>
       <c r="AO213" s="82"/>
     </row>
-    <row r="214" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="15" t="s">
         <v>630</v>
       </c>
@@ -33879,7 +33875,7 @@
       <c r="AN214" s="82"/>
       <c r="AO214" s="82"/>
     </row>
-    <row r="215" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="15" t="s">
         <v>633</v>
       </c>
@@ -33969,7 +33965,7 @@
       <c r="AN215" s="82"/>
       <c r="AO215" s="82"/>
     </row>
-    <row r="216" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="15" t="s">
         <v>636</v>
       </c>
@@ -34055,7 +34051,7 @@
       <c r="AN216" s="82"/>
       <c r="AO216" s="82"/>
     </row>
-    <row r="217" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="15" t="s">
         <v>638</v>
       </c>
@@ -34143,7 +34139,7 @@
       <c r="AN217" s="82"/>
       <c r="AO217" s="82"/>
     </row>
-    <row r="218" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="15" t="s">
         <v>641</v>
       </c>
@@ -34229,7 +34225,7 @@
       <c r="AN218" s="82"/>
       <c r="AO218" s="82"/>
     </row>
-    <row r="219" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="15" t="s">
         <v>643</v>
       </c>
@@ -34315,7 +34311,7 @@
       <c r="AN219" s="82"/>
       <c r="AO219" s="82"/>
     </row>
-    <row r="220" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="15" t="s">
         <v>645</v>
       </c>
@@ -34397,7 +34393,7 @@
       <c r="AN220" s="82"/>
       <c r="AO220" s="82"/>
     </row>
-    <row r="221" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="15" t="s">
         <v>646</v>
       </c>
@@ -34483,7 +34479,7 @@
       <c r="AN221" s="82"/>
       <c r="AO221" s="82"/>
     </row>
-    <row r="222" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="15" t="s">
         <v>649</v>
       </c>
@@ -34569,7 +34565,7 @@
       <c r="AN222" s="82"/>
       <c r="AO222" s="82"/>
     </row>
-    <row r="223" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="15" t="s">
         <v>652</v>
       </c>
@@ -34655,7 +34651,7 @@
       <c r="AN223" s="82"/>
       <c r="AO223" s="82"/>
     </row>
-    <row r="224" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="15" t="s">
         <v>654</v>
       </c>
@@ -34745,7 +34741,7 @@
       <c r="AN224" s="82"/>
       <c r="AO224" s="82"/>
     </row>
-    <row r="225" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="15" t="s">
         <v>656</v>
       </c>
@@ -34829,7 +34825,7 @@
       <c r="AN225" s="82"/>
       <c r="AO225" s="82"/>
     </row>
-    <row r="226" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="15" t="s">
         <v>658</v>
       </c>
@@ -34917,7 +34913,7 @@
       <c r="AN226" s="82"/>
       <c r="AO226" s="82"/>
     </row>
-    <row r="227" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="15" t="s">
         <v>660</v>
       </c>
@@ -35005,7 +35001,7 @@
       <c r="AN227" s="82"/>
       <c r="AO227" s="82"/>
     </row>
-    <row r="228" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="15" t="s">
         <v>663</v>
       </c>
@@ -35091,7 +35087,7 @@
       <c r="AN228" s="82"/>
       <c r="AO228" s="82"/>
     </row>
-    <row r="229" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="15" t="s">
         <v>665</v>
       </c>
@@ -35175,7 +35171,7 @@
       <c r="AN229" s="82"/>
       <c r="AO229" s="82"/>
     </row>
-    <row r="230" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="15" t="s">
         <v>666</v>
       </c>
@@ -35261,7 +35257,7 @@
       <c r="AN230" s="82"/>
       <c r="AO230" s="82"/>
     </row>
-    <row r="231" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="15" t="s">
         <v>668</v>
       </c>
@@ -35347,7 +35343,7 @@
       <c r="AN231" s="82"/>
       <c r="AO231" s="82"/>
     </row>
-    <row r="232" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="15" t="s">
         <v>670</v>
       </c>
@@ -35429,7 +35425,7 @@
       <c r="AN232" s="82"/>
       <c r="AO232" s="82"/>
     </row>
-    <row r="233" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="15" t="s">
         <v>671</v>
       </c>
@@ -35515,7 +35511,7 @@
       <c r="AN233" s="82"/>
       <c r="AO233" s="82"/>
     </row>
-    <row r="234" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="15" t="s">
         <v>673</v>
       </c>
@@ -35605,7 +35601,7 @@
       <c r="AN234" s="82"/>
       <c r="AO234" s="82"/>
     </row>
-    <row r="235" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="15" t="s">
         <v>674</v>
       </c>
@@ -35693,7 +35689,7 @@
       <c r="AN235" s="82"/>
       <c r="AO235" s="82"/>
     </row>
-    <row r="236" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="15" t="s">
         <v>677</v>
       </c>
@@ -35781,7 +35777,7 @@
       <c r="AN236" s="82"/>
       <c r="AO236" s="82"/>
     </row>
-    <row r="237" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" s="15" t="s">
         <v>679</v>
       </c>
@@ -35869,7 +35865,7 @@
       <c r="AN237" s="82"/>
       <c r="AO237" s="82"/>
     </row>
-    <row r="238" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="15" t="s">
         <v>682</v>
       </c>
@@ -35961,7 +35957,7 @@
       <c r="AN238" s="82"/>
       <c r="AO238" s="82"/>
     </row>
-    <row r="239" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="15" t="s">
         <v>685</v>
       </c>
@@ -36053,7 +36049,7 @@
       <c r="AN239" s="82"/>
       <c r="AO239" s="82"/>
     </row>
-    <row r="240" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" s="15" t="s">
         <v>687</v>
       </c>
@@ -36145,7 +36141,7 @@
       <c r="AN240" s="82"/>
       <c r="AO240" s="82"/>
     </row>
-    <row r="241" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" s="15" t="s">
         <v>689</v>
       </c>
@@ -36235,7 +36231,7 @@
       <c r="AN241" s="82"/>
       <c r="AO241" s="82"/>
     </row>
-    <row r="242" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" s="15" t="s">
         <v>691</v>
       </c>
@@ -36323,7 +36319,7 @@
       <c r="AN242" s="82"/>
       <c r="AO242" s="82"/>
     </row>
-    <row r="243" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" s="15" t="s">
         <v>693</v>
       </c>
@@ -36417,7 +36413,7 @@
       <c r="AN243" s="82"/>
       <c r="AO243" s="82"/>
     </row>
-    <row r="244" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="15" t="s">
         <v>695</v>
       </c>
@@ -36505,7 +36501,7 @@
       <c r="AN244" s="82"/>
       <c r="AO244" s="82"/>
     </row>
-    <row r="245" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="15" t="s">
         <v>697</v>
       </c>
@@ -36591,7 +36587,7 @@
       <c r="AN245" s="82"/>
       <c r="AO245" s="82"/>
     </row>
-    <row r="246" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="15" t="s">
         <v>699</v>
       </c>
@@ -36679,7 +36675,7 @@
       <c r="AN246" s="82"/>
       <c r="AO246" s="82"/>
     </row>
-    <row r="247" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="15" t="s">
         <v>701</v>
       </c>
@@ -36767,7 +36763,7 @@
       <c r="AN247" s="82"/>
       <c r="AO247" s="82"/>
     </row>
-    <row r="248" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" s="15" t="s">
         <v>703</v>
       </c>
@@ -36855,7 +36851,7 @@
       <c r="AN248" s="82"/>
       <c r="AO248" s="82"/>
     </row>
-    <row r="249" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="15" t="s">
         <v>705</v>
       </c>
@@ -36943,7 +36939,7 @@
       <c r="AN249" s="82"/>
       <c r="AO249" s="82"/>
     </row>
-    <row r="250" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" s="15" t="s">
         <v>707</v>
       </c>
@@ -37033,7 +37029,7 @@
       <c r="AN250" s="82"/>
       <c r="AO250" s="82"/>
     </row>
-    <row r="251" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" s="15" t="s">
         <v>708</v>
       </c>
@@ -37119,7 +37115,7 @@
       <c r="AN251" s="82"/>
       <c r="AO251" s="82"/>
     </row>
-    <row r="252" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="15" t="s">
         <v>710</v>
       </c>
@@ -37205,7 +37201,7 @@
       <c r="AN252" s="82"/>
       <c r="AO252" s="82"/>
     </row>
-    <row r="253" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="15" t="s">
         <v>712</v>
       </c>
@@ -37291,7 +37287,7 @@
       <c r="AN253" s="82"/>
       <c r="AO253" s="82"/>
     </row>
-    <row r="254" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="15" t="s">
         <v>714</v>
       </c>
@@ -37377,7 +37373,7 @@
       <c r="AN254" s="82"/>
       <c r="AO254" s="82"/>
     </row>
-    <row r="255" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="15" t="s">
         <v>716</v>
       </c>
@@ -37465,7 +37461,7 @@
       <c r="AN255" s="82"/>
       <c r="AO255" s="82"/>
     </row>
-    <row r="256" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="15" t="s">
         <v>718</v>
       </c>
@@ -37555,7 +37551,7 @@
       <c r="AN256" s="82"/>
       <c r="AO256" s="82"/>
     </row>
-    <row r="257" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="15" t="s">
         <v>720</v>
       </c>
@@ -37643,7 +37639,7 @@
       <c r="AN257" s="82"/>
       <c r="AO257" s="82"/>
     </row>
-    <row r="258" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="15" t="s">
         <v>722</v>
       </c>
@@ -37731,7 +37727,7 @@
       <c r="AN258" s="82"/>
       <c r="AO258" s="82"/>
     </row>
-    <row r="259" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="15" t="s">
         <v>724</v>
       </c>
@@ -37819,7 +37815,7 @@
       <c r="AN259" s="82"/>
       <c r="AO259" s="82"/>
     </row>
-    <row r="260" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="15" t="s">
         <v>726</v>
       </c>
@@ -37905,7 +37901,7 @@
       <c r="AN260" s="82"/>
       <c r="AO260" s="82"/>
     </row>
-    <row r="261" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="15" t="s">
         <v>727</v>
       </c>
@@ -37987,7 +37983,7 @@
       <c r="AN261" s="82"/>
       <c r="AO261" s="82"/>
     </row>
-    <row r="262" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="15" t="s">
         <v>728</v>
       </c>
@@ -38069,7 +38065,7 @@
       <c r="AN262" s="82"/>
       <c r="AO262" s="82"/>
     </row>
-    <row r="263" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="15" t="s">
         <v>729</v>
       </c>
@@ -38147,7 +38143,7 @@
       <c r="AN263" s="82"/>
       <c r="AO263" s="82"/>
     </row>
-    <row r="264" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="15" t="s">
         <v>731</v>
       </c>
@@ -38229,7 +38225,7 @@
       <c r="AN264" s="82"/>
       <c r="AO264" s="82"/>
     </row>
-    <row r="265" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="15" t="s">
         <v>732</v>
       </c>
@@ -38307,7 +38303,7 @@
       <c r="AN265" s="82"/>
       <c r="AO265" s="82"/>
     </row>
-    <row r="266" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" s="15" t="s">
         <v>733</v>
       </c>
@@ -38389,7 +38385,7 @@
       <c r="AN266" s="82"/>
       <c r="AO266" s="82"/>
     </row>
-    <row r="267" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" s="15" t="s">
         <v>734</v>
       </c>
@@ -38473,7 +38469,7 @@
       <c r="AN267" s="82"/>
       <c r="AO267" s="82"/>
     </row>
-    <row r="268" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" s="15" t="s">
         <v>735</v>
       </c>
@@ -38555,7 +38551,7 @@
       <c r="AN268" s="82"/>
       <c r="AO268" s="82"/>
     </row>
-    <row r="269" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="15" t="s">
         <v>737</v>
       </c>
@@ -38637,7 +38633,7 @@
       <c r="AN269" s="82"/>
       <c r="AO269" s="82"/>
     </row>
-    <row r="270" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="15" t="s">
         <v>738</v>
       </c>
@@ -38719,7 +38715,7 @@
       <c r="AN270" s="82"/>
       <c r="AO270" s="82"/>
     </row>
-    <row r="271" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="15" t="s">
         <v>739</v>
       </c>
@@ -38801,7 +38797,7 @@
       <c r="AN271" s="82"/>
       <c r="AO271" s="82"/>
     </row>
-    <row r="272" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="31" t="s">
         <v>740</v>
       </c>
@@ -38883,7 +38879,7 @@
       <c r="AN272" s="82"/>
       <c r="AO272" s="82"/>
     </row>
-    <row r="273" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" s="15" t="s">
         <v>741</v>
       </c>
@@ -38967,7 +38963,7 @@
       <c r="AN273" s="82"/>
       <c r="AO273" s="82"/>
     </row>
-    <row r="274" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" s="15" t="s">
         <v>742</v>
       </c>
@@ -39049,7 +39045,7 @@
       <c r="AN274" s="82"/>
       <c r="AO274" s="82"/>
     </row>
-    <row r="275" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" s="15" t="s">
         <v>743</v>
       </c>
@@ -39131,7 +39127,7 @@
       <c r="AN275" s="82"/>
       <c r="AO275" s="82"/>
     </row>
-    <row r="276" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" s="15" t="s">
         <v>744</v>
       </c>
@@ -39213,7 +39209,7 @@
       <c r="AN276" s="82"/>
       <c r="AO276" s="82"/>
     </row>
-    <row r="277" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" s="15" t="s">
         <v>745</v>
       </c>
@@ -39295,7 +39291,7 @@
       <c r="AN277" s="82"/>
       <c r="AO277" s="82"/>
     </row>
-    <row r="278" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" s="15" t="s">
         <v>746</v>
       </c>
@@ -39377,7 +39373,7 @@
       <c r="AN278" s="82"/>
       <c r="AO278" s="82"/>
     </row>
-    <row r="279" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A279" s="22" t="s">
         <v>747</v>
       </c>
@@ -39493,9 +39489,11 @@
       <c r="AN279" s="82">
         <v>46266</v>
       </c>
-      <c r="AO279" s="82"/>
+      <c r="AO279" s="82" t="s">
+        <v>1514</v>
+      </c>
     </row>
-    <row r="280" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A280" s="22" t="s">
         <v>757</v>
       </c>
@@ -39609,9 +39607,11 @@
       <c r="AN280" s="82">
         <v>46266</v>
       </c>
-      <c r="AO280" s="82"/>
+      <c r="AO280" s="82" t="s">
+        <v>1514</v>
+      </c>
     </row>
-    <row r="281" spans="1:41" s="26" customFormat="1" ht="122.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:41" s="26" customFormat="1" ht="122.4" x14ac:dyDescent="0.3">
       <c r="A281" s="22" t="s">
         <v>759</v>
       </c>
@@ -39727,9 +39727,11 @@
       <c r="AN281" s="82">
         <v>46266</v>
       </c>
-      <c r="AO281" s="82"/>
+      <c r="AO281" s="82" t="s">
+        <v>1514</v>
+      </c>
     </row>
-    <row r="282" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A282" s="22" t="s">
         <v>767</v>
       </c>
@@ -39843,7 +39845,7 @@
       <c r="AN282" s="82"/>
       <c r="AO282" s="82"/>
     </row>
-    <row r="283" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A283" s="22" t="s">
         <v>561</v>
       </c>
@@ -39957,9 +39959,11 @@
       <c r="AN283" s="82">
         <v>46235</v>
       </c>
-      <c r="AO283" s="82"/>
+      <c r="AO283" s="82" t="s">
+        <v>1514</v>
+      </c>
     </row>
-    <row r="284" spans="1:41" s="26" customFormat="1" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:41" s="26" customFormat="1" ht="81.599999999999994" x14ac:dyDescent="0.3">
       <c r="A284" s="22" t="s">
         <v>777</v>
       </c>
@@ -40075,7 +40079,7 @@
       <c r="AN284" s="82"/>
       <c r="AO284" s="82"/>
     </row>
-    <row r="285" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A285" s="22" t="s">
         <v>781</v>
       </c>
@@ -40191,7 +40195,7 @@
       <c r="AN285" s="82"/>
       <c r="AO285" s="82"/>
     </row>
-    <row r="286" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A286" s="22" t="s">
         <v>785</v>
       </c>
@@ -40307,7 +40311,7 @@
       <c r="AN286" s="82"/>
       <c r="AO286" s="82"/>
     </row>
-    <row r="287" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A287" s="22" t="s">
         <v>789</v>
       </c>
@@ -40423,7 +40427,7 @@
       <c r="AN287" s="82"/>
       <c r="AO287" s="82"/>
     </row>
-    <row r="288" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A288" s="22" t="s">
         <v>791</v>
       </c>
@@ -40539,7 +40543,7 @@
       <c r="AN288" s="82"/>
       <c r="AO288" s="82"/>
     </row>
-    <row r="289" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A289" s="22" t="s">
         <v>794</v>
       </c>
@@ -40655,7 +40659,7 @@
       <c r="AN289" s="82"/>
       <c r="AO289" s="82"/>
     </row>
-    <row r="290" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A290" s="22" t="s">
         <v>206</v>
       </c>
@@ -40753,7 +40757,7 @@
       <c r="AN290" s="82"/>
       <c r="AO290" s="82"/>
     </row>
-    <row r="291" spans="1:41" s="26" customFormat="1" ht="30.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:41" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A291" s="22" t="s">
         <v>803</v>
       </c>
@@ -40867,7 +40871,7 @@
       <c r="AN291" s="82"/>
       <c r="AO291" s="82"/>
     </row>
-    <row r="292" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A292" s="22" t="s">
         <v>808</v>
       </c>
@@ -40963,7 +40967,7 @@
       <c r="AN292" s="82"/>
       <c r="AO292" s="82"/>
     </row>
-    <row r="293" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A293" s="22" t="s">
         <v>811</v>
       </c>
@@ -41053,7 +41057,7 @@
       <c r="AN293" s="82"/>
       <c r="AO293" s="82"/>
     </row>
-    <row r="294" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A294" s="22" t="s">
         <v>814</v>
       </c>
@@ -41145,7 +41149,7 @@
       <c r="AN294" s="82"/>
       <c r="AO294" s="82"/>
     </row>
-    <row r="295" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A295" s="22" t="s">
         <v>816</v>
       </c>
@@ -41231,7 +41235,7 @@
       <c r="AN295" s="82"/>
       <c r="AO295" s="82"/>
     </row>
-    <row r="296" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A296" s="22" t="s">
         <v>820</v>
       </c>
@@ -41323,7 +41327,7 @@
       <c r="AN296" s="82"/>
       <c r="AO296" s="82"/>
     </row>
-    <row r="297" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A297" s="22" t="s">
         <v>727</v>
       </c>
@@ -41415,7 +41419,7 @@
       <c r="AN297" s="82"/>
       <c r="AO297" s="82"/>
     </row>
-    <row r="298" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A298" s="22" t="s">
         <v>155</v>
       </c>
@@ -41505,7 +41509,7 @@
       <c r="AN298" s="82"/>
       <c r="AO298" s="82"/>
     </row>
-    <row r="299" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A299" s="22" t="s">
         <v>827</v>
       </c>
@@ -41597,7 +41601,7 @@
       <c r="AN299" s="82"/>
       <c r="AO299" s="82"/>
     </row>
-    <row r="300" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A300" s="22" t="s">
         <v>828</v>
       </c>
@@ -41687,7 +41691,7 @@
       <c r="AN300" s="82"/>
       <c r="AO300" s="82"/>
     </row>
-    <row r="301" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A301" s="22" t="s">
         <v>390</v>
       </c>
@@ -41779,7 +41783,7 @@
       <c r="AN301" s="82"/>
       <c r="AO301" s="82"/>
     </row>
-    <row r="302" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A302" s="22" t="s">
         <v>265</v>
       </c>
@@ -41869,7 +41873,7 @@
       <c r="AN302" s="82"/>
       <c r="AO302" s="82"/>
     </row>
-    <row r="303" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A303" s="22" t="s">
         <v>835</v>
       </c>
@@ -41961,7 +41965,7 @@
       <c r="AN303" s="82"/>
       <c r="AO303" s="82"/>
     </row>
-    <row r="304" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A304" s="22" t="s">
         <v>838</v>
       </c>
@@ -42053,7 +42057,7 @@
       <c r="AN304" s="82"/>
       <c r="AO304" s="82"/>
     </row>
-    <row r="305" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A305" s="22" t="s">
         <v>52</v>
       </c>
@@ -42145,7 +42149,7 @@
       <c r="AN305" s="82"/>
       <c r="AO305" s="82"/>
     </row>
-    <row r="306" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A306" s="22" t="s">
         <v>842</v>
       </c>
@@ -42229,7 +42233,7 @@
       <c r="AN306" s="82"/>
       <c r="AO306" s="82"/>
     </row>
-    <row r="307" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A307" s="22" t="s">
         <v>844</v>
       </c>
@@ -42321,7 +42325,7 @@
       <c r="AN307" s="82"/>
       <c r="AO307" s="82"/>
     </row>
-    <row r="308" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A308" s="22" t="s">
         <v>846</v>
       </c>
@@ -42411,7 +42415,7 @@
       <c r="AN308" s="82"/>
       <c r="AO308" s="82"/>
     </row>
-    <row r="309" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A309" s="22" t="s">
         <v>847</v>
       </c>
@@ -42503,7 +42507,7 @@
       <c r="AN309" s="82"/>
       <c r="AO309" s="82"/>
     </row>
-    <row r="310" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A310" s="22" t="s">
         <v>649</v>
       </c>
@@ -42589,7 +42593,7 @@
       <c r="AN310" s="82"/>
       <c r="AO310" s="82"/>
     </row>
-    <row r="311" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A311" s="22" t="s">
         <v>738</v>
       </c>
@@ -42681,7 +42685,7 @@
       <c r="AN311" s="82"/>
       <c r="AO311" s="82"/>
     </row>
-    <row r="312" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A312" s="22" t="s">
         <v>117</v>
       </c>
@@ -42771,7 +42775,7 @@
       <c r="AN312" s="82"/>
       <c r="AO312" s="82"/>
     </row>
-    <row r="313" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A313" s="22">
         <v>98451</v>
       </c>
@@ -42845,7 +42849,7 @@
       <c r="AN313" s="82"/>
       <c r="AO313" s="82"/>
     </row>
-    <row r="314" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A314" s="22" t="s">
         <v>853</v>
       </c>
@@ -42941,7 +42945,7 @@
       <c r="AN314" s="82"/>
       <c r="AO314" s="82"/>
     </row>
-    <row r="315" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A315" s="22" t="s">
         <v>856</v>
       </c>
@@ -43033,7 +43037,7 @@
       <c r="AN315" s="82"/>
       <c r="AO315" s="82"/>
     </row>
-    <row r="316" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A316" s="3" t="s">
         <v>858</v>
       </c>
@@ -43121,7 +43125,7 @@
       <c r="AN316" s="82"/>
       <c r="AO316" s="82"/>
     </row>
-    <row r="317" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A317" s="22" t="s">
         <v>643</v>
       </c>
@@ -43207,7 +43211,7 @@
       <c r="AN317" s="82"/>
       <c r="AO317" s="82"/>
     </row>
-    <row r="318" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A318" s="22" t="s">
         <v>861</v>
       </c>
@@ -43299,7 +43303,7 @@
       <c r="AN318" s="82"/>
       <c r="AO318" s="82"/>
     </row>
-    <row r="319" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A319" s="22" t="s">
         <v>863</v>
       </c>
@@ -43395,7 +43399,7 @@
       <c r="AN319" s="82"/>
       <c r="AO319" s="82"/>
     </row>
-    <row r="320" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A320" s="22" t="s">
         <v>324</v>
       </c>
@@ -43485,7 +43489,7 @@
       <c r="AN320" s="82"/>
       <c r="AO320" s="82"/>
     </row>
-    <row r="321" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A321" s="22" t="s">
         <v>865</v>
       </c>
@@ -43567,7 +43571,7 @@
       <c r="AN321" s="82"/>
       <c r="AO321" s="82"/>
     </row>
-    <row r="322" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A322" s="3" t="s">
         <v>867</v>
       </c>
@@ -43655,7 +43659,7 @@
       <c r="AN322" s="82"/>
       <c r="AO322" s="82"/>
     </row>
-    <row r="323" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A323" s="22" t="s">
         <v>868</v>
       </c>
@@ -43743,7 +43747,7 @@
       <c r="AN323" s="82"/>
       <c r="AO323" s="82"/>
     </row>
-    <row r="324" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A324" s="22" t="s">
         <v>869</v>
       </c>
@@ -43827,7 +43831,7 @@
       <c r="AN324" s="82"/>
       <c r="AO324" s="82"/>
     </row>
-    <row r="325" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A325" s="22" t="s">
         <v>131</v>
       </c>
@@ -43917,7 +43921,7 @@
       <c r="AN325" s="82"/>
       <c r="AO325" s="82"/>
     </row>
-    <row r="326" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A326" s="3" t="s">
         <v>873</v>
       </c>
@@ -44007,7 +44011,7 @@
       <c r="AN326" s="82"/>
       <c r="AO326" s="82"/>
     </row>
-    <row r="327" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A327" s="22" t="s">
         <v>645</v>
       </c>
@@ -44093,7 +44097,7 @@
       <c r="AN327" s="82"/>
       <c r="AO327" s="82"/>
     </row>
-    <row r="328" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A328" s="3" t="s">
         <v>875</v>
       </c>
@@ -44181,7 +44185,7 @@
       <c r="AN328" s="82"/>
       <c r="AO328" s="82"/>
     </row>
-    <row r="329" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
         <v>876</v>
       </c>
@@ -44269,7 +44273,7 @@
       <c r="AN329" s="82"/>
       <c r="AO329" s="82"/>
     </row>
-    <row r="330" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A330" s="3" t="s">
         <v>877</v>
       </c>
@@ -44357,7 +44361,7 @@
       <c r="AN330" s="82"/>
       <c r="AO330" s="82"/>
     </row>
-    <row r="331" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
         <v>879</v>
       </c>
@@ -44441,7 +44445,7 @@
       <c r="AN331" s="82"/>
       <c r="AO331" s="82"/>
     </row>
-    <row r="332" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A332" s="3" t="s">
         <v>882</v>
       </c>
@@ -44525,7 +44529,7 @@
       <c r="AN332" s="82"/>
       <c r="AO332" s="82"/>
     </row>
-    <row r="333" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
         <v>885</v>
       </c>
@@ -44613,7 +44617,7 @@
       <c r="AN333" s="82"/>
       <c r="AO333" s="82"/>
     </row>
-    <row r="334" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A334" s="22" t="s">
         <v>886</v>
       </c>
@@ -44705,7 +44709,7 @@
       <c r="AN334" s="82"/>
       <c r="AO334" s="82"/>
     </row>
-    <row r="335" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A335" s="22" t="s">
         <v>889</v>
       </c>
@@ -44789,7 +44793,7 @@
       <c r="AN335" s="82"/>
       <c r="AO335" s="82"/>
     </row>
-    <row r="336" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A336" s="3" t="s">
         <v>274</v>
       </c>
@@ -44867,7 +44871,7 @@
       <c r="AN336" s="82"/>
       <c r="AO336" s="82"/>
     </row>
-    <row r="337" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A337" s="22" t="s">
         <v>891</v>
       </c>
@@ -44959,7 +44963,7 @@
       <c r="AN337" s="82"/>
       <c r="AO337" s="82"/>
     </row>
-    <row r="338" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A338" s="3" t="s">
         <v>663</v>
       </c>
@@ -45043,7 +45047,7 @@
       <c r="AN338" s="82"/>
       <c r="AO338" s="82"/>
     </row>
-    <row r="339" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A339" s="22" t="s">
         <v>894</v>
       </c>
@@ -45127,7 +45131,7 @@
       <c r="AN339" s="82"/>
       <c r="AO339" s="82"/>
     </row>
-    <row r="340" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A340" s="3" t="s">
         <v>897</v>
       </c>
@@ -45211,7 +45215,7 @@
       <c r="AN340" s="82"/>
       <c r="AO340" s="82"/>
     </row>
-    <row r="341" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A341" s="22" t="s">
         <v>899</v>
       </c>
@@ -45295,7 +45299,7 @@
       <c r="AN341" s="82"/>
       <c r="AO341" s="82"/>
     </row>
-    <row r="342" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A342" s="22" t="s">
         <v>901</v>
       </c>
@@ -45379,7 +45383,7 @@
       <c r="AN342" s="82"/>
       <c r="AO342" s="82"/>
     </row>
-    <row r="343" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
         <v>903</v>
       </c>
@@ -45469,7 +45473,7 @@
       <c r="AN343" s="82"/>
       <c r="AO343" s="82"/>
     </row>
-    <row r="344" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A344" s="22" t="s">
         <v>904</v>
       </c>
@@ -45557,7 +45561,7 @@
       <c r="AN344" s="82"/>
       <c r="AO344" s="82"/>
     </row>
-    <row r="345" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
         <v>906</v>
       </c>
@@ -45645,7 +45649,7 @@
       <c r="AN345" s="82"/>
       <c r="AO345" s="82"/>
     </row>
-    <row r="346" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A346" s="3" t="s">
         <v>654</v>
       </c>
@@ -45733,7 +45737,7 @@
       <c r="AN346" s="82"/>
       <c r="AO346" s="82"/>
     </row>
-    <row r="347" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A347" s="22" t="s">
         <v>908</v>
       </c>
@@ -45813,7 +45817,7 @@
       <c r="AN347" s="82"/>
       <c r="AO347" s="82"/>
     </row>
-    <row r="348" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A348" s="3" t="s">
         <v>911</v>
       </c>
@@ -45901,7 +45905,7 @@
       <c r="AN348" s="82"/>
       <c r="AO348" s="82"/>
     </row>
-    <row r="349" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A349" s="22" t="s">
         <v>912</v>
       </c>
@@ -45989,7 +45993,7 @@
       <c r="AN349" s="82"/>
       <c r="AO349" s="82"/>
     </row>
-    <row r="350" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A350" s="3" t="s">
         <v>914</v>
       </c>
@@ -46073,7 +46077,7 @@
       <c r="AN350" s="82"/>
       <c r="AO350" s="82"/>
     </row>
-    <row r="351" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A351" s="22" t="s">
         <v>916</v>
       </c>
@@ -46165,7 +46169,7 @@
       <c r="AN351" s="82"/>
       <c r="AO351" s="82"/>
     </row>
-    <row r="352" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A352" s="22" t="s">
         <v>917</v>
       </c>
@@ -46249,7 +46253,7 @@
       <c r="AN352" s="82"/>
       <c r="AO352" s="82"/>
     </row>
-    <row r="353" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
         <v>919</v>
       </c>
@@ -46337,7 +46341,7 @@
       <c r="AN353" s="82"/>
       <c r="AO353" s="82"/>
     </row>
-    <row r="354" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A354" s="3" t="s">
         <v>920</v>
       </c>
@@ -46421,7 +46425,7 @@
       <c r="AN354" s="82"/>
       <c r="AO354" s="82"/>
     </row>
-    <row r="355" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A355" s="22" t="s">
         <v>921</v>
       </c>
@@ -46513,7 +46517,7 @@
       <c r="AN355" s="82"/>
       <c r="AO355" s="82"/>
     </row>
-    <row r="356" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A356" s="3" t="s">
         <v>393</v>
       </c>
@@ -46597,7 +46601,7 @@
       <c r="AN356" s="82"/>
       <c r="AO356" s="82"/>
     </row>
-    <row r="357" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A357" s="22" t="s">
         <v>922</v>
       </c>
@@ -46681,7 +46685,7 @@
       <c r="AN357" s="82"/>
       <c r="AO357" s="82"/>
     </row>
-    <row r="358" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A358" s="22" t="s">
         <v>926</v>
       </c>
@@ -46765,7 +46769,7 @@
       <c r="AN358" s="82"/>
       <c r="AO358" s="82"/>
     </row>
-    <row r="359" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
         <v>927</v>
       </c>
@@ -46853,7 +46857,7 @@
       <c r="AN359" s="82"/>
       <c r="AO359" s="82"/>
     </row>
-    <row r="360" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A360" s="22" t="s">
         <v>928</v>
       </c>
@@ -46945,7 +46949,7 @@
       <c r="AN360" s="82"/>
       <c r="AO360" s="82"/>
     </row>
-    <row r="361" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
         <v>369</v>
       </c>
@@ -47029,7 +47033,7 @@
       <c r="AN361" s="82"/>
       <c r="AO361" s="82"/>
     </row>
-    <row r="362" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A362" s="3" t="s">
         <v>929</v>
       </c>
@@ -47117,7 +47121,7 @@
       <c r="AN362" s="82"/>
       <c r="AO362" s="82"/>
     </row>
-    <row r="363" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A363" s="22" t="s">
         <v>931</v>
       </c>
@@ -47201,7 +47205,7 @@
       <c r="AN363" s="82"/>
       <c r="AO363" s="82"/>
     </row>
-    <row r="364" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A364" s="3" t="s">
         <v>658</v>
       </c>
@@ -47285,7 +47289,7 @@
       <c r="AN364" s="82"/>
       <c r="AO364" s="82"/>
     </row>
-    <row r="365" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A365" s="22" t="s">
         <v>932</v>
       </c>
@@ -47369,7 +47373,7 @@
       <c r="AN365" s="82"/>
       <c r="AO365" s="82"/>
     </row>
-    <row r="366" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A366" s="3" t="s">
         <v>933</v>
       </c>
@@ -47453,7 +47457,7 @@
       <c r="AN366" s="82"/>
       <c r="AO366" s="82"/>
     </row>
-    <row r="367" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
         <v>739</v>
       </c>
@@ -47537,7 +47541,7 @@
       <c r="AN367" s="82"/>
       <c r="AO367" s="82"/>
     </row>
-    <row r="368" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A368" s="3" t="s">
         <v>673</v>
       </c>
@@ -47621,7 +47625,7 @@
       <c r="AN368" s="82"/>
       <c r="AO368" s="82"/>
     </row>
-    <row r="369" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
         <v>937</v>
       </c>
@@ -47705,7 +47709,7 @@
       <c r="AN369" s="82"/>
       <c r="AO369" s="82"/>
     </row>
-    <row r="370" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A370" s="22" t="s">
         <v>939</v>
       </c>
@@ -47789,7 +47793,7 @@
       <c r="AN370" s="82"/>
       <c r="AO370" s="82"/>
     </row>
-    <row r="371" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A371" s="22" t="s">
         <v>942</v>
       </c>
@@ -47873,7 +47877,7 @@
       <c r="AN371" s="82"/>
       <c r="AO371" s="82"/>
     </row>
-    <row r="372" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A372" s="22" t="s">
         <v>944</v>
       </c>
@@ -47957,7 +47961,7 @@
       <c r="AN372" s="82"/>
       <c r="AO372" s="82"/>
     </row>
-    <row r="373" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
         <v>945</v>
       </c>
@@ -48041,7 +48045,7 @@
       <c r="AN373" s="82"/>
       <c r="AO373" s="82"/>
     </row>
-    <row r="374" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A374" s="3" t="s">
         <v>947</v>
       </c>
@@ -48125,7 +48129,7 @@
       <c r="AN374" s="82"/>
       <c r="AO374" s="82"/>
     </row>
-    <row r="375" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A375" s="22" t="s">
         <v>948</v>
       </c>
@@ -48209,7 +48213,7 @@
       <c r="AN375" s="82"/>
       <c r="AO375" s="82"/>
     </row>
-    <row r="376" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A376" s="3" t="s">
         <v>949</v>
       </c>
@@ -48293,7 +48297,7 @@
       <c r="AN376" s="82"/>
       <c r="AO376" s="82"/>
     </row>
-    <row r="377" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A377" s="22" t="s">
         <v>950</v>
       </c>
@@ -48377,7 +48381,7 @@
       <c r="AN377" s="82"/>
       <c r="AO377" s="82"/>
     </row>
-    <row r="378" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A378" s="22" t="s">
         <v>952</v>
       </c>
@@ -48461,7 +48465,7 @@
       <c r="AN378" s="82"/>
       <c r="AO378" s="82"/>
     </row>
-    <row r="379" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A379" s="22" t="s">
         <v>955</v>
       </c>
@@ -48545,7 +48549,7 @@
       <c r="AN379" s="82"/>
       <c r="AO379" s="82"/>
     </row>
-    <row r="380" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A380" s="22" t="s">
         <v>957</v>
       </c>
@@ -48629,7 +48633,7 @@
       <c r="AN380" s="82"/>
       <c r="AO380" s="82"/>
     </row>
-    <row r="381" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A381" s="22" t="s">
         <v>961</v>
       </c>
@@ -48717,7 +48721,7 @@
       <c r="AN381" s="82"/>
       <c r="AO381" s="82"/>
     </row>
-    <row r="382" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A382" s="3" t="s">
         <v>963</v>
       </c>
@@ -48797,7 +48801,7 @@
       <c r="AN382" s="82"/>
       <c r="AO382" s="82"/>
     </row>
-    <row r="383" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A383" s="22" t="s">
         <v>965</v>
       </c>
@@ -48881,7 +48885,7 @@
       <c r="AN383" s="82"/>
       <c r="AO383" s="82"/>
     </row>
-    <row r="384" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A384" s="22" t="s">
         <v>322</v>
       </c>
@@ -48965,7 +48969,7 @@
       <c r="AN384" s="82"/>
       <c r="AO384" s="82"/>
     </row>
-    <row r="385" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
         <v>966</v>
       </c>
@@ -49053,7 +49057,7 @@
       <c r="AN385" s="82"/>
       <c r="AO385" s="82"/>
     </row>
-    <row r="386" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A386" s="22" t="s">
         <v>470</v>
       </c>
@@ -49137,7 +49141,7 @@
       <c r="AN386" s="82"/>
       <c r="AO386" s="82"/>
     </row>
-    <row r="387" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A387" s="22" t="s">
         <v>315</v>
       </c>
@@ -49221,7 +49225,7 @@
       <c r="AN387" s="82"/>
       <c r="AO387" s="82"/>
     </row>
-    <row r="388" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A388" s="3" t="s">
         <v>970</v>
       </c>
@@ -49305,7 +49309,7 @@
       <c r="AN388" s="82"/>
       <c r="AO388" s="82"/>
     </row>
-    <row r="389" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A389" s="22" t="s">
         <v>971</v>
       </c>
@@ -49397,7 +49401,7 @@
       <c r="AN389" s="82"/>
       <c r="AO389" s="82"/>
     </row>
-    <row r="390" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A390" s="22" t="s">
         <v>972</v>
       </c>
@@ -49489,7 +49493,7 @@
       <c r="AN390" s="82"/>
       <c r="AO390" s="82"/>
     </row>
-    <row r="391" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A391" s="22" t="s">
         <v>973</v>
       </c>
@@ -49573,7 +49577,7 @@
       <c r="AN391" s="82"/>
       <c r="AO391" s="82"/>
     </row>
-    <row r="392" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A392" s="22" t="s">
         <v>974</v>
       </c>
@@ -49657,7 +49661,7 @@
       <c r="AN392" s="82"/>
       <c r="AO392" s="82"/>
     </row>
-    <row r="393" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A393" s="22" t="s">
         <v>976</v>
       </c>
@@ -49749,7 +49753,7 @@
       <c r="AN393" s="82"/>
       <c r="AO393" s="82"/>
     </row>
-    <row r="394" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A394" s="22" t="s">
         <v>445</v>
       </c>
@@ -49833,7 +49837,7 @@
       <c r="AN394" s="82"/>
       <c r="AO394" s="82"/>
     </row>
-    <row r="395" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A395" s="22" t="s">
         <v>978</v>
       </c>
@@ -49925,7 +49929,7 @@
       <c r="AN395" s="82"/>
       <c r="AO395" s="82"/>
     </row>
-    <row r="396" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A396" s="22" t="s">
         <v>481</v>
       </c>
@@ -50009,7 +50013,7 @@
       <c r="AN396" s="82"/>
       <c r="AO396" s="82"/>
     </row>
-    <row r="397" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A397" s="22" t="s">
         <v>981</v>
       </c>
@@ -50093,7 +50097,7 @@
       <c r="AN397" s="82"/>
       <c r="AO397" s="82"/>
     </row>
-    <row r="398" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A398" s="22" t="s">
         <v>982</v>
       </c>
@@ -50177,7 +50181,7 @@
       <c r="AN398" s="82"/>
       <c r="AO398" s="82"/>
     </row>
-    <row r="399" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A399" s="22" t="s">
         <v>984</v>
       </c>
@@ -50261,7 +50265,7 @@
       <c r="AN399" s="82"/>
       <c r="AO399" s="82"/>
     </row>
-    <row r="400" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A400" s="3" t="s">
         <v>985</v>
       </c>
@@ -50345,7 +50349,7 @@
       <c r="AN400" s="82"/>
       <c r="AO400" s="82"/>
     </row>
-    <row r="401" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
         <v>986</v>
       </c>
@@ -50433,7 +50437,7 @@
       <c r="AN401" s="82"/>
       <c r="AO401" s="82"/>
     </row>
-    <row r="402" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A402" s="22" t="s">
         <v>987</v>
       </c>
@@ -50517,7 +50521,7 @@
       <c r="AN402" s="82"/>
       <c r="AO402" s="82"/>
     </row>
-    <row r="403" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A403" s="22" t="s">
         <v>988</v>
       </c>
@@ -50601,7 +50605,7 @@
       <c r="AN403" s="82"/>
       <c r="AO403" s="82"/>
     </row>
-    <row r="404" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A404" s="22" t="s">
         <v>991</v>
       </c>
@@ -50691,7 +50695,7 @@
       <c r="AN404" s="82"/>
       <c r="AO404" s="82"/>
     </row>
-    <row r="405" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A405" s="22" t="s">
         <v>992</v>
       </c>
@@ -50783,7 +50787,7 @@
       <c r="AN405" s="82"/>
       <c r="AO405" s="82"/>
     </row>
-    <row r="406" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A406" s="3" t="s">
         <v>994</v>
       </c>
@@ -50871,7 +50875,7 @@
       <c r="AN406" s="82"/>
       <c r="AO406" s="82"/>
     </row>
-    <row r="407" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A407" s="22" t="s">
         <v>996</v>
       </c>
@@ -50963,7 +50967,7 @@
       <c r="AN407" s="82"/>
       <c r="AO407" s="82"/>
     </row>
-    <row r="408" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A408" s="22" t="s">
         <v>998</v>
       </c>
@@ -51047,7 +51051,7 @@
       <c r="AN408" s="82"/>
       <c r="AO408" s="82"/>
     </row>
-    <row r="409" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A409" s="22" t="s">
         <v>1000</v>
       </c>
@@ -51131,7 +51135,7 @@
       <c r="AN409" s="82"/>
       <c r="AO409" s="82"/>
     </row>
-    <row r="410" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A410" s="22" t="s">
         <v>1002</v>
       </c>
@@ -51215,7 +51219,7 @@
       <c r="AN410" s="82"/>
       <c r="AO410" s="82"/>
     </row>
-    <row r="411" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A411" s="22" t="s">
         <v>413</v>
       </c>
@@ -51299,7 +51303,7 @@
       <c r="AN411" s="82"/>
       <c r="AO411" s="82"/>
     </row>
-    <row r="412" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A412" s="22" t="s">
         <v>1004</v>
       </c>
@@ -51383,7 +51387,7 @@
       <c r="AN412" s="82"/>
       <c r="AO412" s="82"/>
     </row>
-    <row r="413" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A413" s="22" t="s">
         <v>1005</v>
       </c>
@@ -51467,7 +51471,7 @@
       <c r="AN413" s="82"/>
       <c r="AO413" s="82"/>
     </row>
-    <row r="414" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A414" s="22" t="s">
         <v>1007</v>
       </c>
@@ -51551,7 +51555,7 @@
       <c r="AN414" s="82"/>
       <c r="AO414" s="82"/>
     </row>
-    <row r="415" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A415" s="22" t="s">
         <v>1009</v>
       </c>
@@ -51641,7 +51645,7 @@
       <c r="AN415" s="82"/>
       <c r="AO415" s="82"/>
     </row>
-    <row r="416" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A416" s="22" t="s">
         <v>1010</v>
       </c>
@@ -51733,7 +51737,7 @@
       <c r="AN416" s="82"/>
       <c r="AO416" s="82"/>
     </row>
-    <row r="417" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A417" s="22" t="s">
         <v>1011</v>
       </c>
@@ -51825,7 +51829,7 @@
       <c r="AN417" s="82"/>
       <c r="AO417" s="82"/>
     </row>
-    <row r="418" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A418" s="22" t="s">
         <v>1012</v>
       </c>
@@ -51915,7 +51919,7 @@
       <c r="AN418" s="82"/>
       <c r="AO418" s="82"/>
     </row>
-    <row r="419" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A419" s="22" t="s">
         <v>1013</v>
       </c>
@@ -52007,7 +52011,7 @@
       <c r="AN419" s="82"/>
       <c r="AO419" s="82"/>
     </row>
-    <row r="420" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A420" s="22" t="s">
         <v>1014</v>
       </c>
@@ -52091,7 +52095,7 @@
       <c r="AN420" s="82"/>
       <c r="AO420" s="82"/>
     </row>
-    <row r="421" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A421" s="22" t="s">
         <v>1016</v>
       </c>
@@ -52175,7 +52179,7 @@
       <c r="AN421" s="82"/>
       <c r="AO421" s="82"/>
     </row>
-    <row r="422" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A422" s="22" t="s">
         <v>1018</v>
       </c>
@@ -52259,7 +52263,7 @@
       <c r="AN422" s="82"/>
       <c r="AO422" s="82"/>
     </row>
-    <row r="423" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A423" s="22" t="s">
         <v>1020</v>
       </c>
@@ -52343,7 +52347,7 @@
       <c r="AN423" s="82"/>
       <c r="AO423" s="82"/>
     </row>
-    <row r="424" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A424" s="22" t="s">
         <v>1023</v>
       </c>
@@ -52427,7 +52431,7 @@
       <c r="AN424" s="82"/>
       <c r="AO424" s="82"/>
     </row>
-    <row r="425" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A425" s="22" t="s">
         <v>1025</v>
       </c>
@@ -52511,7 +52515,7 @@
       <c r="AN425" s="82"/>
       <c r="AO425" s="82"/>
     </row>
-    <row r="426" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A426" s="22" t="s">
         <v>1027</v>
       </c>
@@ -52595,7 +52599,7 @@
       <c r="AN426" s="82"/>
       <c r="AO426" s="82"/>
     </row>
-    <row r="427" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A427" s="22" t="s">
         <v>1028</v>
       </c>
@@ -52679,7 +52683,7 @@
       <c r="AN427" s="82"/>
       <c r="AO427" s="82"/>
     </row>
-    <row r="428" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A428" s="22" t="s">
         <v>1029</v>
       </c>
@@ -52763,7 +52767,7 @@
       <c r="AN428" s="82"/>
       <c r="AO428" s="82"/>
     </row>
-    <row r="429" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A429" s="22" t="s">
         <v>1031</v>
       </c>
@@ -52847,7 +52851,7 @@
       <c r="AN429" s="82"/>
       <c r="AO429" s="82"/>
     </row>
-    <row r="430" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A430" s="22" t="s">
         <v>1033</v>
       </c>
@@ -52931,7 +52935,7 @@
       <c r="AN430" s="82"/>
       <c r="AO430" s="82"/>
     </row>
-    <row r="431" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A431" s="22" t="s">
         <v>1035</v>
       </c>
@@ -53015,7 +53019,7 @@
       <c r="AN431" s="82"/>
       <c r="AO431" s="82"/>
     </row>
-    <row r="432" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A432" s="22" t="s">
         <v>641</v>
       </c>
@@ -53099,7 +53103,7 @@
       <c r="AN432" s="82"/>
       <c r="AO432" s="82"/>
     </row>
-    <row r="433" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A433" s="22" t="s">
         <v>1040</v>
       </c>
@@ -53183,7 +53187,7 @@
       <c r="AN433" s="82"/>
       <c r="AO433" s="82"/>
     </row>
-    <row r="434" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A434" s="22" t="s">
         <v>1042</v>
       </c>
@@ -53267,7 +53271,7 @@
       <c r="AN434" s="82"/>
       <c r="AO434" s="82"/>
     </row>
-    <row r="435" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A435" s="22" t="s">
         <v>1043</v>
       </c>
@@ -53351,7 +53355,7 @@
       <c r="AN435" s="82"/>
       <c r="AO435" s="82"/>
     </row>
-    <row r="436" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A436" s="22" t="s">
         <v>1045</v>
       </c>
@@ -53435,7 +53439,7 @@
       <c r="AN436" s="82"/>
       <c r="AO436" s="82"/>
     </row>
-    <row r="437" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A437" s="22" t="s">
         <v>1047</v>
       </c>
@@ -53519,7 +53523,7 @@
       <c r="AN437" s="82"/>
       <c r="AO437" s="82"/>
     </row>
-    <row r="438" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A438" s="22" t="s">
         <v>397</v>
       </c>
@@ -53603,7 +53607,7 @@
       <c r="AN438" s="82"/>
       <c r="AO438" s="82"/>
     </row>
-    <row r="439" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A439" s="22" t="s">
         <v>744</v>
       </c>
@@ -53687,7 +53691,7 @@
       <c r="AN439" s="82"/>
       <c r="AO439" s="82"/>
     </row>
-    <row r="440" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A440" s="22" t="s">
         <v>1052</v>
       </c>
@@ -53771,7 +53775,7 @@
       <c r="AN440" s="82"/>
       <c r="AO440" s="82"/>
     </row>
-    <row r="441" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A441" s="22" t="s">
         <v>1053</v>
       </c>
@@ -53855,7 +53859,7 @@
       <c r="AN441" s="82"/>
       <c r="AO441" s="82"/>
     </row>
-    <row r="442" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A442" s="22" t="s">
         <v>1054</v>
       </c>
@@ -53939,7 +53943,7 @@
       <c r="AN442" s="82"/>
       <c r="AO442" s="82"/>
     </row>
-    <row r="443" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A443" s="22" t="s">
         <v>1056</v>
       </c>
@@ -54023,7 +54027,7 @@
       <c r="AN443" s="82"/>
       <c r="AO443" s="82"/>
     </row>
-    <row r="444" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A444" s="22" t="s">
         <v>1058</v>
       </c>
@@ -54107,7 +54111,7 @@
       <c r="AN444" s="82"/>
       <c r="AO444" s="82"/>
     </row>
-    <row r="445" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A445" s="22" t="s">
         <v>1061</v>
       </c>
@@ -54191,7 +54195,7 @@
       <c r="AN445" s="82"/>
       <c r="AO445" s="82"/>
     </row>
-    <row r="446" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A446" s="22" t="s">
         <v>1062</v>
       </c>
@@ -54275,7 +54279,7 @@
       <c r="AN446" s="82"/>
       <c r="AO446" s="82"/>
     </row>
-    <row r="447" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A447" s="3" t="s">
         <v>652</v>
       </c>
@@ -54351,7 +54355,7 @@
       <c r="AN447" s="82"/>
       <c r="AO447" s="82"/>
     </row>
-    <row r="448" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A448" s="3" t="s">
         <v>1063</v>
       </c>
@@ -54435,7 +54439,7 @@
       <c r="AN448" s="82"/>
       <c r="AO448" s="82"/>
     </row>
-    <row r="449" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A449" s="3" t="s">
         <v>1064</v>
       </c>
@@ -54519,7 +54523,7 @@
       <c r="AN449" s="82"/>
       <c r="AO449" s="82"/>
     </row>
-    <row r="450" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A450" s="3" t="s">
         <v>1065</v>
       </c>
@@ -54603,7 +54607,7 @@
       <c r="AN450" s="82"/>
       <c r="AO450" s="82"/>
     </row>
-    <row r="451" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A451" s="3" t="s">
         <v>1066</v>
       </c>
@@ -54687,7 +54691,7 @@
       <c r="AN451" s="82"/>
       <c r="AO451" s="82"/>
     </row>
-    <row r="452" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A452" s="3" t="s">
         <v>1067</v>
       </c>
@@ -54771,7 +54775,7 @@
       <c r="AN452" s="82"/>
       <c r="AO452" s="82"/>
     </row>
-    <row r="453" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A453" s="3" t="s">
         <v>1068</v>
       </c>
@@ -54855,7 +54859,7 @@
       <c r="AN453" s="82"/>
       <c r="AO453" s="82"/>
     </row>
-    <row r="454" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A454" s="3" t="s">
         <v>1069</v>
       </c>
@@ -54939,7 +54943,7 @@
       <c r="AN454" s="82"/>
       <c r="AO454" s="82"/>
     </row>
-    <row r="455" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A455" s="3" t="s">
         <v>1070</v>
       </c>
@@ -55023,7 +55027,7 @@
       <c r="AN455" s="82"/>
       <c r="AO455" s="82"/>
     </row>
-    <row r="456" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A456" s="3" t="s">
         <v>1071</v>
       </c>
@@ -55107,7 +55111,7 @@
       <c r="AN456" s="82"/>
       <c r="AO456" s="82"/>
     </row>
-    <row r="457" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A457" s="3" t="s">
         <v>1073</v>
       </c>
@@ -55191,7 +55195,7 @@
       <c r="AN457" s="82"/>
       <c r="AO457" s="82"/>
     </row>
-    <row r="458" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A458" s="3" t="s">
         <v>1074</v>
       </c>
@@ -55275,7 +55279,7 @@
       <c r="AN458" s="82"/>
       <c r="AO458" s="82"/>
     </row>
-    <row r="459" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A459" s="3" t="s">
         <v>1075</v>
       </c>
@@ -55359,7 +55363,7 @@
       <c r="AN459" s="82"/>
       <c r="AO459" s="82"/>
     </row>
-    <row r="460" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A460" s="3" t="s">
         <v>1077</v>
       </c>
@@ -55443,7 +55447,7 @@
       <c r="AN460" s="82"/>
       <c r="AO460" s="82"/>
     </row>
-    <row r="461" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A461" s="3" t="s">
         <v>1078</v>
       </c>
@@ -55527,7 +55531,7 @@
       <c r="AN461" s="82"/>
       <c r="AO461" s="82"/>
     </row>
-    <row r="462" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A462" s="3" t="s">
         <v>1079</v>
       </c>
@@ -55611,7 +55615,7 @@
       <c r="AN462" s="82"/>
       <c r="AO462" s="82"/>
     </row>
-    <row r="463" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A463" s="3" t="s">
         <v>1080</v>
       </c>
@@ -55699,7 +55703,7 @@
       <c r="AN463" s="82"/>
       <c r="AO463" s="82"/>
     </row>
-    <row r="464" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A464" s="3" t="s">
         <v>1081</v>
       </c>
@@ -55783,7 +55787,7 @@
       <c r="AN464" s="82"/>
       <c r="AO464" s="82"/>
     </row>
-    <row r="465" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A465" s="3" t="s">
         <v>1082</v>
       </c>
@@ -55867,7 +55871,7 @@
       <c r="AN465" s="82"/>
       <c r="AO465" s="82"/>
     </row>
-    <row r="466" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A466" s="3" t="s">
         <v>1083</v>
       </c>
@@ -55951,7 +55955,7 @@
       <c r="AN466" s="82"/>
       <c r="AO466" s="82"/>
     </row>
-    <row r="467" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A467" s="3" t="s">
         <v>1085</v>
       </c>
@@ -56035,7 +56039,7 @@
       <c r="AN467" s="82"/>
       <c r="AO467" s="82"/>
     </row>
-    <row r="468" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A468" s="3" t="s">
         <v>1087</v>
       </c>
@@ -56119,7 +56123,7 @@
       <c r="AN468" s="82"/>
       <c r="AO468" s="82"/>
     </row>
-    <row r="469" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A469" s="3" t="s">
         <v>1089</v>
       </c>
@@ -56203,7 +56207,7 @@
       <c r="AN469" s="82"/>
       <c r="AO469" s="82"/>
     </row>
-    <row r="470" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A470" s="3" t="s">
         <v>1090</v>
       </c>
@@ -56287,7 +56291,7 @@
       <c r="AN470" s="82"/>
       <c r="AO470" s="82"/>
     </row>
-    <row r="471" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A471" s="3" t="s">
         <v>1091</v>
       </c>
@@ -56371,7 +56375,7 @@
       <c r="AN471" s="82"/>
       <c r="AO471" s="82"/>
     </row>
-    <row r="472" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A472" s="3" t="s">
         <v>1092</v>
       </c>
@@ -56455,7 +56459,7 @@
       <c r="AN472" s="82"/>
       <c r="AO472" s="82"/>
     </row>
-    <row r="473" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A473" s="3" t="s">
         <v>1094</v>
       </c>
@@ -56539,7 +56543,7 @@
       <c r="AN473" s="82"/>
       <c r="AO473" s="82"/>
     </row>
-    <row r="474" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A474" s="3" t="s">
         <v>1096</v>
       </c>
@@ -56623,7 +56627,7 @@
       <c r="AN474" s="82"/>
       <c r="AO474" s="82"/>
     </row>
-    <row r="475" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A475" s="3" t="s">
         <v>1098</v>
       </c>
@@ -56707,7 +56711,7 @@
       <c r="AN475" s="82"/>
       <c r="AO475" s="82"/>
     </row>
-    <row r="476" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A476" s="3" t="s">
         <v>1100</v>
       </c>
@@ -56791,7 +56795,7 @@
       <c r="AN476" s="82"/>
       <c r="AO476" s="82"/>
     </row>
-    <row r="477" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A477" s="3" t="s">
         <v>1102</v>
       </c>
@@ -56879,7 +56883,7 @@
       <c r="AN477" s="82"/>
       <c r="AO477" s="82"/>
     </row>
-    <row r="478" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A478" s="3" t="s">
         <v>1103</v>
       </c>
@@ -56967,7 +56971,7 @@
       <c r="AN478" s="82"/>
       <c r="AO478" s="82"/>
     </row>
-    <row r="479" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A479" s="3" t="s">
         <v>1104</v>
       </c>
@@ -57055,7 +57059,7 @@
       <c r="AN479" s="82"/>
       <c r="AO479" s="82"/>
     </row>
-    <row r="480" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A480" s="3" t="s">
         <v>1105</v>
       </c>
@@ -57139,7 +57143,7 @@
       <c r="AN480" s="82"/>
       <c r="AO480" s="82"/>
     </row>
-    <row r="481" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A481" s="3" t="s">
         <v>1107</v>
       </c>
@@ -57223,7 +57227,7 @@
       <c r="AN481" s="82"/>
       <c r="AO481" s="82"/>
     </row>
-    <row r="482" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A482" s="3" t="s">
         <v>1108</v>
       </c>
@@ -57307,7 +57311,7 @@
       <c r="AN482" s="82"/>
       <c r="AO482" s="82"/>
     </row>
-    <row r="483" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A483" s="3" t="s">
         <v>1109</v>
       </c>
@@ -57395,7 +57399,7 @@
       <c r="AN483" s="82"/>
       <c r="AO483" s="82"/>
     </row>
-    <row r="484" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A484" s="3" t="s">
         <v>1110</v>
       </c>
@@ -57483,7 +57487,7 @@
       <c r="AN484" s="82"/>
       <c r="AO484" s="82"/>
     </row>
-    <row r="485" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A485" s="3" t="s">
         <v>1111</v>
       </c>
@@ -57567,7 +57571,7 @@
       <c r="AN485" s="82"/>
       <c r="AO485" s="82"/>
     </row>
-    <row r="486" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A486" s="22" t="s">
         <v>1113</v>
       </c>
@@ -57651,7 +57655,7 @@
       <c r="AN486" s="82"/>
       <c r="AO486" s="82"/>
     </row>
-    <row r="487" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A487" s="22" t="s">
         <v>1114</v>
       </c>
@@ -57735,7 +57739,7 @@
       <c r="AN487" s="82"/>
       <c r="AO487" s="82"/>
     </row>
-    <row r="488" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A488" s="22" t="s">
         <v>1116</v>
       </c>
@@ -57819,7 +57823,7 @@
       <c r="AN488" s="82"/>
       <c r="AO488" s="82"/>
     </row>
-    <row r="489" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A489" s="22" t="s">
         <v>1117</v>
       </c>
@@ -57903,7 +57907,7 @@
       <c r="AN489" s="82"/>
       <c r="AO489" s="82"/>
     </row>
-    <row r="490" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A490" s="22" t="s">
         <v>1118</v>
       </c>
@@ -57987,7 +57991,7 @@
       <c r="AN490" s="82"/>
       <c r="AO490" s="82"/>
     </row>
-    <row r="491" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A491" s="22" t="s">
         <v>1119</v>
       </c>
@@ -58079,7 +58083,7 @@
       <c r="AN491" s="82"/>
       <c r="AO491" s="82"/>
     </row>
-    <row r="492" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A492" s="22" t="s">
         <v>452</v>
       </c>
@@ -58159,7 +58163,7 @@
       <c r="AN492" s="82"/>
       <c r="AO492" s="82"/>
     </row>
-    <row r="493" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A493" s="22" t="s">
         <v>1122</v>
       </c>
@@ -58229,7 +58233,7 @@
       <c r="AN493" s="82"/>
       <c r="AO493" s="82"/>
     </row>
-    <row r="494" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A494" s="22" t="s">
         <v>1124</v>
       </c>
@@ -58299,7 +58303,7 @@
       <c r="AN494" s="82"/>
       <c r="AO494" s="82"/>
     </row>
-    <row r="495" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A495" s="22" t="s">
         <v>1125</v>
       </c>
@@ -58369,7 +58373,7 @@
       <c r="AN495" s="82"/>
       <c r="AO495" s="82"/>
     </row>
-    <row r="496" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A496" s="22" t="s">
         <v>1126</v>
       </c>
@@ -58439,7 +58443,7 @@
       <c r="AN496" s="82"/>
       <c r="AO496" s="82"/>
     </row>
-    <row r="497" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A497" s="22" t="s">
         <v>1127</v>
       </c>
@@ -77475,7 +77479,7 @@
   <autoFilter ref="A2:AO710" xr:uid="{2AA437EE-405D-4A43-9EB9-23F1BEB36011}">
     <filterColumn colId="17">
       <filters>
-        <filter val="Diadema"/>
+        <filter val="Ferraz"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -78441,15 +78445,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="f5ab1930-d403-4c69-b2cd-8cc48f527d10" xsi:nil="true"/>
@@ -78458,6 +78453,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -78656,26 +78660,26 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AE26D3A-03CC-4B3D-9F98-6F77A1AEA74E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE495743-F761-4961-A762-7A3D120C6961}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f5ab1930-d403-4c69-b2cd-8cc48f527d10"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="c06ce65c-ed18-47f4-a957-afd315448c9c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE495743-F761-4961-A762-7A3D120C6961}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AE26D3A-03CC-4B3D-9F98-6F77A1AEA74E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="f5ab1930-d403-4c69-b2cd-8cc48f527d10"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c06ce65c-ed18-47f4-a957-afd315448c9c"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/dados_atuais.xlsx
+++ b/data/dados_atuais.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr codeName="EsteLivro"/>
+  <workbookPr codeName="EsteLivro" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delgadiadema.sharepoint.com/sites/GestoEstratgica/Documentos Compartilhados/Controle Master/BSW/Novo controle (Em processo)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2488" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2F73A0B-6A14-4CC5-847D-AF5F93B89CE2}"/>
+  <xr:revisionPtr revIDLastSave="2498" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32103F0E-BF9F-4EC1-9DFF-E41936453E47}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3E398004-7492-4AA0-94C2-EA9B761AAA49}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3E398004-7492-4AA0-94C2-EA9B761AAA49}"/>
   </bookViews>
   <sheets>
     <sheet name="Controle" sheetId="1" r:id="rId1"/>
@@ -14647,50 +14647,50 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AA437EE-405D-4A43-9EB9-23F1BEB36011}">
   <sheetPr codeName="Folha1" filterMode="1"/>
   <dimension ref="A1:AO720"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.453125" customWidth="1"/>
-    <col min="7" max="7" width="28.54296875" customWidth="1"/>
-    <col min="8" max="8" width="14.453125" customWidth="1"/>
-    <col min="9" max="9" width="10.08984375" customWidth="1"/>
-    <col min="10" max="10" width="9.54296875" customWidth="1"/>
-    <col min="11" max="11" width="21.453125" customWidth="1"/>
-    <col min="12" max="12" width="20.453125" customWidth="1"/>
-    <col min="13" max="13" width="23.54296875" customWidth="1"/>
-    <col min="14" max="14" width="32.453125" customWidth="1"/>
-    <col min="15" max="15" width="8.54296875" customWidth="1"/>
-    <col min="16" max="16" width="10.453125" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="12.453125" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="11.54296875" customWidth="1"/>
+    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" customWidth="1"/>
+    <col min="7" max="7" width="28.5546875" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" customWidth="1"/>
+    <col min="10" max="10" width="9.5546875" customWidth="1"/>
+    <col min="11" max="11" width="21.44140625" customWidth="1"/>
+    <col min="12" max="12" width="20.44140625" customWidth="1"/>
+    <col min="13" max="13" width="23.5546875" customWidth="1"/>
+    <col min="14" max="14" width="32.44140625" customWidth="1"/>
+    <col min="15" max="15" width="8.5546875" customWidth="1"/>
+    <col min="16" max="16" width="10.44140625" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="12.44140625" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="11.5546875" customWidth="1"/>
     <col min="19" max="19" width="15" customWidth="1"/>
-    <col min="20" max="20" width="15.54296875" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="16.453125" hidden="1" customWidth="1"/>
-    <col min="22" max="24" width="15.453125" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="15.453125" customWidth="1"/>
-    <col min="26" max="26" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.5546875" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="16.44140625" hidden="1" customWidth="1"/>
+    <col min="22" max="24" width="15.44140625" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="15.44140625" customWidth="1"/>
+    <col min="26" max="26" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="13" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.90625" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="24.08984375" customWidth="1"/>
-    <col min="37" max="37" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.90625" hidden="1" customWidth="1"/>
-    <col min="39" max="39" width="91.08984375" customWidth="1"/>
+    <col min="34" max="34" width="12.88671875" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="24.109375" customWidth="1"/>
+    <col min="37" max="37" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.88671875" hidden="1" customWidth="1"/>
+    <col min="39" max="39" width="91.109375" customWidth="1"/>
     <col min="40" max="40" width="24" style="50" customWidth="1"/>
-    <col min="41" max="41" width="24.36328125" style="50" customWidth="1"/>
+    <col min="41" max="41" width="24.33203125" style="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="151.4" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:41" ht="31.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:41" ht="151.35" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:41" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A2" s="39" t="s">
         <v>0</v>
       </c>
@@ -14815,7 +14815,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>41</v>
       </c>
@@ -14931,7 +14931,7 @@
       <c r="AN3" s="81"/>
       <c r="AO3" s="81"/>
     </row>
-    <row r="4" spans="1:41" s="26" customFormat="1" ht="134" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:41" s="26" customFormat="1" ht="132.6" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
         <v>54</v>
       </c>
@@ -15051,7 +15051,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
         <v>65</v>
       </c>
@@ -15171,7 +15171,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
         <v>72</v>
       </c>
@@ -15281,7 +15281,7 @@
       <c r="AN6" s="81"/>
       <c r="AO6" s="81"/>
     </row>
-    <row r="7" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="22" t="s">
         <v>80</v>
       </c>
@@ -15397,7 +15397,7 @@
       <c r="AN7" s="81"/>
       <c r="AO7" s="81"/>
     </row>
-    <row r="8" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
         <v>87</v>
       </c>
@@ -15497,7 +15497,7 @@
       <c r="AN8" s="81"/>
       <c r="AO8" s="81"/>
     </row>
-    <row r="9" spans="1:41" s="26" customFormat="1" ht="20" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
         <v>92</v>
       </c>
@@ -15617,7 +15617,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>99</v>
       </c>
@@ -15737,7 +15737,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="22" t="s">
         <v>105</v>
       </c>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="AO11" s="81"/>
     </row>
-    <row r="12" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
         <v>110</v>
       </c>
@@ -15973,7 +15973,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="22" t="s">
         <v>114</v>
       </c>
@@ -16089,7 +16089,7 @@
       <c r="AN13" s="81"/>
       <c r="AO13" s="81"/>
     </row>
-    <row r="14" spans="1:41" s="26" customFormat="1" ht="20.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
         <v>117</v>
       </c>
@@ -16205,7 +16205,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="22" t="s">
         <v>120</v>
       </c>
@@ -16319,7 +16319,7 @@
       <c r="AN15" s="81"/>
       <c r="AO15" s="81"/>
     </row>
-    <row r="16" spans="1:41" s="26" customFormat="1" ht="30" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:41" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
         <v>126</v>
       </c>
@@ -16439,7 +16439,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:41" s="26" customFormat="1" ht="20" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A17" s="22" t="s">
         <v>131</v>
       </c>
@@ -16553,7 +16553,7 @@
       <c r="AN17" s="81"/>
       <c r="AO17" s="81"/>
     </row>
-    <row r="18" spans="1:41" s="26" customFormat="1" ht="50" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:41" s="26" customFormat="1" ht="51" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
         <v>136</v>
       </c>
@@ -16669,7 +16669,7 @@
       <c r="AN18" s="81"/>
       <c r="AO18" s="81"/>
     </row>
-    <row r="19" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="22" t="s">
         <v>141</v>
       </c>
@@ -16787,7 +16787,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
         <v>147</v>
       </c>
@@ -16887,7 +16887,7 @@
       <c r="AN20" s="81"/>
       <c r="AO20" s="81"/>
     </row>
-    <row r="21" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A21" s="22" t="s">
         <v>151</v>
       </c>
@@ -17007,7 +17007,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="22" t="s">
         <v>158</v>
       </c>
@@ -17107,7 +17107,7 @@
       <c r="AN22" s="81"/>
       <c r="AO22" s="81"/>
     </row>
-    <row r="23" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A23" s="22" t="s">
         <v>162</v>
       </c>
@@ -17225,7 +17225,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="22" t="s">
         <v>166</v>
       </c>
@@ -17323,7 +17323,7 @@
       <c r="AN24" s="81"/>
       <c r="AO24" s="81"/>
     </row>
-    <row r="25" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="22" t="s">
         <v>168</v>
       </c>
@@ -17421,7 +17421,7 @@
       <c r="AN25" s="81"/>
       <c r="AO25" s="81"/>
     </row>
-    <row r="26" spans="1:41" s="26" customFormat="1" ht="30" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:41" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A26" s="22" t="s">
         <v>171</v>
       </c>
@@ -17517,7 +17517,7 @@
       <c r="AN26" s="81"/>
       <c r="AO26" s="81"/>
     </row>
-    <row r="27" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A27" s="22" t="s">
         <v>174</v>
       </c>
@@ -17615,7 +17615,7 @@
       <c r="AN27" s="81"/>
       <c r="AO27" s="81"/>
     </row>
-    <row r="28" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="22" t="s">
         <v>178</v>
       </c>
@@ -17731,7 +17731,7 @@
       <c r="AN28" s="81"/>
       <c r="AO28" s="81"/>
     </row>
-    <row r="29" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="22" t="s">
         <v>183</v>
       </c>
@@ -17829,7 +17829,7 @@
       <c r="AN29" s="81"/>
       <c r="AO29" s="81"/>
     </row>
-    <row r="30" spans="1:41" s="26" customFormat="1" ht="30" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:41" s="26" customFormat="1" ht="30.6" x14ac:dyDescent="0.3">
       <c r="A30" s="22" t="s">
         <v>187</v>
       </c>
@@ -17927,7 +17927,7 @@
       <c r="AN30" s="81"/>
       <c r="AO30" s="81"/>
     </row>
-    <row r="31" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="22" t="s">
         <v>192</v>
       </c>
@@ -18019,7 +18019,7 @@
       <c r="AN31" s="81"/>
       <c r="AO31" s="81"/>
     </row>
-    <row r="32" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="22" t="s">
         <v>195</v>
       </c>
@@ -18139,7 +18139,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="22" t="s">
         <v>198</v>
       </c>
@@ -18257,7 +18257,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="22" t="s">
         <v>204</v>
       </c>
@@ -18351,7 +18351,7 @@
       <c r="AN34" s="81"/>
       <c r="AO34" s="81"/>
     </row>
-    <row r="35" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="22" t="s">
         <v>208</v>
       </c>
@@ -18471,7 +18471,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A36" s="22" t="s">
         <v>214</v>
       </c>
@@ -18567,7 +18567,7 @@
       <c r="AN36" s="81"/>
       <c r="AO36" s="81"/>
     </row>
-    <row r="37" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A37" s="22" t="s">
         <v>215</v>
       </c>
@@ -18655,7 +18655,7 @@
       <c r="AN37" s="81"/>
       <c r="AO37" s="81"/>
     </row>
-    <row r="38" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="22" t="s">
         <v>218</v>
       </c>
@@ -18757,7 +18757,7 @@
       <c r="AN38" s="81"/>
       <c r="AO38" s="81"/>
     </row>
-    <row r="39" spans="1:41" s="26" customFormat="1" ht="71.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:41" s="26" customFormat="1" ht="71.400000000000006" x14ac:dyDescent="0.3">
       <c r="A39" s="22" t="s">
         <v>221</v>
       </c>
@@ -18879,7 +18879,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="22" t="s">
         <v>225</v>
       </c>
@@ -18973,7 +18973,7 @@
       <c r="AN40" s="81"/>
       <c r="AO40" s="81"/>
     </row>
-    <row r="41" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="22" t="s">
         <v>228</v>
       </c>
@@ -19067,7 +19067,7 @@
       <c r="AN41" s="81"/>
       <c r="AO41" s="81"/>
     </row>
-    <row r="42" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="22" t="s">
         <v>231</v>
       </c>
@@ -19161,7 +19161,7 @@
       <c r="AN42" s="81"/>
       <c r="AO42" s="81"/>
     </row>
-    <row r="43" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A43" s="22" t="s">
         <v>235</v>
       </c>
@@ -19255,7 +19255,7 @@
       <c r="AN43" s="81"/>
       <c r="AO43" s="81"/>
     </row>
-    <row r="44" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A44" s="22" t="s">
         <v>239</v>
       </c>
@@ -19375,7 +19375,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="45" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A45" s="22" t="s">
         <v>244</v>
       </c>
@@ -19491,7 +19491,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="46" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A46" s="22" t="s">
         <v>248</v>
       </c>
@@ -19585,7 +19585,7 @@
       <c r="AN46" s="81"/>
       <c r="AO46" s="81"/>
     </row>
-    <row r="47" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A47" s="22" t="s">
         <v>255</v>
       </c>
@@ -19679,7 +19679,7 @@
       <c r="AN47" s="81"/>
       <c r="AO47" s="81"/>
     </row>
-    <row r="48" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="22" t="s">
         <v>258</v>
       </c>
@@ -19773,7 +19773,7 @@
       <c r="AN48" s="81"/>
       <c r="AO48" s="81"/>
     </row>
-    <row r="49" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A49" s="22" t="s">
         <v>260</v>
       </c>
@@ -19867,7 +19867,7 @@
       <c r="AN49" s="81"/>
       <c r="AO49" s="81"/>
     </row>
-    <row r="50" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A50" s="22" t="s">
         <v>262</v>
       </c>
@@ -19961,7 +19961,7 @@
       <c r="AN50" s="81"/>
       <c r="AO50" s="81"/>
     </row>
-    <row r="51" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A51" s="22" t="s">
         <v>265</v>
       </c>
@@ -20055,7 +20055,7 @@
       <c r="AN51" s="81"/>
       <c r="AO51" s="81"/>
     </row>
-    <row r="52" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A52" s="22" t="s">
         <v>268</v>
       </c>
@@ -20149,7 +20149,7 @@
       <c r="AN52" s="81"/>
       <c r="AO52" s="81"/>
     </row>
-    <row r="53" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A53" s="22" t="s">
         <v>271</v>
       </c>
@@ -20243,7 +20243,7 @@
       <c r="AN53" s="81"/>
       <c r="AO53" s="81"/>
     </row>
-    <row r="54" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A54" s="22" t="s">
         <v>273</v>
       </c>
@@ -20337,7 +20337,7 @@
       <c r="AN54" s="81"/>
       <c r="AO54" s="81"/>
     </row>
-    <row r="55" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="22" t="s">
         <v>277</v>
       </c>
@@ -20431,7 +20431,7 @@
       <c r="AN55" s="81"/>
       <c r="AO55" s="81"/>
     </row>
-    <row r="56" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A56" s="22" t="s">
         <v>280</v>
       </c>
@@ -20551,7 +20551,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="57" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A57" s="22" t="s">
         <v>284</v>
       </c>
@@ -20645,7 +20645,7 @@
       <c r="AN57" s="81"/>
       <c r="AO57" s="81"/>
     </row>
-    <row r="58" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A58" s="22" t="s">
         <v>285</v>
       </c>
@@ -20739,7 +20739,7 @@
       <c r="AN58" s="81"/>
       <c r="AO58" s="81"/>
     </row>
-    <row r="59" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A59" s="22" t="s">
         <v>287</v>
       </c>
@@ -20833,7 +20833,7 @@
       <c r="AN59" s="81"/>
       <c r="AO59" s="81"/>
     </row>
-    <row r="60" spans="1:41" s="26" customFormat="1" ht="21" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A60" s="22" t="s">
         <v>289</v>
       </c>
@@ -20945,7 +20945,7 @@
       <c r="AN60" s="81"/>
       <c r="AO60" s="81"/>
     </row>
-    <row r="61" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A61" s="22" t="s">
         <v>295</v>
       </c>
@@ -21061,7 +21061,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="62" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A62" s="22" t="s">
         <v>301</v>
       </c>
@@ -21155,7 +21155,7 @@
       <c r="AN62" s="81"/>
       <c r="AO62" s="81"/>
     </row>
-    <row r="63" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A63" s="22" t="s">
         <v>303</v>
       </c>
@@ -21249,7 +21249,7 @@
       <c r="AN63" s="81"/>
       <c r="AO63" s="81"/>
     </row>
-    <row r="64" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A64" s="22" t="s">
         <v>306</v>
       </c>
@@ -21343,7 +21343,7 @@
       <c r="AN64" s="81"/>
       <c r="AO64" s="81"/>
     </row>
-    <row r="65" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A65" s="22" t="s">
         <v>308</v>
       </c>
@@ -21439,7 +21439,7 @@
       <c r="AN65" s="81"/>
       <c r="AO65" s="81"/>
     </row>
-    <row r="66" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A66" s="22" t="s">
         <v>310</v>
       </c>
@@ -21535,7 +21535,7 @@
       <c r="AN66" s="81"/>
       <c r="AO66" s="81"/>
     </row>
-    <row r="67" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A67" s="22" t="s">
         <v>312</v>
       </c>
@@ -21625,7 +21625,7 @@
       <c r="AN67" s="81"/>
       <c r="AO67" s="81"/>
     </row>
-    <row r="68" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A68" s="22" t="s">
         <v>313</v>
       </c>
@@ -21719,7 +21719,7 @@
       <c r="AN68" s="81"/>
       <c r="AO68" s="81"/>
     </row>
-    <row r="69" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A69" s="22" t="s">
         <v>315</v>
       </c>
@@ -21815,7 +21815,7 @@
       <c r="AN69" s="81"/>
       <c r="AO69" s="81"/>
     </row>
-    <row r="70" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A70" s="22" t="s">
         <v>318</v>
       </c>
@@ -21909,7 +21909,7 @@
       <c r="AN70" s="81"/>
       <c r="AO70" s="81"/>
     </row>
-    <row r="71" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A71" s="22" t="s">
         <v>320</v>
       </c>
@@ -22003,7 +22003,7 @@
       <c r="AN71" s="81"/>
       <c r="AO71" s="81"/>
     </row>
-    <row r="72" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A72" s="22" t="s">
         <v>323</v>
       </c>
@@ -22099,7 +22099,7 @@
       <c r="AN72" s="81"/>
       <c r="AO72" s="81"/>
     </row>
-    <row r="73" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A73" s="22" t="s">
         <v>326</v>
       </c>
@@ -22193,7 +22193,7 @@
       <c r="AN73" s="81"/>
       <c r="AO73" s="81"/>
     </row>
-    <row r="74" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A74" s="22" t="s">
         <v>328</v>
       </c>
@@ -22287,7 +22287,7 @@
       <c r="AN74" s="81"/>
       <c r="AO74" s="81"/>
     </row>
-    <row r="75" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A75" s="22" t="s">
         <v>330</v>
       </c>
@@ -22379,7 +22379,7 @@
       <c r="AN75" s="81"/>
       <c r="AO75" s="81"/>
     </row>
-    <row r="76" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A76" s="22" t="s">
         <v>333</v>
       </c>
@@ -22473,7 +22473,7 @@
       <c r="AN76" s="81"/>
       <c r="AO76" s="81"/>
     </row>
-    <row r="77" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A77" s="22" t="s">
         <v>337</v>
       </c>
@@ -22565,7 +22565,7 @@
       <c r="AN77" s="81"/>
       <c r="AO77" s="81"/>
     </row>
-    <row r="78" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="22" t="s">
         <v>339</v>
       </c>
@@ -22681,7 +22681,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="79" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A79" s="22" t="s">
         <v>343</v>
       </c>
@@ -22775,7 +22775,7 @@
       <c r="AN79" s="81"/>
       <c r="AO79" s="81"/>
     </row>
-    <row r="80" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A80" s="22" t="s">
         <v>346</v>
       </c>
@@ -22891,7 +22891,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="81" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A81" s="22" t="s">
         <v>350</v>
       </c>
@@ -22987,7 +22987,7 @@
       <c r="AN81" s="81"/>
       <c r="AO81" s="81"/>
     </row>
-    <row r="82" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A82" s="22" t="s">
         <v>352</v>
       </c>
@@ -23081,7 +23081,7 @@
       <c r="AN82" s="81"/>
       <c r="AO82" s="81"/>
     </row>
-    <row r="83" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A83" s="22" t="s">
         <v>354</v>
       </c>
@@ -23175,7 +23175,7 @@
       <c r="AN83" s="81"/>
       <c r="AO83" s="81"/>
     </row>
-    <row r="84" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A84" s="22" t="s">
         <v>356</v>
       </c>
@@ -23271,7 +23271,7 @@
       <c r="AN84" s="81"/>
       <c r="AO84" s="81"/>
     </row>
-    <row r="85" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A85" s="22" t="s">
         <v>359</v>
       </c>
@@ -23365,7 +23365,7 @@
       <c r="AN85" s="81"/>
       <c r="AO85" s="81"/>
     </row>
-    <row r="86" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A86" s="22" t="s">
         <v>361</v>
       </c>
@@ -23455,7 +23455,7 @@
       <c r="AN86" s="81"/>
       <c r="AO86" s="81"/>
     </row>
-    <row r="87" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A87" s="22" t="s">
         <v>366</v>
       </c>
@@ -23549,7 +23549,7 @@
       <c r="AN87" s="81"/>
       <c r="AO87" s="81"/>
     </row>
-    <row r="88" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A88" s="22" t="s">
         <v>368</v>
       </c>
@@ -23645,7 +23645,7 @@
       <c r="AN88" s="81"/>
       <c r="AO88" s="81"/>
     </row>
-    <row r="89" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A89" s="22" t="s">
         <v>373</v>
       </c>
@@ -23739,7 +23739,7 @@
       <c r="AN89" s="81"/>
       <c r="AO89" s="81"/>
     </row>
-    <row r="90" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A90" s="22" t="s">
         <v>376</v>
       </c>
@@ -23833,7 +23833,7 @@
       <c r="AN90" s="81"/>
       <c r="AO90" s="81"/>
     </row>
-    <row r="91" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A91" s="22" t="s">
         <v>378</v>
       </c>
@@ -23927,7 +23927,7 @@
       <c r="AN91" s="81"/>
       <c r="AO91" s="81"/>
     </row>
-    <row r="92" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A92" s="22" t="s">
         <v>381</v>
       </c>
@@ -24021,7 +24021,7 @@
       <c r="AN92" s="81"/>
       <c r="AO92" s="81"/>
     </row>
-    <row r="93" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A93" s="22" t="s">
         <v>384</v>
       </c>
@@ -24113,7 +24113,7 @@
       <c r="AN93" s="81"/>
       <c r="AO93" s="81"/>
     </row>
-    <row r="94" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A94" s="22" t="s">
         <v>386</v>
       </c>
@@ -24207,7 +24207,7 @@
       <c r="AN94" s="81"/>
       <c r="AO94" s="81"/>
     </row>
-    <row r="95" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A95" s="15" t="s">
         <v>389</v>
       </c>
@@ -24301,7 +24301,7 @@
       <c r="AN95" s="81"/>
       <c r="AO95" s="81"/>
     </row>
-    <row r="96" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A96" s="22" t="s">
         <v>392</v>
       </c>
@@ -24417,7 +24417,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="97" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A97" s="22" t="s">
         <v>395</v>
       </c>
@@ -24505,7 +24505,7 @@
       <c r="AN97" s="81"/>
       <c r="AO97" s="81"/>
     </row>
-    <row r="98" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>396</v>
       </c>
@@ -24601,7 +24601,7 @@
       <c r="AN98" s="81"/>
       <c r="AO98" s="81"/>
     </row>
-    <row r="99" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A99" s="22" t="s">
         <v>400</v>
       </c>
@@ -24697,7 +24697,7 @@
       <c r="AN99" s="81"/>
       <c r="AO99" s="81"/>
     </row>
-    <row r="100" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="22" t="s">
         <v>402</v>
       </c>
@@ -24791,7 +24791,7 @@
       <c r="AN100" s="81"/>
       <c r="AO100" s="81"/>
     </row>
-    <row r="101" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A101" s="22" t="s">
         <v>405</v>
       </c>
@@ -24885,7 +24885,7 @@
       <c r="AN101" s="81"/>
       <c r="AO101" s="81"/>
     </row>
-    <row r="102" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A102" s="22" t="s">
         <v>408</v>
       </c>
@@ -24975,7 +24975,7 @@
       <c r="AN102" s="81"/>
       <c r="AO102" s="81"/>
     </row>
-    <row r="103" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A103" s="22" t="s">
         <v>411</v>
       </c>
@@ -25069,7 +25069,7 @@
       <c r="AN103" s="81"/>
       <c r="AO103" s="81"/>
     </row>
-    <row r="104" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A104" s="22" t="s">
         <v>412</v>
       </c>
@@ -25165,7 +25165,7 @@
       <c r="AN104" s="81"/>
       <c r="AO104" s="81"/>
     </row>
-    <row r="105" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A105" s="22" t="s">
         <v>414</v>
       </c>
@@ -25253,7 +25253,7 @@
       <c r="AN105" s="81"/>
       <c r="AO105" s="81"/>
     </row>
-    <row r="106" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A106" s="22" t="s">
         <v>416</v>
       </c>
@@ -25347,7 +25347,7 @@
       <c r="AN106" s="81"/>
       <c r="AO106" s="81"/>
     </row>
-    <row r="107" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A107" s="15" t="s">
         <v>418</v>
       </c>
@@ -25435,7 +25435,7 @@
       <c r="AN107" s="81"/>
       <c r="AO107" s="81"/>
     </row>
-    <row r="108" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A108" s="22" t="s">
         <v>420</v>
       </c>
@@ -25527,7 +25527,7 @@
       <c r="AN108" s="81"/>
       <c r="AO108" s="81"/>
     </row>
-    <row r="109" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A109" s="22" t="s">
         <v>422</v>
       </c>
@@ -25621,7 +25621,7 @@
       <c r="AN109" s="81"/>
       <c r="AO109" s="81"/>
     </row>
-    <row r="110" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A110" s="22" t="s">
         <v>424</v>
       </c>
@@ -25739,7 +25739,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="111" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A111" s="22" t="s">
         <v>428</v>
       </c>
@@ -25835,7 +25835,7 @@
       <c r="AN111" s="81"/>
       <c r="AO111" s="81"/>
     </row>
-    <row r="112" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A112" s="22" t="s">
         <v>430</v>
       </c>
@@ -25953,7 +25953,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="113" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A113" s="22" t="s">
         <v>433</v>
       </c>
@@ -26043,7 +26043,7 @@
       <c r="AN113" s="81"/>
       <c r="AO113" s="81"/>
     </row>
-    <row r="114" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A114" s="22" t="s">
         <v>437</v>
       </c>
@@ -26131,7 +26131,7 @@
       <c r="AN114" s="81"/>
       <c r="AO114" s="81"/>
     </row>
-    <row r="115" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>438</v>
       </c>
@@ -26225,7 +26225,7 @@
       <c r="AN115" s="81"/>
       <c r="AO115" s="81"/>
     </row>
-    <row r="116" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A116" s="22" t="s">
         <v>440</v>
       </c>
@@ -26311,7 +26311,7 @@
       <c r="AN116" s="81"/>
       <c r="AO116" s="81"/>
     </row>
-    <row r="117" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A117" s="22" t="s">
         <v>442</v>
       </c>
@@ -26407,7 +26407,7 @@
       <c r="AN117" s="81"/>
       <c r="AO117" s="81"/>
     </row>
-    <row r="118" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A118" s="22" t="s">
         <v>444</v>
       </c>
@@ -26501,7 +26501,7 @@
       <c r="AN118" s="81"/>
       <c r="AO118" s="81"/>
     </row>
-    <row r="119" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A119" s="22" t="s">
         <v>446</v>
       </c>
@@ -26593,7 +26593,7 @@
       <c r="AN119" s="81"/>
       <c r="AO119" s="81"/>
     </row>
-    <row r="120" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A120" s="15" t="s">
         <v>448</v>
       </c>
@@ -26679,7 +26679,7 @@
       <c r="AN120" s="81"/>
       <c r="AO120" s="81"/>
     </row>
-    <row r="121" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A121" s="22" t="s">
         <v>449</v>
       </c>
@@ -26771,7 +26771,7 @@
       <c r="AN121" s="81"/>
       <c r="AO121" s="81"/>
     </row>
-    <row r="122" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A122" s="15" t="s">
         <v>451</v>
       </c>
@@ -26859,7 +26859,7 @@
       <c r="AN122" s="81"/>
       <c r="AO122" s="81"/>
     </row>
-    <row r="123" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A123" s="22" t="s">
         <v>452</v>
       </c>
@@ -26973,7 +26973,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="124" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A124" s="22" t="s">
         <v>454</v>
       </c>
@@ -27059,7 +27059,7 @@
       <c r="AN124" s="81"/>
       <c r="AO124" s="81"/>
     </row>
-    <row r="125" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A125" s="22" t="s">
         <v>455</v>
       </c>
@@ -27155,7 +27155,7 @@
       <c r="AN125" s="81"/>
       <c r="AO125" s="81"/>
     </row>
-    <row r="126" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A126" s="22" t="s">
         <v>457</v>
       </c>
@@ -27245,7 +27245,7 @@
       <c r="AN126" s="81"/>
       <c r="AO126" s="81"/>
     </row>
-    <row r="127" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A127" s="22" t="s">
         <v>460</v>
       </c>
@@ -27339,7 +27339,7 @@
       <c r="AN127" s="81"/>
       <c r="AO127" s="81"/>
     </row>
-    <row r="128" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A128" s="22" t="s">
         <v>462</v>
       </c>
@@ -27429,7 +27429,7 @@
       <c r="AN128" s="81"/>
       <c r="AO128" s="81"/>
     </row>
-    <row r="129" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A129" s="15" t="s">
         <v>465</v>
       </c>
@@ -27523,7 +27523,7 @@
       <c r="AN129" s="81"/>
       <c r="AO129" s="81"/>
     </row>
-    <row r="130" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A130" s="22" t="s">
         <v>467</v>
       </c>
@@ -27607,7 +27607,7 @@
       <c r="AN130" s="81"/>
       <c r="AO130" s="81"/>
     </row>
-    <row r="131" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A131" s="22" t="s">
         <v>468</v>
       </c>
@@ -27691,7 +27691,7 @@
       <c r="AN131" s="81"/>
       <c r="AO131" s="81"/>
     </row>
-    <row r="132" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A132" s="22" t="s">
         <v>469</v>
       </c>
@@ -27785,7 +27785,7 @@
       <c r="AN132" s="81"/>
       <c r="AO132" s="81"/>
     </row>
-    <row r="133" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A133" s="22" t="s">
         <v>471</v>
       </c>
@@ -27881,7 +27881,7 @@
       <c r="AN133" s="81"/>
       <c r="AO133" s="81"/>
     </row>
-    <row r="134" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A134" s="22" t="s">
         <v>473</v>
       </c>
@@ -27973,7 +27973,7 @@
       <c r="AN134" s="81"/>
       <c r="AO134" s="81"/>
     </row>
-    <row r="135" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A135" s="15" t="s">
         <v>475</v>
       </c>
@@ -28063,7 +28063,7 @@
       <c r="AN135" s="81"/>
       <c r="AO135" s="81"/>
     </row>
-    <row r="136" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A136" s="22" t="s">
         <v>477</v>
       </c>
@@ -28155,7 +28155,7 @@
       <c r="AN136" s="81"/>
       <c r="AO136" s="81"/>
     </row>
-    <row r="137" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A137" s="15" t="s">
         <v>479</v>
       </c>
@@ -28241,7 +28241,7 @@
       <c r="AN137" s="81"/>
       <c r="AO137" s="81"/>
     </row>
-    <row r="138" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A138" s="22" t="s">
         <v>481</v>
       </c>
@@ -28333,7 +28333,7 @@
       <c r="AN138" s="81"/>
       <c r="AO138" s="81"/>
     </row>
-    <row r="139" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A139" s="15" t="s">
         <v>482</v>
       </c>
@@ -28421,7 +28421,7 @@
       <c r="AN139" s="81"/>
       <c r="AO139" s="81"/>
     </row>
-    <row r="140" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A140" s="22" t="s">
         <v>485</v>
       </c>
@@ -28513,7 +28513,7 @@
       <c r="AN140" s="81"/>
       <c r="AO140" s="81"/>
     </row>
-    <row r="141" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A141" s="22" t="s">
         <v>488</v>
       </c>
@@ -28599,7 +28599,7 @@
       <c r="AN141" s="81"/>
       <c r="AO141" s="81"/>
     </row>
-    <row r="142" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A142" s="15" t="s">
         <v>489</v>
       </c>
@@ -28691,7 +28691,7 @@
       <c r="AN142" s="81"/>
       <c r="AO142" s="81"/>
     </row>
-    <row r="143" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A143" s="15" t="s">
         <v>491</v>
       </c>
@@ -28779,7 +28779,7 @@
       <c r="AN143" s="81"/>
       <c r="AO143" s="81"/>
     </row>
-    <row r="144" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A144" s="15" t="s">
         <v>494</v>
       </c>
@@ -28875,7 +28875,7 @@
       <c r="AN144" s="81"/>
       <c r="AO144" s="81"/>
     </row>
-    <row r="145" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A145" s="15" t="s">
         <v>496</v>
       </c>
@@ -28963,7 +28963,7 @@
       <c r="AN145" s="81"/>
       <c r="AO145" s="81"/>
     </row>
-    <row r="146" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A146" s="15" t="s">
         <v>497</v>
       </c>
@@ -29049,7 +29049,7 @@
       <c r="AN146" s="81"/>
       <c r="AO146" s="81"/>
     </row>
-    <row r="147" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A147" s="15" t="s">
         <v>498</v>
       </c>
@@ -29131,7 +29131,7 @@
       <c r="AN147" s="81"/>
       <c r="AO147" s="81"/>
     </row>
-    <row r="148" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A148" s="15" t="s">
         <v>499</v>
       </c>
@@ -29225,7 +29225,7 @@
       <c r="AN148" s="81"/>
       <c r="AO148" s="81"/>
     </row>
-    <row r="149" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A149" s="15" t="s">
         <v>501</v>
       </c>
@@ -29317,7 +29317,7 @@
       <c r="AN149" s="81"/>
       <c r="AO149" s="81"/>
     </row>
-    <row r="150" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A150" s="15" t="s">
         <v>503</v>
       </c>
@@ -29399,7 +29399,7 @@
       <c r="AN150" s="81"/>
       <c r="AO150" s="81"/>
     </row>
-    <row r="151" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A151" s="15" t="s">
         <v>504</v>
       </c>
@@ -29487,7 +29487,7 @@
       <c r="AN151" s="81"/>
       <c r="AO151" s="81"/>
     </row>
-    <row r="152" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A152" s="15" t="s">
         <v>506</v>
       </c>
@@ -29579,7 +29579,7 @@
       <c r="AN152" s="81"/>
       <c r="AO152" s="81"/>
     </row>
-    <row r="153" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A153" s="15" t="s">
         <v>509</v>
       </c>
@@ -29667,7 +29667,7 @@
       <c r="AN153" s="81"/>
       <c r="AO153" s="81"/>
     </row>
-    <row r="154" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A154" s="15" t="s">
         <v>511</v>
       </c>
@@ -29755,7 +29755,7 @@
       <c r="AN154" s="81"/>
       <c r="AO154" s="81"/>
     </row>
-    <row r="155" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A155" s="15" t="s">
         <v>513</v>
       </c>
@@ -29843,7 +29843,7 @@
       <c r="AN155" s="81"/>
       <c r="AO155" s="81"/>
     </row>
-    <row r="156" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A156" s="15" t="s">
         <v>515</v>
       </c>
@@ -29933,7 +29933,7 @@
       <c r="AN156" s="81"/>
       <c r="AO156" s="81"/>
     </row>
-    <row r="157" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A157" s="15" t="s">
         <v>518</v>
       </c>
@@ -30021,7 +30021,7 @@
       <c r="AN157" s="81"/>
       <c r="AO157" s="81"/>
     </row>
-    <row r="158" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A158" s="15" t="s">
         <v>520</v>
       </c>
@@ -30109,7 +30109,7 @@
       <c r="AN158" s="81"/>
       <c r="AO158" s="81"/>
     </row>
-    <row r="159" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A159" s="15" t="s">
         <v>522</v>
       </c>
@@ -30199,7 +30199,7 @@
       <c r="AN159" s="81"/>
       <c r="AO159" s="81"/>
     </row>
-    <row r="160" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A160" s="15" t="s">
         <v>524</v>
       </c>
@@ -30287,7 +30287,7 @@
       <c r="AN160" s="81"/>
       <c r="AO160" s="81"/>
     </row>
-    <row r="161" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A161" s="15" t="s">
         <v>526</v>
       </c>
@@ -30375,7 +30375,7 @@
       <c r="AN161" s="81"/>
       <c r="AO161" s="81"/>
     </row>
-    <row r="162" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A162" s="15" t="s">
         <v>528</v>
       </c>
@@ -30467,7 +30467,7 @@
       <c r="AN162" s="81"/>
       <c r="AO162" s="81"/>
     </row>
-    <row r="163" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A163" s="15" t="s">
         <v>531</v>
       </c>
@@ -30555,7 +30555,7 @@
       <c r="AN163" s="81"/>
       <c r="AO163" s="81"/>
     </row>
-    <row r="164" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A164" s="15" t="s">
         <v>533</v>
       </c>
@@ -30643,7 +30643,7 @@
       <c r="AN164" s="81"/>
       <c r="AO164" s="81"/>
     </row>
-    <row r="165" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A165" s="15" t="s">
         <v>535</v>
       </c>
@@ -30733,7 +30733,7 @@
       <c r="AN165" s="81"/>
       <c r="AO165" s="81"/>
     </row>
-    <row r="166" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A166" s="15" t="s">
         <v>537</v>
       </c>
@@ -30823,7 +30823,7 @@
       <c r="AN166" s="81"/>
       <c r="AO166" s="81"/>
     </row>
-    <row r="167" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A167" s="15" t="s">
         <v>539</v>
       </c>
@@ -30913,7 +30913,7 @@
       <c r="AN167" s="81"/>
       <c r="AO167" s="81"/>
     </row>
-    <row r="168" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A168" s="15" t="s">
         <v>541</v>
       </c>
@@ -31003,7 +31003,7 @@
       <c r="AN168" s="81"/>
       <c r="AO168" s="81"/>
     </row>
-    <row r="169" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A169" s="15" t="s">
         <v>543</v>
       </c>
@@ -31091,7 +31091,7 @@
       <c r="AN169" s="81"/>
       <c r="AO169" s="81"/>
     </row>
-    <row r="170" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A170" s="15" t="s">
         <v>545</v>
       </c>
@@ -31181,7 +31181,7 @@
       <c r="AN170" s="81"/>
       <c r="AO170" s="81"/>
     </row>
-    <row r="171" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A171" s="15" t="s">
         <v>547</v>
       </c>
@@ -31271,7 +31271,7 @@
       <c r="AN171" s="81"/>
       <c r="AO171" s="81"/>
     </row>
-    <row r="172" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A172" s="15" t="s">
         <v>549</v>
       </c>
@@ -31359,7 +31359,7 @@
       <c r="AN172" s="81"/>
       <c r="AO172" s="81"/>
     </row>
-    <row r="173" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A173" s="15" t="s">
         <v>551</v>
       </c>
@@ -31449,7 +31449,7 @@
       <c r="AN173" s="81"/>
       <c r="AO173" s="81"/>
     </row>
-    <row r="174" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A174" s="15" t="s">
         <v>553</v>
       </c>
@@ -31539,7 +31539,7 @@
       <c r="AN174" s="81"/>
       <c r="AO174" s="81"/>
     </row>
-    <row r="175" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A175" s="15" t="s">
         <v>555</v>
       </c>
@@ -31613,7 +31613,7 @@
       <c r="AN175" s="81"/>
       <c r="AO175" s="81"/>
     </row>
-    <row r="176" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A176" s="15" t="s">
         <v>556</v>
       </c>
@@ -31701,7 +31701,7 @@
       <c r="AN176" s="81"/>
       <c r="AO176" s="81"/>
     </row>
-    <row r="177" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A177" s="15" t="s">
         <v>559</v>
       </c>
@@ -31787,7 +31787,7 @@
       <c r="AN177" s="81"/>
       <c r="AO177" s="81"/>
     </row>
-    <row r="178" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A178" s="15" t="s">
         <v>561</v>
       </c>
@@ -31879,7 +31879,7 @@
       <c r="AN178" s="81"/>
       <c r="AO178" s="81"/>
     </row>
-    <row r="179" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A179" s="15" t="s">
         <v>562</v>
       </c>
@@ -31967,7 +31967,7 @@
       <c r="AN179" s="81"/>
       <c r="AO179" s="81"/>
     </row>
-    <row r="180" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A180" s="15" t="s">
         <v>566</v>
       </c>
@@ -32085,7 +32085,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="181" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A181" s="15" t="s">
         <v>571</v>
       </c>
@@ -32203,7 +32203,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="182" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A182" s="15" t="s">
         <v>576</v>
       </c>
@@ -32295,7 +32295,7 @@
       <c r="AN182" s="81"/>
       <c r="AO182" s="81"/>
     </row>
-    <row r="183" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A183" s="15" t="s">
         <v>578</v>
       </c>
@@ -32385,7 +32385,7 @@
       <c r="AN183" s="81"/>
       <c r="AO183" s="81"/>
     </row>
-    <row r="184" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A184" s="15" t="s">
         <v>579</v>
       </c>
@@ -32475,7 +32475,7 @@
       <c r="AN184" s="81"/>
       <c r="AO184" s="81"/>
     </row>
-    <row r="185" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A185" s="15" t="s">
         <v>581</v>
       </c>
@@ -32563,7 +32563,7 @@
       <c r="AN185" s="81"/>
       <c r="AO185" s="81"/>
     </row>
-    <row r="186" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A186" s="15" t="s">
         <v>584</v>
       </c>
@@ -32651,7 +32651,7 @@
       <c r="AN186" s="81"/>
       <c r="AO186" s="81"/>
     </row>
-    <row r="187" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A187" s="15" t="s">
         <v>586</v>
       </c>
@@ -32739,7 +32739,7 @@
       <c r="AN187" s="81"/>
       <c r="AO187" s="81"/>
     </row>
-    <row r="188" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A188" s="15" t="s">
         <v>589</v>
       </c>
@@ -32827,7 +32827,7 @@
       <c r="AN188" s="81"/>
       <c r="AO188" s="81"/>
     </row>
-    <row r="189" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A189" s="15" t="s">
         <v>592</v>
       </c>
@@ -32915,7 +32915,7 @@
       <c r="AN189" s="81"/>
       <c r="AO189" s="81"/>
     </row>
-    <row r="190" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A190" s="15" t="s">
         <v>594</v>
       </c>
@@ -33003,7 +33003,7 @@
       <c r="AN190" s="81"/>
       <c r="AO190" s="81"/>
     </row>
-    <row r="191" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A191" s="15" t="s">
         <v>596</v>
       </c>
@@ -33085,7 +33085,7 @@
       <c r="AN191" s="81"/>
       <c r="AO191" s="81"/>
     </row>
-    <row r="192" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A192" s="15" t="s">
         <v>598</v>
       </c>
@@ -33173,7 +33173,7 @@
       <c r="AN192" s="81"/>
       <c r="AO192" s="81"/>
     </row>
-    <row r="193" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A193" s="15" t="s">
         <v>600</v>
       </c>
@@ -33263,7 +33263,7 @@
       <c r="AN193" s="81"/>
       <c r="AO193" s="81"/>
     </row>
-    <row r="194" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A194" s="15" t="s">
         <v>603</v>
       </c>
@@ -33351,7 +33351,7 @@
       <c r="AN194" s="81"/>
       <c r="AO194" s="81"/>
     </row>
-    <row r="195" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A195" s="15" t="s">
         <v>606</v>
       </c>
@@ -33439,7 +33439,7 @@
       <c r="AN195" s="81"/>
       <c r="AO195" s="81"/>
     </row>
-    <row r="196" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A196" s="15" t="s">
         <v>609</v>
       </c>
@@ -33529,7 +33529,7 @@
       <c r="AN196" s="81"/>
       <c r="AO196" s="81"/>
     </row>
-    <row r="197" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A197" s="15" t="s">
         <v>613</v>
       </c>
@@ -33619,7 +33619,7 @@
       <c r="AN197" s="81"/>
       <c r="AO197" s="81"/>
     </row>
-    <row r="198" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A198" s="15" t="s">
         <v>615</v>
       </c>
@@ -33709,7 +33709,7 @@
       <c r="AN198" s="81"/>
       <c r="AO198" s="81"/>
     </row>
-    <row r="199" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A199" s="15" t="s">
         <v>617</v>
       </c>
@@ -33797,7 +33797,7 @@
       <c r="AN199" s="81"/>
       <c r="AO199" s="81"/>
     </row>
-    <row r="200" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A200" s="15" t="s">
         <v>619</v>
       </c>
@@ -33885,7 +33885,7 @@
       <c r="AN200" s="81"/>
       <c r="AO200" s="81"/>
     </row>
-    <row r="201" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A201" s="15" t="s">
         <v>621</v>
       </c>
@@ -33973,7 +33973,7 @@
       <c r="AN201" s="81"/>
       <c r="AO201" s="81"/>
     </row>
-    <row r="202" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A202" s="15" t="s">
         <v>624</v>
       </c>
@@ -34065,7 +34065,7 @@
       <c r="AN202" s="81"/>
       <c r="AO202" s="81"/>
     </row>
-    <row r="203" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A203" s="15" t="s">
         <v>625</v>
       </c>
@@ -34153,7 +34153,7 @@
       <c r="AN203" s="81"/>
       <c r="AO203" s="81"/>
     </row>
-    <row r="204" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A204" s="15" t="s">
         <v>626</v>
       </c>
@@ -34241,7 +34241,7 @@
       <c r="AN204" s="81"/>
       <c r="AO204" s="81"/>
     </row>
-    <row r="205" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A205" s="15" t="s">
         <v>628</v>
       </c>
@@ -34331,7 +34331,7 @@
       <c r="AN205" s="81"/>
       <c r="AO205" s="81"/>
     </row>
-    <row r="206" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A206" s="15" t="s">
         <v>629</v>
       </c>
@@ -34425,7 +34425,7 @@
       <c r="AN206" s="81"/>
       <c r="AO206" s="81"/>
     </row>
-    <row r="207" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A207" s="15" t="s">
         <v>630</v>
       </c>
@@ -34513,7 +34513,7 @@
       <c r="AN207" s="81"/>
       <c r="AO207" s="81"/>
     </row>
-    <row r="208" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A208" s="15" t="s">
         <v>633</v>
       </c>
@@ -34603,7 +34603,7 @@
       <c r="AN208" s="81"/>
       <c r="AO208" s="81"/>
     </row>
-    <row r="209" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A209" s="15" t="s">
         <v>635</v>
       </c>
@@ -34691,7 +34691,7 @@
       <c r="AN209" s="81"/>
       <c r="AO209" s="81"/>
     </row>
-    <row r="210" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A210" s="15" t="s">
         <v>637</v>
       </c>
@@ -34779,7 +34779,7 @@
       <c r="AN210" s="81"/>
       <c r="AO210" s="81"/>
     </row>
-    <row r="211" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A211" s="15" t="s">
         <v>639</v>
       </c>
@@ -34867,7 +34867,7 @@
       <c r="AN211" s="81"/>
       <c r="AO211" s="81"/>
     </row>
-    <row r="212" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A212" s="15" t="s">
         <v>641</v>
       </c>
@@ -34957,7 +34957,7 @@
       <c r="AN212" s="81"/>
       <c r="AO212" s="81"/>
     </row>
-    <row r="213" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A213" s="15" t="s">
         <v>643</v>
       </c>
@@ -35045,7 +35045,7 @@
       <c r="AN213" s="81"/>
       <c r="AO213" s="81"/>
     </row>
-    <row r="214" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A214" s="15" t="s">
         <v>645</v>
       </c>
@@ -35133,7 +35133,7 @@
       <c r="AN214" s="81"/>
       <c r="AO214" s="81"/>
     </row>
-    <row r="215" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A215" s="15" t="s">
         <v>648</v>
       </c>
@@ -35223,7 +35223,7 @@
       <c r="AN215" s="81"/>
       <c r="AO215" s="81"/>
     </row>
-    <row r="216" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A216" s="15" t="s">
         <v>651</v>
       </c>
@@ -35309,7 +35309,7 @@
       <c r="AN216" s="81"/>
       <c r="AO216" s="81"/>
     </row>
-    <row r="217" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A217" s="15" t="s">
         <v>653</v>
       </c>
@@ -35397,7 +35397,7 @@
       <c r="AN217" s="81"/>
       <c r="AO217" s="81"/>
     </row>
-    <row r="218" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A218" s="15" t="s">
         <v>656</v>
       </c>
@@ -35483,7 +35483,7 @@
       <c r="AN218" s="81"/>
       <c r="AO218" s="81"/>
     </row>
-    <row r="219" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A219" s="15" t="s">
         <v>658</v>
       </c>
@@ -35569,7 +35569,7 @@
       <c r="AN219" s="81"/>
       <c r="AO219" s="81"/>
     </row>
-    <row r="220" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A220" s="15" t="s">
         <v>660</v>
       </c>
@@ -35651,7 +35651,7 @@
       <c r="AN220" s="81"/>
       <c r="AO220" s="81"/>
     </row>
-    <row r="221" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A221" s="15" t="s">
         <v>661</v>
       </c>
@@ -35737,7 +35737,7 @@
       <c r="AN221" s="81"/>
       <c r="AO221" s="81"/>
     </row>
-    <row r="222" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A222" s="15" t="s">
         <v>664</v>
       </c>
@@ -35823,7 +35823,7 @@
       <c r="AN222" s="81"/>
       <c r="AO222" s="81"/>
     </row>
-    <row r="223" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A223" s="15" t="s">
         <v>667</v>
       </c>
@@ -35909,7 +35909,7 @@
       <c r="AN223" s="81"/>
       <c r="AO223" s="81"/>
     </row>
-    <row r="224" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A224" s="15" t="s">
         <v>669</v>
       </c>
@@ -35999,7 +35999,7 @@
       <c r="AN224" s="81"/>
       <c r="AO224" s="81"/>
     </row>
-    <row r="225" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A225" s="15" t="s">
         <v>671</v>
       </c>
@@ -36083,7 +36083,7 @@
       <c r="AN225" s="81"/>
       <c r="AO225" s="81"/>
     </row>
-    <row r="226" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A226" s="15" t="s">
         <v>673</v>
       </c>
@@ -36171,7 +36171,7 @@
       <c r="AN226" s="81"/>
       <c r="AO226" s="81"/>
     </row>
-    <row r="227" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A227" s="15" t="s">
         <v>675</v>
       </c>
@@ -36259,7 +36259,7 @@
       <c r="AN227" s="81"/>
       <c r="AO227" s="81"/>
     </row>
-    <row r="228" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A228" s="15" t="s">
         <v>678</v>
       </c>
@@ -36345,7 +36345,7 @@
       <c r="AN228" s="81"/>
       <c r="AO228" s="81"/>
     </row>
-    <row r="229" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A229" s="15" t="s">
         <v>680</v>
       </c>
@@ -36429,7 +36429,7 @@
       <c r="AN229" s="81"/>
       <c r="AO229" s="81"/>
     </row>
-    <row r="230" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A230" s="15" t="s">
         <v>681</v>
       </c>
@@ -36515,7 +36515,7 @@
       <c r="AN230" s="81"/>
       <c r="AO230" s="81"/>
     </row>
-    <row r="231" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A231" s="15" t="s">
         <v>683</v>
       </c>
@@ -36601,7 +36601,7 @@
       <c r="AN231" s="81"/>
       <c r="AO231" s="81"/>
     </row>
-    <row r="232" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A232" s="15" t="s">
         <v>685</v>
       </c>
@@ -36683,7 +36683,7 @@
       <c r="AN232" s="81"/>
       <c r="AO232" s="81"/>
     </row>
-    <row r="233" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A233" s="15" t="s">
         <v>686</v>
       </c>
@@ -36769,7 +36769,7 @@
       <c r="AN233" s="81"/>
       <c r="AO233" s="81"/>
     </row>
-    <row r="234" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A234" s="15" t="s">
         <v>688</v>
       </c>
@@ -36859,7 +36859,7 @@
       <c r="AN234" s="81"/>
       <c r="AO234" s="81"/>
     </row>
-    <row r="235" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A235" s="15" t="s">
         <v>689</v>
       </c>
@@ -36947,7 +36947,7 @@
       <c r="AN235" s="81"/>
       <c r="AO235" s="81"/>
     </row>
-    <row r="236" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A236" s="15" t="s">
         <v>692</v>
       </c>
@@ -37035,7 +37035,7 @@
       <c r="AN236" s="81"/>
       <c r="AO236" s="81"/>
     </row>
-    <row r="237" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A237" s="15" t="s">
         <v>694</v>
       </c>
@@ -37123,7 +37123,7 @@
       <c r="AN237" s="81"/>
       <c r="AO237" s="81"/>
     </row>
-    <row r="238" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A238" s="15" t="s">
         <v>697</v>
       </c>
@@ -37215,7 +37215,7 @@
       <c r="AN238" s="81"/>
       <c r="AO238" s="81"/>
     </row>
-    <row r="239" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A239" s="15" t="s">
         <v>700</v>
       </c>
@@ -37307,7 +37307,7 @@
       <c r="AN239" s="81"/>
       <c r="AO239" s="81"/>
     </row>
-    <row r="240" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A240" s="15" t="s">
         <v>702</v>
       </c>
@@ -37399,7 +37399,7 @@
       <c r="AN240" s="81"/>
       <c r="AO240" s="81"/>
     </row>
-    <row r="241" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A241" s="15" t="s">
         <v>704</v>
       </c>
@@ -37489,7 +37489,7 @@
       <c r="AN241" s="81"/>
       <c r="AO241" s="81"/>
     </row>
-    <row r="242" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A242" s="15" t="s">
         <v>706</v>
       </c>
@@ -37577,7 +37577,7 @@
       <c r="AN242" s="81"/>
       <c r="AO242" s="81"/>
     </row>
-    <row r="243" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A243" s="15" t="s">
         <v>708</v>
       </c>
@@ -37671,7 +37671,7 @@
       <c r="AN243" s="81"/>
       <c r="AO243" s="81"/>
     </row>
-    <row r="244" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A244" s="15" t="s">
         <v>710</v>
       </c>
@@ -37759,7 +37759,7 @@
       <c r="AN244" s="81"/>
       <c r="AO244" s="81"/>
     </row>
-    <row r="245" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A245" s="15" t="s">
         <v>712</v>
       </c>
@@ -37845,7 +37845,7 @@
       <c r="AN245" s="81"/>
       <c r="AO245" s="81"/>
     </row>
-    <row r="246" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A246" s="15" t="s">
         <v>714</v>
       </c>
@@ -37933,7 +37933,7 @@
       <c r="AN246" s="81"/>
       <c r="AO246" s="81"/>
     </row>
-    <row r="247" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A247" s="15" t="s">
         <v>716</v>
       </c>
@@ -38021,7 +38021,7 @@
       <c r="AN247" s="81"/>
       <c r="AO247" s="81"/>
     </row>
-    <row r="248" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A248" s="15" t="s">
         <v>718</v>
       </c>
@@ -38109,7 +38109,7 @@
       <c r="AN248" s="81"/>
       <c r="AO248" s="81"/>
     </row>
-    <row r="249" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A249" s="15" t="s">
         <v>720</v>
       </c>
@@ -38197,7 +38197,7 @@
       <c r="AN249" s="81"/>
       <c r="AO249" s="81"/>
     </row>
-    <row r="250" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A250" s="15" t="s">
         <v>722</v>
       </c>
@@ -38287,7 +38287,7 @@
       <c r="AN250" s="81"/>
       <c r="AO250" s="81"/>
     </row>
-    <row r="251" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A251" s="15" t="s">
         <v>723</v>
       </c>
@@ -38373,7 +38373,7 @@
       <c r="AN251" s="81"/>
       <c r="AO251" s="81"/>
     </row>
-    <row r="252" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A252" s="15" t="s">
         <v>725</v>
       </c>
@@ -38459,7 +38459,7 @@
       <c r="AN252" s="81"/>
       <c r="AO252" s="81"/>
     </row>
-    <row r="253" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A253" s="15" t="s">
         <v>727</v>
       </c>
@@ -38545,7 +38545,7 @@
       <c r="AN253" s="81"/>
       <c r="AO253" s="81"/>
     </row>
-    <row r="254" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A254" s="15" t="s">
         <v>729</v>
       </c>
@@ -38631,7 +38631,7 @@
       <c r="AN254" s="81"/>
       <c r="AO254" s="81"/>
     </row>
-    <row r="255" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A255" s="15" t="s">
         <v>731</v>
       </c>
@@ -38719,7 +38719,7 @@
       <c r="AN255" s="81"/>
       <c r="AO255" s="81"/>
     </row>
-    <row r="256" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A256" s="15" t="s">
         <v>733</v>
       </c>
@@ -38809,7 +38809,7 @@
       <c r="AN256" s="81"/>
       <c r="AO256" s="81"/>
     </row>
-    <row r="257" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A257" s="15" t="s">
         <v>735</v>
       </c>
@@ -38897,7 +38897,7 @@
       <c r="AN257" s="81"/>
       <c r="AO257" s="81"/>
     </row>
-    <row r="258" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A258" s="15" t="s">
         <v>737</v>
       </c>
@@ -38985,7 +38985,7 @@
       <c r="AN258" s="81"/>
       <c r="AO258" s="81"/>
     </row>
-    <row r="259" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A259" s="15" t="s">
         <v>739</v>
       </c>
@@ -39073,7 +39073,7 @@
       <c r="AN259" s="81"/>
       <c r="AO259" s="81"/>
     </row>
-    <row r="260" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A260" s="15" t="s">
         <v>741</v>
       </c>
@@ -39159,7 +39159,7 @@
       <c r="AN260" s="81"/>
       <c r="AO260" s="81"/>
     </row>
-    <row r="261" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A261" s="15" t="s">
         <v>742</v>
       </c>
@@ -39241,7 +39241,7 @@
       <c r="AN261" s="81"/>
       <c r="AO261" s="81"/>
     </row>
-    <row r="262" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A262" s="15" t="s">
         <v>743</v>
       </c>
@@ -39323,7 +39323,7 @@
       <c r="AN262" s="81"/>
       <c r="AO262" s="81"/>
     </row>
-    <row r="263" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A263" s="15" t="s">
         <v>744</v>
       </c>
@@ -39401,7 +39401,7 @@
       <c r="AN263" s="81"/>
       <c r="AO263" s="81"/>
     </row>
-    <row r="264" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A264" s="15" t="s">
         <v>746</v>
       </c>
@@ -39483,7 +39483,7 @@
       <c r="AN264" s="81"/>
       <c r="AO264" s="81"/>
     </row>
-    <row r="265" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A265" s="15" t="s">
         <v>747</v>
       </c>
@@ -39561,7 +39561,7 @@
       <c r="AN265" s="81"/>
       <c r="AO265" s="81"/>
     </row>
-    <row r="266" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A266" s="15" t="s">
         <v>748</v>
       </c>
@@ -39643,7 +39643,7 @@
       <c r="AN266" s="81"/>
       <c r="AO266" s="81"/>
     </row>
-    <row r="267" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A267" s="15" t="s">
         <v>749</v>
       </c>
@@ -39727,7 +39727,7 @@
       <c r="AN267" s="81"/>
       <c r="AO267" s="81"/>
     </row>
-    <row r="268" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A268" s="15" t="s">
         <v>750</v>
       </c>
@@ -39809,7 +39809,7 @@
       <c r="AN268" s="81"/>
       <c r="AO268" s="81"/>
     </row>
-    <row r="269" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A269" s="15" t="s">
         <v>752</v>
       </c>
@@ -39891,7 +39891,7 @@
       <c r="AN269" s="81"/>
       <c r="AO269" s="81"/>
     </row>
-    <row r="270" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A270" s="15" t="s">
         <v>753</v>
       </c>
@@ -39973,7 +39973,7 @@
       <c r="AN270" s="81"/>
       <c r="AO270" s="81"/>
     </row>
-    <row r="271" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A271" s="15" t="s">
         <v>754</v>
       </c>
@@ -40055,7 +40055,7 @@
       <c r="AN271" s="81"/>
       <c r="AO271" s="81"/>
     </row>
-    <row r="272" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A272" s="31" t="s">
         <v>755</v>
       </c>
@@ -40137,7 +40137,7 @@
       <c r="AN272" s="81"/>
       <c r="AO272" s="81"/>
     </row>
-    <row r="273" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A273" s="15" t="s">
         <v>756</v>
       </c>
@@ -40221,7 +40221,7 @@
       <c r="AN273" s="81"/>
       <c r="AO273" s="81"/>
     </row>
-    <row r="274" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A274" s="15" t="s">
         <v>757</v>
       </c>
@@ -40303,7 +40303,7 @@
       <c r="AN274" s="81"/>
       <c r="AO274" s="81"/>
     </row>
-    <row r="275" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A275" s="15" t="s">
         <v>758</v>
       </c>
@@ -40385,7 +40385,7 @@
       <c r="AN275" s="81"/>
       <c r="AO275" s="81"/>
     </row>
-    <row r="276" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A276" s="15" t="s">
         <v>759</v>
       </c>
@@ -40467,7 +40467,7 @@
       <c r="AN276" s="81"/>
       <c r="AO276" s="81"/>
     </row>
-    <row r="277" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A277" s="15" t="s">
         <v>760</v>
       </c>
@@ -40549,7 +40549,7 @@
       <c r="AN277" s="81"/>
       <c r="AO277" s="81"/>
     </row>
-    <row r="278" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A278" s="15" t="s">
         <v>761</v>
       </c>
@@ -40631,7 +40631,7 @@
       <c r="AN278" s="81"/>
       <c r="AO278" s="81"/>
     </row>
-    <row r="279" spans="1:41" s="26" customFormat="1" ht="20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="22" t="s">
         <v>762</v>
       </c>
@@ -40752,7 +40752,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="280" spans="1:41" s="26" customFormat="1" ht="20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" s="22" t="s">
         <v>772</v>
       </c>
@@ -40870,7 +40870,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="281" spans="1:41" s="26" customFormat="1" ht="120" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:41" s="26" customFormat="1" ht="122.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" s="22" t="s">
         <v>774</v>
       </c>
@@ -40990,7 +40990,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="282" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" s="22" t="s">
         <v>782</v>
       </c>
@@ -41110,7 +41110,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="283" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" s="22" t="s">
         <v>576</v>
       </c>
@@ -41228,7 +41228,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="284" spans="1:41" s="26" customFormat="1" ht="80" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:41" s="26" customFormat="1" ht="81.599999999999994" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" s="22" t="s">
         <v>792</v>
       </c>
@@ -41342,7 +41342,7 @@
       <c r="AN284" s="81"/>
       <c r="AO284" s="81"/>
     </row>
-    <row r="285" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" s="22" t="s">
         <v>796</v>
       </c>
@@ -41462,7 +41462,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="286" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" s="22" t="s">
         <v>800</v>
       </c>
@@ -41582,7 +41582,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="287" spans="1:41" s="26" customFormat="1" ht="20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="22" t="s">
         <v>803</v>
       </c>
@@ -41696,7 +41696,7 @@
       <c r="AN287" s="81"/>
       <c r="AO287" s="81"/>
     </row>
-    <row r="288" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" s="22" t="s">
         <v>805</v>
       </c>
@@ -41816,7 +41816,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="289" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" s="22" t="s">
         <v>808</v>
       </c>
@@ -41930,7 +41930,7 @@
       <c r="AN289" s="81"/>
       <c r="AO289" s="81"/>
     </row>
-    <row r="290" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" s="22" t="s">
         <v>221</v>
       </c>
@@ -42028,7 +42028,7 @@
       <c r="AN290" s="81"/>
       <c r="AO290" s="81"/>
     </row>
-    <row r="291" spans="1:41" s="26" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:41" s="26" customFormat="1" ht="30.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" s="22" t="s">
         <v>816</v>
       </c>
@@ -42146,7 +42146,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="292" spans="1:41" s="26" customFormat="1" ht="40" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:41" s="26" customFormat="1" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" s="22" t="s">
         <v>821</v>
       </c>
@@ -42262,7 +42262,7 @@
       <c r="AN292" s="81"/>
       <c r="AO292" s="81"/>
     </row>
-    <row r="293" spans="1:41" s="26" customFormat="1" ht="40" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:41" s="26" customFormat="1" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" s="22" t="s">
         <v>824</v>
       </c>
@@ -42376,7 +42376,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="294" spans="1:41" s="26" customFormat="1" ht="40" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:41" s="26" customFormat="1" ht="40.799999999999997" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="22" t="s">
         <v>827</v>
       </c>
@@ -42492,7 +42492,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="295" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="22" t="s">
         <v>829</v>
       </c>
@@ -42598,7 +42598,7 @@
       <c r="AN295" s="81"/>
       <c r="AO295" s="81"/>
     </row>
-    <row r="296" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="22" t="s">
         <v>833</v>
       </c>
@@ -42690,7 +42690,7 @@
       <c r="AN296" s="81"/>
       <c r="AO296" s="81"/>
     </row>
-    <row r="297" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="22" t="s">
         <v>742</v>
       </c>
@@ -42780,7 +42780,7 @@
       <c r="AN297" s="81"/>
       <c r="AO297" s="81"/>
     </row>
-    <row r="298" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="22" t="s">
         <v>162</v>
       </c>
@@ -42870,7 +42870,7 @@
       <c r="AN298" s="81"/>
       <c r="AO298" s="81"/>
     </row>
-    <row r="299" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="22" t="s">
         <v>839</v>
       </c>
@@ -42962,7 +42962,7 @@
       <c r="AN299" s="81"/>
       <c r="AO299" s="81"/>
     </row>
-    <row r="300" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="22" t="s">
         <v>840</v>
       </c>
@@ -43052,7 +43052,7 @@
       <c r="AN300" s="81"/>
       <c r="AO300" s="81"/>
     </row>
-    <row r="301" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="22" t="s">
         <v>405</v>
       </c>
@@ -43144,7 +43144,7 @@
       <c r="AN301" s="81"/>
       <c r="AO301" s="81"/>
     </row>
-    <row r="302" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="22" t="s">
         <v>280</v>
       </c>
@@ -43234,7 +43234,7 @@
       <c r="AN302" s="81"/>
       <c r="AO302" s="81"/>
     </row>
-    <row r="303" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="22" t="s">
         <v>847</v>
       </c>
@@ -43326,7 +43326,7 @@
       <c r="AN303" s="81"/>
       <c r="AO303" s="81"/>
     </row>
-    <row r="304" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="22" t="s">
         <v>850</v>
       </c>
@@ -43418,7 +43418,7 @@
       <c r="AN304" s="81"/>
       <c r="AO304" s="81"/>
     </row>
-    <row r="305" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="22" t="s">
         <v>54</v>
       </c>
@@ -43510,7 +43510,7 @@
       <c r="AN305" s="81"/>
       <c r="AO305" s="81"/>
     </row>
-    <row r="306" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="22" t="s">
         <v>854</v>
       </c>
@@ -43594,7 +43594,7 @@
       <c r="AN306" s="81"/>
       <c r="AO306" s="81"/>
     </row>
-    <row r="307" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="22" t="s">
         <v>856</v>
       </c>
@@ -43686,7 +43686,7 @@
       <c r="AN307" s="81"/>
       <c r="AO307" s="81"/>
     </row>
-    <row r="308" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="22" t="s">
         <v>858</v>
       </c>
@@ -43776,7 +43776,7 @@
       <c r="AN308" s="81"/>
       <c r="AO308" s="81"/>
     </row>
-    <row r="309" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="22" t="s">
         <v>859</v>
       </c>
@@ -43868,7 +43868,7 @@
       <c r="AN309" s="81"/>
       <c r="AO309" s="81"/>
     </row>
-    <row r="310" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" s="22" t="s">
         <v>664</v>
       </c>
@@ -43954,7 +43954,7 @@
       <c r="AN310" s="81"/>
       <c r="AO310" s="81"/>
     </row>
-    <row r="311" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" s="22" t="s">
         <v>753</v>
       </c>
@@ -44046,7 +44046,7 @@
       <c r="AN311" s="81"/>
       <c r="AO311" s="81"/>
     </row>
-    <row r="312" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" s="22" t="s">
         <v>120</v>
       </c>
@@ -44136,7 +44136,7 @@
       <c r="AN312" s="81"/>
       <c r="AO312" s="81"/>
     </row>
-    <row r="313" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" s="22">
         <v>98451</v>
       </c>
@@ -44210,7 +44210,7 @@
       <c r="AN313" s="81"/>
       <c r="AO313" s="81"/>
     </row>
-    <row r="314" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="22" t="s">
         <v>865</v>
       </c>
@@ -44306,7 +44306,7 @@
       <c r="AN314" s="81"/>
       <c r="AO314" s="81"/>
     </row>
-    <row r="315" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" s="22" t="s">
         <v>868</v>
       </c>
@@ -44398,7 +44398,7 @@
       <c r="AN315" s="81"/>
       <c r="AO315" s="81"/>
     </row>
-    <row r="316" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" s="3" t="s">
         <v>870</v>
       </c>
@@ -44486,7 +44486,7 @@
       <c r="AN316" s="81"/>
       <c r="AO316" s="81"/>
     </row>
-    <row r="317" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" s="22" t="s">
         <v>658</v>
       </c>
@@ -44572,7 +44572,7 @@
       <c r="AN317" s="81"/>
       <c r="AO317" s="81"/>
     </row>
-    <row r="318" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="22" t="s">
         <v>873</v>
       </c>
@@ -44664,7 +44664,7 @@
       <c r="AN318" s="81"/>
       <c r="AO318" s="81"/>
     </row>
-    <row r="319" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="22" t="s">
         <v>875</v>
       </c>
@@ -44760,7 +44760,7 @@
       <c r="AN319" s="81"/>
       <c r="AO319" s="81"/>
     </row>
-    <row r="320" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="22" t="s">
         <v>339</v>
       </c>
@@ -44850,7 +44850,7 @@
       <c r="AN320" s="81"/>
       <c r="AO320" s="81"/>
     </row>
-    <row r="321" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" s="22" t="s">
         <v>877</v>
       </c>
@@ -44932,7 +44932,7 @@
       <c r="AN321" s="81"/>
       <c r="AO321" s="81"/>
     </row>
-    <row r="322" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" s="3" t="s">
         <v>879</v>
       </c>
@@ -45020,7 +45020,7 @@
       <c r="AN322" s="81"/>
       <c r="AO322" s="81"/>
     </row>
-    <row r="323" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" s="22" t="s">
         <v>880</v>
       </c>
@@ -45108,7 +45108,7 @@
       <c r="AN323" s="81"/>
       <c r="AO323" s="81"/>
     </row>
-    <row r="324" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="22" t="s">
         <v>881</v>
       </c>
@@ -45192,7 +45192,7 @@
       <c r="AN324" s="81"/>
       <c r="AO324" s="81"/>
     </row>
-    <row r="325" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="22" t="s">
         <v>136</v>
       </c>
@@ -45282,7 +45282,7 @@
       <c r="AN325" s="81"/>
       <c r="AO325" s="81"/>
     </row>
-    <row r="326" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="3" t="s">
         <v>885</v>
       </c>
@@ -45372,7 +45372,7 @@
       <c r="AN326" s="81"/>
       <c r="AO326" s="81"/>
     </row>
-    <row r="327" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="22" t="s">
         <v>660</v>
       </c>
@@ -45458,7 +45458,7 @@
       <c r="AN327" s="81"/>
       <c r="AO327" s="81"/>
     </row>
-    <row r="328" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" s="3" t="s">
         <v>887</v>
       </c>
@@ -45546,7 +45546,7 @@
       <c r="AN328" s="81"/>
       <c r="AO328" s="81"/>
     </row>
-    <row r="329" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
         <v>888</v>
       </c>
@@ -45634,7 +45634,7 @@
       <c r="AN329" s="81"/>
       <c r="AO329" s="81"/>
     </row>
-    <row r="330" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" s="3" t="s">
         <v>889</v>
       </c>
@@ -45722,7 +45722,7 @@
       <c r="AN330" s="81"/>
       <c r="AO330" s="81"/>
     </row>
-    <row r="331" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
         <v>891</v>
       </c>
@@ -45806,7 +45806,7 @@
       <c r="AN331" s="81"/>
       <c r="AO331" s="81"/>
     </row>
-    <row r="332" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="3" t="s">
         <v>894</v>
       </c>
@@ -45890,7 +45890,7 @@
       <c r="AN332" s="81"/>
       <c r="AO332" s="81"/>
     </row>
-    <row r="333" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
         <v>897</v>
       </c>
@@ -45978,7 +45978,7 @@
       <c r="AN333" s="81"/>
       <c r="AO333" s="81"/>
     </row>
-    <row r="334" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" s="22" t="s">
         <v>898</v>
       </c>
@@ -46070,7 +46070,7 @@
       <c r="AN334" s="81"/>
       <c r="AO334" s="81"/>
     </row>
-    <row r="335" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" s="22" t="s">
         <v>901</v>
       </c>
@@ -46154,7 +46154,7 @@
       <c r="AN335" s="81"/>
       <c r="AO335" s="81"/>
     </row>
-    <row r="336" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="3" t="s">
         <v>289</v>
       </c>
@@ -46232,7 +46232,7 @@
       <c r="AN336" s="81"/>
       <c r="AO336" s="81"/>
     </row>
-    <row r="337" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="22" t="s">
         <v>903</v>
       </c>
@@ -46324,7 +46324,7 @@
       <c r="AN337" s="81"/>
       <c r="AO337" s="81"/>
     </row>
-    <row r="338" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="3" t="s">
         <v>678</v>
       </c>
@@ -46408,7 +46408,7 @@
       <c r="AN338" s="81"/>
       <c r="AO338" s="81"/>
     </row>
-    <row r="339" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="22" t="s">
         <v>906</v>
       </c>
@@ -46492,7 +46492,7 @@
       <c r="AN339" s="81"/>
       <c r="AO339" s="81"/>
     </row>
-    <row r="340" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="3" t="s">
         <v>909</v>
       </c>
@@ -46576,7 +46576,7 @@
       <c r="AN340" s="81"/>
       <c r="AO340" s="81"/>
     </row>
-    <row r="341" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" s="22" t="s">
         <v>911</v>
       </c>
@@ -46660,7 +46660,7 @@
       <c r="AN341" s="81"/>
       <c r="AO341" s="81"/>
     </row>
-    <row r="342" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="22" t="s">
         <v>913</v>
       </c>
@@ -46744,7 +46744,7 @@
       <c r="AN342" s="81"/>
       <c r="AO342" s="81"/>
     </row>
-    <row r="343" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
         <v>915</v>
       </c>
@@ -46834,7 +46834,7 @@
       <c r="AN343" s="81"/>
       <c r="AO343" s="81"/>
     </row>
-    <row r="344" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="22" t="s">
         <v>916</v>
       </c>
@@ -46922,7 +46922,7 @@
       <c r="AN344" s="81"/>
       <c r="AO344" s="81"/>
     </row>
-    <row r="345" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
         <v>918</v>
       </c>
@@ -47010,7 +47010,7 @@
       <c r="AN345" s="81"/>
       <c r="AO345" s="81"/>
     </row>
-    <row r="346" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="3" t="s">
         <v>669</v>
       </c>
@@ -47098,7 +47098,7 @@
       <c r="AN346" s="81"/>
       <c r="AO346" s="81"/>
     </row>
-    <row r="347" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="22" t="s">
         <v>920</v>
       </c>
@@ -47178,7 +47178,7 @@
       <c r="AN347" s="81"/>
       <c r="AO347" s="81"/>
     </row>
-    <row r="348" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="3" t="s">
         <v>923</v>
       </c>
@@ -47266,7 +47266,7 @@
       <c r="AN348" s="81"/>
       <c r="AO348" s="81"/>
     </row>
-    <row r="349" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="22" t="s">
         <v>924</v>
       </c>
@@ -47354,7 +47354,7 @@
       <c r="AN349" s="81"/>
       <c r="AO349" s="81"/>
     </row>
-    <row r="350" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="3" t="s">
         <v>926</v>
       </c>
@@ -47438,7 +47438,7 @@
       <c r="AN350" s="81"/>
       <c r="AO350" s="81"/>
     </row>
-    <row r="351" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="22" t="s">
         <v>928</v>
       </c>
@@ -47530,7 +47530,7 @@
       <c r="AN351" s="81"/>
       <c r="AO351" s="81"/>
     </row>
-    <row r="352" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="22" t="s">
         <v>929</v>
       </c>
@@ -47614,7 +47614,7 @@
       <c r="AN352" s="81"/>
       <c r="AO352" s="81"/>
     </row>
-    <row r="353" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
         <v>931</v>
       </c>
@@ -47702,7 +47702,7 @@
       <c r="AN353" s="81"/>
       <c r="AO353" s="81"/>
     </row>
-    <row r="354" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="3" t="s">
         <v>932</v>
       </c>
@@ -47786,7 +47786,7 @@
       <c r="AN354" s="81"/>
       <c r="AO354" s="81"/>
     </row>
-    <row r="355" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="22" t="s">
         <v>933</v>
       </c>
@@ -47878,7 +47878,7 @@
       <c r="AN355" s="81"/>
       <c r="AO355" s="81"/>
     </row>
-    <row r="356" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="3" t="s">
         <v>408</v>
       </c>
@@ -47962,7 +47962,7 @@
       <c r="AN356" s="81"/>
       <c r="AO356" s="81"/>
     </row>
-    <row r="357" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="22" t="s">
         <v>934</v>
       </c>
@@ -48046,7 +48046,7 @@
       <c r="AN357" s="81"/>
       <c r="AO357" s="81"/>
     </row>
-    <row r="358" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="22" t="s">
         <v>938</v>
       </c>
@@ -48130,7 +48130,7 @@
       <c r="AN358" s="81"/>
       <c r="AO358" s="81"/>
     </row>
-    <row r="359" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
         <v>939</v>
       </c>
@@ -48218,7 +48218,7 @@
       <c r="AN359" s="81"/>
       <c r="AO359" s="81"/>
     </row>
-    <row r="360" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="22" t="s">
         <v>940</v>
       </c>
@@ -48310,7 +48310,7 @@
       <c r="AN360" s="81"/>
       <c r="AO360" s="81"/>
     </row>
-    <row r="361" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
         <v>384</v>
       </c>
@@ -48394,7 +48394,7 @@
       <c r="AN361" s="81"/>
       <c r="AO361" s="81"/>
     </row>
-    <row r="362" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="3" t="s">
         <v>941</v>
       </c>
@@ -48482,7 +48482,7 @@
       <c r="AN362" s="81"/>
       <c r="AO362" s="81"/>
     </row>
-    <row r="363" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="22" t="s">
         <v>943</v>
       </c>
@@ -48566,7 +48566,7 @@
       <c r="AN363" s="81"/>
       <c r="AO363" s="81"/>
     </row>
-    <row r="364" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" s="3" t="s">
         <v>673</v>
       </c>
@@ -48650,7 +48650,7 @@
       <c r="AN364" s="81"/>
       <c r="AO364" s="81"/>
     </row>
-    <row r="365" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" s="22" t="s">
         <v>944</v>
       </c>
@@ -48734,7 +48734,7 @@
       <c r="AN365" s="81"/>
       <c r="AO365" s="81"/>
     </row>
-    <row r="366" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="3" t="s">
         <v>945</v>
       </c>
@@ -48818,7 +48818,7 @@
       <c r="AN366" s="81"/>
       <c r="AO366" s="81"/>
     </row>
-    <row r="367" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
         <v>754</v>
       </c>
@@ -48902,7 +48902,7 @@
       <c r="AN367" s="81"/>
       <c r="AO367" s="81"/>
     </row>
-    <row r="368" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="3" t="s">
         <v>688</v>
       </c>
@@ -48986,7 +48986,7 @@
       <c r="AN368" s="81"/>
       <c r="AO368" s="81"/>
     </row>
-    <row r="369" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
         <v>949</v>
       </c>
@@ -49070,7 +49070,7 @@
       <c r="AN369" s="81"/>
       <c r="AO369" s="81"/>
     </row>
-    <row r="370" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" s="22" t="s">
         <v>951</v>
       </c>
@@ -49154,7 +49154,7 @@
       <c r="AN370" s="81"/>
       <c r="AO370" s="81"/>
     </row>
-    <row r="371" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="22" t="s">
         <v>954</v>
       </c>
@@ -49238,7 +49238,7 @@
       <c r="AN371" s="81"/>
       <c r="AO371" s="81"/>
     </row>
-    <row r="372" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="22" t="s">
         <v>956</v>
       </c>
@@ -49322,7 +49322,7 @@
       <c r="AN372" s="81"/>
       <c r="AO372" s="81"/>
     </row>
-    <row r="373" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
         <v>957</v>
       </c>
@@ -49406,7 +49406,7 @@
       <c r="AN373" s="81"/>
       <c r="AO373" s="81"/>
     </row>
-    <row r="374" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" s="3" t="s">
         <v>959</v>
       </c>
@@ -49490,7 +49490,7 @@
       <c r="AN374" s="81"/>
       <c r="AO374" s="81"/>
     </row>
-    <row r="375" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="22" t="s">
         <v>960</v>
       </c>
@@ -49574,7 +49574,7 @@
       <c r="AN375" s="81"/>
       <c r="AO375" s="81"/>
     </row>
-    <row r="376" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="3" t="s">
         <v>961</v>
       </c>
@@ -49658,7 +49658,7 @@
       <c r="AN376" s="81"/>
       <c r="AO376" s="81"/>
     </row>
-    <row r="377" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="22" t="s">
         <v>962</v>
       </c>
@@ -49742,7 +49742,7 @@
       <c r="AN377" s="81"/>
       <c r="AO377" s="81"/>
     </row>
-    <row r="378" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="22" t="s">
         <v>964</v>
       </c>
@@ -49826,7 +49826,7 @@
       <c r="AN378" s="81"/>
       <c r="AO378" s="81"/>
     </row>
-    <row r="379" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="22" t="s">
         <v>967</v>
       </c>
@@ -49910,7 +49910,7 @@
       <c r="AN379" s="81"/>
       <c r="AO379" s="81"/>
     </row>
-    <row r="380" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="22" t="s">
         <v>969</v>
       </c>
@@ -49994,7 +49994,7 @@
       <c r="AN380" s="81"/>
       <c r="AO380" s="81"/>
     </row>
-    <row r="381" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="22" t="s">
         <v>973</v>
       </c>
@@ -50082,7 +50082,7 @@
       <c r="AN381" s="81"/>
       <c r="AO381" s="81"/>
     </row>
-    <row r="382" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="3" t="s">
         <v>975</v>
       </c>
@@ -50162,7 +50162,7 @@
       <c r="AN382" s="81"/>
       <c r="AO382" s="81"/>
     </row>
-    <row r="383" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" s="22" t="s">
         <v>977</v>
       </c>
@@ -50246,7 +50246,7 @@
       <c r="AN383" s="81"/>
       <c r="AO383" s="81"/>
     </row>
-    <row r="384" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" s="22" t="s">
         <v>337</v>
       </c>
@@ -50330,7 +50330,7 @@
       <c r="AN384" s="81"/>
       <c r="AO384" s="81"/>
     </row>
-    <row r="385" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
         <v>978</v>
       </c>
@@ -50418,7 +50418,7 @@
       <c r="AN385" s="81"/>
       <c r="AO385" s="81"/>
     </row>
-    <row r="386" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="22" t="s">
         <v>485</v>
       </c>
@@ -50502,7 +50502,7 @@
       <c r="AN386" s="81"/>
       <c r="AO386" s="81"/>
     </row>
-    <row r="387" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="22" t="s">
         <v>330</v>
       </c>
@@ -50586,7 +50586,7 @@
       <c r="AN387" s="81"/>
       <c r="AO387" s="81"/>
     </row>
-    <row r="388" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="3" t="s">
         <v>982</v>
       </c>
@@ -50670,7 +50670,7 @@
       <c r="AN388" s="81"/>
       <c r="AO388" s="81"/>
     </row>
-    <row r="389" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="22" t="s">
         <v>983</v>
       </c>
@@ -50762,7 +50762,7 @@
       <c r="AN389" s="81"/>
       <c r="AO389" s="81"/>
     </row>
-    <row r="390" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="22" t="s">
         <v>984</v>
       </c>
@@ -50854,7 +50854,7 @@
       <c r="AN390" s="81"/>
       <c r="AO390" s="81"/>
     </row>
-    <row r="391" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="22" t="s">
         <v>985</v>
       </c>
@@ -50938,7 +50938,7 @@
       <c r="AN391" s="81"/>
       <c r="AO391" s="81"/>
     </row>
-    <row r="392" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="22" t="s">
         <v>986</v>
       </c>
@@ -51022,7 +51022,7 @@
       <c r="AN392" s="81"/>
       <c r="AO392" s="81"/>
     </row>
-    <row r="393" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="22" t="s">
         <v>988</v>
       </c>
@@ -51114,7 +51114,7 @@
       <c r="AN393" s="81"/>
       <c r="AO393" s="81"/>
     </row>
-    <row r="394" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="22" t="s">
         <v>460</v>
       </c>
@@ -51198,7 +51198,7 @@
       <c r="AN394" s="81"/>
       <c r="AO394" s="81"/>
     </row>
-    <row r="395" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="22" t="s">
         <v>990</v>
       </c>
@@ -51290,7 +51290,7 @@
       <c r="AN395" s="81"/>
       <c r="AO395" s="81"/>
     </row>
-    <row r="396" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="22" t="s">
         <v>496</v>
       </c>
@@ -51374,7 +51374,7 @@
       <c r="AN396" s="81"/>
       <c r="AO396" s="81"/>
     </row>
-    <row r="397" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="22" t="s">
         <v>993</v>
       </c>
@@ -51458,7 +51458,7 @@
       <c r="AN397" s="81"/>
       <c r="AO397" s="81"/>
     </row>
-    <row r="398" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="22" t="s">
         <v>994</v>
       </c>
@@ -51542,7 +51542,7 @@
       <c r="AN398" s="81"/>
       <c r="AO398" s="81"/>
     </row>
-    <row r="399" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="22" t="s">
         <v>996</v>
       </c>
@@ -51626,7 +51626,7 @@
       <c r="AN399" s="81"/>
       <c r="AO399" s="81"/>
     </row>
-    <row r="400" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="3" t="s">
         <v>997</v>
       </c>
@@ -51710,7 +51710,7 @@
       <c r="AN400" s="81"/>
       <c r="AO400" s="81"/>
     </row>
-    <row r="401" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
         <v>998</v>
       </c>
@@ -51798,7 +51798,7 @@
       <c r="AN401" s="81"/>
       <c r="AO401" s="81"/>
     </row>
-    <row r="402" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="22" t="s">
         <v>999</v>
       </c>
@@ -51882,7 +51882,7 @@
       <c r="AN402" s="81"/>
       <c r="AO402" s="81"/>
     </row>
-    <row r="403" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="22" t="s">
         <v>1000</v>
       </c>
@@ -51966,7 +51966,7 @@
       <c r="AN403" s="81"/>
       <c r="AO403" s="81"/>
     </row>
-    <row r="404" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="22" t="s">
         <v>1003</v>
       </c>
@@ -52056,7 +52056,7 @@
       <c r="AN404" s="81"/>
       <c r="AO404" s="81"/>
     </row>
-    <row r="405" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="22" t="s">
         <v>1004</v>
       </c>
@@ -52148,7 +52148,7 @@
       <c r="AN405" s="81"/>
       <c r="AO405" s="81"/>
     </row>
-    <row r="406" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" s="3" t="s">
         <v>1006</v>
       </c>
@@ -52236,7 +52236,7 @@
       <c r="AN406" s="81"/>
       <c r="AO406" s="81"/>
     </row>
-    <row r="407" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" s="22" t="s">
         <v>1008</v>
       </c>
@@ -52328,7 +52328,7 @@
       <c r="AN407" s="81"/>
       <c r="AO407" s="81"/>
     </row>
-    <row r="408" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" s="22" t="s">
         <v>1010</v>
       </c>
@@ -52412,7 +52412,7 @@
       <c r="AN408" s="81"/>
       <c r="AO408" s="81"/>
     </row>
-    <row r="409" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="22" t="s">
         <v>1012</v>
       </c>
@@ -52496,7 +52496,7 @@
       <c r="AN409" s="81"/>
       <c r="AO409" s="81"/>
     </row>
-    <row r="410" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="22" t="s">
         <v>1014</v>
       </c>
@@ -52580,7 +52580,7 @@
       <c r="AN410" s="81"/>
       <c r="AO410" s="81"/>
     </row>
-    <row r="411" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="22" t="s">
         <v>428</v>
       </c>
@@ -52664,7 +52664,7 @@
       <c r="AN411" s="81"/>
       <c r="AO411" s="81"/>
     </row>
-    <row r="412" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" s="22" t="s">
         <v>1016</v>
       </c>
@@ -52748,7 +52748,7 @@
       <c r="AN412" s="81"/>
       <c r="AO412" s="81"/>
     </row>
-    <row r="413" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" s="22" t="s">
         <v>1017</v>
       </c>
@@ -52832,7 +52832,7 @@
       <c r="AN413" s="81"/>
       <c r="AO413" s="81"/>
     </row>
-    <row r="414" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" s="22" t="s">
         <v>1019</v>
       </c>
@@ -52916,7 +52916,7 @@
       <c r="AN414" s="81"/>
       <c r="AO414" s="81"/>
     </row>
-    <row r="415" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" s="22" t="s">
         <v>1021</v>
       </c>
@@ -53006,7 +53006,7 @@
       <c r="AN415" s="81"/>
       <c r="AO415" s="81"/>
     </row>
-    <row r="416" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" s="22" t="s">
         <v>1022</v>
       </c>
@@ -53098,7 +53098,7 @@
       <c r="AN416" s="81"/>
       <c r="AO416" s="81"/>
     </row>
-    <row r="417" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" s="22" t="s">
         <v>1023</v>
       </c>
@@ -53190,7 +53190,7 @@
       <c r="AN417" s="81"/>
       <c r="AO417" s="81"/>
     </row>
-    <row r="418" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="22" t="s">
         <v>1024</v>
       </c>
@@ -53280,7 +53280,7 @@
       <c r="AN418" s="81"/>
       <c r="AO418" s="81"/>
     </row>
-    <row r="419" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" s="22" t="s">
         <v>1025</v>
       </c>
@@ -53372,7 +53372,7 @@
       <c r="AN419" s="81"/>
       <c r="AO419" s="81"/>
     </row>
-    <row r="420" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" s="22" t="s">
         <v>1026</v>
       </c>
@@ -53456,7 +53456,7 @@
       <c r="AN420" s="81"/>
       <c r="AO420" s="81"/>
     </row>
-    <row r="421" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" s="22" t="s">
         <v>1028</v>
       </c>
@@ -53540,7 +53540,7 @@
       <c r="AN421" s="81"/>
       <c r="AO421" s="81"/>
     </row>
-    <row r="422" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" s="22" t="s">
         <v>1030</v>
       </c>
@@ -53624,7 +53624,7 @@
       <c r="AN422" s="81"/>
       <c r="AO422" s="81"/>
     </row>
-    <row r="423" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" s="22" t="s">
         <v>1032</v>
       </c>
@@ -53708,7 +53708,7 @@
       <c r="AN423" s="81"/>
       <c r="AO423" s="81"/>
     </row>
-    <row r="424" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" s="22" t="s">
         <v>1035</v>
       </c>
@@ -53792,7 +53792,7 @@
       <c r="AN424" s="81"/>
       <c r="AO424" s="81"/>
     </row>
-    <row r="425" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" s="22" t="s">
         <v>1037</v>
       </c>
@@ -53876,7 +53876,7 @@
       <c r="AN425" s="81"/>
       <c r="AO425" s="81"/>
     </row>
-    <row r="426" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="22" t="s">
         <v>1039</v>
       </c>
@@ -53960,7 +53960,7 @@
       <c r="AN426" s="81"/>
       <c r="AO426" s="81"/>
     </row>
-    <row r="427" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" s="22" t="s">
         <v>1040</v>
       </c>
@@ -54044,7 +54044,7 @@
       <c r="AN427" s="81"/>
       <c r="AO427" s="81"/>
     </row>
-    <row r="428" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" s="22" t="s">
         <v>1041</v>
       </c>
@@ -54128,7 +54128,7 @@
       <c r="AN428" s="81"/>
       <c r="AO428" s="81"/>
     </row>
-    <row r="429" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" s="22" t="s">
         <v>1043</v>
       </c>
@@ -54212,7 +54212,7 @@
       <c r="AN429" s="81"/>
       <c r="AO429" s="81"/>
     </row>
-    <row r="430" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" s="22" t="s">
         <v>1045</v>
       </c>
@@ -54296,7 +54296,7 @@
       <c r="AN430" s="81"/>
       <c r="AO430" s="81"/>
     </row>
-    <row r="431" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" s="22" t="s">
         <v>1047</v>
       </c>
@@ -54380,7 +54380,7 @@
       <c r="AN431" s="81"/>
       <c r="AO431" s="81"/>
     </row>
-    <row r="432" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" s="22" t="s">
         <v>656</v>
       </c>
@@ -54464,7 +54464,7 @@
       <c r="AN432" s="81"/>
       <c r="AO432" s="81"/>
     </row>
-    <row r="433" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="22" t="s">
         <v>1052</v>
       </c>
@@ -54548,7 +54548,7 @@
       <c r="AN433" s="81"/>
       <c r="AO433" s="81"/>
     </row>
-    <row r="434" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" s="22" t="s">
         <v>1054</v>
       </c>
@@ -54632,7 +54632,7 @@
       <c r="AN434" s="81"/>
       <c r="AO434" s="81"/>
     </row>
-    <row r="435" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" s="22" t="s">
         <v>1055</v>
       </c>
@@ -54716,7 +54716,7 @@
       <c r="AN435" s="81"/>
       <c r="AO435" s="81"/>
     </row>
-    <row r="436" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" s="22" t="s">
         <v>1057</v>
       </c>
@@ -54800,7 +54800,7 @@
       <c r="AN436" s="81"/>
       <c r="AO436" s="81"/>
     </row>
-    <row r="437" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" s="22" t="s">
         <v>1059</v>
       </c>
@@ -54884,7 +54884,7 @@
       <c r="AN437" s="81"/>
       <c r="AO437" s="81"/>
     </row>
-    <row r="438" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="22" t="s">
         <v>412</v>
       </c>
@@ -54968,7 +54968,7 @@
       <c r="AN438" s="81"/>
       <c r="AO438" s="81"/>
     </row>
-    <row r="439" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" s="22" t="s">
         <v>759</v>
       </c>
@@ -55052,7 +55052,7 @@
       <c r="AN439" s="81"/>
       <c r="AO439" s="81"/>
     </row>
-    <row r="440" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" s="22" t="s">
         <v>1064</v>
       </c>
@@ -55136,7 +55136,7 @@
       <c r="AN440" s="81"/>
       <c r="AO440" s="81"/>
     </row>
-    <row r="441" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" s="22" t="s">
         <v>1065</v>
       </c>
@@ -55220,7 +55220,7 @@
       <c r="AN441" s="81"/>
       <c r="AO441" s="81"/>
     </row>
-    <row r="442" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" s="22" t="s">
         <v>1066</v>
       </c>
@@ -55304,7 +55304,7 @@
       <c r="AN442" s="81"/>
       <c r="AO442" s="81"/>
     </row>
-    <row r="443" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" s="22" t="s">
         <v>1068</v>
       </c>
@@ -55388,7 +55388,7 @@
       <c r="AN443" s="81"/>
       <c r="AO443" s="81"/>
     </row>
-    <row r="444" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" s="22" t="s">
         <v>1070</v>
       </c>
@@ -55472,7 +55472,7 @@
       <c r="AN444" s="81"/>
       <c r="AO444" s="81"/>
     </row>
-    <row r="445" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" s="22" t="s">
         <v>1073</v>
       </c>
@@ -55556,7 +55556,7 @@
       <c r="AN445" s="81"/>
       <c r="AO445" s="81"/>
     </row>
-    <row r="446" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="22" t="s">
         <v>1074</v>
       </c>
@@ -55640,7 +55640,7 @@
       <c r="AN446" s="81"/>
       <c r="AO446" s="81"/>
     </row>
-    <row r="447" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" s="3" t="s">
         <v>667</v>
       </c>
@@ -55716,7 +55716,7 @@
       <c r="AN447" s="81"/>
       <c r="AO447" s="81"/>
     </row>
-    <row r="448" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" s="3" t="s">
         <v>1075</v>
       </c>
@@ -55800,7 +55800,7 @@
       <c r="AN448" s="81"/>
       <c r="AO448" s="81"/>
     </row>
-    <row r="449" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" s="3" t="s">
         <v>1076</v>
       </c>
@@ -55884,7 +55884,7 @@
       <c r="AN449" s="81"/>
       <c r="AO449" s="81"/>
     </row>
-    <row r="450" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" s="3" t="s">
         <v>1077</v>
       </c>
@@ -55968,7 +55968,7 @@
       <c r="AN450" s="81"/>
       <c r="AO450" s="81"/>
     </row>
-    <row r="451" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" s="3" t="s">
         <v>1078</v>
       </c>
@@ -56052,7 +56052,7 @@
       <c r="AN451" s="81"/>
       <c r="AO451" s="81"/>
     </row>
-    <row r="452" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" s="3" t="s">
         <v>1079</v>
       </c>
@@ -56136,7 +56136,7 @@
       <c r="AN452" s="81"/>
       <c r="AO452" s="81"/>
     </row>
-    <row r="453" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" s="3" t="s">
         <v>1080</v>
       </c>
@@ -56220,7 +56220,7 @@
       <c r="AN453" s="81"/>
       <c r="AO453" s="81"/>
     </row>
-    <row r="454" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" s="3" t="s">
         <v>1081</v>
       </c>
@@ -56304,7 +56304,7 @@
       <c r="AN454" s="81"/>
       <c r="AO454" s="81"/>
     </row>
-    <row r="455" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" s="3" t="s">
         <v>1082</v>
       </c>
@@ -56388,7 +56388,7 @@
       <c r="AN455" s="81"/>
       <c r="AO455" s="81"/>
     </row>
-    <row r="456" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" s="3" t="s">
         <v>1083</v>
       </c>
@@ -56472,7 +56472,7 @@
       <c r="AN456" s="81"/>
       <c r="AO456" s="81"/>
     </row>
-    <row r="457" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" s="3" t="s">
         <v>1085</v>
       </c>
@@ -56556,7 +56556,7 @@
       <c r="AN457" s="81"/>
       <c r="AO457" s="81"/>
     </row>
-    <row r="458" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" s="3" t="s">
         <v>1086</v>
       </c>
@@ -56640,7 +56640,7 @@
       <c r="AN458" s="81"/>
       <c r="AO458" s="81"/>
     </row>
-    <row r="459" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="3" t="s">
         <v>1087</v>
       </c>
@@ -56724,7 +56724,7 @@
       <c r="AN459" s="81"/>
       <c r="AO459" s="81"/>
     </row>
-    <row r="460" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="3" t="s">
         <v>1089</v>
       </c>
@@ -56808,7 +56808,7 @@
       <c r="AN460" s="81"/>
       <c r="AO460" s="81"/>
     </row>
-    <row r="461" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="3" t="s">
         <v>1090</v>
       </c>
@@ -56892,7 +56892,7 @@
       <c r="AN461" s="81"/>
       <c r="AO461" s="81"/>
     </row>
-    <row r="462" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="3" t="s">
         <v>1091</v>
       </c>
@@ -56976,7 +56976,7 @@
       <c r="AN462" s="81"/>
       <c r="AO462" s="81"/>
     </row>
-    <row r="463" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="3" t="s">
         <v>1092</v>
       </c>
@@ -57064,7 +57064,7 @@
       <c r="AN463" s="81"/>
       <c r="AO463" s="81"/>
     </row>
-    <row r="464" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="3" t="s">
         <v>1093</v>
       </c>
@@ -57148,7 +57148,7 @@
       <c r="AN464" s="81"/>
       <c r="AO464" s="81"/>
     </row>
-    <row r="465" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="3" t="s">
         <v>1094</v>
       </c>
@@ -57232,7 +57232,7 @@
       <c r="AN465" s="81"/>
       <c r="AO465" s="81"/>
     </row>
-    <row r="466" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="3" t="s">
         <v>1095</v>
       </c>
@@ -57316,7 +57316,7 @@
       <c r="AN466" s="81"/>
       <c r="AO466" s="81"/>
     </row>
-    <row r="467" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="3" t="s">
         <v>1097</v>
       </c>
@@ -57400,7 +57400,7 @@
       <c r="AN467" s="81"/>
       <c r="AO467" s="81"/>
     </row>
-    <row r="468" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="3" t="s">
         <v>1099</v>
       </c>
@@ -57484,7 +57484,7 @@
       <c r="AN468" s="81"/>
       <c r="AO468" s="81"/>
     </row>
-    <row r="469" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" s="3" t="s">
         <v>1101</v>
       </c>
@@ -57568,7 +57568,7 @@
       <c r="AN469" s="81"/>
       <c r="AO469" s="81"/>
     </row>
-    <row r="470" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" s="3" t="s">
         <v>1102</v>
       </c>
@@ -57652,7 +57652,7 @@
       <c r="AN470" s="81"/>
       <c r="AO470" s="81"/>
     </row>
-    <row r="471" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" s="3" t="s">
         <v>1103</v>
       </c>
@@ -57736,7 +57736,7 @@
       <c r="AN471" s="81"/>
       <c r="AO471" s="81"/>
     </row>
-    <row r="472" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="3" t="s">
         <v>1104</v>
       </c>
@@ -57820,7 +57820,7 @@
       <c r="AN472" s="81"/>
       <c r="AO472" s="81"/>
     </row>
-    <row r="473" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" s="3" t="s">
         <v>1106</v>
       </c>
@@ -57904,7 +57904,7 @@
       <c r="AN473" s="81"/>
       <c r="AO473" s="81"/>
     </row>
-    <row r="474" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" s="3" t="s">
         <v>1108</v>
       </c>
@@ -57988,7 +57988,7 @@
       <c r="AN474" s="81"/>
       <c r="AO474" s="81"/>
     </row>
-    <row r="475" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" s="3" t="s">
         <v>1110</v>
       </c>
@@ -58072,7 +58072,7 @@
       <c r="AN475" s="81"/>
       <c r="AO475" s="81"/>
     </row>
-    <row r="476" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" s="3" t="s">
         <v>1112</v>
       </c>
@@ -58156,7 +58156,7 @@
       <c r="AN476" s="81"/>
       <c r="AO476" s="81"/>
     </row>
-    <row r="477" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" s="3" t="s">
         <v>1114</v>
       </c>
@@ -58244,7 +58244,7 @@
       <c r="AN477" s="81"/>
       <c r="AO477" s="81"/>
     </row>
-    <row r="478" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" s="3" t="s">
         <v>1115</v>
       </c>
@@ -58332,7 +58332,7 @@
       <c r="AN478" s="81"/>
       <c r="AO478" s="81"/>
     </row>
-    <row r="479" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" s="3" t="s">
         <v>1116</v>
       </c>
@@ -58420,7 +58420,7 @@
       <c r="AN479" s="81"/>
       <c r="AO479" s="81"/>
     </row>
-    <row r="480" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" s="3" t="s">
         <v>1117</v>
       </c>
@@ -58504,7 +58504,7 @@
       <c r="AN480" s="81"/>
       <c r="AO480" s="81"/>
     </row>
-    <row r="481" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" s="3" t="s">
         <v>1119</v>
       </c>
@@ -58588,7 +58588,7 @@
       <c r="AN481" s="81"/>
       <c r="AO481" s="81"/>
     </row>
-    <row r="482" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" s="3" t="s">
         <v>1120</v>
       </c>
@@ -58672,7 +58672,7 @@
       <c r="AN482" s="81"/>
       <c r="AO482" s="81"/>
     </row>
-    <row r="483" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" s="3" t="s">
         <v>1121</v>
       </c>
@@ -58760,7 +58760,7 @@
       <c r="AN483" s="81"/>
       <c r="AO483" s="81"/>
     </row>
-    <row r="484" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" s="3" t="s">
         <v>1122</v>
       </c>
@@ -58848,7 +58848,7 @@
       <c r="AN484" s="81"/>
       <c r="AO484" s="81"/>
     </row>
-    <row r="485" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="3" t="s">
         <v>1123</v>
       </c>
@@ -58932,7 +58932,7 @@
       <c r="AN485" s="81"/>
       <c r="AO485" s="81"/>
     </row>
-    <row r="486" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="22" t="s">
         <v>1125</v>
       </c>
@@ -59016,7 +59016,7 @@
       <c r="AN486" s="81"/>
       <c r="AO486" s="81"/>
     </row>
-    <row r="487" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" s="22" t="s">
         <v>1126</v>
       </c>
@@ -59100,7 +59100,7 @@
       <c r="AN487" s="81"/>
       <c r="AO487" s="81"/>
     </row>
-    <row r="488" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" s="22" t="s">
         <v>1128</v>
       </c>
@@ -59184,7 +59184,7 @@
       <c r="AN488" s="81"/>
       <c r="AO488" s="81"/>
     </row>
-    <row r="489" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" s="22" t="s">
         <v>1129</v>
       </c>
@@ -59268,7 +59268,7 @@
       <c r="AN489" s="81"/>
       <c r="AO489" s="81"/>
     </row>
-    <row r="490" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="22" t="s">
         <v>1130</v>
       </c>
@@ -59352,7 +59352,7 @@
       <c r="AN490" s="81"/>
       <c r="AO490" s="81"/>
     </row>
-    <row r="491" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" s="22" t="s">
         <v>1131</v>
       </c>
@@ -59444,7 +59444,7 @@
       <c r="AN491" s="81"/>
       <c r="AO491" s="81"/>
     </row>
-    <row r="492" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" s="22" t="s">
         <v>467</v>
       </c>
@@ -59524,7 +59524,7 @@
       <c r="AN492" s="81"/>
       <c r="AO492" s="81"/>
     </row>
-    <row r="493" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" s="22" t="s">
         <v>1134</v>
       </c>
@@ -59594,7 +59594,7 @@
       <c r="AN493" s="81"/>
       <c r="AO493" s="81"/>
     </row>
-    <row r="494" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494" s="22" t="s">
         <v>1136</v>
       </c>
@@ -59664,7 +59664,7 @@
       <c r="AN494" s="81"/>
       <c r="AO494" s="81"/>
     </row>
-    <row r="495" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495" s="22" t="s">
         <v>1137</v>
       </c>
@@ -59734,7 +59734,7 @@
       <c r="AN495" s="81"/>
       <c r="AO495" s="81"/>
     </row>
-    <row r="496" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" s="22" t="s">
         <v>1138</v>
       </c>
@@ -59804,7 +59804,7 @@
       <c r="AN496" s="81"/>
       <c r="AO496" s="81"/>
     </row>
-    <row r="497" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497" s="22" t="s">
         <v>1139</v>
       </c>
@@ -59874,7 +59874,7 @@
       <c r="AN497" s="81"/>
       <c r="AO497" s="81"/>
     </row>
-    <row r="498" spans="1:41" s="26" customFormat="1" ht="20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" s="19" t="s">
         <v>1140</v>
       </c>
@@ -59989,7 +59989,7 @@
       </c>
       <c r="AO498" s="93"/>
     </row>
-    <row r="499" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" s="19" t="s">
         <v>1147</v>
       </c>
@@ -60106,7 +60106,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="500" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" s="19" t="s">
         <v>1152</v>
       </c>
@@ -60221,7 +60221,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="501" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" s="19" t="s">
         <v>1158</v>
       </c>
@@ -60338,7 +60338,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="502" spans="1:41" s="26" customFormat="1" ht="20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" s="19" t="s">
         <v>1161</v>
       </c>
@@ -60455,7 +60455,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="503" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" s="19" t="s">
         <v>1165</v>
       </c>
@@ -60572,7 +60572,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="504" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" s="19" t="s">
         <v>1169</v>
       </c>
@@ -60674,7 +60674,7 @@
       <c r="AN504" s="81"/>
       <c r="AO504" s="81"/>
     </row>
-    <row r="505" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" s="19" t="s">
         <v>1173</v>
       </c>
@@ -60791,7 +60791,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="506" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" s="19" t="s">
         <v>1177</v>
       </c>
@@ -60908,7 +60908,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="507" spans="1:41" s="26" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:41" s="26" customFormat="1" ht="30.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" s="19" t="s">
         <v>1180</v>
       </c>
@@ -61025,7 +61025,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="508" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" s="19" t="s">
         <v>1183</v>
       </c>
@@ -61130,7 +61130,7 @@
       <c r="AN508" s="81"/>
       <c r="AO508" s="81"/>
     </row>
-    <row r="509" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" s="19" t="s">
         <v>1185</v>
       </c>
@@ -61247,7 +61247,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="510" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" s="19" t="s">
         <v>1188</v>
       </c>
@@ -61355,7 +61355,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="511" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" s="19" t="s">
         <v>1190</v>
       </c>
@@ -61458,7 +61458,7 @@
       <c r="AN511" s="81"/>
       <c r="AO511" s="81"/>
     </row>
-    <row r="512" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" s="19" t="s">
         <v>1192</v>
       </c>
@@ -61573,7 +61573,7 @@
       </c>
       <c r="AO512" s="93"/>
     </row>
-    <row r="513" spans="1:41" s="26" customFormat="1" ht="20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" s="19" t="s">
         <v>1195</v>
       </c>
@@ -61688,7 +61688,7 @@
       </c>
       <c r="AO513" s="93"/>
     </row>
-    <row r="514" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" s="19" t="s">
         <v>1198</v>
       </c>
@@ -61805,7 +61805,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="515" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" s="19" t="s">
         <v>1201</v>
       </c>
@@ -61922,7 +61922,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="516" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="19" t="s">
         <v>1204</v>
       </c>
@@ -62037,7 +62037,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="517" spans="1:41" s="26" customFormat="1" ht="20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" s="19" t="s">
         <v>402</v>
       </c>
@@ -62152,7 +62152,7 @@
       </c>
       <c r="AO517" s="93"/>
     </row>
-    <row r="518" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" s="19" t="s">
         <v>1209</v>
       </c>
@@ -62236,7 +62236,7 @@
       </c>
       <c r="AO518" s="93"/>
     </row>
-    <row r="519" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519" s="19" t="s">
         <v>1210</v>
       </c>
@@ -62306,7 +62306,7 @@
       </c>
       <c r="AO519" s="93"/>
     </row>
-    <row r="520" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" s="19" t="s">
         <v>1211</v>
       </c>
@@ -62423,7 +62423,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="521" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" s="19" t="s">
         <v>1216</v>
       </c>
@@ -62536,7 +62536,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="522" spans="1:41" s="26" customFormat="1" ht="20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" s="19" t="s">
         <v>1218</v>
       </c>
@@ -62651,7 +62651,7 @@
       </c>
       <c r="AO522" s="93"/>
     </row>
-    <row r="523" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" s="19" t="s">
         <v>1221</v>
       </c>
@@ -62756,7 +62756,7 @@
       <c r="AN523" s="81"/>
       <c r="AO523" s="81"/>
     </row>
-    <row r="524" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" s="19" t="s">
         <v>1225</v>
       </c>
@@ -62871,7 +62871,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="525" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" s="19" t="s">
         <v>1229</v>
       </c>
@@ -62972,7 +62972,7 @@
       <c r="AN525" s="81"/>
       <c r="AO525" s="81"/>
     </row>
-    <row r="526" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" s="19" t="s">
         <v>1232</v>
       </c>
@@ -63089,7 +63089,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="527" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" s="19" t="s">
         <v>1235</v>
       </c>
@@ -63204,7 +63204,7 @@
       </c>
       <c r="AO527" s="93"/>
     </row>
-    <row r="528" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" s="19" t="s">
         <v>1239</v>
       </c>
@@ -63321,7 +63321,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="529" spans="1:41" s="26" customFormat="1" ht="20" hidden="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:41" s="26" customFormat="1" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="19" t="s">
         <v>1242</v>
       </c>
@@ -63439,7 +63439,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="530" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" s="19" t="s">
         <v>737</v>
       </c>
@@ -63539,7 +63539,7 @@
       <c r="AN530" s="81"/>
       <c r="AO530" s="81"/>
     </row>
-    <row r="531" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" s="19" t="s">
         <v>1245</v>
       </c>
@@ -63654,7 +63654,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="532" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" s="19" t="s">
         <v>1248</v>
       </c>
@@ -63758,7 +63758,7 @@
       <c r="AN532" s="81"/>
       <c r="AO532" s="81"/>
     </row>
-    <row r="533" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" s="19" t="s">
         <v>1250</v>
       </c>
@@ -63862,7 +63862,7 @@
       <c r="AN533" s="81"/>
       <c r="AO533" s="81"/>
     </row>
-    <row r="534" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" s="19" t="s">
         <v>1252</v>
       </c>
@@ -63979,7 +63979,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="535" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" s="19" t="s">
         <v>1256</v>
       </c>
@@ -64090,7 +64090,7 @@
       <c r="AN535" s="81"/>
       <c r="AO535" s="81"/>
     </row>
-    <row r="536" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" s="19" t="s">
         <v>1258</v>
       </c>
@@ -64194,7 +64194,7 @@
       <c r="AN536" s="81"/>
       <c r="AO536" s="81"/>
     </row>
-    <row r="537" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" s="19" t="s">
         <v>748</v>
       </c>
@@ -64309,7 +64309,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="538" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" s="19" t="s">
         <v>1262</v>
       </c>
@@ -64424,7 +64424,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="539" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" s="19" t="s">
         <v>1264</v>
       </c>
@@ -64541,7 +64541,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="540" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" s="19" t="s">
         <v>1267</v>
       </c>
@@ -64645,7 +64645,7 @@
       <c r="AN540" s="81"/>
       <c r="AO540" s="81"/>
     </row>
-    <row r="541" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" s="19" t="s">
         <v>733</v>
       </c>
@@ -64745,7 +64745,7 @@
       <c r="AN541" s="81"/>
       <c r="AO541" s="81"/>
     </row>
-    <row r="542" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" s="19" t="s">
         <v>1270</v>
       </c>
@@ -64862,7 +64862,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="543" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" s="19" t="s">
         <v>1272</v>
       </c>
@@ -64966,7 +64966,7 @@
       <c r="AN543" s="81"/>
       <c r="AO543" s="81"/>
     </row>
-    <row r="544" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" s="19" t="s">
         <v>1274</v>
       </c>
@@ -65083,7 +65083,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="545" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="19" t="s">
         <v>1277</v>
       </c>
@@ -65200,7 +65200,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="546" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="19" t="s">
         <v>1279</v>
       </c>
@@ -65317,7 +65317,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="547" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" s="19" t="s">
         <v>1281</v>
       </c>
@@ -65421,7 +65421,7 @@
       <c r="AN547" s="81"/>
       <c r="AO547" s="81"/>
     </row>
-    <row r="548" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="19" t="s">
         <v>1282</v>
       </c>
@@ -65538,7 +65538,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="549" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="19" t="s">
         <v>1285</v>
       </c>
@@ -65642,7 +65642,7 @@
       <c r="AN549" s="81"/>
       <c r="AO549" s="81"/>
     </row>
-    <row r="550" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="19" t="s">
         <v>1286</v>
       </c>
@@ -65746,7 +65746,7 @@
       <c r="AN550" s="81"/>
       <c r="AO550" s="81"/>
     </row>
-    <row r="551" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" s="19" t="s">
         <v>1288</v>
       </c>
@@ -65850,7 +65850,7 @@
       <c r="AN551" s="81"/>
       <c r="AO551" s="81"/>
     </row>
-    <row r="552" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" s="19" t="s">
         <v>752</v>
       </c>
@@ -65952,7 +65952,7 @@
       <c r="AN552" s="81"/>
       <c r="AO552" s="81"/>
     </row>
-    <row r="553" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="19" t="s">
         <v>1289</v>
       </c>
@@ -66069,7 +66069,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="554" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" s="19" t="s">
         <v>1293</v>
       </c>
@@ -66173,7 +66173,7 @@
       <c r="AN554" s="81"/>
       <c r="AO554" s="81"/>
     </row>
-    <row r="555" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" s="19" t="s">
         <v>1294</v>
       </c>
@@ -66275,7 +66275,7 @@
       <c r="AN555" s="81"/>
       <c r="AO555" s="81"/>
     </row>
-    <row r="556" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" s="19" t="s">
         <v>1295</v>
       </c>
@@ -66392,7 +66392,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="557" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="19" t="s">
         <v>1298</v>
       </c>
@@ -66496,7 +66496,7 @@
       <c r="AN557" s="81"/>
       <c r="AO557" s="81"/>
     </row>
-    <row r="558" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" s="19" t="s">
         <v>1300</v>
       </c>
@@ -66598,7 +66598,7 @@
       <c r="AN558" s="81"/>
       <c r="AO558" s="81"/>
     </row>
-    <row r="559" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" s="19" t="s">
         <v>1302</v>
       </c>
@@ -66700,7 +66700,7 @@
       <c r="AN559" s="81"/>
       <c r="AO559" s="81"/>
     </row>
-    <row r="560" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" s="19" t="s">
         <v>1304</v>
       </c>
@@ -66815,7 +66815,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="561" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" s="19" t="s">
         <v>600</v>
       </c>
@@ -66919,7 +66919,7 @@
       <c r="AN561" s="81"/>
       <c r="AO561" s="81"/>
     </row>
-    <row r="562" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" s="19" t="s">
         <v>1307</v>
       </c>
@@ -67036,7 +67036,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="563" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" s="19" t="s">
         <v>1309</v>
       </c>
@@ -67153,7 +67153,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="564" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="19" t="s">
         <v>1312</v>
       </c>
@@ -67268,7 +67268,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="565" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="19" t="s">
         <v>1315</v>
       </c>
@@ -67370,7 +67370,7 @@
       <c r="AN565" s="81"/>
       <c r="AO565" s="81"/>
     </row>
-    <row r="566" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="19" t="s">
         <v>1317</v>
       </c>
@@ -67474,7 +67474,7 @@
       <c r="AN566" s="81"/>
       <c r="AO566" s="81"/>
     </row>
-    <row r="567" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" s="32" t="s">
         <v>1319</v>
       </c>
@@ -67576,7 +67576,7 @@
       <c r="AN567" s="81"/>
       <c r="AO567" s="81"/>
     </row>
-    <row r="568" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" s="19" t="s">
         <v>1321</v>
       </c>
@@ -67680,7 +67680,7 @@
       <c r="AN568" s="81"/>
       <c r="AO568" s="81"/>
     </row>
-    <row r="569" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" s="19" t="s">
         <v>1323</v>
       </c>
@@ -67797,7 +67797,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="570" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" s="19" t="s">
         <v>1326</v>
       </c>
@@ -67899,7 +67899,7 @@
       <c r="AN570" s="81"/>
       <c r="AO570" s="81"/>
     </row>
-    <row r="571" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="19" t="s">
         <v>1328</v>
       </c>
@@ -68001,7 +68001,7 @@
       <c r="AN571" s="81"/>
       <c r="AO571" s="81"/>
     </row>
-    <row r="572" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" s="19" t="s">
         <v>1329</v>
       </c>
@@ -68103,7 +68103,7 @@
       <c r="AN572" s="81"/>
       <c r="AO572" s="81"/>
     </row>
-    <row r="573" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" s="19" t="s">
         <v>1331</v>
       </c>
@@ -68207,7 +68207,7 @@
       <c r="AN573" s="81"/>
       <c r="AO573" s="81"/>
     </row>
-    <row r="574" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="19" t="s">
         <v>1333</v>
       </c>
@@ -68311,7 +68311,7 @@
       <c r="AN574" s="81"/>
       <c r="AO574" s="81"/>
     </row>
-    <row r="575" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" s="19" t="s">
         <v>1336</v>
       </c>
@@ -68415,7 +68415,7 @@
       <c r="AN575" s="81"/>
       <c r="AO575" s="81"/>
     </row>
-    <row r="576" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" s="19" t="s">
         <v>1338</v>
       </c>
@@ -68519,7 +68519,7 @@
       <c r="AN576" s="81"/>
       <c r="AO576" s="81"/>
     </row>
-    <row r="577" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" s="19" t="s">
         <v>1340</v>
       </c>
@@ -68623,7 +68623,7 @@
       <c r="AN577" s="81"/>
       <c r="AO577" s="81"/>
     </row>
-    <row r="578" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" s="19" t="s">
         <v>1342</v>
       </c>
@@ -68725,7 +68725,7 @@
       <c r="AN578" s="81"/>
       <c r="AO578" s="81"/>
     </row>
-    <row r="579" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579" s="19" t="s">
         <v>1343</v>
       </c>
@@ -68829,7 +68829,7 @@
       <c r="AN579" s="81"/>
       <c r="AO579" s="81"/>
     </row>
-    <row r="580" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" s="19" t="s">
         <v>1345</v>
       </c>
@@ -68933,7 +68933,7 @@
       <c r="AN580" s="81"/>
       <c r="AO580" s="81"/>
     </row>
-    <row r="581" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" s="19" t="s">
         <v>1346</v>
       </c>
@@ -69037,7 +69037,7 @@
       <c r="AN581" s="81"/>
       <c r="AO581" s="81"/>
     </row>
-    <row r="582" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582" s="19" t="s">
         <v>1348</v>
       </c>
@@ -69141,7 +69141,7 @@
       <c r="AN582" s="81"/>
       <c r="AO582" s="81"/>
     </row>
-    <row r="583" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="19" t="s">
         <v>1350</v>
       </c>
@@ -69205,7 +69205,7 @@
       <c r="AN583" s="81"/>
       <c r="AO583" s="81"/>
     </row>
-    <row r="584" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="19" t="s">
         <v>1351</v>
       </c>
@@ -69309,7 +69309,7 @@
       <c r="AN584" s="81"/>
       <c r="AO584" s="81"/>
     </row>
-    <row r="585" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" s="19" t="s">
         <v>1353</v>
       </c>
@@ -69413,7 +69413,7 @@
       <c r="AN585" s="81"/>
       <c r="AO585" s="81"/>
     </row>
-    <row r="586" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" s="19" t="s">
         <v>1355</v>
       </c>
@@ -69517,7 +69517,7 @@
       <c r="AN586" s="81"/>
       <c r="AO586" s="81"/>
     </row>
-    <row r="587" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" s="19" t="s">
         <v>1357</v>
       </c>
@@ -69617,7 +69617,7 @@
       <c r="AN587" s="81"/>
       <c r="AO587" s="81"/>
     </row>
-    <row r="588" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" s="19" t="s">
         <v>313</v>
       </c>
@@ -69717,7 +69717,7 @@
       <c r="AN588" s="81"/>
       <c r="AO588" s="81"/>
     </row>
-    <row r="589" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" s="19" t="s">
         <v>1360</v>
       </c>
@@ -69821,7 +69821,7 @@
       <c r="AN589" s="81"/>
       <c r="AO589" s="81"/>
     </row>
-    <row r="590" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" s="19" t="s">
         <v>1362</v>
       </c>
@@ -69925,7 +69925,7 @@
       <c r="AN590" s="81"/>
       <c r="AO590" s="81"/>
     </row>
-    <row r="591" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591" s="22" t="s">
         <v>1364</v>
       </c>
@@ -70003,7 +70003,7 @@
       <c r="AN591" s="81"/>
       <c r="AO591" s="81"/>
     </row>
-    <row r="592" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592" s="22" t="s">
         <v>1367</v>
       </c>
@@ -70077,7 +70077,7 @@
       <c r="AN592" s="81"/>
       <c r="AO592" s="81"/>
     </row>
-    <row r="593" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" s="22" t="s">
         <v>1370</v>
       </c>
@@ -70151,7 +70151,7 @@
       <c r="AN593" s="81"/>
       <c r="AO593" s="81"/>
     </row>
-    <row r="594" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" s="22" t="s">
         <v>1371</v>
       </c>
@@ -70225,7 +70225,7 @@
       <c r="AN594" s="81"/>
       <c r="AO594" s="81"/>
     </row>
-    <row r="595" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="22" t="s">
         <v>661</v>
       </c>
@@ -70299,7 +70299,7 @@
       <c r="AN595" s="81"/>
       <c r="AO595" s="81"/>
     </row>
-    <row r="596" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="22" t="s">
         <v>1374</v>
       </c>
@@ -70373,7 +70373,7 @@
       <c r="AN596" s="81"/>
       <c r="AO596" s="81"/>
     </row>
-    <row r="597" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" s="22" t="s">
         <v>1375</v>
       </c>
@@ -70447,7 +70447,7 @@
       <c r="AN597" s="81"/>
       <c r="AO597" s="81"/>
     </row>
-    <row r="598" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" s="22" t="s">
         <v>1376</v>
       </c>
@@ -70521,7 +70521,7 @@
       <c r="AN598" s="81"/>
       <c r="AO598" s="81"/>
     </row>
-    <row r="599" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="22" t="s">
         <v>1379</v>
       </c>
@@ -70595,7 +70595,7 @@
       <c r="AN599" s="81"/>
       <c r="AO599" s="81"/>
     </row>
-    <row r="600" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" s="22" t="s">
         <v>1380</v>
       </c>
@@ -70669,7 +70669,7 @@
       <c r="AN600" s="81"/>
       <c r="AO600" s="81"/>
     </row>
-    <row r="601" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" s="22" t="s">
         <v>1382</v>
       </c>
@@ -70743,7 +70743,7 @@
       <c r="AN601" s="81"/>
       <c r="AO601" s="81"/>
     </row>
-    <row r="602" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" s="22" t="s">
         <v>879</v>
       </c>
@@ -70817,7 +70817,7 @@
       <c r="AN602" s="81"/>
       <c r="AO602" s="81"/>
     </row>
-    <row r="603" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603" s="22" t="s">
         <v>1384</v>
       </c>
@@ -70891,7 +70891,7 @@
       <c r="AN603" s="81"/>
       <c r="AO603" s="81"/>
     </row>
-    <row r="604" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604" s="22" t="s">
         <v>1385</v>
       </c>
@@ -70965,7 +70965,7 @@
       <c r="AN604" s="81"/>
       <c r="AO604" s="81"/>
     </row>
-    <row r="605" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605" s="22" t="s">
         <v>669</v>
       </c>
@@ -71039,7 +71039,7 @@
       <c r="AN605" s="81"/>
       <c r="AO605" s="81"/>
     </row>
-    <row r="606" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606" s="22" t="s">
         <v>289</v>
       </c>
@@ -71115,7 +71115,7 @@
       <c r="AN606" s="81"/>
       <c r="AO606" s="81"/>
     </row>
-    <row r="607" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607" s="22" t="s">
         <v>1388</v>
       </c>
@@ -71189,7 +71189,7 @@
       <c r="AN607" s="81"/>
       <c r="AO607" s="81"/>
     </row>
-    <row r="608" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608" s="22" t="s">
         <v>1389</v>
       </c>
@@ -71263,7 +71263,7 @@
       <c r="AN608" s="81"/>
       <c r="AO608" s="81"/>
     </row>
-    <row r="609" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609" s="22" t="s">
         <v>392</v>
       </c>
@@ -71337,7 +71337,7 @@
       <c r="AN609" s="81"/>
       <c r="AO609" s="81"/>
     </row>
-    <row r="610" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610" s="22" t="s">
         <v>384</v>
       </c>
@@ -71411,7 +71411,7 @@
       <c r="AN610" s="81"/>
       <c r="AO610" s="81"/>
     </row>
-    <row r="611" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611" s="22" t="s">
         <v>1390</v>
       </c>
@@ -71485,7 +71485,7 @@
       <c r="AN611" s="81"/>
       <c r="AO611" s="81"/>
     </row>
-    <row r="612" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612" s="22" t="s">
         <v>1391</v>
       </c>
@@ -71559,7 +71559,7 @@
       <c r="AN612" s="81"/>
       <c r="AO612" s="81"/>
     </row>
-    <row r="613" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613" s="22" t="s">
         <v>1392</v>
       </c>
@@ -71633,7 +71633,7 @@
       <c r="AN613" s="81"/>
       <c r="AO613" s="81"/>
     </row>
-    <row r="614" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614" s="22" t="s">
         <v>1394</v>
       </c>
@@ -71707,7 +71707,7 @@
       <c r="AN614" s="81"/>
       <c r="AO614" s="81"/>
     </row>
-    <row r="615" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615" s="22" t="s">
         <v>686</v>
       </c>
@@ -71781,7 +71781,7 @@
       <c r="AN615" s="81"/>
       <c r="AO615" s="81"/>
     </row>
-    <row r="616" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616" s="22" t="s">
         <v>1395</v>
       </c>
@@ -71855,7 +71855,7 @@
       <c r="AN616" s="81"/>
       <c r="AO616" s="81"/>
     </row>
-    <row r="617" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617" s="22" t="s">
         <v>1397</v>
       </c>
@@ -71929,7 +71929,7 @@
       <c r="AN617" s="81"/>
       <c r="AO617" s="81"/>
     </row>
-    <row r="618" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618" s="22" t="s">
         <v>891</v>
       </c>
@@ -72003,7 +72003,7 @@
       <c r="AN618" s="81"/>
       <c r="AO618" s="81"/>
     </row>
-    <row r="619" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619" s="22" t="s">
         <v>918</v>
       </c>
@@ -72077,7 +72077,7 @@
       <c r="AN619" s="81"/>
       <c r="AO619" s="81"/>
     </row>
-    <row r="620" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620" s="22" t="s">
         <v>888</v>
       </c>
@@ -72151,7 +72151,7 @@
       <c r="AN620" s="81"/>
       <c r="AO620" s="81"/>
     </row>
-    <row r="621" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621" s="22" t="s">
         <v>1400</v>
       </c>
@@ -72225,7 +72225,7 @@
       <c r="AN621" s="81"/>
       <c r="AO621" s="81"/>
     </row>
-    <row r="622" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622" s="22" t="s">
         <v>1401</v>
       </c>
@@ -72299,7 +72299,7 @@
       <c r="AN622" s="81"/>
       <c r="AO622" s="81"/>
     </row>
-    <row r="623" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" s="22" t="s">
         <v>870</v>
       </c>
@@ -72373,7 +72373,7 @@
       <c r="AN623" s="81"/>
       <c r="AO623" s="81"/>
     </row>
-    <row r="624" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" s="22" t="s">
         <v>1403</v>
       </c>
@@ -72447,7 +72447,7 @@
       <c r="AN624" s="81"/>
       <c r="AO624" s="81"/>
     </row>
-    <row r="625" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" s="22" t="s">
         <v>1404</v>
       </c>
@@ -72521,7 +72521,7 @@
       <c r="AN625" s="81"/>
       <c r="AO625" s="81"/>
     </row>
-    <row r="626" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626" s="22" t="s">
         <v>420</v>
       </c>
@@ -72595,7 +72595,7 @@
       <c r="AN626" s="81"/>
       <c r="AO626" s="81"/>
     </row>
-    <row r="627" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A627" s="22" t="s">
         <v>1407</v>
       </c>
@@ -72667,7 +72667,7 @@
       <c r="AN627" s="81"/>
       <c r="AO627" s="81"/>
     </row>
-    <row r="628" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628" s="22" t="s">
         <v>932</v>
       </c>
@@ -72741,7 +72741,7 @@
       <c r="AN628" s="81"/>
       <c r="AO628" s="81"/>
     </row>
-    <row r="629" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629" s="22" t="s">
         <v>1409</v>
       </c>
@@ -72815,7 +72815,7 @@
       <c r="AN629" s="81"/>
       <c r="AO629" s="81"/>
     </row>
-    <row r="630" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" s="22" t="s">
         <v>903</v>
       </c>
@@ -72889,7 +72889,7 @@
       <c r="AN630" s="81"/>
       <c r="AO630" s="81"/>
     </row>
-    <row r="631" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631" s="22" t="s">
         <v>1411</v>
       </c>
@@ -72963,7 +72963,7 @@
       <c r="AN631" s="81"/>
       <c r="AO631" s="81"/>
     </row>
-    <row r="632" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632" s="22" t="s">
         <v>1412</v>
       </c>
@@ -73037,7 +73037,7 @@
       <c r="AN632" s="81"/>
       <c r="AO632" s="81"/>
     </row>
-    <row r="633" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633" s="22" t="s">
         <v>1414</v>
       </c>
@@ -73111,7 +73111,7 @@
       <c r="AN633" s="81"/>
       <c r="AO633" s="81"/>
     </row>
-    <row r="634" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634" s="22" t="s">
         <v>1415</v>
       </c>
@@ -73185,7 +73185,7 @@
       <c r="AN634" s="81"/>
       <c r="AO634" s="81"/>
     </row>
-    <row r="635" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635" s="22" t="s">
         <v>1416</v>
       </c>
@@ -73259,7 +73259,7 @@
       <c r="AN635" s="81"/>
       <c r="AO635" s="81"/>
     </row>
-    <row r="636" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636" s="22" t="s">
         <v>1417</v>
       </c>
@@ -73333,7 +73333,7 @@
       <c r="AN636" s="81"/>
       <c r="AO636" s="81"/>
     </row>
-    <row r="637" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637" s="22" t="s">
         <v>1418</v>
       </c>
@@ -73407,7 +73407,7 @@
       <c r="AN637" s="81"/>
       <c r="AO637" s="81"/>
     </row>
-    <row r="638" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638" s="22" t="s">
         <v>1420</v>
       </c>
@@ -73481,7 +73481,7 @@
       <c r="AN638" s="81"/>
       <c r="AO638" s="81"/>
     </row>
-    <row r="639" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639" s="22" t="s">
         <v>1421</v>
       </c>
@@ -73555,7 +73555,7 @@
       <c r="AN639" s="81"/>
       <c r="AO639" s="81"/>
     </row>
-    <row r="640" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" s="22" t="s">
         <v>1422</v>
       </c>
@@ -73629,7 +73629,7 @@
       <c r="AN640" s="81"/>
       <c r="AO640" s="81"/>
     </row>
-    <row r="641" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" s="22" t="s">
         <v>909</v>
       </c>
@@ -73703,7 +73703,7 @@
       <c r="AN641" s="81"/>
       <c r="AO641" s="81"/>
     </row>
-    <row r="642" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" s="22" t="s">
         <v>978</v>
       </c>
@@ -73777,7 +73777,7 @@
       <c r="AN642" s="81"/>
       <c r="AO642" s="81"/>
     </row>
-    <row r="643" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" s="22" t="s">
         <v>1423</v>
       </c>
@@ -73851,7 +73851,7 @@
       <c r="AN643" s="81"/>
       <c r="AO643" s="81"/>
     </row>
-    <row r="644" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644" s="22" t="s">
         <v>1425</v>
       </c>
@@ -73925,7 +73925,7 @@
       <c r="AN644" s="81"/>
       <c r="AO644" s="81"/>
     </row>
-    <row r="645" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645" s="22" t="s">
         <v>885</v>
       </c>
@@ -73999,7 +73999,7 @@
       <c r="AN645" s="81"/>
       <c r="AO645" s="81"/>
     </row>
-    <row r="646" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646" s="22" t="s">
         <v>1426</v>
       </c>
@@ -74073,7 +74073,7 @@
       <c r="AN646" s="81"/>
       <c r="AO646" s="81"/>
     </row>
-    <row r="647" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647" s="22" t="s">
         <v>957</v>
       </c>
@@ -74147,7 +74147,7 @@
       <c r="AN647" s="81"/>
       <c r="AO647" s="81"/>
     </row>
-    <row r="648" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648" s="22" t="s">
         <v>1427</v>
       </c>
@@ -74221,7 +74221,7 @@
       <c r="AN648" s="81"/>
       <c r="AO648" s="81"/>
     </row>
-    <row r="649" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649" s="22" t="s">
         <v>99</v>
       </c>
@@ -74297,7 +74297,7 @@
       <c r="AN649" s="81"/>
       <c r="AO649" s="81"/>
     </row>
-    <row r="650" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650" s="22" t="s">
         <v>1430</v>
       </c>
@@ -74371,7 +74371,7 @@
       <c r="AN650" s="81"/>
       <c r="AO650" s="81"/>
     </row>
-    <row r="651" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651" s="22" t="s">
         <v>1431</v>
       </c>
@@ -74443,7 +74443,7 @@
       <c r="AN651" s="81"/>
       <c r="AO651" s="81"/>
     </row>
-    <row r="652" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A652" s="22" t="s">
         <v>664</v>
       </c>
@@ -74517,7 +74517,7 @@
       <c r="AN652" s="81"/>
       <c r="AO652" s="81"/>
     </row>
-    <row r="653" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653" s="22" t="s">
         <v>1432</v>
       </c>
@@ -74591,7 +74591,7 @@
       <c r="AN653" s="81"/>
       <c r="AO653" s="81"/>
     </row>
-    <row r="654" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654" s="22" t="s">
         <v>1434</v>
       </c>
@@ -74665,7 +74665,7 @@
       <c r="AN654" s="81"/>
       <c r="AO654" s="81"/>
     </row>
-    <row r="655" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655" s="22" t="s">
         <v>1435</v>
       </c>
@@ -74739,7 +74739,7 @@
       <c r="AN655" s="81"/>
       <c r="AO655" s="81"/>
     </row>
-    <row r="656" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A656" s="22" t="s">
         <v>1437</v>
       </c>
@@ -74813,7 +74813,7 @@
       <c r="AN656" s="81"/>
       <c r="AO656" s="81"/>
     </row>
-    <row r="657" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A657" s="22" t="s">
         <v>1438</v>
       </c>
@@ -74887,7 +74887,7 @@
       <c r="AN657" s="81"/>
       <c r="AO657" s="81"/>
     </row>
-    <row r="658" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A658" s="22" t="s">
         <v>1439</v>
       </c>
@@ -74961,7 +74961,7 @@
       <c r="AN658" s="81"/>
       <c r="AO658" s="81"/>
     </row>
-    <row r="659" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A659" s="22" t="s">
         <v>1440</v>
       </c>
@@ -75035,7 +75035,7 @@
       <c r="AN659" s="81"/>
       <c r="AO659" s="81"/>
     </row>
-    <row r="660" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660" s="22" t="s">
         <v>1441</v>
       </c>
@@ -75109,7 +75109,7 @@
       <c r="AN660" s="81"/>
       <c r="AO660" s="81"/>
     </row>
-    <row r="661" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A661" s="22" t="s">
         <v>1442</v>
       </c>
@@ -75183,7 +75183,7 @@
       <c r="AN661" s="81"/>
       <c r="AO661" s="81"/>
     </row>
-    <row r="662" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662" s="22" t="s">
         <v>1443</v>
       </c>
@@ -75257,7 +75257,7 @@
       <c r="AN662" s="81"/>
       <c r="AO662" s="81"/>
     </row>
-    <row r="663" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663" s="22" t="s">
         <v>977</v>
       </c>
@@ -75331,7 +75331,7 @@
       <c r="AN663" s="81"/>
       <c r="AO663" s="81"/>
     </row>
-    <row r="664" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664" s="22" t="s">
         <v>592</v>
       </c>
@@ -75415,7 +75415,7 @@
       <c r="AN664" s="81"/>
       <c r="AO664" s="81"/>
     </row>
-    <row r="665" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665" s="22" t="s">
         <v>1446</v>
       </c>
@@ -75489,7 +75489,7 @@
       <c r="AN665" s="81"/>
       <c r="AO665" s="81"/>
     </row>
-    <row r="666" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A666" s="22" t="s">
         <v>1448</v>
       </c>
@@ -75563,7 +75563,7 @@
       <c r="AN666" s="81"/>
       <c r="AO666" s="81"/>
     </row>
-    <row r="667" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A667" s="22" t="s">
         <v>1450</v>
       </c>
@@ -75637,7 +75637,7 @@
       <c r="AN667" s="81"/>
       <c r="AO667" s="81"/>
     </row>
-    <row r="668" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A668" s="22" t="s">
         <v>1452</v>
       </c>
@@ -75711,7 +75711,7 @@
       <c r="AN668" s="81"/>
       <c r="AO668" s="81"/>
     </row>
-    <row r="669" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A669" s="22" t="s">
         <v>1453</v>
       </c>
@@ -75785,7 +75785,7 @@
       <c r="AN669" s="81"/>
       <c r="AO669" s="81"/>
     </row>
-    <row r="670" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A670" s="22" t="s">
         <v>1454</v>
       </c>
@@ -75859,7 +75859,7 @@
       <c r="AN670" s="81"/>
       <c r="AO670" s="81"/>
     </row>
-    <row r="671" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A671" s="22" t="s">
         <v>1456</v>
       </c>
@@ -75933,7 +75933,7 @@
       <c r="AN671" s="81"/>
       <c r="AO671" s="81"/>
     </row>
-    <row r="672" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A672" s="22" t="s">
         <v>1458</v>
       </c>
@@ -76007,7 +76007,7 @@
       <c r="AN672" s="81"/>
       <c r="AO672" s="81"/>
     </row>
-    <row r="673" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A673" s="22" t="s">
         <v>1459</v>
       </c>
@@ -76081,7 +76081,7 @@
       <c r="AN673" s="81"/>
       <c r="AO673" s="81"/>
     </row>
-    <row r="674" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A674" s="22" t="s">
         <v>1460</v>
       </c>
@@ -76153,7 +76153,7 @@
       <c r="AN674" s="81"/>
       <c r="AO674" s="81"/>
     </row>
-    <row r="675" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A675" s="22" t="s">
         <v>1461</v>
       </c>
@@ -76227,7 +76227,7 @@
       <c r="AN675" s="81"/>
       <c r="AO675" s="81"/>
     </row>
-    <row r="676" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A676" s="22" t="s">
         <v>1462</v>
       </c>
@@ -76301,7 +76301,7 @@
       <c r="AN676" s="81"/>
       <c r="AO676" s="81"/>
     </row>
-    <row r="677" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A677" s="22" t="s">
         <v>1463</v>
       </c>
@@ -76375,7 +76375,7 @@
       <c r="AN677" s="81"/>
       <c r="AO677" s="81"/>
     </row>
-    <row r="678" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A678" s="22" t="s">
         <v>1464</v>
       </c>
@@ -76449,7 +76449,7 @@
       <c r="AN678" s="81"/>
       <c r="AO678" s="81"/>
     </row>
-    <row r="679" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A679" s="22" t="s">
         <v>1465</v>
       </c>
@@ -76523,7 +76523,7 @@
       <c r="AN679" s="81"/>
       <c r="AO679" s="81"/>
     </row>
-    <row r="680" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A680" s="22" t="s">
         <v>1466</v>
       </c>
@@ -76597,7 +76597,7 @@
       <c r="AN680" s="81"/>
       <c r="AO680" s="81"/>
     </row>
-    <row r="681" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A681" s="22" t="s">
         <v>881</v>
       </c>
@@ -76671,7 +76671,7 @@
       <c r="AN681" s="81"/>
       <c r="AO681" s="81"/>
     </row>
-    <row r="682" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A682" s="22" t="s">
         <v>1467</v>
       </c>
@@ -76745,7 +76745,7 @@
       <c r="AN682" s="81"/>
       <c r="AO682" s="81"/>
     </row>
-    <row r="683" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A683" s="22" t="s">
         <v>1468</v>
       </c>
@@ -76819,7 +76819,7 @@
       <c r="AN683" s="81"/>
       <c r="AO683" s="81"/>
     </row>
-    <row r="684" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A684" s="22" t="s">
         <v>1469</v>
       </c>
@@ -76893,7 +76893,7 @@
       <c r="AN684" s="81"/>
       <c r="AO684" s="81"/>
     </row>
-    <row r="685" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A685" s="22" t="s">
         <v>1470</v>
       </c>
@@ -76967,7 +76967,7 @@
       <c r="AN685" s="81"/>
       <c r="AO685" s="81"/>
     </row>
-    <row r="686" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A686" s="22" t="s">
         <v>1471</v>
       </c>
@@ -77041,7 +77041,7 @@
       <c r="AN686" s="81"/>
       <c r="AO686" s="81"/>
     </row>
-    <row r="687" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A687" s="22" t="s">
         <v>1472</v>
       </c>
@@ -77115,7 +77115,7 @@
       <c r="AN687" s="81"/>
       <c r="AO687" s="81"/>
     </row>
-    <row r="688" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A688" s="22" t="s">
         <v>1473</v>
       </c>
@@ -77189,7 +77189,7 @@
       <c r="AN688" s="81"/>
       <c r="AO688" s="81"/>
     </row>
-    <row r="689" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A689" s="22" t="s">
         <v>1474</v>
       </c>
@@ -77263,7 +77263,7 @@
       <c r="AN689" s="81"/>
       <c r="AO689" s="81"/>
     </row>
-    <row r="690" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A690" s="22" t="s">
         <v>1475</v>
       </c>
@@ -77337,7 +77337,7 @@
       <c r="AN690" s="81"/>
       <c r="AO690" s="81"/>
     </row>
-    <row r="691" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A691" s="22" t="s">
         <v>1476</v>
       </c>
@@ -77411,7 +77411,7 @@
       <c r="AN691" s="81"/>
       <c r="AO691" s="81"/>
     </row>
-    <row r="692" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A692" s="22" t="s">
         <v>1477</v>
       </c>
@@ -77485,7 +77485,7 @@
       <c r="AN692" s="81"/>
       <c r="AO692" s="81"/>
     </row>
-    <row r="693" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A693" s="22" t="s">
         <v>1478</v>
       </c>
@@ -77559,7 +77559,7 @@
       <c r="AN693" s="81"/>
       <c r="AO693" s="81"/>
     </row>
-    <row r="694" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A694" s="22" t="s">
         <v>1479</v>
       </c>
@@ -77633,7 +77633,7 @@
       <c r="AN694" s="81"/>
       <c r="AO694" s="81"/>
     </row>
-    <row r="695" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A695" s="22" t="s">
         <v>1480</v>
       </c>
@@ -77707,7 +77707,7 @@
       <c r="AN695" s="81"/>
       <c r="AO695" s="81"/>
     </row>
-    <row r="696" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A696" s="22" t="s">
         <v>1481</v>
       </c>
@@ -77781,7 +77781,7 @@
       <c r="AN696" s="81"/>
       <c r="AO696" s="81"/>
     </row>
-    <row r="697" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A697" s="22" t="s">
         <v>1092</v>
       </c>
@@ -77855,7 +77855,7 @@
       <c r="AN697" s="81"/>
       <c r="AO697" s="81"/>
     </row>
-    <row r="698" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A698" s="22" t="s">
         <v>1483</v>
       </c>
@@ -77929,7 +77929,7 @@
       <c r="AN698" s="81"/>
       <c r="AO698" s="81"/>
     </row>
-    <row r="699" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A699" s="22" t="s">
         <v>1484</v>
       </c>
@@ -78003,7 +78003,7 @@
       <c r="AN699" s="81"/>
       <c r="AO699" s="81"/>
     </row>
-    <row r="700" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A700" s="22" t="s">
         <v>1485</v>
       </c>
@@ -78077,7 +78077,7 @@
       <c r="AN700" s="81"/>
       <c r="AO700" s="81"/>
     </row>
-    <row r="701" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A701" s="22" t="s">
         <v>1486</v>
       </c>
@@ -78151,7 +78151,7 @@
       <c r="AN701" s="81"/>
       <c r="AO701" s="81"/>
     </row>
-    <row r="702" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A702" s="22" t="s">
         <v>1487</v>
       </c>
@@ -78225,7 +78225,7 @@
       <c r="AN702" s="81"/>
       <c r="AO702" s="81"/>
     </row>
-    <row r="703" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A703" s="22" t="s">
         <v>1488</v>
       </c>
@@ -78299,7 +78299,7 @@
       <c r="AN703" s="81"/>
       <c r="AO703" s="81"/>
     </row>
-    <row r="704" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A704" s="22" t="s">
         <v>1120</v>
       </c>
@@ -78373,7 +78373,7 @@
       <c r="AN704" s="81"/>
       <c r="AO704" s="81"/>
     </row>
-    <row r="705" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A705" s="22" t="s">
         <v>1489</v>
       </c>
@@ -78447,7 +78447,7 @@
       <c r="AN705" s="81"/>
       <c r="AO705" s="81"/>
     </row>
-    <row r="706" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A706" s="22" t="s">
         <v>1490</v>
       </c>
@@ -78521,7 +78521,7 @@
       <c r="AN706" s="81"/>
       <c r="AO706" s="81"/>
     </row>
-    <row r="707" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A707" s="22" t="s">
         <v>1491</v>
       </c>
@@ -78595,7 +78595,7 @@
       <c r="AN707" s="81"/>
       <c r="AO707" s="81"/>
     </row>
-    <row r="708" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A708" s="22" t="s">
         <v>1492</v>
       </c>
@@ -78669,7 +78669,7 @@
       <c r="AN708" s="81"/>
       <c r="AO708" s="81"/>
     </row>
-    <row r="709" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A709" s="22" t="s">
         <v>1493</v>
       </c>
@@ -78743,7 +78743,7 @@
       <c r="AN709" s="81"/>
       <c r="AO709" s="81"/>
     </row>
-    <row r="710" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:41" s="26" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A710" s="22" t="s">
         <v>1494</v>
       </c>
@@ -78817,7 +78817,7 @@
       <c r="AN710" s="81"/>
       <c r="AO710" s="81"/>
     </row>
-    <row r="711" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:41" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A711" s="39"/>
       <c r="B711" s="40"/>
       <c r="C711" s="40"/>
@@ -78880,14 +78880,14 @@
       <c r="AN711" s="81"/>
       <c r="AO711" s="81"/>
     </row>
-    <row r="716" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:41" x14ac:dyDescent="0.3">
       <c r="AA716" s="73"/>
       <c r="AB716" s="73"/>
       <c r="AC716" s="73"/>
       <c r="AN716" s="92"/>
       <c r="AO716" s="92"/>
     </row>
-    <row r="717" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:41" x14ac:dyDescent="0.3">
       <c r="Z717" s="73"/>
       <c r="AA717" s="73"/>
       <c r="AB717" s="73"/>
@@ -78895,15 +78895,15 @@
       <c r="AN717" s="92"/>
       <c r="AO717" s="92"/>
     </row>
-    <row r="718" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:41" x14ac:dyDescent="0.3">
       <c r="Z718" s="73"/>
       <c r="AA718" s="73"/>
       <c r="AB718" s="73"/>
     </row>
-    <row r="719" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:41" x14ac:dyDescent="0.3">
       <c r="Z719" s="73"/>
     </row>
-    <row r="720" spans="1:41" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:41" x14ac:dyDescent="0.3">
       <c r="Z720" s="73"/>
       <c r="AA720" s="73"/>
       <c r="AB720" s="73"/>
@@ -78915,9 +78915,6 @@
         <filter val="Diadema"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A279:AO497">
-      <sortCondition descending="1" ref="Y2:Y710"/>
-    </sortState>
   </autoFilter>
   <conditionalFormatting sqref="A193:A213 A4:A95 A97:A118">
     <cfRule type="duplicateValues" dxfId="4" priority="12"/>
@@ -78994,18 +78991,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D813743-8135-4F32-BACA-A0CD44F9427F}">
   <dimension ref="A1:H44"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="21.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="69" t="s">
         <v>1496</v>
       </c>
@@ -79028,7 +79025,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>769</v>
       </c>
@@ -79057,7 +79054,7 @@
         <v>67899.734166666662</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>50</v>
       </c>
@@ -79086,7 +79083,7 @@
         <v>263045.13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>155</v>
       </c>
@@ -79115,7 +79112,7 @@
         <v>108718.67750000002</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>201</v>
       </c>
@@ -79144,7 +79141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="53" t="s">
         <v>1502</v>
       </c>
@@ -79173,7 +79170,7 @@
         <v>439663.54166666663</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="69" t="s">
         <v>1503</v>
       </c>
@@ -79190,7 +79187,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
         <v>778</v>
       </c>
@@ -79211,7 +79208,7 @@
         <v>179739.03333333333</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="47" t="s">
         <v>1144</v>
       </c>
@@ -79232,7 +79229,7 @@
         <v>101921.69083333333</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="47" t="s">
         <v>766</v>
       </c>
@@ -79253,7 +79250,7 @@
         <v>33682.781666666669</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="47" t="s">
         <v>94</v>
       </c>
@@ -79274,7 +79271,7 @@
         <v>114804.44249999999</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="47" t="s">
         <v>75</v>
       </c>
@@ -79295,7 +79292,7 @@
         <v>19578.05</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="47" t="s">
         <v>46</v>
       </c>
@@ -79316,7 +79313,7 @@
         <v>18301.009999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="47" t="s">
         <v>84</v>
       </c>
@@ -79337,7 +79334,7 @@
         <v>8786.4108333333334</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="47" t="s">
         <v>1156</v>
       </c>
@@ -79358,7 +79355,7 @@
         <v>17038.2366666667</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="47" t="s">
         <v>852</v>
       </c>
@@ -79379,7 +79376,7 @@
         <v>3342.1949999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="47" t="s">
         <v>251</v>
       </c>
@@ -79400,7 +79397,7 @@
         <v>1642.21</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="47" t="s">
         <v>1172</v>
       </c>
@@ -79421,7 +79418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="47" t="s">
         <v>883</v>
       </c>
@@ -79442,7 +79439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="47" t="s">
         <v>370</v>
       </c>
@@ -79463,7 +79460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="47" t="s">
         <v>237</v>
       </c>
@@ -79484,7 +79481,7 @@
         <v>4586.75</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="47" t="s">
         <v>1373</v>
       </c>
@@ -79505,7 +79502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="47" t="s">
         <v>234</v>
       </c>
@@ -79526,7 +79523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="47" t="s">
         <v>1231</v>
       </c>
@@ -79547,7 +79544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="47" t="s">
         <v>332</v>
       </c>
@@ -79568,7 +79565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="47" t="s">
         <v>363</v>
       </c>
@@ -79589,7 +79586,7 @@
         <v>1311.99</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="47" t="s">
         <v>267</v>
       </c>
@@ -79610,7 +79607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="47" t="s">
         <v>317</v>
       </c>
@@ -79631,7 +79628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="47" t="s">
         <v>890</v>
       </c>
@@ -79652,7 +79649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="47" t="s">
         <v>1369</v>
       </c>
@@ -79673,7 +79670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="47" t="s">
         <v>908</v>
       </c>
@@ -79694,7 +79691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="47" t="s">
         <v>1378</v>
       </c>
@@ -79715,7 +79712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="47" t="s">
         <v>936</v>
       </c>
@@ -79736,7 +79733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="47" t="s">
         <v>153</v>
       </c>
@@ -79757,7 +79754,7 @@
         <v>238.71</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="47" t="s">
         <v>950</v>
       </c>
@@ -79778,7 +79775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="47" t="s">
         <v>1406</v>
       </c>
@@ -79799,7 +79796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="47" t="s">
         <v>1428</v>
       </c>
@@ -79820,7 +79817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="47"/>
       <c r="B40">
         <f>COUNTIF(Controle!L:L,Formulas!A41)</f>
@@ -79839,7 +79836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="47">
         <v>0</v>
       </c>
@@ -79860,7 +79857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="59" t="s">
         <v>1502</v>
       </c>
@@ -79881,12 +79878,12 @@
         <v>504973.51083333336</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="47"/>
       <c r="C43" s="57"/>
       <c r="D43" s="48"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="47"/>
     </row>
   </sheetData>
@@ -80121,16 +80118,16 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE495743-F761-4961-A762-7A3D120C6961}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="f5ab1930-d403-4c69-b2cd-8cc48f527d10"/>
+    <ds:schemaRef ds:uri="c06ce65c-ed18-47f4-a957-afd315448c9c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c06ce65c-ed18-47f4-a957-afd315448c9c"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="f5ab1930-d403-4c69-b2cd-8cc48f527d10"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/dados_atuais.xlsx
+++ b/data/dados_atuais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://delgadiadema.sharepoint.com/sites/GestoEstratgica/Documentos Compartilhados/Controle Master/BSW/Novo controle (Em processo)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2683" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BF31522-63C2-44F2-92E2-6243D55F93EA}"/>
+  <xr:revisionPtr revIDLastSave="2719" documentId="1_{DDE4A242-D13A-46DE-8B65-653B9F6ECEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2824D0D7-71E6-4996-A31D-C014224F42CB}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="598" xr2:uid="{3E398004-7492-4AA0-94C2-EA9B761AAA49}"/>
+    <workbookView xWindow="-20610" yWindow="1695" windowWidth="20730" windowHeight="11040" tabRatio="598" xr2:uid="{3E398004-7492-4AA0-94C2-EA9B761AAA49}"/>
   </bookViews>
   <sheets>
     <sheet name="Controle" sheetId="1" r:id="rId1"/>
@@ -7180,11 +7180,60 @@
           </c:dPt>
           <c:dLbls>
             <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.14283029505732006"/>
+                  <c:y val="-8.3333333333333329E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-CE24-4963-8ADF-5B47D2E4531B}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="8.6449915429430549E-2"/>
+                  <c:y val="-2.7777777777777856E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="0.23529411764705882"/>
+                      <c:h val="0.15645833333333331"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-CE24-4963-8ADF-5B47D2E4531B}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
               <c:idx val="2"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-9.7486321075885035E-2"/>
-                  <c:y val="-0.13476124436532735"/>
+                  <c:x val="-0.13883187548370962"/>
+                  <c:y val="5.2738681102362205E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -7211,8 +7260,8 @@
               <c:idx val="3"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="0.14373589460356051"/>
-                  <c:y val="-0.12928088076993671"/>
+                  <c:x val="-0.1231311975873341"/>
+                  <c:y val="-7.3725120297462823E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -7322,7 +7371,7 @@
                   <c:v>136436.7233333333</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>293333.73</c:v>
+                  <c:v>24444.477500000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7611,7 +7660,7 @@
                 <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>801639.24083333323</c:v>
+                  <c:v>532749.98833333328</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12758,7 +12807,7 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>566570</xdr:colOff>
+      <xdr:colOff>560220</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>35860</xdr:rowOff>
     </xdr:from>
@@ -12770,7 +12819,7 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="12" name="Gráfico 11">
+        <xdr:cNvPr id="32" name="Gráfico 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B54A52A7-FB35-49E2-8FF2-5CDCD47387D0}"/>
@@ -12949,8 +12998,40 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Resumo"/>
+      <sheetName val="Dados internos - Laser"/>
+      <sheetName val="Curva A"/>
+      <sheetName val="Planilha2"/>
+      <sheetName val="Tendência"/>
+      <sheetName val="Custo aço"/>
+      <sheetName val="MAIO"/>
+      <sheetName val="JUNHO"/>
+      <sheetName val="JULHO"/>
+      <sheetName val="AGOSTO"/>
+      <sheetName val="MB002286AB"/>
+      <sheetName val="MB002287AA"/>
+      <sheetName val="SV000122PL"/>
+      <sheetName val="SV000157LA"/>
+      <sheetName val="SV000152LA"/>
+      <sheetName val="MB002402LA"/>
+      <sheetName val="MB000311LA"/>
+      <sheetName val="MB002401LA"/>
+      <sheetName val="MB002183LQ"/>
+      <sheetName val="SV000153LA"/>
+      <sheetName val="DA000078LA_80LA"/>
+      <sheetName val="BOQ1275BA1250"/>
+      <sheetName val="BOQ1575BA1250"/>
+      <sheetName val="BOQ1225BA1250"/>
+      <sheetName val="BOQ1175AY1050"/>
+      <sheetName val="VB000221LA"/>
+      <sheetName val="VB000221LB"/>
+      <sheetName val="SV000151_156Z"/>
+      <sheetName val="MB002183LG"/>
+      <sheetName val="Listas"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -13207,7 +13288,7 @@
             <v>B</v>
           </cell>
           <cell r="B32" t="str">
-            <v>BOQ0630IH1300</v>
+            <v>BOQ0200DV1000</v>
           </cell>
         </row>
         <row r="33">
@@ -13215,7 +13296,7 @@
             <v>B</v>
           </cell>
           <cell r="B33" t="str">
-            <v>BOQ0475EJ1400</v>
+            <v>BOQ0630IH1300</v>
           </cell>
         </row>
         <row r="34">
@@ -13223,7 +13304,7 @@
             <v>B</v>
           </cell>
           <cell r="B34" t="str">
-            <v>BOQ0800ZN1300</v>
+            <v>BOQ0475EJ1400</v>
           </cell>
         </row>
         <row r="35">
@@ -13231,7 +13312,7 @@
             <v>B</v>
           </cell>
           <cell r="B35" t="str">
-            <v>BOQ0600LA1050</v>
+            <v>BOQ0800ZN1300</v>
           </cell>
         </row>
         <row r="36">
@@ -13239,7 +13320,7 @@
             <v>B</v>
           </cell>
           <cell r="B36" t="str">
-            <v>BOQ0800IH1200</v>
+            <v>BOQ0600LA1050</v>
           </cell>
         </row>
         <row r="37">
@@ -13247,7 +13328,7 @@
             <v>B</v>
           </cell>
           <cell r="B37" t="str">
-            <v>BOQ0875AS1400</v>
+            <v>BOQ0800IH1200</v>
           </cell>
         </row>
         <row r="38">
@@ -13255,7 +13336,7 @@
             <v>B</v>
           </cell>
           <cell r="B38" t="str">
-            <v>BOQ0800ZL1220</v>
+            <v>BOQ0875AS1400</v>
           </cell>
         </row>
         <row r="39">
@@ -13263,7 +13344,7 @@
             <v>B</v>
           </cell>
           <cell r="B39" t="str">
-            <v>BOQ0300JU1220</v>
+            <v>BOQ0800ZL1220</v>
           </cell>
         </row>
         <row r="40">
@@ -13271,7 +13352,7 @@
             <v>B</v>
           </cell>
           <cell r="B40" t="str">
-            <v>BOQ0630LA1220</v>
+            <v>BOQ0300JU1220</v>
           </cell>
         </row>
         <row r="41">
@@ -13279,7 +13360,7 @@
             <v>B</v>
           </cell>
           <cell r="B41" t="str">
-            <v>BOQ0300BF1200</v>
+            <v>BOQ0630LA1220</v>
           </cell>
         </row>
         <row r="42">
@@ -13287,7 +13368,7 @@
             <v>B</v>
           </cell>
           <cell r="B42" t="str">
-            <v>BOQ0800AP1200</v>
+            <v>BOQ0300BF1200</v>
           </cell>
         </row>
         <row r="43">
@@ -13295,7 +13376,7 @@
             <v>B</v>
           </cell>
           <cell r="B43" t="str">
-            <v>BOQ0350EA1200</v>
+            <v>BOQ0800AP1200</v>
           </cell>
         </row>
         <row r="44">
@@ -13303,7 +13384,7 @@
             <v>B</v>
           </cell>
           <cell r="B44" t="str">
-            <v>BOQ0300ED1200</v>
+            <v>BOQ0350EA1200</v>
           </cell>
         </row>
         <row r="45">
@@ -13311,7 +13392,7 @@
             <v>B</v>
           </cell>
           <cell r="B45" t="str">
-            <v>BOQ1075BA1250</v>
+            <v>BOQ0300ED1200</v>
           </cell>
         </row>
         <row r="46">
@@ -13319,7 +13400,7 @@
             <v>B</v>
           </cell>
           <cell r="B46" t="str">
-            <v>BOQ0300LN1200</v>
+            <v>BOQ1075BA1250</v>
           </cell>
         </row>
         <row r="47">
@@ -13327,7 +13408,7 @@
             <v>B</v>
           </cell>
           <cell r="B47" t="str">
-            <v>BOQ0200EJ1200</v>
+            <v>BOQ0300LN1200</v>
           </cell>
         </row>
         <row r="48">
@@ -13335,7 +13416,7 @@
             <v>B</v>
           </cell>
           <cell r="B48" t="str">
-            <v>BOQ0300DX1200</v>
+            <v>BOQ0200EJ1200</v>
           </cell>
         </row>
         <row r="49">
@@ -13343,7 +13424,7 @@
             <v>B</v>
           </cell>
           <cell r="B49" t="str">
-            <v>CHQ1600EB12002000</v>
+            <v>BOQ0300DX1200</v>
           </cell>
         </row>
         <row r="50">
@@ -13351,7 +13432,7 @@
             <v>B</v>
           </cell>
           <cell r="B50" t="str">
-            <v>BOQ0300EB1150</v>
+            <v>CHQ1600EB12002000</v>
           </cell>
         </row>
         <row r="51">
@@ -13359,7 +13440,7 @@
             <v>B</v>
           </cell>
           <cell r="B51" t="str">
-            <v>BOQ1200AT1100</v>
+            <v>BOQ0300EB1150</v>
           </cell>
         </row>
         <row r="52">
@@ -13367,7 +13448,7 @@
             <v>B</v>
           </cell>
           <cell r="B52" t="str">
-            <v>BOQ0400EJ1350</v>
+            <v>BOQ1200AT1100</v>
           </cell>
         </row>
         <row r="53">
@@ -13375,7 +13456,7 @@
             <v>B</v>
           </cell>
           <cell r="B53" t="str">
-            <v>BOQ0400ED1200</v>
+            <v>BOQ0400EJ1350</v>
           </cell>
         </row>
         <row r="54">
@@ -13383,7 +13464,7 @@
             <v>B</v>
           </cell>
           <cell r="B54" t="str">
-            <v>BOQ0950AT1200</v>
+            <v>BOQ0400ED1200</v>
           </cell>
         </row>
         <row r="55">
@@ -13391,7 +13472,7 @@
             <v>B</v>
           </cell>
           <cell r="B55" t="str">
-            <v>BOF0150AK1030</v>
+            <v>BOQ0950AT1200</v>
           </cell>
         </row>
         <row r="56">
@@ -13399,7 +13480,7 @@
             <v>B</v>
           </cell>
           <cell r="B56" t="str">
-            <v>CHQ0300AO12003000</v>
+            <v>BOF0150AK1030</v>
           </cell>
         </row>
         <row r="57">
@@ -13407,7 +13488,7 @@
             <v>B</v>
           </cell>
           <cell r="B57" t="str">
-            <v>CHQ0300EA11502550</v>
+            <v>CHQ0300AO12003000</v>
           </cell>
         </row>
         <row r="58">
@@ -13415,7 +13496,7 @@
             <v>B</v>
           </cell>
           <cell r="B58" t="str">
-            <v>BOQ0600AV1200</v>
+            <v>CHQ0300EA11502550</v>
           </cell>
         </row>
         <row r="59">
@@ -13423,7 +13504,7 @@
             <v>B</v>
           </cell>
           <cell r="B59" t="str">
-            <v>BOF0150AK1200</v>
+            <v>BOQ0600AV1200</v>
           </cell>
         </row>
         <row r="60">
@@ -13431,7 +13512,7 @@
             <v>B</v>
           </cell>
           <cell r="B60" t="str">
-            <v>BOQ0800JW1200</v>
+            <v>BOF0150AK1200</v>
           </cell>
         </row>
         <row r="61">
@@ -13439,7 +13520,7 @@
             <v>B</v>
           </cell>
           <cell r="B61" t="str">
-            <v>BOQ0950AS1200</v>
+            <v>BOQ0800JW1200</v>
           </cell>
         </row>
         <row r="62">
@@ -13447,7 +13528,7 @@
             <v>B</v>
           </cell>
           <cell r="B62" t="str">
-            <v>CHQ0600AP12002000</v>
+            <v>BOQ0950AS1200</v>
           </cell>
         </row>
         <row r="63">
@@ -13455,7 +13536,7 @@
             <v>B</v>
           </cell>
           <cell r="B63" t="str">
-            <v>CHQ0400AO12503000</v>
+            <v>CHQ0600AP12002000</v>
           </cell>
         </row>
         <row r="64">
@@ -13463,7 +13544,7 @@
             <v>B</v>
           </cell>
           <cell r="B64" t="str">
-            <v>CHQ0400EA12002000</v>
+            <v>CHQ0400AO12503000</v>
           </cell>
         </row>
         <row r="65">
@@ -13471,7 +13552,7 @@
             <v>B</v>
           </cell>
           <cell r="B65" t="str">
-            <v>CHQ0300EE10001600</v>
+            <v>CHQ0400EA12002000</v>
           </cell>
         </row>
         <row r="66">
@@ -13479,7 +13560,7 @@
             <v>B</v>
           </cell>
           <cell r="B66" t="str">
-            <v>CHQ0400EE12002100</v>
+            <v>CHQ0300EE10001600</v>
           </cell>
         </row>
         <row r="67">
@@ -13487,7 +13568,7 @@
             <v>B</v>
           </cell>
           <cell r="B67" t="str">
-            <v>BOQ0600LN1400</v>
+            <v>CHQ0400EE12002100</v>
           </cell>
         </row>
         <row r="68">
@@ -13495,7 +13576,7 @@
             <v>B</v>
           </cell>
           <cell r="B68" t="str">
-            <v>CHQ0700AO12002360</v>
+            <v>BOQ0600LN1400</v>
           </cell>
         </row>
         <row r="69">
@@ -13503,7 +13584,7 @@
             <v>B</v>
           </cell>
           <cell r="B69" t="str">
-            <v>CHQ0300EG12002000</v>
+            <v>CHQ0700AO12002360</v>
           </cell>
         </row>
         <row r="70">
@@ -13511,15 +13592,15 @@
             <v>B</v>
           </cell>
           <cell r="B70" t="str">
-            <v>CHQ0400DT11501500</v>
+            <v>CHQ0300EG12002000</v>
           </cell>
         </row>
         <row r="71">
           <cell r="A71" t="str">
-            <v>C</v>
+            <v>B</v>
           </cell>
           <cell r="B71" t="str">
-            <v>CHQ0475DZ12502880</v>
+            <v>CHQ0400DT11501500</v>
           </cell>
         </row>
         <row r="72">
@@ -13527,7 +13608,7 @@
             <v>C</v>
           </cell>
           <cell r="B72" t="str">
-            <v>CHQ0950AO12502890</v>
+            <v>CHQ0475DZ12502880</v>
           </cell>
         </row>
         <row r="73">
@@ -13535,7 +13616,7 @@
             <v>C</v>
           </cell>
           <cell r="B73" t="str">
-            <v>CHQ0300EA11502450</v>
+            <v>CHQ0950AO12502890</v>
           </cell>
         </row>
         <row r="74">
@@ -13543,7 +13624,7 @@
             <v>C</v>
           </cell>
           <cell r="B74" t="str">
-            <v>CHQ0475AP12002000</v>
+            <v>CHQ0300EA11502450</v>
           </cell>
         </row>
         <row r="75">
@@ -13551,7 +13632,7 @@
             <v>C</v>
           </cell>
           <cell r="B75" t="str">
-            <v>BOQ0400EG1200</v>
+            <v>CHQ0475AP12002000</v>
           </cell>
         </row>
         <row r="76">
@@ -13559,7 +13640,7 @@
             <v>C</v>
           </cell>
           <cell r="B76" t="str">
-            <v>BOQ0200LN1200</v>
+            <v>BOQ0400EG1200</v>
           </cell>
         </row>
         <row r="77">
@@ -13567,7 +13648,7 @@
             <v>C</v>
           </cell>
           <cell r="B77" t="str">
-            <v>CHF0190AL12001030</v>
+            <v>BOQ0200LN1200</v>
           </cell>
         </row>
         <row r="78">
@@ -13575,7 +13656,7 @@
             <v>C</v>
           </cell>
           <cell r="B78" t="str">
-            <v>CHQ0200AO11502840</v>
+            <v>CHF0190AL12001030</v>
           </cell>
         </row>
         <row r="79">
@@ -13583,7 +13664,7 @@
             <v>C</v>
           </cell>
           <cell r="B79" t="str">
-            <v>BOQ0800AT1300</v>
+            <v>CHQ0200AO11502840</v>
           </cell>
         </row>
         <row r="80">
@@ -13591,7 +13672,7 @@
             <v>C</v>
           </cell>
           <cell r="B80" t="str">
-            <v>BOQ0200ED1200</v>
+            <v>BOQ0800AT1300</v>
           </cell>
         </row>
         <row r="81">
@@ -13599,7 +13680,7 @@
             <v>C</v>
           </cell>
           <cell r="B81" t="str">
-            <v>BLD0150DP04901150</v>
+            <v>BOQ0200ED1200</v>
           </cell>
         </row>
         <row r="82">
@@ -13607,7 +13688,7 @@
             <v>C</v>
           </cell>
           <cell r="B82" t="str">
-            <v>CHQ0475AV12002000</v>
+            <v>BLD0150DP04901150</v>
           </cell>
         </row>
         <row r="83">
@@ -13615,7 +13696,7 @@
             <v>C</v>
           </cell>
           <cell r="B83" t="str">
-            <v>CHQ1250AS12002900</v>
+            <v>CHQ0475AV12002000</v>
           </cell>
         </row>
         <row r="84">
@@ -13623,7 +13704,7 @@
             <v>C</v>
           </cell>
           <cell r="B84" t="str">
-            <v>BOQ0950DM1200</v>
+            <v>CHQ1250AS12002900</v>
           </cell>
         </row>
         <row r="85">
@@ -13631,7 +13712,7 @@
             <v>C</v>
           </cell>
           <cell r="B85" t="str">
-            <v>BLD0150DP04901230</v>
+            <v>BOQ0950DM1200</v>
           </cell>
         </row>
         <row r="86">
@@ -13639,7 +13720,7 @@
             <v>C</v>
           </cell>
           <cell r="B86" t="str">
-            <v>BOQ1100AY1050</v>
+            <v>BLD0150DP04901230</v>
           </cell>
         </row>
         <row r="87">
@@ -13647,7 +13728,7 @@
             <v>C</v>
           </cell>
           <cell r="B87" t="str">
-            <v>CHQ0250AO12002000</v>
+            <v>BOQ1100AY1050</v>
           </cell>
         </row>
         <row r="88">
@@ -13655,7 +13736,7 @@
             <v>C</v>
           </cell>
           <cell r="B88" t="str">
-            <v>BOZ0150CV1200</v>
+            <v>CHQ0250AO12002000</v>
           </cell>
         </row>
         <row r="89">
@@ -13663,7 +13744,7 @@
             <v>C</v>
           </cell>
           <cell r="B89" t="str">
-            <v>CHQ0600AV12002000</v>
+            <v>BOZ0150CV1200</v>
           </cell>
         </row>
         <row r="90">
@@ -13671,7 +13752,7 @@
             <v>C</v>
           </cell>
           <cell r="B90" t="str">
-            <v>CHQ0700AS10002000</v>
+            <v>CHQ0600AV12002000</v>
           </cell>
         </row>
         <row r="91">
@@ -13679,7 +13760,7 @@
             <v>C</v>
           </cell>
           <cell r="B91" t="str">
-            <v>CHQ0200EH12002000</v>
+            <v>CHQ0700AS10002000</v>
           </cell>
         </row>
         <row r="92">
@@ -13687,7 +13768,7 @@
             <v>C</v>
           </cell>
           <cell r="B92" t="str">
-            <v>CHQ0700AQ12002000</v>
+            <v>CHQ0200EH12002000</v>
           </cell>
         </row>
         <row r="93">
@@ -13695,7 +13776,7 @@
             <v>C</v>
           </cell>
           <cell r="B93" t="str">
-            <v>CHF0200AH12002000</v>
+            <v>CHQ0700AQ12002000</v>
           </cell>
         </row>
         <row r="94">
@@ -13703,7 +13784,7 @@
             <v>C</v>
           </cell>
           <cell r="B94" t="str">
-            <v>BOQ0200AT1100</v>
+            <v>CHF0200AH12002000</v>
           </cell>
         </row>
         <row r="95">
@@ -13711,7 +13792,7 @@
             <v>C</v>
           </cell>
           <cell r="B95" t="str">
-            <v>BOQ0600DW1200</v>
+            <v>BOQ0200AT1100</v>
           </cell>
         </row>
         <row r="96">
@@ -13719,7 +13800,7 @@
             <v>C</v>
           </cell>
           <cell r="B96" t="str">
-            <v>BOQ0600KX1220</v>
+            <v>BOQ0600DW1200</v>
           </cell>
         </row>
         <row r="97">
@@ -13727,7 +13808,7 @@
             <v>C</v>
           </cell>
           <cell r="B97" t="str">
-            <v>BOQ0265DX1200</v>
+            <v>BOQ0600KX1220</v>
           </cell>
         </row>
         <row r="98">
@@ -13735,7 +13816,7 @@
             <v>C</v>
           </cell>
           <cell r="B98" t="str">
-            <v>CHQ0400EJ13501850</v>
+            <v>BOQ0265DX1200</v>
           </cell>
         </row>
         <row r="99">
@@ -13743,7 +13824,7 @@
             <v>C</v>
           </cell>
           <cell r="B99" t="str">
-            <v>CHQ0400EE12002000</v>
+            <v>CHQ0400EJ13501850</v>
           </cell>
         </row>
         <row r="100">
@@ -13751,7 +13832,7 @@
             <v>C</v>
           </cell>
           <cell r="B100" t="str">
-            <v>BOQ0775LN1100</v>
+            <v>CHQ0400EE12002000</v>
           </cell>
         </row>
         <row r="101">
@@ -13759,7 +13840,7 @@
             <v>C</v>
           </cell>
           <cell r="B101" t="str">
-            <v>CHQ0200EG10501600</v>
+            <v>BOQ0775LN1100</v>
           </cell>
         </row>
         <row r="102">
@@ -13767,7 +13848,7 @@
             <v>C</v>
           </cell>
           <cell r="B102" t="str">
-            <v>CHQ0600BF12002000</v>
+            <v>CHQ0200EG10501600</v>
           </cell>
         </row>
         <row r="103">
@@ -13775,7 +13856,7 @@
             <v>C</v>
           </cell>
           <cell r="B103" t="str">
-            <v>BLD0150DP07552060</v>
+            <v>CHQ0600BF12002000</v>
           </cell>
         </row>
         <row r="104">
@@ -13783,7 +13864,7 @@
             <v>C</v>
           </cell>
           <cell r="B104" t="str">
-            <v>CHF0106AH08001520</v>
+            <v>BLD0150DP07552060</v>
           </cell>
         </row>
         <row r="105">
@@ -13791,7 +13872,7 @@
             <v>C</v>
           </cell>
           <cell r="B105" t="str">
-            <v>BOF0170DH1200</v>
+            <v>CHF0106AH08001520</v>
           </cell>
         </row>
         <row r="106">
@@ -13799,7 +13880,7 @@
             <v>C</v>
           </cell>
           <cell r="B106" t="str">
-            <v>CHQ0500BF12002250</v>
+            <v>BOF0170DH1200</v>
           </cell>
         </row>
         <row r="107">
@@ -13807,7 +13888,7 @@
             <v>C</v>
           </cell>
           <cell r="B107" t="str">
-            <v>BOQ0475SJ1230</v>
+            <v>CHQ0500BF12002250</v>
           </cell>
         </row>
         <row r="108">
@@ -13815,7 +13896,7 @@
             <v>C</v>
           </cell>
           <cell r="B108" t="str">
-            <v>BLD0150DP04902000</v>
+            <v>BOQ0475SJ1230</v>
           </cell>
         </row>
         <row r="109">
@@ -13823,7 +13904,7 @@
             <v>C</v>
           </cell>
           <cell r="B109" t="str">
-            <v>CHQ0600DV12002000</v>
+            <v>BLD0150DP04902000</v>
           </cell>
         </row>
         <row r="110">
@@ -13831,7 +13912,7 @@
             <v>C</v>
           </cell>
           <cell r="B110" t="str">
-            <v>BOF0170AK1030</v>
+            <v>CHQ0600DV12002000</v>
           </cell>
         </row>
         <row r="111">
@@ -13839,7 +13920,7 @@
             <v>C</v>
           </cell>
           <cell r="B111" t="str">
-            <v>CHQ0425DX12002500</v>
+            <v>BOF0170AK1030</v>
           </cell>
         </row>
         <row r="112">
@@ -13847,7 +13928,7 @@
             <v>C</v>
           </cell>
           <cell r="B112" t="str">
-            <v>CHQ0425EA12002000</v>
+            <v>CHQ0425DX12002500</v>
           </cell>
         </row>
         <row r="113">
@@ -13855,7 +13936,7 @@
             <v>C</v>
           </cell>
           <cell r="B113" t="str">
-            <v>CHQ0300EJ12201400</v>
+            <v>CHQ0425EA12002000</v>
           </cell>
         </row>
         <row r="114">
@@ -13863,7 +13944,7 @@
             <v>C</v>
           </cell>
           <cell r="B114" t="str">
-            <v>CHQ0200DV12002000</v>
+            <v>CHQ0300EJ12201400</v>
           </cell>
         </row>
         <row r="115">
@@ -13871,7 +13952,7 @@
             <v>C</v>
           </cell>
           <cell r="B115" t="str">
-            <v>CHF0150BS12002000</v>
+            <v>CHQ0200DV12002000</v>
           </cell>
         </row>
         <row r="116">
@@ -13879,7 +13960,7 @@
             <v>C</v>
           </cell>
           <cell r="B116" t="str">
-            <v>BOQ0475EE1250</v>
+            <v>CHF0150BS12002000</v>
           </cell>
         </row>
         <row r="117">
@@ -13887,7 +13968,7 @@
             <v>C</v>
           </cell>
           <cell r="B117" t="str">
-            <v>BOQ1175AY1000</v>
+            <v>BOQ0475EE1250</v>
           </cell>
         </row>
         <row r="118">
@@ -13895,7 +13976,7 @@
             <v>C</v>
           </cell>
           <cell r="B118" t="str">
-            <v>CHQ1175AY10006900</v>
+            <v>BOQ1175AY1000</v>
           </cell>
         </row>
         <row r="119">
@@ -13903,7 +13984,7 @@
             <v>C</v>
           </cell>
           <cell r="B119" t="str">
-            <v>BOQ0300BF1100</v>
+            <v>CHQ1175AY10006900</v>
           </cell>
         </row>
         <row r="120">
@@ -13911,7 +13992,7 @@
             <v>C</v>
           </cell>
           <cell r="B120" t="str">
-            <v>BOZ0150CD1000</v>
+            <v>BOQ0300BF1100</v>
           </cell>
         </row>
         <row r="121">
@@ -13919,7 +14000,7 @@
             <v>C</v>
           </cell>
           <cell r="B121" t="str">
-            <v>BOQ0475EJ1450</v>
+            <v>BOZ0150CD1000</v>
           </cell>
         </row>
         <row r="122">
@@ -13927,7 +14008,7 @@
             <v>C</v>
           </cell>
           <cell r="B122" t="str">
-            <v>CHQ0200EJ12001950</v>
+            <v>BOQ0475EJ1450</v>
           </cell>
         </row>
         <row r="123">
@@ -13935,7 +14016,7 @@
             <v>C</v>
           </cell>
           <cell r="B123" t="str">
-            <v>CHF0150BC11002000</v>
+            <v>CHQ0200EJ12001950</v>
           </cell>
         </row>
         <row r="124">
@@ -13943,7 +14024,7 @@
             <v>C</v>
           </cell>
           <cell r="B124" t="str">
-            <v>BOQ1000EE1300</v>
+            <v>CHF0150BC11002000</v>
           </cell>
         </row>
         <row r="125">
@@ -13951,7 +14032,7 @@
             <v>C</v>
           </cell>
           <cell r="B125" t="str">
-            <v>CHQ0300BF12002900</v>
+            <v>BOQ1000EE1300</v>
           </cell>
         </row>
         <row r="126">
@@ -13959,7 +14040,7 @@
             <v>C</v>
           </cell>
           <cell r="B126" t="str">
-            <v>CHQ0265AP12002000</v>
+            <v>CHQ0300BF12002900</v>
           </cell>
         </row>
         <row r="127">
@@ -13967,7 +14048,7 @@
             <v>C</v>
           </cell>
           <cell r="B127" t="str">
-            <v>CHF0120AH12002000</v>
+            <v>CHQ0265AP12002000</v>
           </cell>
         </row>
         <row r="128">
@@ -13975,7 +14056,7 @@
             <v>C</v>
           </cell>
           <cell r="B128" t="str">
-            <v>CHF0106AH10001520</v>
+            <v>CHF0120AH12002000</v>
           </cell>
         </row>
         <row r="129">
@@ -13983,7 +14064,7 @@
             <v>C</v>
           </cell>
           <cell r="B129" t="str">
-            <v>BOF0120HJ1150</v>
+            <v>CHF0106AH10001520</v>
           </cell>
         </row>
         <row r="130">
@@ -13991,7 +14072,7 @@
             <v>C</v>
           </cell>
           <cell r="B130" t="str">
-            <v>CHF0090FH12002000</v>
+            <v>BOF0120HJ1150</v>
           </cell>
         </row>
         <row r="131">
@@ -13999,7 +14080,7 @@
             <v>C</v>
           </cell>
           <cell r="B131" t="str">
-            <v>BOQ0475EE1300</v>
+            <v>CHF0090FH12002000</v>
           </cell>
         </row>
         <row r="132">
@@ -14007,7 +14088,7 @@
             <v>C</v>
           </cell>
           <cell r="B132" t="str">
-            <v>CHQ2000BF12506000</v>
+            <v>BOQ0475EE1300</v>
           </cell>
         </row>
         <row r="133">
@@ -14015,7 +14096,7 @@
             <v>C</v>
           </cell>
           <cell r="B133" t="str">
-            <v>CHQ0400BT12001000</v>
+            <v>CHQ2000BF12506000</v>
           </cell>
         </row>
         <row r="134">
@@ -14023,7 +14104,7 @@
             <v>C</v>
           </cell>
           <cell r="B134" t="str">
-            <v>BOQ0300BF1500</v>
+            <v>CHQ0400BT12001000</v>
           </cell>
         </row>
         <row r="135">
@@ -14031,7 +14112,7 @@
             <v>C</v>
           </cell>
           <cell r="B135" t="str">
-            <v>CHF0100BC12002000</v>
+            <v>BOQ0300BF1500</v>
           </cell>
         </row>
         <row r="136">
@@ -14039,7 +14120,7 @@
             <v>C</v>
           </cell>
           <cell r="B136" t="str">
-            <v>CHF0190AM11001660</v>
+            <v>CHF0100BC12002000</v>
           </cell>
         </row>
         <row r="137">
@@ -14047,7 +14128,7 @@
             <v>C</v>
           </cell>
           <cell r="B137" t="str">
-            <v>BOQ0400EB1250</v>
+            <v>CHF0190AM11001660</v>
           </cell>
         </row>
         <row r="138">
@@ -14055,7 +14136,7 @@
             <v>C</v>
           </cell>
           <cell r="B138" t="str">
-            <v>CHQ0300EA10002000</v>
+            <v>BOQ0400EB1250</v>
           </cell>
         </row>
         <row r="139">
@@ -14063,21 +14144,54 @@
             <v>C</v>
           </cell>
           <cell r="B139" t="str">
-            <v>CHQ0300BF12002000</v>
+            <v>CHQ0300EA10002000</v>
           </cell>
         </row>
         <row r="140">
           <cell r="A140" t="str">
-            <v>B</v>
+            <v>C</v>
           </cell>
           <cell r="B140" t="str">
-            <v>BOQ0200DV1000</v>
+            <v>CHQ0300BF12002000</v>
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+      <sheetData sheetId="29"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
+<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14424,50 +14538,50 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/sprea